--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G43" t="n">

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI43"/>
+  <dimension ref="A1:BI46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6658,12 +6658,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6846,7 +6846,7 @@
         <v>0</v>
       </c>
       <c r="BI32" s="3" t="n">
-        <v>46147.60416666666</v>
+        <v>46147.58333333334</v>
       </c>
     </row>
     <row r="33">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7043,7 +7043,7 @@
         <v>0</v>
       </c>
       <c r="BI33" s="3" t="n">
-        <v>46147.60416666666</v>
+        <v>46147.58333333334</v>
       </c>
     </row>
     <row r="34">
@@ -7052,12 +7052,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7240,7 +7240,7 @@
         <v>0</v>
       </c>
       <c r="BI34" s="3" t="n">
-        <v>46147.60416666666</v>
+        <v>46147.58333333334</v>
       </c>
     </row>
     <row r="35">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7634,7 +7634,7 @@
         <v>0</v>
       </c>
       <c r="BI36" s="3" t="n">
-        <v>46147.625</v>
+        <v>46147.60416666666</v>
       </c>
     </row>
     <row r="37">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7831,7 +7831,7 @@
         <v>0</v>
       </c>
       <c r="BI37" s="3" t="n">
-        <v>46147.66666666666</v>
+        <v>46147.60416666666</v>
       </c>
     </row>
     <row r="38">
@@ -7840,27 +7840,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8028,7 +8028,7 @@
         <v>0</v>
       </c>
       <c r="BI38" s="3" t="n">
-        <v>46147.83333333334</v>
+        <v>46147.60416666666</v>
       </c>
     </row>
     <row r="39">
@@ -8037,12 +8037,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8225,7 +8225,7 @@
         <v>0</v>
       </c>
       <c r="BI39" s="3" t="n">
-        <v>46147.875</v>
+        <v>46147.625</v>
       </c>
     </row>
     <row r="40">
@@ -8234,12 +8234,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8422,7 +8422,7 @@
         <v>0</v>
       </c>
       <c r="BI40" s="3" t="n">
-        <v>46147.875</v>
+        <v>46147.66666666666</v>
       </c>
     </row>
     <row r="41">
@@ -8431,27 +8431,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8619,7 +8619,7 @@
         <v>0</v>
       </c>
       <c r="BI41" s="3" t="n">
-        <v>46147.875</v>
+        <v>46147.83333333334</v>
       </c>
     </row>
     <row r="42">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9013,6 +9013,597 @@
         <v>0</v>
       </c>
       <c r="BI43" s="3" t="n">
+        <v>46147.875</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Dubočica</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>FAP</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI44" s="3" t="n">
+        <v>46147.875</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Dinamo Jug</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Stepojevac Vaga</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N45" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI45" s="3" t="n">
+        <v>46147.875</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Kabel Novi Sad</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Trajal Krusevac</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI46" s="3" t="n">
         <v>46147.875</v>
       </c>
     </row>

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G46" t="n">

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4195,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G44" t="n">

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>6.29</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G46" t="n">

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>6.29</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>6.29</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G46" t="n">

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.95</v>
+        <v>2.83</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="R32" t="n">
-        <v>3.79</v>
+        <v>2.32</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G46" t="n">

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>6.29</v>
+        <v>3.63</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.48</v>
+        <v>3.02</v>
       </c>
       <c r="R37" t="n">
-        <v>1.53</v>
+        <v>2.03</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.06</v>
+        <v>6.29</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.8</v>
+        <v>3.48</v>
       </c>
       <c r="R38" t="n">
-        <v>3.89</v>
+        <v>1.53</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G46" t="n">

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.95</v>
+        <v>2.83</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="R31" t="n">
-        <v>3.79</v>
+        <v>2.32</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.06</v>
+        <v>3.63</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.8</v>
+        <v>3.02</v>
       </c>
       <c r="R35" t="n">
-        <v>3.89</v>
+        <v>2.03</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>6.29</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>6.29</v>
+        <v>2.06</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.48</v>
+        <v>2.8</v>
       </c>
       <c r="R38" t="n">
-        <v>1.53</v>
+        <v>3.89</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G46" t="n">

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G46" t="n">

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.83</v>
+        <v>1.95</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="R34" t="n">
-        <v>2.32</v>
+        <v>3.79</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>6.29</v>
+        <v>2.06</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.48</v>
+        <v>2.8</v>
       </c>
       <c r="R36" t="n">
-        <v>1.53</v>
+        <v>3.89</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.06</v>
+        <v>6.29</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.8</v>
+        <v>3.48</v>
       </c>
       <c r="R38" t="n">
-        <v>3.89</v>
+        <v>1.53</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G46" t="n">

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.83</v>
+        <v>1.95</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="R31" t="n">
-        <v>2.32</v>
+        <v>3.79</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.06</v>
+        <v>6.29</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.8</v>
+        <v>3.48</v>
       </c>
       <c r="R36" t="n">
-        <v>3.89</v>
+        <v>1.53</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>6.29</v>
+        <v>2.06</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.48</v>
+        <v>2.8</v>
       </c>
       <c r="R38" t="n">
-        <v>1.53</v>
+        <v>3.89</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G46" t="n">

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI46"/>
+  <dimension ref="A1:BI42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.83</v>
+        <v>1.95</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="R32" t="n">
-        <v>2.32</v>
+        <v>3.79</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>3.63</v>
+        <v>2.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.02</v>
+        <v>2.8</v>
       </c>
       <c r="R35" t="n">
-        <v>2.03</v>
+        <v>3.4</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.2</v>
+        <v>3.63</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.8</v>
+        <v>3.02</v>
       </c>
       <c r="R37" t="n">
-        <v>3.4</v>
+        <v>2.03</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8816,794 +8816,6 @@
         <v>0</v>
       </c>
       <c r="BI42" s="3" t="n">
-        <v>46147.875</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="n">
-        <v>46147</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Dinamo Jug</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Stepojevac Vaga</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N43" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI43" s="3" t="n">
-        <v>46147.875</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="n">
-        <v>46147</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Tekstilac Odžaci</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Semendrija 1924</t>
-        </is>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N44" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" t="n">
-        <v>0</v>
-      </c>
-      <c r="W44" t="n">
-        <v>0</v>
-      </c>
-      <c r="X44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ44" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA44" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB44" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC44" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD44" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE44" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF44" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG44" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH44" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI44" s="3" t="n">
-        <v>46147.875</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="n">
-        <v>46147</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Kabel Novi Sad</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Trajal Krusevac</t>
-        </is>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N45" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0</v>
-      </c>
-      <c r="W45" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI45" s="3" t="n">
-        <v>46147.875</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
-        <v>46147</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Borac Čačak</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Grafičar</t>
-        </is>
-      </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N46" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI46" s="3" t="n">
         <v>46147.875</v>
       </c>
     </row>

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.2</v>
+        <v>3.63</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.8</v>
+        <v>3.02</v>
       </c>
       <c r="R35" t="n">
-        <v>3.4</v>
+        <v>2.03</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>3.63</v>
+        <v>2.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.02</v>
+        <v>2.8</v>
       </c>
       <c r="R37" t="n">
-        <v>2.03</v>
+        <v>3.4</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.95</v>
+        <v>2.83</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="R32" t="n">
-        <v>3.79</v>
+        <v>2.32</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>6.29</v>
+        <v>2.06</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.48</v>
+        <v>2.8</v>
       </c>
       <c r="R36" t="n">
-        <v>1.53</v>
+        <v>3.89</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.06</v>
+        <v>6.29</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.8</v>
+        <v>3.48</v>
       </c>
       <c r="R38" t="n">
-        <v>3.89</v>
+        <v>1.53</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -307,12 +307,12 @@
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
     <t>Egypt Egyptian Premier League</t>
   </si>
   <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
     <t>South Africa Premier Soccer League</t>
   </si>
   <si>
@@ -337,21 +337,21 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Jeonbuk Motors</t>
+  </si>
+  <si>
     <t>Bucheon 1995</t>
   </si>
   <si>
-    <t>Jeonbuk Motors</t>
+    <t>Sangju Sangmu</t>
+  </si>
+  <si>
+    <t>Gangwon</t>
   </si>
   <si>
     <t>Daejeon Citizen</t>
   </si>
   <si>
-    <t>Gangwon</t>
-  </si>
-  <si>
-    <t>Sangju Sangmu</t>
-  </si>
-  <si>
     <t>Madura United</t>
   </si>
   <si>
@@ -376,15 +376,15 @@
     <t>Karvan FK</t>
   </si>
   <si>
+    <t>Borneo</t>
+  </si>
+  <si>
     <t>Chongqing Tongliang Long</t>
   </si>
   <si>
     <t>Dire Dawa Kenema</t>
   </si>
   <si>
-    <t>Borneo</t>
-  </si>
-  <si>
     <t>Mekelle Kenema</t>
   </si>
   <si>
@@ -412,42 +412,42 @@
     <t>Maccabi Tel Aviv</t>
   </si>
   <si>
+    <t>Bani Yas</t>
+  </si>
+  <si>
     <t>Dibba Al Fujairah</t>
   </si>
   <si>
     <t>Al Ittihad Kalba</t>
   </si>
   <si>
-    <t>Bani Yas</t>
+    <t>Lokomotiv Sofia 1929</t>
+  </si>
+  <si>
+    <t>Falkenberg</t>
   </si>
   <si>
     <t>Smouha SC</t>
   </si>
   <si>
+    <t>Al Ahly</t>
+  </si>
+  <si>
     <t>Ceramica Cleopatra</t>
   </si>
   <si>
-    <t>Falkenberg</t>
-  </si>
-  <si>
-    <t>Al Ahly</t>
-  </si>
-  <si>
-    <t>Lokomotiv Sofia 1929</t>
+    <t>Stellenbosch</t>
+  </si>
+  <si>
+    <t>Magesi</t>
   </si>
   <si>
     <t>Chippa United</t>
   </si>
   <si>
-    <t>Magesi</t>
-  </si>
-  <si>
     <t>Siwelele</t>
   </si>
   <si>
-    <t>Stellenbosch</t>
-  </si>
-  <si>
     <t>Al Khaleej</t>
   </si>
   <si>
@@ -460,21 +460,21 @@
     <t>Kabel Novi Sad</t>
   </si>
   <si>
+    <t>Gwangju</t>
+  </si>
+  <si>
     <t>Jeju United</t>
   </si>
   <si>
-    <t>Gwangju</t>
+    <t>Ulsan</t>
+  </si>
+  <si>
+    <t>Pohang Steelers</t>
   </si>
   <si>
     <t>Incheon United</t>
   </si>
   <si>
-    <t>Pohang Steelers</t>
-  </si>
-  <si>
-    <t>Ulsan</t>
-  </si>
-  <si>
     <t>Bali United</t>
   </si>
   <si>
@@ -499,15 +499,15 @@
     <t>Neftçi</t>
   </si>
   <si>
+    <t>Persita</t>
+  </si>
+  <si>
     <t>Henan Jianye</t>
   </si>
   <si>
     <t>Ethiopia Bunna</t>
   </si>
   <si>
-    <t>Persita</t>
-  </si>
-  <si>
     <t>Arba Minch Kenema</t>
   </si>
   <si>
@@ -535,37 +535,37 @@
     <t>Hapoel Petah Tikva</t>
   </si>
   <si>
+    <t>Al Dhafra</t>
+  </si>
+  <si>
     <t>Al Bataeh</t>
   </si>
   <si>
-    <t>Al Dhafra</t>
+    <t>Botev Vratsa</t>
+  </si>
+  <si>
+    <t>Norrköping</t>
   </si>
   <si>
     <t>Zamalek</t>
   </si>
   <si>
+    <t>ENPPI</t>
+  </si>
+  <si>
     <t>Pyramids FC</t>
   </si>
   <si>
-    <t>Norrköping</t>
-  </si>
-  <si>
-    <t>ENPPI</t>
-  </si>
-  <si>
-    <t>Botev Vratsa</t>
+    <t>Orlando Pirates</t>
+  </si>
+  <si>
+    <t>Orbit College</t>
   </si>
   <si>
     <t>Sekhukhune United</t>
   </si>
   <si>
-    <t>Orbit College</t>
-  </si>
-  <si>
     <t>Durban City</t>
-  </si>
-  <si>
-    <t>Orlando Pirates</t>
   </si>
   <si>
     <t>Al Hilal</t>
@@ -3545,10 +3545,10 @@
         <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E15" t="s">
         <v>120</v>
@@ -3730,10 +3730,10 @@
         <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E16" t="s">
         <v>121</v>
@@ -3915,7 +3915,7 @@
         <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D17" t="s">
         <v>105</v>
@@ -5959,7 +5959,7 @@
         <v>133</v>
       </c>
       <c r="F28" t="s">
-        <v>144</v>
+        <v>174</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -6144,7 +6144,7 @@
         <v>134</v>
       </c>
       <c r="F29" t="s">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -6320,7 +6320,7 @@
         <v>79</v>
       </c>
       <c r="C30" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D30" t="s">
         <v>105</v>
@@ -6359,13 +6359,13 @@
         <v>188</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="S30">
         <v>0</v>
@@ -6508,7 +6508,7 @@
         <v>97</v>
       </c>
       <c r="D31" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E31" t="s">
         <v>136</v>
@@ -6544,13 +6544,13 @@
         <v>188</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -6693,7 +6693,7 @@
         <v>98</v>
       </c>
       <c r="D32" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E32" t="s">
         <v>137</v>
@@ -6729,13 +6729,13 @@
         <v>188</v>
       </c>
       <c r="P32">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q32">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R32">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -6875,7 +6875,7 @@
         <v>79</v>
       </c>
       <c r="C33" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D33" t="s">
         <v>105</v>
@@ -7060,7 +7060,7 @@
         <v>79</v>
       </c>
       <c r="C34" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D34" t="s">
         <v>105</v>
@@ -7099,13 +7099,13 @@
         <v>188</v>
       </c>
       <c r="P34">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q34">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R34">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="S34">
         <v>0</v>
@@ -7284,13 +7284,13 @@
         <v>188</v>
       </c>
       <c r="P35">
-        <v>3.63</v>
+        <v>6.29</v>
       </c>
       <c r="Q35">
-        <v>3.02</v>
+        <v>3.48</v>
       </c>
       <c r="R35">
-        <v>2.03</v>
+        <v>1.53</v>
       </c>
       <c r="S35">
         <v>0</v>
@@ -7654,13 +7654,13 @@
         <v>188</v>
       </c>
       <c r="P37">
-        <v>2.2</v>
+        <v>3.63</v>
       </c>
       <c r="Q37">
-        <v>2.8</v>
+        <v>3.02</v>
       </c>
       <c r="R37">
-        <v>3.4</v>
+        <v>2.03</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -7839,13 +7839,13 @@
         <v>188</v>
       </c>
       <c r="P38">
-        <v>6.29</v>
+        <v>2.2</v>
       </c>
       <c r="Q38">
-        <v>3.48</v>
+        <v>2.8</v>
       </c>
       <c r="R38">
-        <v>1.53</v>
+        <v>3.4</v>
       </c>
       <c r="S38">
         <v>0</v>

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="185">
   <si>
     <t>Date</t>
   </si>
@@ -268,9 +268,6 @@
     <t>20:00</t>
   </si>
   <si>
-    <t>21:00</t>
-  </si>
-  <si>
     <t>South Korea K League 1</t>
   </si>
   <si>
@@ -325,9 +322,6 @@
     <t>USA MLS Next Pro</t>
   </si>
   <si>
-    <t>Serbia Prva Liga</t>
-  </si>
-  <si>
     <t>2026</t>
   </si>
   <si>
@@ -343,15 +337,15 @@
     <t>Bucheon 1995</t>
   </si>
   <si>
+    <t>Daejeon Citizen</t>
+  </si>
+  <si>
     <t>Sangju Sangmu</t>
   </si>
   <si>
     <t>Gangwon</t>
   </si>
   <si>
-    <t>Daejeon Citizen</t>
-  </si>
-  <si>
     <t>Madura United</t>
   </si>
   <si>
@@ -373,18 +367,18 @@
     <t>Shandong Luneng</t>
   </si>
   <si>
+    <t>Dire Dawa Kenema</t>
+  </si>
+  <si>
+    <t>Chongqing Tongliang Long</t>
+  </si>
+  <si>
     <t>Karvan FK</t>
   </si>
   <si>
     <t>Borneo</t>
   </si>
   <si>
-    <t>Chongqing Tongliang Long</t>
-  </si>
-  <si>
-    <t>Dire Dawa Kenema</t>
-  </si>
-  <si>
     <t>Mekelle Kenema</t>
   </si>
   <si>
@@ -412,39 +406,39 @@
     <t>Maccabi Tel Aviv</t>
   </si>
   <si>
+    <t>Dibba Al Fujairah</t>
+  </si>
+  <si>
     <t>Bani Yas</t>
   </si>
   <si>
-    <t>Dibba Al Fujairah</t>
-  </si>
-  <si>
     <t>Al Ittihad Kalba</t>
   </si>
   <si>
+    <t>Falkenberg</t>
+  </si>
+  <si>
+    <t>Smouha SC</t>
+  </si>
+  <si>
     <t>Lokomotiv Sofia 1929</t>
   </si>
   <si>
-    <t>Falkenberg</t>
-  </si>
-  <si>
-    <t>Smouha SC</t>
-  </si>
-  <si>
     <t>Al Ahly</t>
   </si>
   <si>
     <t>Ceramica Cleopatra</t>
   </si>
   <si>
+    <t>Magesi</t>
+  </si>
+  <si>
+    <t>Chippa United</t>
+  </si>
+  <si>
     <t>Stellenbosch</t>
   </si>
   <si>
-    <t>Magesi</t>
-  </si>
-  <si>
-    <t>Chippa United</t>
-  </si>
-  <si>
     <t>Siwelele</t>
   </si>
   <si>
@@ -457,24 +451,21 @@
     <t>New York City II</t>
   </si>
   <si>
-    <t>Kabel Novi Sad</t>
-  </si>
-  <si>
     <t>Gwangju</t>
   </si>
   <si>
     <t>Jeju United</t>
   </si>
   <si>
+    <t>Incheon United</t>
+  </si>
+  <si>
     <t>Ulsan</t>
   </si>
   <si>
     <t>Pohang Steelers</t>
   </si>
   <si>
-    <t>Incheon United</t>
-  </si>
-  <si>
     <t>Bali United</t>
   </si>
   <si>
@@ -496,18 +487,18 @@
     <t>Shanghai Shenhua</t>
   </si>
   <si>
+    <t>Ethiopia Bunna</t>
+  </si>
+  <si>
+    <t>Henan Jianye</t>
+  </si>
+  <si>
     <t>Neftçi</t>
   </si>
   <si>
     <t>Persita</t>
   </si>
   <si>
-    <t>Henan Jianye</t>
-  </si>
-  <si>
-    <t>Ethiopia Bunna</t>
-  </si>
-  <si>
     <t>Arba Minch Kenema</t>
   </si>
   <si>
@@ -535,36 +526,36 @@
     <t>Hapoel Petah Tikva</t>
   </si>
   <si>
+    <t>Al Bataeh</t>
+  </si>
+  <si>
     <t>Al Dhafra</t>
   </si>
   <si>
-    <t>Al Bataeh</t>
+    <t>Norrköping</t>
+  </si>
+  <si>
+    <t>Zamalek</t>
   </si>
   <si>
     <t>Botev Vratsa</t>
   </si>
   <si>
-    <t>Norrköping</t>
-  </si>
-  <si>
-    <t>Zamalek</t>
-  </si>
-  <si>
     <t>ENPPI</t>
   </si>
   <si>
     <t>Pyramids FC</t>
   </si>
   <si>
+    <t>Orbit College</t>
+  </si>
+  <si>
+    <t>Sekhukhune United</t>
+  </si>
+  <si>
     <t>Orlando Pirates</t>
   </si>
   <si>
-    <t>Orbit College</t>
-  </si>
-  <si>
-    <t>Sekhukhune United</t>
-  </si>
-  <si>
     <t>Durban City</t>
   </si>
   <si>
@@ -575,9 +566,6 @@
   </si>
   <si>
     <t>Chicago Fire II</t>
-  </si>
-  <si>
-    <t>Trajal Krusevac</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -944,7 +932,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BI42"/>
+  <dimension ref="A1:BI41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:61">
@@ -1140,16 +1128,16 @@
         <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1176,7 +1164,7 @@
         <v>-1</v>
       </c>
       <c r="O2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -1325,16 +1313,16 @@
         <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1361,7 +1349,7 @@
         <v>-1</v>
       </c>
       <c r="O3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -1510,16 +1498,16 @@
         <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1546,7 +1534,7 @@
         <v>-1</v>
       </c>
       <c r="O4" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -1695,16 +1683,16 @@
         <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1731,7 +1719,7 @@
         <v>-1</v>
       </c>
       <c r="O5" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -1880,16 +1868,16 @@
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1916,7 +1904,7 @@
         <v>-1</v>
       </c>
       <c r="O6" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -2065,16 +2053,16 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F7" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -2101,7 +2089,7 @@
         <v>-1</v>
       </c>
       <c r="O7" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -2250,16 +2238,16 @@
         <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F8" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2286,7 +2274,7 @@
         <v>-1</v>
       </c>
       <c r="O8" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -2435,16 +2423,16 @@
         <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2471,7 +2459,7 @@
         <v>-1</v>
       </c>
       <c r="O9" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -2620,16 +2608,16 @@
         <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D10" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E10" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F10" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2656,7 +2644,7 @@
         <v>-1</v>
       </c>
       <c r="O10" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -2805,16 +2793,16 @@
         <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E11" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F11" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2841,7 +2829,7 @@
         <v>-1</v>
       </c>
       <c r="O11" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -2990,16 +2978,16 @@
         <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D12" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F12" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -3026,7 +3014,7 @@
         <v>-1</v>
       </c>
       <c r="O12" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -3175,16 +3163,16 @@
         <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D13" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E13" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F13" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -3211,7 +3199,7 @@
         <v>-1</v>
       </c>
       <c r="O13" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -3360,16 +3348,16 @@
         <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D14" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E14" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F14" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -3396,7 +3384,7 @@
         <v>-1</v>
       </c>
       <c r="O14" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -3545,16 +3533,16 @@
         <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D15" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E15" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F15" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -3581,7 +3569,7 @@
         <v>-1</v>
       </c>
       <c r="O15" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -3730,16 +3718,16 @@
         <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E16" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F16" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -3766,7 +3754,7 @@
         <v>-1</v>
       </c>
       <c r="O16" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -3915,16 +3903,16 @@
         <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D17" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E17" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F17" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -3951,7 +3939,7 @@
         <v>-1</v>
       </c>
       <c r="O17" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -4100,16 +4088,16 @@
         <v>69</v>
       </c>
       <c r="C18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D18" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E18" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F18" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -4136,7 +4124,7 @@
         <v>-1</v>
       </c>
       <c r="O18" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -4285,16 +4273,16 @@
         <v>70</v>
       </c>
       <c r="C19" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D19" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E19" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F19" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -4321,7 +4309,7 @@
         <v>-1</v>
       </c>
       <c r="O19" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P19">
         <v>2.8</v>
@@ -4470,16 +4458,16 @@
         <v>71</v>
       </c>
       <c r="C20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D20" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E20" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F20" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -4506,7 +4494,7 @@
         <v>-1</v>
       </c>
       <c r="O20" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -4655,16 +4643,16 @@
         <v>72</v>
       </c>
       <c r="C21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D21" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E21" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F21" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -4691,7 +4679,7 @@
         <v>-1</v>
       </c>
       <c r="O21" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P21">
         <v>2.11</v>
@@ -4840,16 +4828,16 @@
         <v>73</v>
       </c>
       <c r="C22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D22" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E22" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F22" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -4876,7 +4864,7 @@
         <v>-1</v>
       </c>
       <c r="O22" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P22">
         <v>0</v>
@@ -5025,16 +5013,16 @@
         <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D23" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E23" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F23" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -5061,16 +5049,16 @@
         <v>-1</v>
       </c>
       <c r="O23" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -5210,16 +5198,16 @@
         <v>75</v>
       </c>
       <c r="C24" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D24" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E24" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F24" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -5246,16 +5234,16 @@
         <v>-1</v>
       </c>
       <c r="O24" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="S24">
         <v>0</v>
@@ -5395,16 +5383,16 @@
         <v>76</v>
       </c>
       <c r="C25" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D25" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E25" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F25" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -5431,7 +5419,7 @@
         <v>-1</v>
       </c>
       <c r="O25" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P25">
         <v>0</v>
@@ -5580,16 +5568,16 @@
         <v>77</v>
       </c>
       <c r="C26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D26" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E26" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F26" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -5616,7 +5604,7 @@
         <v>-1</v>
       </c>
       <c r="O26" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P26">
         <v>0</v>
@@ -5765,16 +5753,16 @@
         <v>78</v>
       </c>
       <c r="C27" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D27" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E27" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F27" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -5801,7 +5789,7 @@
         <v>-1</v>
       </c>
       <c r="O27" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -5950,16 +5938,16 @@
         <v>78</v>
       </c>
       <c r="C28" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D28" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E28" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F28" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -5986,7 +5974,7 @@
         <v>-1</v>
       </c>
       <c r="O28" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -6135,16 +6123,16 @@
         <v>78</v>
       </c>
       <c r="C29" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D29" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E29" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F29" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -6171,7 +6159,7 @@
         <v>-1</v>
       </c>
       <c r="O29" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P29">
         <v>0</v>
@@ -6320,16 +6308,16 @@
         <v>79</v>
       </c>
       <c r="C30" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D30" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E30" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F30" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -6356,16 +6344,16 @@
         <v>-1</v>
       </c>
       <c r="O30" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P30">
-        <v>1.95</v>
+        <v>2.83</v>
       </c>
       <c r="Q30">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="R30">
-        <v>3.79</v>
+        <v>2.32</v>
       </c>
       <c r="S30">
         <v>0</v>
@@ -6508,13 +6496,13 @@
         <v>97</v>
       </c>
       <c r="D31" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E31" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F31" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -6541,16 +6529,16 @@
         <v>-1</v>
       </c>
       <c r="O31" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P31">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q31">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R31">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -6690,16 +6678,16 @@
         <v>79</v>
       </c>
       <c r="C32" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D32" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E32" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F32" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -6726,16 +6714,16 @@
         <v>-1</v>
       </c>
       <c r="O32" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -6875,16 +6863,16 @@
         <v>79</v>
       </c>
       <c r="C33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D33" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E33" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F33" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -6911,7 +6899,7 @@
         <v>-1</v>
       </c>
       <c r="O33" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P33">
         <v>0</v>
@@ -7060,16 +7048,16 @@
         <v>79</v>
       </c>
       <c r="C34" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D34" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E34" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F34" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -7096,7 +7084,7 @@
         <v>-1</v>
       </c>
       <c r="O34" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P34">
         <v>0</v>
@@ -7245,16 +7233,16 @@
         <v>80</v>
       </c>
       <c r="C35" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D35" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E35" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F35" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -7281,16 +7269,16 @@
         <v>-1</v>
       </c>
       <c r="O35" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P35">
-        <v>6.29</v>
+        <v>2.06</v>
       </c>
       <c r="Q35">
-        <v>3.48</v>
+        <v>2.8</v>
       </c>
       <c r="R35">
-        <v>1.53</v>
+        <v>3.89</v>
       </c>
       <c r="S35">
         <v>0</v>
@@ -7430,16 +7418,16 @@
         <v>80</v>
       </c>
       <c r="C36" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D36" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E36" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F36" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -7466,16 +7454,16 @@
         <v>-1</v>
       </c>
       <c r="O36" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P36">
-        <v>2.06</v>
+        <v>3.63</v>
       </c>
       <c r="Q36">
-        <v>2.8</v>
+        <v>3.02</v>
       </c>
       <c r="R36">
-        <v>3.89</v>
+        <v>2.03</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -7615,16 +7603,16 @@
         <v>80</v>
       </c>
       <c r="C37" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D37" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E37" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F37" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -7651,16 +7639,16 @@
         <v>-1</v>
       </c>
       <c r="O37" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P37">
-        <v>3.63</v>
+        <v>6.29</v>
       </c>
       <c r="Q37">
-        <v>3.02</v>
+        <v>3.48</v>
       </c>
       <c r="R37">
-        <v>2.03</v>
+        <v>1.53</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -7800,16 +7788,16 @@
         <v>80</v>
       </c>
       <c r="C38" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D38" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E38" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F38" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -7836,7 +7824,7 @@
         <v>-1</v>
       </c>
       <c r="O38" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P38">
         <v>2.2</v>
@@ -7985,16 +7973,16 @@
         <v>81</v>
       </c>
       <c r="C39" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D39" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E39" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F39" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -8021,7 +8009,7 @@
         <v>-1</v>
       </c>
       <c r="O39" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P39">
         <v>0</v>
@@ -8170,16 +8158,16 @@
         <v>82</v>
       </c>
       <c r="C40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D40" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E40" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F40" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -8206,7 +8194,7 @@
         <v>-1</v>
       </c>
       <c r="O40" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P40">
         <v>1.82</v>
@@ -8355,16 +8343,16 @@
         <v>83</v>
       </c>
       <c r="C41" t="s">
+        <v>101</v>
+      </c>
+      <c r="D41" t="s">
         <v>102</v>
       </c>
-      <c r="D41" t="s">
-        <v>104</v>
-      </c>
       <c r="E41" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F41" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -8391,7 +8379,7 @@
         <v>-1</v>
       </c>
       <c r="O41" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P41">
         <v>0</v>
@@ -8530,191 +8518,6 @@
       </c>
       <c r="BI41" s="3">
         <v>46147.83333333334</v>
-      </c>
-    </row>
-    <row r="42" spans="1:61">
-      <c r="A42" s="2">
-        <v>46147</v>
-      </c>
-      <c r="B42" t="s">
-        <v>84</v>
-      </c>
-      <c r="C42" t="s">
-        <v>103</v>
-      </c>
-      <c r="D42" t="s">
-        <v>105</v>
-      </c>
-      <c r="E42" t="s">
-        <v>147</v>
-      </c>
-      <c r="F42" t="s">
-        <v>187</v>
-      </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
-      <c r="H42">
-        <v>0</v>
-      </c>
-      <c r="I42">
-        <v>0</v>
-      </c>
-      <c r="J42">
-        <v>0</v>
-      </c>
-      <c r="K42">
-        <v>0</v>
-      </c>
-      <c r="L42">
-        <v>0</v>
-      </c>
-      <c r="M42">
-        <v>-1</v>
-      </c>
-      <c r="N42">
-        <v>-1</v>
-      </c>
-      <c r="O42" t="s">
-        <v>188</v>
-      </c>
-      <c r="P42">
-        <v>0</v>
-      </c>
-      <c r="Q42">
-        <v>0</v>
-      </c>
-      <c r="R42">
-        <v>0</v>
-      </c>
-      <c r="S42">
-        <v>0</v>
-      </c>
-      <c r="T42">
-        <v>0</v>
-      </c>
-      <c r="U42">
-        <v>0</v>
-      </c>
-      <c r="V42">
-        <v>0</v>
-      </c>
-      <c r="W42">
-        <v>0</v>
-      </c>
-      <c r="X42">
-        <v>0</v>
-      </c>
-      <c r="Y42">
-        <v>0</v>
-      </c>
-      <c r="Z42">
-        <v>0</v>
-      </c>
-      <c r="AA42">
-        <v>0</v>
-      </c>
-      <c r="AB42">
-        <v>0</v>
-      </c>
-      <c r="AC42">
-        <v>0</v>
-      </c>
-      <c r="AD42">
-        <v>0</v>
-      </c>
-      <c r="AE42">
-        <v>0</v>
-      </c>
-      <c r="AF42">
-        <v>0</v>
-      </c>
-      <c r="AG42">
-        <v>0</v>
-      </c>
-      <c r="AH42">
-        <v>0</v>
-      </c>
-      <c r="AI42">
-        <v>0</v>
-      </c>
-      <c r="AJ42">
-        <v>0</v>
-      </c>
-      <c r="AK42">
-        <v>0</v>
-      </c>
-      <c r="AL42">
-        <v>0</v>
-      </c>
-      <c r="AM42">
-        <v>0</v>
-      </c>
-      <c r="AN42">
-        <v>0</v>
-      </c>
-      <c r="AO42">
-        <v>0</v>
-      </c>
-      <c r="AP42">
-        <v>0</v>
-      </c>
-      <c r="AQ42">
-        <v>0</v>
-      </c>
-      <c r="AR42">
-        <v>0</v>
-      </c>
-      <c r="AS42">
-        <v>0</v>
-      </c>
-      <c r="AT42">
-        <v>0</v>
-      </c>
-      <c r="AU42">
-        <v>0</v>
-      </c>
-      <c r="AV42">
-        <v>0</v>
-      </c>
-      <c r="AW42">
-        <v>0</v>
-      </c>
-      <c r="AX42">
-        <v>0</v>
-      </c>
-      <c r="AY42">
-        <v>0</v>
-      </c>
-      <c r="AZ42">
-        <v>0</v>
-      </c>
-      <c r="BA42">
-        <v>0</v>
-      </c>
-      <c r="BB42">
-        <v>0</v>
-      </c>
-      <c r="BC42">
-        <v>0</v>
-      </c>
-      <c r="BD42">
-        <v>0</v>
-      </c>
-      <c r="BE42">
-        <v>0</v>
-      </c>
-      <c r="BF42">
-        <v>0</v>
-      </c>
-      <c r="BG42">
-        <v>0</v>
-      </c>
-      <c r="BH42">
-        <v>0</v>
-      </c>
-      <c r="BI42" s="3">
-        <v>46147.875</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -337,15 +337,15 @@
     <t>Bucheon 1995</t>
   </si>
   <si>
+    <t>Gangwon</t>
+  </si>
+  <si>
     <t>Daejeon Citizen</t>
   </si>
   <si>
     <t>Sangju Sangmu</t>
   </si>
   <si>
-    <t>Gangwon</t>
-  </si>
-  <si>
     <t>Madura United</t>
   </si>
   <si>
@@ -367,18 +367,18 @@
     <t>Shandong Luneng</t>
   </si>
   <si>
+    <t>Borneo</t>
+  </si>
+  <si>
+    <t>Karvan FK</t>
+  </si>
+  <si>
+    <t>Chongqing Tongliang Long</t>
+  </si>
+  <si>
     <t>Dire Dawa Kenema</t>
   </si>
   <si>
-    <t>Chongqing Tongliang Long</t>
-  </si>
-  <si>
-    <t>Karvan FK</t>
-  </si>
-  <si>
-    <t>Borneo</t>
-  </si>
-  <si>
     <t>Mekelle Kenema</t>
   </si>
   <si>
@@ -415,19 +415,25 @@
     <t>Al Ittihad Kalba</t>
   </si>
   <si>
+    <t>Lokomotiv Sofia 1929</t>
+  </si>
+  <si>
     <t>Falkenberg</t>
   </si>
   <si>
+    <t>Al Ahly</t>
+  </si>
+  <si>
+    <t>Ceramica Cleopatra</t>
+  </si>
+  <si>
     <t>Smouha SC</t>
   </si>
   <si>
-    <t>Lokomotiv Sofia 1929</t>
-  </si>
-  <si>
-    <t>Al Ahly</t>
-  </si>
-  <si>
-    <t>Ceramica Cleopatra</t>
+    <t>Stellenbosch</t>
+  </si>
+  <si>
+    <t>Siwelele</t>
   </si>
   <si>
     <t>Magesi</t>
@@ -436,12 +442,6 @@
     <t>Chippa United</t>
   </si>
   <si>
-    <t>Stellenbosch</t>
-  </si>
-  <si>
-    <t>Siwelele</t>
-  </si>
-  <si>
     <t>Al Khaleej</t>
   </si>
   <si>
@@ -457,15 +457,15 @@
     <t>Jeju United</t>
   </si>
   <si>
+    <t>Pohang Steelers</t>
+  </si>
+  <si>
     <t>Incheon United</t>
   </si>
   <si>
     <t>Ulsan</t>
   </si>
   <si>
-    <t>Pohang Steelers</t>
-  </si>
-  <si>
     <t>Bali United</t>
   </si>
   <si>
@@ -487,18 +487,18 @@
     <t>Shanghai Shenhua</t>
   </si>
   <si>
+    <t>Persita</t>
+  </si>
+  <si>
+    <t>Neftçi</t>
+  </si>
+  <si>
+    <t>Henan Jianye</t>
+  </si>
+  <si>
     <t>Ethiopia Bunna</t>
   </si>
   <si>
-    <t>Henan Jianye</t>
-  </si>
-  <si>
-    <t>Neftçi</t>
-  </si>
-  <si>
-    <t>Persita</t>
-  </si>
-  <si>
     <t>Arba Minch Kenema</t>
   </si>
   <si>
@@ -532,31 +532,31 @@
     <t>Al Dhafra</t>
   </si>
   <si>
+    <t>Botev Vratsa</t>
+  </si>
+  <si>
     <t>Norrköping</t>
   </si>
   <si>
+    <t>ENPPI</t>
+  </si>
+  <si>
+    <t>Pyramids FC</t>
+  </si>
+  <si>
     <t>Zamalek</t>
   </si>
   <si>
-    <t>Botev Vratsa</t>
-  </si>
-  <si>
-    <t>ENPPI</t>
-  </si>
-  <si>
-    <t>Pyramids FC</t>
+    <t>Orlando Pirates</t>
+  </si>
+  <si>
+    <t>Durban City</t>
   </si>
   <si>
     <t>Orbit College</t>
   </si>
   <si>
     <t>Sekhukhune United</t>
-  </si>
-  <si>
-    <t>Orlando Pirates</t>
-  </si>
-  <si>
-    <t>Durban City</t>
   </si>
   <si>
     <t>Al Hilal</t>
@@ -3348,7 +3348,7 @@
         <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D14" t="s">
         <v>103</v>
@@ -3533,10 +3533,10 @@
         <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E15" t="s">
         <v>118</v>
@@ -3718,10 +3718,10 @@
         <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E16" t="s">
         <v>119</v>
@@ -3903,7 +3903,7 @@
         <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D17" t="s">
         <v>103</v>
@@ -5607,13 +5607,13 @@
         <v>184</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -6308,10 +6308,10 @@
         <v>79</v>
       </c>
       <c r="C30" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D30" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E30" t="s">
         <v>133</v>
@@ -6347,13 +6347,13 @@
         <v>184</v>
       </c>
       <c r="P30">
-        <v>2.83</v>
+        <v>1.95</v>
       </c>
       <c r="Q30">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="R30">
-        <v>2.32</v>
+        <v>3.79</v>
       </c>
       <c r="S30">
         <v>0</v>
@@ -6493,10 +6493,10 @@
         <v>79</v>
       </c>
       <c r="C31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D31" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E31" t="s">
         <v>134</v>
@@ -6532,13 +6532,13 @@
         <v>184</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -6678,7 +6678,7 @@
         <v>79</v>
       </c>
       <c r="C32" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D32" t="s">
         <v>103</v>
@@ -6717,13 +6717,13 @@
         <v>184</v>
       </c>
       <c r="P32">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q32">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R32">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -7272,13 +7272,13 @@
         <v>184</v>
       </c>
       <c r="P35">
-        <v>2.06</v>
+        <v>6.29</v>
       </c>
       <c r="Q35">
-        <v>2.8</v>
+        <v>3.48</v>
       </c>
       <c r="R35">
-        <v>3.89</v>
+        <v>1.53</v>
       </c>
       <c r="S35">
         <v>0</v>
@@ -7457,13 +7457,13 @@
         <v>184</v>
       </c>
       <c r="P36">
-        <v>3.63</v>
+        <v>2.2</v>
       </c>
       <c r="Q36">
-        <v>3.02</v>
+        <v>2.8</v>
       </c>
       <c r="R36">
-        <v>2.03</v>
+        <v>3.4</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -7642,13 +7642,13 @@
         <v>184</v>
       </c>
       <c r="P37">
-        <v>6.29</v>
+        <v>2.06</v>
       </c>
       <c r="Q37">
-        <v>3.48</v>
+        <v>2.8</v>
       </c>
       <c r="R37">
-        <v>1.53</v>
+        <v>3.89</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -7827,13 +7827,13 @@
         <v>184</v>
       </c>
       <c r="P38">
-        <v>2.2</v>
+        <v>3.63</v>
       </c>
       <c r="Q38">
-        <v>2.8</v>
+        <v>3.02</v>
       </c>
       <c r="R38">
-        <v>3.4</v>
+        <v>2.03</v>
       </c>
       <c r="S38">
         <v>0</v>

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -304,12 +304,12 @@
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
+    <t>Egypt Egyptian Premier League</t>
+  </si>
+  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
-    <t>Egypt Egyptian Premier League</t>
-  </si>
-  <si>
     <t>South Africa Premier Soccer League</t>
   </si>
   <si>
@@ -337,24 +337,24 @@
     <t>Bucheon 1995</t>
   </si>
   <si>
+    <t>Daejeon Citizen</t>
+  </si>
+  <si>
     <t>Gangwon</t>
   </si>
   <si>
-    <t>Daejeon Citizen</t>
-  </si>
-  <si>
     <t>Sangju Sangmu</t>
   </si>
   <si>
     <t>Madura United</t>
   </si>
   <si>
+    <t>Ethiopia Nigd Bank</t>
+  </si>
+  <si>
     <t>FC Seoul</t>
   </si>
   <si>
-    <t>Ethiopia Nigd Bank</t>
-  </si>
-  <si>
     <t>Qingdao Youth Island</t>
   </si>
   <si>
@@ -367,18 +367,18 @@
     <t>Shandong Luneng</t>
   </si>
   <si>
+    <t>Karvan FK</t>
+  </si>
+  <si>
+    <t>Chongqing Tongliang Long</t>
+  </si>
+  <si>
+    <t>Dire Dawa Kenema</t>
+  </si>
+  <si>
     <t>Borneo</t>
   </si>
   <si>
-    <t>Karvan FK</t>
-  </si>
-  <si>
-    <t>Chongqing Tongliang Long</t>
-  </si>
-  <si>
-    <t>Dire Dawa Kenema</t>
-  </si>
-  <si>
     <t>Mekelle Kenema</t>
   </si>
   <si>
@@ -406,13 +406,19 @@
     <t>Maccabi Tel Aviv</t>
   </si>
   <si>
+    <t>Bani Yas</t>
+  </si>
+  <si>
+    <t>Al Ittihad Kalba</t>
+  </si>
+  <si>
     <t>Dibba Al Fujairah</t>
   </si>
   <si>
-    <t>Bani Yas</t>
-  </si>
-  <si>
-    <t>Al Ittihad Kalba</t>
+    <t>Al Ahly</t>
+  </si>
+  <si>
+    <t>Smouha SC</t>
   </si>
   <si>
     <t>Lokomotiv Sofia 1929</t>
@@ -421,27 +427,21 @@
     <t>Falkenberg</t>
   </si>
   <si>
-    <t>Al Ahly</t>
-  </si>
-  <si>
     <t>Ceramica Cleopatra</t>
   </si>
   <si>
-    <t>Smouha SC</t>
+    <t>Siwelele</t>
   </si>
   <si>
     <t>Stellenbosch</t>
   </si>
   <si>
-    <t>Siwelele</t>
+    <t>Chippa United</t>
   </si>
   <si>
     <t>Magesi</t>
   </si>
   <si>
-    <t>Chippa United</t>
-  </si>
-  <si>
     <t>Al Khaleej</t>
   </si>
   <si>
@@ -457,24 +457,24 @@
     <t>Jeju United</t>
   </si>
   <si>
+    <t>Incheon United</t>
+  </si>
+  <si>
     <t>Pohang Steelers</t>
   </si>
   <si>
-    <t>Incheon United</t>
-  </si>
-  <si>
     <t>Ulsan</t>
   </si>
   <si>
     <t>Bali United</t>
   </si>
   <si>
+    <t>Kedus Giorgis</t>
+  </si>
+  <si>
     <t>Anyang</t>
   </si>
   <si>
-    <t>Kedus Giorgis</t>
-  </si>
-  <si>
     <t>Tianjin Teda</t>
   </si>
   <si>
@@ -487,18 +487,18 @@
     <t>Shanghai Shenhua</t>
   </si>
   <si>
+    <t>Neftçi</t>
+  </si>
+  <si>
+    <t>Henan Jianye</t>
+  </si>
+  <si>
+    <t>Ethiopia Bunna</t>
+  </si>
+  <si>
     <t>Persita</t>
   </si>
   <si>
-    <t>Neftçi</t>
-  </si>
-  <si>
-    <t>Henan Jianye</t>
-  </si>
-  <si>
-    <t>Ethiopia Bunna</t>
-  </si>
-  <si>
     <t>Arba Minch Kenema</t>
   </si>
   <si>
@@ -526,10 +526,16 @@
     <t>Hapoel Petah Tikva</t>
   </si>
   <si>
+    <t>Al Dhafra</t>
+  </si>
+  <si>
     <t>Al Bataeh</t>
   </si>
   <si>
-    <t>Al Dhafra</t>
+    <t>ENPPI</t>
+  </si>
+  <si>
+    <t>Zamalek</t>
   </si>
   <si>
     <t>Botev Vratsa</t>
@@ -538,25 +544,19 @@
     <t>Norrköping</t>
   </si>
   <si>
-    <t>ENPPI</t>
-  </si>
-  <si>
     <t>Pyramids FC</t>
   </si>
   <si>
-    <t>Zamalek</t>
+    <t>Durban City</t>
   </si>
   <si>
     <t>Orlando Pirates</t>
   </si>
   <si>
-    <t>Durban City</t>
+    <t>Sekhukhune United</t>
   </si>
   <si>
     <t>Orbit College</t>
-  </si>
-  <si>
-    <t>Sekhukhune United</t>
   </si>
   <si>
     <t>Al Hilal</t>
@@ -2238,10 +2238,10 @@
         <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E8" t="s">
         <v>111</v>
@@ -2423,10 +2423,10 @@
         <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E9" t="s">
         <v>112</v>
@@ -3348,7 +3348,7 @@
         <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
         <v>103</v>
@@ -3533,10 +3533,10 @@
         <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E15" t="s">
         <v>118</v>
@@ -3718,10 +3718,10 @@
         <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E16" t="s">
         <v>119</v>
@@ -3903,7 +3903,7 @@
         <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D17" t="s">
         <v>103</v>
@@ -5947,7 +5947,7 @@
         <v>131</v>
       </c>
       <c r="F28" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -6132,7 +6132,7 @@
         <v>132</v>
       </c>
       <c r="F29" t="s">
-        <v>142</v>
+        <v>171</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -6308,7 +6308,7 @@
         <v>79</v>
       </c>
       <c r="C30" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D30" t="s">
         <v>103</v>
@@ -6347,13 +6347,13 @@
         <v>184</v>
       </c>
       <c r="P30">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q30">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R30">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="S30">
         <v>0</v>
@@ -6496,7 +6496,7 @@
         <v>96</v>
       </c>
       <c r="D31" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E31" t="s">
         <v>134</v>
@@ -6532,13 +6532,13 @@
         <v>184</v>
       </c>
       <c r="P31">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q31">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R31">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -6678,7 +6678,7 @@
         <v>79</v>
       </c>
       <c r="C32" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D32" t="s">
         <v>103</v>
@@ -6717,13 +6717,13 @@
         <v>184</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -6866,7 +6866,7 @@
         <v>97</v>
       </c>
       <c r="D33" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E33" t="s">
         <v>136</v>
@@ -6902,13 +6902,13 @@
         <v>184</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S33">
         <v>0</v>
@@ -7048,7 +7048,7 @@
         <v>79</v>
       </c>
       <c r="C34" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D34" t="s">
         <v>103</v>
@@ -7272,13 +7272,13 @@
         <v>184</v>
       </c>
       <c r="P35">
-        <v>6.29</v>
+        <v>2.2</v>
       </c>
       <c r="Q35">
-        <v>3.48</v>
+        <v>2.8</v>
       </c>
       <c r="R35">
-        <v>1.53</v>
+        <v>3.4</v>
       </c>
       <c r="S35">
         <v>0</v>
@@ -7457,13 +7457,13 @@
         <v>184</v>
       </c>
       <c r="P36">
-        <v>2.2</v>
+        <v>6.29</v>
       </c>
       <c r="Q36">
-        <v>2.8</v>
+        <v>3.48</v>
       </c>
       <c r="R36">
-        <v>3.4</v>
+        <v>1.53</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -7642,13 +7642,13 @@
         <v>184</v>
       </c>
       <c r="P37">
-        <v>2.06</v>
+        <v>3.63</v>
       </c>
       <c r="Q37">
-        <v>2.8</v>
+        <v>3.02</v>
       </c>
       <c r="R37">
-        <v>3.89</v>
+        <v>2.03</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -7827,13 +7827,13 @@
         <v>184</v>
       </c>
       <c r="P38">
-        <v>3.63</v>
+        <v>2.06</v>
       </c>
       <c r="Q38">
-        <v>3.02</v>
+        <v>2.8</v>
       </c>
       <c r="R38">
-        <v>2.03</v>
+        <v>3.89</v>
       </c>
       <c r="S38">
         <v>0</v>

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -331,48 +331,48 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Bucheon 1995</t>
+  </si>
+  <si>
     <t>Jeonbuk Motors</t>
   </si>
   <si>
-    <t>Bucheon 1995</t>
-  </si>
-  <si>
     <t>Daejeon Citizen</t>
   </si>
   <si>
+    <t>Sangju Sangmu</t>
+  </si>
+  <si>
     <t>Gangwon</t>
   </si>
   <si>
-    <t>Sangju Sangmu</t>
-  </si>
-  <si>
     <t>Madura United</t>
   </si>
   <si>
+    <t>FC Seoul</t>
+  </si>
+  <si>
     <t>Ethiopia Nigd Bank</t>
   </si>
   <si>
-    <t>FC Seoul</t>
-  </si>
-  <si>
     <t>Qingdao Youth Island</t>
   </si>
   <si>
     <t>Tanjong Pagar</t>
   </si>
   <si>
+    <t>Shandong Luneng</t>
+  </si>
+  <si>
     <t>Shenyang Urban</t>
   </si>
   <si>
-    <t>Shandong Luneng</t>
+    <t>Chongqing Tongliang Long</t>
   </si>
   <si>
     <t>Karvan FK</t>
   </si>
   <si>
-    <t>Chongqing Tongliang Long</t>
-  </si>
-  <si>
     <t>Dire Dawa Kenema</t>
   </si>
   <si>
@@ -406,28 +406,34 @@
     <t>Maccabi Tel Aviv</t>
   </si>
   <si>
+    <t>Dibba Al Fujairah</t>
+  </si>
+  <si>
+    <t>Al Ittihad Kalba</t>
+  </si>
+  <si>
     <t>Bani Yas</t>
   </si>
   <si>
-    <t>Al Ittihad Kalba</t>
-  </si>
-  <si>
-    <t>Dibba Al Fujairah</t>
+    <t>Ceramica Cleopatra</t>
+  </si>
+  <si>
+    <t>Falkenberg</t>
+  </si>
+  <si>
+    <t>Smouha SC</t>
   </si>
   <si>
     <t>Al Ahly</t>
   </si>
   <si>
-    <t>Smouha SC</t>
-  </si>
-  <si>
     <t>Lokomotiv Sofia 1929</t>
   </si>
   <si>
-    <t>Falkenberg</t>
-  </si>
-  <si>
-    <t>Ceramica Cleopatra</t>
+    <t>Magesi</t>
+  </si>
+  <si>
+    <t>Chippa United</t>
   </si>
   <si>
     <t>Siwelele</t>
@@ -436,12 +442,6 @@
     <t>Stellenbosch</t>
   </si>
   <si>
-    <t>Chippa United</t>
-  </si>
-  <si>
-    <t>Magesi</t>
-  </si>
-  <si>
     <t>Al Khaleej</t>
   </si>
   <si>
@@ -451,48 +451,48 @@
     <t>New York City II</t>
   </si>
   <si>
+    <t>Jeju United</t>
+  </si>
+  <si>
     <t>Gwangju</t>
   </si>
   <si>
-    <t>Jeju United</t>
-  </si>
-  <si>
     <t>Incheon United</t>
   </si>
   <si>
+    <t>Ulsan</t>
+  </si>
+  <si>
     <t>Pohang Steelers</t>
   </si>
   <si>
-    <t>Ulsan</t>
-  </si>
-  <si>
     <t>Bali United</t>
   </si>
   <si>
+    <t>Anyang</t>
+  </si>
+  <si>
     <t>Kedus Giorgis</t>
   </si>
   <si>
-    <t>Anyang</t>
-  </si>
-  <si>
     <t>Tianjin Teda</t>
   </si>
   <si>
     <t>Hougang United</t>
   </si>
   <si>
+    <t>Shanghai Shenhua</t>
+  </si>
+  <si>
     <t>Chengdu Better City FC</t>
   </si>
   <si>
-    <t>Shanghai Shenhua</t>
+    <t>Henan Jianye</t>
   </si>
   <si>
     <t>Neftçi</t>
   </si>
   <si>
-    <t>Henan Jianye</t>
-  </si>
-  <si>
     <t>Ethiopia Bunna</t>
   </si>
   <si>
@@ -526,37 +526,37 @@
     <t>Hapoel Petah Tikva</t>
   </si>
   <si>
+    <t>Al Bataeh</t>
+  </si>
+  <si>
     <t>Al Dhafra</t>
   </si>
   <si>
-    <t>Al Bataeh</t>
+    <t>Pyramids FC</t>
+  </si>
+  <si>
+    <t>Norrköping</t>
+  </si>
+  <si>
+    <t>Zamalek</t>
   </si>
   <si>
     <t>ENPPI</t>
   </si>
   <si>
-    <t>Zamalek</t>
-  </si>
-  <si>
     <t>Botev Vratsa</t>
   </si>
   <si>
-    <t>Norrköping</t>
-  </si>
-  <si>
-    <t>Pyramids FC</t>
+    <t>Orbit College</t>
+  </si>
+  <si>
+    <t>Sekhukhune United</t>
   </si>
   <si>
     <t>Durban City</t>
   </si>
   <si>
     <t>Orlando Pirates</t>
-  </si>
-  <si>
-    <t>Sekhukhune United</t>
-  </si>
-  <si>
-    <t>Orbit College</t>
   </si>
   <si>
     <t>Al Hilal</t>
@@ -2238,10 +2238,10 @@
         <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
         <v>111</v>
@@ -2423,10 +2423,10 @@
         <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E9" t="s">
         <v>112</v>
@@ -3348,10 +3348,10 @@
         <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E14" t="s">
         <v>117</v>
@@ -3533,10 +3533,10 @@
         <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E15" t="s">
         <v>118</v>
@@ -6493,10 +6493,10 @@
         <v>79</v>
       </c>
       <c r="C31" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D31" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E31" t="s">
         <v>134</v>
@@ -6532,13 +6532,13 @@
         <v>184</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -6678,7 +6678,7 @@
         <v>79</v>
       </c>
       <c r="C32" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D32" t="s">
         <v>103</v>
@@ -6717,13 +6717,13 @@
         <v>184</v>
       </c>
       <c r="P32">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q32">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R32">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -6863,10 +6863,10 @@
         <v>79</v>
       </c>
       <c r="C33" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E33" t="s">
         <v>136</v>
@@ -6902,13 +6902,13 @@
         <v>184</v>
       </c>
       <c r="P33">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q33">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R33">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S33">
         <v>0</v>
@@ -7048,7 +7048,7 @@
         <v>79</v>
       </c>
       <c r="C34" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D34" t="s">
         <v>103</v>
@@ -7087,13 +7087,13 @@
         <v>184</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="S34">
         <v>0</v>
@@ -7272,13 +7272,13 @@
         <v>184</v>
       </c>
       <c r="P35">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="Q35">
         <v>2.8</v>
       </c>
       <c r="R35">
-        <v>3.4</v>
+        <v>3.89</v>
       </c>
       <c r="S35">
         <v>0</v>
@@ -7457,13 +7457,13 @@
         <v>184</v>
       </c>
       <c r="P36">
-        <v>6.29</v>
+        <v>3.63</v>
       </c>
       <c r="Q36">
-        <v>3.48</v>
+        <v>3.02</v>
       </c>
       <c r="R36">
-        <v>1.53</v>
+        <v>2.03</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -7642,13 +7642,13 @@
         <v>184</v>
       </c>
       <c r="P37">
-        <v>3.63</v>
+        <v>2.2</v>
       </c>
       <c r="Q37">
-        <v>3.02</v>
+        <v>2.8</v>
       </c>
       <c r="R37">
-        <v>2.03</v>
+        <v>3.4</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -7827,13 +7827,13 @@
         <v>184</v>
       </c>
       <c r="P38">
-        <v>2.06</v>
+        <v>6.29</v>
       </c>
       <c r="Q38">
-        <v>2.8</v>
+        <v>3.48</v>
       </c>
       <c r="R38">
-        <v>3.89</v>
+        <v>1.53</v>
       </c>
       <c r="S38">
         <v>0</v>

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -331,18 +331,18 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Jeonbuk Motors</t>
+  </si>
+  <si>
     <t>Bucheon 1995</t>
   </si>
   <si>
-    <t>Jeonbuk Motors</t>
+    <t>Sangju Sangmu</t>
   </si>
   <si>
     <t>Daejeon Citizen</t>
   </si>
   <si>
-    <t>Sangju Sangmu</t>
-  </si>
-  <si>
     <t>Gangwon</t>
   </si>
   <si>
@@ -373,12 +373,12 @@
     <t>Karvan FK</t>
   </si>
   <si>
+    <t>Borneo</t>
+  </si>
+  <si>
     <t>Dire Dawa Kenema</t>
   </si>
   <si>
-    <t>Borneo</t>
-  </si>
-  <si>
     <t>Mekelle Kenema</t>
   </si>
   <si>
@@ -409,39 +409,39 @@
     <t>Dibba Al Fujairah</t>
   </si>
   <si>
+    <t>Bani Yas</t>
+  </si>
+  <si>
     <t>Al Ittihad Kalba</t>
   </si>
   <si>
-    <t>Bani Yas</t>
+    <t>Al Ahly</t>
   </si>
   <si>
     <t>Ceramica Cleopatra</t>
   </si>
   <si>
+    <t>Lokomotiv Sofia 1929</t>
+  </si>
+  <si>
     <t>Falkenberg</t>
   </si>
   <si>
     <t>Smouha SC</t>
   </si>
   <si>
-    <t>Al Ahly</t>
-  </si>
-  <si>
-    <t>Lokomotiv Sofia 1929</t>
+    <t>Siwelele</t>
+  </si>
+  <si>
+    <t>Stellenbosch</t>
+  </si>
+  <si>
+    <t>Chippa United</t>
   </si>
   <si>
     <t>Magesi</t>
   </si>
   <si>
-    <t>Chippa United</t>
-  </si>
-  <si>
-    <t>Siwelele</t>
-  </si>
-  <si>
-    <t>Stellenbosch</t>
-  </si>
-  <si>
     <t>Al Khaleej</t>
   </si>
   <si>
@@ -451,18 +451,18 @@
     <t>New York City II</t>
   </si>
   <si>
+    <t>Gwangju</t>
+  </si>
+  <si>
     <t>Jeju United</t>
   </si>
   <si>
-    <t>Gwangju</t>
+    <t>Ulsan</t>
   </si>
   <si>
     <t>Incheon United</t>
   </si>
   <si>
-    <t>Ulsan</t>
-  </si>
-  <si>
     <t>Pohang Steelers</t>
   </si>
   <si>
@@ -493,12 +493,12 @@
     <t>Neftçi</t>
   </si>
   <si>
+    <t>Persita</t>
+  </si>
+  <si>
     <t>Ethiopia Bunna</t>
   </si>
   <si>
-    <t>Persita</t>
-  </si>
-  <si>
     <t>Arba Minch Kenema</t>
   </si>
   <si>
@@ -532,31 +532,31 @@
     <t>Al Dhafra</t>
   </si>
   <si>
+    <t>ENPPI</t>
+  </si>
+  <si>
     <t>Pyramids FC</t>
   </si>
   <si>
+    <t>Botev Vratsa</t>
+  </si>
+  <si>
     <t>Norrköping</t>
   </si>
   <si>
     <t>Zamalek</t>
   </si>
   <si>
-    <t>ENPPI</t>
-  </si>
-  <si>
-    <t>Botev Vratsa</t>
+    <t>Durban City</t>
+  </si>
+  <si>
+    <t>Orlando Pirates</t>
+  </si>
+  <si>
+    <t>Sekhukhune United</t>
   </si>
   <si>
     <t>Orbit College</t>
-  </si>
-  <si>
-    <t>Sekhukhune United</t>
-  </si>
-  <si>
-    <t>Durban City</t>
-  </si>
-  <si>
-    <t>Orlando Pirates</t>
   </si>
   <si>
     <t>Al Hilal</t>
@@ -2101,70 +2101,70 @@
         <v>0</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN7">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO7">
         <v>0</v>
@@ -2206,19 +2206,19 @@
         <v>0</v>
       </c>
       <c r="BB7">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC7">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BD7">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE7">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BF7">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG7">
         <v>0</v>
@@ -2656,70 +2656,70 @@
         <v>0</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AO10">
         <v>0</v>
@@ -2761,19 +2761,19 @@
         <v>0</v>
       </c>
       <c r="BB10">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="BD10">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="BE10">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BF10">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG10">
         <v>0</v>
@@ -3017,79 +3017,79 @@
         <v>184</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AO12">
         <v>0</v>
@@ -3131,19 +3131,19 @@
         <v>0</v>
       </c>
       <c r="BB12">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC12">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BD12">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BE12">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BF12">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG12">
         <v>0</v>
@@ -3211,70 +3211,70 @@
         <v>0</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN13">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AO13">
         <v>0</v>
@@ -3316,19 +3316,19 @@
         <v>0</v>
       </c>
       <c r="BB13">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC13">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD13">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE13">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BF13">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BG13">
         <v>0</v>
@@ -3396,70 +3396,70 @@
         <v>0</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO14">
         <v>0</v>
@@ -3501,19 +3501,19 @@
         <v>0</v>
       </c>
       <c r="BB14">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC14">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="BD14">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="BE14">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF14">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG14">
         <v>0</v>
@@ -3718,7 +3718,7 @@
         <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D16" t="s">
         <v>103</v>
@@ -3903,7 +3903,7 @@
         <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D17" t="s">
         <v>103</v>
@@ -4312,13 +4312,13 @@
         <v>184</v>
       </c>
       <c r="P19">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="Q19">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R19">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -4691,52 +4691,52 @@
         <v>3.49</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB21">
         <v>0</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AH21">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI21">
         <v>0</v>
@@ -4745,67 +4745,67 @@
         <v>0</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL21">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN21">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AO21">
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AU21">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AV21">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AW21">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AX21">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY21">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ21">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BA21">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="BB21">
         <v>0</v>
       </c>
       <c r="BC21">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BD21">
         <v>0</v>
       </c>
       <c r="BE21">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF21">
         <v>0</v>
@@ -5061,13 +5061,13 @@
         <v>1.8</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V23">
         <v>0</v>
@@ -5076,10 +5076,10 @@
         <v>0</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -5091,40 +5091,40 @@
         <v>0</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AH23">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI23">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL23">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AM23">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN23">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AO23">
         <v>0</v>
@@ -5169,13 +5169,13 @@
         <v>0</v>
       </c>
       <c r="BC23">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BD23">
         <v>0</v>
       </c>
       <c r="BE23">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF23">
         <v>0</v>
@@ -5616,13 +5616,13 @@
         <v>6.25</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="V26">
         <v>0</v>
@@ -5631,10 +5631,10 @@
         <v>0</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -5646,40 +5646,40 @@
         <v>0</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH26">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI26">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL26">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AM26">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AN26">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AO26">
         <v>0</v>
@@ -5724,13 +5724,13 @@
         <v>0</v>
       </c>
       <c r="BC26">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BD26">
         <v>0</v>
       </c>
       <c r="BE26">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BF26">
         <v>0</v>
@@ -5947,7 +5947,7 @@
         <v>131</v>
       </c>
       <c r="F28" t="s">
-        <v>142</v>
+        <v>171</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -6132,7 +6132,7 @@
         <v>132</v>
       </c>
       <c r="F29" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -6493,10 +6493,10 @@
         <v>79</v>
       </c>
       <c r="C31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D31" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E31" t="s">
         <v>134</v>
@@ -6532,13 +6532,13 @@
         <v>184</v>
       </c>
       <c r="P31">
-        <v>2.83</v>
+        <v>4</v>
       </c>
       <c r="Q31">
-        <v>3.46</v>
+        <v>3.1</v>
       </c>
       <c r="R31">
-        <v>2.32</v>
+        <v>1.8</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -6577,10 +6577,10 @@
         <v>0</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG31">
         <v>0</v>
@@ -6678,7 +6678,7 @@
         <v>79</v>
       </c>
       <c r="C32" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D32" t="s">
         <v>103</v>
@@ -6717,13 +6717,13 @@
         <v>184</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -6863,10 +6863,10 @@
         <v>79</v>
       </c>
       <c r="C33" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D33" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E33" t="s">
         <v>136</v>
@@ -6902,13 +6902,13 @@
         <v>184</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S33">
         <v>0</v>
@@ -7048,7 +7048,7 @@
         <v>79</v>
       </c>
       <c r="C34" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D34" t="s">
         <v>103</v>
@@ -7087,13 +7087,13 @@
         <v>184</v>
       </c>
       <c r="P34">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q34">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R34">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="S34">
         <v>0</v>
@@ -7272,133 +7272,133 @@
         <v>184</v>
       </c>
       <c r="P35">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="Q35">
         <v>2.8</v>
       </c>
       <c r="R35">
-        <v>3.89</v>
+        <v>3.4</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AH35">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI35">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL35">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM35">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN35">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AO35">
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AQ35">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AR35">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AS35">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AT35">
         <v>0</v>
       </c>
       <c r="AU35">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AV35">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AW35">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AX35">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AY35">
         <v>0</v>
       </c>
       <c r="AZ35">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BA35">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BB35">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BC35">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="BD35">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="BE35">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BF35">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="BG35">
         <v>0</v>
@@ -7457,133 +7457,133 @@
         <v>184</v>
       </c>
       <c r="P36">
-        <v>3.63</v>
+        <v>6.29</v>
       </c>
       <c r="Q36">
-        <v>3.02</v>
+        <v>3.48</v>
       </c>
       <c r="R36">
-        <v>2.03</v>
+        <v>1.53</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>6.93</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AH36">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI36">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL36">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM36">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN36">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AO36">
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AQ36">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AR36">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AS36">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AT36">
         <v>0</v>
       </c>
       <c r="AU36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV36">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AW36">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AX36">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AY36">
         <v>0</v>
       </c>
       <c r="AZ36">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BA36">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BB36">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BC36">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BD36">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BE36">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="BF36">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG36">
         <v>0</v>
@@ -7642,133 +7642,133 @@
         <v>184</v>
       </c>
       <c r="P37">
-        <v>2.2</v>
+        <v>3.63</v>
       </c>
       <c r="Q37">
+        <v>3.02</v>
+      </c>
+      <c r="R37">
+        <v>2.03</v>
+      </c>
+      <c r="S37">
+        <v>4.43</v>
+      </c>
+      <c r="T37">
+        <v>1.88</v>
+      </c>
+      <c r="U37">
+        <v>2.88</v>
+      </c>
+      <c r="V37">
+        <v>1.51</v>
+      </c>
+      <c r="W37">
+        <v>2.31</v>
+      </c>
+      <c r="X37">
+        <v>3.38</v>
+      </c>
+      <c r="Y37">
+        <v>1.25</v>
+      </c>
+      <c r="Z37">
+        <v>9.1</v>
+      </c>
+      <c r="AA37">
+        <v>1</v>
+      </c>
+      <c r="AB37">
+        <v>1.05</v>
+      </c>
+      <c r="AC37">
+        <v>1.43</v>
+      </c>
+      <c r="AD37">
+        <v>2.46</v>
+      </c>
+      <c r="AE37">
+        <v>2.44</v>
+      </c>
+      <c r="AF37">
+        <v>1.49</v>
+      </c>
+      <c r="AG37">
+        <v>4.6</v>
+      </c>
+      <c r="AH37">
+        <v>1.13</v>
+      </c>
+      <c r="AI37">
+        <v>8.5</v>
+      </c>
+      <c r="AJ37">
+        <v>1.03</v>
+      </c>
+      <c r="AK37">
+        <v>2.04</v>
+      </c>
+      <c r="AL37">
+        <v>1.68</v>
+      </c>
+      <c r="AM37">
+        <v>1.3</v>
+      </c>
+      <c r="AN37">
+        <v>1.24</v>
+      </c>
+      <c r="AO37">
+        <v>0</v>
+      </c>
+      <c r="AP37">
+        <v>1.37</v>
+      </c>
+      <c r="AQ37">
+        <v>1.63</v>
+      </c>
+      <c r="AR37">
+        <v>2.02</v>
+      </c>
+      <c r="AS37">
+        <v>2.6</v>
+      </c>
+      <c r="AT37">
+        <v>3.4</v>
+      </c>
+      <c r="AU37">
         <v>2.8</v>
       </c>
-      <c r="R37">
-        <v>3.4</v>
-      </c>
-      <c r="S37">
-        <v>0</v>
-      </c>
-      <c r="T37">
-        <v>0</v>
-      </c>
-      <c r="U37">
-        <v>0</v>
-      </c>
-      <c r="V37">
-        <v>0</v>
-      </c>
-      <c r="W37">
-        <v>0</v>
-      </c>
-      <c r="X37">
-        <v>0</v>
-      </c>
-      <c r="Y37">
-        <v>0</v>
-      </c>
-      <c r="Z37">
-        <v>0</v>
-      </c>
-      <c r="AA37">
-        <v>0</v>
-      </c>
-      <c r="AB37">
-        <v>0</v>
-      </c>
-      <c r="AC37">
-        <v>0</v>
-      </c>
-      <c r="AD37">
-        <v>0</v>
-      </c>
-      <c r="AE37">
-        <v>0</v>
-      </c>
-      <c r="AF37">
-        <v>0</v>
-      </c>
-      <c r="AG37">
-        <v>0</v>
-      </c>
-      <c r="AH37">
-        <v>0</v>
-      </c>
-      <c r="AI37">
-        <v>0</v>
-      </c>
-      <c r="AJ37">
-        <v>0</v>
-      </c>
-      <c r="AK37">
-        <v>0</v>
-      </c>
-      <c r="AL37">
-        <v>0</v>
-      </c>
-      <c r="AM37">
-        <v>0</v>
-      </c>
-      <c r="AN37">
-        <v>0</v>
-      </c>
-      <c r="AO37">
-        <v>0</v>
-      </c>
-      <c r="AP37">
-        <v>0</v>
-      </c>
-      <c r="AQ37">
-        <v>0</v>
-      </c>
-      <c r="AR37">
-        <v>0</v>
-      </c>
-      <c r="AS37">
-        <v>0</v>
-      </c>
-      <c r="AT37">
-        <v>0</v>
-      </c>
-      <c r="AU37">
-        <v>0</v>
-      </c>
       <c r="AV37">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AW37">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX37">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY37">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ37">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BA37">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BB37">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BC37">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="BD37">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BE37">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BF37">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG37">
         <v>0</v>
@@ -7827,133 +7827,133 @@
         <v>184</v>
       </c>
       <c r="P38">
-        <v>6.29</v>
+        <v>2.06</v>
       </c>
       <c r="Q38">
-        <v>3.48</v>
+        <v>2.8</v>
       </c>
       <c r="R38">
-        <v>1.53</v>
+        <v>3.89</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AH38">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AI38">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL38">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AM38">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN38">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AO38">
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AQ38">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AR38">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AS38">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AT38">
         <v>0</v>
       </c>
       <c r="AU38">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AV38">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AW38">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AX38">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AY38">
         <v>0</v>
       </c>
       <c r="AZ38">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BA38">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BB38">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="BC38">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="BD38">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BE38">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BF38">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BG38">
         <v>0</v>

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -337,15 +337,15 @@
     <t>Bucheon 1995</t>
   </si>
   <si>
+    <t>Gangwon</t>
+  </si>
+  <si>
+    <t>Daejeon Citizen</t>
+  </si>
+  <si>
     <t>Sangju Sangmu</t>
   </si>
   <si>
-    <t>Daejeon Citizen</t>
-  </si>
-  <si>
-    <t>Gangwon</t>
-  </si>
-  <si>
     <t>Madura United</t>
   </si>
   <si>
@@ -373,12 +373,12 @@
     <t>Karvan FK</t>
   </si>
   <si>
+    <t>Dire Dawa Kenema</t>
+  </si>
+  <si>
     <t>Borneo</t>
   </si>
   <si>
-    <t>Dire Dawa Kenema</t>
-  </si>
-  <si>
     <t>Mekelle Kenema</t>
   </si>
   <si>
@@ -409,39 +409,39 @@
     <t>Dibba Al Fujairah</t>
   </si>
   <si>
+    <t>Al Ittihad Kalba</t>
+  </si>
+  <si>
     <t>Bani Yas</t>
   </si>
   <si>
-    <t>Al Ittihad Kalba</t>
-  </si>
-  <si>
     <t>Al Ahly</t>
   </si>
   <si>
+    <t>Lokomotiv Sofia 1929</t>
+  </si>
+  <si>
+    <t>Falkenberg</t>
+  </si>
+  <si>
     <t>Ceramica Cleopatra</t>
   </si>
   <si>
-    <t>Lokomotiv Sofia 1929</t>
-  </si>
-  <si>
-    <t>Falkenberg</t>
-  </si>
-  <si>
     <t>Smouha SC</t>
   </si>
   <si>
+    <t>Magesi</t>
+  </si>
+  <si>
+    <t>Chippa United</t>
+  </si>
+  <si>
     <t>Siwelele</t>
   </si>
   <si>
     <t>Stellenbosch</t>
   </si>
   <si>
-    <t>Chippa United</t>
-  </si>
-  <si>
-    <t>Magesi</t>
-  </si>
-  <si>
     <t>Al Khaleej</t>
   </si>
   <si>
@@ -457,15 +457,15 @@
     <t>Jeju United</t>
   </si>
   <si>
+    <t>Pohang Steelers</t>
+  </si>
+  <si>
+    <t>Incheon United</t>
+  </si>
+  <si>
     <t>Ulsan</t>
   </si>
   <si>
-    <t>Incheon United</t>
-  </si>
-  <si>
-    <t>Pohang Steelers</t>
-  </si>
-  <si>
     <t>Bali United</t>
   </si>
   <si>
@@ -493,12 +493,12 @@
     <t>Neftçi</t>
   </si>
   <si>
+    <t>Ethiopia Bunna</t>
+  </si>
+  <si>
     <t>Persita</t>
   </si>
   <si>
-    <t>Ethiopia Bunna</t>
-  </si>
-  <si>
     <t>Arba Minch Kenema</t>
   </si>
   <si>
@@ -535,28 +535,28 @@
     <t>ENPPI</t>
   </si>
   <si>
+    <t>Botev Vratsa</t>
+  </si>
+  <si>
+    <t>Norrköping</t>
+  </si>
+  <si>
     <t>Pyramids FC</t>
   </si>
   <si>
-    <t>Botev Vratsa</t>
-  </si>
-  <si>
-    <t>Norrköping</t>
-  </si>
-  <si>
     <t>Zamalek</t>
   </si>
   <si>
+    <t>Orbit College</t>
+  </si>
+  <si>
+    <t>Sekhukhune United</t>
+  </si>
+  <si>
     <t>Durban City</t>
   </si>
   <si>
     <t>Orlando Pirates</t>
-  </si>
-  <si>
-    <t>Sekhukhune United</t>
-  </si>
-  <si>
-    <t>Orbit College</t>
   </si>
   <si>
     <t>Al Hilal</t>
@@ -2170,40 +2170,40 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU7">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="AV7">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AW7">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AX7">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AY7">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AZ7">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="BA7">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BB7">
         <v>1.16</v>
@@ -3718,7 +3718,7 @@
         <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D16" t="s">
         <v>103</v>
@@ -3903,7 +3903,7 @@
         <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D17" t="s">
         <v>103</v>
@@ -3942,133 +3942,133 @@
         <v>184</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI17">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM17">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AO17">
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AU17">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AV17">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AW17">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AX17">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AY17">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AZ17">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="BA17">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="BB17">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC17">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BD17">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="BE17">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BF17">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG17">
         <v>0</v>
@@ -5947,7 +5947,7 @@
         <v>131</v>
       </c>
       <c r="F28" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -6132,7 +6132,7 @@
         <v>132</v>
       </c>
       <c r="F29" t="s">
-        <v>142</v>
+        <v>171</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -6347,13 +6347,13 @@
         <v>184</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S30">
         <v>0</v>
@@ -6493,7 +6493,7 @@
         <v>79</v>
       </c>
       <c r="C31" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D31" t="s">
         <v>103</v>
@@ -6532,130 +6532,130 @@
         <v>184</v>
       </c>
       <c r="P31">
-        <v>4</v>
+        <v>1.95</v>
       </c>
       <c r="Q31">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R31">
+        <v>3.79</v>
+      </c>
+      <c r="S31">
+        <v>2.48</v>
+      </c>
+      <c r="T31">
+        <v>2.1</v>
+      </c>
+      <c r="U31">
+        <v>4.1</v>
+      </c>
+      <c r="V31">
+        <v>1.37</v>
+      </c>
+      <c r="W31">
+        <v>2.7</v>
+      </c>
+      <c r="X31">
+        <v>2.88</v>
+      </c>
+      <c r="Y31">
+        <v>1.33</v>
+      </c>
+      <c r="Z31">
+        <v>7</v>
+      </c>
+      <c r="AA31">
+        <v>1.03</v>
+      </c>
+      <c r="AB31">
+        <v>0</v>
+      </c>
+      <c r="AC31">
+        <v>1.32</v>
+      </c>
+      <c r="AD31">
+        <v>3</v>
+      </c>
+      <c r="AE31">
+        <v>2.02</v>
+      </c>
+      <c r="AF31">
+        <v>1.68</v>
+      </c>
+      <c r="AG31">
+        <v>3.6</v>
+      </c>
+      <c r="AH31">
+        <v>1.24</v>
+      </c>
+      <c r="AI31">
+        <v>6.75</v>
+      </c>
+      <c r="AJ31">
+        <v>1.07</v>
+      </c>
+      <c r="AK31">
         <v>1.8</v>
       </c>
-      <c r="S31">
-        <v>0</v>
-      </c>
-      <c r="T31">
-        <v>0</v>
-      </c>
-      <c r="U31">
-        <v>0</v>
-      </c>
-      <c r="V31">
-        <v>0</v>
-      </c>
-      <c r="W31">
-        <v>0</v>
-      </c>
-      <c r="X31">
-        <v>0</v>
-      </c>
-      <c r="Y31">
-        <v>0</v>
-      </c>
-      <c r="Z31">
-        <v>0</v>
-      </c>
-      <c r="AA31">
-        <v>0</v>
-      </c>
-      <c r="AB31">
-        <v>0</v>
-      </c>
-      <c r="AC31">
-        <v>0</v>
-      </c>
-      <c r="AD31">
-        <v>0</v>
-      </c>
-      <c r="AE31">
-        <v>2.2</v>
-      </c>
-      <c r="AF31">
-        <v>1.58</v>
-      </c>
-      <c r="AG31">
-        <v>0</v>
-      </c>
-      <c r="AH31">
-        <v>0</v>
-      </c>
-      <c r="AI31">
-        <v>0</v>
-      </c>
-      <c r="AJ31">
-        <v>0</v>
-      </c>
-      <c r="AK31">
-        <v>0</v>
-      </c>
       <c r="AL31">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM31">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN31">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO31">
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR31">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AU31">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV31">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AW31">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AX31">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY31">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ31">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BA31">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BB31">
         <v>0</v>
       </c>
       <c r="BC31">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD31">
         <v>0</v>
       </c>
       <c r="BE31">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF31">
         <v>0</v>
@@ -6678,10 +6678,10 @@
         <v>79</v>
       </c>
       <c r="C32" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D32" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E32" t="s">
         <v>135</v>
@@ -6717,13 +6717,13 @@
         <v>184</v>
       </c>
       <c r="P32">
-        <v>1.95</v>
+        <v>2.83</v>
       </c>
       <c r="Q32">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="R32">
-        <v>3.79</v>
+        <v>2.32</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -6863,10 +6863,10 @@
         <v>79</v>
       </c>
       <c r="C33" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E33" t="s">
         <v>136</v>
@@ -6902,133 +6902,133 @@
         <v>184</v>
       </c>
       <c r="P33">
-        <v>2.83</v>
+        <v>4</v>
       </c>
       <c r="Q33">
-        <v>3.46</v>
+        <v>3.1</v>
       </c>
       <c r="R33">
-        <v>2.32</v>
+        <v>1.8</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH33">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI33">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL33">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM33">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN33">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AO33">
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ33">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AR33">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS33">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT33">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AU33">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV33">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AW33">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AX33">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AY33">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AZ33">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="BA33">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BB33">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC33">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD33">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE33">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF33">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG33">
         <v>0</v>
@@ -7087,13 +7087,13 @@
         <v>184</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S34">
         <v>0</v>
@@ -7272,37 +7272,37 @@
         <v>184</v>
       </c>
       <c r="P35">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="Q35">
         <v>2.8</v>
       </c>
       <c r="R35">
-        <v>3.4</v>
+        <v>3.89</v>
       </c>
       <c r="S35">
-        <v>3.01</v>
+        <v>2.95</v>
       </c>
       <c r="T35">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="U35">
-        <v>4.53</v>
+        <v>5.15</v>
       </c>
       <c r="V35">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="W35">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="X35">
-        <v>4.1</v>
+        <v>3.92</v>
       </c>
       <c r="Y35">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z35">
-        <v>9.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA35">
         <v>1.02</v>
@@ -7311,94 +7311,94 @@
         <v>1.08</v>
       </c>
       <c r="AC35">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AD35">
-        <v>2.09</v>
+        <v>2.21</v>
       </c>
       <c r="AE35">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AF35">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG35">
-        <v>6.35</v>
+        <v>5.8</v>
       </c>
       <c r="AH35">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AI35">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AJ35">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AK35">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AL35">
+        <v>1.54</v>
+      </c>
+      <c r="AM35">
+        <v>1.35</v>
+      </c>
+      <c r="AN35">
+        <v>1.59</v>
+      </c>
+      <c r="AO35">
+        <v>0</v>
+      </c>
+      <c r="AP35">
+        <v>1.45</v>
+      </c>
+      <c r="AQ35">
+        <v>1.77</v>
+      </c>
+      <c r="AR35">
+        <v>2.23</v>
+      </c>
+      <c r="AS35">
+        <v>2.9</v>
+      </c>
+      <c r="AT35">
+        <v>0</v>
+      </c>
+      <c r="AU35">
+        <v>2.5</v>
+      </c>
+      <c r="AV35">
+        <v>1.92</v>
+      </c>
+      <c r="AW35">
+        <v>1.57</v>
+      </c>
+      <c r="AX35">
+        <v>1.35</v>
+      </c>
+      <c r="AY35">
+        <v>0</v>
+      </c>
+      <c r="AZ35">
         <v>1.5</v>
       </c>
-      <c r="AM35">
-        <v>1.32</v>
-      </c>
-      <c r="AN35">
-        <v>1.55</v>
-      </c>
-      <c r="AO35">
-        <v>0</v>
-      </c>
-      <c r="AP35">
-        <v>1.53</v>
-      </c>
-      <c r="AQ35">
-        <v>1.89</v>
-      </c>
-      <c r="AR35">
-        <v>2.45</v>
-      </c>
-      <c r="AS35">
-        <v>3.25</v>
-      </c>
-      <c r="AT35">
-        <v>0</v>
-      </c>
-      <c r="AU35">
-        <v>2.3</v>
-      </c>
-      <c r="AV35">
-        <v>1.79</v>
-      </c>
-      <c r="AW35">
-        <v>1.47</v>
-      </c>
-      <c r="AX35">
-        <v>1.28</v>
-      </c>
-      <c r="AY35">
-        <v>0</v>
-      </c>
-      <c r="AZ35">
-        <v>1.92</v>
-      </c>
       <c r="BA35">
-        <v>2.05</v>
+        <v>2.8</v>
       </c>
       <c r="BB35">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="BC35">
-        <v>3.12</v>
+        <v>2.91</v>
       </c>
       <c r="BD35">
-        <v>2.53</v>
+        <v>2.66</v>
       </c>
       <c r="BE35">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BF35">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="BG35">
         <v>0</v>
@@ -7457,133 +7457,133 @@
         <v>184</v>
       </c>
       <c r="P36">
-        <v>6.29</v>
+        <v>3.63</v>
       </c>
       <c r="Q36">
-        <v>3.48</v>
+        <v>3.02</v>
       </c>
       <c r="R36">
-        <v>1.53</v>
+        <v>2.03</v>
       </c>
       <c r="S36">
-        <v>6.93</v>
+        <v>4.43</v>
       </c>
       <c r="T36">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="U36">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="V36">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="W36">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="X36">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="Y36">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z36">
-        <v>7.8</v>
+        <v>9.1</v>
       </c>
       <c r="AA36">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AB36">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AC36">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AD36">
-        <v>2.35</v>
+        <v>2.46</v>
       </c>
       <c r="AE36">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="AF36">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AG36">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AH36">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AI36">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AJ36">
         <v>1.03</v>
       </c>
       <c r="AK36">
-        <v>2.4</v>
+        <v>2.04</v>
       </c>
       <c r="AL36">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AM36">
+        <v>1.3</v>
+      </c>
+      <c r="AN36">
+        <v>1.24</v>
+      </c>
+      <c r="AO36">
+        <v>0</v>
+      </c>
+      <c r="AP36">
+        <v>1.37</v>
+      </c>
+      <c r="AQ36">
+        <v>1.63</v>
+      </c>
+      <c r="AR36">
+        <v>2.02</v>
+      </c>
+      <c r="AS36">
+        <v>2.6</v>
+      </c>
+      <c r="AT36">
+        <v>3.4</v>
+      </c>
+      <c r="AU36">
+        <v>2.8</v>
+      </c>
+      <c r="AV36">
+        <v>2.1</v>
+      </c>
+      <c r="AW36">
+        <v>1.68</v>
+      </c>
+      <c r="AX36">
+        <v>1.43</v>
+      </c>
+      <c r="AY36">
         <v>1.26</v>
       </c>
-      <c r="AN36">
-        <v>1.07</v>
-      </c>
-      <c r="AO36">
-        <v>0</v>
-      </c>
-      <c r="AP36">
-        <v>1.7</v>
-      </c>
-      <c r="AQ36">
-        <v>2.15</v>
-      </c>
-      <c r="AR36">
-        <v>2.85</v>
-      </c>
-      <c r="AS36">
-        <v>3.85</v>
-      </c>
-      <c r="AT36">
-        <v>0</v>
-      </c>
-      <c r="AU36">
-        <v>2</v>
-      </c>
-      <c r="AV36">
-        <v>1.61</v>
-      </c>
-      <c r="AW36">
-        <v>1.36</v>
-      </c>
-      <c r="AX36">
-        <v>1.21</v>
-      </c>
-      <c r="AY36">
-        <v>0</v>
-      </c>
       <c r="AZ36">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="BA36">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="BB36">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="BC36">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="BD36">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="BE36">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="BF36">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="BG36">
         <v>0</v>
@@ -7642,133 +7642,133 @@
         <v>184</v>
       </c>
       <c r="P37">
-        <v>3.63</v>
+        <v>2.2</v>
       </c>
       <c r="Q37">
-        <v>3.02</v>
+        <v>2.8</v>
       </c>
       <c r="R37">
-        <v>2.03</v>
+        <v>3.4</v>
       </c>
       <c r="S37">
-        <v>4.43</v>
+        <v>3.01</v>
       </c>
       <c r="T37">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="U37">
-        <v>2.88</v>
+        <v>4.53</v>
       </c>
       <c r="V37">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="W37">
-        <v>2.31</v>
+        <v>2.17</v>
       </c>
       <c r="X37">
-        <v>3.38</v>
+        <v>4.1</v>
       </c>
       <c r="Y37">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="Z37">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA37">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AB37">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AC37">
+        <v>1.66</v>
+      </c>
+      <c r="AD37">
+        <v>2.09</v>
+      </c>
+      <c r="AE37">
+        <v>3</v>
+      </c>
+      <c r="AF37">
+        <v>1.36</v>
+      </c>
+      <c r="AG37">
+        <v>6.35</v>
+      </c>
+      <c r="AH37">
+        <v>1.06</v>
+      </c>
+      <c r="AI37">
+        <v>10.5</v>
+      </c>
+      <c r="AJ37">
+        <v>1.02</v>
+      </c>
+      <c r="AK37">
+        <v>2.4</v>
+      </c>
+      <c r="AL37">
+        <v>1.5</v>
+      </c>
+      <c r="AM37">
+        <v>1.32</v>
+      </c>
+      <c r="AN37">
+        <v>1.55</v>
+      </c>
+      <c r="AO37">
+        <v>0</v>
+      </c>
+      <c r="AP37">
+        <v>1.53</v>
+      </c>
+      <c r="AQ37">
+        <v>1.89</v>
+      </c>
+      <c r="AR37">
+        <v>2.45</v>
+      </c>
+      <c r="AS37">
+        <v>3.25</v>
+      </c>
+      <c r="AT37">
+        <v>0</v>
+      </c>
+      <c r="AU37">
+        <v>2.3</v>
+      </c>
+      <c r="AV37">
+        <v>1.79</v>
+      </c>
+      <c r="AW37">
+        <v>1.47</v>
+      </c>
+      <c r="AX37">
+        <v>1.28</v>
+      </c>
+      <c r="AY37">
+        <v>0</v>
+      </c>
+      <c r="AZ37">
+        <v>1.92</v>
+      </c>
+      <c r="BA37">
+        <v>2.05</v>
+      </c>
+      <c r="BB37">
         <v>1.43</v>
       </c>
-      <c r="AD37">
-        <v>2.46</v>
-      </c>
-      <c r="AE37">
-        <v>2.44</v>
-      </c>
-      <c r="AF37">
-        <v>1.49</v>
-      </c>
-      <c r="AG37">
-        <v>4.6</v>
-      </c>
-      <c r="AH37">
-        <v>1.13</v>
-      </c>
-      <c r="AI37">
-        <v>8.5</v>
-      </c>
-      <c r="AJ37">
-        <v>1.03</v>
-      </c>
-      <c r="AK37">
-        <v>2.04</v>
-      </c>
-      <c r="AL37">
-        <v>1.68</v>
-      </c>
-      <c r="AM37">
-        <v>1.3</v>
-      </c>
-      <c r="AN37">
-        <v>1.24</v>
-      </c>
-      <c r="AO37">
-        <v>0</v>
-      </c>
-      <c r="AP37">
-        <v>1.37</v>
-      </c>
-      <c r="AQ37">
-        <v>1.63</v>
-      </c>
-      <c r="AR37">
-        <v>2.02</v>
-      </c>
-      <c r="AS37">
-        <v>2.6</v>
-      </c>
-      <c r="AT37">
-        <v>3.4</v>
-      </c>
-      <c r="AU37">
-        <v>2.8</v>
-      </c>
-      <c r="AV37">
-        <v>2.1</v>
-      </c>
-      <c r="AW37">
-        <v>1.68</v>
-      </c>
-      <c r="AX37">
-        <v>1.43</v>
-      </c>
-      <c r="AY37">
-        <v>1.26</v>
-      </c>
-      <c r="AZ37">
-        <v>2.35</v>
-      </c>
-      <c r="BA37">
-        <v>1.68</v>
-      </c>
-      <c r="BB37">
-        <v>1.32</v>
-      </c>
       <c r="BC37">
-        <v>2.59</v>
+        <v>3.12</v>
       </c>
       <c r="BD37">
-        <v>2.96</v>
+        <v>2.53</v>
       </c>
       <c r="BE37">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="BF37">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="BG37">
         <v>0</v>
@@ -7827,133 +7827,133 @@
         <v>184</v>
       </c>
       <c r="P38">
-        <v>2.06</v>
+        <v>6.29</v>
       </c>
       <c r="Q38">
-        <v>2.8</v>
+        <v>3.48</v>
       </c>
       <c r="R38">
-        <v>3.89</v>
+        <v>1.53</v>
       </c>
       <c r="S38">
-        <v>2.95</v>
+        <v>6.93</v>
       </c>
       <c r="T38">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="U38">
-        <v>5.15</v>
+        <v>2.3</v>
       </c>
       <c r="V38">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="W38">
-        <v>2.11</v>
+        <v>2.28</v>
       </c>
       <c r="X38">
-        <v>3.92</v>
+        <v>3.5</v>
       </c>
       <c r="Y38">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z38">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AA38">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AB38">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AC38">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="AD38">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="AE38">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AF38">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AG38">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="AH38">
+        <v>1.11</v>
+      </c>
+      <c r="AI38">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AJ38">
+        <v>1.03</v>
+      </c>
+      <c r="AK38">
+        <v>2.4</v>
+      </c>
+      <c r="AL38">
+        <v>1.5</v>
+      </c>
+      <c r="AM38">
+        <v>1.26</v>
+      </c>
+      <c r="AN38">
         <v>1.07</v>
       </c>
-      <c r="AI38">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AJ38">
-        <v>1.01</v>
-      </c>
-      <c r="AK38">
-        <v>2.3</v>
-      </c>
-      <c r="AL38">
-        <v>1.54</v>
-      </c>
-      <c r="AM38">
+      <c r="AO38">
+        <v>0</v>
+      </c>
+      <c r="AP38">
+        <v>1.7</v>
+      </c>
+      <c r="AQ38">
+        <v>2.15</v>
+      </c>
+      <c r="AR38">
+        <v>2.85</v>
+      </c>
+      <c r="AS38">
+        <v>3.85</v>
+      </c>
+      <c r="AT38">
+        <v>0</v>
+      </c>
+      <c r="AU38">
+        <v>2</v>
+      </c>
+      <c r="AV38">
+        <v>1.61</v>
+      </c>
+      <c r="AW38">
+        <v>1.36</v>
+      </c>
+      <c r="AX38">
+        <v>1.21</v>
+      </c>
+      <c r="AY38">
+        <v>0</v>
+      </c>
+      <c r="AZ38">
+        <v>3.1</v>
+      </c>
+      <c r="BA38">
+        <v>1.44</v>
+      </c>
+      <c r="BB38">
         <v>1.35</v>
       </c>
-      <c r="AN38">
-        <v>1.59</v>
-      </c>
-      <c r="AO38">
-        <v>0</v>
-      </c>
-      <c r="AP38">
-        <v>1.45</v>
-      </c>
-      <c r="AQ38">
-        <v>1.77</v>
-      </c>
-      <c r="AR38">
-        <v>2.23</v>
-      </c>
-      <c r="AS38">
-        <v>2.9</v>
-      </c>
-      <c r="AT38">
-        <v>0</v>
-      </c>
-      <c r="AU38">
-        <v>2.5</v>
-      </c>
-      <c r="AV38">
-        <v>1.92</v>
-      </c>
-      <c r="AW38">
-        <v>1.57</v>
-      </c>
-      <c r="AX38">
-        <v>1.35</v>
-      </c>
-      <c r="AY38">
-        <v>0</v>
-      </c>
-      <c r="AZ38">
-        <v>1.5</v>
-      </c>
-      <c r="BA38">
-        <v>2.8</v>
-      </c>
-      <c r="BB38">
+      <c r="BC38">
+        <v>2.66</v>
+      </c>
+      <c r="BD38">
+        <v>2.82</v>
+      </c>
+      <c r="BE38">
         <v>1.39</v>
       </c>
-      <c r="BC38">
-        <v>2.91</v>
-      </c>
-      <c r="BD38">
-        <v>2.66</v>
-      </c>
-      <c r="BE38">
-        <v>1.33</v>
-      </c>
       <c r="BF38">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BG38">
         <v>0</v>
@@ -8206,40 +8206,40 @@
         <v>5.28</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE40">
         <v>1.95</v>
@@ -8248,82 +8248,82 @@
         <v>1.75</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AH40">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI40">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AL40">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AM40">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN40">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO40">
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ40">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR40">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS40">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AT40">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU40">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AV40">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW40">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX40">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AY40">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AZ40">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BA40">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BB40">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC40">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD40">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="BE40">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF40">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG40">
         <v>0</v>

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -331,54 +331,54 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Bucheon 1995</t>
+  </si>
+  <si>
     <t>Jeonbuk Motors</t>
   </si>
   <si>
-    <t>Bucheon 1995</t>
+    <t>Daejeon Citizen</t>
   </si>
   <si>
     <t>Gangwon</t>
   </si>
   <si>
-    <t>Daejeon Citizen</t>
-  </si>
-  <si>
     <t>Sangju Sangmu</t>
   </si>
   <si>
     <t>Madura United</t>
   </si>
   <si>
+    <t>Ethiopia Nigd Bank</t>
+  </si>
+  <si>
     <t>FC Seoul</t>
   </si>
   <si>
-    <t>Ethiopia Nigd Bank</t>
-  </si>
-  <si>
     <t>Qingdao Youth Island</t>
   </si>
   <si>
     <t>Tanjong Pagar</t>
   </si>
   <si>
+    <t>Shenyang Urban</t>
+  </si>
+  <si>
     <t>Shandong Luneng</t>
   </si>
   <si>
-    <t>Shenyang Urban</t>
+    <t>Karvan FK</t>
   </si>
   <si>
     <t>Chongqing Tongliang Long</t>
   </si>
   <si>
-    <t>Karvan FK</t>
+    <t>Borneo</t>
   </si>
   <si>
     <t>Dire Dawa Kenema</t>
   </si>
   <si>
-    <t>Borneo</t>
-  </si>
-  <si>
     <t>Mekelle Kenema</t>
   </si>
   <si>
@@ -418,16 +418,19 @@
     <t>Al Ahly</t>
   </si>
   <si>
+    <t>Smouha SC</t>
+  </si>
+  <si>
+    <t>Falkenberg</t>
+  </si>
+  <si>
     <t>Lokomotiv Sofia 1929</t>
   </si>
   <si>
-    <t>Falkenberg</t>
-  </si>
-  <si>
     <t>Ceramica Cleopatra</t>
   </si>
   <si>
-    <t>Smouha SC</t>
+    <t>Siwelele</t>
   </si>
   <si>
     <t>Magesi</t>
@@ -436,9 +439,6 @@
     <t>Chippa United</t>
   </si>
   <si>
-    <t>Siwelele</t>
-  </si>
-  <si>
     <t>Stellenbosch</t>
   </si>
   <si>
@@ -451,54 +451,54 @@
     <t>New York City II</t>
   </si>
   <si>
+    <t>Jeju United</t>
+  </si>
+  <si>
     <t>Gwangju</t>
   </si>
   <si>
-    <t>Jeju United</t>
+    <t>Incheon United</t>
   </si>
   <si>
     <t>Pohang Steelers</t>
   </si>
   <si>
-    <t>Incheon United</t>
-  </si>
-  <si>
     <t>Ulsan</t>
   </si>
   <si>
     <t>Bali United</t>
   </si>
   <si>
+    <t>Kedus Giorgis</t>
+  </si>
+  <si>
     <t>Anyang</t>
   </si>
   <si>
-    <t>Kedus Giorgis</t>
-  </si>
-  <si>
     <t>Tianjin Teda</t>
   </si>
   <si>
     <t>Hougang United</t>
   </si>
   <si>
+    <t>Chengdu Better City FC</t>
+  </si>
+  <si>
     <t>Shanghai Shenhua</t>
   </si>
   <si>
-    <t>Chengdu Better City FC</t>
+    <t>Neftçi</t>
   </si>
   <si>
     <t>Henan Jianye</t>
   </si>
   <si>
-    <t>Neftçi</t>
+    <t>Persita</t>
   </si>
   <si>
     <t>Ethiopia Bunna</t>
   </si>
   <si>
-    <t>Persita</t>
-  </si>
-  <si>
     <t>Arba Minch Kenema</t>
   </si>
   <si>
@@ -535,25 +535,25 @@
     <t>ENPPI</t>
   </si>
   <si>
+    <t>Zamalek</t>
+  </si>
+  <si>
+    <t>Norrköping</t>
+  </si>
+  <si>
     <t>Botev Vratsa</t>
   </si>
   <si>
-    <t>Norrköping</t>
-  </si>
-  <si>
     <t>Pyramids FC</t>
   </si>
   <si>
-    <t>Zamalek</t>
+    <t>Durban City</t>
   </si>
   <si>
     <t>Orbit College</t>
   </si>
   <si>
     <t>Sekhukhune United</t>
-  </si>
-  <si>
-    <t>Durban City</t>
   </si>
   <si>
     <t>Orlando Pirates</t>
@@ -2238,10 +2238,10 @@
         <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E8" t="s">
         <v>111</v>
@@ -2423,10 +2423,10 @@
         <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E9" t="s">
         <v>112</v>
@@ -2656,70 +2656,70 @@
         <v>0</v>
       </c>
       <c r="S10">
-        <v>2.62</v>
+        <v>2.51</v>
       </c>
       <c r="T10">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="U10">
-        <v>4.15</v>
+        <v>4.4</v>
       </c>
       <c r="V10">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W10">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="X10">
-        <v>2.85</v>
+        <v>2.77</v>
       </c>
       <c r="Y10">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z10">
-        <v>6.75</v>
+        <v>6.55</v>
       </c>
       <c r="AA10">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AB10">
         <v>1.02</v>
       </c>
       <c r="AC10">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AD10">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="AE10">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AF10">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AG10">
-        <v>3.34</v>
+        <v>3.14</v>
       </c>
       <c r="AH10">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AI10">
-        <v>6.3</v>
+        <v>5.95</v>
       </c>
       <c r="AJ10">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK10">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AL10">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AM10">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AN10">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AO10">
         <v>0</v>
@@ -2761,19 +2761,19 @@
         <v>0</v>
       </c>
       <c r="BB10">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BC10">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="BD10">
-        <v>3.44</v>
+        <v>3.58</v>
       </c>
       <c r="BE10">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="BF10">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BG10">
         <v>0</v>
@@ -3017,79 +3017,79 @@
         <v>184</v>
       </c>
       <c r="P12">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>3.12</v>
+        <v>5.65</v>
       </c>
       <c r="T12">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="U12">
-        <v>2.89</v>
+        <v>2.01</v>
       </c>
       <c r="V12">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="W12">
-        <v>3.44</v>
+        <v>3.05</v>
       </c>
       <c r="X12">
-        <v>2.17</v>
+        <v>2.56</v>
       </c>
       <c r="Y12">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="Z12">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="AA12">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AB12">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC12">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="AD12">
-        <v>5.15</v>
+        <v>3.58</v>
       </c>
       <c r="AE12">
-        <v>1.44</v>
+        <v>1.81</v>
       </c>
       <c r="AF12">
-        <v>2.43</v>
+        <v>2.02</v>
       </c>
       <c r="AG12">
-        <v>2.25</v>
+        <v>2.83</v>
       </c>
       <c r="AH12">
-        <v>1.66</v>
+        <v>1.33</v>
       </c>
       <c r="AI12">
-        <v>3.58</v>
+        <v>5.25</v>
       </c>
       <c r="AJ12">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="AK12">
-        <v>1.4</v>
+        <v>1.84</v>
       </c>
       <c r="AL12">
-        <v>2.73</v>
+        <v>1.86</v>
       </c>
       <c r="AM12">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AN12">
-        <v>1.47</v>
+        <v>1.13</v>
       </c>
       <c r="AO12">
         <v>0</v>
@@ -3131,19 +3131,19 @@
         <v>0</v>
       </c>
       <c r="BB12">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="BC12">
-        <v>1.69</v>
+        <v>2.01</v>
       </c>
       <c r="BD12">
-        <v>5.3</v>
+        <v>4.05</v>
       </c>
       <c r="BE12">
-        <v>2.08</v>
+        <v>1.74</v>
       </c>
       <c r="BF12">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="BG12">
         <v>0</v>
@@ -3202,79 +3202,79 @@
         <v>184</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S13">
-        <v>5.25</v>
+        <v>2.95</v>
       </c>
       <c r="T13">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="U13">
-        <v>2.05</v>
+        <v>3.02</v>
       </c>
       <c r="V13">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W13">
-        <v>3.16</v>
+        <v>3.6</v>
       </c>
       <c r="X13">
-        <v>2.47</v>
+        <v>2.08</v>
       </c>
       <c r="Y13">
-        <v>1.47</v>
+        <v>1.69</v>
       </c>
       <c r="Z13">
-        <v>5.75</v>
+        <v>4.45</v>
       </c>
       <c r="AA13">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AB13">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC13">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AD13">
-        <v>3.86</v>
+        <v>5.65</v>
       </c>
       <c r="AE13">
+        <v>1.39</v>
+      </c>
+      <c r="AF13">
+        <v>2.59</v>
+      </c>
+      <c r="AG13">
+        <v>2.1</v>
+      </c>
+      <c r="AH13">
         <v>1.75</v>
       </c>
-      <c r="AF13">
-        <v>2.1</v>
-      </c>
-      <c r="AG13">
-        <v>2.69</v>
-      </c>
-      <c r="AH13">
+      <c r="AI13">
+        <v>3.28</v>
+      </c>
+      <c r="AJ13">
+        <v>1.25</v>
+      </c>
+      <c r="AK13">
         <v>1.36</v>
       </c>
-      <c r="AI13">
-        <v>4.95</v>
-      </c>
-      <c r="AJ13">
-        <v>1.11</v>
-      </c>
-      <c r="AK13">
-        <v>1.76</v>
-      </c>
       <c r="AL13">
-        <v>1.96</v>
+        <v>2.9</v>
       </c>
       <c r="AM13">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AN13">
-        <v>1.15</v>
+        <v>1.51</v>
       </c>
       <c r="AO13">
         <v>0</v>
@@ -3316,19 +3316,19 @@
         <v>0</v>
       </c>
       <c r="BB13">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="BC13">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="BD13">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="BE13">
-        <v>1.78</v>
+        <v>2.17</v>
       </c>
       <c r="BF13">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="BG13">
         <v>0</v>
@@ -3348,10 +3348,10 @@
         <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E14" t="s">
         <v>117</v>
@@ -3396,70 +3396,70 @@
         <v>0</v>
       </c>
       <c r="S14">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AD14">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AH14">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI14">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AJ14">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK14">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AL14">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AM14">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN14">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO14">
         <v>0</v>
@@ -3501,19 +3501,19 @@
         <v>0</v>
       </c>
       <c r="BB14">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC14">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="BD14">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="BE14">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BF14">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG14">
         <v>0</v>
@@ -3533,10 +3533,10 @@
         <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E15" t="s">
         <v>118</v>
@@ -3718,7 +3718,7 @@
         <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D16" t="s">
         <v>103</v>
@@ -3757,133 +3757,133 @@
         <v>184</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM16">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AO16">
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AU16">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AV16">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AW16">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AX16">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AY16">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AZ16">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="BA16">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="BB16">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC16">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BD16">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="BE16">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BF16">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG16">
         <v>0</v>
@@ -3903,7 +3903,7 @@
         <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D17" t="s">
         <v>103</v>
@@ -3942,133 +3942,133 @@
         <v>184</v>
       </c>
       <c r="P17">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R17">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>5.61</v>
+        <v>0</v>
       </c>
       <c r="V17">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W17">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X17">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y17">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z17">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA17">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC17">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD17">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AE17">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AG17">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AH17">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AI17">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AJ17">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK17">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM17">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AN17">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AO17">
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ17">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AR17">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AS17">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AT17">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AU17">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AV17">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="AW17">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AX17">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AY17">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AZ17">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="BA17">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="BB17">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC17">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BD17">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="BE17">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BF17">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG17">
         <v>0</v>
@@ -6493,7 +6493,7 @@
         <v>79</v>
       </c>
       <c r="C31" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D31" t="s">
         <v>103</v>
@@ -6532,130 +6532,130 @@
         <v>184</v>
       </c>
       <c r="P31">
-        <v>1.95</v>
+        <v>4.6</v>
       </c>
       <c r="Q31">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R31">
-        <v>3.79</v>
+        <v>1.72</v>
       </c>
       <c r="S31">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="T31">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U31">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="V31">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W31">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X31">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y31">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z31">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA31">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB31">
         <v>0</v>
       </c>
       <c r="AC31">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD31">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE31">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF31">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG31">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AH31">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI31">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AJ31">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK31">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL31">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AM31">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN31">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AO31">
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AQ31">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AR31">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS31">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AT31">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AU31">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV31">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AW31">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AX31">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AY31">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ31">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BA31">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BB31">
         <v>0</v>
       </c>
       <c r="BC31">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD31">
         <v>0</v>
       </c>
       <c r="BE31">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BF31">
         <v>0</v>
@@ -6863,7 +6863,7 @@
         <v>79</v>
       </c>
       <c r="C33" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D33" t="s">
         <v>103</v>
@@ -6902,133 +6902,133 @@
         <v>184</v>
       </c>
       <c r="P33">
-        <v>4</v>
+        <v>1.95</v>
       </c>
       <c r="Q33">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R33">
+        <v>3.79</v>
+      </c>
+      <c r="S33">
+        <v>2.48</v>
+      </c>
+      <c r="T33">
+        <v>2.1</v>
+      </c>
+      <c r="U33">
+        <v>4.1</v>
+      </c>
+      <c r="V33">
+        <v>1.37</v>
+      </c>
+      <c r="W33">
+        <v>2.7</v>
+      </c>
+      <c r="X33">
+        <v>2.88</v>
+      </c>
+      <c r="Y33">
+        <v>1.33</v>
+      </c>
+      <c r="Z33">
+        <v>7</v>
+      </c>
+      <c r="AA33">
+        <v>1.03</v>
+      </c>
+      <c r="AB33">
+        <v>0</v>
+      </c>
+      <c r="AC33">
+        <v>1.32</v>
+      </c>
+      <c r="AD33">
+        <v>3</v>
+      </c>
+      <c r="AE33">
+        <v>2.02</v>
+      </c>
+      <c r="AF33">
+        <v>1.68</v>
+      </c>
+      <c r="AG33">
+        <v>3.6</v>
+      </c>
+      <c r="AH33">
+        <v>1.24</v>
+      </c>
+      <c r="AI33">
+        <v>6.75</v>
+      </c>
+      <c r="AJ33">
+        <v>1.07</v>
+      </c>
+      <c r="AK33">
         <v>1.8</v>
       </c>
-      <c r="S33">
-        <v>5.29</v>
-      </c>
-      <c r="T33">
-        <v>1.96</v>
-      </c>
-      <c r="U33">
-        <v>2.46</v>
-      </c>
-      <c r="V33">
-        <v>1.47</v>
-      </c>
-      <c r="W33">
-        <v>2.41</v>
-      </c>
-      <c r="X33">
-        <v>3.08</v>
-      </c>
-      <c r="Y33">
-        <v>1.3</v>
-      </c>
-      <c r="Z33">
-        <v>7.7</v>
-      </c>
-      <c r="AA33">
-        <v>1.02</v>
-      </c>
-      <c r="AB33">
-        <v>1.04</v>
-      </c>
-      <c r="AC33">
-        <v>1.35</v>
-      </c>
-      <c r="AD33">
-        <v>2.74</v>
-      </c>
-      <c r="AE33">
-        <v>2.2</v>
-      </c>
-      <c r="AF33">
-        <v>1.58</v>
-      </c>
-      <c r="AG33">
-        <v>3.8</v>
-      </c>
-      <c r="AH33">
-        <v>1.19</v>
-      </c>
-      <c r="AI33">
-        <v>7.3</v>
-      </c>
-      <c r="AJ33">
-        <v>1.03</v>
-      </c>
-      <c r="AK33">
-        <v>1.97</v>
-      </c>
       <c r="AL33">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AM33">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AN33">
-        <v>1.14</v>
+        <v>1.75</v>
       </c>
       <c r="AO33">
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AQ33">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AR33">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AS33">
         <v>2.7</v>
       </c>
       <c r="AT33">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="AU33">
         <v>2.7</v>
       </c>
       <c r="AV33">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AW33">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AX33">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AY33">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AZ33">
-        <v>2.65</v>
+        <v>1.68</v>
       </c>
       <c r="BA33">
-        <v>1.55</v>
+        <v>2.5</v>
       </c>
       <c r="BB33">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BC33">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="BD33">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BE33">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="BF33">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG33">
         <v>0</v>
@@ -7087,133 +7087,133 @@
         <v>184</v>
       </c>
       <c r="P34">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="Q34">
         <v>3.1</v>
       </c>
       <c r="R34">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH34">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI34">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL34">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM34">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN34">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AO34">
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ34">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AR34">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS34">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT34">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AU34">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV34">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AW34">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AX34">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AY34">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AZ34">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="BA34">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BB34">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC34">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD34">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE34">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF34">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG34">
         <v>0</v>
@@ -7272,37 +7272,37 @@
         <v>184</v>
       </c>
       <c r="P35">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="Q35">
         <v>2.8</v>
       </c>
       <c r="R35">
-        <v>3.89</v>
+        <v>3.4</v>
       </c>
       <c r="S35">
-        <v>2.95</v>
+        <v>3.01</v>
       </c>
       <c r="T35">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="U35">
-        <v>5.15</v>
+        <v>4.53</v>
       </c>
       <c r="V35">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="W35">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="X35">
-        <v>3.92</v>
+        <v>4.1</v>
       </c>
       <c r="Y35">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z35">
-        <v>8.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA35">
         <v>1.02</v>
@@ -7311,94 +7311,94 @@
         <v>1.08</v>
       </c>
       <c r="AC35">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="AD35">
-        <v>2.21</v>
+        <v>2.09</v>
       </c>
       <c r="AE35">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AF35">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG35">
-        <v>5.8</v>
+        <v>6.35</v>
       </c>
       <c r="AH35">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AI35">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AJ35">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AK35">
+        <v>2.4</v>
+      </c>
+      <c r="AL35">
+        <v>1.5</v>
+      </c>
+      <c r="AM35">
+        <v>1.32</v>
+      </c>
+      <c r="AN35">
+        <v>1.55</v>
+      </c>
+      <c r="AO35">
+        <v>0</v>
+      </c>
+      <c r="AP35">
+        <v>1.53</v>
+      </c>
+      <c r="AQ35">
+        <v>1.89</v>
+      </c>
+      <c r="AR35">
+        <v>2.45</v>
+      </c>
+      <c r="AS35">
+        <v>3.25</v>
+      </c>
+      <c r="AT35">
+        <v>0</v>
+      </c>
+      <c r="AU35">
         <v>2.3</v>
       </c>
-      <c r="AL35">
-        <v>1.54</v>
-      </c>
-      <c r="AM35">
-        <v>1.35</v>
-      </c>
-      <c r="AN35">
-        <v>1.59</v>
-      </c>
-      <c r="AO35">
-        <v>0</v>
-      </c>
-      <c r="AP35">
-        <v>1.45</v>
-      </c>
-      <c r="AQ35">
-        <v>1.77</v>
-      </c>
-      <c r="AR35">
-        <v>2.23</v>
-      </c>
-      <c r="AS35">
-        <v>2.9</v>
-      </c>
-      <c r="AT35">
-        <v>0</v>
-      </c>
-      <c r="AU35">
-        <v>2.5</v>
-      </c>
       <c r="AV35">
+        <v>1.79</v>
+      </c>
+      <c r="AW35">
+        <v>1.47</v>
+      </c>
+      <c r="AX35">
+        <v>1.28</v>
+      </c>
+      <c r="AY35">
+        <v>0</v>
+      </c>
+      <c r="AZ35">
         <v>1.92</v>
       </c>
-      <c r="AW35">
-        <v>1.57</v>
-      </c>
-      <c r="AX35">
-        <v>1.35</v>
-      </c>
-      <c r="AY35">
-        <v>0</v>
-      </c>
-      <c r="AZ35">
-        <v>1.5</v>
-      </c>
       <c r="BA35">
-        <v>2.8</v>
+        <v>2.05</v>
       </c>
       <c r="BB35">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="BC35">
-        <v>2.91</v>
+        <v>3.12</v>
       </c>
       <c r="BD35">
-        <v>2.66</v>
+        <v>2.53</v>
       </c>
       <c r="BE35">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="BF35">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BG35">
         <v>0</v>
@@ -7457,133 +7457,133 @@
         <v>184</v>
       </c>
       <c r="P36">
-        <v>3.63</v>
+        <v>2.06</v>
       </c>
       <c r="Q36">
-        <v>3.02</v>
+        <v>2.8</v>
       </c>
       <c r="R36">
-        <v>2.03</v>
+        <v>3.89</v>
       </c>
       <c r="S36">
-        <v>4.43</v>
+        <v>2.95</v>
       </c>
       <c r="T36">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="U36">
-        <v>2.88</v>
+        <v>5.15</v>
       </c>
       <c r="V36">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="W36">
-        <v>2.31</v>
+        <v>2.11</v>
       </c>
       <c r="X36">
-        <v>3.38</v>
+        <v>3.92</v>
       </c>
       <c r="Y36">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z36">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA36">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AB36">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AC36">
-        <v>1.43</v>
+        <v>1.59</v>
       </c>
       <c r="AD36">
-        <v>2.46</v>
+        <v>2.21</v>
       </c>
       <c r="AE36">
-        <v>2.44</v>
+        <v>2.75</v>
       </c>
       <c r="AF36">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AG36">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="AH36">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AI36">
-        <v>8.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AJ36">
+        <v>1.01</v>
+      </c>
+      <c r="AK36">
+        <v>2.3</v>
+      </c>
+      <c r="AL36">
+        <v>1.54</v>
+      </c>
+      <c r="AM36">
+        <v>1.35</v>
+      </c>
+      <c r="AN36">
+        <v>1.59</v>
+      </c>
+      <c r="AO36">
+        <v>0</v>
+      </c>
+      <c r="AP36">
+        <v>1.45</v>
+      </c>
+      <c r="AQ36">
+        <v>1.77</v>
+      </c>
+      <c r="AR36">
+        <v>2.23</v>
+      </c>
+      <c r="AS36">
+        <v>2.9</v>
+      </c>
+      <c r="AT36">
+        <v>0</v>
+      </c>
+      <c r="AU36">
+        <v>2.5</v>
+      </c>
+      <c r="AV36">
+        <v>1.92</v>
+      </c>
+      <c r="AW36">
+        <v>1.57</v>
+      </c>
+      <c r="AX36">
+        <v>1.35</v>
+      </c>
+      <c r="AY36">
+        <v>0</v>
+      </c>
+      <c r="AZ36">
+        <v>1.5</v>
+      </c>
+      <c r="BA36">
+        <v>2.8</v>
+      </c>
+      <c r="BB36">
+        <v>1.39</v>
+      </c>
+      <c r="BC36">
+        <v>2.91</v>
+      </c>
+      <c r="BD36">
+        <v>2.66</v>
+      </c>
+      <c r="BE36">
+        <v>1.33</v>
+      </c>
+      <c r="BF36">
         <v>1.03</v>
-      </c>
-      <c r="AK36">
-        <v>2.04</v>
-      </c>
-      <c r="AL36">
-        <v>1.68</v>
-      </c>
-      <c r="AM36">
-        <v>1.3</v>
-      </c>
-      <c r="AN36">
-        <v>1.24</v>
-      </c>
-      <c r="AO36">
-        <v>0</v>
-      </c>
-      <c r="AP36">
-        <v>1.37</v>
-      </c>
-      <c r="AQ36">
-        <v>1.63</v>
-      </c>
-      <c r="AR36">
-        <v>2.02</v>
-      </c>
-      <c r="AS36">
-        <v>2.6</v>
-      </c>
-      <c r="AT36">
-        <v>3.4</v>
-      </c>
-      <c r="AU36">
-        <v>2.8</v>
-      </c>
-      <c r="AV36">
-        <v>2.1</v>
-      </c>
-      <c r="AW36">
-        <v>1.68</v>
-      </c>
-      <c r="AX36">
-        <v>1.43</v>
-      </c>
-      <c r="AY36">
-        <v>1.26</v>
-      </c>
-      <c r="AZ36">
-        <v>2.35</v>
-      </c>
-      <c r="BA36">
-        <v>1.68</v>
-      </c>
-      <c r="BB36">
-        <v>1.32</v>
-      </c>
-      <c r="BC36">
-        <v>2.59</v>
-      </c>
-      <c r="BD36">
-        <v>2.96</v>
-      </c>
-      <c r="BE36">
-        <v>1.41</v>
-      </c>
-      <c r="BF36">
-        <v>1.06</v>
       </c>
       <c r="BG36">
         <v>0</v>
@@ -7642,133 +7642,133 @@
         <v>184</v>
       </c>
       <c r="P37">
-        <v>2.2</v>
+        <v>3.63</v>
       </c>
       <c r="Q37">
+        <v>3.02</v>
+      </c>
+      <c r="R37">
+        <v>2.03</v>
+      </c>
+      <c r="S37">
+        <v>4.43</v>
+      </c>
+      <c r="T37">
+        <v>1.88</v>
+      </c>
+      <c r="U37">
+        <v>2.88</v>
+      </c>
+      <c r="V37">
+        <v>1.51</v>
+      </c>
+      <c r="W37">
+        <v>2.31</v>
+      </c>
+      <c r="X37">
+        <v>3.38</v>
+      </c>
+      <c r="Y37">
+        <v>1.25</v>
+      </c>
+      <c r="Z37">
+        <v>9.1</v>
+      </c>
+      <c r="AA37">
+        <v>1</v>
+      </c>
+      <c r="AB37">
+        <v>1.05</v>
+      </c>
+      <c r="AC37">
+        <v>1.43</v>
+      </c>
+      <c r="AD37">
+        <v>2.46</v>
+      </c>
+      <c r="AE37">
+        <v>2.44</v>
+      </c>
+      <c r="AF37">
+        <v>1.49</v>
+      </c>
+      <c r="AG37">
+        <v>4.6</v>
+      </c>
+      <c r="AH37">
+        <v>1.13</v>
+      </c>
+      <c r="AI37">
+        <v>8.5</v>
+      </c>
+      <c r="AJ37">
+        <v>1.03</v>
+      </c>
+      <c r="AK37">
+        <v>2.04</v>
+      </c>
+      <c r="AL37">
+        <v>1.68</v>
+      </c>
+      <c r="AM37">
+        <v>1.3</v>
+      </c>
+      <c r="AN37">
+        <v>1.24</v>
+      </c>
+      <c r="AO37">
+        <v>0</v>
+      </c>
+      <c r="AP37">
+        <v>1.37</v>
+      </c>
+      <c r="AQ37">
+        <v>1.63</v>
+      </c>
+      <c r="AR37">
+        <v>2.02</v>
+      </c>
+      <c r="AS37">
+        <v>2.6</v>
+      </c>
+      <c r="AT37">
+        <v>3.4</v>
+      </c>
+      <c r="AU37">
         <v>2.8</v>
       </c>
-      <c r="R37">
-        <v>3.4</v>
-      </c>
-      <c r="S37">
-        <v>3.01</v>
-      </c>
-      <c r="T37">
-        <v>1.81</v>
-      </c>
-      <c r="U37">
-        <v>4.53</v>
-      </c>
-      <c r="V37">
-        <v>1.61</v>
-      </c>
-      <c r="W37">
-        <v>2.17</v>
-      </c>
-      <c r="X37">
-        <v>4.1</v>
-      </c>
-      <c r="Y37">
-        <v>1.16</v>
-      </c>
-      <c r="Z37">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AA37">
-        <v>1.02</v>
-      </c>
-      <c r="AB37">
-        <v>1.08</v>
-      </c>
-      <c r="AC37">
-        <v>1.66</v>
-      </c>
-      <c r="AD37">
-        <v>2.09</v>
-      </c>
-      <c r="AE37">
-        <v>3</v>
-      </c>
-      <c r="AF37">
-        <v>1.36</v>
-      </c>
-      <c r="AG37">
-        <v>6.35</v>
-      </c>
-      <c r="AH37">
+      <c r="AV37">
+        <v>2.1</v>
+      </c>
+      <c r="AW37">
+        <v>1.68</v>
+      </c>
+      <c r="AX37">
+        <v>1.43</v>
+      </c>
+      <c r="AY37">
+        <v>1.26</v>
+      </c>
+      <c r="AZ37">
+        <v>2.35</v>
+      </c>
+      <c r="BA37">
+        <v>1.68</v>
+      </c>
+      <c r="BB37">
+        <v>1.32</v>
+      </c>
+      <c r="BC37">
+        <v>2.59</v>
+      </c>
+      <c r="BD37">
+        <v>2.96</v>
+      </c>
+      <c r="BE37">
+        <v>1.41</v>
+      </c>
+      <c r="BF37">
         <v>1.06</v>
-      </c>
-      <c r="AI37">
-        <v>10.5</v>
-      </c>
-      <c r="AJ37">
-        <v>1.02</v>
-      </c>
-      <c r="AK37">
-        <v>2.4</v>
-      </c>
-      <c r="AL37">
-        <v>1.5</v>
-      </c>
-      <c r="AM37">
-        <v>1.32</v>
-      </c>
-      <c r="AN37">
-        <v>1.55</v>
-      </c>
-      <c r="AO37">
-        <v>0</v>
-      </c>
-      <c r="AP37">
-        <v>1.53</v>
-      </c>
-      <c r="AQ37">
-        <v>1.89</v>
-      </c>
-      <c r="AR37">
-        <v>2.45</v>
-      </c>
-      <c r="AS37">
-        <v>3.25</v>
-      </c>
-      <c r="AT37">
-        <v>0</v>
-      </c>
-      <c r="AU37">
-        <v>2.3</v>
-      </c>
-      <c r="AV37">
-        <v>1.79</v>
-      </c>
-      <c r="AW37">
-        <v>1.47</v>
-      </c>
-      <c r="AX37">
-        <v>1.28</v>
-      </c>
-      <c r="AY37">
-        <v>0</v>
-      </c>
-      <c r="AZ37">
-        <v>1.92</v>
-      </c>
-      <c r="BA37">
-        <v>2.05</v>
-      </c>
-      <c r="BB37">
-        <v>1.43</v>
-      </c>
-      <c r="BC37">
-        <v>3.12</v>
-      </c>
-      <c r="BD37">
-        <v>2.53</v>
-      </c>
-      <c r="BE37">
-        <v>1.29</v>
-      </c>
-      <c r="BF37">
-        <v>1.02</v>
       </c>
       <c r="BG37">
         <v>0</v>

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -304,12 +304,12 @@
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
     <t>Egypt Egyptian Premier League</t>
   </si>
   <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
     <t>South Africa Premier Soccer League</t>
   </si>
   <si>
@@ -337,12 +337,12 @@
     <t>Jeonbuk Motors</t>
   </si>
   <si>
+    <t>Gangwon</t>
+  </si>
+  <si>
     <t>Daejeon Citizen</t>
   </si>
   <si>
-    <t>Gangwon</t>
-  </si>
-  <si>
     <t>Sangju Sangmu</t>
   </si>
   <si>
@@ -367,18 +367,18 @@
     <t>Shandong Luneng</t>
   </si>
   <si>
+    <t>Borneo</t>
+  </si>
+  <si>
+    <t>Dire Dawa Kenema</t>
+  </si>
+  <si>
     <t>Karvan FK</t>
   </si>
   <si>
     <t>Chongqing Tongliang Long</t>
   </si>
   <si>
-    <t>Borneo</t>
-  </si>
-  <si>
-    <t>Dire Dawa Kenema</t>
-  </si>
-  <si>
     <t>Mekelle Kenema</t>
   </si>
   <si>
@@ -406,42 +406,42 @@
     <t>Maccabi Tel Aviv</t>
   </si>
   <si>
+    <t>Al Ittihad Kalba</t>
+  </si>
+  <si>
     <t>Dibba Al Fujairah</t>
   </si>
   <si>
-    <t>Al Ittihad Kalba</t>
-  </si>
-  <si>
     <t>Bani Yas</t>
   </si>
   <si>
+    <t>Falkenberg</t>
+  </si>
+  <si>
     <t>Al Ahly</t>
   </si>
   <si>
+    <t>Ceramica Cleopatra</t>
+  </si>
+  <si>
     <t>Smouha SC</t>
   </si>
   <si>
-    <t>Falkenberg</t>
-  </si>
-  <si>
     <t>Lokomotiv Sofia 1929</t>
   </si>
   <si>
-    <t>Ceramica Cleopatra</t>
-  </si>
-  <si>
     <t>Siwelele</t>
   </si>
   <si>
+    <t>Stellenbosch</t>
+  </si>
+  <si>
+    <t>Chippa United</t>
+  </si>
+  <si>
     <t>Magesi</t>
   </si>
   <si>
-    <t>Chippa United</t>
-  </si>
-  <si>
-    <t>Stellenbosch</t>
-  </si>
-  <si>
     <t>Al Khaleej</t>
   </si>
   <si>
@@ -457,12 +457,12 @@
     <t>Gwangju</t>
   </si>
   <si>
+    <t>Pohang Steelers</t>
+  </si>
+  <si>
     <t>Incheon United</t>
   </si>
   <si>
-    <t>Pohang Steelers</t>
-  </si>
-  <si>
     <t>Ulsan</t>
   </si>
   <si>
@@ -487,18 +487,18 @@
     <t>Shanghai Shenhua</t>
   </si>
   <si>
+    <t>Persita</t>
+  </si>
+  <si>
+    <t>Ethiopia Bunna</t>
+  </si>
+  <si>
     <t>Neftçi</t>
   </si>
   <si>
     <t>Henan Jianye</t>
   </si>
   <si>
-    <t>Persita</t>
-  </si>
-  <si>
-    <t>Ethiopia Bunna</t>
-  </si>
-  <si>
     <t>Arba Minch Kenema</t>
   </si>
   <si>
@@ -532,31 +532,31 @@
     <t>Al Dhafra</t>
   </si>
   <si>
+    <t>Norrköping</t>
+  </si>
+  <si>
     <t>ENPPI</t>
   </si>
   <si>
+    <t>Pyramids FC</t>
+  </si>
+  <si>
     <t>Zamalek</t>
   </si>
   <si>
-    <t>Norrköping</t>
-  </si>
-  <si>
     <t>Botev Vratsa</t>
   </si>
   <si>
-    <t>Pyramids FC</t>
-  </si>
-  <si>
     <t>Durban City</t>
   </si>
   <si>
+    <t>Orlando Pirates</t>
+  </si>
+  <si>
+    <t>Sekhukhune United</t>
+  </si>
+  <si>
     <t>Orbit College</t>
-  </si>
-  <si>
-    <t>Sekhukhune United</t>
-  </si>
-  <si>
-    <t>Orlando Pirates</t>
   </si>
   <si>
     <t>Al Hilal</t>
@@ -3348,7 +3348,7 @@
         <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D14" t="s">
         <v>103</v>
@@ -3387,133 +3387,133 @@
         <v>184</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AO14">
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AU14">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AV14">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AW14">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AX14">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AY14">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AZ14">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="BA14">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="BB14">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC14">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BD14">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="BE14">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BF14">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG14">
         <v>0</v>
@@ -3533,10 +3533,10 @@
         <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E15" t="s">
         <v>118</v>
@@ -3718,7 +3718,7 @@
         <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D16" t="s">
         <v>103</v>
@@ -3757,133 +3757,133 @@
         <v>184</v>
       </c>
       <c r="P16">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q16">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R16">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>5.61</v>
+        <v>0</v>
       </c>
       <c r="V16">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W16">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X16">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z16">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC16">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD16">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AE16">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AH16">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AI16">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AJ16">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK16">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM16">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AN16">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AO16">
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ16">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AR16">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AS16">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AT16">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AU16">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AV16">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="AW16">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AX16">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AY16">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AZ16">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="BA16">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="BB16">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC16">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BD16">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="BE16">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BF16">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG16">
         <v>0</v>
@@ -3903,10 +3903,10 @@
         <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E17" t="s">
         <v>120</v>
@@ -5762,7 +5762,7 @@
         <v>130</v>
       </c>
       <c r="F27" t="s">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -5947,7 +5947,7 @@
         <v>131</v>
       </c>
       <c r="F28" t="s">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -6311,7 +6311,7 @@
         <v>96</v>
       </c>
       <c r="D30" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E30" t="s">
         <v>133</v>
@@ -6347,13 +6347,13 @@
         <v>184</v>
       </c>
       <c r="P30">
-        <v>1.4</v>
+        <v>2.83</v>
       </c>
       <c r="Q30">
-        <v>3.9</v>
+        <v>3.46</v>
       </c>
       <c r="R30">
-        <v>7</v>
+        <v>2.32</v>
       </c>
       <c r="S30">
         <v>0</v>
@@ -6493,7 +6493,7 @@
         <v>79</v>
       </c>
       <c r="C31" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D31" t="s">
         <v>103</v>
@@ -6532,13 +6532,13 @@
         <v>184</v>
       </c>
       <c r="P31">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="Q31">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="R31">
-        <v>1.72</v>
+        <v>7</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -6681,7 +6681,7 @@
         <v>97</v>
       </c>
       <c r="D32" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E32" t="s">
         <v>135</v>
@@ -6717,133 +6717,133 @@
         <v>184</v>
       </c>
       <c r="P32">
-        <v>2.83</v>
+        <v>4</v>
       </c>
       <c r="Q32">
-        <v>3.46</v>
+        <v>3.1</v>
       </c>
       <c r="R32">
-        <v>2.32</v>
+        <v>1.8</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH32">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI32">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL32">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM32">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN32">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AO32">
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ32">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AR32">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS32">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT32">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AU32">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV32">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AW32">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AX32">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AY32">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AZ32">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="BA32">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BB32">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC32">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD32">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE32">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF32">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG32">
         <v>0</v>
@@ -6863,7 +6863,7 @@
         <v>79</v>
       </c>
       <c r="C33" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D33" t="s">
         <v>103</v>
@@ -6902,130 +6902,130 @@
         <v>184</v>
       </c>
       <c r="P33">
-        <v>1.95</v>
+        <v>4.6</v>
       </c>
       <c r="Q33">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R33">
-        <v>3.79</v>
+        <v>1.72</v>
       </c>
       <c r="S33">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="T33">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U33">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="V33">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W33">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X33">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y33">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z33">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA33">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB33">
         <v>0</v>
       </c>
       <c r="AC33">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD33">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE33">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF33">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG33">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AH33">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI33">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AJ33">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK33">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL33">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AM33">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN33">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AO33">
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AQ33">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AR33">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS33">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AT33">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AU33">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV33">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AW33">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AX33">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AY33">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ33">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BA33">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BB33">
         <v>0</v>
       </c>
       <c r="BC33">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD33">
         <v>0</v>
       </c>
       <c r="BE33">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BF33">
         <v>0</v>
@@ -7048,7 +7048,7 @@
         <v>79</v>
       </c>
       <c r="C34" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D34" t="s">
         <v>103</v>
@@ -7087,133 +7087,133 @@
         <v>184</v>
       </c>
       <c r="P34">
-        <v>4</v>
+        <v>1.95</v>
       </c>
       <c r="Q34">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R34">
+        <v>3.79</v>
+      </c>
+      <c r="S34">
+        <v>2.48</v>
+      </c>
+      <c r="T34">
+        <v>2.1</v>
+      </c>
+      <c r="U34">
+        <v>4.1</v>
+      </c>
+      <c r="V34">
+        <v>1.37</v>
+      </c>
+      <c r="W34">
+        <v>2.7</v>
+      </c>
+      <c r="X34">
+        <v>2.88</v>
+      </c>
+      <c r="Y34">
+        <v>1.33</v>
+      </c>
+      <c r="Z34">
+        <v>7</v>
+      </c>
+      <c r="AA34">
+        <v>1.03</v>
+      </c>
+      <c r="AB34">
+        <v>0</v>
+      </c>
+      <c r="AC34">
+        <v>1.32</v>
+      </c>
+      <c r="AD34">
+        <v>3</v>
+      </c>
+      <c r="AE34">
+        <v>2.02</v>
+      </c>
+      <c r="AF34">
+        <v>1.68</v>
+      </c>
+      <c r="AG34">
+        <v>3.6</v>
+      </c>
+      <c r="AH34">
+        <v>1.24</v>
+      </c>
+      <c r="AI34">
+        <v>6.75</v>
+      </c>
+      <c r="AJ34">
+        <v>1.07</v>
+      </c>
+      <c r="AK34">
         <v>1.8</v>
       </c>
-      <c r="S34">
-        <v>5.29</v>
-      </c>
-      <c r="T34">
-        <v>1.96</v>
-      </c>
-      <c r="U34">
-        <v>2.46</v>
-      </c>
-      <c r="V34">
-        <v>1.47</v>
-      </c>
-      <c r="W34">
-        <v>2.41</v>
-      </c>
-      <c r="X34">
-        <v>3.08</v>
-      </c>
-      <c r="Y34">
-        <v>1.3</v>
-      </c>
-      <c r="Z34">
-        <v>7.7</v>
-      </c>
-      <c r="AA34">
-        <v>1.02</v>
-      </c>
-      <c r="AB34">
-        <v>1.04</v>
-      </c>
-      <c r="AC34">
-        <v>1.35</v>
-      </c>
-      <c r="AD34">
-        <v>2.74</v>
-      </c>
-      <c r="AE34">
-        <v>2.2</v>
-      </c>
-      <c r="AF34">
-        <v>1.58</v>
-      </c>
-      <c r="AG34">
-        <v>3.8</v>
-      </c>
-      <c r="AH34">
-        <v>1.19</v>
-      </c>
-      <c r="AI34">
-        <v>7.3</v>
-      </c>
-      <c r="AJ34">
-        <v>1.03</v>
-      </c>
-      <c r="AK34">
-        <v>1.97</v>
-      </c>
       <c r="AL34">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AM34">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AN34">
-        <v>1.14</v>
+        <v>1.75</v>
       </c>
       <c r="AO34">
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AQ34">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AR34">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AS34">
         <v>2.7</v>
       </c>
       <c r="AT34">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="AU34">
         <v>2.7</v>
       </c>
       <c r="AV34">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AW34">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AX34">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AY34">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AZ34">
-        <v>2.65</v>
+        <v>1.68</v>
       </c>
       <c r="BA34">
-        <v>1.55</v>
+        <v>2.5</v>
       </c>
       <c r="BB34">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BC34">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="BD34">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BE34">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="BF34">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG34">
         <v>0</v>
@@ -7457,133 +7457,133 @@
         <v>184</v>
       </c>
       <c r="P36">
-        <v>2.06</v>
+        <v>6.29</v>
       </c>
       <c r="Q36">
-        <v>2.8</v>
+        <v>3.48</v>
       </c>
       <c r="R36">
-        <v>3.89</v>
+        <v>1.53</v>
       </c>
       <c r="S36">
-        <v>2.95</v>
+        <v>6.93</v>
       </c>
       <c r="T36">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="U36">
-        <v>5.15</v>
+        <v>2.3</v>
       </c>
       <c r="V36">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="W36">
-        <v>2.11</v>
+        <v>2.28</v>
       </c>
       <c r="X36">
-        <v>3.92</v>
+        <v>3.5</v>
       </c>
       <c r="Y36">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z36">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AA36">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AB36">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AC36">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="AD36">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="AE36">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AF36">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AG36">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="AH36">
+        <v>1.11</v>
+      </c>
+      <c r="AI36">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AJ36">
+        <v>1.03</v>
+      </c>
+      <c r="AK36">
+        <v>2.4</v>
+      </c>
+      <c r="AL36">
+        <v>1.5</v>
+      </c>
+      <c r="AM36">
+        <v>1.26</v>
+      </c>
+      <c r="AN36">
         <v>1.07</v>
       </c>
-      <c r="AI36">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AJ36">
-        <v>1.01</v>
-      </c>
-      <c r="AK36">
-        <v>2.3</v>
-      </c>
-      <c r="AL36">
-        <v>1.54</v>
-      </c>
-      <c r="AM36">
+      <c r="AO36">
+        <v>0</v>
+      </c>
+      <c r="AP36">
+        <v>1.7</v>
+      </c>
+      <c r="AQ36">
+        <v>2.15</v>
+      </c>
+      <c r="AR36">
+        <v>2.85</v>
+      </c>
+      <c r="AS36">
+        <v>3.85</v>
+      </c>
+      <c r="AT36">
+        <v>0</v>
+      </c>
+      <c r="AU36">
+        <v>2</v>
+      </c>
+      <c r="AV36">
+        <v>1.61</v>
+      </c>
+      <c r="AW36">
+        <v>1.36</v>
+      </c>
+      <c r="AX36">
+        <v>1.21</v>
+      </c>
+      <c r="AY36">
+        <v>0</v>
+      </c>
+      <c r="AZ36">
+        <v>3.1</v>
+      </c>
+      <c r="BA36">
+        <v>1.44</v>
+      </c>
+      <c r="BB36">
         <v>1.35</v>
       </c>
-      <c r="AN36">
-        <v>1.59</v>
-      </c>
-      <c r="AO36">
-        <v>0</v>
-      </c>
-      <c r="AP36">
-        <v>1.45</v>
-      </c>
-      <c r="AQ36">
-        <v>1.77</v>
-      </c>
-      <c r="AR36">
-        <v>2.23</v>
-      </c>
-      <c r="AS36">
-        <v>2.9</v>
-      </c>
-      <c r="AT36">
-        <v>0</v>
-      </c>
-      <c r="AU36">
-        <v>2.5</v>
-      </c>
-      <c r="AV36">
-        <v>1.92</v>
-      </c>
-      <c r="AW36">
-        <v>1.57</v>
-      </c>
-      <c r="AX36">
-        <v>1.35</v>
-      </c>
-      <c r="AY36">
-        <v>0</v>
-      </c>
-      <c r="AZ36">
-        <v>1.5</v>
-      </c>
-      <c r="BA36">
-        <v>2.8</v>
-      </c>
-      <c r="BB36">
+      <c r="BC36">
+        <v>2.66</v>
+      </c>
+      <c r="BD36">
+        <v>2.82</v>
+      </c>
+      <c r="BE36">
         <v>1.39</v>
       </c>
-      <c r="BC36">
-        <v>2.91</v>
-      </c>
-      <c r="BD36">
-        <v>2.66</v>
-      </c>
-      <c r="BE36">
-        <v>1.33</v>
-      </c>
       <c r="BF36">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BG36">
         <v>0</v>
@@ -7827,133 +7827,133 @@
         <v>184</v>
       </c>
       <c r="P38">
-        <v>6.29</v>
+        <v>2.06</v>
       </c>
       <c r="Q38">
-        <v>3.48</v>
+        <v>2.8</v>
       </c>
       <c r="R38">
-        <v>1.53</v>
+        <v>3.89</v>
       </c>
       <c r="S38">
-        <v>6.93</v>
+        <v>2.95</v>
       </c>
       <c r="T38">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="U38">
+        <v>5.15</v>
+      </c>
+      <c r="V38">
+        <v>1.64</v>
+      </c>
+      <c r="W38">
+        <v>2.11</v>
+      </c>
+      <c r="X38">
+        <v>3.92</v>
+      </c>
+      <c r="Y38">
+        <v>1.18</v>
+      </c>
+      <c r="Z38">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AA38">
+        <v>1.02</v>
+      </c>
+      <c r="AB38">
+        <v>1.08</v>
+      </c>
+      <c r="AC38">
+        <v>1.59</v>
+      </c>
+      <c r="AD38">
+        <v>2.21</v>
+      </c>
+      <c r="AE38">
+        <v>2.75</v>
+      </c>
+      <c r="AF38">
+        <v>1.4</v>
+      </c>
+      <c r="AG38">
+        <v>5.8</v>
+      </c>
+      <c r="AH38">
+        <v>1.07</v>
+      </c>
+      <c r="AI38">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AJ38">
+        <v>1.01</v>
+      </c>
+      <c r="AK38">
         <v>2.3</v>
       </c>
-      <c r="V38">
-        <v>1.55</v>
-      </c>
-      <c r="W38">
-        <v>2.28</v>
-      </c>
-      <c r="X38">
-        <v>3.5</v>
-      </c>
-      <c r="Y38">
-        <v>1.22</v>
-      </c>
-      <c r="Z38">
-        <v>7.8</v>
-      </c>
-      <c r="AA38">
-        <v>1.04</v>
-      </c>
-      <c r="AB38">
-        <v>1.06</v>
-      </c>
-      <c r="AC38">
-        <v>1.47</v>
-      </c>
-      <c r="AD38">
-        <v>2.35</v>
-      </c>
-      <c r="AE38">
-        <v>2.55</v>
-      </c>
-      <c r="AF38">
+      <c r="AL38">
+        <v>1.54</v>
+      </c>
+      <c r="AM38">
+        <v>1.35</v>
+      </c>
+      <c r="AN38">
+        <v>1.59</v>
+      </c>
+      <c r="AO38">
+        <v>0</v>
+      </c>
+      <c r="AP38">
         <v>1.45</v>
       </c>
-      <c r="AG38">
-        <v>4.9</v>
-      </c>
-      <c r="AH38">
-        <v>1.11</v>
-      </c>
-      <c r="AI38">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="AJ38">
+      <c r="AQ38">
+        <v>1.77</v>
+      </c>
+      <c r="AR38">
+        <v>2.23</v>
+      </c>
+      <c r="AS38">
+        <v>2.9</v>
+      </c>
+      <c r="AT38">
+        <v>0</v>
+      </c>
+      <c r="AU38">
+        <v>2.5</v>
+      </c>
+      <c r="AV38">
+        <v>1.92</v>
+      </c>
+      <c r="AW38">
+        <v>1.57</v>
+      </c>
+      <c r="AX38">
+        <v>1.35</v>
+      </c>
+      <c r="AY38">
+        <v>0</v>
+      </c>
+      <c r="AZ38">
+        <v>1.5</v>
+      </c>
+      <c r="BA38">
+        <v>2.8</v>
+      </c>
+      <c r="BB38">
+        <v>1.39</v>
+      </c>
+      <c r="BC38">
+        <v>2.91</v>
+      </c>
+      <c r="BD38">
+        <v>2.66</v>
+      </c>
+      <c r="BE38">
+        <v>1.33</v>
+      </c>
+      <c r="BF38">
         <v>1.03</v>
-      </c>
-      <c r="AK38">
-        <v>2.4</v>
-      </c>
-      <c r="AL38">
-        <v>1.5</v>
-      </c>
-      <c r="AM38">
-        <v>1.26</v>
-      </c>
-      <c r="AN38">
-        <v>1.07</v>
-      </c>
-      <c r="AO38">
-        <v>0</v>
-      </c>
-      <c r="AP38">
-        <v>1.7</v>
-      </c>
-      <c r="AQ38">
-        <v>2.15</v>
-      </c>
-      <c r="AR38">
-        <v>2.85</v>
-      </c>
-      <c r="AS38">
-        <v>3.85</v>
-      </c>
-      <c r="AT38">
-        <v>0</v>
-      </c>
-      <c r="AU38">
-        <v>2</v>
-      </c>
-      <c r="AV38">
-        <v>1.61</v>
-      </c>
-      <c r="AW38">
-        <v>1.36</v>
-      </c>
-      <c r="AX38">
-        <v>1.21</v>
-      </c>
-      <c r="AY38">
-        <v>0</v>
-      </c>
-      <c r="AZ38">
-        <v>3.1</v>
-      </c>
-      <c r="BA38">
-        <v>1.44</v>
-      </c>
-      <c r="BB38">
-        <v>1.35</v>
-      </c>
-      <c r="BC38">
-        <v>2.66</v>
-      </c>
-      <c r="BD38">
-        <v>2.82</v>
-      </c>
-      <c r="BE38">
-        <v>1.39</v>
-      </c>
-      <c r="BF38">
-        <v>1.05</v>
       </c>
       <c r="BG38">
         <v>0</v>

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -304,12 +304,12 @@
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
+    <t>Egypt Egyptian Premier League</t>
+  </si>
+  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
-    <t>Egypt Egyptian Premier League</t>
-  </si>
-  <si>
     <t>South Africa Premier Soccer League</t>
   </si>
   <si>
@@ -337,15 +337,15 @@
     <t>Jeonbuk Motors</t>
   </si>
   <si>
+    <t>Daejeon Citizen</t>
+  </si>
+  <si>
+    <t>Sangju Sangmu</t>
+  </si>
+  <si>
     <t>Gangwon</t>
   </si>
   <si>
-    <t>Daejeon Citizen</t>
-  </si>
-  <si>
-    <t>Sangju Sangmu</t>
-  </si>
-  <si>
     <t>Madura United</t>
   </si>
   <si>
@@ -361,12 +361,12 @@
     <t>Tanjong Pagar</t>
   </si>
   <si>
+    <t>Shandong Luneng</t>
+  </si>
+  <si>
     <t>Shenyang Urban</t>
   </si>
   <si>
-    <t>Shandong Luneng</t>
-  </si>
-  <si>
     <t>Borneo</t>
   </si>
   <si>
@@ -406,42 +406,42 @@
     <t>Maccabi Tel Aviv</t>
   </si>
   <si>
+    <t>Bani Yas</t>
+  </si>
+  <si>
     <t>Al Ittihad Kalba</t>
   </si>
   <si>
     <t>Dibba Al Fujairah</t>
   </si>
   <si>
-    <t>Bani Yas</t>
+    <t>Al Ahly</t>
+  </si>
+  <si>
+    <t>Ceramica Cleopatra</t>
+  </si>
+  <si>
+    <t>Smouha SC</t>
   </si>
   <si>
     <t>Falkenberg</t>
   </si>
   <si>
-    <t>Al Ahly</t>
-  </si>
-  <si>
-    <t>Ceramica Cleopatra</t>
-  </si>
-  <si>
-    <t>Smouha SC</t>
-  </si>
-  <si>
     <t>Lokomotiv Sofia 1929</t>
   </si>
   <si>
+    <t>Chippa United</t>
+  </si>
+  <si>
+    <t>Stellenbosch</t>
+  </si>
+  <si>
+    <t>Magesi</t>
+  </si>
+  <si>
     <t>Siwelele</t>
   </si>
   <si>
-    <t>Stellenbosch</t>
-  </si>
-  <si>
-    <t>Chippa United</t>
-  </si>
-  <si>
-    <t>Magesi</t>
-  </si>
-  <si>
     <t>Al Khaleej</t>
   </si>
   <si>
@@ -457,15 +457,15 @@
     <t>Gwangju</t>
   </si>
   <si>
+    <t>Incheon United</t>
+  </si>
+  <si>
+    <t>Ulsan</t>
+  </si>
+  <si>
     <t>Pohang Steelers</t>
   </si>
   <si>
-    <t>Incheon United</t>
-  </si>
-  <si>
-    <t>Ulsan</t>
-  </si>
-  <si>
     <t>Bali United</t>
   </si>
   <si>
@@ -481,12 +481,12 @@
     <t>Hougang United</t>
   </si>
   <si>
+    <t>Shanghai Shenhua</t>
+  </si>
+  <si>
     <t>Chengdu Better City FC</t>
   </si>
   <si>
-    <t>Shanghai Shenhua</t>
-  </si>
-  <si>
     <t>Persita</t>
   </si>
   <si>
@@ -526,37 +526,37 @@
     <t>Hapoel Petah Tikva</t>
   </si>
   <si>
+    <t>Al Dhafra</t>
+  </si>
+  <si>
     <t>Al Bataeh</t>
   </si>
   <si>
-    <t>Al Dhafra</t>
+    <t>ENPPI</t>
+  </si>
+  <si>
+    <t>Pyramids FC</t>
+  </si>
+  <si>
+    <t>Zamalek</t>
   </si>
   <si>
     <t>Norrköping</t>
   </si>
   <si>
-    <t>ENPPI</t>
-  </si>
-  <si>
-    <t>Pyramids FC</t>
-  </si>
-  <si>
-    <t>Zamalek</t>
-  </si>
-  <si>
     <t>Botev Vratsa</t>
   </si>
   <si>
+    <t>Sekhukhune United</t>
+  </si>
+  <si>
+    <t>Orlando Pirates</t>
+  </si>
+  <si>
+    <t>Orbit College</t>
+  </si>
+  <si>
     <t>Durban City</t>
-  </si>
-  <si>
-    <t>Orlando Pirates</t>
-  </si>
-  <si>
-    <t>Sekhukhune United</t>
-  </si>
-  <si>
-    <t>Orbit College</t>
   </si>
   <si>
     <t>Al Hilal</t>
@@ -2704,10 +2704,10 @@
         <v>1.27</v>
       </c>
       <c r="AI10">
-        <v>5.95</v>
+        <v>6.45</v>
       </c>
       <c r="AJ10">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AK10">
         <v>1.78</v>
@@ -2725,40 +2725,40 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AU10">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AV10">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AW10">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX10">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AY10">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ10">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BA10">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="BB10">
         <v>1.22</v>
@@ -3017,133 +3017,133 @@
         <v>184</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S12">
+        <v>2.95</v>
+      </c>
+      <c r="T12">
+        <v>2.27</v>
+      </c>
+      <c r="U12">
+        <v>3.02</v>
+      </c>
+      <c r="V12">
+        <v>1.22</v>
+      </c>
+      <c r="W12">
+        <v>3.6</v>
+      </c>
+      <c r="X12">
+        <v>2.08</v>
+      </c>
+      <c r="Y12">
+        <v>1.69</v>
+      </c>
+      <c r="Z12">
+        <v>4.45</v>
+      </c>
+      <c r="AA12">
+        <v>1.14</v>
+      </c>
+      <c r="AB12">
+        <v>1.02</v>
+      </c>
+      <c r="AC12">
+        <v>1.08</v>
+      </c>
+      <c r="AD12">
         <v>5.65</v>
       </c>
-      <c r="T12">
-        <v>2.29</v>
-      </c>
-      <c r="U12">
-        <v>2.01</v>
-      </c>
-      <c r="V12">
-        <v>1.32</v>
-      </c>
-      <c r="W12">
-        <v>3.05</v>
-      </c>
-      <c r="X12">
-        <v>2.56</v>
-      </c>
-      <c r="Y12">
-        <v>1.44</v>
-      </c>
-      <c r="Z12">
-        <v>6</v>
-      </c>
-      <c r="AA12">
-        <v>1.06</v>
-      </c>
-      <c r="AB12">
-        <v>1.03</v>
-      </c>
-      <c r="AC12">
-        <v>1.21</v>
-      </c>
-      <c r="AD12">
-        <v>3.58</v>
-      </c>
       <c r="AE12">
-        <v>1.81</v>
+        <v>1.39</v>
       </c>
       <c r="AF12">
-        <v>2.02</v>
+        <v>2.59</v>
       </c>
       <c r="AG12">
-        <v>2.83</v>
+        <v>2.1</v>
       </c>
       <c r="AH12">
+        <v>1.75</v>
+      </c>
+      <c r="AI12">
+        <v>3.28</v>
+      </c>
+      <c r="AJ12">
+        <v>1.25</v>
+      </c>
+      <c r="AK12">
+        <v>1.36</v>
+      </c>
+      <c r="AL12">
+        <v>2.9</v>
+      </c>
+      <c r="AM12">
+        <v>1.28</v>
+      </c>
+      <c r="AN12">
+        <v>1.51</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>1.12</v>
+      </c>
+      <c r="AQ12">
+        <v>1.3</v>
+      </c>
+      <c r="AR12">
+        <v>1.72</v>
+      </c>
+      <c r="AS12">
+        <v>1.92</v>
+      </c>
+      <c r="AT12">
+        <v>2.44</v>
+      </c>
+      <c r="AU12">
+        <v>4.5</v>
+      </c>
+      <c r="AV12">
+        <v>3</v>
+      </c>
+      <c r="AW12">
+        <v>2.23</v>
+      </c>
+      <c r="AX12">
+        <v>1.78</v>
+      </c>
+      <c r="AY12">
+        <v>1.47</v>
+      </c>
+      <c r="AZ12">
+        <v>1.65</v>
+      </c>
+      <c r="BA12">
+        <v>2.88</v>
+      </c>
+      <c r="BB12">
+        <v>1.08</v>
+      </c>
+      <c r="BC12">
+        <v>1.63</v>
+      </c>
+      <c r="BD12">
+        <v>5.7</v>
+      </c>
+      <c r="BE12">
+        <v>2.17</v>
+      </c>
+      <c r="BF12">
         <v>1.33</v>
-      </c>
-      <c r="AI12">
-        <v>5.25</v>
-      </c>
-      <c r="AJ12">
-        <v>1.09</v>
-      </c>
-      <c r="AK12">
-        <v>1.84</v>
-      </c>
-      <c r="AL12">
-        <v>1.86</v>
-      </c>
-      <c r="AM12">
-        <v>1.22</v>
-      </c>
-      <c r="AN12">
-        <v>1.13</v>
-      </c>
-      <c r="AO12">
-        <v>0</v>
-      </c>
-      <c r="AP12">
-        <v>0</v>
-      </c>
-      <c r="AQ12">
-        <v>0</v>
-      </c>
-      <c r="AR12">
-        <v>0</v>
-      </c>
-      <c r="AS12">
-        <v>0</v>
-      </c>
-      <c r="AT12">
-        <v>0</v>
-      </c>
-      <c r="AU12">
-        <v>0</v>
-      </c>
-      <c r="AV12">
-        <v>0</v>
-      </c>
-      <c r="AW12">
-        <v>0</v>
-      </c>
-      <c r="AX12">
-        <v>0</v>
-      </c>
-      <c r="AY12">
-        <v>0</v>
-      </c>
-      <c r="AZ12">
-        <v>0</v>
-      </c>
-      <c r="BA12">
-        <v>0</v>
-      </c>
-      <c r="BB12">
-        <v>1.18</v>
-      </c>
-      <c r="BC12">
-        <v>2.01</v>
-      </c>
-      <c r="BD12">
-        <v>4.05</v>
-      </c>
-      <c r="BE12">
-        <v>1.74</v>
-      </c>
-      <c r="BF12">
-        <v>1.17</v>
       </c>
       <c r="BG12">
         <v>0</v>
@@ -3202,79 +3202,79 @@
         <v>184</v>
       </c>
       <c r="P13">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q13">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R13">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S13">
-        <v>2.95</v>
+        <v>5.65</v>
       </c>
       <c r="T13">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="U13">
-        <v>3.02</v>
+        <v>2.01</v>
       </c>
       <c r="V13">
+        <v>1.32</v>
+      </c>
+      <c r="W13">
+        <v>3.05</v>
+      </c>
+      <c r="X13">
+        <v>2.56</v>
+      </c>
+      <c r="Y13">
+        <v>1.44</v>
+      </c>
+      <c r="Z13">
+        <v>6</v>
+      </c>
+      <c r="AA13">
+        <v>1.06</v>
+      </c>
+      <c r="AB13">
+        <v>1.03</v>
+      </c>
+      <c r="AC13">
+        <v>1.21</v>
+      </c>
+      <c r="AD13">
+        <v>3.58</v>
+      </c>
+      <c r="AE13">
+        <v>1.81</v>
+      </c>
+      <c r="AF13">
+        <v>2.02</v>
+      </c>
+      <c r="AG13">
+        <v>2.83</v>
+      </c>
+      <c r="AH13">
+        <v>1.33</v>
+      </c>
+      <c r="AI13">
+        <v>5.25</v>
+      </c>
+      <c r="AJ13">
+        <v>1.09</v>
+      </c>
+      <c r="AK13">
+        <v>1.84</v>
+      </c>
+      <c r="AL13">
+        <v>1.86</v>
+      </c>
+      <c r="AM13">
         <v>1.22</v>
       </c>
-      <c r="W13">
-        <v>3.6</v>
-      </c>
-      <c r="X13">
-        <v>2.08</v>
-      </c>
-      <c r="Y13">
-        <v>1.69</v>
-      </c>
-      <c r="Z13">
-        <v>4.45</v>
-      </c>
-      <c r="AA13">
-        <v>1.14</v>
-      </c>
-      <c r="AB13">
-        <v>1.02</v>
-      </c>
-      <c r="AC13">
-        <v>1.08</v>
-      </c>
-      <c r="AD13">
-        <v>5.65</v>
-      </c>
-      <c r="AE13">
-        <v>1.39</v>
-      </c>
-      <c r="AF13">
-        <v>2.59</v>
-      </c>
-      <c r="AG13">
-        <v>2.1</v>
-      </c>
-      <c r="AH13">
-        <v>1.75</v>
-      </c>
-      <c r="AI13">
-        <v>3.28</v>
-      </c>
-      <c r="AJ13">
-        <v>1.25</v>
-      </c>
-      <c r="AK13">
-        <v>1.36</v>
-      </c>
-      <c r="AL13">
-        <v>2.9</v>
-      </c>
-      <c r="AM13">
-        <v>1.28</v>
-      </c>
       <c r="AN13">
-        <v>1.51</v>
+        <v>1.13</v>
       </c>
       <c r="AO13">
         <v>0</v>
@@ -3316,19 +3316,19 @@
         <v>0</v>
       </c>
       <c r="BB13">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="BC13">
-        <v>1.63</v>
+        <v>2.01</v>
       </c>
       <c r="BD13">
-        <v>5.7</v>
+        <v>4.05</v>
       </c>
       <c r="BE13">
-        <v>2.17</v>
+        <v>1.74</v>
       </c>
       <c r="BF13">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="BG13">
         <v>0</v>
@@ -3951,70 +3951,70 @@
         <v>0</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI17">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL17">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AM17">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AO17">
         <v>0</v>
@@ -4056,19 +4056,19 @@
         <v>0</v>
       </c>
       <c r="BB17">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC17">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BD17">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="BE17">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF17">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG17">
         <v>0</v>
@@ -4312,10 +4312,10 @@
         <v>184</v>
       </c>
       <c r="P19">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="Q19">
-        <v>3.2</v>
+        <v>3.29</v>
       </c>
       <c r="R19">
         <v>2.36</v>
@@ -5276,40 +5276,40 @@
         <v>0</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH24">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI24">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL24">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AM24">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AN24">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AO24">
         <v>0</v>
@@ -5762,7 +5762,7 @@
         <v>130</v>
       </c>
       <c r="F27" t="s">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -5947,7 +5947,7 @@
         <v>131</v>
       </c>
       <c r="F28" t="s">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -6311,7 +6311,7 @@
         <v>96</v>
       </c>
       <c r="D30" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E30" t="s">
         <v>133</v>
@@ -6347,13 +6347,13 @@
         <v>184</v>
       </c>
       <c r="P30">
-        <v>2.83</v>
+        <v>1.4</v>
       </c>
       <c r="Q30">
-        <v>3.46</v>
+        <v>3.9</v>
       </c>
       <c r="R30">
-        <v>2.32</v>
+        <v>7</v>
       </c>
       <c r="S30">
         <v>0</v>
@@ -6493,7 +6493,7 @@
         <v>79</v>
       </c>
       <c r="C31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D31" t="s">
         <v>103</v>
@@ -6532,133 +6532,133 @@
         <v>184</v>
       </c>
       <c r="P31">
+        <v>4</v>
+      </c>
+      <c r="Q31">
+        <v>3.1</v>
+      </c>
+      <c r="R31">
+        <v>1.8</v>
+      </c>
+      <c r="S31">
+        <v>5.29</v>
+      </c>
+      <c r="T31">
+        <v>1.96</v>
+      </c>
+      <c r="U31">
+        <v>2.46</v>
+      </c>
+      <c r="V31">
+        <v>1.47</v>
+      </c>
+      <c r="W31">
+        <v>2.41</v>
+      </c>
+      <c r="X31">
+        <v>3.08</v>
+      </c>
+      <c r="Y31">
+        <v>1.3</v>
+      </c>
+      <c r="Z31">
+        <v>7.7</v>
+      </c>
+      <c r="AA31">
+        <v>1.02</v>
+      </c>
+      <c r="AB31">
+        <v>1.04</v>
+      </c>
+      <c r="AC31">
+        <v>1.35</v>
+      </c>
+      <c r="AD31">
+        <v>2.74</v>
+      </c>
+      <c r="AE31">
+        <v>2.2</v>
+      </c>
+      <c r="AF31">
+        <v>1.58</v>
+      </c>
+      <c r="AG31">
+        <v>3.8</v>
+      </c>
+      <c r="AH31">
+        <v>1.19</v>
+      </c>
+      <c r="AI31">
+        <v>7.3</v>
+      </c>
+      <c r="AJ31">
+        <v>1.03</v>
+      </c>
+      <c r="AK31">
+        <v>1.97</v>
+      </c>
+      <c r="AL31">
+        <v>1.73</v>
+      </c>
+      <c r="AM31">
+        <v>1.26</v>
+      </c>
+      <c r="AN31">
+        <v>1.14</v>
+      </c>
+      <c r="AO31">
+        <v>0</v>
+      </c>
+      <c r="AP31">
+        <v>1.38</v>
+      </c>
+      <c r="AQ31">
+        <v>1.66</v>
+      </c>
+      <c r="AR31">
+        <v>2.08</v>
+      </c>
+      <c r="AS31">
+        <v>2.7</v>
+      </c>
+      <c r="AT31">
+        <v>3.55</v>
+      </c>
+      <c r="AU31">
+        <v>2.7</v>
+      </c>
+      <c r="AV31">
+        <v>2.06</v>
+      </c>
+      <c r="AW31">
+        <v>1.65</v>
+      </c>
+      <c r="AX31">
         <v>1.4</v>
       </c>
-      <c r="Q31">
-        <v>3.9</v>
-      </c>
-      <c r="R31">
-        <v>7</v>
-      </c>
-      <c r="S31">
-        <v>0</v>
-      </c>
-      <c r="T31">
-        <v>0</v>
-      </c>
-      <c r="U31">
-        <v>0</v>
-      </c>
-      <c r="V31">
-        <v>0</v>
-      </c>
-      <c r="W31">
-        <v>0</v>
-      </c>
-      <c r="X31">
-        <v>0</v>
-      </c>
-      <c r="Y31">
-        <v>0</v>
-      </c>
-      <c r="Z31">
-        <v>0</v>
-      </c>
-      <c r="AA31">
-        <v>0</v>
-      </c>
-      <c r="AB31">
-        <v>0</v>
-      </c>
-      <c r="AC31">
-        <v>0</v>
-      </c>
-      <c r="AD31">
-        <v>0</v>
-      </c>
-      <c r="AE31">
-        <v>0</v>
-      </c>
-      <c r="AF31">
-        <v>0</v>
-      </c>
-      <c r="AG31">
-        <v>0</v>
-      </c>
-      <c r="AH31">
-        <v>0</v>
-      </c>
-      <c r="AI31">
-        <v>0</v>
-      </c>
-      <c r="AJ31">
-        <v>0</v>
-      </c>
-      <c r="AK31">
-        <v>0</v>
-      </c>
-      <c r="AL31">
-        <v>0</v>
-      </c>
-      <c r="AM31">
-        <v>0</v>
-      </c>
-      <c r="AN31">
-        <v>0</v>
-      </c>
-      <c r="AO31">
-        <v>0</v>
-      </c>
-      <c r="AP31">
-        <v>0</v>
-      </c>
-      <c r="AQ31">
-        <v>0</v>
-      </c>
-      <c r="AR31">
-        <v>0</v>
-      </c>
-      <c r="AS31">
-        <v>0</v>
-      </c>
-      <c r="AT31">
-        <v>0</v>
-      </c>
-      <c r="AU31">
-        <v>0</v>
-      </c>
-      <c r="AV31">
-        <v>0</v>
-      </c>
-      <c r="AW31">
-        <v>0</v>
-      </c>
-      <c r="AX31">
-        <v>0</v>
-      </c>
       <c r="AY31">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AZ31">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="BA31">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BB31">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC31">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD31">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE31">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF31">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG31">
         <v>0</v>
@@ -6678,7 +6678,7 @@
         <v>79</v>
       </c>
       <c r="C32" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D32" t="s">
         <v>103</v>
@@ -6717,133 +6717,133 @@
         <v>184</v>
       </c>
       <c r="P32">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="Q32">
         <v>3.1</v>
       </c>
       <c r="R32">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="S32">
-        <v>5.29</v>
+        <v>0</v>
       </c>
       <c r="T32">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="U32">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="V32">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W32">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="X32">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Y32">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z32">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AA32">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB32">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC32">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD32">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AE32">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF32">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG32">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH32">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI32">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AJ32">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK32">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL32">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM32">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN32">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AO32">
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AQ32">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AR32">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AS32">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AT32">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AU32">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV32">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AW32">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AX32">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AY32">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AZ32">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="BA32">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BB32">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BC32">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD32">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BE32">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BF32">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG32">
         <v>0</v>
@@ -6866,7 +6866,7 @@
         <v>97</v>
       </c>
       <c r="D33" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E33" t="s">
         <v>136</v>
@@ -6902,13 +6902,13 @@
         <v>184</v>
       </c>
       <c r="P33">
-        <v>4.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q33">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="R33">
-        <v>1.72</v>
+        <v>2.52</v>
       </c>
       <c r="S33">
         <v>0</v>
@@ -6947,10 +6947,10 @@
         <v>0</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG33">
         <v>0</v>
@@ -7272,133 +7272,133 @@
         <v>184</v>
       </c>
       <c r="P35">
-        <v>2.2</v>
+        <v>3.63</v>
       </c>
       <c r="Q35">
+        <v>3.02</v>
+      </c>
+      <c r="R35">
+        <v>2.03</v>
+      </c>
+      <c r="S35">
+        <v>4.43</v>
+      </c>
+      <c r="T35">
+        <v>1.88</v>
+      </c>
+      <c r="U35">
+        <v>2.88</v>
+      </c>
+      <c r="V35">
+        <v>1.51</v>
+      </c>
+      <c r="W35">
+        <v>2.31</v>
+      </c>
+      <c r="X35">
+        <v>3.38</v>
+      </c>
+      <c r="Y35">
+        <v>1.25</v>
+      </c>
+      <c r="Z35">
+        <v>9.1</v>
+      </c>
+      <c r="AA35">
+        <v>1</v>
+      </c>
+      <c r="AB35">
+        <v>1.05</v>
+      </c>
+      <c r="AC35">
+        <v>1.43</v>
+      </c>
+      <c r="AD35">
+        <v>2.46</v>
+      </c>
+      <c r="AE35">
+        <v>2.44</v>
+      </c>
+      <c r="AF35">
+        <v>1.49</v>
+      </c>
+      <c r="AG35">
+        <v>4.6</v>
+      </c>
+      <c r="AH35">
+        <v>1.13</v>
+      </c>
+      <c r="AI35">
+        <v>8.5</v>
+      </c>
+      <c r="AJ35">
+        <v>1.03</v>
+      </c>
+      <c r="AK35">
+        <v>2.04</v>
+      </c>
+      <c r="AL35">
+        <v>1.68</v>
+      </c>
+      <c r="AM35">
+        <v>1.3</v>
+      </c>
+      <c r="AN35">
+        <v>1.24</v>
+      </c>
+      <c r="AO35">
+        <v>0</v>
+      </c>
+      <c r="AP35">
+        <v>1.37</v>
+      </c>
+      <c r="AQ35">
+        <v>1.63</v>
+      </c>
+      <c r="AR35">
+        <v>2.02</v>
+      </c>
+      <c r="AS35">
+        <v>2.6</v>
+      </c>
+      <c r="AT35">
+        <v>3.4</v>
+      </c>
+      <c r="AU35">
         <v>2.8</v>
       </c>
-      <c r="R35">
-        <v>3.4</v>
-      </c>
-      <c r="S35">
-        <v>3.01</v>
-      </c>
-      <c r="T35">
-        <v>1.81</v>
-      </c>
-      <c r="U35">
-        <v>4.53</v>
-      </c>
-      <c r="V35">
-        <v>1.61</v>
-      </c>
-      <c r="W35">
-        <v>2.17</v>
-      </c>
-      <c r="X35">
-        <v>4.1</v>
-      </c>
-      <c r="Y35">
-        <v>1.16</v>
-      </c>
-      <c r="Z35">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AA35">
-        <v>1.02</v>
-      </c>
-      <c r="AB35">
-        <v>1.08</v>
-      </c>
-      <c r="AC35">
-        <v>1.66</v>
-      </c>
-      <c r="AD35">
-        <v>2.09</v>
-      </c>
-      <c r="AE35">
-        <v>3</v>
-      </c>
-      <c r="AF35">
-        <v>1.36</v>
-      </c>
-      <c r="AG35">
-        <v>6.35</v>
-      </c>
-      <c r="AH35">
+      <c r="AV35">
+        <v>2.1</v>
+      </c>
+      <c r="AW35">
+        <v>1.68</v>
+      </c>
+      <c r="AX35">
+        <v>1.43</v>
+      </c>
+      <c r="AY35">
+        <v>1.26</v>
+      </c>
+      <c r="AZ35">
+        <v>2.35</v>
+      </c>
+      <c r="BA35">
+        <v>1.68</v>
+      </c>
+      <c r="BB35">
+        <v>1.32</v>
+      </c>
+      <c r="BC35">
+        <v>2.59</v>
+      </c>
+      <c r="BD35">
+        <v>2.96</v>
+      </c>
+      <c r="BE35">
+        <v>1.41</v>
+      </c>
+      <c r="BF35">
         <v>1.06</v>
-      </c>
-      <c r="AI35">
-        <v>10.5</v>
-      </c>
-      <c r="AJ35">
-        <v>1.02</v>
-      </c>
-      <c r="AK35">
-        <v>2.4</v>
-      </c>
-      <c r="AL35">
-        <v>1.5</v>
-      </c>
-      <c r="AM35">
-        <v>1.32</v>
-      </c>
-      <c r="AN35">
-        <v>1.55</v>
-      </c>
-      <c r="AO35">
-        <v>0</v>
-      </c>
-      <c r="AP35">
-        <v>1.53</v>
-      </c>
-      <c r="AQ35">
-        <v>1.89</v>
-      </c>
-      <c r="AR35">
-        <v>2.45</v>
-      </c>
-      <c r="AS35">
-        <v>3.25</v>
-      </c>
-      <c r="AT35">
-        <v>0</v>
-      </c>
-      <c r="AU35">
-        <v>2.3</v>
-      </c>
-      <c r="AV35">
-        <v>1.79</v>
-      </c>
-      <c r="AW35">
-        <v>1.47</v>
-      </c>
-      <c r="AX35">
-        <v>1.28</v>
-      </c>
-      <c r="AY35">
-        <v>0</v>
-      </c>
-      <c r="AZ35">
-        <v>1.92</v>
-      </c>
-      <c r="BA35">
-        <v>2.05</v>
-      </c>
-      <c r="BB35">
-        <v>1.43</v>
-      </c>
-      <c r="BC35">
-        <v>3.12</v>
-      </c>
-      <c r="BD35">
-        <v>2.53</v>
-      </c>
-      <c r="BE35">
-        <v>1.29</v>
-      </c>
-      <c r="BF35">
-        <v>1.02</v>
       </c>
       <c r="BG35">
         <v>0</v>
@@ -7642,133 +7642,133 @@
         <v>184</v>
       </c>
       <c r="P37">
-        <v>3.63</v>
+        <v>2.06</v>
       </c>
       <c r="Q37">
-        <v>3.02</v>
+        <v>2.8</v>
       </c>
       <c r="R37">
-        <v>2.03</v>
+        <v>3.89</v>
       </c>
       <c r="S37">
-        <v>4.43</v>
+        <v>2.95</v>
       </c>
       <c r="T37">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="U37">
-        <v>2.88</v>
+        <v>5.15</v>
       </c>
       <c r="V37">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="W37">
-        <v>2.31</v>
+        <v>2.11</v>
       </c>
       <c r="X37">
-        <v>3.38</v>
+        <v>3.92</v>
       </c>
       <c r="Y37">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z37">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA37">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AB37">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AC37">
-        <v>1.43</v>
+        <v>1.59</v>
       </c>
       <c r="AD37">
-        <v>2.46</v>
+        <v>2.21</v>
       </c>
       <c r="AE37">
-        <v>2.44</v>
+        <v>2.75</v>
       </c>
       <c r="AF37">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AG37">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="AH37">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AI37">
-        <v>8.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AJ37">
+        <v>1.01</v>
+      </c>
+      <c r="AK37">
+        <v>2.3</v>
+      </c>
+      <c r="AL37">
+        <v>1.54</v>
+      </c>
+      <c r="AM37">
+        <v>1.35</v>
+      </c>
+      <c r="AN37">
+        <v>1.59</v>
+      </c>
+      <c r="AO37">
+        <v>0</v>
+      </c>
+      <c r="AP37">
+        <v>1.45</v>
+      </c>
+      <c r="AQ37">
+        <v>1.77</v>
+      </c>
+      <c r="AR37">
+        <v>2.23</v>
+      </c>
+      <c r="AS37">
+        <v>2.9</v>
+      </c>
+      <c r="AT37">
+        <v>0</v>
+      </c>
+      <c r="AU37">
+        <v>2.5</v>
+      </c>
+      <c r="AV37">
+        <v>1.92</v>
+      </c>
+      <c r="AW37">
+        <v>1.57</v>
+      </c>
+      <c r="AX37">
+        <v>1.35</v>
+      </c>
+      <c r="AY37">
+        <v>0</v>
+      </c>
+      <c r="AZ37">
+        <v>1.5</v>
+      </c>
+      <c r="BA37">
+        <v>2.8</v>
+      </c>
+      <c r="BB37">
+        <v>1.39</v>
+      </c>
+      <c r="BC37">
+        <v>2.91</v>
+      </c>
+      <c r="BD37">
+        <v>2.66</v>
+      </c>
+      <c r="BE37">
+        <v>1.33</v>
+      </c>
+      <c r="BF37">
         <v>1.03</v>
-      </c>
-      <c r="AK37">
-        <v>2.04</v>
-      </c>
-      <c r="AL37">
-        <v>1.68</v>
-      </c>
-      <c r="AM37">
-        <v>1.3</v>
-      </c>
-      <c r="AN37">
-        <v>1.24</v>
-      </c>
-      <c r="AO37">
-        <v>0</v>
-      </c>
-      <c r="AP37">
-        <v>1.37</v>
-      </c>
-      <c r="AQ37">
-        <v>1.63</v>
-      </c>
-      <c r="AR37">
-        <v>2.02</v>
-      </c>
-      <c r="AS37">
-        <v>2.6</v>
-      </c>
-      <c r="AT37">
-        <v>3.4</v>
-      </c>
-      <c r="AU37">
-        <v>2.8</v>
-      </c>
-      <c r="AV37">
-        <v>2.1</v>
-      </c>
-      <c r="AW37">
-        <v>1.68</v>
-      </c>
-      <c r="AX37">
-        <v>1.43</v>
-      </c>
-      <c r="AY37">
-        <v>1.26</v>
-      </c>
-      <c r="AZ37">
-        <v>2.35</v>
-      </c>
-      <c r="BA37">
-        <v>1.68</v>
-      </c>
-      <c r="BB37">
-        <v>1.32</v>
-      </c>
-      <c r="BC37">
-        <v>2.59</v>
-      </c>
-      <c r="BD37">
-        <v>2.96</v>
-      </c>
-      <c r="BE37">
-        <v>1.41</v>
-      </c>
-      <c r="BF37">
-        <v>1.06</v>
       </c>
       <c r="BG37">
         <v>0</v>
@@ -7827,37 +7827,37 @@
         <v>184</v>
       </c>
       <c r="P38">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="Q38">
         <v>2.8</v>
       </c>
       <c r="R38">
-        <v>3.89</v>
+        <v>3.4</v>
       </c>
       <c r="S38">
-        <v>2.95</v>
+        <v>3.01</v>
       </c>
       <c r="T38">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="U38">
-        <v>5.15</v>
+        <v>4.53</v>
       </c>
       <c r="V38">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="W38">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="X38">
-        <v>3.92</v>
+        <v>4.1</v>
       </c>
       <c r="Y38">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z38">
-        <v>8.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA38">
         <v>1.02</v>
@@ -7866,94 +7866,94 @@
         <v>1.08</v>
       </c>
       <c r="AC38">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="AD38">
-        <v>2.21</v>
+        <v>2.09</v>
       </c>
       <c r="AE38">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AF38">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG38">
-        <v>5.8</v>
+        <v>6.35</v>
       </c>
       <c r="AH38">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AI38">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AJ38">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AK38">
+        <v>2.4</v>
+      </c>
+      <c r="AL38">
+        <v>1.5</v>
+      </c>
+      <c r="AM38">
+        <v>1.32</v>
+      </c>
+      <c r="AN38">
+        <v>1.55</v>
+      </c>
+      <c r="AO38">
+        <v>0</v>
+      </c>
+      <c r="AP38">
+        <v>1.53</v>
+      </c>
+      <c r="AQ38">
+        <v>1.89</v>
+      </c>
+      <c r="AR38">
+        <v>2.45</v>
+      </c>
+      <c r="AS38">
+        <v>3.25</v>
+      </c>
+      <c r="AT38">
+        <v>0</v>
+      </c>
+      <c r="AU38">
         <v>2.3</v>
       </c>
-      <c r="AL38">
-        <v>1.54</v>
-      </c>
-      <c r="AM38">
-        <v>1.35</v>
-      </c>
-      <c r="AN38">
-        <v>1.59</v>
-      </c>
-      <c r="AO38">
-        <v>0</v>
-      </c>
-      <c r="AP38">
-        <v>1.45</v>
-      </c>
-      <c r="AQ38">
-        <v>1.77</v>
-      </c>
-      <c r="AR38">
-        <v>2.23</v>
-      </c>
-      <c r="AS38">
-        <v>2.9</v>
-      </c>
-      <c r="AT38">
-        <v>0</v>
-      </c>
-      <c r="AU38">
-        <v>2.5</v>
-      </c>
       <c r="AV38">
+        <v>1.79</v>
+      </c>
+      <c r="AW38">
+        <v>1.47</v>
+      </c>
+      <c r="AX38">
+        <v>1.28</v>
+      </c>
+      <c r="AY38">
+        <v>0</v>
+      </c>
+      <c r="AZ38">
         <v>1.92</v>
       </c>
-      <c r="AW38">
-        <v>1.57</v>
-      </c>
-      <c r="AX38">
-        <v>1.35</v>
-      </c>
-      <c r="AY38">
-        <v>0</v>
-      </c>
-      <c r="AZ38">
-        <v>1.5</v>
-      </c>
       <c r="BA38">
-        <v>2.8</v>
+        <v>2.05</v>
       </c>
       <c r="BB38">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="BC38">
-        <v>2.91</v>
+        <v>3.12</v>
       </c>
       <c r="BD38">
-        <v>2.66</v>
+        <v>2.53</v>
       </c>
       <c r="BE38">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="BF38">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BG38">
         <v>0</v>

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -340,45 +340,45 @@
     <t>Daejeon Citizen</t>
   </si>
   <si>
+    <t>Gangwon</t>
+  </si>
+  <si>
     <t>Sangju Sangmu</t>
   </si>
   <si>
-    <t>Gangwon</t>
-  </si>
-  <si>
     <t>Madura United</t>
   </si>
   <si>
+    <t>FC Seoul</t>
+  </si>
+  <si>
     <t>Ethiopia Nigd Bank</t>
   </si>
   <si>
-    <t>FC Seoul</t>
-  </si>
-  <si>
     <t>Qingdao Youth Island</t>
   </si>
   <si>
     <t>Tanjong Pagar</t>
   </si>
   <si>
+    <t>Shenyang Urban</t>
+  </si>
+  <si>
     <t>Shandong Luneng</t>
   </si>
   <si>
-    <t>Shenyang Urban</t>
+    <t>Dire Dawa Kenema</t>
   </si>
   <si>
     <t>Borneo</t>
   </si>
   <si>
-    <t>Dire Dawa Kenema</t>
+    <t>Chongqing Tongliang Long</t>
   </si>
   <si>
     <t>Karvan FK</t>
   </si>
   <si>
-    <t>Chongqing Tongliang Long</t>
-  </si>
-  <si>
     <t>Mekelle Kenema</t>
   </si>
   <si>
@@ -406,36 +406,36 @@
     <t>Maccabi Tel Aviv</t>
   </si>
   <si>
+    <t>Dibba Al Fujairah</t>
+  </si>
+  <si>
     <t>Bani Yas</t>
   </si>
   <si>
     <t>Al Ittihad Kalba</t>
   </si>
   <si>
-    <t>Dibba Al Fujairah</t>
+    <t>Lokomotiv Sofia 1929</t>
+  </si>
+  <si>
+    <t>Ceramica Cleopatra</t>
+  </si>
+  <si>
+    <t>Falkenberg</t>
+  </si>
+  <si>
+    <t>Smouha SC</t>
   </si>
   <si>
     <t>Al Ahly</t>
   </si>
   <si>
-    <t>Ceramica Cleopatra</t>
-  </si>
-  <si>
-    <t>Smouha SC</t>
-  </si>
-  <si>
-    <t>Falkenberg</t>
-  </si>
-  <si>
-    <t>Lokomotiv Sofia 1929</t>
+    <t>Stellenbosch</t>
   </si>
   <si>
     <t>Chippa United</t>
   </si>
   <si>
-    <t>Stellenbosch</t>
-  </si>
-  <si>
     <t>Magesi</t>
   </si>
   <si>
@@ -460,45 +460,45 @@
     <t>Incheon United</t>
   </si>
   <si>
+    <t>Pohang Steelers</t>
+  </si>
+  <si>
     <t>Ulsan</t>
   </si>
   <si>
-    <t>Pohang Steelers</t>
-  </si>
-  <si>
     <t>Bali United</t>
   </si>
   <si>
+    <t>Anyang</t>
+  </si>
+  <si>
     <t>Kedus Giorgis</t>
   </si>
   <si>
-    <t>Anyang</t>
-  </si>
-  <si>
     <t>Tianjin Teda</t>
   </si>
   <si>
     <t>Hougang United</t>
   </si>
   <si>
+    <t>Chengdu Better City FC</t>
+  </si>
+  <si>
     <t>Shanghai Shenhua</t>
   </si>
   <si>
-    <t>Chengdu Better City FC</t>
+    <t>Ethiopia Bunna</t>
   </si>
   <si>
     <t>Persita</t>
   </si>
   <si>
-    <t>Ethiopia Bunna</t>
+    <t>Henan Jianye</t>
   </si>
   <si>
     <t>Neftçi</t>
   </si>
   <si>
-    <t>Henan Jianye</t>
-  </si>
-  <si>
     <t>Arba Minch Kenema</t>
   </si>
   <si>
@@ -526,31 +526,31 @@
     <t>Hapoel Petah Tikva</t>
   </si>
   <si>
+    <t>Al Bataeh</t>
+  </si>
+  <si>
     <t>Al Dhafra</t>
   </si>
   <si>
-    <t>Al Bataeh</t>
+    <t>Botev Vratsa</t>
+  </si>
+  <si>
+    <t>Pyramids FC</t>
+  </si>
+  <si>
+    <t>Norrköping</t>
+  </si>
+  <si>
+    <t>Zamalek</t>
   </si>
   <si>
     <t>ENPPI</t>
   </si>
   <si>
-    <t>Pyramids FC</t>
-  </si>
-  <si>
-    <t>Zamalek</t>
-  </si>
-  <si>
-    <t>Norrköping</t>
-  </si>
-  <si>
-    <t>Botev Vratsa</t>
+    <t>Orlando Pirates</t>
   </si>
   <si>
     <t>Sekhukhune United</t>
-  </si>
-  <si>
-    <t>Orlando Pirates</t>
   </si>
   <si>
     <t>Orbit College</t>
@@ -2116,10 +2116,10 @@
         <v>2.88</v>
       </c>
       <c r="X7">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="Y7">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="Z7">
         <v>5.65</v>
@@ -2155,7 +2155,7 @@
         <v>1.12</v>
       </c>
       <c r="AK7">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AL7">
         <v>2.24</v>
@@ -2238,10 +2238,10 @@
         <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
         <v>111</v>
@@ -2423,10 +2423,10 @@
         <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E9" t="s">
         <v>112</v>
@@ -3017,133 +3017,133 @@
         <v>184</v>
       </c>
       <c r="P12">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>2.95</v>
+        <v>5.65</v>
       </c>
       <c r="T12">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="U12">
-        <v>3.02</v>
+        <v>2.01</v>
       </c>
       <c r="V12">
+        <v>1.32</v>
+      </c>
+      <c r="W12">
+        <v>3.05</v>
+      </c>
+      <c r="X12">
+        <v>2.56</v>
+      </c>
+      <c r="Y12">
+        <v>1.44</v>
+      </c>
+      <c r="Z12">
+        <v>6</v>
+      </c>
+      <c r="AA12">
+        <v>1.06</v>
+      </c>
+      <c r="AB12">
+        <v>1.03</v>
+      </c>
+      <c r="AC12">
+        <v>1.21</v>
+      </c>
+      <c r="AD12">
+        <v>3.58</v>
+      </c>
+      <c r="AE12">
+        <v>1.81</v>
+      </c>
+      <c r="AF12">
+        <v>2.02</v>
+      </c>
+      <c r="AG12">
+        <v>2.83</v>
+      </c>
+      <c r="AH12">
+        <v>1.33</v>
+      </c>
+      <c r="AI12">
+        <v>5.25</v>
+      </c>
+      <c r="AJ12">
+        <v>1.09</v>
+      </c>
+      <c r="AK12">
+        <v>1.84</v>
+      </c>
+      <c r="AL12">
+        <v>1.86</v>
+      </c>
+      <c r="AM12">
         <v>1.22</v>
       </c>
-      <c r="W12">
-        <v>3.6</v>
-      </c>
-      <c r="X12">
-        <v>2.08</v>
-      </c>
-      <c r="Y12">
-        <v>1.69</v>
-      </c>
-      <c r="Z12">
-        <v>4.45</v>
-      </c>
-      <c r="AA12">
-        <v>1.14</v>
-      </c>
-      <c r="AB12">
-        <v>1.02</v>
-      </c>
-      <c r="AC12">
-        <v>1.08</v>
-      </c>
-      <c r="AD12">
-        <v>5.65</v>
-      </c>
-      <c r="AE12">
-        <v>1.39</v>
-      </c>
-      <c r="AF12">
-        <v>2.59</v>
-      </c>
-      <c r="AG12">
-        <v>2.1</v>
-      </c>
-      <c r="AH12">
-        <v>1.75</v>
-      </c>
-      <c r="AI12">
-        <v>3.28</v>
-      </c>
-      <c r="AJ12">
-        <v>1.25</v>
-      </c>
-      <c r="AK12">
-        <v>1.36</v>
-      </c>
-      <c r="AL12">
-        <v>2.9</v>
-      </c>
-      <c r="AM12">
-        <v>1.28</v>
-      </c>
       <c r="AN12">
-        <v>1.51</v>
+        <v>1.13</v>
       </c>
       <c r="AO12">
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AQ12">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR12">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AS12">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AT12">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AU12">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AV12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AW12">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AX12">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AY12">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AZ12">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BA12">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BB12">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="BC12">
-        <v>1.63</v>
+        <v>2.01</v>
       </c>
       <c r="BD12">
-        <v>5.7</v>
+        <v>4.05</v>
       </c>
       <c r="BE12">
-        <v>2.17</v>
+        <v>1.74</v>
       </c>
       <c r="BF12">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="BG12">
         <v>0</v>
@@ -3202,133 +3202,133 @@
         <v>184</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S13">
+        <v>2.95</v>
+      </c>
+      <c r="T13">
+        <v>2.27</v>
+      </c>
+      <c r="U13">
+        <v>3.02</v>
+      </c>
+      <c r="V13">
+        <v>1.22</v>
+      </c>
+      <c r="W13">
+        <v>3.6</v>
+      </c>
+      <c r="X13">
+        <v>2.08</v>
+      </c>
+      <c r="Y13">
+        <v>1.69</v>
+      </c>
+      <c r="Z13">
+        <v>4.45</v>
+      </c>
+      <c r="AA13">
+        <v>1.14</v>
+      </c>
+      <c r="AB13">
+        <v>1.02</v>
+      </c>
+      <c r="AC13">
+        <v>1.08</v>
+      </c>
+      <c r="AD13">
         <v>5.65</v>
       </c>
-      <c r="T13">
-        <v>2.29</v>
-      </c>
-      <c r="U13">
-        <v>2.01</v>
-      </c>
-      <c r="V13">
-        <v>1.32</v>
-      </c>
-      <c r="W13">
-        <v>3.05</v>
-      </c>
-      <c r="X13">
-        <v>2.56</v>
-      </c>
-      <c r="Y13">
-        <v>1.44</v>
-      </c>
-      <c r="Z13">
-        <v>6</v>
-      </c>
-      <c r="AA13">
-        <v>1.06</v>
-      </c>
-      <c r="AB13">
-        <v>1.03</v>
-      </c>
-      <c r="AC13">
-        <v>1.21</v>
-      </c>
-      <c r="AD13">
-        <v>3.58</v>
-      </c>
       <c r="AE13">
-        <v>1.81</v>
+        <v>1.39</v>
       </c>
       <c r="AF13">
-        <v>2.02</v>
+        <v>2.59</v>
       </c>
       <c r="AG13">
-        <v>2.83</v>
+        <v>2.1</v>
       </c>
       <c r="AH13">
+        <v>1.75</v>
+      </c>
+      <c r="AI13">
+        <v>3.28</v>
+      </c>
+      <c r="AJ13">
+        <v>1.25</v>
+      </c>
+      <c r="AK13">
+        <v>1.36</v>
+      </c>
+      <c r="AL13">
+        <v>2.9</v>
+      </c>
+      <c r="AM13">
+        <v>1.28</v>
+      </c>
+      <c r="AN13">
+        <v>1.51</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>1.12</v>
+      </c>
+      <c r="AQ13">
+        <v>1.3</v>
+      </c>
+      <c r="AR13">
+        <v>1.72</v>
+      </c>
+      <c r="AS13">
+        <v>1.92</v>
+      </c>
+      <c r="AT13">
+        <v>2.44</v>
+      </c>
+      <c r="AU13">
+        <v>4.5</v>
+      </c>
+      <c r="AV13">
+        <v>3</v>
+      </c>
+      <c r="AW13">
+        <v>2.23</v>
+      </c>
+      <c r="AX13">
+        <v>1.78</v>
+      </c>
+      <c r="AY13">
+        <v>1.47</v>
+      </c>
+      <c r="AZ13">
+        <v>1.65</v>
+      </c>
+      <c r="BA13">
+        <v>2.88</v>
+      </c>
+      <c r="BB13">
+        <v>1.08</v>
+      </c>
+      <c r="BC13">
+        <v>1.63</v>
+      </c>
+      <c r="BD13">
+        <v>5.7</v>
+      </c>
+      <c r="BE13">
+        <v>2.17</v>
+      </c>
+      <c r="BF13">
         <v>1.33</v>
-      </c>
-      <c r="AI13">
-        <v>5.25</v>
-      </c>
-      <c r="AJ13">
-        <v>1.09</v>
-      </c>
-      <c r="AK13">
-        <v>1.84</v>
-      </c>
-      <c r="AL13">
-        <v>1.86</v>
-      </c>
-      <c r="AM13">
-        <v>1.22</v>
-      </c>
-      <c r="AN13">
-        <v>1.13</v>
-      </c>
-      <c r="AO13">
-        <v>0</v>
-      </c>
-      <c r="AP13">
-        <v>0</v>
-      </c>
-      <c r="AQ13">
-        <v>0</v>
-      </c>
-      <c r="AR13">
-        <v>0</v>
-      </c>
-      <c r="AS13">
-        <v>0</v>
-      </c>
-      <c r="AT13">
-        <v>0</v>
-      </c>
-      <c r="AU13">
-        <v>0</v>
-      </c>
-      <c r="AV13">
-        <v>0</v>
-      </c>
-      <c r="AW13">
-        <v>0</v>
-      </c>
-      <c r="AX13">
-        <v>0</v>
-      </c>
-      <c r="AY13">
-        <v>0</v>
-      </c>
-      <c r="AZ13">
-        <v>0</v>
-      </c>
-      <c r="BA13">
-        <v>0</v>
-      </c>
-      <c r="BB13">
-        <v>1.18</v>
-      </c>
-      <c r="BC13">
-        <v>2.01</v>
-      </c>
-      <c r="BD13">
-        <v>4.05</v>
-      </c>
-      <c r="BE13">
-        <v>1.74</v>
-      </c>
-      <c r="BF13">
-        <v>1.17</v>
       </c>
       <c r="BG13">
         <v>0</v>
@@ -3348,7 +3348,7 @@
         <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D14" t="s">
         <v>103</v>
@@ -3387,133 +3387,133 @@
         <v>184</v>
       </c>
       <c r="P14">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R14">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>5.61</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD14">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AH14">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AI14">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AJ14">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK14">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM14">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AN14">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AO14">
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ14">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AR14">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AS14">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AT14">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AU14">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AV14">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="AW14">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AX14">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AY14">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AZ14">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="BA14">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="BB14">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC14">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BD14">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="BE14">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BF14">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG14">
         <v>0</v>
@@ -3533,7 +3533,7 @@
         <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D15" t="s">
         <v>103</v>
@@ -3572,133 +3572,133 @@
         <v>184</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI15">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM15">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN15">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AO15">
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AU15">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AV15">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AW15">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AX15">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY15">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AZ15">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="BA15">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="BB15">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC15">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BD15">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="BE15">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BF15">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG15">
         <v>0</v>
@@ -3718,10 +3718,10 @@
         <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E16" t="s">
         <v>119</v>
@@ -3766,70 +3766,70 @@
         <v>0</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL16">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AM16">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AO16">
         <v>0</v>
@@ -3871,19 +3871,19 @@
         <v>0</v>
       </c>
       <c r="BB16">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC16">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BD16">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="BE16">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF16">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG16">
         <v>0</v>
@@ -3903,10 +3903,10 @@
         <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E17" t="s">
         <v>120</v>
@@ -3951,70 +3951,70 @@
         <v>0</v>
       </c>
       <c r="S17">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="V17">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W17">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="X17">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y17">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z17">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AA17">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC17">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD17">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AE17">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG17">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AH17">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI17">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AJ17">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK17">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AL17">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AM17">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN17">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AO17">
         <v>0</v>
@@ -4056,19 +4056,19 @@
         <v>0</v>
       </c>
       <c r="BB17">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC17">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="BD17">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="BE17">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF17">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG17">
         <v>0</v>
@@ -5947,7 +5947,7 @@
         <v>131</v>
       </c>
       <c r="F28" t="s">
-        <v>142</v>
+        <v>171</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -6132,7 +6132,7 @@
         <v>132</v>
       </c>
       <c r="F29" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -6308,7 +6308,7 @@
         <v>79</v>
       </c>
       <c r="C30" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D30" t="s">
         <v>103</v>
@@ -6347,130 +6347,130 @@
         <v>184</v>
       </c>
       <c r="P30">
+        <v>1.95</v>
+      </c>
+      <c r="Q30">
+        <v>3.25</v>
+      </c>
+      <c r="R30">
+        <v>3.79</v>
+      </c>
+      <c r="S30">
+        <v>2.48</v>
+      </c>
+      <c r="T30">
+        <v>2.1</v>
+      </c>
+      <c r="U30">
+        <v>4.1</v>
+      </c>
+      <c r="V30">
+        <v>1.37</v>
+      </c>
+      <c r="W30">
+        <v>2.7</v>
+      </c>
+      <c r="X30">
+        <v>2.88</v>
+      </c>
+      <c r="Y30">
+        <v>1.33</v>
+      </c>
+      <c r="Z30">
+        <v>7</v>
+      </c>
+      <c r="AA30">
+        <v>1.03</v>
+      </c>
+      <c r="AB30">
+        <v>0</v>
+      </c>
+      <c r="AC30">
+        <v>1.32</v>
+      </c>
+      <c r="AD30">
+        <v>3</v>
+      </c>
+      <c r="AE30">
+        <v>2.02</v>
+      </c>
+      <c r="AF30">
+        <v>1.68</v>
+      </c>
+      <c r="AG30">
+        <v>3.6</v>
+      </c>
+      <c r="AH30">
+        <v>1.24</v>
+      </c>
+      <c r="AI30">
+        <v>6.75</v>
+      </c>
+      <c r="AJ30">
+        <v>1.07</v>
+      </c>
+      <c r="AK30">
+        <v>1.8</v>
+      </c>
+      <c r="AL30">
+        <v>1.84</v>
+      </c>
+      <c r="AM30">
+        <v>1.27</v>
+      </c>
+      <c r="AN30">
+        <v>1.75</v>
+      </c>
+      <c r="AO30">
+        <v>0</v>
+      </c>
+      <c r="AP30">
         <v>1.4</v>
       </c>
-      <c r="Q30">
-        <v>3.9</v>
-      </c>
-      <c r="R30">
-        <v>7</v>
-      </c>
-      <c r="S30">
-        <v>0</v>
-      </c>
-      <c r="T30">
-        <v>0</v>
-      </c>
-      <c r="U30">
-        <v>0</v>
-      </c>
-      <c r="V30">
-        <v>0</v>
-      </c>
-      <c r="W30">
-        <v>0</v>
-      </c>
-      <c r="X30">
-        <v>0</v>
-      </c>
-      <c r="Y30">
-        <v>0</v>
-      </c>
-      <c r="Z30">
-        <v>0</v>
-      </c>
-      <c r="AA30">
-        <v>0</v>
-      </c>
-      <c r="AB30">
-        <v>0</v>
-      </c>
-      <c r="AC30">
-        <v>0</v>
-      </c>
-      <c r="AD30">
-        <v>0</v>
-      </c>
-      <c r="AE30">
-        <v>0</v>
-      </c>
-      <c r="AF30">
-        <v>0</v>
-      </c>
-      <c r="AG30">
-        <v>0</v>
-      </c>
-      <c r="AH30">
-        <v>0</v>
-      </c>
-      <c r="AI30">
-        <v>0</v>
-      </c>
-      <c r="AJ30">
-        <v>0</v>
-      </c>
-      <c r="AK30">
-        <v>0</v>
-      </c>
-      <c r="AL30">
-        <v>0</v>
-      </c>
-      <c r="AM30">
-        <v>0</v>
-      </c>
-      <c r="AN30">
-        <v>0</v>
-      </c>
-      <c r="AO30">
-        <v>0</v>
-      </c>
-      <c r="AP30">
-        <v>0</v>
-      </c>
       <c r="AQ30">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT30">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AU30">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV30">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AW30">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AX30">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY30">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ30">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BA30">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BB30">
         <v>0</v>
       </c>
       <c r="BC30">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD30">
         <v>0</v>
       </c>
       <c r="BE30">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF30">
         <v>0</v>
@@ -6535,7 +6535,7 @@
         <v>4</v>
       </c>
       <c r="Q31">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R31">
         <v>1.8</v>
@@ -6556,10 +6556,10 @@
         <v>2.41</v>
       </c>
       <c r="X31">
-        <v>3.08</v>
+        <v>3.32</v>
       </c>
       <c r="Y31">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z31">
         <v>7.7</v>
@@ -6571,16 +6571,16 @@
         <v>1.04</v>
       </c>
       <c r="AC31">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AD31">
         <v>2.74</v>
       </c>
       <c r="AE31">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AF31">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AG31">
         <v>3.8</v>
@@ -6610,40 +6610,40 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AQ31">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AR31">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AS31">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="AT31">
-        <v>3.55</v>
+        <v>3.48</v>
       </c>
       <c r="AU31">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="AV31">
-        <v>2.06</v>
+        <v>2.21</v>
       </c>
       <c r="AW31">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AX31">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AY31">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AZ31">
-        <v>2.65</v>
+        <v>2.48</v>
       </c>
       <c r="BA31">
-        <v>1.55</v>
+        <v>1.84</v>
       </c>
       <c r="BB31">
         <v>1.27</v>
@@ -6678,10 +6678,10 @@
         <v>79</v>
       </c>
       <c r="C32" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D32" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E32" t="s">
         <v>135</v>
@@ -6717,13 +6717,13 @@
         <v>184</v>
       </c>
       <c r="P32">
-        <v>4.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q32">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="R32">
-        <v>1.72</v>
+        <v>2.52</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -6762,10 +6762,10 @@
         <v>0</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG32">
         <v>0</v>
@@ -6863,10 +6863,10 @@
         <v>79</v>
       </c>
       <c r="C33" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E33" t="s">
         <v>136</v>
@@ -6902,133 +6902,133 @@
         <v>184</v>
       </c>
       <c r="P33">
-        <v>2.5</v>
+        <v>5.05</v>
       </c>
       <c r="Q33">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="R33">
-        <v>2.52</v>
+        <v>1.73</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AE33">
-        <v>1.66</v>
+        <v>2.75</v>
       </c>
       <c r="AF33">
-        <v>2.15</v>
+        <v>1.47</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="AH33">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI33">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AL33">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AM33">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN33">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AO33">
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AQ33">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AR33">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AS33">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AT33">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AU33">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AV33">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AW33">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AX33">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY33">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ33">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BA33">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BB33">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC33">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="BD33">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="BE33">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BF33">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG33">
         <v>0</v>
@@ -7048,7 +7048,7 @@
         <v>79</v>
       </c>
       <c r="C34" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D34" t="s">
         <v>103</v>
@@ -7087,133 +7087,133 @@
         <v>184</v>
       </c>
       <c r="P34">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="Q34">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="R34">
-        <v>3.79</v>
+        <v>6.5</v>
       </c>
       <c r="S34">
-        <v>2.48</v>
+        <v>2.01</v>
       </c>
       <c r="T34">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="U34">
-        <v>4.1</v>
+        <v>7.7</v>
       </c>
       <c r="V34">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="W34">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="X34">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="Y34">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z34">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="AA34">
         <v>1.03</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC34">
         <v>1.32</v>
       </c>
       <c r="AD34">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AE34">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="AF34">
         <v>1.68</v>
       </c>
       <c r="AG34">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AH34">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AI34">
         <v>6.75</v>
       </c>
       <c r="AJ34">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AK34">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AL34">
-        <v>1.84</v>
+        <v>1.54</v>
       </c>
       <c r="AM34">
+        <v>1.17</v>
+      </c>
+      <c r="AN34">
+        <v>2.57</v>
+      </c>
+      <c r="AO34">
+        <v>0</v>
+      </c>
+      <c r="AP34">
+        <v>1.24</v>
+      </c>
+      <c r="AQ34">
+        <v>1.46</v>
+      </c>
+      <c r="AR34">
+        <v>2.13</v>
+      </c>
+      <c r="AS34">
+        <v>2.33</v>
+      </c>
+      <c r="AT34">
+        <v>3.14</v>
+      </c>
+      <c r="AU34">
+        <v>3.34</v>
+      </c>
+      <c r="AV34">
+        <v>2.38</v>
+      </c>
+      <c r="AW34">
+        <v>1.83</v>
+      </c>
+      <c r="AX34">
+        <v>1.48</v>
+      </c>
+      <c r="AY34">
         <v>1.27</v>
       </c>
-      <c r="AN34">
-        <v>1.75</v>
-      </c>
-      <c r="AO34">
-        <v>0</v>
-      </c>
-      <c r="AP34">
-        <v>1.4</v>
-      </c>
-      <c r="AQ34">
-        <v>1.67</v>
-      </c>
-      <c r="AR34">
-        <v>2.1</v>
-      </c>
-      <c r="AS34">
-        <v>2.7</v>
-      </c>
-      <c r="AT34">
-        <v>3.65</v>
-      </c>
-      <c r="AU34">
-        <v>2.7</v>
-      </c>
-      <c r="AV34">
-        <v>2.04</v>
-      </c>
-      <c r="AW34">
-        <v>1.64</v>
-      </c>
-      <c r="AX34">
-        <v>1.38</v>
-      </c>
-      <c r="AY34">
-        <v>1.23</v>
-      </c>
       <c r="AZ34">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="BA34">
-        <v>2.5</v>
+        <v>4.32</v>
       </c>
       <c r="BB34">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC34">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="BD34">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="BE34">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="BF34">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG34">
         <v>0</v>
@@ -7272,133 +7272,133 @@
         <v>184</v>
       </c>
       <c r="P35">
+        <v>4.65</v>
+      </c>
+      <c r="Q35">
+        <v>3.3</v>
+      </c>
+      <c r="R35">
+        <v>1.62</v>
+      </c>
+      <c r="S35">
+        <v>6.93</v>
+      </c>
+      <c r="T35">
+        <v>1.9</v>
+      </c>
+      <c r="U35">
+        <v>2.3</v>
+      </c>
+      <c r="V35">
+        <v>1.55</v>
+      </c>
+      <c r="W35">
+        <v>2.28</v>
+      </c>
+      <c r="X35">
+        <v>3.5</v>
+      </c>
+      <c r="Y35">
+        <v>1.22</v>
+      </c>
+      <c r="Z35">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AA35">
+        <v>1.04</v>
+      </c>
+      <c r="AB35">
+        <v>1.1</v>
+      </c>
+      <c r="AC35">
+        <v>1.49</v>
+      </c>
+      <c r="AD35">
+        <v>2.35</v>
+      </c>
+      <c r="AE35">
+        <v>2.65</v>
+      </c>
+      <c r="AF35">
+        <v>1.45</v>
+      </c>
+      <c r="AG35">
+        <v>5.18</v>
+      </c>
+      <c r="AH35">
+        <v>1.11</v>
+      </c>
+      <c r="AI35">
+        <v>11</v>
+      </c>
+      <c r="AJ35">
+        <v>1.04</v>
+      </c>
+      <c r="AK35">
+        <v>2.3</v>
+      </c>
+      <c r="AL35">
+        <v>1.5</v>
+      </c>
+      <c r="AM35">
+        <v>1.26</v>
+      </c>
+      <c r="AN35">
+        <v>1.07</v>
+      </c>
+      <c r="AO35">
+        <v>0</v>
+      </c>
+      <c r="AP35">
+        <v>1.32</v>
+      </c>
+      <c r="AQ35">
+        <v>1.61</v>
+      </c>
+      <c r="AR35">
+        <v>2.34</v>
+      </c>
+      <c r="AS35">
+        <v>2.61</v>
+      </c>
+      <c r="AT35">
         <v>3.63</v>
       </c>
-      <c r="Q35">
-        <v>3.02</v>
-      </c>
-      <c r="R35">
-        <v>2.03</v>
-      </c>
-      <c r="S35">
-        <v>4.43</v>
-      </c>
-      <c r="T35">
-        <v>1.88</v>
-      </c>
-      <c r="U35">
-        <v>2.88</v>
-      </c>
-      <c r="V35">
-        <v>1.51</v>
-      </c>
-      <c r="W35">
-        <v>2.31</v>
-      </c>
-      <c r="X35">
-        <v>3.38</v>
-      </c>
-      <c r="Y35">
-        <v>1.25</v>
-      </c>
-      <c r="Z35">
-        <v>9.1</v>
-      </c>
-      <c r="AA35">
-        <v>1</v>
-      </c>
-      <c r="AB35">
+      <c r="AU35">
+        <v>2.94</v>
+      </c>
+      <c r="AV35">
+        <v>2.16</v>
+      </c>
+      <c r="AW35">
+        <v>1.71</v>
+      </c>
+      <c r="AX35">
+        <v>1.4</v>
+      </c>
+      <c r="AY35">
+        <v>1.2</v>
+      </c>
+      <c r="AZ35">
+        <v>4.42</v>
+      </c>
+      <c r="BA35">
+        <v>1.37</v>
+      </c>
+      <c r="BB35">
+        <v>1.35</v>
+      </c>
+      <c r="BC35">
+        <v>2.66</v>
+      </c>
+      <c r="BD35">
+        <v>2.82</v>
+      </c>
+      <c r="BE35">
+        <v>1.39</v>
+      </c>
+      <c r="BF35">
         <v>1.05</v>
-      </c>
-      <c r="AC35">
-        <v>1.43</v>
-      </c>
-      <c r="AD35">
-        <v>2.46</v>
-      </c>
-      <c r="AE35">
-        <v>2.44</v>
-      </c>
-      <c r="AF35">
-        <v>1.49</v>
-      </c>
-      <c r="AG35">
-        <v>4.6</v>
-      </c>
-      <c r="AH35">
-        <v>1.13</v>
-      </c>
-      <c r="AI35">
-        <v>8.5</v>
-      </c>
-      <c r="AJ35">
-        <v>1.03</v>
-      </c>
-      <c r="AK35">
-        <v>2.04</v>
-      </c>
-      <c r="AL35">
-        <v>1.68</v>
-      </c>
-      <c r="AM35">
-        <v>1.3</v>
-      </c>
-      <c r="AN35">
-        <v>1.24</v>
-      </c>
-      <c r="AO35">
-        <v>0</v>
-      </c>
-      <c r="AP35">
-        <v>1.37</v>
-      </c>
-      <c r="AQ35">
-        <v>1.63</v>
-      </c>
-      <c r="AR35">
-        <v>2.02</v>
-      </c>
-      <c r="AS35">
-        <v>2.6</v>
-      </c>
-      <c r="AT35">
-        <v>3.4</v>
-      </c>
-      <c r="AU35">
-        <v>2.8</v>
-      </c>
-      <c r="AV35">
-        <v>2.1</v>
-      </c>
-      <c r="AW35">
-        <v>1.68</v>
-      </c>
-      <c r="AX35">
-        <v>1.43</v>
-      </c>
-      <c r="AY35">
-        <v>1.26</v>
-      </c>
-      <c r="AZ35">
-        <v>2.35</v>
-      </c>
-      <c r="BA35">
-        <v>1.68</v>
-      </c>
-      <c r="BB35">
-        <v>1.32</v>
-      </c>
-      <c r="BC35">
-        <v>2.59</v>
-      </c>
-      <c r="BD35">
-        <v>2.96</v>
-      </c>
-      <c r="BE35">
-        <v>1.41</v>
-      </c>
-      <c r="BF35">
-        <v>1.06</v>
       </c>
       <c r="BG35">
         <v>0</v>
@@ -7457,133 +7457,133 @@
         <v>184</v>
       </c>
       <c r="P36">
-        <v>6.29</v>
+        <v>3.2</v>
       </c>
       <c r="Q36">
-        <v>3.48</v>
+        <v>3</v>
       </c>
       <c r="R36">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="S36">
-        <v>6.93</v>
+        <v>4.43</v>
       </c>
       <c r="T36">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="U36">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="V36">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="W36">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="X36">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="Y36">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z36">
-        <v>7.8</v>
+        <v>9.1</v>
       </c>
       <c r="AA36">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AB36">
+        <v>1.05</v>
+      </c>
+      <c r="AC36">
+        <v>1.43</v>
+      </c>
+      <c r="AD36">
+        <v>2.46</v>
+      </c>
+      <c r="AE36">
+        <v>2.44</v>
+      </c>
+      <c r="AF36">
+        <v>1.49</v>
+      </c>
+      <c r="AG36">
+        <v>4.6</v>
+      </c>
+      <c r="AH36">
+        <v>1.13</v>
+      </c>
+      <c r="AI36">
+        <v>10</v>
+      </c>
+      <c r="AJ36">
+        <v>1.05</v>
+      </c>
+      <c r="AK36">
+        <v>2.04</v>
+      </c>
+      <c r="AL36">
+        <v>1.68</v>
+      </c>
+      <c r="AM36">
+        <v>1.3</v>
+      </c>
+      <c r="AN36">
+        <v>1.24</v>
+      </c>
+      <c r="AO36">
+        <v>0</v>
+      </c>
+      <c r="AP36">
+        <v>1.31</v>
+      </c>
+      <c r="AQ36">
+        <v>1.72</v>
+      </c>
+      <c r="AR36">
+        <v>2.31</v>
+      </c>
+      <c r="AS36">
+        <v>2.57</v>
+      </c>
+      <c r="AT36">
+        <v>3.56</v>
+      </c>
+      <c r="AU36">
+        <v>2.98</v>
+      </c>
+      <c r="AV36">
+        <v>2.18</v>
+      </c>
+      <c r="AW36">
+        <v>1.73</v>
+      </c>
+      <c r="AX36">
+        <v>1.42</v>
+      </c>
+      <c r="AY36">
+        <v>1.21</v>
+      </c>
+      <c r="AZ36">
+        <v>2.16</v>
+      </c>
+      <c r="BA36">
+        <v>2.1</v>
+      </c>
+      <c r="BB36">
+        <v>1.32</v>
+      </c>
+      <c r="BC36">
+        <v>2.59</v>
+      </c>
+      <c r="BD36">
+        <v>2.9</v>
+      </c>
+      <c r="BE36">
+        <v>1.41</v>
+      </c>
+      <c r="BF36">
         <v>1.06</v>
-      </c>
-      <c r="AC36">
-        <v>1.47</v>
-      </c>
-      <c r="AD36">
-        <v>2.35</v>
-      </c>
-      <c r="AE36">
-        <v>2.55</v>
-      </c>
-      <c r="AF36">
-        <v>1.45</v>
-      </c>
-      <c r="AG36">
-        <v>4.9</v>
-      </c>
-      <c r="AH36">
-        <v>1.11</v>
-      </c>
-      <c r="AI36">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="AJ36">
-        <v>1.03</v>
-      </c>
-      <c r="AK36">
-        <v>2.4</v>
-      </c>
-      <c r="AL36">
-        <v>1.5</v>
-      </c>
-      <c r="AM36">
-        <v>1.26</v>
-      </c>
-      <c r="AN36">
-        <v>1.07</v>
-      </c>
-      <c r="AO36">
-        <v>0</v>
-      </c>
-      <c r="AP36">
-        <v>1.7</v>
-      </c>
-      <c r="AQ36">
-        <v>2.15</v>
-      </c>
-      <c r="AR36">
-        <v>2.85</v>
-      </c>
-      <c r="AS36">
-        <v>3.85</v>
-      </c>
-      <c r="AT36">
-        <v>0</v>
-      </c>
-      <c r="AU36">
-        <v>2</v>
-      </c>
-      <c r="AV36">
-        <v>1.61</v>
-      </c>
-      <c r="AW36">
-        <v>1.36</v>
-      </c>
-      <c r="AX36">
-        <v>1.21</v>
-      </c>
-      <c r="AY36">
-        <v>0</v>
-      </c>
-      <c r="AZ36">
-        <v>3.1</v>
-      </c>
-      <c r="BA36">
-        <v>1.44</v>
-      </c>
-      <c r="BB36">
-        <v>1.35</v>
-      </c>
-      <c r="BC36">
-        <v>2.66</v>
-      </c>
-      <c r="BD36">
-        <v>2.82</v>
-      </c>
-      <c r="BE36">
-        <v>1.39</v>
-      </c>
-      <c r="BF36">
-        <v>1.05</v>
       </c>
       <c r="BG36">
         <v>0</v>
@@ -7642,22 +7642,22 @@
         <v>184</v>
       </c>
       <c r="P37">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="Q37">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="R37">
-        <v>3.89</v>
+        <v>3.7</v>
       </c>
       <c r="S37">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="T37">
         <v>1.75</v>
       </c>
       <c r="U37">
-        <v>5.15</v>
+        <v>5.37</v>
       </c>
       <c r="V37">
         <v>1.64</v>
@@ -7666,7 +7666,7 @@
         <v>2.11</v>
       </c>
       <c r="X37">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="Y37">
         <v>1.18</v>
@@ -7678,31 +7678,31 @@
         <v>1.02</v>
       </c>
       <c r="AB37">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AC37">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AD37">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AE37">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="AF37">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AG37">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="AH37">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AI37">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="AJ37">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AK37">
         <v>2.3</v>
@@ -7714,52 +7714,52 @@
         <v>1.35</v>
       </c>
       <c r="AN37">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="AO37">
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ37">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AR37">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="AS37">
-        <v>2.9</v>
+        <v>2.66</v>
       </c>
       <c r="AT37">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="AU37">
-        <v>2.5</v>
+        <v>2.89</v>
       </c>
       <c r="AV37">
-        <v>1.92</v>
+        <v>2.13</v>
       </c>
       <c r="AW37">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AX37">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AY37">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AZ37">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BA37">
-        <v>2.8</v>
+        <v>3.44</v>
       </c>
       <c r="BB37">
         <v>1.39</v>
       </c>
       <c r="BC37">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="BD37">
         <v>2.66</v>
@@ -7827,13 +7827,13 @@
         <v>184</v>
       </c>
       <c r="P38">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="Q38">
         <v>2.8</v>
       </c>
       <c r="R38">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="S38">
         <v>3.01</v>
@@ -7872,10 +7872,10 @@
         <v>2.09</v>
       </c>
       <c r="AE38">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AF38">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AG38">
         <v>6.35</v>
@@ -7884,7 +7884,7 @@
         <v>1.06</v>
       </c>
       <c r="AI38">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="AJ38">
         <v>1.02</v>
@@ -7905,40 +7905,40 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AQ38">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="AR38">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AS38">
-        <v>3.25</v>
+        <v>2.68</v>
       </c>
       <c r="AT38">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AU38">
-        <v>2.3</v>
+        <v>2.86</v>
       </c>
       <c r="AV38">
-        <v>1.79</v>
+        <v>2.12</v>
       </c>
       <c r="AW38">
-        <v>1.47</v>
+        <v>1.68</v>
       </c>
       <c r="AX38">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AY38">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AZ38">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="BA38">
-        <v>2.05</v>
+        <v>2.31</v>
       </c>
       <c r="BB38">
         <v>1.43</v>
@@ -8197,13 +8197,13 @@
         <v>184</v>
       </c>
       <c r="P40">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="Q40">
-        <v>3.62</v>
+        <v>3.92</v>
       </c>
       <c r="R40">
-        <v>5.28</v>
+        <v>4.7</v>
       </c>
       <c r="S40">
         <v>2.21</v>
@@ -8227,7 +8227,7 @@
         <v>1.43</v>
       </c>
       <c r="Z40">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AA40">
         <v>1.06</v>
@@ -8242,10 +8242,10 @@
         <v>3.4</v>
       </c>
       <c r="AE40">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AF40">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="AG40">
         <v>3.14</v>
@@ -8254,16 +8254,16 @@
         <v>1.3</v>
       </c>
       <c r="AI40">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="AJ40">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK40">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AL40">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AM40">
         <v>1.28</v>

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="189">
   <si>
     <t>Date</t>
   </si>
@@ -238,6 +238,9 @@
     <t>12:00</t>
   </si>
   <si>
+    <t>12:10</t>
+  </si>
+  <si>
     <t>12:30</t>
   </si>
   <si>
@@ -295,6 +298,9 @@
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>Oman Professional League</t>
+  </si>
+  <si>
     <t>Lithuania A Lyga</t>
   </si>
   <si>
@@ -331,12 +337,12 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Jeonbuk Motors</t>
+  </si>
+  <si>
     <t>Bucheon 1995</t>
   </si>
   <si>
-    <t>Jeonbuk Motors</t>
-  </si>
-  <si>
     <t>Daejeon Citizen</t>
   </si>
   <si>
@@ -367,18 +373,18 @@
     <t>Shandong Luneng</t>
   </si>
   <si>
+    <t>Chongqing Tongliang Long</t>
+  </si>
+  <si>
+    <t>Karvan FK</t>
+  </si>
+  <si>
     <t>Dire Dawa Kenema</t>
   </si>
   <si>
     <t>Borneo</t>
   </si>
   <si>
-    <t>Chongqing Tongliang Long</t>
-  </si>
-  <si>
-    <t>Karvan FK</t>
-  </si>
-  <si>
     <t>Mekelle Kenema</t>
   </si>
   <si>
@@ -394,6 +400,9 @@
     <t>Shire Endaselassie</t>
   </si>
   <si>
+    <t>Oman Club</t>
+  </si>
+  <si>
     <t>Trakai</t>
   </si>
   <si>
@@ -409,36 +418,36 @@
     <t>Dibba Al Fujairah</t>
   </si>
   <si>
+    <t>Al Ittihad Kalba</t>
+  </si>
+  <si>
     <t>Bani Yas</t>
   </si>
   <si>
-    <t>Al Ittihad Kalba</t>
+    <t>Ceramica Cleopatra</t>
+  </si>
+  <si>
+    <t>Al Ahly</t>
+  </si>
+  <si>
+    <t>Smouha SC</t>
   </si>
   <si>
     <t>Lokomotiv Sofia 1929</t>
   </si>
   <si>
-    <t>Ceramica Cleopatra</t>
-  </si>
-  <si>
     <t>Falkenberg</t>
   </si>
   <si>
-    <t>Smouha SC</t>
-  </si>
-  <si>
-    <t>Al Ahly</t>
+    <t>Chippa United</t>
+  </si>
+  <si>
+    <t>Magesi</t>
   </si>
   <si>
     <t>Stellenbosch</t>
   </si>
   <si>
-    <t>Chippa United</t>
-  </si>
-  <si>
-    <t>Magesi</t>
-  </si>
-  <si>
     <t>Siwelele</t>
   </si>
   <si>
@@ -451,12 +460,12 @@
     <t>New York City II</t>
   </si>
   <si>
+    <t>Gwangju</t>
+  </si>
+  <si>
     <t>Jeju United</t>
   </si>
   <si>
-    <t>Gwangju</t>
-  </si>
-  <si>
     <t>Incheon United</t>
   </si>
   <si>
@@ -487,18 +496,18 @@
     <t>Shanghai Shenhua</t>
   </si>
   <si>
+    <t>Henan Jianye</t>
+  </si>
+  <si>
+    <t>Neftçi</t>
+  </si>
+  <si>
     <t>Ethiopia Bunna</t>
   </si>
   <si>
     <t>Persita</t>
   </si>
   <si>
-    <t>Henan Jianye</t>
-  </si>
-  <si>
-    <t>Neftçi</t>
-  </si>
-  <si>
     <t>Arba Minch Kenema</t>
   </si>
   <si>
@@ -514,6 +523,9 @@
     <t>Mebrat Hayl</t>
   </si>
   <si>
+    <t>Smail</t>
+  </si>
+  <si>
     <t>Banga</t>
   </si>
   <si>
@@ -532,28 +544,28 @@
     <t>Al Dhafra</t>
   </si>
   <si>
+    <t>Pyramids FC</t>
+  </si>
+  <si>
+    <t>ENPPI</t>
+  </si>
+  <si>
+    <t>Zamalek</t>
+  </si>
+  <si>
     <t>Botev Vratsa</t>
   </si>
   <si>
-    <t>Pyramids FC</t>
-  </si>
-  <si>
     <t>Norrköping</t>
   </si>
   <si>
-    <t>Zamalek</t>
-  </si>
-  <si>
-    <t>ENPPI</t>
+    <t>Sekhukhune United</t>
+  </si>
+  <si>
+    <t>Orbit College</t>
   </si>
   <si>
     <t>Orlando Pirates</t>
-  </si>
-  <si>
-    <t>Sekhukhune United</t>
-  </si>
-  <si>
-    <t>Orbit College</t>
   </si>
   <si>
     <t>Durban City</t>
@@ -932,7 +944,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BI41"/>
+  <dimension ref="A1:BI42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:61">
@@ -1128,16 +1140,16 @@
         <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1164,7 +1176,7 @@
         <v>-1</v>
       </c>
       <c r="O2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -1313,16 +1325,16 @@
         <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1349,7 +1361,7 @@
         <v>-1</v>
       </c>
       <c r="O3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -1498,16 +1510,16 @@
         <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F4" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1534,7 +1546,7 @@
         <v>-1</v>
       </c>
       <c r="O4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -1683,16 +1695,16 @@
         <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1719,7 +1731,7 @@
         <v>-1</v>
       </c>
       <c r="O5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -1868,16 +1880,16 @@
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F6" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1904,7 +1916,7 @@
         <v>-1</v>
       </c>
       <c r="O6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1916,124 +1928,124 @@
         <v>0</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO6">
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AU6">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AV6">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AW6">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX6">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY6">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ6">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BA6">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC6">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD6">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BE6">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF6">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG6">
         <v>0</v>
@@ -2053,16 +2065,16 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F7" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -2089,7 +2101,7 @@
         <v>-1</v>
       </c>
       <c r="O7" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -2238,16 +2250,16 @@
         <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F8" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2274,7 +2286,7 @@
         <v>-1</v>
       </c>
       <c r="O8" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -2423,16 +2435,16 @@
         <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F9" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2459,7 +2471,7 @@
         <v>-1</v>
       </c>
       <c r="O9" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -2608,16 +2620,16 @@
         <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E10" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F10" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2644,7 +2656,7 @@
         <v>-1</v>
       </c>
       <c r="O10" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -2793,16 +2805,16 @@
         <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D11" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E11" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F11" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2829,7 +2841,7 @@
         <v>-1</v>
       </c>
       <c r="O11" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -2978,16 +2990,16 @@
         <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D12" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E12" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F12" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -3014,7 +3026,7 @@
         <v>-1</v>
       </c>
       <c r="O12" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -3163,16 +3175,16 @@
         <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E13" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F13" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -3199,7 +3211,7 @@
         <v>-1</v>
       </c>
       <c r="O13" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P13">
         <v>2.45</v>
@@ -3348,16 +3360,16 @@
         <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E14" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F14" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -3384,7 +3396,7 @@
         <v>-1</v>
       </c>
       <c r="O14" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -3396,70 +3408,70 @@
         <v>0</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AO14">
         <v>0</v>
@@ -3501,19 +3513,19 @@
         <v>0</v>
       </c>
       <c r="BB14">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC14">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BD14">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="BE14">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF14">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG14">
         <v>0</v>
@@ -3533,16 +3545,16 @@
         <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E15" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F15" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -3569,136 +3581,136 @@
         <v>-1</v>
       </c>
       <c r="O15" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P15">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Q15">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R15">
-        <v>4.87</v>
+        <v>0</v>
       </c>
       <c r="S15">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="T15">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>5.61</v>
+        <v>0</v>
       </c>
       <c r="V15">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W15">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X15">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y15">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z15">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA15">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC15">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD15">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AE15">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF15">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AG15">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AH15">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AI15">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AJ15">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK15">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM15">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AN15">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AO15">
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ15">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AR15">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AS15">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AT15">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AU15">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AV15">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="AW15">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AX15">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AY15">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AZ15">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="BA15">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="BB15">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC15">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BD15">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="BE15">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BF15">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG15">
         <v>0</v>
@@ -3721,13 +3733,13 @@
         <v>87</v>
       </c>
       <c r="D16" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E16" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -3754,7 +3766,7 @@
         <v>-1</v>
       </c>
       <c r="O16" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -3766,70 +3778,70 @@
         <v>0</v>
       </c>
       <c r="S16">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="V16">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W16">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="X16">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z16">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC16">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD16">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AE16">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AH16">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI16">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AJ16">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK16">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AL16">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AM16">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN16">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AO16">
         <v>0</v>
@@ -3871,19 +3883,19 @@
         <v>0</v>
       </c>
       <c r="BB16">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC16">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="BD16">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="BE16">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF16">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG16">
         <v>0</v>
@@ -3903,16 +3915,16 @@
         <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D17" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E17" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F17" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -3939,136 +3951,136 @@
         <v>-1</v>
       </c>
       <c r="O17" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI17">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM17">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AO17">
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AU17">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AV17">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AW17">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AX17">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY17">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AZ17">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="BA17">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="BB17">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC17">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BD17">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="BE17">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BF17">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG17">
         <v>0</v>
@@ -4088,16 +4100,16 @@
         <v>69</v>
       </c>
       <c r="C18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D18" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E18" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F18" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -4124,7 +4136,7 @@
         <v>-1</v>
       </c>
       <c r="O18" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -4273,16 +4285,16 @@
         <v>70</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D19" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E19" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F19" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -4309,7 +4321,7 @@
         <v>-1</v>
       </c>
       <c r="O19" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P19">
         <v>2.65</v>
@@ -4458,16 +4470,16 @@
         <v>71</v>
       </c>
       <c r="C20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D20" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F20" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -4494,7 +4506,7 @@
         <v>-1</v>
       </c>
       <c r="O20" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -4643,16 +4655,16 @@
         <v>72</v>
       </c>
       <c r="C21" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E21" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F21" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -4679,7 +4691,7 @@
         <v>-1</v>
       </c>
       <c r="O21" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P21">
         <v>2.11</v>
@@ -4828,16 +4840,16 @@
         <v>73</v>
       </c>
       <c r="C22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D22" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E22" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F22" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -4864,7 +4876,7 @@
         <v>-1</v>
       </c>
       <c r="O22" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P22">
         <v>0</v>
@@ -5013,16 +5025,16 @@
         <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D23" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E23" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F23" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -5049,25 +5061,25 @@
         <v>-1</v>
       </c>
       <c r="O23" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P23">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q23">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R23">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S23">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="T23">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U23">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V23">
         <v>0</v>
@@ -5076,10 +5088,10 @@
         <v>0</v>
       </c>
       <c r="X23">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Y23">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -5091,40 +5103,40 @@
         <v>0</v>
       </c>
       <c r="AC23">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AD23">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE23">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF23">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG23">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AH23">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI23">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AJ23">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK23">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL23">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AM23">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN23">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AO23">
         <v>0</v>
@@ -5169,13 +5181,13 @@
         <v>0</v>
       </c>
       <c r="BC23">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="BD23">
         <v>0</v>
       </c>
       <c r="BE23">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF23">
         <v>0</v>
@@ -5187,7 +5199,7 @@
         <v>0</v>
       </c>
       <c r="BI23" s="3">
-        <v>46147.52083333334</v>
+        <v>46147.50694444445</v>
       </c>
     </row>
     <row r="24" spans="1:61">
@@ -5198,16 +5210,16 @@
         <v>75</v>
       </c>
       <c r="C24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D24" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E24" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F24" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -5234,25 +5246,25 @@
         <v>-1</v>
       </c>
       <c r="O24" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P24">
-        <v>1.45</v>
+        <v>4</v>
       </c>
       <c r="Q24">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="R24">
-        <v>6.36</v>
+        <v>1.8</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V24">
         <v>0</v>
@@ -5261,10 +5273,10 @@
         <v>0</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -5276,40 +5288,40 @@
         <v>0</v>
       </c>
       <c r="AC24">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AD24">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AE24">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AF24">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AG24">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AH24">
         <v>1.3</v>
       </c>
       <c r="AI24">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AJ24">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AK24">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AL24">
-        <v>1.76</v>
+        <v>1.94</v>
       </c>
       <c r="AM24">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AN24">
-        <v>2.23</v>
+        <v>1.16</v>
       </c>
       <c r="AO24">
         <v>0</v>
@@ -5354,13 +5366,13 @@
         <v>0</v>
       </c>
       <c r="BC24">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BD24">
         <v>0</v>
       </c>
       <c r="BE24">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF24">
         <v>0</v>
@@ -5372,7 +5384,7 @@
         <v>0</v>
       </c>
       <c r="BI24" s="3">
-        <v>46147.53125</v>
+        <v>46147.52083333334</v>
       </c>
     </row>
     <row r="25" spans="1:61">
@@ -5383,16 +5395,16 @@
         <v>76</v>
       </c>
       <c r="C25" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D25" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E25" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F25" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -5419,16 +5431,16 @@
         <v>-1</v>
       </c>
       <c r="O25" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -5461,40 +5473,40 @@
         <v>0</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH25">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI25">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL25">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AM25">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AN25">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AO25">
         <v>0</v>
@@ -5557,7 +5569,7 @@
         <v>0</v>
       </c>
       <c r="BI25" s="3">
-        <v>46147.54166666666</v>
+        <v>46147.53125</v>
       </c>
     </row>
     <row r="26" spans="1:61">
@@ -5568,16 +5580,16 @@
         <v>77</v>
       </c>
       <c r="C26" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F26" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -5604,25 +5616,25 @@
         <v>-1</v>
       </c>
       <c r="O26" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P26">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q26">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R26">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="S26">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="T26">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U26">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="V26">
         <v>0</v>
@@ -5631,10 +5643,10 @@
         <v>0</v>
       </c>
       <c r="X26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y26">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -5646,40 +5658,40 @@
         <v>0</v>
       </c>
       <c r="AC26">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AD26">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AE26">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF26">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG26">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH26">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI26">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AJ26">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK26">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL26">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AM26">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AN26">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AO26">
         <v>0</v>
@@ -5724,13 +5736,13 @@
         <v>0</v>
       </c>
       <c r="BC26">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BD26">
         <v>0</v>
       </c>
       <c r="BE26">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="BF26">
         <v>0</v>
@@ -5742,7 +5754,7 @@
         <v>0</v>
       </c>
       <c r="BI26" s="3">
-        <v>46147.5625</v>
+        <v>46147.54166666666</v>
       </c>
     </row>
     <row r="27" spans="1:61">
@@ -5753,16 +5765,16 @@
         <v>78</v>
       </c>
       <c r="C27" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D27" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E27" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F27" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -5789,25 +5801,25 @@
         <v>-1</v>
       </c>
       <c r="O27" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="V27">
         <v>0</v>
@@ -5816,10 +5828,10 @@
         <v>0</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -5831,40 +5843,40 @@
         <v>0</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH27">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI27">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL27">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AM27">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AN27">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AO27">
         <v>0</v>
@@ -5909,13 +5921,13 @@
         <v>0</v>
       </c>
       <c r="BC27">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BD27">
         <v>0</v>
       </c>
       <c r="BE27">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BF27">
         <v>0</v>
@@ -5927,7 +5939,7 @@
         <v>0</v>
       </c>
       <c r="BI27" s="3">
-        <v>46147.57291666666</v>
+        <v>46147.5625</v>
       </c>
     </row>
     <row r="28" spans="1:61">
@@ -5935,19 +5947,19 @@
         <v>46147</v>
       </c>
       <c r="B28" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C28" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D28" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E28" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F28" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -5974,7 +5986,7 @@
         <v>-1</v>
       </c>
       <c r="O28" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -6120,19 +6132,19 @@
         <v>46147</v>
       </c>
       <c r="B29" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C29" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D29" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E29" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F29" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -6159,7 +6171,7 @@
         <v>-1</v>
       </c>
       <c r="O29" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P29">
         <v>0</v>
@@ -6311,13 +6323,13 @@
         <v>92</v>
       </c>
       <c r="D30" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E30" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F30" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -6344,133 +6356,133 @@
         <v>-1</v>
       </c>
       <c r="O30" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P30">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q30">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R30">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="S30">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="T30">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U30">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="V30">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W30">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X30">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y30">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z30">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA30">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB30">
         <v>0</v>
       </c>
       <c r="AC30">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD30">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE30">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF30">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG30">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AH30">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI30">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AJ30">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK30">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL30">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AM30">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN30">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AO30">
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AQ30">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AR30">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS30">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AT30">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AU30">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV30">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AW30">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AX30">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AY30">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ30">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BA30">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BB30">
         <v>0</v>
       </c>
       <c r="BC30">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD30">
         <v>0</v>
       </c>
       <c r="BE30">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BF30">
         <v>0</v>
@@ -6482,7 +6494,7 @@
         <v>0</v>
       </c>
       <c r="BI30" s="3">
-        <v>46147.58333333334</v>
+        <v>46147.57291666666</v>
       </c>
     </row>
     <row r="31" spans="1:61">
@@ -6490,19 +6502,19 @@
         <v>46147</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C31" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D31" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E31" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F31" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -6529,7 +6541,7 @@
         <v>-1</v>
       </c>
       <c r="O31" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P31">
         <v>4</v>
@@ -6675,19 +6687,19 @@
         <v>46147</v>
       </c>
       <c r="B32" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C32" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D32" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E32" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F32" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -6714,136 +6726,136 @@
         <v>-1</v>
       </c>
       <c r="O32" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P32">
+        <v>1.4</v>
+      </c>
+      <c r="Q32">
+        <v>3.8</v>
+      </c>
+      <c r="R32">
+        <v>6.5</v>
+      </c>
+      <c r="S32">
+        <v>2.01</v>
+      </c>
+      <c r="T32">
+        <v>2.09</v>
+      </c>
+      <c r="U32">
+        <v>7.7</v>
+      </c>
+      <c r="V32">
+        <v>1.44</v>
+      </c>
+      <c r="W32">
         <v>2.5</v>
       </c>
-      <c r="Q32">
-        <v>3.55</v>
-      </c>
-      <c r="R32">
-        <v>2.52</v>
-      </c>
-      <c r="S32">
-        <v>0</v>
-      </c>
-      <c r="T32">
-        <v>0</v>
-      </c>
-      <c r="U32">
-        <v>0</v>
-      </c>
-      <c r="V32">
-        <v>0</v>
-      </c>
-      <c r="W32">
-        <v>0</v>
-      </c>
       <c r="X32">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE32">
-        <v>1.66</v>
+        <v>2.06</v>
       </c>
       <c r="AF32">
-        <v>2.15</v>
+        <v>1.68</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AH32">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI32">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL32">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AM32">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN32">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AO32">
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ32">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR32">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AS32">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT32">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AU32">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AV32">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW32">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AX32">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY32">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ32">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BA32">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="BB32">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC32">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD32">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="BE32">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF32">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG32">
         <v>0</v>
@@ -6860,19 +6872,19 @@
         <v>46147</v>
       </c>
       <c r="B33" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C33" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E33" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F33" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -6899,7 +6911,7 @@
         <v>-1</v>
       </c>
       <c r="O33" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P33">
         <v>5.05</v>
@@ -7045,19 +7057,19 @@
         <v>46147</v>
       </c>
       <c r="B34" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C34" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D34" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E34" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F34" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -7084,136 +7096,136 @@
         <v>-1</v>
       </c>
       <c r="O34" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P34">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="Q34">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="R34">
-        <v>6.5</v>
+        <v>3.79</v>
       </c>
       <c r="S34">
-        <v>2.01</v>
+        <v>2.48</v>
       </c>
       <c r="T34">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="U34">
-        <v>7.7</v>
+        <v>4.1</v>
       </c>
       <c r="V34">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="W34">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="X34">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="Y34">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z34">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="AA34">
         <v>1.03</v>
       </c>
       <c r="AB34">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC34">
         <v>1.32</v>
       </c>
       <c r="AD34">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AE34">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="AF34">
         <v>1.68</v>
       </c>
       <c r="AG34">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AH34">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AI34">
         <v>6.75</v>
       </c>
       <c r="AJ34">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AK34">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AL34">
-        <v>1.54</v>
+        <v>1.84</v>
       </c>
       <c r="AM34">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AN34">
-        <v>2.57</v>
+        <v>1.75</v>
       </c>
       <c r="AO34">
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AQ34">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="AR34">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AS34">
-        <v>2.33</v>
+        <v>2.7</v>
       </c>
       <c r="AT34">
-        <v>3.14</v>
+        <v>3.65</v>
       </c>
       <c r="AU34">
-        <v>3.34</v>
+        <v>2.7</v>
       </c>
       <c r="AV34">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="AW34">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="AX34">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AY34">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AZ34">
-        <v>1.3</v>
+        <v>1.68</v>
       </c>
       <c r="BA34">
-        <v>4.32</v>
+        <v>2.5</v>
       </c>
       <c r="BB34">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC34">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="BD34">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="BE34">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="BF34">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG34">
         <v>0</v>
@@ -7233,16 +7245,16 @@
         <v>80</v>
       </c>
       <c r="C35" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D35" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E35" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F35" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -7269,136 +7281,136 @@
         <v>-1</v>
       </c>
       <c r="O35" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P35">
-        <v>4.65</v>
+        <v>2.5</v>
       </c>
       <c r="Q35">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="R35">
-        <v>1.62</v>
+        <v>2.52</v>
       </c>
       <c r="S35">
-        <v>6.93</v>
+        <v>0</v>
       </c>
       <c r="T35">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="U35">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V35">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W35">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="X35">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y35">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z35">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA35">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB35">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC35">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AD35">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE35">
-        <v>2.65</v>
+        <v>1.66</v>
       </c>
       <c r="AF35">
-        <v>1.45</v>
+        <v>2.15</v>
       </c>
       <c r="AG35">
-        <v>5.18</v>
+        <v>0</v>
       </c>
       <c r="AH35">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI35">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AJ35">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK35">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL35">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM35">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN35">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AO35">
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AQ35">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AR35">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AS35">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AT35">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="AU35">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AV35">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AW35">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AX35">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AY35">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ35">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="BA35">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BB35">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BC35">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="BD35">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="BE35">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="BF35">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG35">
         <v>0</v>
@@ -7407,7 +7419,7 @@
         <v>0</v>
       </c>
       <c r="BI35" s="3">
-        <v>46147.60416666666</v>
+        <v>46147.58333333334</v>
       </c>
     </row>
     <row r="36" spans="1:61">
@@ -7415,19 +7427,19 @@
         <v>46147</v>
       </c>
       <c r="B36" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C36" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D36" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E36" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F36" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -7454,7 +7466,7 @@
         <v>-1</v>
       </c>
       <c r="O36" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P36">
         <v>3.2</v>
@@ -7600,19 +7612,19 @@
         <v>46147</v>
       </c>
       <c r="B37" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C37" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D37" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E37" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F37" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -7639,7 +7651,7 @@
         <v>-1</v>
       </c>
       <c r="O37" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P37">
         <v>2.05</v>
@@ -7785,19 +7797,19 @@
         <v>46147</v>
       </c>
       <c r="B38" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C38" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D38" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E38" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F38" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -7824,136 +7836,136 @@
         <v>-1</v>
       </c>
       <c r="O38" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P38">
-        <v>2.11</v>
+        <v>4.65</v>
       </c>
       <c r="Q38">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="R38">
-        <v>3.45</v>
+        <v>1.62</v>
       </c>
       <c r="S38">
-        <v>3.01</v>
+        <v>6.93</v>
       </c>
       <c r="T38">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="U38">
-        <v>4.53</v>
+        <v>2.3</v>
       </c>
       <c r="V38">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="W38">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="X38">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="Y38">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z38">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA38">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AB38">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AC38">
-        <v>1.66</v>
+        <v>1.49</v>
       </c>
       <c r="AD38">
-        <v>2.09</v>
+        <v>2.35</v>
       </c>
       <c r="AE38">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="AF38">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="AG38">
-        <v>6.35</v>
+        <v>5.18</v>
       </c>
       <c r="AH38">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AI38">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AJ38">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AK38">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AL38">
         <v>1.5</v>
       </c>
       <c r="AM38">
+        <v>1.26</v>
+      </c>
+      <c r="AN38">
+        <v>1.07</v>
+      </c>
+      <c r="AO38">
+        <v>0</v>
+      </c>
+      <c r="AP38">
         <v>1.32</v>
       </c>
-      <c r="AN38">
-        <v>1.55</v>
-      </c>
-      <c r="AO38">
-        <v>0</v>
-      </c>
-      <c r="AP38">
-        <v>1.33</v>
-      </c>
       <c r="AQ38">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AR38">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="AS38">
-        <v>2.68</v>
+        <v>2.61</v>
       </c>
       <c r="AT38">
-        <v>3.75</v>
+        <v>3.63</v>
       </c>
       <c r="AU38">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="AV38">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AW38">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AX38">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AY38">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AZ38">
-        <v>1.98</v>
+        <v>4.42</v>
       </c>
       <c r="BA38">
-        <v>2.31</v>
+        <v>1.37</v>
       </c>
       <c r="BB38">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="BC38">
-        <v>3.12</v>
+        <v>2.66</v>
       </c>
       <c r="BD38">
-        <v>2.53</v>
+        <v>2.82</v>
       </c>
       <c r="BE38">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="BF38">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="BG38">
         <v>0</v>
@@ -7973,16 +7985,16 @@
         <v>81</v>
       </c>
       <c r="C39" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D39" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E39" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F39" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -8009,136 +8021,136 @@
         <v>-1</v>
       </c>
       <c r="O39" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AH39">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI39">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL39">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM39">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN39">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AO39">
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AQ39">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR39">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AS39">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AT39">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AU39">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AV39">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AW39">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX39">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY39">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AZ39">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BA39">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="BB39">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BC39">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="BD39">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="BE39">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BF39">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="BG39">
         <v>0</v>
@@ -8147,7 +8159,7 @@
         <v>0</v>
       </c>
       <c r="BI39" s="3">
-        <v>46147.625</v>
+        <v>46147.60416666666</v>
       </c>
     </row>
     <row r="40" spans="1:61">
@@ -8158,16 +8170,16 @@
         <v>82</v>
       </c>
       <c r="C40" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D40" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E40" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F40" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -8194,136 +8206,136 @@
         <v>-1</v>
       </c>
       <c r="O40" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P40">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q40">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R40">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="S40">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="T40">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="U40">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="V40">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W40">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="X40">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y40">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z40">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA40">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB40">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC40">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AD40">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE40">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF40">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG40">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AH40">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI40">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="AJ40">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK40">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AL40">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM40">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN40">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO40">
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ40">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR40">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AS40">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AT40">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU40">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AV40">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AW40">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX40">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AY40">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AZ40">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BA40">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BB40">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC40">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD40">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="BE40">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF40">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG40">
         <v>0</v>
@@ -8332,7 +8344,7 @@
         <v>0</v>
       </c>
       <c r="BI40" s="3">
-        <v>46147.66666666666</v>
+        <v>46147.625</v>
       </c>
     </row>
     <row r="41" spans="1:61">
@@ -8343,16 +8355,16 @@
         <v>83</v>
       </c>
       <c r="C41" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D41" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E41" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F41" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -8379,136 +8391,136 @@
         <v>-1</v>
       </c>
       <c r="O41" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AH41">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI41">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL41">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM41">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN41">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO41">
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ41">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR41">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS41">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AT41">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU41">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AV41">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW41">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX41">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AY41">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AZ41">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BA41">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BB41">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC41">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD41">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="BE41">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF41">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG41">
         <v>0</v>
@@ -8517,6 +8529,191 @@
         <v>0</v>
       </c>
       <c r="BI41" s="3">
+        <v>46147.66666666666</v>
+      </c>
+    </row>
+    <row r="42" spans="1:61">
+      <c r="A42" s="2">
+        <v>46147</v>
+      </c>
+      <c r="B42" t="s">
+        <v>84</v>
+      </c>
+      <c r="C42" t="s">
+        <v>103</v>
+      </c>
+      <c r="D42" t="s">
+        <v>104</v>
+      </c>
+      <c r="E42" t="s">
+        <v>147</v>
+      </c>
+      <c r="F42" t="s">
+        <v>187</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>-1</v>
+      </c>
+      <c r="N42">
+        <v>-1</v>
+      </c>
+      <c r="O42" t="s">
+        <v>188</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>0</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="T42">
+        <v>0</v>
+      </c>
+      <c r="U42">
+        <v>0</v>
+      </c>
+      <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="W42">
+        <v>0</v>
+      </c>
+      <c r="X42">
+        <v>0</v>
+      </c>
+      <c r="Y42">
+        <v>0</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+      <c r="AA42">
+        <v>0</v>
+      </c>
+      <c r="AB42">
+        <v>0</v>
+      </c>
+      <c r="AC42">
+        <v>0</v>
+      </c>
+      <c r="AD42">
+        <v>0</v>
+      </c>
+      <c r="AE42">
+        <v>0</v>
+      </c>
+      <c r="AF42">
+        <v>0</v>
+      </c>
+      <c r="AG42">
+        <v>0</v>
+      </c>
+      <c r="AH42">
+        <v>0</v>
+      </c>
+      <c r="AI42">
+        <v>0</v>
+      </c>
+      <c r="AJ42">
+        <v>0</v>
+      </c>
+      <c r="AK42">
+        <v>0</v>
+      </c>
+      <c r="AL42">
+        <v>0</v>
+      </c>
+      <c r="AM42">
+        <v>0</v>
+      </c>
+      <c r="AN42">
+        <v>0</v>
+      </c>
+      <c r="AO42">
+        <v>0</v>
+      </c>
+      <c r="AP42">
+        <v>0</v>
+      </c>
+      <c r="AQ42">
+        <v>0</v>
+      </c>
+      <c r="AR42">
+        <v>0</v>
+      </c>
+      <c r="AS42">
+        <v>0</v>
+      </c>
+      <c r="AT42">
+        <v>0</v>
+      </c>
+      <c r="AU42">
+        <v>0</v>
+      </c>
+      <c r="AV42">
+        <v>0</v>
+      </c>
+      <c r="AW42">
+        <v>0</v>
+      </c>
+      <c r="AX42">
+        <v>0</v>
+      </c>
+      <c r="AY42">
+        <v>0</v>
+      </c>
+      <c r="AZ42">
+        <v>0</v>
+      </c>
+      <c r="BA42">
+        <v>0</v>
+      </c>
+      <c r="BB42">
+        <v>0</v>
+      </c>
+      <c r="BC42">
+        <v>0</v>
+      </c>
+      <c r="BD42">
+        <v>0</v>
+      </c>
+      <c r="BE42">
+        <v>0</v>
+      </c>
+      <c r="BF42">
+        <v>0</v>
+      </c>
+      <c r="BG42">
+        <v>0</v>
+      </c>
+      <c r="BH42">
+        <v>0</v>
+      </c>
+      <c r="BI42" s="3">
         <v>46147.83333333334</v>
       </c>
     </row>

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -337,21 +337,21 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Bucheon 1995</t>
+  </si>
+  <si>
     <t>Jeonbuk Motors</t>
   </si>
   <si>
-    <t>Bucheon 1995</t>
+    <t>Gangwon</t>
+  </si>
+  <si>
+    <t>Sangju Sangmu</t>
   </si>
   <si>
     <t>Daejeon Citizen</t>
   </si>
   <si>
-    <t>Gangwon</t>
-  </si>
-  <si>
-    <t>Sangju Sangmu</t>
-  </si>
-  <si>
     <t>Madura United</t>
   </si>
   <si>
@@ -373,18 +373,18 @@
     <t>Shandong Luneng</t>
   </si>
   <si>
+    <t>Dire Dawa Kenema</t>
+  </si>
+  <si>
+    <t>Borneo</t>
+  </si>
+  <si>
     <t>Chongqing Tongliang Long</t>
   </si>
   <si>
     <t>Karvan FK</t>
   </si>
   <si>
-    <t>Dire Dawa Kenema</t>
-  </si>
-  <si>
-    <t>Borneo</t>
-  </si>
-  <si>
     <t>Mekelle Kenema</t>
   </si>
   <si>
@@ -415,42 +415,42 @@
     <t>Maccabi Tel Aviv</t>
   </si>
   <si>
+    <t>Bani Yas</t>
+  </si>
+  <si>
     <t>Dibba Al Fujairah</t>
   </si>
   <si>
     <t>Al Ittihad Kalba</t>
   </si>
   <si>
-    <t>Bani Yas</t>
-  </si>
-  <si>
     <t>Ceramica Cleopatra</t>
   </si>
   <si>
+    <t>Falkenberg</t>
+  </si>
+  <si>
+    <t>Smouha SC</t>
+  </si>
+  <si>
     <t>Al Ahly</t>
   </si>
   <si>
-    <t>Smouha SC</t>
-  </si>
-  <si>
     <t>Lokomotiv Sofia 1929</t>
   </si>
   <si>
-    <t>Falkenberg</t>
-  </si>
-  <si>
     <t>Chippa United</t>
   </si>
   <si>
+    <t>Siwelele</t>
+  </si>
+  <si>
+    <t>Stellenbosch</t>
+  </si>
+  <si>
     <t>Magesi</t>
   </si>
   <si>
-    <t>Stellenbosch</t>
-  </si>
-  <si>
-    <t>Siwelele</t>
-  </si>
-  <si>
     <t>Al Khaleej</t>
   </si>
   <si>
@@ -460,21 +460,21 @@
     <t>New York City II</t>
   </si>
   <si>
+    <t>Jeju United</t>
+  </si>
+  <si>
     <t>Gwangju</t>
   </si>
   <si>
-    <t>Jeju United</t>
+    <t>Pohang Steelers</t>
+  </si>
+  <si>
+    <t>Ulsan</t>
   </si>
   <si>
     <t>Incheon United</t>
   </si>
   <si>
-    <t>Pohang Steelers</t>
-  </si>
-  <si>
-    <t>Ulsan</t>
-  </si>
-  <si>
     <t>Bali United</t>
   </si>
   <si>
@@ -496,18 +496,18 @@
     <t>Shanghai Shenhua</t>
   </si>
   <si>
+    <t>Ethiopia Bunna</t>
+  </si>
+  <si>
+    <t>Persita</t>
+  </si>
+  <si>
     <t>Henan Jianye</t>
   </si>
   <si>
     <t>Neftçi</t>
   </si>
   <si>
-    <t>Ethiopia Bunna</t>
-  </si>
-  <si>
-    <t>Persita</t>
-  </si>
-  <si>
     <t>Arba Minch Kenema</t>
   </si>
   <si>
@@ -538,37 +538,37 @@
     <t>Hapoel Petah Tikva</t>
   </si>
   <si>
+    <t>Al Dhafra</t>
+  </si>
+  <si>
     <t>Al Bataeh</t>
   </si>
   <si>
-    <t>Al Dhafra</t>
-  </si>
-  <si>
     <t>Pyramids FC</t>
   </si>
   <si>
+    <t>Norrköping</t>
+  </si>
+  <si>
+    <t>Zamalek</t>
+  </si>
+  <si>
     <t>ENPPI</t>
   </si>
   <si>
-    <t>Zamalek</t>
-  </si>
-  <si>
     <t>Botev Vratsa</t>
   </si>
   <si>
-    <t>Norrköping</t>
-  </si>
-  <si>
     <t>Sekhukhune United</t>
   </si>
   <si>
+    <t>Durban City</t>
+  </si>
+  <si>
+    <t>Orlando Pirates</t>
+  </si>
+  <si>
     <t>Orbit College</t>
-  </si>
-  <si>
-    <t>Orlando Pirates</t>
-  </si>
-  <si>
-    <t>Durban City</t>
   </si>
   <si>
     <t>Al Hilal</t>
@@ -1179,13 +1179,13 @@
         <v>188</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -1364,13 +1364,13 @@
         <v>188</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -1549,13 +1549,13 @@
         <v>188</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -1743,124 +1743,124 @@
         <v>0</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AO5">
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AU5">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AV5">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AW5">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX5">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY5">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ5">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BA5">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="BB5">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC5">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD5">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="BE5">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BF5">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG5">
         <v>0</v>
@@ -1919,133 +1919,133 @@
         <v>188</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="S6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X6">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y6">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z6">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA6">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC6">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD6">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE6">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH6">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ6">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK6">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL6">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM6">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN6">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AO6">
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ6">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR6">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AS6">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT6">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AU6">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AV6">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AW6">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AX6">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY6">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ6">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="BA6">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="BB6">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC6">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BD6">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BE6">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BF6">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG6">
         <v>0</v>
@@ -2146,7 +2146,7 @@
         <v>1.19</v>
       </c>
       <c r="AD7">
-        <v>3.78</v>
+        <v>4.1</v>
       </c>
       <c r="AE7">
         <v>1.69</v>
@@ -2164,7 +2164,7 @@
         <v>4.65</v>
       </c>
       <c r="AJ7">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AK7">
         <v>1.62</v>
@@ -2185,13 +2185,13 @@
         <v>1.14</v>
       </c>
       <c r="AQ7">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AR7">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AS7">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="AT7">
         <v>2.55</v>
@@ -2200,10 +2200,10 @@
         <v>4.23</v>
       </c>
       <c r="AV7">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="AW7">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AX7">
         <v>1.73</v>
@@ -2215,7 +2215,7 @@
         <v>2.07</v>
       </c>
       <c r="BA7">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="BB7">
         <v>1.16</v>
@@ -2289,13 +2289,13 @@
         <v>188</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -2668,25 +2668,25 @@
         <v>0</v>
       </c>
       <c r="S10">
-        <v>2.51</v>
+        <v>2.61</v>
       </c>
       <c r="T10">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="U10">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="V10">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W10">
         <v>2.69</v>
       </c>
       <c r="X10">
-        <v>2.77</v>
+        <v>2.94</v>
       </c>
       <c r="Y10">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Z10">
         <v>6.55</v>
@@ -2698,16 +2698,16 @@
         <v>1.02</v>
       </c>
       <c r="AC10">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AD10">
-        <v>3.14</v>
+        <v>3.39</v>
       </c>
       <c r="AE10">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AF10">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG10">
         <v>3.14</v>
@@ -2716,10 +2716,10 @@
         <v>1.27</v>
       </c>
       <c r="AI10">
-        <v>6.45</v>
+        <v>5.95</v>
       </c>
       <c r="AJ10">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AK10">
         <v>1.78</v>
@@ -2728,10 +2728,10 @@
         <v>1.93</v>
       </c>
       <c r="AM10">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AN10">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AO10">
         <v>0</v>
@@ -2740,7 +2740,7 @@
         <v>1.24</v>
       </c>
       <c r="AQ10">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AR10">
         <v>2.1</v>
@@ -2755,7 +2755,7 @@
         <v>3.32</v>
       </c>
       <c r="AV10">
-        <v>2.37</v>
+        <v>2.49</v>
       </c>
       <c r="AW10">
         <v>1.85</v>
@@ -2770,7 +2770,7 @@
         <v>1.53</v>
       </c>
       <c r="BA10">
-        <v>3.34</v>
+        <v>2.78</v>
       </c>
       <c r="BB10">
         <v>1.22</v>
@@ -3038,25 +3038,25 @@
         <v>0</v>
       </c>
       <c r="S12">
-        <v>5.65</v>
+        <v>6.02</v>
       </c>
       <c r="T12">
-        <v>2.29</v>
+        <v>2.43</v>
       </c>
       <c r="U12">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="V12">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W12">
-        <v>3.05</v>
+        <v>3.22</v>
       </c>
       <c r="X12">
-        <v>2.56</v>
+        <v>2.67</v>
       </c>
       <c r="Y12">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="Z12">
         <v>6</v>
@@ -3068,19 +3068,19 @@
         <v>1.03</v>
       </c>
       <c r="AC12">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AD12">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="AE12">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AF12">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AG12">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AH12">
         <v>1.33</v>
@@ -3095,7 +3095,7 @@
         <v>1.84</v>
       </c>
       <c r="AL12">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AM12">
         <v>1.22</v>
@@ -3146,13 +3146,13 @@
         <v>1.18</v>
       </c>
       <c r="BC12">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="BD12">
         <v>4.05</v>
       </c>
       <c r="BE12">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="BF12">
         <v>1.17</v>
@@ -3223,10 +3223,10 @@
         <v>2.45</v>
       </c>
       <c r="S13">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="T13">
-        <v>2.27</v>
+        <v>2.59</v>
       </c>
       <c r="U13">
         <v>3.02</v>
@@ -3238,10 +3238,10 @@
         <v>3.6</v>
       </c>
       <c r="X13">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="Y13">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Z13">
         <v>4.45</v>
@@ -3253,10 +3253,10 @@
         <v>1.02</v>
       </c>
       <c r="AC13">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AD13">
-        <v>5.65</v>
+        <v>5.82</v>
       </c>
       <c r="AE13">
         <v>1.39</v>
@@ -3274,13 +3274,13 @@
         <v>3.28</v>
       </c>
       <c r="AJ13">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK13">
         <v>1.36</v>
       </c>
       <c r="AL13">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="AM13">
         <v>1.28</v>
@@ -3295,49 +3295,49 @@
         <v>1.12</v>
       </c>
       <c r="AQ13">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AR13">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AS13">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AT13">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="AU13">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AV13">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AW13">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
       <c r="AX13">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AY13">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AZ13">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="BA13">
-        <v>2.88</v>
+        <v>2.21</v>
       </c>
       <c r="BB13">
         <v>1.08</v>
       </c>
       <c r="BC13">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="BD13">
         <v>5.7</v>
       </c>
       <c r="BE13">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="BF13">
         <v>1.33</v>
@@ -3360,10 +3360,10 @@
         <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E14" t="s">
         <v>119</v>
@@ -3408,70 +3408,70 @@
         <v>0</v>
       </c>
       <c r="S14">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD14">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AH14">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI14">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AJ14">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK14">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AL14">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AM14">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN14">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AO14">
         <v>0</v>
@@ -3513,19 +3513,19 @@
         <v>0</v>
       </c>
       <c r="BB14">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC14">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="BD14">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="BE14">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF14">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG14">
         <v>0</v>
@@ -3545,7 +3545,7 @@
         <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D15" t="s">
         <v>105</v>
@@ -3584,133 +3584,133 @@
         <v>188</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI15">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AM15">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN15">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AO15">
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AU15">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AV15">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AW15">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AX15">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY15">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AZ15">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BA15">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="BB15">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC15">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BD15">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="BE15">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BF15">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG15">
         <v>0</v>
@@ -3730,10 +3730,10 @@
         <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E16" t="s">
         <v>121</v>
@@ -3778,70 +3778,70 @@
         <v>0</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL16">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AM16">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO16">
         <v>0</v>
@@ -3883,19 +3883,19 @@
         <v>0</v>
       </c>
       <c r="BB16">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC16">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BD16">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="BE16">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF16">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG16">
         <v>0</v>
@@ -3915,7 +3915,7 @@
         <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D17" t="s">
         <v>105</v>
@@ -3954,133 +3954,133 @@
         <v>188</v>
       </c>
       <c r="P17">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R17">
-        <v>4.87</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>5.61</v>
+        <v>0</v>
       </c>
       <c r="V17">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W17">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X17">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y17">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z17">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA17">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC17">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD17">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AE17">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AG17">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AH17">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AI17">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AJ17">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK17">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM17">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AN17">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AO17">
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ17">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AR17">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AS17">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AT17">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AU17">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AV17">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="AW17">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AX17">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AY17">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AZ17">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="BA17">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="BB17">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC17">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BD17">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="BE17">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BF17">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG17">
         <v>0</v>
@@ -4694,13 +4694,13 @@
         <v>188</v>
       </c>
       <c r="P21">
-        <v>2.11</v>
+        <v>1.99</v>
       </c>
       <c r="Q21">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="R21">
-        <v>3.49</v>
+        <v>3.96</v>
       </c>
       <c r="S21">
         <v>2.7</v>
@@ -6144,7 +6144,7 @@
         <v>134</v>
       </c>
       <c r="F29" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -6329,7 +6329,7 @@
         <v>135</v>
       </c>
       <c r="F30" t="s">
-        <v>175</v>
+        <v>145</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -6690,10 +6690,10 @@
         <v>80</v>
       </c>
       <c r="C32" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E32" t="s">
         <v>137</v>
@@ -6729,133 +6729,133 @@
         <v>188</v>
       </c>
       <c r="P32">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q32">
-        <v>3.8</v>
+        <v>3.54</v>
       </c>
       <c r="R32">
-        <v>6.5</v>
+        <v>2.52</v>
       </c>
       <c r="S32">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="T32">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U32">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="V32">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W32">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X32">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="Y32">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z32">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA32">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB32">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC32">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD32">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AE32">
-        <v>2.06</v>
+        <v>1.66</v>
       </c>
       <c r="AF32">
-        <v>1.68</v>
+        <v>2.15</v>
       </c>
       <c r="AG32">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AH32">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI32">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AJ32">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK32">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL32">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AM32">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN32">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AO32">
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ32">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR32">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AS32">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AT32">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AU32">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AV32">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AW32">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AX32">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AY32">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ32">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BA32">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="BB32">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC32">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BD32">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="BE32">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF32">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG32">
         <v>0</v>
@@ -7060,7 +7060,7 @@
         <v>80</v>
       </c>
       <c r="C34" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D34" t="s">
         <v>105</v>
@@ -7099,133 +7099,133 @@
         <v>188</v>
       </c>
       <c r="P34">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="Q34">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="R34">
-        <v>3.79</v>
+        <v>6.5</v>
       </c>
       <c r="S34">
-        <v>2.48</v>
+        <v>2.01</v>
       </c>
       <c r="T34">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="U34">
-        <v>4.1</v>
+        <v>7.7</v>
       </c>
       <c r="V34">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="W34">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="X34">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="Y34">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z34">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="AA34">
         <v>1.03</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC34">
         <v>1.32</v>
       </c>
       <c r="AD34">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AE34">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="AF34">
         <v>1.68</v>
       </c>
       <c r="AG34">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AH34">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AI34">
         <v>6.75</v>
       </c>
       <c r="AJ34">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AK34">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AL34">
-        <v>1.84</v>
+        <v>1.54</v>
       </c>
       <c r="AM34">
+        <v>1.17</v>
+      </c>
+      <c r="AN34">
+        <v>2.57</v>
+      </c>
+      <c r="AO34">
+        <v>0</v>
+      </c>
+      <c r="AP34">
+        <v>1.24</v>
+      </c>
+      <c r="AQ34">
+        <v>1.46</v>
+      </c>
+      <c r="AR34">
+        <v>2.13</v>
+      </c>
+      <c r="AS34">
+        <v>2.33</v>
+      </c>
+      <c r="AT34">
+        <v>3.14</v>
+      </c>
+      <c r="AU34">
+        <v>3.34</v>
+      </c>
+      <c r="AV34">
+        <v>2.38</v>
+      </c>
+      <c r="AW34">
+        <v>1.83</v>
+      </c>
+      <c r="AX34">
+        <v>1.48</v>
+      </c>
+      <c r="AY34">
         <v>1.27</v>
       </c>
-      <c r="AN34">
-        <v>1.75</v>
-      </c>
-      <c r="AO34">
-        <v>0</v>
-      </c>
-      <c r="AP34">
-        <v>1.4</v>
-      </c>
-      <c r="AQ34">
-        <v>1.67</v>
-      </c>
-      <c r="AR34">
-        <v>2.1</v>
-      </c>
-      <c r="AS34">
-        <v>2.7</v>
-      </c>
-      <c r="AT34">
-        <v>3.65</v>
-      </c>
-      <c r="AU34">
-        <v>2.7</v>
-      </c>
-      <c r="AV34">
-        <v>2.04</v>
-      </c>
-      <c r="AW34">
-        <v>1.64</v>
-      </c>
-      <c r="AX34">
-        <v>1.38</v>
-      </c>
-      <c r="AY34">
-        <v>1.23</v>
-      </c>
       <c r="AZ34">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="BA34">
-        <v>2.5</v>
+        <v>4.32</v>
       </c>
       <c r="BB34">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC34">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="BD34">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="BE34">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="BF34">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG34">
         <v>0</v>
@@ -7245,10 +7245,10 @@
         <v>80</v>
       </c>
       <c r="C35" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D35" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E35" t="s">
         <v>140</v>
@@ -7284,130 +7284,130 @@
         <v>188</v>
       </c>
       <c r="P35">
+        <v>1.95</v>
+      </c>
+      <c r="Q35">
+        <v>3.25</v>
+      </c>
+      <c r="R35">
+        <v>3.79</v>
+      </c>
+      <c r="S35">
+        <v>2.48</v>
+      </c>
+      <c r="T35">
+        <v>2.1</v>
+      </c>
+      <c r="U35">
+        <v>4.1</v>
+      </c>
+      <c r="V35">
+        <v>1.37</v>
+      </c>
+      <c r="W35">
+        <v>2.7</v>
+      </c>
+      <c r="X35">
+        <v>2.88</v>
+      </c>
+      <c r="Y35">
+        <v>1.33</v>
+      </c>
+      <c r="Z35">
+        <v>7</v>
+      </c>
+      <c r="AA35">
+        <v>1.03</v>
+      </c>
+      <c r="AB35">
+        <v>0</v>
+      </c>
+      <c r="AC35">
+        <v>1.32</v>
+      </c>
+      <c r="AD35">
+        <v>3</v>
+      </c>
+      <c r="AE35">
+        <v>2.02</v>
+      </c>
+      <c r="AF35">
+        <v>1.68</v>
+      </c>
+      <c r="AG35">
+        <v>3.6</v>
+      </c>
+      <c r="AH35">
+        <v>1.24</v>
+      </c>
+      <c r="AI35">
+        <v>6.75</v>
+      </c>
+      <c r="AJ35">
+        <v>1.07</v>
+      </c>
+      <c r="AK35">
+        <v>1.8</v>
+      </c>
+      <c r="AL35">
+        <v>1.84</v>
+      </c>
+      <c r="AM35">
+        <v>1.27</v>
+      </c>
+      <c r="AN35">
+        <v>1.75</v>
+      </c>
+      <c r="AO35">
+        <v>0</v>
+      </c>
+      <c r="AP35">
+        <v>1.4</v>
+      </c>
+      <c r="AQ35">
+        <v>1.67</v>
+      </c>
+      <c r="AR35">
+        <v>2.1</v>
+      </c>
+      <c r="AS35">
+        <v>2.7</v>
+      </c>
+      <c r="AT35">
+        <v>3.65</v>
+      </c>
+      <c r="AU35">
+        <v>2.7</v>
+      </c>
+      <c r="AV35">
+        <v>2.04</v>
+      </c>
+      <c r="AW35">
+        <v>1.64</v>
+      </c>
+      <c r="AX35">
+        <v>1.38</v>
+      </c>
+      <c r="AY35">
+        <v>1.23</v>
+      </c>
+      <c r="AZ35">
+        <v>1.68</v>
+      </c>
+      <c r="BA35">
         <v>2.5</v>
       </c>
-      <c r="Q35">
-        <v>3.55</v>
-      </c>
-      <c r="R35">
-        <v>2.52</v>
-      </c>
-      <c r="S35">
-        <v>0</v>
-      </c>
-      <c r="T35">
-        <v>0</v>
-      </c>
-      <c r="U35">
-        <v>0</v>
-      </c>
-      <c r="V35">
-        <v>0</v>
-      </c>
-      <c r="W35">
-        <v>0</v>
-      </c>
-      <c r="X35">
-        <v>0</v>
-      </c>
-      <c r="Y35">
-        <v>0</v>
-      </c>
-      <c r="Z35">
-        <v>0</v>
-      </c>
-      <c r="AA35">
-        <v>0</v>
-      </c>
-      <c r="AB35">
-        <v>0</v>
-      </c>
-      <c r="AC35">
-        <v>0</v>
-      </c>
-      <c r="AD35">
-        <v>0</v>
-      </c>
-      <c r="AE35">
-        <v>1.66</v>
-      </c>
-      <c r="AF35">
-        <v>2.15</v>
-      </c>
-      <c r="AG35">
-        <v>0</v>
-      </c>
-      <c r="AH35">
-        <v>0</v>
-      </c>
-      <c r="AI35">
-        <v>0</v>
-      </c>
-      <c r="AJ35">
-        <v>0</v>
-      </c>
-      <c r="AK35">
-        <v>0</v>
-      </c>
-      <c r="AL35">
-        <v>0</v>
-      </c>
-      <c r="AM35">
-        <v>0</v>
-      </c>
-      <c r="AN35">
-        <v>0</v>
-      </c>
-      <c r="AO35">
-        <v>0</v>
-      </c>
-      <c r="AP35">
-        <v>0</v>
-      </c>
-      <c r="AQ35">
-        <v>0</v>
-      </c>
-      <c r="AR35">
-        <v>0</v>
-      </c>
-      <c r="AS35">
-        <v>0</v>
-      </c>
-      <c r="AT35">
-        <v>0</v>
-      </c>
-      <c r="AU35">
-        <v>0</v>
-      </c>
-      <c r="AV35">
-        <v>0</v>
-      </c>
-      <c r="AW35">
-        <v>0</v>
-      </c>
-      <c r="AX35">
-        <v>0</v>
-      </c>
-      <c r="AY35">
-        <v>0</v>
-      </c>
-      <c r="AZ35">
-        <v>0</v>
-      </c>
-      <c r="BA35">
-        <v>0</v>
-      </c>
       <c r="BB35">
         <v>0</v>
       </c>
       <c r="BC35">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD35">
         <v>0</v>
       </c>
       <c r="BE35">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF35">
         <v>0</v>
@@ -7654,79 +7654,79 @@
         <v>188</v>
       </c>
       <c r="P37">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="Q37">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="R37">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="S37">
-        <v>2.88</v>
+        <v>3.01</v>
       </c>
       <c r="T37">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="U37">
-        <v>5.37</v>
+        <v>4.53</v>
       </c>
       <c r="V37">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="W37">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="X37">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="Y37">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z37">
-        <v>8.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA37">
         <v>1.02</v>
       </c>
       <c r="AB37">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AC37">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AD37">
-        <v>2.23</v>
+        <v>2.09</v>
       </c>
       <c r="AE37">
-        <v>2.74</v>
+        <v>2.85</v>
       </c>
       <c r="AF37">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AG37">
-        <v>4.8</v>
+        <v>6.35</v>
       </c>
       <c r="AH37">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AI37">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AJ37">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK37">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AL37">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AM37">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AN37">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AO37">
         <v>0</v>
@@ -7735,52 +7735,52 @@
         <v>1.33</v>
       </c>
       <c r="AQ37">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AR37">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AS37">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="AT37">
-        <v>3.71</v>
+        <v>3.75</v>
       </c>
       <c r="AU37">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="AV37">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="AW37">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AX37">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AY37">
         <v>1.19</v>
       </c>
       <c r="AZ37">
-        <v>1.53</v>
+        <v>1.98</v>
       </c>
       <c r="BA37">
-        <v>3.44</v>
+        <v>2.31</v>
       </c>
       <c r="BB37">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="BC37">
-        <v>2.9</v>
+        <v>3.12</v>
       </c>
       <c r="BD37">
-        <v>2.66</v>
+        <v>2.53</v>
       </c>
       <c r="BE37">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="BF37">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BG37">
         <v>0</v>
@@ -8024,79 +8024,79 @@
         <v>188</v>
       </c>
       <c r="P39">
+        <v>2.05</v>
+      </c>
+      <c r="Q39">
+        <v>2.87</v>
+      </c>
+      <c r="R39">
+        <v>3.7</v>
+      </c>
+      <c r="S39">
+        <v>2.88</v>
+      </c>
+      <c r="T39">
+        <v>1.75</v>
+      </c>
+      <c r="U39">
+        <v>5.37</v>
+      </c>
+      <c r="V39">
+        <v>1.64</v>
+      </c>
+      <c r="W39">
         <v>2.11</v>
       </c>
-      <c r="Q39">
-        <v>2.8</v>
-      </c>
-      <c r="R39">
-        <v>3.45</v>
-      </c>
-      <c r="S39">
-        <v>3.01</v>
-      </c>
-      <c r="T39">
-        <v>1.81</v>
-      </c>
-      <c r="U39">
-        <v>4.53</v>
-      </c>
-      <c r="V39">
-        <v>1.61</v>
-      </c>
-      <c r="W39">
-        <v>2.17</v>
-      </c>
       <c r="X39">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="Y39">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z39">
-        <v>9.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA39">
         <v>1.02</v>
       </c>
       <c r="AB39">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AC39">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AD39">
-        <v>2.09</v>
+        <v>2.23</v>
       </c>
       <c r="AE39">
-        <v>2.85</v>
+        <v>2.74</v>
       </c>
       <c r="AF39">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AG39">
-        <v>6.35</v>
+        <v>4.8</v>
       </c>
       <c r="AH39">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AI39">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AJ39">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK39">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AL39">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AM39">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AN39">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="AO39">
         <v>0</v>
@@ -8105,52 +8105,52 @@
         <v>1.33</v>
       </c>
       <c r="AQ39">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AR39">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AS39">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="AT39">
-        <v>3.75</v>
+        <v>3.71</v>
       </c>
       <c r="AU39">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="AV39">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AW39">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AX39">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AY39">
         <v>1.19</v>
       </c>
       <c r="AZ39">
-        <v>1.98</v>
+        <v>1.53</v>
       </c>
       <c r="BA39">
-        <v>2.31</v>
+        <v>3.44</v>
       </c>
       <c r="BB39">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="BC39">
-        <v>3.12</v>
+        <v>2.9</v>
       </c>
       <c r="BD39">
-        <v>2.53</v>
+        <v>2.66</v>
       </c>
       <c r="BE39">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BF39">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="BG39">
         <v>0</v>

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -310,12 +310,12 @@
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
     <t>Egypt Egyptian Premier League</t>
   </si>
   <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
     <t>South Africa Premier Soccer League</t>
   </si>
   <si>
@@ -367,24 +367,24 @@
     <t>Tanjong Pagar</t>
   </si>
   <si>
+    <t>Shandong Luneng</t>
+  </si>
+  <si>
     <t>Shenyang Urban</t>
   </si>
   <si>
-    <t>Shandong Luneng</t>
-  </si>
-  <si>
     <t>Dire Dawa Kenema</t>
   </si>
   <si>
+    <t>Chongqing Tongliang Long</t>
+  </si>
+  <si>
+    <t>Karvan FK</t>
+  </si>
+  <si>
     <t>Borneo</t>
   </si>
   <si>
-    <t>Chongqing Tongliang Long</t>
-  </si>
-  <si>
-    <t>Karvan FK</t>
-  </si>
-  <si>
     <t>Mekelle Kenema</t>
   </si>
   <si>
@@ -418,39 +418,39 @@
     <t>Bani Yas</t>
   </si>
   <si>
+    <t>Al Ittihad Kalba</t>
+  </si>
+  <si>
     <t>Dibba Al Fujairah</t>
   </si>
   <si>
-    <t>Al Ittihad Kalba</t>
+    <t>Falkenberg</t>
+  </si>
+  <si>
+    <t>Lokomotiv Sofia 1929</t>
   </si>
   <si>
     <t>Ceramica Cleopatra</t>
   </si>
   <si>
-    <t>Falkenberg</t>
-  </si>
-  <si>
     <t>Smouha SC</t>
   </si>
   <si>
     <t>Al Ahly</t>
   </si>
   <si>
-    <t>Lokomotiv Sofia 1929</t>
-  </si>
-  <si>
     <t>Chippa United</t>
   </si>
   <si>
+    <t>Magesi</t>
+  </si>
+  <si>
+    <t>Stellenbosch</t>
+  </si>
+  <si>
     <t>Siwelele</t>
   </si>
   <si>
-    <t>Stellenbosch</t>
-  </si>
-  <si>
-    <t>Magesi</t>
-  </si>
-  <si>
     <t>Al Khaleej</t>
   </si>
   <si>
@@ -490,24 +490,24 @@
     <t>Hougang United</t>
   </si>
   <si>
+    <t>Shanghai Shenhua</t>
+  </si>
+  <si>
     <t>Chengdu Better City FC</t>
   </si>
   <si>
-    <t>Shanghai Shenhua</t>
-  </si>
-  <si>
     <t>Ethiopia Bunna</t>
   </si>
   <si>
+    <t>Henan Jianye</t>
+  </si>
+  <si>
+    <t>Neftçi</t>
+  </si>
+  <si>
     <t>Persita</t>
   </si>
   <si>
-    <t>Henan Jianye</t>
-  </si>
-  <si>
-    <t>Neftçi</t>
-  </si>
-  <si>
     <t>Arba Minch Kenema</t>
   </si>
   <si>
@@ -544,31 +544,31 @@
     <t>Al Bataeh</t>
   </si>
   <si>
+    <t>Norrköping</t>
+  </si>
+  <si>
+    <t>Botev Vratsa</t>
+  </si>
+  <si>
     <t>Pyramids FC</t>
   </si>
   <si>
-    <t>Norrköping</t>
-  </si>
-  <si>
     <t>Zamalek</t>
   </si>
   <si>
     <t>ENPPI</t>
   </si>
   <si>
-    <t>Botev Vratsa</t>
-  </si>
-  <si>
     <t>Sekhukhune United</t>
   </si>
   <si>
+    <t>Orbit College</t>
+  </si>
+  <si>
+    <t>Orlando Pirates</t>
+  </si>
+  <si>
     <t>Durban City</t>
-  </si>
-  <si>
-    <t>Orlando Pirates</t>
-  </si>
-  <si>
-    <t>Orbit College</t>
   </si>
   <si>
     <t>Al Hilal</t>
@@ -2113,13 +2113,13 @@
         <v>0</v>
       </c>
       <c r="S7">
-        <v>3.49</v>
+        <v>3.38</v>
       </c>
       <c r="T7">
-        <v>2.08</v>
+        <v>2.33</v>
       </c>
       <c r="U7">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="V7">
         <v>1.33</v>
@@ -2131,7 +2131,7 @@
         <v>2.55</v>
       </c>
       <c r="Y7">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="Z7">
         <v>5.65</v>
@@ -2143,10 +2143,10 @@
         <v>1</v>
       </c>
       <c r="AC7">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AD7">
-        <v>4.1</v>
+        <v>4.11</v>
       </c>
       <c r="AE7">
         <v>1.69</v>
@@ -2167,16 +2167,16 @@
         <v>1.16</v>
       </c>
       <c r="AK7">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AL7">
         <v>2.24</v>
       </c>
       <c r="AM7">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AN7">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AO7">
         <v>0</v>
@@ -2206,7 +2206,7 @@
         <v>2.13</v>
       </c>
       <c r="AX7">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AY7">
         <v>1.43</v>
@@ -2221,7 +2221,7 @@
         <v>1.16</v>
       </c>
       <c r="BC7">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="BD7">
         <v>4.15</v>
@@ -2668,58 +2668,58 @@
         <v>0</v>
       </c>
       <c r="S10">
-        <v>2.61</v>
+        <v>2.73</v>
       </c>
       <c r="T10">
-        <v>2.23</v>
+        <v>2.03</v>
       </c>
       <c r="U10">
-        <v>4.33</v>
+        <v>3.98</v>
       </c>
       <c r="V10">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W10">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="X10">
-        <v>2.94</v>
+        <v>3.01</v>
       </c>
       <c r="Y10">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="Z10">
-        <v>6.55</v>
+        <v>6.75</v>
       </c>
       <c r="AA10">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AB10">
         <v>1.02</v>
       </c>
       <c r="AC10">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AD10">
-        <v>3.39</v>
+        <v>3.29</v>
       </c>
       <c r="AE10">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="AF10">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AG10">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="AH10">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AI10">
-        <v>5.95</v>
+        <v>6.25</v>
       </c>
       <c r="AJ10">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK10">
         <v>1.78</v>
@@ -2728,10 +2728,10 @@
         <v>1.93</v>
       </c>
       <c r="AM10">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AN10">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AO10">
         <v>0</v>
@@ -2743,16 +2743,16 @@
         <v>1.49</v>
       </c>
       <c r="AR10">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AS10">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AT10">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="AU10">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="AV10">
         <v>2.49</v>
@@ -2761,31 +2761,31 @@
         <v>1.85</v>
       </c>
       <c r="AX10">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AY10">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AZ10">
         <v>1.53</v>
       </c>
       <c r="BA10">
-        <v>2.78</v>
+        <v>3.34</v>
       </c>
       <c r="BB10">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="BC10">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="BD10">
-        <v>3.58</v>
+        <v>3.44</v>
       </c>
       <c r="BE10">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="BF10">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BG10">
         <v>0</v>
@@ -3029,133 +3029,133 @@
         <v>188</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S12">
-        <v>6.02</v>
+        <v>3.13</v>
       </c>
       <c r="T12">
-        <v>2.43</v>
+        <v>2.59</v>
       </c>
       <c r="U12">
-        <v>1.95</v>
+        <v>2.81</v>
       </c>
       <c r="V12">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="W12">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="X12">
-        <v>2.67</v>
+        <v>2.1</v>
       </c>
       <c r="Y12">
-        <v>1.46</v>
+        <v>1.71</v>
       </c>
       <c r="Z12">
-        <v>6</v>
+        <v>4.45</v>
       </c>
       <c r="AA12">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AB12">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC12">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AD12">
-        <v>3.68</v>
+        <v>5.81</v>
       </c>
       <c r="AE12">
-        <v>1.8</v>
+        <v>1.39</v>
       </c>
       <c r="AF12">
-        <v>2.03</v>
+        <v>2.59</v>
       </c>
       <c r="AG12">
-        <v>2.9</v>
+        <v>2.09</v>
       </c>
       <c r="AH12">
-        <v>1.33</v>
+        <v>1.76</v>
       </c>
       <c r="AI12">
-        <v>5.25</v>
+        <v>3.28</v>
       </c>
       <c r="AJ12">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AK12">
+        <v>1.36</v>
+      </c>
+      <c r="AL12">
+        <v>2.84</v>
+      </c>
+      <c r="AM12">
+        <v>1.28</v>
+      </c>
+      <c r="AN12">
+        <v>1.44</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>1.12</v>
+      </c>
+      <c r="AQ12">
+        <v>1.26</v>
+      </c>
+      <c r="AR12">
+        <v>1.66</v>
+      </c>
+      <c r="AS12">
+        <v>1.86</v>
+      </c>
+      <c r="AT12">
+        <v>2.29</v>
+      </c>
+      <c r="AU12">
+        <v>4.8</v>
+      </c>
+      <c r="AV12">
+        <v>3.2</v>
+      </c>
+      <c r="AW12">
+        <v>2.32</v>
+      </c>
+      <c r="AX12">
         <v>1.84</v>
       </c>
-      <c r="AL12">
+      <c r="AY12">
+        <v>1.57</v>
+      </c>
+      <c r="AZ12">
         <v>1.84</v>
       </c>
-      <c r="AM12">
-        <v>1.22</v>
-      </c>
-      <c r="AN12">
-        <v>1.13</v>
-      </c>
-      <c r="AO12">
-        <v>0</v>
-      </c>
-      <c r="AP12">
-        <v>0</v>
-      </c>
-      <c r="AQ12">
-        <v>0</v>
-      </c>
-      <c r="AR12">
-        <v>0</v>
-      </c>
-      <c r="AS12">
-        <v>0</v>
-      </c>
-      <c r="AT12">
-        <v>0</v>
-      </c>
-      <c r="AU12">
-        <v>0</v>
-      </c>
-      <c r="AV12">
-        <v>0</v>
-      </c>
-      <c r="AW12">
-        <v>0</v>
-      </c>
-      <c r="AX12">
-        <v>0</v>
-      </c>
-      <c r="AY12">
-        <v>0</v>
-      </c>
-      <c r="AZ12">
-        <v>0</v>
-      </c>
       <c r="BA12">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="BB12">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="BC12">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="BD12">
-        <v>4.05</v>
+        <v>5.3</v>
       </c>
       <c r="BE12">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="BF12">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="BG12">
         <v>0</v>
@@ -3214,133 +3214,133 @@
         <v>188</v>
       </c>
       <c r="P13">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q13">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R13">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S13">
-        <v>2.93</v>
+        <v>5.1</v>
       </c>
       <c r="T13">
-        <v>2.59</v>
+        <v>2.23</v>
       </c>
       <c r="U13">
-        <v>3.02</v>
+        <v>2.14</v>
       </c>
       <c r="V13">
+        <v>1.35</v>
+      </c>
+      <c r="W13">
+        <v>3.14</v>
+      </c>
+      <c r="X13">
+        <v>2.62</v>
+      </c>
+      <c r="Y13">
+        <v>1.42</v>
+      </c>
+      <c r="Z13">
+        <v>6.2</v>
+      </c>
+      <c r="AA13">
+        <v>1.06</v>
+      </c>
+      <c r="AB13">
+        <v>1</v>
+      </c>
+      <c r="AC13">
         <v>1.22</v>
       </c>
-      <c r="W13">
-        <v>3.6</v>
-      </c>
-      <c r="X13">
-        <v>2.09</v>
-      </c>
-      <c r="Y13">
+      <c r="AD13">
+        <v>3.5</v>
+      </c>
+      <c r="AE13">
+        <v>1.85</v>
+      </c>
+      <c r="AF13">
+        <v>1.97</v>
+      </c>
+      <c r="AG13">
+        <v>3.01</v>
+      </c>
+      <c r="AH13">
+        <v>1.31</v>
+      </c>
+      <c r="AI13">
+        <v>5.5</v>
+      </c>
+      <c r="AJ13">
+        <v>1.08</v>
+      </c>
+      <c r="AK13">
+        <v>1.85</v>
+      </c>
+      <c r="AL13">
+        <v>1.85</v>
+      </c>
+      <c r="AM13">
+        <v>1.24</v>
+      </c>
+      <c r="AN13">
+        <v>1.16</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>0</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>0</v>
+      </c>
+      <c r="AV13">
+        <v>0</v>
+      </c>
+      <c r="AW13">
+        <v>0</v>
+      </c>
+      <c r="AX13">
+        <v>0</v>
+      </c>
+      <c r="AY13">
+        <v>0</v>
+      </c>
+      <c r="AZ13">
+        <v>0</v>
+      </c>
+      <c r="BA13">
+        <v>0</v>
+      </c>
+      <c r="BB13">
+        <v>1.19</v>
+      </c>
+      <c r="BC13">
+        <v>2.05</v>
+      </c>
+      <c r="BD13">
+        <v>3.9</v>
+      </c>
+      <c r="BE13">
         <v>1.71</v>
       </c>
-      <c r="Z13">
-        <v>4.45</v>
-      </c>
-      <c r="AA13">
-        <v>1.14</v>
-      </c>
-      <c r="AB13">
-        <v>1.02</v>
-      </c>
-      <c r="AC13">
-        <v>1.13</v>
-      </c>
-      <c r="AD13">
-        <v>5.82</v>
-      </c>
-      <c r="AE13">
-        <v>1.39</v>
-      </c>
-      <c r="AF13">
-        <v>2.59</v>
-      </c>
-      <c r="AG13">
-        <v>2.1</v>
-      </c>
-      <c r="AH13">
-        <v>1.75</v>
-      </c>
-      <c r="AI13">
-        <v>3.28</v>
-      </c>
-      <c r="AJ13">
-        <v>1.31</v>
-      </c>
-      <c r="AK13">
-        <v>1.36</v>
-      </c>
-      <c r="AL13">
-        <v>2.84</v>
-      </c>
-      <c r="AM13">
-        <v>1.28</v>
-      </c>
-      <c r="AN13">
-        <v>1.51</v>
-      </c>
-      <c r="AO13">
-        <v>0</v>
-      </c>
-      <c r="AP13">
-        <v>1.12</v>
-      </c>
-      <c r="AQ13">
-        <v>1.26</v>
-      </c>
-      <c r="AR13">
-        <v>1.66</v>
-      </c>
-      <c r="AS13">
-        <v>1.86</v>
-      </c>
-      <c r="AT13">
-        <v>2.29</v>
-      </c>
-      <c r="AU13">
-        <v>4.8</v>
-      </c>
-      <c r="AV13">
-        <v>3.2</v>
-      </c>
-      <c r="AW13">
-        <v>2.32</v>
-      </c>
-      <c r="AX13">
-        <v>1.84</v>
-      </c>
-      <c r="AY13">
-        <v>1.57</v>
-      </c>
-      <c r="AZ13">
-        <v>1.84</v>
-      </c>
-      <c r="BA13">
-        <v>2.21</v>
-      </c>
-      <c r="BB13">
-        <v>1.08</v>
-      </c>
-      <c r="BC13">
-        <v>1.62</v>
-      </c>
-      <c r="BD13">
-        <v>5.7</v>
-      </c>
-      <c r="BE13">
-        <v>2.15</v>
-      </c>
       <c r="BF13">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="BG13">
         <v>0</v>
@@ -3545,10 +3545,10 @@
         <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E15" t="s">
         <v>120</v>
@@ -3584,133 +3584,133 @@
         <v>188</v>
       </c>
       <c r="P15">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q15">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R15">
-        <v>4.87</v>
+        <v>0</v>
       </c>
       <c r="S15">
-        <v>2.01</v>
+        <v>3.3</v>
       </c>
       <c r="T15">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="U15">
-        <v>5.61</v>
+        <v>3.42</v>
       </c>
       <c r="V15">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="W15">
-        <v>3.2</v>
+        <v>2.56</v>
       </c>
       <c r="X15">
-        <v>2.39</v>
+        <v>2.99</v>
       </c>
       <c r="Y15">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="Z15">
-        <v>5.75</v>
+        <v>8</v>
       </c>
       <c r="AA15">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AB15">
         <v>1.02</v>
       </c>
       <c r="AC15">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AD15">
-        <v>4.2</v>
+        <v>2.97</v>
       </c>
       <c r="AE15">
-        <v>1.62</v>
+        <v>2.13</v>
       </c>
       <c r="AF15">
-        <v>2.13</v>
+        <v>1.73</v>
       </c>
       <c r="AG15">
-        <v>2.52</v>
+        <v>3.72</v>
       </c>
       <c r="AH15">
-        <v>1.41</v>
+        <v>1.21</v>
       </c>
       <c r="AI15">
-        <v>4.65</v>
+        <v>7.4</v>
       </c>
       <c r="AJ15">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AK15">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AL15">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="AM15">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AN15">
-        <v>2.32</v>
+        <v>1.44</v>
       </c>
       <c r="AO15">
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ15">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AR15">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AS15">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AT15">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AU15">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AV15">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="AW15">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AX15">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AY15">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AZ15">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BA15">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="BB15">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="BC15">
-        <v>1.84</v>
+        <v>2.27</v>
       </c>
       <c r="BD15">
-        <v>4.55</v>
+        <v>3.44</v>
       </c>
       <c r="BE15">
-        <v>1.84</v>
+        <v>1.58</v>
       </c>
       <c r="BF15">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="BG15">
         <v>0</v>
@@ -3730,10 +3730,10 @@
         <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E16" t="s">
         <v>121</v>
@@ -3778,70 +3778,70 @@
         <v>0</v>
       </c>
       <c r="S16">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="V16">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W16">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="X16">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z16">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC16">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD16">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="AE16">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AH16">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI16">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AJ16">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK16">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL16">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AM16">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN16">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AO16">
         <v>0</v>
@@ -3883,19 +3883,19 @@
         <v>0</v>
       </c>
       <c r="BB16">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC16">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="BD16">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="BE16">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF16">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG16">
         <v>0</v>
@@ -3915,7 +3915,7 @@
         <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D17" t="s">
         <v>105</v>
@@ -3954,133 +3954,133 @@
         <v>188</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI17">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL17">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AM17">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AO17">
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AU17">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AV17">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AW17">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AX17">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY17">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AZ17">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BA17">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="BB17">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC17">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BD17">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="BE17">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BF17">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG17">
         <v>0</v>
@@ -4327,10 +4327,10 @@
         <v>2.65</v>
       </c>
       <c r="Q19">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="R19">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -5318,7 +5318,7 @@
         <v>1.94</v>
       </c>
       <c r="AM24">
-        <v>1.21</v>
+        <v>1.81</v>
       </c>
       <c r="AN24">
         <v>1.16</v>
@@ -6144,7 +6144,7 @@
         <v>134</v>
       </c>
       <c r="F29" t="s">
-        <v>175</v>
+        <v>145</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -6329,7 +6329,7 @@
         <v>135</v>
       </c>
       <c r="F30" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -6508,7 +6508,7 @@
         <v>98</v>
       </c>
       <c r="D31" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E31" t="s">
         <v>136</v>
@@ -6544,133 +6544,133 @@
         <v>188</v>
       </c>
       <c r="P31">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="Q31">
-        <v>3.2</v>
+        <v>3.54</v>
       </c>
       <c r="R31">
-        <v>1.8</v>
+        <v>2.52</v>
       </c>
       <c r="S31">
-        <v>5.29</v>
+        <v>0</v>
       </c>
       <c r="T31">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="U31">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="V31">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W31">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="X31">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Y31">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z31">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AA31">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB31">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC31">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD31">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AE31">
-        <v>2.25</v>
+        <v>1.66</v>
       </c>
       <c r="AF31">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="AG31">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH31">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI31">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AJ31">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK31">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL31">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM31">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN31">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AO31">
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ31">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR31">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AS31">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AT31">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AU31">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AV31">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AW31">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AX31">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY31">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ31">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="BA31">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BB31">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BC31">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD31">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BE31">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BF31">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG31">
         <v>0</v>
@@ -6690,10 +6690,10 @@
         <v>80</v>
       </c>
       <c r="C32" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D32" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E32" t="s">
         <v>137</v>
@@ -6729,130 +6729,130 @@
         <v>188</v>
       </c>
       <c r="P32">
+        <v>1.95</v>
+      </c>
+      <c r="Q32">
+        <v>3.25</v>
+      </c>
+      <c r="R32">
+        <v>3.79</v>
+      </c>
+      <c r="S32">
+        <v>2.48</v>
+      </c>
+      <c r="T32">
+        <v>2.1</v>
+      </c>
+      <c r="U32">
+        <v>4.1</v>
+      </c>
+      <c r="V32">
+        <v>1.37</v>
+      </c>
+      <c r="W32">
+        <v>2.7</v>
+      </c>
+      <c r="X32">
+        <v>2.88</v>
+      </c>
+      <c r="Y32">
+        <v>1.33</v>
+      </c>
+      <c r="Z32">
+        <v>7</v>
+      </c>
+      <c r="AA32">
+        <v>1.03</v>
+      </c>
+      <c r="AB32">
+        <v>0</v>
+      </c>
+      <c r="AC32">
+        <v>1.32</v>
+      </c>
+      <c r="AD32">
+        <v>3</v>
+      </c>
+      <c r="AE32">
+        <v>2.02</v>
+      </c>
+      <c r="AF32">
+        <v>1.68</v>
+      </c>
+      <c r="AG32">
+        <v>3.6</v>
+      </c>
+      <c r="AH32">
+        <v>1.24</v>
+      </c>
+      <c r="AI32">
+        <v>6.75</v>
+      </c>
+      <c r="AJ32">
+        <v>1.07</v>
+      </c>
+      <c r="AK32">
+        <v>1.8</v>
+      </c>
+      <c r="AL32">
+        <v>1.84</v>
+      </c>
+      <c r="AM32">
+        <v>1.27</v>
+      </c>
+      <c r="AN32">
+        <v>1.75</v>
+      </c>
+      <c r="AO32">
+        <v>0</v>
+      </c>
+      <c r="AP32">
+        <v>1.4</v>
+      </c>
+      <c r="AQ32">
+        <v>1.67</v>
+      </c>
+      <c r="AR32">
+        <v>2.1</v>
+      </c>
+      <c r="AS32">
+        <v>2.7</v>
+      </c>
+      <c r="AT32">
+        <v>3.65</v>
+      </c>
+      <c r="AU32">
+        <v>2.7</v>
+      </c>
+      <c r="AV32">
+        <v>2.04</v>
+      </c>
+      <c r="AW32">
+        <v>1.64</v>
+      </c>
+      <c r="AX32">
+        <v>1.38</v>
+      </c>
+      <c r="AY32">
+        <v>1.23</v>
+      </c>
+      <c r="AZ32">
+        <v>1.68</v>
+      </c>
+      <c r="BA32">
         <v>2.5</v>
       </c>
-      <c r="Q32">
-        <v>3.54</v>
-      </c>
-      <c r="R32">
-        <v>2.52</v>
-      </c>
-      <c r="S32">
-        <v>0</v>
-      </c>
-      <c r="T32">
-        <v>0</v>
-      </c>
-      <c r="U32">
-        <v>0</v>
-      </c>
-      <c r="V32">
-        <v>0</v>
-      </c>
-      <c r="W32">
-        <v>0</v>
-      </c>
-      <c r="X32">
-        <v>0</v>
-      </c>
-      <c r="Y32">
-        <v>0</v>
-      </c>
-      <c r="Z32">
-        <v>0</v>
-      </c>
-      <c r="AA32">
-        <v>0</v>
-      </c>
-      <c r="AB32">
-        <v>0</v>
-      </c>
-      <c r="AC32">
-        <v>0</v>
-      </c>
-      <c r="AD32">
-        <v>0</v>
-      </c>
-      <c r="AE32">
-        <v>1.66</v>
-      </c>
-      <c r="AF32">
-        <v>2.15</v>
-      </c>
-      <c r="AG32">
-        <v>0</v>
-      </c>
-      <c r="AH32">
-        <v>0</v>
-      </c>
-      <c r="AI32">
-        <v>0</v>
-      </c>
-      <c r="AJ32">
-        <v>0</v>
-      </c>
-      <c r="AK32">
-        <v>0</v>
-      </c>
-      <c r="AL32">
-        <v>0</v>
-      </c>
-      <c r="AM32">
-        <v>0</v>
-      </c>
-      <c r="AN32">
-        <v>0</v>
-      </c>
-      <c r="AO32">
-        <v>0</v>
-      </c>
-      <c r="AP32">
-        <v>0</v>
-      </c>
-      <c r="AQ32">
-        <v>0</v>
-      </c>
-      <c r="AR32">
-        <v>0</v>
-      </c>
-      <c r="AS32">
-        <v>0</v>
-      </c>
-      <c r="AT32">
-        <v>0</v>
-      </c>
-      <c r="AU32">
-        <v>0</v>
-      </c>
-      <c r="AV32">
-        <v>0</v>
-      </c>
-      <c r="AW32">
-        <v>0</v>
-      </c>
-      <c r="AX32">
-        <v>0</v>
-      </c>
-      <c r="AY32">
-        <v>0</v>
-      </c>
-      <c r="AZ32">
-        <v>0</v>
-      </c>
-      <c r="BA32">
-        <v>0</v>
-      </c>
       <c r="BB32">
         <v>0</v>
       </c>
       <c r="BC32">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD32">
         <v>0</v>
       </c>
       <c r="BE32">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF32">
         <v>0</v>
@@ -6875,7 +6875,7 @@
         <v>80</v>
       </c>
       <c r="C33" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D33" t="s">
         <v>105</v>
@@ -6914,133 +6914,133 @@
         <v>188</v>
       </c>
       <c r="P33">
-        <v>5.05</v>
+        <v>4.4</v>
       </c>
       <c r="Q33">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="R33">
+        <v>1.8</v>
+      </c>
+      <c r="S33">
+        <v>5.18</v>
+      </c>
+      <c r="T33">
+        <v>2.13</v>
+      </c>
+      <c r="U33">
+        <v>2.46</v>
+      </c>
+      <c r="V33">
+        <v>1.47</v>
+      </c>
+      <c r="W33">
+        <v>2.41</v>
+      </c>
+      <c r="X33">
+        <v>3.32</v>
+      </c>
+      <c r="Y33">
+        <v>1.33</v>
+      </c>
+      <c r="Z33">
+        <v>7.7</v>
+      </c>
+      <c r="AA33">
+        <v>1.02</v>
+      </c>
+      <c r="AB33">
+        <v>1.04</v>
+      </c>
+      <c r="AC33">
+        <v>1.35</v>
+      </c>
+      <c r="AD33">
+        <v>2.74</v>
+      </c>
+      <c r="AE33">
+        <v>2.25</v>
+      </c>
+      <c r="AF33">
+        <v>1.62</v>
+      </c>
+      <c r="AG33">
+        <v>3.8</v>
+      </c>
+      <c r="AH33">
+        <v>1.19</v>
+      </c>
+      <c r="AI33">
+        <v>7.3</v>
+      </c>
+      <c r="AJ33">
+        <v>1.03</v>
+      </c>
+      <c r="AK33">
+        <v>1.97</v>
+      </c>
+      <c r="AL33">
         <v>1.73</v>
       </c>
-      <c r="S33">
-        <v>6.17</v>
-      </c>
-      <c r="T33">
-        <v>1.87</v>
-      </c>
-      <c r="U33">
-        <v>2.45</v>
-      </c>
-      <c r="V33">
-        <v>1.56</v>
-      </c>
-      <c r="W33">
-        <v>2.26</v>
-      </c>
-      <c r="X33">
-        <v>3.25</v>
-      </c>
-      <c r="Y33">
+      <c r="AM33">
+        <v>1.26</v>
+      </c>
+      <c r="AN33">
+        <v>1.14</v>
+      </c>
+      <c r="AO33">
+        <v>0</v>
+      </c>
+      <c r="AP33">
+        <v>1.28</v>
+      </c>
+      <c r="AQ33">
+        <v>1.53</v>
+      </c>
+      <c r="AR33">
+        <v>1.95</v>
+      </c>
+      <c r="AS33">
+        <v>2.52</v>
+      </c>
+      <c r="AT33">
+        <v>3.48</v>
+      </c>
+      <c r="AU33">
+        <v>3.05</v>
+      </c>
+      <c r="AV33">
+        <v>2.21</v>
+      </c>
+      <c r="AW33">
+        <v>1.73</v>
+      </c>
+      <c r="AX33">
+        <v>1.41</v>
+      </c>
+      <c r="AY33">
         <v>1.22</v>
-      </c>
-      <c r="Z33">
-        <v>9.1</v>
-      </c>
-      <c r="AA33">
-        <v>1.03</v>
-      </c>
-      <c r="AB33">
-        <v>1.06</v>
-      </c>
-      <c r="AC33">
-        <v>1.57</v>
-      </c>
-      <c r="AD33">
-        <v>2.38</v>
-      </c>
-      <c r="AE33">
-        <v>2.75</v>
-      </c>
-      <c r="AF33">
-        <v>1.47</v>
-      </c>
-      <c r="AG33">
-        <v>5.36</v>
-      </c>
-      <c r="AH33">
-        <v>1.12</v>
-      </c>
-      <c r="AI33">
-        <v>10</v>
-      </c>
-      <c r="AJ33">
-        <v>1.02</v>
-      </c>
-      <c r="AK33">
-        <v>2.28</v>
-      </c>
-      <c r="AL33">
-        <v>1.55</v>
-      </c>
-      <c r="AM33">
-        <v>1.28</v>
-      </c>
-      <c r="AN33">
-        <v>1.1</v>
-      </c>
-      <c r="AO33">
-        <v>0</v>
-      </c>
-      <c r="AP33">
-        <v>1.41</v>
-      </c>
-      <c r="AQ33">
-        <v>1.71</v>
-      </c>
-      <c r="AR33">
-        <v>2.55</v>
-      </c>
-      <c r="AS33">
-        <v>2.75</v>
-      </c>
-      <c r="AT33">
-        <v>3.7</v>
-      </c>
-      <c r="AU33">
-        <v>2.65</v>
-      </c>
-      <c r="AV33">
-        <v>2.04</v>
-      </c>
-      <c r="AW33">
-        <v>1.63</v>
-      </c>
-      <c r="AX33">
-        <v>1.38</v>
-      </c>
-      <c r="AY33">
-        <v>1.23</v>
       </c>
       <c r="AZ33">
         <v>2.48</v>
       </c>
       <c r="BA33">
-        <v>1.63</v>
+        <v>1.84</v>
       </c>
       <c r="BB33">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="BC33">
-        <v>2.59</v>
+        <v>2.29</v>
       </c>
       <c r="BD33">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="BE33">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="BF33">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="BG33">
         <v>0</v>
@@ -7060,7 +7060,7 @@
         <v>80</v>
       </c>
       <c r="C34" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D34" t="s">
         <v>105</v>
@@ -7099,133 +7099,133 @@
         <v>188</v>
       </c>
       <c r="P34">
-        <v>1.4</v>
+        <v>4.75</v>
       </c>
       <c r="Q34">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="R34">
-        <v>6.5</v>
+        <v>1.72</v>
       </c>
       <c r="S34">
-        <v>2.01</v>
+        <v>6.17</v>
       </c>
       <c r="T34">
-        <v>2.09</v>
+        <v>1.87</v>
       </c>
       <c r="U34">
-        <v>7.7</v>
+        <v>2.45</v>
       </c>
       <c r="V34">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="W34">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="X34">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="Y34">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="Z34">
-        <v>7.3</v>
+        <v>9.1</v>
       </c>
       <c r="AA34">
         <v>1.03</v>
       </c>
       <c r="AB34">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AC34">
+        <v>1.46</v>
+      </c>
+      <c r="AD34">
+        <v>2.38</v>
+      </c>
+      <c r="AE34">
+        <v>2.75</v>
+      </c>
+      <c r="AF34">
+        <v>1.47</v>
+      </c>
+      <c r="AG34">
+        <v>5.36</v>
+      </c>
+      <c r="AH34">
+        <v>1.12</v>
+      </c>
+      <c r="AI34">
+        <v>10</v>
+      </c>
+      <c r="AJ34">
+        <v>1.02</v>
+      </c>
+      <c r="AK34">
+        <v>2.28</v>
+      </c>
+      <c r="AL34">
+        <v>1.55</v>
+      </c>
+      <c r="AM34">
+        <v>1.28</v>
+      </c>
+      <c r="AN34">
+        <v>1.1</v>
+      </c>
+      <c r="AO34">
+        <v>0</v>
+      </c>
+      <c r="AP34">
+        <v>1.36</v>
+      </c>
+      <c r="AQ34">
+        <v>1.69</v>
+      </c>
+      <c r="AR34">
+        <v>2.14</v>
+      </c>
+      <c r="AS34">
+        <v>2.88</v>
+      </c>
+      <c r="AT34">
+        <v>3.7</v>
+      </c>
+      <c r="AU34">
+        <v>2.7</v>
+      </c>
+      <c r="AV34">
+        <v>2</v>
+      </c>
+      <c r="AW34">
+        <v>1.57</v>
+      </c>
+      <c r="AX34">
         <v>1.32</v>
       </c>
-      <c r="AD34">
-        <v>2.88</v>
-      </c>
-      <c r="AE34">
-        <v>2.06</v>
-      </c>
-      <c r="AF34">
-        <v>1.68</v>
-      </c>
-      <c r="AG34">
-        <v>3.75</v>
-      </c>
-      <c r="AH34">
-        <v>1.22</v>
-      </c>
-      <c r="AI34">
-        <v>6.75</v>
-      </c>
-      <c r="AJ34">
-        <v>1.04</v>
-      </c>
-      <c r="AK34">
-        <v>2.3</v>
-      </c>
-      <c r="AL34">
-        <v>1.54</v>
-      </c>
-      <c r="AM34">
-        <v>1.17</v>
-      </c>
-      <c r="AN34">
-        <v>2.57</v>
-      </c>
-      <c r="AO34">
-        <v>0</v>
-      </c>
-      <c r="AP34">
-        <v>1.24</v>
-      </c>
-      <c r="AQ34">
-        <v>1.46</v>
-      </c>
-      <c r="AR34">
-        <v>2.13</v>
-      </c>
-      <c r="AS34">
-        <v>2.33</v>
-      </c>
-      <c r="AT34">
-        <v>3.14</v>
-      </c>
-      <c r="AU34">
-        <v>3.34</v>
-      </c>
-      <c r="AV34">
-        <v>2.38</v>
-      </c>
-      <c r="AW34">
-        <v>1.83</v>
-      </c>
-      <c r="AX34">
-        <v>1.48</v>
-      </c>
       <c r="AY34">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AZ34">
-        <v>1.3</v>
+        <v>2.43</v>
       </c>
       <c r="BA34">
-        <v>4.32</v>
+        <v>1.89</v>
       </c>
       <c r="BB34">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="BC34">
-        <v>2.24</v>
+        <v>2.59</v>
       </c>
       <c r="BD34">
-        <v>3.34</v>
+        <v>2.91</v>
       </c>
       <c r="BE34">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="BF34">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BG34">
         <v>0</v>
@@ -7245,7 +7245,7 @@
         <v>80</v>
       </c>
       <c r="C35" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D35" t="s">
         <v>105</v>
@@ -7284,133 +7284,133 @@
         <v>188</v>
       </c>
       <c r="P35">
-        <v>1.95</v>
+        <v>1.42</v>
       </c>
       <c r="Q35">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="R35">
-        <v>3.79</v>
+        <v>7.4</v>
       </c>
       <c r="S35">
-        <v>2.48</v>
+        <v>2.01</v>
       </c>
       <c r="T35">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="U35">
-        <v>4.1</v>
+        <v>7.7</v>
       </c>
       <c r="V35">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="W35">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="X35">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="Y35">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z35">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="AA35">
         <v>1.03</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC35">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AD35">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="AE35">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="AF35">
         <v>1.68</v>
       </c>
       <c r="AG35">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AH35">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AI35">
         <v>6.75</v>
       </c>
       <c r="AJ35">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AK35">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AL35">
-        <v>1.84</v>
+        <v>1.54</v>
       </c>
       <c r="AM35">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AN35">
-        <v>1.75</v>
+        <v>2.57</v>
       </c>
       <c r="AO35">
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AQ35">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AR35">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AS35">
-        <v>2.7</v>
+        <v>2.33</v>
       </c>
       <c r="AT35">
-        <v>3.65</v>
+        <v>2.95</v>
       </c>
       <c r="AU35">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="AV35">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="AW35">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AX35">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AY35">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AZ35">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="BA35">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="BB35">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC35">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="BD35">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="BE35">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="BF35">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG35">
         <v>0</v>
@@ -7654,79 +7654,79 @@
         <v>188</v>
       </c>
       <c r="P37">
+        <v>2.05</v>
+      </c>
+      <c r="Q37">
+        <v>2.87</v>
+      </c>
+      <c r="R37">
+        <v>3.7</v>
+      </c>
+      <c r="S37">
+        <v>2.88</v>
+      </c>
+      <c r="T37">
+        <v>1.75</v>
+      </c>
+      <c r="U37">
+        <v>5.37</v>
+      </c>
+      <c r="V37">
+        <v>1.64</v>
+      </c>
+      <c r="W37">
         <v>2.11</v>
       </c>
-      <c r="Q37">
-        <v>2.8</v>
-      </c>
-      <c r="R37">
-        <v>3.45</v>
-      </c>
-      <c r="S37">
-        <v>3.01</v>
-      </c>
-      <c r="T37">
-        <v>1.81</v>
-      </c>
-      <c r="U37">
-        <v>4.53</v>
-      </c>
-      <c r="V37">
-        <v>1.61</v>
-      </c>
-      <c r="W37">
-        <v>2.17</v>
-      </c>
       <c r="X37">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="Y37">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z37">
-        <v>9.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA37">
         <v>1.02</v>
       </c>
       <c r="AB37">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AC37">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AD37">
-        <v>2.09</v>
+        <v>2.23</v>
       </c>
       <c r="AE37">
-        <v>2.85</v>
+        <v>2.74</v>
       </c>
       <c r="AF37">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AG37">
-        <v>6.35</v>
+        <v>4.8</v>
       </c>
       <c r="AH37">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AI37">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AJ37">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK37">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AL37">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AM37">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AN37">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="AO37">
         <v>0</v>
@@ -7735,52 +7735,52 @@
         <v>1.33</v>
       </c>
       <c r="AQ37">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AR37">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AS37">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="AT37">
-        <v>3.75</v>
+        <v>3.71</v>
       </c>
       <c r="AU37">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="AV37">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AW37">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AX37">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AY37">
         <v>1.19</v>
       </c>
       <c r="AZ37">
-        <v>1.98</v>
+        <v>1.53</v>
       </c>
       <c r="BA37">
-        <v>2.31</v>
+        <v>3.44</v>
       </c>
       <c r="BB37">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="BC37">
-        <v>3.12</v>
+        <v>2.9</v>
       </c>
       <c r="BD37">
-        <v>2.53</v>
+        <v>2.66</v>
       </c>
       <c r="BE37">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BF37">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="BG37">
         <v>0</v>
@@ -8024,79 +8024,79 @@
         <v>188</v>
       </c>
       <c r="P39">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="Q39">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="R39">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="S39">
-        <v>2.88</v>
+        <v>3.01</v>
       </c>
       <c r="T39">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="U39">
-        <v>5.37</v>
+        <v>4.53</v>
       </c>
       <c r="V39">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="W39">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="X39">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="Y39">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z39">
-        <v>8.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA39">
         <v>1.02</v>
       </c>
       <c r="AB39">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AC39">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AD39">
-        <v>2.23</v>
+        <v>2.09</v>
       </c>
       <c r="AE39">
-        <v>2.74</v>
+        <v>2.85</v>
       </c>
       <c r="AF39">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AG39">
-        <v>4.8</v>
+        <v>6.35</v>
       </c>
       <c r="AH39">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AI39">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AJ39">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK39">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AL39">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AM39">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AN39">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AO39">
         <v>0</v>
@@ -8105,52 +8105,52 @@
         <v>1.33</v>
       </c>
       <c r="AQ39">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AR39">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AS39">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="AT39">
-        <v>3.71</v>
+        <v>3.75</v>
       </c>
       <c r="AU39">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="AV39">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="AW39">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AX39">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AY39">
         <v>1.19</v>
       </c>
       <c r="AZ39">
-        <v>1.53</v>
+        <v>1.98</v>
       </c>
       <c r="BA39">
-        <v>3.44</v>
+        <v>2.31</v>
       </c>
       <c r="BB39">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="BC39">
-        <v>2.9</v>
+        <v>3.12</v>
       </c>
       <c r="BD39">
-        <v>2.66</v>
+        <v>2.53</v>
       </c>
       <c r="BE39">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="BF39">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BG39">
         <v>0</v>

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -310,12 +310,12 @@
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
+    <t>Egypt Egyptian Premier League</t>
+  </si>
+  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
-    <t>Egypt Egyptian Premier League</t>
-  </si>
-  <si>
     <t>South Africa Premier Soccer League</t>
   </si>
   <si>
@@ -337,30 +337,30 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Jeonbuk Motors</t>
+  </si>
+  <si>
     <t>Bucheon 1995</t>
   </si>
   <si>
-    <t>Jeonbuk Motors</t>
-  </si>
-  <si>
     <t>Gangwon</t>
   </si>
   <si>
+    <t>Daejeon Citizen</t>
+  </si>
+  <si>
     <t>Sangju Sangmu</t>
   </si>
   <si>
-    <t>Daejeon Citizen</t>
-  </si>
-  <si>
     <t>Madura United</t>
   </si>
   <si>
+    <t>Ethiopia Nigd Bank</t>
+  </si>
+  <si>
     <t>FC Seoul</t>
   </si>
   <si>
-    <t>Ethiopia Nigd Bank</t>
-  </si>
-  <si>
     <t>Qingdao Youth Island</t>
   </si>
   <si>
@@ -373,18 +373,18 @@
     <t>Shenyang Urban</t>
   </si>
   <si>
+    <t>Karvan FK</t>
+  </si>
+  <si>
+    <t>Borneo</t>
+  </si>
+  <si>
     <t>Dire Dawa Kenema</t>
   </si>
   <si>
     <t>Chongqing Tongliang Long</t>
   </si>
   <si>
-    <t>Karvan FK</t>
-  </si>
-  <si>
-    <t>Borneo</t>
-  </si>
-  <si>
     <t>Mekelle Kenema</t>
   </si>
   <si>
@@ -418,39 +418,39 @@
     <t>Bani Yas</t>
   </si>
   <si>
+    <t>Dibba Al Fujairah</t>
+  </si>
+  <si>
     <t>Al Ittihad Kalba</t>
   </si>
   <si>
-    <t>Dibba Al Fujairah</t>
+    <t>Ceramica Cleopatra</t>
+  </si>
+  <si>
+    <t>Lokomotiv Sofia 1929</t>
+  </si>
+  <si>
+    <t>Smouha SC</t>
+  </si>
+  <si>
+    <t>Al Ahly</t>
   </si>
   <si>
     <t>Falkenberg</t>
   </si>
   <si>
-    <t>Lokomotiv Sofia 1929</t>
-  </si>
-  <si>
-    <t>Ceramica Cleopatra</t>
-  </si>
-  <si>
-    <t>Smouha SC</t>
-  </si>
-  <si>
-    <t>Al Ahly</t>
-  </si>
-  <si>
     <t>Chippa United</t>
   </si>
   <si>
     <t>Magesi</t>
   </si>
   <si>
+    <t>Siwelele</t>
+  </si>
+  <si>
     <t>Stellenbosch</t>
   </si>
   <si>
-    <t>Siwelele</t>
-  </si>
-  <si>
     <t>Al Khaleej</t>
   </si>
   <si>
@@ -460,30 +460,30 @@
     <t>New York City II</t>
   </si>
   <si>
+    <t>Gwangju</t>
+  </si>
+  <si>
     <t>Jeju United</t>
   </si>
   <si>
-    <t>Gwangju</t>
-  </si>
-  <si>
     <t>Pohang Steelers</t>
   </si>
   <si>
+    <t>Incheon United</t>
+  </si>
+  <si>
     <t>Ulsan</t>
   </si>
   <si>
-    <t>Incheon United</t>
-  </si>
-  <si>
     <t>Bali United</t>
   </si>
   <si>
+    <t>Kedus Giorgis</t>
+  </si>
+  <si>
     <t>Anyang</t>
   </si>
   <si>
-    <t>Kedus Giorgis</t>
-  </si>
-  <si>
     <t>Tianjin Teda</t>
   </si>
   <si>
@@ -496,18 +496,18 @@
     <t>Chengdu Better City FC</t>
   </si>
   <si>
+    <t>Neftçi</t>
+  </si>
+  <si>
+    <t>Persita</t>
+  </si>
+  <si>
     <t>Ethiopia Bunna</t>
   </si>
   <si>
     <t>Henan Jianye</t>
   </si>
   <si>
-    <t>Neftçi</t>
-  </si>
-  <si>
-    <t>Persita</t>
-  </si>
-  <si>
     <t>Arba Minch Kenema</t>
   </si>
   <si>
@@ -544,31 +544,31 @@
     <t>Al Bataeh</t>
   </si>
   <si>
+    <t>Pyramids FC</t>
+  </si>
+  <si>
+    <t>Botev Vratsa</t>
+  </si>
+  <si>
+    <t>Zamalek</t>
+  </si>
+  <si>
+    <t>ENPPI</t>
+  </si>
+  <si>
     <t>Norrköping</t>
   </si>
   <si>
-    <t>Botev Vratsa</t>
-  </si>
-  <si>
-    <t>Pyramids FC</t>
-  </si>
-  <si>
-    <t>Zamalek</t>
-  </si>
-  <si>
-    <t>ENPPI</t>
-  </si>
-  <si>
     <t>Sekhukhune United</t>
   </si>
   <si>
     <t>Orbit College</t>
   </si>
   <si>
+    <t>Durban City</t>
+  </si>
+  <si>
     <t>Orlando Pirates</t>
-  </si>
-  <si>
-    <t>Durban City</t>
   </si>
   <si>
     <t>Al Hilal</t>
@@ -1179,133 +1179,133 @@
         <v>188</v>
       </c>
       <c r="P2">
-        <v>2.52</v>
+        <v>1.4</v>
       </c>
       <c r="Q2">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="R2">
-        <v>2.87</v>
+        <v>6.5</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>7.95</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AO2">
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="AU2">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AV2">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AW2">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AX2">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AY2">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AZ2">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BA2">
-        <v>0</v>
+        <v>5.49</v>
       </c>
       <c r="BB2">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC2">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BD2">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="BE2">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF2">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG2">
         <v>0</v>
@@ -1364,13 +1364,13 @@
         <v>188</v>
       </c>
       <c r="P3">
-        <v>1.37</v>
+        <v>2.4</v>
       </c>
       <c r="Q3">
-        <v>4.55</v>
+        <v>3</v>
       </c>
       <c r="R3">
-        <v>8.449999999999999</v>
+        <v>2.87</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -1549,133 +1549,133 @@
         <v>188</v>
       </c>
       <c r="P4">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="Q4">
+        <v>3.2</v>
+      </c>
+      <c r="R4">
+        <v>3.6</v>
+      </c>
+      <c r="S4">
+        <v>2.77</v>
+      </c>
+      <c r="T4">
+        <v>1.91</v>
+      </c>
+      <c r="U4">
+        <v>4.76</v>
+      </c>
+      <c r="V4">
+        <v>1.53</v>
+      </c>
+      <c r="W4">
+        <v>2.34</v>
+      </c>
+      <c r="X4">
+        <v>3.25</v>
+      </c>
+      <c r="Y4">
+        <v>1.27</v>
+      </c>
+      <c r="Z4">
+        <v>8.5</v>
+      </c>
+      <c r="AA4">
+        <v>1.01</v>
+      </c>
+      <c r="AB4">
+        <v>1.05</v>
+      </c>
+      <c r="AC4">
+        <v>1.42</v>
+      </c>
+      <c r="AD4">
+        <v>2.51</v>
+      </c>
+      <c r="AE4">
+        <v>2.42</v>
+      </c>
+      <c r="AF4">
+        <v>1.54</v>
+      </c>
+      <c r="AG4">
+        <v>4.33</v>
+      </c>
+      <c r="AH4">
+        <v>1.15</v>
+      </c>
+      <c r="AI4">
+        <v>8.5</v>
+      </c>
+      <c r="AJ4">
+        <v>1.01</v>
+      </c>
+      <c r="AK4">
+        <v>2.05</v>
+      </c>
+      <c r="AL4">
+        <v>1.69</v>
+      </c>
+      <c r="AM4">
+        <v>1.33</v>
+      </c>
+      <c r="AN4">
+        <v>1.71</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>1.5</v>
+      </c>
+      <c r="AQ4">
+        <v>1.84</v>
+      </c>
+      <c r="AR4">
+        <v>2.35</v>
+      </c>
+      <c r="AS4">
         <v>3.1</v>
       </c>
-      <c r="R4">
-        <v>3.15</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4">
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <v>0</v>
-      </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0</v>
-      </c>
-      <c r="AC4">
-        <v>0</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>0</v>
-      </c>
-      <c r="AH4">
-        <v>0</v>
-      </c>
-      <c r="AI4">
-        <v>0</v>
-      </c>
-      <c r="AJ4">
-        <v>0</v>
-      </c>
-      <c r="AK4">
-        <v>0</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>0</v>
-      </c>
-      <c r="AO4">
-        <v>0</v>
-      </c>
-      <c r="AP4">
-        <v>0</v>
-      </c>
-      <c r="AQ4">
-        <v>0</v>
-      </c>
-      <c r="AR4">
-        <v>0</v>
-      </c>
-      <c r="AS4">
-        <v>0</v>
-      </c>
       <c r="AT4">
         <v>0</v>
       </c>
       <c r="AU4">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AV4">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AW4">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AX4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY4">
         <v>0</v>
       </c>
       <c r="AZ4">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BA4">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BB4">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC4">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="BD4">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="BE4">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BF4">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG4">
         <v>0</v>
@@ -1734,37 +1734,37 @@
         <v>188</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S5">
-        <v>3.24</v>
+        <v>2.84</v>
       </c>
       <c r="T5">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="U5">
-        <v>2.9</v>
+        <v>4.12</v>
       </c>
       <c r="V5">
+        <v>1.44</v>
+      </c>
+      <c r="W5">
+        <v>2.59</v>
+      </c>
+      <c r="X5">
+        <v>3.04</v>
+      </c>
+      <c r="Y5">
         <v>1.33</v>
       </c>
-      <c r="W5">
-        <v>2.77</v>
-      </c>
-      <c r="X5">
-        <v>2.65</v>
-      </c>
-      <c r="Y5">
-        <v>1.36</v>
-      </c>
       <c r="Z5">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="AA5">
         <v>1.03</v>
@@ -1773,94 +1773,94 @@
         <v>1.02</v>
       </c>
       <c r="AC5">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AD5">
-        <v>3.37</v>
+        <v>2.94</v>
       </c>
       <c r="AE5">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AF5">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AG5">
-        <v>3.38</v>
+        <v>3.54</v>
       </c>
       <c r="AH5">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AI5">
-        <v>6.75</v>
+        <v>7.1</v>
       </c>
       <c r="AJ5">
         <v>1.04</v>
       </c>
       <c r="AK5">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AL5">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AM5">
         <v>1.31</v>
       </c>
       <c r="AN5">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="AO5">
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="AQ5">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="AR5">
-        <v>2.02</v>
+        <v>2.23</v>
       </c>
       <c r="AS5">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="AT5">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AU5">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AV5">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AW5">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AX5">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AY5">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ5">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="BA5">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="BB5">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BC5">
-        <v>2.18</v>
+        <v>2.27</v>
       </c>
       <c r="BD5">
-        <v>3.66</v>
+        <v>3.42</v>
       </c>
       <c r="BE5">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="BF5">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BG5">
         <v>0</v>
@@ -1919,133 +1919,133 @@
         <v>188</v>
       </c>
       <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>3.25</v>
+      </c>
+      <c r="T6">
+        <v>2.01</v>
+      </c>
+      <c r="U6">
+        <v>2.88</v>
+      </c>
+      <c r="V6">
+        <v>1.33</v>
+      </c>
+      <c r="W6">
+        <v>2.77</v>
+      </c>
+      <c r="X6">
+        <v>2.65</v>
+      </c>
+      <c r="Y6">
+        <v>1.36</v>
+      </c>
+      <c r="Z6">
+        <v>7.5</v>
+      </c>
+      <c r="AA6">
+        <v>1.03</v>
+      </c>
+      <c r="AB6">
+        <v>1.02</v>
+      </c>
+      <c r="AC6">
+        <v>1.32</v>
+      </c>
+      <c r="AD6">
+        <v>3.37</v>
+      </c>
+      <c r="AE6">
+        <v>2.01</v>
+      </c>
+      <c r="AF6">
+        <v>1.8</v>
+      </c>
+      <c r="AG6">
+        <v>3.38</v>
+      </c>
+      <c r="AH6">
+        <v>1.24</v>
+      </c>
+      <c r="AI6">
+        <v>6.75</v>
+      </c>
+      <c r="AJ6">
+        <v>1.04</v>
+      </c>
+      <c r="AK6">
+        <v>1.73</v>
+      </c>
+      <c r="AL6">
+        <v>2</v>
+      </c>
+      <c r="AM6">
+        <v>1.31</v>
+      </c>
+      <c r="AN6">
+        <v>1.46</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>1.37</v>
+      </c>
+      <c r="AQ6">
+        <v>1.64</v>
+      </c>
+      <c r="AR6">
+        <v>2.02</v>
+      </c>
+      <c r="AS6">
+        <v>2.6</v>
+      </c>
+      <c r="AT6">
+        <v>3.45</v>
+      </c>
+      <c r="AU6">
+        <v>2.8</v>
+      </c>
+      <c r="AV6">
+        <v>2.1</v>
+      </c>
+      <c r="AW6">
+        <v>1.68</v>
+      </c>
+      <c r="AX6">
+        <v>1.42</v>
+      </c>
+      <c r="AY6">
+        <v>1.26</v>
+      </c>
+      <c r="AZ6">
+        <v>1.81</v>
+      </c>
+      <c r="BA6">
         <v>2.17</v>
       </c>
-      <c r="Q6">
-        <v>3.25</v>
-      </c>
-      <c r="R6">
-        <v>3.34</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-      <c r="W6">
-        <v>0</v>
-      </c>
-      <c r="X6">
-        <v>0</v>
-      </c>
-      <c r="Y6">
-        <v>0</v>
-      </c>
-      <c r="Z6">
-        <v>0</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0</v>
-      </c>
-      <c r="AC6">
-        <v>0</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>0</v>
-      </c>
-      <c r="AG6">
-        <v>0</v>
-      </c>
-      <c r="AH6">
-        <v>0</v>
-      </c>
-      <c r="AI6">
-        <v>0</v>
-      </c>
-      <c r="AJ6">
-        <v>0</v>
-      </c>
-      <c r="AK6">
-        <v>0</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>0</v>
-      </c>
-      <c r="AO6">
-        <v>0</v>
-      </c>
-      <c r="AP6">
-        <v>0</v>
-      </c>
-      <c r="AQ6">
-        <v>0</v>
-      </c>
-      <c r="AR6">
-        <v>0</v>
-      </c>
-      <c r="AS6">
-        <v>0</v>
-      </c>
-      <c r="AT6">
-        <v>0</v>
-      </c>
-      <c r="AU6">
-        <v>0</v>
-      </c>
-      <c r="AV6">
-        <v>0</v>
-      </c>
-      <c r="AW6">
-        <v>0</v>
-      </c>
-      <c r="AX6">
-        <v>0</v>
-      </c>
-      <c r="AY6">
-        <v>0</v>
-      </c>
-      <c r="AZ6">
-        <v>0</v>
-      </c>
-      <c r="BA6">
-        <v>0</v>
-      </c>
       <c r="BB6">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC6">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD6">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="BE6">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BF6">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG6">
         <v>0</v>
@@ -2113,10 +2113,10 @@
         <v>0</v>
       </c>
       <c r="S7">
-        <v>3.38</v>
+        <v>3.58</v>
       </c>
       <c r="T7">
-        <v>2.33</v>
+        <v>2.08</v>
       </c>
       <c r="U7">
         <v>2.86</v>
@@ -2173,10 +2173,10 @@
         <v>2.24</v>
       </c>
       <c r="AM7">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AN7">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AO7">
         <v>0</v>
@@ -2188,10 +2188,10 @@
         <v>1.32</v>
       </c>
       <c r="AR7">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AS7">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="AT7">
         <v>2.55</v>
@@ -2200,10 +2200,10 @@
         <v>4.23</v>
       </c>
       <c r="AV7">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="AW7">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AX7">
         <v>1.71</v>
@@ -2221,7 +2221,7 @@
         <v>1.16</v>
       </c>
       <c r="BC7">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="BD7">
         <v>4.15</v>
@@ -2250,10 +2250,10 @@
         <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E8" t="s">
         <v>113</v>
@@ -2289,13 +2289,13 @@
         <v>188</v>
       </c>
       <c r="P8">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R8">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -2435,10 +2435,10 @@
         <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E9" t="s">
         <v>114</v>
@@ -2474,133 +2474,133 @@
         <v>188</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AO9">
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AU9">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AV9">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AX9">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ9">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BA9">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BD9">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE9">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG9">
         <v>0</v>
@@ -3360,7 +3360,7 @@
         <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D14" t="s">
         <v>105</v>
@@ -3438,28 +3438,28 @@
         <v>0</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK14">
         <v>0</v>
@@ -3468,10 +3468,10 @@
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AO14">
         <v>0</v>
@@ -3545,10 +3545,10 @@
         <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E15" t="s">
         <v>120</v>
@@ -3584,133 +3584,133 @@
         <v>188</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>5.59</v>
       </c>
       <c r="S15">
-        <v>3.3</v>
+        <v>2.01</v>
       </c>
       <c r="T15">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="U15">
-        <v>3.42</v>
+        <v>5.61</v>
       </c>
       <c r="V15">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="W15">
-        <v>2.56</v>
+        <v>3.2</v>
       </c>
       <c r="X15">
-        <v>2.99</v>
+        <v>2.39</v>
       </c>
       <c r="Y15">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="Z15">
-        <v>8</v>
+        <v>5.75</v>
       </c>
       <c r="AA15">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AB15">
         <v>1.02</v>
       </c>
       <c r="AC15">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AD15">
-        <v>2.97</v>
+        <v>4.24</v>
       </c>
       <c r="AE15">
+        <v>1.62</v>
+      </c>
+      <c r="AF15">
         <v>2.13</v>
       </c>
-      <c r="AF15">
-        <v>1.73</v>
-      </c>
       <c r="AG15">
-        <v>3.72</v>
+        <v>2.52</v>
       </c>
       <c r="AH15">
+        <v>1.47</v>
+      </c>
+      <c r="AI15">
+        <v>4.65</v>
+      </c>
+      <c r="AJ15">
+        <v>1.12</v>
+      </c>
+      <c r="AK15">
+        <v>1.69</v>
+      </c>
+      <c r="AL15">
+        <v>2</v>
+      </c>
+      <c r="AM15">
+        <v>1.16</v>
+      </c>
+      <c r="AN15">
+        <v>2.32</v>
+      </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <v>1.19</v>
+      </c>
+      <c r="AQ15">
+        <v>1.37</v>
+      </c>
+      <c r="AR15">
+        <v>1.95</v>
+      </c>
+      <c r="AS15">
+        <v>2.18</v>
+      </c>
+      <c r="AT15">
+        <v>2.86</v>
+      </c>
+      <c r="AU15">
+        <v>3.68</v>
+      </c>
+      <c r="AV15">
+        <v>2.57</v>
+      </c>
+      <c r="AW15">
+        <v>1.97</v>
+      </c>
+      <c r="AX15">
+        <v>1.6</v>
+      </c>
+      <c r="AY15">
+        <v>1.34</v>
+      </c>
+      <c r="AZ15">
+        <v>1.44</v>
+      </c>
+      <c r="BA15">
+        <v>3.16</v>
+      </c>
+      <c r="BB15">
+        <v>1.13</v>
+      </c>
+      <c r="BC15">
+        <v>1.84</v>
+      </c>
+      <c r="BD15">
+        <v>4.55</v>
+      </c>
+      <c r="BE15">
+        <v>1.84</v>
+      </c>
+      <c r="BF15">
         <v>1.21</v>
-      </c>
-      <c r="AI15">
-        <v>7.4</v>
-      </c>
-      <c r="AJ15">
-        <v>1.03</v>
-      </c>
-      <c r="AK15">
-        <v>1.75</v>
-      </c>
-      <c r="AL15">
-        <v>1.89</v>
-      </c>
-      <c r="AM15">
-        <v>1.33</v>
-      </c>
-      <c r="AN15">
-        <v>1.44</v>
-      </c>
-      <c r="AO15">
-        <v>0</v>
-      </c>
-      <c r="AP15">
-        <v>0</v>
-      </c>
-      <c r="AQ15">
-        <v>0</v>
-      </c>
-      <c r="AR15">
-        <v>0</v>
-      </c>
-      <c r="AS15">
-        <v>0</v>
-      </c>
-      <c r="AT15">
-        <v>0</v>
-      </c>
-      <c r="AU15">
-        <v>0</v>
-      </c>
-      <c r="AV15">
-        <v>0</v>
-      </c>
-      <c r="AW15">
-        <v>0</v>
-      </c>
-      <c r="AX15">
-        <v>0</v>
-      </c>
-      <c r="AY15">
-        <v>0</v>
-      </c>
-      <c r="AZ15">
-        <v>0</v>
-      </c>
-      <c r="BA15">
-        <v>0</v>
-      </c>
-      <c r="BB15">
-        <v>1.24</v>
-      </c>
-      <c r="BC15">
-        <v>2.27</v>
-      </c>
-      <c r="BD15">
-        <v>3.44</v>
-      </c>
-      <c r="BE15">
-        <v>1.58</v>
-      </c>
-      <c r="BF15">
-        <v>1.11</v>
       </c>
       <c r="BG15">
         <v>0</v>
@@ -3730,7 +3730,7 @@
         <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D16" t="s">
         <v>105</v>
@@ -3915,10 +3915,10 @@
         <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E17" t="s">
         <v>122</v>
@@ -3954,133 +3954,133 @@
         <v>188</v>
       </c>
       <c r="P17">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R17">
-        <v>4.87</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>2.01</v>
+        <v>3.3</v>
       </c>
       <c r="T17">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="U17">
-        <v>5.61</v>
+        <v>3.42</v>
       </c>
       <c r="V17">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="W17">
-        <v>3.2</v>
+        <v>2.56</v>
       </c>
       <c r="X17">
-        <v>2.39</v>
+        <v>2.99</v>
       </c>
       <c r="Y17">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="Z17">
-        <v>5.75</v>
+        <v>8</v>
       </c>
       <c r="AA17">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AB17">
         <v>1.02</v>
       </c>
       <c r="AC17">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AD17">
-        <v>4.24</v>
+        <v>2.97</v>
       </c>
       <c r="AE17">
-        <v>1.62</v>
+        <v>2.13</v>
       </c>
       <c r="AF17">
-        <v>2.13</v>
+        <v>1.73</v>
       </c>
       <c r="AG17">
-        <v>2.52</v>
+        <v>3.72</v>
       </c>
       <c r="AH17">
-        <v>1.47</v>
+        <v>1.21</v>
       </c>
       <c r="AI17">
-        <v>4.65</v>
+        <v>7.4</v>
       </c>
       <c r="AJ17">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AK17">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL17">
-        <v>1.99</v>
+        <v>1.89</v>
       </c>
       <c r="AM17">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AN17">
-        <v>2.32</v>
+        <v>1.44</v>
       </c>
       <c r="AO17">
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ17">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR17">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AS17">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AT17">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AU17">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AV17">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="AW17">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AX17">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AY17">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AZ17">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BA17">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="BB17">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="BC17">
-        <v>1.84</v>
+        <v>2.27</v>
       </c>
       <c r="BD17">
-        <v>4.55</v>
+        <v>3.44</v>
       </c>
       <c r="BE17">
-        <v>1.84</v>
+        <v>1.58</v>
       </c>
       <c r="BF17">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="BG17">
         <v>0</v>
@@ -4694,79 +4694,79 @@
         <v>188</v>
       </c>
       <c r="P21">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q21">
-        <v>3.09</v>
+        <v>2.9</v>
       </c>
       <c r="R21">
-        <v>3.96</v>
+        <v>3.6</v>
       </c>
       <c r="S21">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="T21">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U21">
-        <v>3.8</v>
+        <v>4.34</v>
       </c>
       <c r="V21">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W21">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="X21">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="Y21">
         <v>1.3</v>
       </c>
       <c r="Z21">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA21">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC21">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AD21">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AE21">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AF21">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AG21">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AH21">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AI21">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK21">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AL21">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AM21">
         <v>1.3</v>
       </c>
       <c r="AN21">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AO21">
         <v>0</v>
@@ -4808,19 +4808,19 @@
         <v>2.17</v>
       </c>
       <c r="BB21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC21">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="BD21">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="BE21">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="BF21">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG21">
         <v>0</v>
@@ -5064,13 +5064,13 @@
         <v>188</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -5109,10 +5109,10 @@
         <v>0</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG23">
         <v>0</v>
@@ -6144,7 +6144,7 @@
         <v>134</v>
       </c>
       <c r="F29" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -6329,7 +6329,7 @@
         <v>135</v>
       </c>
       <c r="F30" t="s">
-        <v>175</v>
+        <v>145</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -6508,7 +6508,7 @@
         <v>98</v>
       </c>
       <c r="D31" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E31" t="s">
         <v>136</v>
@@ -6544,133 +6544,133 @@
         <v>188</v>
       </c>
       <c r="P31">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q31">
-        <v>3.54</v>
+        <v>3.15</v>
       </c>
       <c r="R31">
+        <v>1.8</v>
+      </c>
+      <c r="S31">
+        <v>5.18</v>
+      </c>
+      <c r="T31">
+        <v>2.13</v>
+      </c>
+      <c r="U31">
+        <v>2.46</v>
+      </c>
+      <c r="V31">
+        <v>1.47</v>
+      </c>
+      <c r="W31">
+        <v>2.41</v>
+      </c>
+      <c r="X31">
+        <v>3.32</v>
+      </c>
+      <c r="Y31">
+        <v>1.33</v>
+      </c>
+      <c r="Z31">
+        <v>7.7</v>
+      </c>
+      <c r="AA31">
+        <v>1.02</v>
+      </c>
+      <c r="AB31">
+        <v>1.04</v>
+      </c>
+      <c r="AC31">
+        <v>1.35</v>
+      </c>
+      <c r="AD31">
+        <v>2.74</v>
+      </c>
+      <c r="AE31">
+        <v>2.25</v>
+      </c>
+      <c r="AF31">
+        <v>1.62</v>
+      </c>
+      <c r="AG31">
+        <v>3.8</v>
+      </c>
+      <c r="AH31">
+        <v>1.19</v>
+      </c>
+      <c r="AI31">
+        <v>7.3</v>
+      </c>
+      <c r="AJ31">
+        <v>1.03</v>
+      </c>
+      <c r="AK31">
+        <v>1.97</v>
+      </c>
+      <c r="AL31">
+        <v>1.73</v>
+      </c>
+      <c r="AM31">
+        <v>1.26</v>
+      </c>
+      <c r="AN31">
+        <v>1.14</v>
+      </c>
+      <c r="AO31">
+        <v>0</v>
+      </c>
+      <c r="AP31">
+        <v>1.28</v>
+      </c>
+      <c r="AQ31">
+        <v>1.53</v>
+      </c>
+      <c r="AR31">
+        <v>1.95</v>
+      </c>
+      <c r="AS31">
         <v>2.52</v>
       </c>
-      <c r="S31">
-        <v>0</v>
-      </c>
-      <c r="T31">
-        <v>0</v>
-      </c>
-      <c r="U31">
-        <v>0</v>
-      </c>
-      <c r="V31">
-        <v>0</v>
-      </c>
-      <c r="W31">
-        <v>0</v>
-      </c>
-      <c r="X31">
-        <v>0</v>
-      </c>
-      <c r="Y31">
-        <v>0</v>
-      </c>
-      <c r="Z31">
-        <v>0</v>
-      </c>
-      <c r="AA31">
-        <v>0</v>
-      </c>
-      <c r="AB31">
-        <v>0</v>
-      </c>
-      <c r="AC31">
-        <v>0</v>
-      </c>
-      <c r="AD31">
-        <v>0</v>
-      </c>
-      <c r="AE31">
-        <v>1.66</v>
-      </c>
-      <c r="AF31">
-        <v>2.15</v>
-      </c>
-      <c r="AG31">
-        <v>0</v>
-      </c>
-      <c r="AH31">
-        <v>0</v>
-      </c>
-      <c r="AI31">
-        <v>0</v>
-      </c>
-      <c r="AJ31">
-        <v>0</v>
-      </c>
-      <c r="AK31">
-        <v>0</v>
-      </c>
-      <c r="AL31">
-        <v>0</v>
-      </c>
-      <c r="AM31">
-        <v>0</v>
-      </c>
-      <c r="AN31">
-        <v>0</v>
-      </c>
-      <c r="AO31">
-        <v>0</v>
-      </c>
-      <c r="AP31">
-        <v>0</v>
-      </c>
-      <c r="AQ31">
-        <v>0</v>
-      </c>
-      <c r="AR31">
-        <v>0</v>
-      </c>
-      <c r="AS31">
-        <v>0</v>
-      </c>
       <c r="AT31">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AU31">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV31">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AW31">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AX31">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY31">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ31">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BA31">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BB31">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC31">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD31">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE31">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF31">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG31">
         <v>0</v>
@@ -6875,7 +6875,7 @@
         <v>80</v>
       </c>
       <c r="C33" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D33" t="s">
         <v>105</v>
@@ -6914,133 +6914,133 @@
         <v>188</v>
       </c>
       <c r="P33">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="Q33">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="R33">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="S33">
-        <v>5.18</v>
+        <v>6.17</v>
       </c>
       <c r="T33">
-        <v>2.13</v>
+        <v>1.87</v>
       </c>
       <c r="U33">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="V33">
+        <v>1.56</v>
+      </c>
+      <c r="W33">
+        <v>2.26</v>
+      </c>
+      <c r="X33">
+        <v>3.25</v>
+      </c>
+      <c r="Y33">
+        <v>1.22</v>
+      </c>
+      <c r="Z33">
+        <v>9.1</v>
+      </c>
+      <c r="AA33">
+        <v>1.03</v>
+      </c>
+      <c r="AB33">
+        <v>1.06</v>
+      </c>
+      <c r="AC33">
+        <v>1.46</v>
+      </c>
+      <c r="AD33">
+        <v>2.38</v>
+      </c>
+      <c r="AE33">
+        <v>2.75</v>
+      </c>
+      <c r="AF33">
         <v>1.47</v>
       </c>
-      <c r="W33">
-        <v>2.41</v>
-      </c>
-      <c r="X33">
-        <v>3.32</v>
-      </c>
-      <c r="Y33">
+      <c r="AG33">
+        <v>5.36</v>
+      </c>
+      <c r="AH33">
+        <v>1.12</v>
+      </c>
+      <c r="AI33">
+        <v>10</v>
+      </c>
+      <c r="AJ33">
+        <v>1.02</v>
+      </c>
+      <c r="AK33">
+        <v>2.28</v>
+      </c>
+      <c r="AL33">
+        <v>1.55</v>
+      </c>
+      <c r="AM33">
+        <v>1.28</v>
+      </c>
+      <c r="AN33">
+        <v>1.1</v>
+      </c>
+      <c r="AO33">
+        <v>0</v>
+      </c>
+      <c r="AP33">
+        <v>1.36</v>
+      </c>
+      <c r="AQ33">
+        <v>1.69</v>
+      </c>
+      <c r="AR33">
+        <v>2.14</v>
+      </c>
+      <c r="AS33">
+        <v>2.88</v>
+      </c>
+      <c r="AT33">
+        <v>3.7</v>
+      </c>
+      <c r="AU33">
+        <v>2.7</v>
+      </c>
+      <c r="AV33">
+        <v>2</v>
+      </c>
+      <c r="AW33">
+        <v>1.57</v>
+      </c>
+      <c r="AX33">
+        <v>1.32</v>
+      </c>
+      <c r="AY33">
+        <v>1.23</v>
+      </c>
+      <c r="AZ33">
+        <v>2.43</v>
+      </c>
+      <c r="BA33">
+        <v>1.89</v>
+      </c>
+      <c r="BB33">
         <v>1.33</v>
       </c>
-      <c r="Z33">
-        <v>7.7</v>
-      </c>
-      <c r="AA33">
-        <v>1.02</v>
-      </c>
-      <c r="AB33">
-        <v>1.04</v>
-      </c>
-      <c r="AC33">
-        <v>1.35</v>
-      </c>
-      <c r="AD33">
-        <v>2.74</v>
-      </c>
-      <c r="AE33">
-        <v>2.25</v>
-      </c>
-      <c r="AF33">
-        <v>1.62</v>
-      </c>
-      <c r="AG33">
-        <v>3.8</v>
-      </c>
-      <c r="AH33">
-        <v>1.19</v>
-      </c>
-      <c r="AI33">
-        <v>7.3</v>
-      </c>
-      <c r="AJ33">
-        <v>1.03</v>
-      </c>
-      <c r="AK33">
-        <v>1.97</v>
-      </c>
-      <c r="AL33">
-        <v>1.73</v>
-      </c>
-      <c r="AM33">
-        <v>1.26</v>
-      </c>
-      <c r="AN33">
-        <v>1.14</v>
-      </c>
-      <c r="AO33">
-        <v>0</v>
-      </c>
-      <c r="AP33">
-        <v>1.28</v>
-      </c>
-      <c r="AQ33">
-        <v>1.53</v>
-      </c>
-      <c r="AR33">
-        <v>1.95</v>
-      </c>
-      <c r="AS33">
-        <v>2.52</v>
-      </c>
-      <c r="AT33">
-        <v>3.48</v>
-      </c>
-      <c r="AU33">
-        <v>3.05</v>
-      </c>
-      <c r="AV33">
-        <v>2.21</v>
-      </c>
-      <c r="AW33">
-        <v>1.73</v>
-      </c>
-      <c r="AX33">
+      <c r="BC33">
+        <v>2.59</v>
+      </c>
+      <c r="BD33">
+        <v>2.91</v>
+      </c>
+      <c r="BE33">
         <v>1.41</v>
       </c>
-      <c r="AY33">
-        <v>1.22</v>
-      </c>
-      <c r="AZ33">
-        <v>2.48</v>
-      </c>
-      <c r="BA33">
-        <v>1.84</v>
-      </c>
-      <c r="BB33">
-        <v>1.27</v>
-      </c>
-      <c r="BC33">
-        <v>2.29</v>
-      </c>
-      <c r="BD33">
-        <v>3.25</v>
-      </c>
-      <c r="BE33">
-        <v>1.52</v>
-      </c>
       <c r="BF33">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="BG33">
         <v>0</v>
@@ -7060,7 +7060,7 @@
         <v>80</v>
       </c>
       <c r="C34" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D34" t="s">
         <v>105</v>
@@ -7099,133 +7099,133 @@
         <v>188</v>
       </c>
       <c r="P34">
-        <v>4.75</v>
+        <v>1.42</v>
       </c>
       <c r="Q34">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="R34">
-        <v>1.72</v>
+        <v>7.4</v>
       </c>
       <c r="S34">
-        <v>6.17</v>
+        <v>2.01</v>
       </c>
       <c r="T34">
-        <v>1.87</v>
+        <v>2.09</v>
       </c>
       <c r="U34">
-        <v>2.45</v>
+        <v>7.7</v>
       </c>
       <c r="V34">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="W34">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="X34">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="Y34">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="Z34">
-        <v>9.1</v>
+        <v>7.3</v>
       </c>
       <c r="AA34">
         <v>1.03</v>
       </c>
       <c r="AB34">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AC34">
+        <v>1.37</v>
+      </c>
+      <c r="AD34">
+        <v>3.01</v>
+      </c>
+      <c r="AE34">
+        <v>2.06</v>
+      </c>
+      <c r="AF34">
+        <v>1.68</v>
+      </c>
+      <c r="AG34">
+        <v>3.75</v>
+      </c>
+      <c r="AH34">
+        <v>1.22</v>
+      </c>
+      <c r="AI34">
+        <v>6.75</v>
+      </c>
+      <c r="AJ34">
+        <v>1.04</v>
+      </c>
+      <c r="AK34">
+        <v>2.3</v>
+      </c>
+      <c r="AL34">
+        <v>1.54</v>
+      </c>
+      <c r="AM34">
+        <v>1.17</v>
+      </c>
+      <c r="AN34">
+        <v>2.57</v>
+      </c>
+      <c r="AO34">
+        <v>0</v>
+      </c>
+      <c r="AP34">
+        <v>1.3</v>
+      </c>
+      <c r="AQ34">
         <v>1.46</v>
       </c>
-      <c r="AD34">
+      <c r="AR34">
+        <v>2.13</v>
+      </c>
+      <c r="AS34">
+        <v>2.33</v>
+      </c>
+      <c r="AT34">
+        <v>2.95</v>
+      </c>
+      <c r="AU34">
+        <v>3.15</v>
+      </c>
+      <c r="AV34">
         <v>2.38</v>
       </c>
-      <c r="AE34">
-        <v>2.75</v>
-      </c>
-      <c r="AF34">
-        <v>1.47</v>
-      </c>
-      <c r="AG34">
-        <v>5.36</v>
-      </c>
-      <c r="AH34">
+      <c r="AW34">
+        <v>1.83</v>
+      </c>
+      <c r="AX34">
+        <v>1.48</v>
+      </c>
+      <c r="AY34">
+        <v>1.34</v>
+      </c>
+      <c r="AZ34">
+        <v>1.3</v>
+      </c>
+      <c r="BA34">
+        <v>4.2</v>
+      </c>
+      <c r="BB34">
+        <v>1.24</v>
+      </c>
+      <c r="BC34">
+        <v>2.24</v>
+      </c>
+      <c r="BD34">
+        <v>3.34</v>
+      </c>
+      <c r="BE34">
+        <v>1.57</v>
+      </c>
+      <c r="BF34">
         <v>1.12</v>
-      </c>
-      <c r="AI34">
-        <v>10</v>
-      </c>
-      <c r="AJ34">
-        <v>1.02</v>
-      </c>
-      <c r="AK34">
-        <v>2.28</v>
-      </c>
-      <c r="AL34">
-        <v>1.55</v>
-      </c>
-      <c r="AM34">
-        <v>1.28</v>
-      </c>
-      <c r="AN34">
-        <v>1.1</v>
-      </c>
-      <c r="AO34">
-        <v>0</v>
-      </c>
-      <c r="AP34">
-        <v>1.36</v>
-      </c>
-      <c r="AQ34">
-        <v>1.69</v>
-      </c>
-      <c r="AR34">
-        <v>2.14</v>
-      </c>
-      <c r="AS34">
-        <v>2.88</v>
-      </c>
-      <c r="AT34">
-        <v>3.7</v>
-      </c>
-      <c r="AU34">
-        <v>2.7</v>
-      </c>
-      <c r="AV34">
-        <v>2</v>
-      </c>
-      <c r="AW34">
-        <v>1.57</v>
-      </c>
-      <c r="AX34">
-        <v>1.32</v>
-      </c>
-      <c r="AY34">
-        <v>1.23</v>
-      </c>
-      <c r="AZ34">
-        <v>2.43</v>
-      </c>
-      <c r="BA34">
-        <v>1.89</v>
-      </c>
-      <c r="BB34">
-        <v>1.33</v>
-      </c>
-      <c r="BC34">
-        <v>2.59</v>
-      </c>
-      <c r="BD34">
-        <v>2.91</v>
-      </c>
-      <c r="BE34">
-        <v>1.41</v>
-      </c>
-      <c r="BF34">
-        <v>1.06</v>
       </c>
       <c r="BG34">
         <v>0</v>
@@ -7248,7 +7248,7 @@
         <v>99</v>
       </c>
       <c r="D35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E35" t="s">
         <v>140</v>
@@ -7284,133 +7284,133 @@
         <v>188</v>
       </c>
       <c r="P35">
-        <v>1.42</v>
+        <v>2.5</v>
       </c>
       <c r="Q35">
-        <v>3.85</v>
+        <v>3.52</v>
       </c>
       <c r="R35">
-        <v>7.4</v>
+        <v>2.53</v>
       </c>
       <c r="S35">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="T35">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U35">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="V35">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W35">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X35">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="Y35">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z35">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA35">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB35">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC35">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AD35">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="AE35">
-        <v>2.06</v>
+        <v>1.66</v>
       </c>
       <c r="AF35">
-        <v>1.68</v>
+        <v>2.15</v>
       </c>
       <c r="AG35">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AH35">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI35">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AJ35">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK35">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL35">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AM35">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN35">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AO35">
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ35">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR35">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AS35">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AT35">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AU35">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AV35">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AW35">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AX35">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AY35">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ35">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BA35">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BB35">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC35">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BD35">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="BE35">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF35">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG35">
         <v>0</v>
@@ -7469,13 +7469,13 @@
         <v>188</v>
       </c>
       <c r="P36">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q36">
         <v>3</v>
       </c>
       <c r="R36">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S36">
         <v>4.43</v>
@@ -7508,28 +7508,28 @@
         <v>1.05</v>
       </c>
       <c r="AC36">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AD36">
         <v>2.46</v>
       </c>
       <c r="AE36">
-        <v>2.44</v>
+        <v>2.65</v>
       </c>
       <c r="AF36">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="AG36">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AH36">
         <v>1.13</v>
       </c>
       <c r="AI36">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="AJ36">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AK36">
         <v>2.04</v>
@@ -7538,49 +7538,49 @@
         <v>1.68</v>
       </c>
       <c r="AM36">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AN36">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AO36">
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AQ36">
         <v>1.72</v>
       </c>
       <c r="AR36">
-        <v>2.31</v>
+        <v>2.6</v>
       </c>
       <c r="AS36">
-        <v>2.57</v>
+        <v>2.9</v>
       </c>
       <c r="AT36">
-        <v>3.56</v>
+        <v>4.15</v>
       </c>
       <c r="AU36">
-        <v>2.98</v>
+        <v>2.66</v>
       </c>
       <c r="AV36">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AW36">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AX36">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AY36">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AZ36">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="BA36">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="BB36">
         <v>1.32</v>
@@ -7589,7 +7589,7 @@
         <v>2.59</v>
       </c>
       <c r="BD36">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="BE36">
         <v>1.41</v>
@@ -7654,13 +7654,13 @@
         <v>188</v>
       </c>
       <c r="P37">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="Q37">
-        <v>2.87</v>
+        <v>2.79</v>
       </c>
       <c r="R37">
-        <v>3.7</v>
+        <v>4.05</v>
       </c>
       <c r="S37">
         <v>2.88</v>
@@ -7678,10 +7678,10 @@
         <v>2.11</v>
       </c>
       <c r="X37">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="Y37">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="Z37">
         <v>8.699999999999999</v>
@@ -7690,10 +7690,10 @@
         <v>1.02</v>
       </c>
       <c r="AB37">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AC37">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AD37">
         <v>2.23</v>
@@ -7702,25 +7702,25 @@
         <v>2.74</v>
       </c>
       <c r="AF37">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AG37">
-        <v>4.8</v>
+        <v>6.25</v>
       </c>
       <c r="AH37">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AI37">
-        <v>13</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AJ37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AK37">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AL37">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="AM37">
         <v>1.35</v>
@@ -7732,40 +7732,40 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AQ37">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="AR37">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="AS37">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="AT37">
-        <v>3.71</v>
+        <v>4.34</v>
       </c>
       <c r="AU37">
-        <v>2.89</v>
+        <v>2.58</v>
       </c>
       <c r="AV37">
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="AW37">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AX37">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AY37">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AZ37">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="BA37">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="BB37">
         <v>1.39</v>
@@ -7777,7 +7777,7 @@
         <v>2.66</v>
       </c>
       <c r="BE37">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="BF37">
         <v>1.03</v>
@@ -7839,133 +7839,133 @@
         <v>188</v>
       </c>
       <c r="P38">
-        <v>4.65</v>
+        <v>2.2</v>
       </c>
       <c r="Q38">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="R38">
-        <v>1.62</v>
+        <v>3.37</v>
       </c>
       <c r="S38">
-        <v>6.93</v>
+        <v>3.01</v>
       </c>
       <c r="T38">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="U38">
-        <v>2.3</v>
+        <v>4.53</v>
       </c>
       <c r="V38">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="W38">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="X38">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="Y38">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z38">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA38">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB38">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AC38">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="AD38">
-        <v>2.35</v>
+        <v>2.09</v>
       </c>
       <c r="AE38">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="AF38">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="AG38">
-        <v>5.18</v>
+        <v>6.35</v>
       </c>
       <c r="AH38">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AI38">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AJ38">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AK38">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AL38">
         <v>1.5</v>
       </c>
       <c r="AM38">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AN38">
-        <v>1.07</v>
+        <v>1.54</v>
       </c>
       <c r="AO38">
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AQ38">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AR38">
-        <v>2.34</v>
+        <v>2.71</v>
       </c>
       <c r="AS38">
-        <v>2.61</v>
+        <v>3.02</v>
       </c>
       <c r="AT38">
-        <v>3.63</v>
+        <v>4.36</v>
       </c>
       <c r="AU38">
-        <v>2.94</v>
+        <v>2.57</v>
       </c>
       <c r="AV38">
-        <v>2.16</v>
+        <v>1.99</v>
       </c>
       <c r="AW38">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AX38">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AY38">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AZ38">
-        <v>4.42</v>
+        <v>1.96</v>
       </c>
       <c r="BA38">
-        <v>1.37</v>
+        <v>2.39</v>
       </c>
       <c r="BB38">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="BC38">
-        <v>2.66</v>
+        <v>3.12</v>
       </c>
       <c r="BD38">
-        <v>2.82</v>
+        <v>2.53</v>
       </c>
       <c r="BE38">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="BF38">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="BG38">
         <v>0</v>
@@ -8024,133 +8024,133 @@
         <v>188</v>
       </c>
       <c r="P39">
-        <v>2.11</v>
+        <v>4.65</v>
       </c>
       <c r="Q39">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="R39">
+        <v>1.62</v>
+      </c>
+      <c r="S39">
+        <v>6.93</v>
+      </c>
+      <c r="T39">
+        <v>1.9</v>
+      </c>
+      <c r="U39">
+        <v>2.3</v>
+      </c>
+      <c r="V39">
+        <v>1.55</v>
+      </c>
+      <c r="W39">
+        <v>2.28</v>
+      </c>
+      <c r="X39">
         <v>3.45</v>
       </c>
-      <c r="S39">
-        <v>3.01</v>
-      </c>
-      <c r="T39">
-        <v>1.81</v>
-      </c>
-      <c r="U39">
-        <v>4.53</v>
-      </c>
-      <c r="V39">
-        <v>1.61</v>
-      </c>
-      <c r="W39">
-        <v>2.17</v>
-      </c>
-      <c r="X39">
-        <v>4.1</v>
-      </c>
       <c r="Y39">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z39">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA39">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AB39">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AC39">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AD39">
-        <v>2.09</v>
+        <v>2.35</v>
       </c>
       <c r="AE39">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="AF39">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="AG39">
-        <v>6.35</v>
+        <v>4.9</v>
       </c>
       <c r="AH39">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AI39">
-        <v>15</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ39">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AK39">
         <v>2.4</v>
       </c>
       <c r="AL39">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AM39">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AN39">
-        <v>1.55</v>
+        <v>1.07</v>
       </c>
       <c r="AO39">
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AQ39">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR39">
-        <v>2.4</v>
+        <v>2.73</v>
       </c>
       <c r="AS39">
-        <v>2.68</v>
+        <v>3.04</v>
       </c>
       <c r="AT39">
-        <v>3.75</v>
+        <v>4.41</v>
       </c>
       <c r="AU39">
-        <v>2.86</v>
+        <v>2.55</v>
       </c>
       <c r="AV39">
-        <v>2.12</v>
+        <v>1.99</v>
       </c>
       <c r="AW39">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="AX39">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AY39">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AZ39">
-        <v>1.98</v>
+        <v>4.1</v>
       </c>
       <c r="BA39">
-        <v>2.31</v>
+        <v>1.42</v>
       </c>
       <c r="BB39">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="BC39">
-        <v>3.12</v>
+        <v>2.66</v>
       </c>
       <c r="BD39">
-        <v>2.53</v>
+        <v>2.82</v>
       </c>
       <c r="BE39">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="BF39">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="BG39">
         <v>0</v>

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -346,12 +346,12 @@
     <t>Gangwon</t>
   </si>
   <si>
+    <t>Sangju Sangmu</t>
+  </si>
+  <si>
     <t>Daejeon Citizen</t>
   </si>
   <si>
-    <t>Sangju Sangmu</t>
-  </si>
-  <si>
     <t>Madura United</t>
   </si>
   <si>
@@ -373,18 +373,18 @@
     <t>Shenyang Urban</t>
   </si>
   <si>
+    <t>Dire Dawa Kenema</t>
+  </si>
+  <si>
+    <t>Borneo</t>
+  </si>
+  <si>
+    <t>Chongqing Tongliang Long</t>
+  </si>
+  <si>
     <t>Karvan FK</t>
   </si>
   <si>
-    <t>Borneo</t>
-  </si>
-  <si>
-    <t>Dire Dawa Kenema</t>
-  </si>
-  <si>
-    <t>Chongqing Tongliang Long</t>
-  </si>
-  <si>
     <t>Mekelle Kenema</t>
   </si>
   <si>
@@ -424,33 +424,33 @@
     <t>Al Ittihad Kalba</t>
   </si>
   <si>
+    <t>Lokomotiv Sofia 1929</t>
+  </si>
+  <si>
     <t>Ceramica Cleopatra</t>
   </si>
   <si>
-    <t>Lokomotiv Sofia 1929</t>
+    <t>Al Ahly</t>
+  </si>
+  <si>
+    <t>Falkenberg</t>
   </si>
   <si>
     <t>Smouha SC</t>
   </si>
   <si>
-    <t>Al Ahly</t>
-  </si>
-  <si>
-    <t>Falkenberg</t>
+    <t>Magesi</t>
   </si>
   <si>
     <t>Chippa United</t>
   </si>
   <si>
-    <t>Magesi</t>
+    <t>Stellenbosch</t>
   </si>
   <si>
     <t>Siwelele</t>
   </si>
   <si>
-    <t>Stellenbosch</t>
-  </si>
-  <si>
     <t>Al Khaleej</t>
   </si>
   <si>
@@ -469,12 +469,12 @@
     <t>Pohang Steelers</t>
   </si>
   <si>
+    <t>Ulsan</t>
+  </si>
+  <si>
     <t>Incheon United</t>
   </si>
   <si>
-    <t>Ulsan</t>
-  </si>
-  <si>
     <t>Bali United</t>
   </si>
   <si>
@@ -496,18 +496,18 @@
     <t>Chengdu Better City FC</t>
   </si>
   <si>
+    <t>Ethiopia Bunna</t>
+  </si>
+  <si>
+    <t>Persita</t>
+  </si>
+  <si>
+    <t>Henan Jianye</t>
+  </si>
+  <si>
     <t>Neftçi</t>
   </si>
   <si>
-    <t>Persita</t>
-  </si>
-  <si>
-    <t>Ethiopia Bunna</t>
-  </si>
-  <si>
-    <t>Henan Jianye</t>
-  </si>
-  <si>
     <t>Arba Minch Kenema</t>
   </si>
   <si>
@@ -544,31 +544,31 @@
     <t>Al Bataeh</t>
   </si>
   <si>
+    <t>Botev Vratsa</t>
+  </si>
+  <si>
     <t>Pyramids FC</t>
   </si>
   <si>
-    <t>Botev Vratsa</t>
+    <t>ENPPI</t>
+  </si>
+  <si>
+    <t>Norrköping</t>
   </si>
   <si>
     <t>Zamalek</t>
   </si>
   <si>
-    <t>ENPPI</t>
-  </si>
-  <si>
-    <t>Norrköping</t>
+    <t>Orbit College</t>
   </si>
   <si>
     <t>Sekhukhune United</t>
   </si>
   <si>
-    <t>Orbit College</t>
+    <t>Orlando Pirates</t>
   </si>
   <si>
     <t>Durban City</t>
-  </si>
-  <si>
-    <t>Orlando Pirates</t>
   </si>
   <si>
     <t>Al Hilal</t>
@@ -1734,37 +1734,37 @@
         <v>188</v>
       </c>
       <c r="P5">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R5">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>2.84</v>
+        <v>3.25</v>
       </c>
       <c r="T5">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="U5">
-        <v>4.12</v>
+        <v>2.88</v>
       </c>
       <c r="V5">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="W5">
-        <v>2.59</v>
+        <v>2.77</v>
       </c>
       <c r="X5">
-        <v>3.04</v>
+        <v>2.65</v>
       </c>
       <c r="Y5">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z5">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="AA5">
         <v>1.03</v>
@@ -1773,94 +1773,94 @@
         <v>1.02</v>
       </c>
       <c r="AC5">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AD5">
-        <v>2.94</v>
+        <v>3.37</v>
       </c>
       <c r="AE5">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AF5">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AG5">
-        <v>3.54</v>
+        <v>3.38</v>
       </c>
       <c r="AH5">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AI5">
-        <v>7.1</v>
+        <v>6.75</v>
       </c>
       <c r="AJ5">
         <v>1.04</v>
       </c>
       <c r="AK5">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AL5">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AM5">
         <v>1.31</v>
       </c>
       <c r="AN5">
+        <v>1.46</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>1.37</v>
+      </c>
+      <c r="AQ5">
         <v>1.64</v>
       </c>
-      <c r="AO5">
-        <v>0</v>
-      </c>
-      <c r="AP5">
-        <v>1.45</v>
-      </c>
-      <c r="AQ5">
-        <v>1.76</v>
-      </c>
       <c r="AR5">
-        <v>2.23</v>
+        <v>2.02</v>
       </c>
       <c r="AS5">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AU5">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AV5">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AW5">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AX5">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AY5">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ5">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="BA5">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="BB5">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC5">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="BD5">
-        <v>3.42</v>
+        <v>3.66</v>
       </c>
       <c r="BE5">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="BF5">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BG5">
         <v>0</v>
@@ -1919,37 +1919,37 @@
         <v>188</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S6">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="T6">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="U6">
-        <v>2.88</v>
+        <v>4.12</v>
       </c>
       <c r="V6">
+        <v>1.44</v>
+      </c>
+      <c r="W6">
+        <v>2.59</v>
+      </c>
+      <c r="X6">
+        <v>3.04</v>
+      </c>
+      <c r="Y6">
         <v>1.33</v>
       </c>
-      <c r="W6">
-        <v>2.77</v>
-      </c>
-      <c r="X6">
-        <v>2.65</v>
-      </c>
-      <c r="Y6">
-        <v>1.36</v>
-      </c>
       <c r="Z6">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="AA6">
         <v>1.03</v>
@@ -1958,94 +1958,94 @@
         <v>1.02</v>
       </c>
       <c r="AC6">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AD6">
-        <v>3.37</v>
+        <v>2.94</v>
       </c>
       <c r="AE6">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AF6">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AG6">
-        <v>3.38</v>
+        <v>3.54</v>
       </c>
       <c r="AH6">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AI6">
-        <v>6.75</v>
+        <v>7.1</v>
       </c>
       <c r="AJ6">
         <v>1.04</v>
       </c>
       <c r="AK6">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AL6">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AM6">
         <v>1.31</v>
       </c>
       <c r="AN6">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="AO6">
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="AQ6">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="AR6">
-        <v>2.02</v>
+        <v>2.23</v>
       </c>
       <c r="AS6">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="AT6">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AU6">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AV6">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AW6">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AX6">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AY6">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ6">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="BA6">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="BB6">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BC6">
-        <v>2.18</v>
+        <v>2.27</v>
       </c>
       <c r="BD6">
-        <v>3.66</v>
+        <v>3.42</v>
       </c>
       <c r="BE6">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="BF6">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BG6">
         <v>0</v>
@@ -3360,7 +3360,7 @@
         <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D14" t="s">
         <v>105</v>
@@ -3438,28 +3438,28 @@
         <v>0</v>
       </c>
       <c r="AC14">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AD14">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH14">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI14">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AJ14">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK14">
         <v>0</v>
@@ -3468,10 +3468,10 @@
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN14">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AO14">
         <v>0</v>
@@ -3730,10 +3730,10 @@
         <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E16" t="s">
         <v>121</v>
@@ -3778,70 +3778,70 @@
         <v>0</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL16">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AM16">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO16">
         <v>0</v>
@@ -3883,19 +3883,19 @@
         <v>0</v>
       </c>
       <c r="BB16">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC16">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BD16">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="BE16">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF16">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG16">
         <v>0</v>
@@ -3915,10 +3915,10 @@
         <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E17" t="s">
         <v>122</v>
@@ -3963,70 +3963,70 @@
         <v>0</v>
       </c>
       <c r="S17">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="V17">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W17">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="X17">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Y17">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z17">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA17">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC17">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AD17">
-        <v>2.97</v>
+        <v>4.8</v>
       </c>
       <c r="AE17">
-        <v>2.13</v>
+        <v>1.45</v>
       </c>
       <c r="AF17">
-        <v>1.73</v>
+        <v>2.43</v>
       </c>
       <c r="AG17">
-        <v>3.72</v>
+        <v>2.14</v>
       </c>
       <c r="AH17">
-        <v>1.21</v>
+        <v>1.58</v>
       </c>
       <c r="AI17">
-        <v>7.4</v>
+        <v>3.5</v>
       </c>
       <c r="AJ17">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="AK17">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL17">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AM17">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AN17">
-        <v>1.44</v>
+        <v>1.05</v>
       </c>
       <c r="AO17">
         <v>0</v>
@@ -4068,19 +4068,19 @@
         <v>0</v>
       </c>
       <c r="BB17">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC17">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="BD17">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="BE17">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BF17">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG17">
         <v>0</v>
@@ -5804,22 +5804,22 @@
         <v>188</v>
       </c>
       <c r="P27">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="Q27">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="R27">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="S27">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="T27">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="U27">
-        <v>5.75</v>
+        <v>6.71</v>
       </c>
       <c r="V27">
         <v>0</v>
@@ -5828,10 +5828,10 @@
         <v>0</v>
       </c>
       <c r="X27">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="Y27">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -5843,28 +5843,28 @@
         <v>0</v>
       </c>
       <c r="AC27">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AD27">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AE27">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="AF27">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AG27">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="AH27">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AI27">
-        <v>3.45</v>
+        <v>3.83</v>
       </c>
       <c r="AJ27">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK27">
         <v>1.63</v>
@@ -6505,7 +6505,7 @@
         <v>80</v>
       </c>
       <c r="C31" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D31" t="s">
         <v>105</v>
@@ -6544,133 +6544,133 @@
         <v>188</v>
       </c>
       <c r="P31">
-        <v>4.4</v>
+        <v>1.95</v>
       </c>
       <c r="Q31">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="R31">
-        <v>1.8</v>
+        <v>3.79</v>
       </c>
       <c r="S31">
-        <v>5.18</v>
+        <v>2.48</v>
       </c>
       <c r="T31">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="U31">
-        <v>2.46</v>
+        <v>4.1</v>
       </c>
       <c r="V31">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="W31">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="X31">
-        <v>3.32</v>
+        <v>2.88</v>
       </c>
       <c r="Y31">
         <v>1.33</v>
       </c>
       <c r="Z31">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="AA31">
+        <v>1.03</v>
+      </c>
+      <c r="AB31">
         <v>1.02</v>
       </c>
-      <c r="AB31">
-        <v>1.04</v>
-      </c>
       <c r="AC31">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AD31">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="AE31">
+        <v>2.02</v>
+      </c>
+      <c r="AF31">
+        <v>1.68</v>
+      </c>
+      <c r="AG31">
+        <v>3.6</v>
+      </c>
+      <c r="AH31">
+        <v>1.24</v>
+      </c>
+      <c r="AI31">
+        <v>6.75</v>
+      </c>
+      <c r="AJ31">
+        <v>1.07</v>
+      </c>
+      <c r="AK31">
+        <v>1.8</v>
+      </c>
+      <c r="AL31">
+        <v>1.84</v>
+      </c>
+      <c r="AM31">
+        <v>1.27</v>
+      </c>
+      <c r="AN31">
+        <v>1.75</v>
+      </c>
+      <c r="AO31">
+        <v>0</v>
+      </c>
+      <c r="AP31">
+        <v>1.4</v>
+      </c>
+      <c r="AQ31">
+        <v>1.67</v>
+      </c>
+      <c r="AR31">
+        <v>2.1</v>
+      </c>
+      <c r="AS31">
+        <v>2.7</v>
+      </c>
+      <c r="AT31">
+        <v>3.65</v>
+      </c>
+      <c r="AU31">
+        <v>2.7</v>
+      </c>
+      <c r="AV31">
+        <v>2.04</v>
+      </c>
+      <c r="AW31">
+        <v>1.64</v>
+      </c>
+      <c r="AX31">
+        <v>1.38</v>
+      </c>
+      <c r="AY31">
+        <v>1.23</v>
+      </c>
+      <c r="AZ31">
+        <v>1.68</v>
+      </c>
+      <c r="BA31">
+        <v>2.5</v>
+      </c>
+      <c r="BB31">
+        <v>1.23</v>
+      </c>
+      <c r="BC31">
         <v>2.25</v>
       </c>
-      <c r="AF31">
-        <v>1.62</v>
-      </c>
-      <c r="AG31">
-        <v>3.8</v>
-      </c>
-      <c r="AH31">
-        <v>1.19</v>
-      </c>
-      <c r="AI31">
-        <v>7.3</v>
-      </c>
-      <c r="AJ31">
-        <v>1.03</v>
-      </c>
-      <c r="AK31">
-        <v>1.97</v>
-      </c>
-      <c r="AL31">
-        <v>1.73</v>
-      </c>
-      <c r="AM31">
-        <v>1.26</v>
-      </c>
-      <c r="AN31">
-        <v>1.14</v>
-      </c>
-      <c r="AO31">
-        <v>0</v>
-      </c>
-      <c r="AP31">
-        <v>1.28</v>
-      </c>
-      <c r="AQ31">
-        <v>1.53</v>
-      </c>
-      <c r="AR31">
-        <v>1.95</v>
-      </c>
-      <c r="AS31">
-        <v>2.52</v>
-      </c>
-      <c r="AT31">
-        <v>3.48</v>
-      </c>
-      <c r="AU31">
-        <v>3.05</v>
-      </c>
-      <c r="AV31">
-        <v>2.21</v>
-      </c>
-      <c r="AW31">
-        <v>1.73</v>
-      </c>
-      <c r="AX31">
-        <v>1.41</v>
-      </c>
-      <c r="AY31">
-        <v>1.22</v>
-      </c>
-      <c r="AZ31">
-        <v>2.48</v>
-      </c>
-      <c r="BA31">
-        <v>1.84</v>
-      </c>
-      <c r="BB31">
-        <v>1.27</v>
-      </c>
-      <c r="BC31">
-        <v>2.29</v>
-      </c>
       <c r="BD31">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="BE31">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="BF31">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="BG31">
         <v>0</v>
@@ -6690,7 +6690,7 @@
         <v>80</v>
       </c>
       <c r="C32" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D32" t="s">
         <v>105</v>
@@ -6729,133 +6729,133 @@
         <v>188</v>
       </c>
       <c r="P32">
-        <v>1.95</v>
+        <v>4.4</v>
       </c>
       <c r="Q32">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="R32">
-        <v>3.79</v>
+        <v>1.8</v>
       </c>
       <c r="S32">
-        <v>2.48</v>
+        <v>5.18</v>
       </c>
       <c r="T32">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="U32">
-        <v>4.1</v>
+        <v>2.46</v>
       </c>
       <c r="V32">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="W32">
-        <v>2.7</v>
+        <v>2.41</v>
       </c>
       <c r="X32">
-        <v>2.88</v>
+        <v>3.32</v>
       </c>
       <c r="Y32">
         <v>1.33</v>
       </c>
       <c r="Z32">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="AA32">
+        <v>1.02</v>
+      </c>
+      <c r="AB32">
+        <v>1.04</v>
+      </c>
+      <c r="AC32">
+        <v>1.35</v>
+      </c>
+      <c r="AD32">
+        <v>2.74</v>
+      </c>
+      <c r="AE32">
+        <v>2.25</v>
+      </c>
+      <c r="AF32">
+        <v>1.62</v>
+      </c>
+      <c r="AG32">
+        <v>3.8</v>
+      </c>
+      <c r="AH32">
+        <v>1.19</v>
+      </c>
+      <c r="AI32">
+        <v>7.3</v>
+      </c>
+      <c r="AJ32">
         <v>1.03</v>
       </c>
-      <c r="AB32">
-        <v>0</v>
-      </c>
-      <c r="AC32">
-        <v>1.32</v>
-      </c>
-      <c r="AD32">
-        <v>3</v>
-      </c>
-      <c r="AE32">
-        <v>2.02</v>
-      </c>
-      <c r="AF32">
-        <v>1.68</v>
-      </c>
-      <c r="AG32">
-        <v>3.6</v>
-      </c>
-      <c r="AH32">
-        <v>1.24</v>
-      </c>
-      <c r="AI32">
-        <v>6.75</v>
-      </c>
-      <c r="AJ32">
-        <v>1.07</v>
-      </c>
       <c r="AK32">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="AL32">
+        <v>1.73</v>
+      </c>
+      <c r="AM32">
+        <v>1.26</v>
+      </c>
+      <c r="AN32">
+        <v>1.14</v>
+      </c>
+      <c r="AO32">
+        <v>0</v>
+      </c>
+      <c r="AP32">
+        <v>1.28</v>
+      </c>
+      <c r="AQ32">
+        <v>1.53</v>
+      </c>
+      <c r="AR32">
+        <v>1.95</v>
+      </c>
+      <c r="AS32">
+        <v>2.52</v>
+      </c>
+      <c r="AT32">
+        <v>3.48</v>
+      </c>
+      <c r="AU32">
+        <v>3.05</v>
+      </c>
+      <c r="AV32">
+        <v>2.21</v>
+      </c>
+      <c r="AW32">
+        <v>1.73</v>
+      </c>
+      <c r="AX32">
+        <v>1.41</v>
+      </c>
+      <c r="AY32">
+        <v>1.22</v>
+      </c>
+      <c r="AZ32">
+        <v>2.48</v>
+      </c>
+      <c r="BA32">
         <v>1.84</v>
       </c>
-      <c r="AM32">
+      <c r="BB32">
         <v>1.27</v>
       </c>
-      <c r="AN32">
-        <v>1.75</v>
-      </c>
-      <c r="AO32">
-        <v>0</v>
-      </c>
-      <c r="AP32">
-        <v>1.4</v>
-      </c>
-      <c r="AQ32">
-        <v>1.67</v>
-      </c>
-      <c r="AR32">
-        <v>2.1</v>
-      </c>
-      <c r="AS32">
-        <v>2.7</v>
-      </c>
-      <c r="AT32">
-        <v>3.65</v>
-      </c>
-      <c r="AU32">
-        <v>2.7</v>
-      </c>
-      <c r="AV32">
-        <v>2.04</v>
-      </c>
-      <c r="AW32">
-        <v>1.64</v>
-      </c>
-      <c r="AX32">
-        <v>1.38</v>
-      </c>
-      <c r="AY32">
-        <v>1.23</v>
-      </c>
-      <c r="AZ32">
-        <v>1.68</v>
-      </c>
-      <c r="BA32">
-        <v>2.5</v>
-      </c>
-      <c r="BB32">
-        <v>0</v>
-      </c>
       <c r="BC32">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="BD32">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE32">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="BF32">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG32">
         <v>0</v>
@@ -6914,133 +6914,133 @@
         <v>188</v>
       </c>
       <c r="P33">
-        <v>4.75</v>
+        <v>1.42</v>
       </c>
       <c r="Q33">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="R33">
-        <v>1.72</v>
+        <v>7.4</v>
       </c>
       <c r="S33">
-        <v>6.17</v>
+        <v>2.01</v>
       </c>
       <c r="T33">
-        <v>1.87</v>
+        <v>2.09</v>
       </c>
       <c r="U33">
-        <v>2.45</v>
+        <v>7.7</v>
       </c>
       <c r="V33">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="W33">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="X33">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="Y33">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="Z33">
-        <v>9.1</v>
+        <v>7.3</v>
       </c>
       <c r="AA33">
         <v>1.03</v>
       </c>
       <c r="AB33">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AC33">
+        <v>1.37</v>
+      </c>
+      <c r="AD33">
+        <v>3.01</v>
+      </c>
+      <c r="AE33">
+        <v>2.06</v>
+      </c>
+      <c r="AF33">
+        <v>1.68</v>
+      </c>
+      <c r="AG33">
+        <v>3.75</v>
+      </c>
+      <c r="AH33">
+        <v>1.22</v>
+      </c>
+      <c r="AI33">
+        <v>6.75</v>
+      </c>
+      <c r="AJ33">
+        <v>1.04</v>
+      </c>
+      <c r="AK33">
+        <v>2.3</v>
+      </c>
+      <c r="AL33">
+        <v>1.54</v>
+      </c>
+      <c r="AM33">
+        <v>1.17</v>
+      </c>
+      <c r="AN33">
+        <v>2.57</v>
+      </c>
+      <c r="AO33">
+        <v>0</v>
+      </c>
+      <c r="AP33">
+        <v>1.3</v>
+      </c>
+      <c r="AQ33">
         <v>1.46</v>
       </c>
-      <c r="AD33">
+      <c r="AR33">
+        <v>2.13</v>
+      </c>
+      <c r="AS33">
+        <v>2.33</v>
+      </c>
+      <c r="AT33">
+        <v>2.95</v>
+      </c>
+      <c r="AU33">
+        <v>3.15</v>
+      </c>
+      <c r="AV33">
         <v>2.38</v>
       </c>
-      <c r="AE33">
-        <v>2.75</v>
-      </c>
-      <c r="AF33">
-        <v>1.47</v>
-      </c>
-      <c r="AG33">
-        <v>5.36</v>
-      </c>
-      <c r="AH33">
+      <c r="AW33">
+        <v>1.83</v>
+      </c>
+      <c r="AX33">
+        <v>1.48</v>
+      </c>
+      <c r="AY33">
+        <v>1.34</v>
+      </c>
+      <c r="AZ33">
+        <v>1.3</v>
+      </c>
+      <c r="BA33">
+        <v>4.2</v>
+      </c>
+      <c r="BB33">
+        <v>1.24</v>
+      </c>
+      <c r="BC33">
+        <v>2.24</v>
+      </c>
+      <c r="BD33">
+        <v>3.34</v>
+      </c>
+      <c r="BE33">
+        <v>1.57</v>
+      </c>
+      <c r="BF33">
         <v>1.12</v>
-      </c>
-      <c r="AI33">
-        <v>10</v>
-      </c>
-      <c r="AJ33">
-        <v>1.02</v>
-      </c>
-      <c r="AK33">
-        <v>2.28</v>
-      </c>
-      <c r="AL33">
-        <v>1.55</v>
-      </c>
-      <c r="AM33">
-        <v>1.28</v>
-      </c>
-      <c r="AN33">
-        <v>1.1</v>
-      </c>
-      <c r="AO33">
-        <v>0</v>
-      </c>
-      <c r="AP33">
-        <v>1.36</v>
-      </c>
-      <c r="AQ33">
-        <v>1.69</v>
-      </c>
-      <c r="AR33">
-        <v>2.14</v>
-      </c>
-      <c r="AS33">
-        <v>2.88</v>
-      </c>
-      <c r="AT33">
-        <v>3.7</v>
-      </c>
-      <c r="AU33">
-        <v>2.7</v>
-      </c>
-      <c r="AV33">
-        <v>2</v>
-      </c>
-      <c r="AW33">
-        <v>1.57</v>
-      </c>
-      <c r="AX33">
-        <v>1.32</v>
-      </c>
-      <c r="AY33">
-        <v>1.23</v>
-      </c>
-      <c r="AZ33">
-        <v>2.43</v>
-      </c>
-      <c r="BA33">
-        <v>1.89</v>
-      </c>
-      <c r="BB33">
-        <v>1.33</v>
-      </c>
-      <c r="BC33">
-        <v>2.59</v>
-      </c>
-      <c r="BD33">
-        <v>2.91</v>
-      </c>
-      <c r="BE33">
-        <v>1.41</v>
-      </c>
-      <c r="BF33">
-        <v>1.06</v>
       </c>
       <c r="BG33">
         <v>0</v>
@@ -7060,10 +7060,10 @@
         <v>80</v>
       </c>
       <c r="C34" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D34" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E34" t="s">
         <v>139</v>
@@ -7099,133 +7099,133 @@
         <v>188</v>
       </c>
       <c r="P34">
-        <v>1.42</v>
+        <v>2.5</v>
       </c>
       <c r="Q34">
-        <v>3.85</v>
+        <v>3.52</v>
       </c>
       <c r="R34">
-        <v>7.4</v>
+        <v>2.53</v>
       </c>
       <c r="S34">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="T34">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U34">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="V34">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W34">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X34">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="Y34">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z34">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA34">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB34">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC34">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AD34">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="AE34">
-        <v>2.06</v>
+        <v>1.66</v>
       </c>
       <c r="AF34">
-        <v>1.68</v>
+        <v>2.15</v>
       </c>
       <c r="AG34">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AH34">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI34">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AJ34">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK34">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL34">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AM34">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN34">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AO34">
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ34">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR34">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AS34">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AT34">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AU34">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AV34">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AW34">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AX34">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AY34">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ34">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BA34">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BB34">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC34">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BD34">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="BE34">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF34">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG34">
         <v>0</v>
@@ -7245,10 +7245,10 @@
         <v>80</v>
       </c>
       <c r="C35" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D35" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E35" t="s">
         <v>140</v>
@@ -7284,133 +7284,133 @@
         <v>188</v>
       </c>
       <c r="P35">
-        <v>2.5</v>
+        <v>4.75</v>
       </c>
       <c r="Q35">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="R35">
-        <v>2.53</v>
+        <v>1.72</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AE35">
-        <v>1.66</v>
+        <v>2.75</v>
       </c>
       <c r="AF35">
-        <v>2.15</v>
+        <v>1.47</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="AH35">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI35">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AL35">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AM35">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN35">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AO35">
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ35">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR35">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS35">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AT35">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AU35">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW35">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AX35">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY35">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ35">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BA35">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BB35">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC35">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="BD35">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="BE35">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BF35">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG35">
         <v>0</v>
@@ -7469,133 +7469,133 @@
         <v>188</v>
       </c>
       <c r="P36">
-        <v>3.3</v>
+        <v>2.07</v>
       </c>
       <c r="Q36">
+        <v>2.79</v>
+      </c>
+      <c r="R36">
+        <v>4.05</v>
+      </c>
+      <c r="S36">
+        <v>2.88</v>
+      </c>
+      <c r="T36">
+        <v>1.75</v>
+      </c>
+      <c r="U36">
+        <v>5.37</v>
+      </c>
+      <c r="V36">
+        <v>1.64</v>
+      </c>
+      <c r="W36">
+        <v>2.11</v>
+      </c>
+      <c r="X36">
+        <v>3.55</v>
+      </c>
+      <c r="Y36">
+        <v>1.24</v>
+      </c>
+      <c r="Z36">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AA36">
+        <v>1.02</v>
+      </c>
+      <c r="AB36">
+        <v>1.08</v>
+      </c>
+      <c r="AC36">
+        <v>1.61</v>
+      </c>
+      <c r="AD36">
+        <v>2.23</v>
+      </c>
+      <c r="AE36">
+        <v>2.74</v>
+      </c>
+      <c r="AF36">
+        <v>1.4</v>
+      </c>
+      <c r="AG36">
+        <v>6.25</v>
+      </c>
+      <c r="AH36">
+        <v>1.07</v>
+      </c>
+      <c r="AI36">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AJ36">
+        <v>1.01</v>
+      </c>
+      <c r="AK36">
+        <v>2.32</v>
+      </c>
+      <c r="AL36">
+        <v>1.58</v>
+      </c>
+      <c r="AM36">
+        <v>1.35</v>
+      </c>
+      <c r="AN36">
+        <v>1.63</v>
+      </c>
+      <c r="AO36">
+        <v>0</v>
+      </c>
+      <c r="AP36">
+        <v>1.42</v>
+      </c>
+      <c r="AQ36">
+        <v>1.76</v>
+      </c>
+      <c r="AR36">
+        <v>2.7</v>
+      </c>
+      <c r="AS36">
         <v>3</v>
       </c>
-      <c r="R36">
-        <v>2.15</v>
-      </c>
-      <c r="S36">
-        <v>4.43</v>
-      </c>
-      <c r="T36">
-        <v>1.88</v>
-      </c>
-      <c r="U36">
-        <v>2.88</v>
-      </c>
-      <c r="V36">
-        <v>1.51</v>
-      </c>
-      <c r="W36">
-        <v>2.31</v>
-      </c>
-      <c r="X36">
-        <v>3.38</v>
-      </c>
-      <c r="Y36">
-        <v>1.25</v>
-      </c>
-      <c r="Z36">
-        <v>9.1</v>
-      </c>
-      <c r="AA36">
-        <v>1</v>
-      </c>
-      <c r="AB36">
-        <v>1.05</v>
-      </c>
-      <c r="AC36">
-        <v>1.53</v>
-      </c>
-      <c r="AD36">
-        <v>2.46</v>
-      </c>
-      <c r="AE36">
-        <v>2.65</v>
-      </c>
-      <c r="AF36">
-        <v>1.41</v>
-      </c>
-      <c r="AG36">
-        <v>5.1</v>
-      </c>
-      <c r="AH36">
+      <c r="AT36">
+        <v>4.34</v>
+      </c>
+      <c r="AU36">
+        <v>2.58</v>
+      </c>
+      <c r="AV36">
+        <v>1.95</v>
+      </c>
+      <c r="AW36">
+        <v>1.57</v>
+      </c>
+      <c r="AX36">
+        <v>1.3</v>
+      </c>
+      <c r="AY36">
         <v>1.13</v>
       </c>
-      <c r="AI36">
-        <v>8.5</v>
-      </c>
-      <c r="AJ36">
+      <c r="AZ36">
+        <v>1.54</v>
+      </c>
+      <c r="BA36">
+        <v>3.42</v>
+      </c>
+      <c r="BB36">
+        <v>1.39</v>
+      </c>
+      <c r="BC36">
+        <v>2.9</v>
+      </c>
+      <c r="BD36">
+        <v>2.66</v>
+      </c>
+      <c r="BE36">
+        <v>1.38</v>
+      </c>
+      <c r="BF36">
         <v>1.03</v>
-      </c>
-      <c r="AK36">
-        <v>2.04</v>
-      </c>
-      <c r="AL36">
-        <v>1.68</v>
-      </c>
-      <c r="AM36">
-        <v>1.57</v>
-      </c>
-      <c r="AN36">
-        <v>1.29</v>
-      </c>
-      <c r="AO36">
-        <v>0</v>
-      </c>
-      <c r="AP36">
-        <v>1.39</v>
-      </c>
-      <c r="AQ36">
-        <v>1.72</v>
-      </c>
-      <c r="AR36">
-        <v>2.6</v>
-      </c>
-      <c r="AS36">
-        <v>2.9</v>
-      </c>
-      <c r="AT36">
-        <v>4.15</v>
-      </c>
-      <c r="AU36">
-        <v>2.66</v>
-      </c>
-      <c r="AV36">
-        <v>2</v>
-      </c>
-      <c r="AW36">
-        <v>1.6</v>
-      </c>
-      <c r="AX36">
-        <v>1.32</v>
-      </c>
-      <c r="AY36">
-        <v>1.15</v>
-      </c>
-      <c r="AZ36">
-        <v>2.12</v>
-      </c>
-      <c r="BA36">
-        <v>2.12</v>
-      </c>
-      <c r="BB36">
-        <v>1.32</v>
-      </c>
-      <c r="BC36">
-        <v>2.59</v>
-      </c>
-      <c r="BD36">
-        <v>2.96</v>
-      </c>
-      <c r="BE36">
-        <v>1.41</v>
-      </c>
-      <c r="BF36">
-        <v>1.06</v>
       </c>
       <c r="BG36">
         <v>0</v>
@@ -7654,133 +7654,133 @@
         <v>188</v>
       </c>
       <c r="P37">
-        <v>2.07</v>
+        <v>3.3</v>
       </c>
       <c r="Q37">
-        <v>2.79</v>
+        <v>3</v>
       </c>
       <c r="R37">
-        <v>4.05</v>
+        <v>2.15</v>
       </c>
       <c r="S37">
+        <v>4.43</v>
+      </c>
+      <c r="T37">
+        <v>1.88</v>
+      </c>
+      <c r="U37">
         <v>2.88</v>
       </c>
-      <c r="T37">
-        <v>1.75</v>
-      </c>
-      <c r="U37">
-        <v>5.37</v>
-      </c>
       <c r="V37">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="W37">
-        <v>2.11</v>
+        <v>2.31</v>
       </c>
       <c r="X37">
-        <v>3.55</v>
+        <v>3.38</v>
       </c>
       <c r="Y37">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z37">
-        <v>8.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="AA37">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AB37">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AC37">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AD37">
-        <v>2.23</v>
+        <v>2.46</v>
       </c>
       <c r="AE37">
-        <v>2.74</v>
+        <v>2.65</v>
       </c>
       <c r="AF37">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AG37">
-        <v>6.25</v>
+        <v>5.1</v>
       </c>
       <c r="AH37">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AI37">
-        <v>9.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="AJ37">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AK37">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="AL37">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AM37">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="AN37">
-        <v>1.63</v>
+        <v>1.29</v>
       </c>
       <c r="AO37">
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AQ37">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AR37">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AS37">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AT37">
-        <v>4.34</v>
+        <v>4.15</v>
       </c>
       <c r="AU37">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="AV37">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AW37">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AX37">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AY37">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AZ37">
-        <v>1.54</v>
+        <v>2.12</v>
       </c>
       <c r="BA37">
-        <v>3.42</v>
+        <v>2.12</v>
       </c>
       <c r="BB37">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="BC37">
-        <v>2.9</v>
+        <v>2.59</v>
       </c>
       <c r="BD37">
-        <v>2.66</v>
+        <v>2.96</v>
       </c>
       <c r="BE37">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BF37">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BG37">
         <v>0</v>
@@ -7839,133 +7839,133 @@
         <v>188</v>
       </c>
       <c r="P38">
-        <v>2.2</v>
+        <v>4.65</v>
       </c>
       <c r="Q38">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="R38">
-        <v>3.37</v>
+        <v>1.62</v>
       </c>
       <c r="S38">
-        <v>3.01</v>
+        <v>6.93</v>
       </c>
       <c r="T38">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="U38">
-        <v>4.53</v>
+        <v>2.3</v>
       </c>
       <c r="V38">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="W38">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="X38">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="Y38">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z38">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA38">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AB38">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AC38">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AD38">
-        <v>2.09</v>
+        <v>2.35</v>
       </c>
       <c r="AE38">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="AF38">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="AG38">
-        <v>6.35</v>
+        <v>4.9</v>
       </c>
       <c r="AH38">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AI38">
-        <v>10.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ38">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AK38">
         <v>2.4</v>
       </c>
       <c r="AL38">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AM38">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AN38">
-        <v>1.54</v>
+        <v>1.07</v>
       </c>
       <c r="AO38">
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AQ38">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AR38">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="AS38">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="AT38">
-        <v>4.36</v>
+        <v>4.41</v>
       </c>
       <c r="AU38">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="AV38">
         <v>1.99</v>
       </c>
       <c r="AW38">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AX38">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AY38">
         <v>1.13</v>
       </c>
       <c r="AZ38">
-        <v>1.96</v>
+        <v>4.1</v>
       </c>
       <c r="BA38">
-        <v>2.39</v>
+        <v>1.42</v>
       </c>
       <c r="BB38">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="BC38">
-        <v>3.12</v>
+        <v>2.66</v>
       </c>
       <c r="BD38">
-        <v>2.53</v>
+        <v>2.82</v>
       </c>
       <c r="BE38">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="BF38">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="BG38">
         <v>0</v>
@@ -8024,133 +8024,133 @@
         <v>188</v>
       </c>
       <c r="P39">
-        <v>4.65</v>
+        <v>2.2</v>
       </c>
       <c r="Q39">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="R39">
-        <v>1.62</v>
+        <v>3.37</v>
       </c>
       <c r="S39">
-        <v>6.93</v>
+        <v>3.01</v>
       </c>
       <c r="T39">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="U39">
-        <v>2.3</v>
+        <v>4.53</v>
       </c>
       <c r="V39">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="W39">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="X39">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="Y39">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z39">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA39">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB39">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AC39">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AD39">
-        <v>2.35</v>
+        <v>2.09</v>
       </c>
       <c r="AE39">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="AF39">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="AG39">
-        <v>4.9</v>
+        <v>6.35</v>
       </c>
       <c r="AH39">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AI39">
-        <v>8.300000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AJ39">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AK39">
         <v>2.4</v>
       </c>
       <c r="AL39">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AM39">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AN39">
-        <v>1.07</v>
+        <v>1.54</v>
       </c>
       <c r="AO39">
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AQ39">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AR39">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="AS39">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="AT39">
-        <v>4.41</v>
+        <v>4.36</v>
       </c>
       <c r="AU39">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="AV39">
         <v>1.99</v>
       </c>
       <c r="AW39">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AX39">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AY39">
         <v>1.13</v>
       </c>
       <c r="AZ39">
-        <v>4.1</v>
+        <v>1.96</v>
       </c>
       <c r="BA39">
-        <v>1.42</v>
+        <v>2.39</v>
       </c>
       <c r="BB39">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="BC39">
-        <v>2.66</v>
+        <v>3.12</v>
       </c>
       <c r="BD39">
-        <v>2.82</v>
+        <v>2.53</v>
       </c>
       <c r="BE39">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="BF39">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="BG39">
         <v>0</v>
@@ -8209,13 +8209,13 @@
         <v>188</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S40">
         <v>0</v>
@@ -8397,28 +8397,28 @@
         <v>1.65</v>
       </c>
       <c r="Q41">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="R41">
         <v>4.7</v>
       </c>
       <c r="S41">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="T41">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="U41">
-        <v>5.65</v>
+        <v>5.7</v>
       </c>
       <c r="V41">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W41">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="X41">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="Y41">
         <v>1.43</v>
@@ -8427,7 +8427,7 @@
         <v>7</v>
       </c>
       <c r="AA41">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AB41">
         <v>1.01</v>
@@ -8439,7 +8439,7 @@
         <v>3.4</v>
       </c>
       <c r="AE41">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AF41">
         <v>1.96</v>
@@ -8466,7 +8466,7 @@
         <v>1.28</v>
       </c>
       <c r="AN41">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="AO41">
         <v>0</v>
@@ -8493,7 +8493,7 @@
         <v>2.6</v>
       </c>
       <c r="AW41">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AX41">
         <v>1.64</v>
@@ -8502,10 +8502,10 @@
         <v>1.41</v>
       </c>
       <c r="AZ41">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="BA41">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BB41">
         <v>1.23</v>

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -337,54 +337,54 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Bucheon 1995</t>
+  </si>
+  <si>
     <t>Jeonbuk Motors</t>
   </si>
   <si>
-    <t>Bucheon 1995</t>
+    <t>Sangju Sangmu</t>
   </si>
   <si>
     <t>Gangwon</t>
   </si>
   <si>
-    <t>Sangju Sangmu</t>
-  </si>
-  <si>
     <t>Daejeon Citizen</t>
   </si>
   <si>
     <t>Madura United</t>
   </si>
   <si>
+    <t>FC Seoul</t>
+  </si>
+  <si>
     <t>Ethiopia Nigd Bank</t>
   </si>
   <si>
-    <t>FC Seoul</t>
-  </si>
-  <si>
     <t>Qingdao Youth Island</t>
   </si>
   <si>
     <t>Tanjong Pagar</t>
   </si>
   <si>
+    <t>Shenyang Urban</t>
+  </si>
+  <si>
     <t>Shandong Luneng</t>
   </si>
   <si>
-    <t>Shenyang Urban</t>
+    <t>Borneo</t>
+  </si>
+  <si>
+    <t>Karvan FK</t>
   </si>
   <si>
     <t>Dire Dawa Kenema</t>
   </si>
   <si>
-    <t>Borneo</t>
-  </si>
-  <si>
     <t>Chongqing Tongliang Long</t>
   </si>
   <si>
-    <t>Karvan FK</t>
-  </si>
-  <si>
     <t>Mekelle Kenema</t>
   </si>
   <si>
@@ -415,42 +415,42 @@
     <t>Maccabi Tel Aviv</t>
   </si>
   <si>
+    <t>Dibba Al Fujairah</t>
+  </si>
+  <si>
     <t>Bani Yas</t>
   </si>
   <si>
-    <t>Dibba Al Fujairah</t>
-  </si>
-  <si>
     <t>Al Ittihad Kalba</t>
   </si>
   <si>
+    <t>Al Ahly</t>
+  </si>
+  <si>
     <t>Lokomotiv Sofia 1929</t>
   </si>
   <si>
     <t>Ceramica Cleopatra</t>
   </si>
   <si>
-    <t>Al Ahly</t>
+    <t>Smouha SC</t>
   </si>
   <si>
     <t>Falkenberg</t>
   </si>
   <si>
-    <t>Smouha SC</t>
-  </si>
-  <si>
     <t>Magesi</t>
   </si>
   <si>
+    <t>Siwelele</t>
+  </si>
+  <si>
     <t>Chippa United</t>
   </si>
   <si>
     <t>Stellenbosch</t>
   </si>
   <si>
-    <t>Siwelele</t>
-  </si>
-  <si>
     <t>Al Khaleej</t>
   </si>
   <si>
@@ -460,54 +460,54 @@
     <t>New York City II</t>
   </si>
   <si>
+    <t>Jeju United</t>
+  </si>
+  <si>
     <t>Gwangju</t>
   </si>
   <si>
-    <t>Jeju United</t>
+    <t>Ulsan</t>
   </si>
   <si>
     <t>Pohang Steelers</t>
   </si>
   <si>
-    <t>Ulsan</t>
-  </si>
-  <si>
     <t>Incheon United</t>
   </si>
   <si>
     <t>Bali United</t>
   </si>
   <si>
+    <t>Anyang</t>
+  </si>
+  <si>
     <t>Kedus Giorgis</t>
   </si>
   <si>
-    <t>Anyang</t>
-  </si>
-  <si>
     <t>Tianjin Teda</t>
   </si>
   <si>
     <t>Hougang United</t>
   </si>
   <si>
+    <t>Chengdu Better City FC</t>
+  </si>
+  <si>
     <t>Shanghai Shenhua</t>
   </si>
   <si>
-    <t>Chengdu Better City FC</t>
+    <t>Persita</t>
+  </si>
+  <si>
+    <t>Neftçi</t>
   </si>
   <si>
     <t>Ethiopia Bunna</t>
   </si>
   <si>
-    <t>Persita</t>
-  </si>
-  <si>
     <t>Henan Jianye</t>
   </si>
   <si>
-    <t>Neftçi</t>
-  </si>
-  <si>
     <t>Arba Minch Kenema</t>
   </si>
   <si>
@@ -538,10 +538,13 @@
     <t>Hapoel Petah Tikva</t>
   </si>
   <si>
+    <t>Al Bataeh</t>
+  </si>
+  <si>
     <t>Al Dhafra</t>
   </si>
   <si>
-    <t>Al Bataeh</t>
+    <t>ENPPI</t>
   </si>
   <si>
     <t>Botev Vratsa</t>
@@ -550,25 +553,22 @@
     <t>Pyramids FC</t>
   </si>
   <si>
-    <t>ENPPI</t>
+    <t>Zamalek</t>
   </si>
   <si>
     <t>Norrköping</t>
   </si>
   <si>
-    <t>Zamalek</t>
-  </si>
-  <si>
     <t>Orbit College</t>
   </si>
   <si>
+    <t>Durban City</t>
+  </si>
+  <si>
     <t>Sekhukhune United</t>
   </si>
   <si>
     <t>Orlando Pirates</t>
-  </si>
-  <si>
-    <t>Durban City</t>
   </si>
   <si>
     <t>Al Hilal</t>
@@ -1179,133 +1179,133 @@
         <v>188</v>
       </c>
       <c r="P2">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="Q2">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="R2">
-        <v>6.5</v>
+        <v>2.87</v>
       </c>
       <c r="S2">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>7.95</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W2">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="X2">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Y2">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z2">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC2">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AE2">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AH2">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK2">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AL2">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN2">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AO2">
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AQ2">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AR2">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="AS2">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AT2">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="AU2">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AV2">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AW2">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AX2">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AY2">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AZ2">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BA2">
-        <v>5.49</v>
+        <v>0</v>
       </c>
       <c r="BB2">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC2">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="BD2">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="BE2">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF2">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG2">
         <v>0</v>
@@ -1364,133 +1364,133 @@
         <v>188</v>
       </c>
       <c r="P3">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q3">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="R3">
-        <v>2.87</v>
+        <v>6.5</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>7.95</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AO3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="AU3">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AV3">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AW3">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AX3">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AY3">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AZ3">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BA3">
-        <v>0</v>
+        <v>5.49</v>
       </c>
       <c r="BB3">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC3">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BD3">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="BE3">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF3">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG3">
         <v>0</v>
@@ -1549,133 +1549,133 @@
         <v>188</v>
       </c>
       <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>3.25</v>
+      </c>
+      <c r="T4">
+        <v>2.01</v>
+      </c>
+      <c r="U4">
+        <v>2.88</v>
+      </c>
+      <c r="V4">
+        <v>1.33</v>
+      </c>
+      <c r="W4">
+        <v>2.77</v>
+      </c>
+      <c r="X4">
+        <v>2.65</v>
+      </c>
+      <c r="Y4">
+        <v>1.36</v>
+      </c>
+      <c r="Z4">
+        <v>7.5</v>
+      </c>
+      <c r="AA4">
+        <v>1.03</v>
+      </c>
+      <c r="AB4">
+        <v>1.02</v>
+      </c>
+      <c r="AC4">
+        <v>1.32</v>
+      </c>
+      <c r="AD4">
+        <v>3.37</v>
+      </c>
+      <c r="AE4">
+        <v>2.01</v>
+      </c>
+      <c r="AF4">
+        <v>1.8</v>
+      </c>
+      <c r="AG4">
+        <v>3.38</v>
+      </c>
+      <c r="AH4">
+        <v>1.24</v>
+      </c>
+      <c r="AI4">
+        <v>6.75</v>
+      </c>
+      <c r="AJ4">
+        <v>1.04</v>
+      </c>
+      <c r="AK4">
+        <v>1.73</v>
+      </c>
+      <c r="AL4">
         <v>2</v>
       </c>
-      <c r="Q4">
-        <v>3.2</v>
-      </c>
-      <c r="R4">
-        <v>3.6</v>
-      </c>
-      <c r="S4">
-        <v>2.77</v>
-      </c>
-      <c r="T4">
-        <v>1.91</v>
-      </c>
-      <c r="U4">
-        <v>4.76</v>
-      </c>
-      <c r="V4">
-        <v>1.53</v>
-      </c>
-      <c r="W4">
-        <v>2.34</v>
-      </c>
-      <c r="X4">
-        <v>3.25</v>
-      </c>
-      <c r="Y4">
-        <v>1.27</v>
-      </c>
-      <c r="Z4">
-        <v>8.5</v>
-      </c>
-      <c r="AA4">
-        <v>1.01</v>
-      </c>
-      <c r="AB4">
-        <v>1.05</v>
-      </c>
-      <c r="AC4">
+      <c r="AM4">
+        <v>1.31</v>
+      </c>
+      <c r="AN4">
+        <v>1.46</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>1.37</v>
+      </c>
+      <c r="AQ4">
+        <v>1.64</v>
+      </c>
+      <c r="AR4">
+        <v>2.02</v>
+      </c>
+      <c r="AS4">
+        <v>2.6</v>
+      </c>
+      <c r="AT4">
+        <v>3.45</v>
+      </c>
+      <c r="AU4">
+        <v>2.8</v>
+      </c>
+      <c r="AV4">
+        <v>2.1</v>
+      </c>
+      <c r="AW4">
+        <v>1.68</v>
+      </c>
+      <c r="AX4">
         <v>1.42</v>
       </c>
-      <c r="AD4">
-        <v>2.51</v>
-      </c>
-      <c r="AE4">
-        <v>2.42</v>
-      </c>
-      <c r="AF4">
-        <v>1.54</v>
-      </c>
-      <c r="AG4">
-        <v>4.33</v>
-      </c>
-      <c r="AH4">
-        <v>1.15</v>
-      </c>
-      <c r="AI4">
-        <v>8.5</v>
-      </c>
-      <c r="AJ4">
-        <v>1.01</v>
-      </c>
-      <c r="AK4">
-        <v>2.05</v>
-      </c>
-      <c r="AL4">
-        <v>1.69</v>
-      </c>
-      <c r="AM4">
-        <v>1.33</v>
-      </c>
-      <c r="AN4">
-        <v>1.71</v>
-      </c>
-      <c r="AO4">
-        <v>0</v>
-      </c>
-      <c r="AP4">
-        <v>1.5</v>
-      </c>
-      <c r="AQ4">
-        <v>1.84</v>
-      </c>
-      <c r="AR4">
-        <v>2.35</v>
-      </c>
-      <c r="AS4">
-        <v>3.1</v>
-      </c>
-      <c r="AT4">
-        <v>0</v>
-      </c>
-      <c r="AU4">
-        <v>2.38</v>
-      </c>
-      <c r="AV4">
-        <v>1.84</v>
-      </c>
-      <c r="AW4">
-        <v>1.5</v>
-      </c>
-      <c r="AX4">
-        <v>1.3</v>
-      </c>
       <c r="AY4">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ4">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="BA4">
-        <v>2.43</v>
+        <v>2.17</v>
       </c>
       <c r="BB4">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="BC4">
-        <v>2.53</v>
+        <v>2.18</v>
       </c>
       <c r="BD4">
-        <v>3.04</v>
+        <v>3.66</v>
       </c>
       <c r="BE4">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="BF4">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="BG4">
         <v>0</v>
@@ -1734,133 +1734,133 @@
         <v>188</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S5">
+        <v>2.77</v>
+      </c>
+      <c r="T5">
+        <v>1.91</v>
+      </c>
+      <c r="U5">
+        <v>4.76</v>
+      </c>
+      <c r="V5">
+        <v>1.53</v>
+      </c>
+      <c r="W5">
+        <v>2.34</v>
+      </c>
+      <c r="X5">
         <v>3.25</v>
       </c>
-      <c r="T5">
-        <v>2.01</v>
-      </c>
-      <c r="U5">
-        <v>2.88</v>
-      </c>
-      <c r="V5">
+      <c r="Y5">
+        <v>1.27</v>
+      </c>
+      <c r="Z5">
+        <v>8.5</v>
+      </c>
+      <c r="AA5">
+        <v>1.01</v>
+      </c>
+      <c r="AB5">
+        <v>1.05</v>
+      </c>
+      <c r="AC5">
+        <v>1.42</v>
+      </c>
+      <c r="AD5">
+        <v>2.51</v>
+      </c>
+      <c r="AE5">
+        <v>2.42</v>
+      </c>
+      <c r="AF5">
+        <v>1.54</v>
+      </c>
+      <c r="AG5">
+        <v>4.33</v>
+      </c>
+      <c r="AH5">
+        <v>1.15</v>
+      </c>
+      <c r="AI5">
+        <v>8.5</v>
+      </c>
+      <c r="AJ5">
+        <v>1.01</v>
+      </c>
+      <c r="AK5">
+        <v>2.05</v>
+      </c>
+      <c r="AL5">
+        <v>1.69</v>
+      </c>
+      <c r="AM5">
         <v>1.33</v>
       </c>
-      <c r="W5">
-        <v>2.77</v>
-      </c>
-      <c r="X5">
-        <v>2.65</v>
-      </c>
-      <c r="Y5">
-        <v>1.36</v>
-      </c>
-      <c r="Z5">
-        <v>7.5</v>
-      </c>
-      <c r="AA5">
-        <v>1.03</v>
-      </c>
-      <c r="AB5">
-        <v>1.02</v>
-      </c>
-      <c r="AC5">
-        <v>1.32</v>
-      </c>
-      <c r="AD5">
-        <v>3.37</v>
-      </c>
-      <c r="AE5">
-        <v>2.01</v>
-      </c>
-      <c r="AF5">
-        <v>1.8</v>
-      </c>
-      <c r="AG5">
-        <v>3.38</v>
-      </c>
-      <c r="AH5">
-        <v>1.24</v>
-      </c>
-      <c r="AI5">
-        <v>6.75</v>
-      </c>
-      <c r="AJ5">
-        <v>1.04</v>
-      </c>
-      <c r="AK5">
-        <v>1.73</v>
-      </c>
-      <c r="AL5">
-        <v>2</v>
-      </c>
-      <c r="AM5">
-        <v>1.31</v>
-      </c>
       <c r="AN5">
+        <v>1.71</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>1.5</v>
+      </c>
+      <c r="AQ5">
+        <v>1.84</v>
+      </c>
+      <c r="AR5">
+        <v>2.35</v>
+      </c>
+      <c r="AS5">
+        <v>3.1</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>2.38</v>
+      </c>
+      <c r="AV5">
+        <v>1.84</v>
+      </c>
+      <c r="AW5">
+        <v>1.5</v>
+      </c>
+      <c r="AX5">
+        <v>1.3</v>
+      </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <v>1.65</v>
+      </c>
+      <c r="BA5">
+        <v>2.43</v>
+      </c>
+      <c r="BB5">
+        <v>1.33</v>
+      </c>
+      <c r="BC5">
+        <v>2.53</v>
+      </c>
+      <c r="BD5">
+        <v>3.04</v>
+      </c>
+      <c r="BE5">
         <v>1.46</v>
       </c>
-      <c r="AO5">
-        <v>0</v>
-      </c>
-      <c r="AP5">
-        <v>1.37</v>
-      </c>
-      <c r="AQ5">
-        <v>1.64</v>
-      </c>
-      <c r="AR5">
-        <v>2.02</v>
-      </c>
-      <c r="AS5">
-        <v>2.6</v>
-      </c>
-      <c r="AT5">
-        <v>3.45</v>
-      </c>
-      <c r="AU5">
-        <v>2.8</v>
-      </c>
-      <c r="AV5">
-        <v>2.1</v>
-      </c>
-      <c r="AW5">
-        <v>1.68</v>
-      </c>
-      <c r="AX5">
-        <v>1.42</v>
-      </c>
-      <c r="AY5">
-        <v>1.26</v>
-      </c>
-      <c r="AZ5">
-        <v>1.81</v>
-      </c>
-      <c r="BA5">
-        <v>2.17</v>
-      </c>
-      <c r="BB5">
-        <v>1.22</v>
-      </c>
-      <c r="BC5">
-        <v>2.18</v>
-      </c>
-      <c r="BD5">
-        <v>3.66</v>
-      </c>
-      <c r="BE5">
-        <v>1.64</v>
-      </c>
       <c r="BF5">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="BG5">
         <v>0</v>
@@ -2250,10 +2250,10 @@
         <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E8" t="s">
         <v>113</v>
@@ -2289,133 +2289,133 @@
         <v>188</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AO8">
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG8">
         <v>0</v>
@@ -2435,10 +2435,10 @@
         <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E9" t="s">
         <v>114</v>
@@ -2474,133 +2474,133 @@
         <v>188</v>
       </c>
       <c r="P9">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>5.42</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z9">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC9">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD9">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AH9">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI9">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AJ9">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK9">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AL9">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AM9">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN9">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AO9">
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ9">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR9">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AS9">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT9">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AU9">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AV9">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AW9">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AX9">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY9">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ9">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BA9">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BB9">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC9">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="BD9">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE9">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="BF9">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG9">
         <v>0</v>
@@ -3029,133 +3029,133 @@
         <v>188</v>
       </c>
       <c r="P12">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>3.13</v>
+        <v>5.1</v>
       </c>
       <c r="T12">
-        <v>2.59</v>
+        <v>2.23</v>
       </c>
       <c r="U12">
-        <v>2.81</v>
+        <v>2.14</v>
       </c>
       <c r="V12">
+        <v>1.35</v>
+      </c>
+      <c r="W12">
+        <v>3.14</v>
+      </c>
+      <c r="X12">
+        <v>2.62</v>
+      </c>
+      <c r="Y12">
+        <v>1.42</v>
+      </c>
+      <c r="Z12">
+        <v>6.2</v>
+      </c>
+      <c r="AA12">
+        <v>1.06</v>
+      </c>
+      <c r="AB12">
+        <v>1</v>
+      </c>
+      <c r="AC12">
         <v>1.22</v>
       </c>
-      <c r="W12">
-        <v>3.6</v>
-      </c>
-      <c r="X12">
-        <v>2.1</v>
-      </c>
-      <c r="Y12">
+      <c r="AD12">
+        <v>3.5</v>
+      </c>
+      <c r="AE12">
+        <v>1.85</v>
+      </c>
+      <c r="AF12">
+        <v>1.97</v>
+      </c>
+      <c r="AG12">
+        <v>3.01</v>
+      </c>
+      <c r="AH12">
+        <v>1.31</v>
+      </c>
+      <c r="AI12">
+        <v>5.5</v>
+      </c>
+      <c r="AJ12">
+        <v>1.08</v>
+      </c>
+      <c r="AK12">
+        <v>1.85</v>
+      </c>
+      <c r="AL12">
+        <v>1.85</v>
+      </c>
+      <c r="AM12">
+        <v>1.24</v>
+      </c>
+      <c r="AN12">
+        <v>1.16</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>0</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>0</v>
+      </c>
+      <c r="AV12">
+        <v>0</v>
+      </c>
+      <c r="AW12">
+        <v>0</v>
+      </c>
+      <c r="AX12">
+        <v>0</v>
+      </c>
+      <c r="AY12">
+        <v>0</v>
+      </c>
+      <c r="AZ12">
+        <v>0</v>
+      </c>
+      <c r="BA12">
+        <v>0</v>
+      </c>
+      <c r="BB12">
+        <v>1.19</v>
+      </c>
+      <c r="BC12">
+        <v>2.05</v>
+      </c>
+      <c r="BD12">
+        <v>3.9</v>
+      </c>
+      <c r="BE12">
         <v>1.71</v>
       </c>
-      <c r="Z12">
-        <v>4.45</v>
-      </c>
-      <c r="AA12">
-        <v>1.15</v>
-      </c>
-      <c r="AB12">
-        <v>1.02</v>
-      </c>
-      <c r="AC12">
-        <v>1.13</v>
-      </c>
-      <c r="AD12">
-        <v>5.81</v>
-      </c>
-      <c r="AE12">
-        <v>1.39</v>
-      </c>
-      <c r="AF12">
-        <v>2.59</v>
-      </c>
-      <c r="AG12">
-        <v>2.09</v>
-      </c>
-      <c r="AH12">
-        <v>1.76</v>
-      </c>
-      <c r="AI12">
-        <v>3.28</v>
-      </c>
-      <c r="AJ12">
-        <v>1.25</v>
-      </c>
-      <c r="AK12">
-        <v>1.36</v>
-      </c>
-      <c r="AL12">
-        <v>2.84</v>
-      </c>
-      <c r="AM12">
-        <v>1.28</v>
-      </c>
-      <c r="AN12">
-        <v>1.44</v>
-      </c>
-      <c r="AO12">
-        <v>0</v>
-      </c>
-      <c r="AP12">
-        <v>1.12</v>
-      </c>
-      <c r="AQ12">
-        <v>1.26</v>
-      </c>
-      <c r="AR12">
-        <v>1.66</v>
-      </c>
-      <c r="AS12">
-        <v>1.86</v>
-      </c>
-      <c r="AT12">
-        <v>2.29</v>
-      </c>
-      <c r="AU12">
-        <v>4.8</v>
-      </c>
-      <c r="AV12">
-        <v>3.2</v>
-      </c>
-      <c r="AW12">
-        <v>2.32</v>
-      </c>
-      <c r="AX12">
-        <v>1.84</v>
-      </c>
-      <c r="AY12">
-        <v>1.57</v>
-      </c>
-      <c r="AZ12">
-        <v>1.84</v>
-      </c>
-      <c r="BA12">
-        <v>2.21</v>
-      </c>
-      <c r="BB12">
-        <v>1.12</v>
-      </c>
-      <c r="BC12">
-        <v>1.62</v>
-      </c>
-      <c r="BD12">
-        <v>5.3</v>
-      </c>
-      <c r="BE12">
-        <v>2.15</v>
-      </c>
       <c r="BF12">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="BG12">
         <v>0</v>
@@ -3214,133 +3214,133 @@
         <v>188</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S13">
-        <v>5.1</v>
+        <v>3.13</v>
       </c>
       <c r="T13">
-        <v>2.23</v>
+        <v>2.59</v>
       </c>
       <c r="U13">
-        <v>2.14</v>
+        <v>2.81</v>
       </c>
       <c r="V13">
+        <v>1.22</v>
+      </c>
+      <c r="W13">
+        <v>3.6</v>
+      </c>
+      <c r="X13">
+        <v>2.1</v>
+      </c>
+      <c r="Y13">
+        <v>1.71</v>
+      </c>
+      <c r="Z13">
+        <v>4.45</v>
+      </c>
+      <c r="AA13">
+        <v>1.15</v>
+      </c>
+      <c r="AB13">
+        <v>1.02</v>
+      </c>
+      <c r="AC13">
+        <v>1.13</v>
+      </c>
+      <c r="AD13">
+        <v>5.81</v>
+      </c>
+      <c r="AE13">
+        <v>1.39</v>
+      </c>
+      <c r="AF13">
+        <v>2.59</v>
+      </c>
+      <c r="AG13">
+        <v>2.09</v>
+      </c>
+      <c r="AH13">
+        <v>1.76</v>
+      </c>
+      <c r="AI13">
+        <v>3.28</v>
+      </c>
+      <c r="AJ13">
+        <v>1.25</v>
+      </c>
+      <c r="AK13">
+        <v>1.36</v>
+      </c>
+      <c r="AL13">
+        <v>2.84</v>
+      </c>
+      <c r="AM13">
+        <v>1.28</v>
+      </c>
+      <c r="AN13">
+        <v>1.44</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>1.12</v>
+      </c>
+      <c r="AQ13">
+        <v>1.26</v>
+      </c>
+      <c r="AR13">
+        <v>1.66</v>
+      </c>
+      <c r="AS13">
+        <v>1.86</v>
+      </c>
+      <c r="AT13">
+        <v>2.29</v>
+      </c>
+      <c r="AU13">
+        <v>4.8</v>
+      </c>
+      <c r="AV13">
+        <v>3.2</v>
+      </c>
+      <c r="AW13">
+        <v>2.32</v>
+      </c>
+      <c r="AX13">
+        <v>1.84</v>
+      </c>
+      <c r="AY13">
+        <v>1.57</v>
+      </c>
+      <c r="AZ13">
+        <v>1.84</v>
+      </c>
+      <c r="BA13">
+        <v>2.21</v>
+      </c>
+      <c r="BB13">
+        <v>1.12</v>
+      </c>
+      <c r="BC13">
+        <v>1.62</v>
+      </c>
+      <c r="BD13">
+        <v>5.3</v>
+      </c>
+      <c r="BE13">
+        <v>2.15</v>
+      </c>
+      <c r="BF13">
         <v>1.35</v>
-      </c>
-      <c r="W13">
-        <v>3.14</v>
-      </c>
-      <c r="X13">
-        <v>2.62</v>
-      </c>
-      <c r="Y13">
-        <v>1.42</v>
-      </c>
-      <c r="Z13">
-        <v>6.2</v>
-      </c>
-      <c r="AA13">
-        <v>1.06</v>
-      </c>
-      <c r="AB13">
-        <v>1</v>
-      </c>
-      <c r="AC13">
-        <v>1.22</v>
-      </c>
-      <c r="AD13">
-        <v>3.5</v>
-      </c>
-      <c r="AE13">
-        <v>1.85</v>
-      </c>
-      <c r="AF13">
-        <v>1.97</v>
-      </c>
-      <c r="AG13">
-        <v>3.01</v>
-      </c>
-      <c r="AH13">
-        <v>1.31</v>
-      </c>
-      <c r="AI13">
-        <v>5.5</v>
-      </c>
-      <c r="AJ13">
-        <v>1.08</v>
-      </c>
-      <c r="AK13">
-        <v>1.85</v>
-      </c>
-      <c r="AL13">
-        <v>1.85</v>
-      </c>
-      <c r="AM13">
-        <v>1.24</v>
-      </c>
-      <c r="AN13">
-        <v>1.16</v>
-      </c>
-      <c r="AO13">
-        <v>0</v>
-      </c>
-      <c r="AP13">
-        <v>0</v>
-      </c>
-      <c r="AQ13">
-        <v>0</v>
-      </c>
-      <c r="AR13">
-        <v>0</v>
-      </c>
-      <c r="AS13">
-        <v>0</v>
-      </c>
-      <c r="AT13">
-        <v>0</v>
-      </c>
-      <c r="AU13">
-        <v>0</v>
-      </c>
-      <c r="AV13">
-        <v>0</v>
-      </c>
-      <c r="AW13">
-        <v>0</v>
-      </c>
-      <c r="AX13">
-        <v>0</v>
-      </c>
-      <c r="AY13">
-        <v>0</v>
-      </c>
-      <c r="AZ13">
-        <v>0</v>
-      </c>
-      <c r="BA13">
-        <v>0</v>
-      </c>
-      <c r="BB13">
-        <v>1.19</v>
-      </c>
-      <c r="BC13">
-        <v>2.05</v>
-      </c>
-      <c r="BD13">
-        <v>3.9</v>
-      </c>
-      <c r="BE13">
-        <v>1.71</v>
-      </c>
-      <c r="BF13">
-        <v>1.16</v>
       </c>
       <c r="BG13">
         <v>0</v>
@@ -3360,7 +3360,7 @@
         <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D14" t="s">
         <v>105</v>
@@ -3399,133 +3399,133 @@
         <v>188</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>5.59</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AO14">
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AU14">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AV14">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AW14">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX14">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY14">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ14">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BA14">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="BB14">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC14">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BD14">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="BE14">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BF14">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG14">
         <v>0</v>
@@ -3545,7 +3545,7 @@
         <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
         <v>105</v>
@@ -3584,133 +3584,133 @@
         <v>188</v>
       </c>
       <c r="P15">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q15">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R15">
-        <v>5.59</v>
+        <v>0</v>
       </c>
       <c r="S15">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="T15">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>5.61</v>
+        <v>0</v>
       </c>
       <c r="V15">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W15">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X15">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y15">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z15">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA15">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC15">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AD15">
-        <v>4.24</v>
+        <v>4.8</v>
       </c>
       <c r="AE15">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="AF15">
-        <v>2.13</v>
+        <v>2.43</v>
       </c>
       <c r="AG15">
-        <v>2.52</v>
+        <v>2.14</v>
       </c>
       <c r="AH15">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="AI15">
-        <v>4.65</v>
+        <v>3.5</v>
       </c>
       <c r="AJ15">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="AK15">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM15">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AN15">
-        <v>2.32</v>
+        <v>1.05</v>
       </c>
       <c r="AO15">
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AQ15">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AR15">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AS15">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT15">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AU15">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AV15">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AW15">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AX15">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AY15">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ15">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BA15">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="BB15">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC15">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BD15">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="BE15">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BF15">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG15">
         <v>0</v>
@@ -3730,10 +3730,10 @@
         <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E16" t="s">
         <v>121</v>
@@ -3778,70 +3778,70 @@
         <v>0</v>
       </c>
       <c r="S16">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="V16">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W16">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="X16">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z16">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC16">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD16">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AE16">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AH16">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI16">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AJ16">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK16">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL16">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AM16">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN16">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AO16">
         <v>0</v>
@@ -3883,19 +3883,19 @@
         <v>0</v>
       </c>
       <c r="BB16">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC16">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="BD16">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="BE16">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BF16">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG16">
         <v>0</v>
@@ -3915,10 +3915,10 @@
         <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E17" t="s">
         <v>122</v>
@@ -3963,124 +3963,124 @@
         <v>0</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC17">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AD17">
-        <v>4.8</v>
+        <v>2.97</v>
       </c>
       <c r="AE17">
-        <v>1.45</v>
+        <v>2.13</v>
       </c>
       <c r="AF17">
-        <v>2.43</v>
+        <v>1.73</v>
       </c>
       <c r="AG17">
-        <v>2.14</v>
+        <v>3.72</v>
       </c>
       <c r="AH17">
+        <v>1.21</v>
+      </c>
+      <c r="AI17">
+        <v>7.4</v>
+      </c>
+      <c r="AJ17">
+        <v>1.03</v>
+      </c>
+      <c r="AK17">
+        <v>1.75</v>
+      </c>
+      <c r="AL17">
+        <v>1.89</v>
+      </c>
+      <c r="AM17">
+        <v>1.33</v>
+      </c>
+      <c r="AN17">
+        <v>1.44</v>
+      </c>
+      <c r="AO17">
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <v>0</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17">
+        <v>0</v>
+      </c>
+      <c r="AV17">
+        <v>0</v>
+      </c>
+      <c r="AW17">
+        <v>0</v>
+      </c>
+      <c r="AX17">
+        <v>0</v>
+      </c>
+      <c r="AY17">
+        <v>0</v>
+      </c>
+      <c r="AZ17">
+        <v>0</v>
+      </c>
+      <c r="BA17">
+        <v>0</v>
+      </c>
+      <c r="BB17">
+        <v>1.24</v>
+      </c>
+      <c r="BC17">
+        <v>2.27</v>
+      </c>
+      <c r="BD17">
+        <v>3.44</v>
+      </c>
+      <c r="BE17">
         <v>1.58</v>
       </c>
-      <c r="AI17">
-        <v>3.5</v>
-      </c>
-      <c r="AJ17">
-        <v>1.23</v>
-      </c>
-      <c r="AK17">
-        <v>0</v>
-      </c>
-      <c r="AL17">
-        <v>0</v>
-      </c>
-      <c r="AM17">
+      <c r="BF17">
         <v>1.11</v>
-      </c>
-      <c r="AN17">
-        <v>1.05</v>
-      </c>
-      <c r="AO17">
-        <v>0</v>
-      </c>
-      <c r="AP17">
-        <v>0</v>
-      </c>
-      <c r="AQ17">
-        <v>0</v>
-      </c>
-      <c r="AR17">
-        <v>0</v>
-      </c>
-      <c r="AS17">
-        <v>0</v>
-      </c>
-      <c r="AT17">
-        <v>0</v>
-      </c>
-      <c r="AU17">
-        <v>0</v>
-      </c>
-      <c r="AV17">
-        <v>0</v>
-      </c>
-      <c r="AW17">
-        <v>0</v>
-      </c>
-      <c r="AX17">
-        <v>0</v>
-      </c>
-      <c r="AY17">
-        <v>0</v>
-      </c>
-      <c r="AZ17">
-        <v>0</v>
-      </c>
-      <c r="BA17">
-        <v>0</v>
-      </c>
-      <c r="BB17">
-        <v>0</v>
-      </c>
-      <c r="BC17">
-        <v>0</v>
-      </c>
-      <c r="BD17">
-        <v>0</v>
-      </c>
-      <c r="BE17">
-        <v>0</v>
-      </c>
-      <c r="BF17">
-        <v>0</v>
       </c>
       <c r="BG17">
         <v>0</v>
@@ -6505,7 +6505,7 @@
         <v>80</v>
       </c>
       <c r="C31" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D31" t="s">
         <v>105</v>
@@ -6544,133 +6544,133 @@
         <v>188</v>
       </c>
       <c r="P31">
-        <v>1.95</v>
+        <v>1.42</v>
       </c>
       <c r="Q31">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="R31">
-        <v>3.79</v>
+        <v>7.4</v>
       </c>
       <c r="S31">
-        <v>2.48</v>
+        <v>2.01</v>
       </c>
       <c r="T31">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="U31">
-        <v>4.1</v>
+        <v>7.7</v>
       </c>
       <c r="V31">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="W31">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="X31">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="Y31">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z31">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="AA31">
         <v>1.03</v>
       </c>
       <c r="AB31">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC31">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AD31">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="AE31">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="AF31">
         <v>1.68</v>
       </c>
       <c r="AG31">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AH31">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AI31">
         <v>6.75</v>
       </c>
       <c r="AJ31">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AK31">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AL31">
-        <v>1.84</v>
+        <v>1.54</v>
       </c>
       <c r="AM31">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AN31">
-        <v>1.75</v>
+        <v>2.57</v>
       </c>
       <c r="AO31">
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AQ31">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AR31">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AS31">
-        <v>2.7</v>
+        <v>2.33</v>
       </c>
       <c r="AT31">
-        <v>3.65</v>
+        <v>2.95</v>
       </c>
       <c r="AU31">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="AV31">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="AW31">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AX31">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AY31">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AZ31">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="BA31">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="BB31">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="BC31">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="BD31">
-        <v>3.7</v>
+        <v>3.34</v>
       </c>
       <c r="BE31">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="BF31">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="BG31">
         <v>0</v>
@@ -6690,7 +6690,7 @@
         <v>80</v>
       </c>
       <c r="C32" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D32" t="s">
         <v>105</v>
@@ -6729,133 +6729,133 @@
         <v>188</v>
       </c>
       <c r="P32">
-        <v>4.4</v>
+        <v>1.95</v>
       </c>
       <c r="Q32">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="R32">
-        <v>1.8</v>
+        <v>3.79</v>
       </c>
       <c r="S32">
-        <v>5.18</v>
+        <v>2.48</v>
       </c>
       <c r="T32">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="U32">
-        <v>2.46</v>
+        <v>4.1</v>
       </c>
       <c r="V32">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="W32">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="X32">
-        <v>3.32</v>
+        <v>2.88</v>
       </c>
       <c r="Y32">
         <v>1.33</v>
       </c>
       <c r="Z32">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="AA32">
+        <v>1.03</v>
+      </c>
+      <c r="AB32">
         <v>1.02</v>
       </c>
-      <c r="AB32">
-        <v>1.04</v>
-      </c>
       <c r="AC32">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AD32">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="AE32">
+        <v>2.02</v>
+      </c>
+      <c r="AF32">
+        <v>1.68</v>
+      </c>
+      <c r="AG32">
+        <v>3.6</v>
+      </c>
+      <c r="AH32">
+        <v>1.24</v>
+      </c>
+      <c r="AI32">
+        <v>6.75</v>
+      </c>
+      <c r="AJ32">
+        <v>1.07</v>
+      </c>
+      <c r="AK32">
+        <v>1.8</v>
+      </c>
+      <c r="AL32">
+        <v>1.84</v>
+      </c>
+      <c r="AM32">
+        <v>1.27</v>
+      </c>
+      <c r="AN32">
+        <v>1.75</v>
+      </c>
+      <c r="AO32">
+        <v>0</v>
+      </c>
+      <c r="AP32">
+        <v>1.4</v>
+      </c>
+      <c r="AQ32">
+        <v>1.67</v>
+      </c>
+      <c r="AR32">
+        <v>2.1</v>
+      </c>
+      <c r="AS32">
+        <v>2.7</v>
+      </c>
+      <c r="AT32">
+        <v>3.65</v>
+      </c>
+      <c r="AU32">
+        <v>2.7</v>
+      </c>
+      <c r="AV32">
+        <v>2.04</v>
+      </c>
+      <c r="AW32">
+        <v>1.64</v>
+      </c>
+      <c r="AX32">
+        <v>1.38</v>
+      </c>
+      <c r="AY32">
+        <v>1.23</v>
+      </c>
+      <c r="AZ32">
+        <v>1.68</v>
+      </c>
+      <c r="BA32">
+        <v>2.5</v>
+      </c>
+      <c r="BB32">
+        <v>1.23</v>
+      </c>
+      <c r="BC32">
         <v>2.25</v>
       </c>
-      <c r="AF32">
-        <v>1.62</v>
-      </c>
-      <c r="AG32">
-        <v>3.8</v>
-      </c>
-      <c r="AH32">
-        <v>1.19</v>
-      </c>
-      <c r="AI32">
-        <v>7.3</v>
-      </c>
-      <c r="AJ32">
-        <v>1.03</v>
-      </c>
-      <c r="AK32">
-        <v>1.97</v>
-      </c>
-      <c r="AL32">
-        <v>1.73</v>
-      </c>
-      <c r="AM32">
-        <v>1.26</v>
-      </c>
-      <c r="AN32">
-        <v>1.14</v>
-      </c>
-      <c r="AO32">
-        <v>0</v>
-      </c>
-      <c r="AP32">
-        <v>1.28</v>
-      </c>
-      <c r="AQ32">
-        <v>1.53</v>
-      </c>
-      <c r="AR32">
-        <v>1.95</v>
-      </c>
-      <c r="AS32">
-        <v>2.52</v>
-      </c>
-      <c r="AT32">
-        <v>3.48</v>
-      </c>
-      <c r="AU32">
-        <v>3.05</v>
-      </c>
-      <c r="AV32">
-        <v>2.21</v>
-      </c>
-      <c r="AW32">
-        <v>1.73</v>
-      </c>
-      <c r="AX32">
-        <v>1.41</v>
-      </c>
-      <c r="AY32">
-        <v>1.22</v>
-      </c>
-      <c r="AZ32">
-        <v>2.48</v>
-      </c>
-      <c r="BA32">
-        <v>1.84</v>
-      </c>
-      <c r="BB32">
-        <v>1.27</v>
-      </c>
-      <c r="BC32">
-        <v>2.29</v>
-      </c>
       <c r="BD32">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="BE32">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="BF32">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="BG32">
         <v>0</v>
@@ -6914,133 +6914,133 @@
         <v>188</v>
       </c>
       <c r="P33">
-        <v>1.42</v>
+        <v>4.4</v>
       </c>
       <c r="Q33">
-        <v>3.85</v>
+        <v>3.15</v>
       </c>
       <c r="R33">
-        <v>7.4</v>
+        <v>1.8</v>
       </c>
       <c r="S33">
-        <v>2.01</v>
+        <v>5.18</v>
       </c>
       <c r="T33">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="U33">
+        <v>2.46</v>
+      </c>
+      <c r="V33">
+        <v>1.47</v>
+      </c>
+      <c r="W33">
+        <v>2.41</v>
+      </c>
+      <c r="X33">
+        <v>3.32</v>
+      </c>
+      <c r="Y33">
+        <v>1.33</v>
+      </c>
+      <c r="Z33">
         <v>7.7</v>
       </c>
-      <c r="V33">
-        <v>1.44</v>
-      </c>
-      <c r="W33">
-        <v>2.5</v>
-      </c>
-      <c r="X33">
-        <v>2.96</v>
-      </c>
-      <c r="Y33">
-        <v>1.32</v>
-      </c>
-      <c r="Z33">
+      <c r="AA33">
+        <v>1.02</v>
+      </c>
+      <c r="AB33">
+        <v>1.04</v>
+      </c>
+      <c r="AC33">
+        <v>1.35</v>
+      </c>
+      <c r="AD33">
+        <v>2.74</v>
+      </c>
+      <c r="AE33">
+        <v>2.25</v>
+      </c>
+      <c r="AF33">
+        <v>1.62</v>
+      </c>
+      <c r="AG33">
+        <v>3.8</v>
+      </c>
+      <c r="AH33">
+        <v>1.19</v>
+      </c>
+      <c r="AI33">
         <v>7.3</v>
       </c>
-      <c r="AA33">
+      <c r="AJ33">
         <v>1.03</v>
       </c>
-      <c r="AB33">
-        <v>1.03</v>
-      </c>
-      <c r="AC33">
-        <v>1.37</v>
-      </c>
-      <c r="AD33">
-        <v>3.01</v>
-      </c>
-      <c r="AE33">
-        <v>2.06</v>
-      </c>
-      <c r="AF33">
-        <v>1.68</v>
-      </c>
-      <c r="AG33">
-        <v>3.75</v>
-      </c>
-      <c r="AH33">
+      <c r="AK33">
+        <v>1.97</v>
+      </c>
+      <c r="AL33">
+        <v>1.73</v>
+      </c>
+      <c r="AM33">
+        <v>1.26</v>
+      </c>
+      <c r="AN33">
+        <v>1.14</v>
+      </c>
+      <c r="AO33">
+        <v>0</v>
+      </c>
+      <c r="AP33">
+        <v>1.28</v>
+      </c>
+      <c r="AQ33">
+        <v>1.53</v>
+      </c>
+      <c r="AR33">
+        <v>1.95</v>
+      </c>
+      <c r="AS33">
+        <v>2.52</v>
+      </c>
+      <c r="AT33">
+        <v>3.48</v>
+      </c>
+      <c r="AU33">
+        <v>3.05</v>
+      </c>
+      <c r="AV33">
+        <v>2.21</v>
+      </c>
+      <c r="AW33">
+        <v>1.73</v>
+      </c>
+      <c r="AX33">
+        <v>1.41</v>
+      </c>
+      <c r="AY33">
         <v>1.22</v>
       </c>
-      <c r="AI33">
-        <v>6.75</v>
-      </c>
-      <c r="AJ33">
-        <v>1.04</v>
-      </c>
-      <c r="AK33">
-        <v>2.3</v>
-      </c>
-      <c r="AL33">
-        <v>1.54</v>
-      </c>
-      <c r="AM33">
-        <v>1.17</v>
-      </c>
-      <c r="AN33">
-        <v>2.57</v>
-      </c>
-      <c r="AO33">
-        <v>0</v>
-      </c>
-      <c r="AP33">
-        <v>1.3</v>
-      </c>
-      <c r="AQ33">
-        <v>1.46</v>
-      </c>
-      <c r="AR33">
-        <v>2.13</v>
-      </c>
-      <c r="AS33">
-        <v>2.33</v>
-      </c>
-      <c r="AT33">
-        <v>2.95</v>
-      </c>
-      <c r="AU33">
-        <v>3.15</v>
-      </c>
-      <c r="AV33">
-        <v>2.38</v>
-      </c>
-      <c r="AW33">
-        <v>1.83</v>
-      </c>
-      <c r="AX33">
-        <v>1.48</v>
-      </c>
-      <c r="AY33">
-        <v>1.34</v>
-      </c>
       <c r="AZ33">
-        <v>1.3</v>
+        <v>2.48</v>
       </c>
       <c r="BA33">
-        <v>4.2</v>
+        <v>1.84</v>
       </c>
       <c r="BB33">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BC33">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
       <c r="BD33">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="BE33">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="BF33">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="BG33">
         <v>0</v>
@@ -7060,10 +7060,10 @@
         <v>80</v>
       </c>
       <c r="C34" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E34" t="s">
         <v>139</v>
@@ -7099,133 +7099,133 @@
         <v>188</v>
       </c>
       <c r="P34">
-        <v>2.5</v>
+        <v>4.75</v>
       </c>
       <c r="Q34">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="R34">
-        <v>2.53</v>
+        <v>1.72</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AE34">
-        <v>1.66</v>
+        <v>2.75</v>
       </c>
       <c r="AF34">
-        <v>2.15</v>
+        <v>1.47</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="AH34">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI34">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AL34">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AM34">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN34">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AO34">
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ34">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR34">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS34">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AT34">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AU34">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW34">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AX34">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY34">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ34">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BA34">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BB34">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC34">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="BD34">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="BE34">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BF34">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG34">
         <v>0</v>
@@ -7245,10 +7245,10 @@
         <v>80</v>
       </c>
       <c r="C35" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E35" t="s">
         <v>140</v>
@@ -7284,133 +7284,133 @@
         <v>188</v>
       </c>
       <c r="P35">
-        <v>4.75</v>
+        <v>2.5</v>
       </c>
       <c r="Q35">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="R35">
-        <v>1.72</v>
+        <v>2.53</v>
       </c>
       <c r="S35">
-        <v>6.17</v>
+        <v>0</v>
       </c>
       <c r="T35">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U35">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V35">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W35">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="X35">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y35">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z35">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="AA35">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB35">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC35">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AD35">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AE35">
-        <v>2.75</v>
+        <v>1.66</v>
       </c>
       <c r="AF35">
-        <v>1.47</v>
+        <v>2.15</v>
       </c>
       <c r="AG35">
-        <v>5.36</v>
+        <v>0</v>
       </c>
       <c r="AH35">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AI35">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ35">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK35">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AL35">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AM35">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN35">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AO35">
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AQ35">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AR35">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AS35">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AT35">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AU35">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW35">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AX35">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AY35">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ35">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="BA35">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BB35">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC35">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="BD35">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="BE35">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BF35">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BG35">
         <v>0</v>
@@ -7654,79 +7654,79 @@
         <v>188</v>
       </c>
       <c r="P37">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q37">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="R37">
-        <v>2.15</v>
+        <v>3.37</v>
       </c>
       <c r="S37">
-        <v>4.43</v>
+        <v>3.01</v>
       </c>
       <c r="T37">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="U37">
-        <v>2.88</v>
+        <v>4.53</v>
       </c>
       <c r="V37">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="W37">
-        <v>2.31</v>
+        <v>2.17</v>
       </c>
       <c r="X37">
-        <v>3.38</v>
+        <v>4.1</v>
       </c>
       <c r="Y37">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="Z37">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA37">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AB37">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AC37">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AD37">
-        <v>2.46</v>
+        <v>2.09</v>
       </c>
       <c r="AE37">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="AF37">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="AG37">
-        <v>5.1</v>
+        <v>6.35</v>
       </c>
       <c r="AH37">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AI37">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="AJ37">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK37">
-        <v>2.04</v>
+        <v>2.4</v>
       </c>
       <c r="AL37">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AM37">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="AN37">
-        <v>1.29</v>
+        <v>1.54</v>
       </c>
       <c r="AO37">
         <v>0</v>
@@ -7735,52 +7735,52 @@
         <v>1.39</v>
       </c>
       <c r="AQ37">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AR37">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="AS37">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="AT37">
-        <v>4.15</v>
+        <v>4.36</v>
       </c>
       <c r="AU37">
-        <v>2.66</v>
+        <v>2.57</v>
       </c>
       <c r="AV37">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AW37">
         <v>1.6</v>
       </c>
       <c r="AX37">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AY37">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AZ37">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="BA37">
-        <v>2.12</v>
+        <v>2.39</v>
       </c>
       <c r="BB37">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="BC37">
-        <v>2.59</v>
+        <v>3.12</v>
       </c>
       <c r="BD37">
-        <v>2.96</v>
+        <v>2.53</v>
       </c>
       <c r="BE37">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="BF37">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="BG37">
         <v>0</v>
@@ -7839,133 +7839,133 @@
         <v>188</v>
       </c>
       <c r="P38">
-        <v>4.65</v>
+        <v>3.3</v>
       </c>
       <c r="Q38">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R38">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="S38">
-        <v>6.93</v>
+        <v>4.43</v>
       </c>
       <c r="T38">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="U38">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="V38">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="W38">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="X38">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="Y38">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z38">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="AA38">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AB38">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AC38">
         <v>1.53</v>
       </c>
       <c r="AD38">
-        <v>2.35</v>
+        <v>2.46</v>
       </c>
       <c r="AE38">
         <v>2.65</v>
       </c>
       <c r="AF38">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AG38">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AH38">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AI38">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AJ38">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AK38">
-        <v>2.4</v>
+        <v>2.04</v>
       </c>
       <c r="AL38">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="AM38">
-        <v>1.26</v>
+        <v>1.57</v>
       </c>
       <c r="AN38">
-        <v>1.07</v>
+        <v>1.29</v>
       </c>
       <c r="AO38">
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AQ38">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AR38">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="AS38">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="AT38">
-        <v>4.41</v>
+        <v>4.15</v>
       </c>
       <c r="AU38">
-        <v>2.55</v>
+        <v>2.66</v>
       </c>
       <c r="AV38">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AW38">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AX38">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AY38">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AZ38">
-        <v>4.1</v>
+        <v>2.12</v>
       </c>
       <c r="BA38">
-        <v>1.42</v>
+        <v>2.12</v>
       </c>
       <c r="BB38">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="BC38">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="BD38">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="BE38">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="BF38">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="BG38">
         <v>0</v>
@@ -8024,133 +8024,133 @@
         <v>188</v>
       </c>
       <c r="P39">
-        <v>2.2</v>
+        <v>4.65</v>
       </c>
       <c r="Q39">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="R39">
-        <v>3.37</v>
+        <v>1.62</v>
       </c>
       <c r="S39">
-        <v>3.01</v>
+        <v>6.93</v>
       </c>
       <c r="T39">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="U39">
-        <v>4.53</v>
+        <v>2.3</v>
       </c>
       <c r="V39">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="W39">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="X39">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="Y39">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z39">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA39">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AB39">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AC39">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AD39">
-        <v>2.09</v>
+        <v>2.35</v>
       </c>
       <c r="AE39">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="AF39">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="AG39">
-        <v>6.35</v>
+        <v>4.9</v>
       </c>
       <c r="AH39">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AI39">
-        <v>10.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ39">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AK39">
         <v>2.4</v>
       </c>
       <c r="AL39">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AM39">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AN39">
-        <v>1.54</v>
+        <v>1.07</v>
       </c>
       <c r="AO39">
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AQ39">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AR39">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="AS39">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="AT39">
-        <v>4.36</v>
+        <v>4.41</v>
       </c>
       <c r="AU39">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="AV39">
         <v>1.99</v>
       </c>
       <c r="AW39">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AX39">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AY39">
         <v>1.13</v>
       </c>
       <c r="AZ39">
-        <v>1.96</v>
+        <v>4.1</v>
       </c>
       <c r="BA39">
-        <v>2.39</v>
+        <v>1.42</v>
       </c>
       <c r="BB39">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="BC39">
-        <v>3.12</v>
+        <v>2.66</v>
       </c>
       <c r="BD39">
-        <v>2.53</v>
+        <v>2.82</v>
       </c>
       <c r="BE39">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="BF39">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="BG39">
         <v>0</v>

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -343,15 +343,15 @@
     <t>Jeonbuk Motors</t>
   </si>
   <si>
+    <t>Daejeon Citizen</t>
+  </si>
+  <si>
     <t>Sangju Sangmu</t>
   </si>
   <si>
     <t>Gangwon</t>
   </si>
   <si>
-    <t>Daejeon Citizen</t>
-  </si>
-  <si>
     <t>Madura United</t>
   </si>
   <si>
@@ -373,18 +373,18 @@
     <t>Shandong Luneng</t>
   </si>
   <si>
+    <t>Dire Dawa Kenema</t>
+  </si>
+  <si>
+    <t>Karvan FK</t>
+  </si>
+  <si>
+    <t>Chongqing Tongliang Long</t>
+  </si>
+  <si>
     <t>Borneo</t>
   </si>
   <si>
-    <t>Karvan FK</t>
-  </si>
-  <si>
-    <t>Dire Dawa Kenema</t>
-  </si>
-  <si>
-    <t>Chongqing Tongliang Long</t>
-  </si>
-  <si>
     <t>Mekelle Kenema</t>
   </si>
   <si>
@@ -418,36 +418,36 @@
     <t>Dibba Al Fujairah</t>
   </si>
   <si>
+    <t>Al Ittihad Kalba</t>
+  </si>
+  <si>
     <t>Bani Yas</t>
   </si>
   <si>
-    <t>Al Ittihad Kalba</t>
-  </si>
-  <si>
     <t>Al Ahly</t>
   </si>
   <si>
+    <t>Smouha SC</t>
+  </si>
+  <si>
+    <t>Ceramica Cleopatra</t>
+  </si>
+  <si>
     <t>Lokomotiv Sofia 1929</t>
   </si>
   <si>
-    <t>Ceramica Cleopatra</t>
-  </si>
-  <si>
-    <t>Smouha SC</t>
-  </si>
-  <si>
     <t>Falkenberg</t>
   </si>
   <si>
     <t>Magesi</t>
   </si>
   <si>
+    <t>Chippa United</t>
+  </si>
+  <si>
     <t>Siwelele</t>
   </si>
   <si>
-    <t>Chippa United</t>
-  </si>
-  <si>
     <t>Stellenbosch</t>
   </si>
   <si>
@@ -466,15 +466,15 @@
     <t>Gwangju</t>
   </si>
   <si>
+    <t>Incheon United</t>
+  </si>
+  <si>
     <t>Ulsan</t>
   </si>
   <si>
     <t>Pohang Steelers</t>
   </si>
   <si>
-    <t>Incheon United</t>
-  </si>
-  <si>
     <t>Bali United</t>
   </si>
   <si>
@@ -496,18 +496,18 @@
     <t>Shanghai Shenhua</t>
   </si>
   <si>
+    <t>Ethiopia Bunna</t>
+  </si>
+  <si>
+    <t>Neftçi</t>
+  </si>
+  <si>
+    <t>Henan Jianye</t>
+  </si>
+  <si>
     <t>Persita</t>
   </si>
   <si>
-    <t>Neftçi</t>
-  </si>
-  <si>
-    <t>Ethiopia Bunna</t>
-  </si>
-  <si>
-    <t>Henan Jianye</t>
-  </si>
-  <si>
     <t>Arba Minch Kenema</t>
   </si>
   <si>
@@ -547,25 +547,25 @@
     <t>ENPPI</t>
   </si>
   <si>
+    <t>Zamalek</t>
+  </si>
+  <si>
+    <t>Pyramids FC</t>
+  </si>
+  <si>
     <t>Botev Vratsa</t>
   </si>
   <si>
-    <t>Pyramids FC</t>
-  </si>
-  <si>
-    <t>Zamalek</t>
-  </si>
-  <si>
     <t>Norrköping</t>
   </si>
   <si>
     <t>Orbit College</t>
   </si>
   <si>
+    <t>Sekhukhune United</t>
+  </si>
+  <si>
     <t>Durban City</t>
-  </si>
-  <si>
-    <t>Sekhukhune United</t>
   </si>
   <si>
     <t>Orlando Pirates</t>
@@ -1549,37 +1549,37 @@
         <v>188</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S4">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="T4">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="U4">
-        <v>2.88</v>
+        <v>4.12</v>
       </c>
       <c r="V4">
+        <v>1.44</v>
+      </c>
+      <c r="W4">
+        <v>2.59</v>
+      </c>
+      <c r="X4">
+        <v>3.04</v>
+      </c>
+      <c r="Y4">
         <v>1.33</v>
       </c>
-      <c r="W4">
-        <v>2.77</v>
-      </c>
-      <c r="X4">
-        <v>2.65</v>
-      </c>
-      <c r="Y4">
-        <v>1.36</v>
-      </c>
       <c r="Z4">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="AA4">
         <v>1.03</v>
@@ -1588,94 +1588,94 @@
         <v>1.02</v>
       </c>
       <c r="AC4">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AD4">
-        <v>3.37</v>
+        <v>2.94</v>
       </c>
       <c r="AE4">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AF4">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AG4">
-        <v>3.38</v>
+        <v>3.54</v>
       </c>
       <c r="AH4">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AI4">
-        <v>6.75</v>
+        <v>7.1</v>
       </c>
       <c r="AJ4">
         <v>1.04</v>
       </c>
       <c r="AK4">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AL4">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AM4">
         <v>1.31</v>
       </c>
       <c r="AN4">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="AO4">
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="AQ4">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="AR4">
-        <v>2.02</v>
+        <v>2.23</v>
       </c>
       <c r="AS4">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="AT4">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AU4">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AV4">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AW4">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AX4">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AY4">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ4">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="BA4">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="BB4">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BC4">
-        <v>2.18</v>
+        <v>2.27</v>
       </c>
       <c r="BD4">
-        <v>3.66</v>
+        <v>3.42</v>
       </c>
       <c r="BE4">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="BF4">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BG4">
         <v>0</v>
@@ -1734,133 +1734,133 @@
         <v>188</v>
       </c>
       <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>3.25</v>
+      </c>
+      <c r="T5">
+        <v>2.01</v>
+      </c>
+      <c r="U5">
+        <v>2.88</v>
+      </c>
+      <c r="V5">
+        <v>1.33</v>
+      </c>
+      <c r="W5">
+        <v>2.77</v>
+      </c>
+      <c r="X5">
+        <v>2.65</v>
+      </c>
+      <c r="Y5">
+        <v>1.36</v>
+      </c>
+      <c r="Z5">
+        <v>7.5</v>
+      </c>
+      <c r="AA5">
+        <v>1.03</v>
+      </c>
+      <c r="AB5">
+        <v>1.02</v>
+      </c>
+      <c r="AC5">
+        <v>1.32</v>
+      </c>
+      <c r="AD5">
+        <v>3.37</v>
+      </c>
+      <c r="AE5">
+        <v>2.01</v>
+      </c>
+      <c r="AF5">
+        <v>1.8</v>
+      </c>
+      <c r="AG5">
+        <v>3.38</v>
+      </c>
+      <c r="AH5">
+        <v>1.24</v>
+      </c>
+      <c r="AI5">
+        <v>6.75</v>
+      </c>
+      <c r="AJ5">
+        <v>1.04</v>
+      </c>
+      <c r="AK5">
+        <v>1.73</v>
+      </c>
+      <c r="AL5">
         <v>2</v>
       </c>
-      <c r="Q5">
-        <v>3.2</v>
-      </c>
-      <c r="R5">
-        <v>3.6</v>
-      </c>
-      <c r="S5">
-        <v>2.77</v>
-      </c>
-      <c r="T5">
-        <v>1.91</v>
-      </c>
-      <c r="U5">
-        <v>4.76</v>
-      </c>
-      <c r="V5">
-        <v>1.53</v>
-      </c>
-      <c r="W5">
-        <v>2.34</v>
-      </c>
-      <c r="X5">
-        <v>3.25</v>
-      </c>
-      <c r="Y5">
-        <v>1.27</v>
-      </c>
-      <c r="Z5">
-        <v>8.5</v>
-      </c>
-      <c r="AA5">
-        <v>1.01</v>
-      </c>
-      <c r="AB5">
-        <v>1.05</v>
-      </c>
-      <c r="AC5">
+      <c r="AM5">
+        <v>1.31</v>
+      </c>
+      <c r="AN5">
+        <v>1.46</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>1.37</v>
+      </c>
+      <c r="AQ5">
+        <v>1.64</v>
+      </c>
+      <c r="AR5">
+        <v>2.02</v>
+      </c>
+      <c r="AS5">
+        <v>2.6</v>
+      </c>
+      <c r="AT5">
+        <v>3.45</v>
+      </c>
+      <c r="AU5">
+        <v>2.8</v>
+      </c>
+      <c r="AV5">
+        <v>2.1</v>
+      </c>
+      <c r="AW5">
+        <v>1.68</v>
+      </c>
+      <c r="AX5">
         <v>1.42</v>
       </c>
-      <c r="AD5">
-        <v>2.51</v>
-      </c>
-      <c r="AE5">
-        <v>2.42</v>
-      </c>
-      <c r="AF5">
-        <v>1.54</v>
-      </c>
-      <c r="AG5">
-        <v>4.33</v>
-      </c>
-      <c r="AH5">
-        <v>1.15</v>
-      </c>
-      <c r="AI5">
-        <v>8.5</v>
-      </c>
-      <c r="AJ5">
-        <v>1.01</v>
-      </c>
-      <c r="AK5">
-        <v>2.05</v>
-      </c>
-      <c r="AL5">
-        <v>1.69</v>
-      </c>
-      <c r="AM5">
-        <v>1.33</v>
-      </c>
-      <c r="AN5">
-        <v>1.71</v>
-      </c>
-      <c r="AO5">
-        <v>0</v>
-      </c>
-      <c r="AP5">
-        <v>1.5</v>
-      </c>
-      <c r="AQ5">
-        <v>1.84</v>
-      </c>
-      <c r="AR5">
-        <v>2.35</v>
-      </c>
-      <c r="AS5">
-        <v>3.1</v>
-      </c>
-      <c r="AT5">
-        <v>0</v>
-      </c>
-      <c r="AU5">
-        <v>2.38</v>
-      </c>
-      <c r="AV5">
-        <v>1.84</v>
-      </c>
-      <c r="AW5">
-        <v>1.5</v>
-      </c>
-      <c r="AX5">
-        <v>1.3</v>
-      </c>
       <c r="AY5">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ5">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="BA5">
-        <v>2.43</v>
+        <v>2.17</v>
       </c>
       <c r="BB5">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="BC5">
-        <v>2.53</v>
+        <v>2.18</v>
       </c>
       <c r="BD5">
-        <v>3.04</v>
+        <v>3.66</v>
       </c>
       <c r="BE5">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="BF5">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="BG5">
         <v>0</v>
@@ -1919,133 +1919,133 @@
         <v>188</v>
       </c>
       <c r="P6">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="Q6">
         <v>3.2</v>
       </c>
       <c r="R6">
-        <v>2.83</v>
+        <v>3.6</v>
       </c>
       <c r="S6">
-        <v>2.84</v>
+        <v>2.77</v>
       </c>
       <c r="T6">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="U6">
-        <v>4.12</v>
+        <v>4.76</v>
       </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W6">
-        <v>2.59</v>
+        <v>2.34</v>
       </c>
       <c r="X6">
+        <v>3.25</v>
+      </c>
+      <c r="Y6">
+        <v>1.27</v>
+      </c>
+      <c r="Z6">
+        <v>8.5</v>
+      </c>
+      <c r="AA6">
+        <v>1.01</v>
+      </c>
+      <c r="AB6">
+        <v>1.05</v>
+      </c>
+      <c r="AC6">
+        <v>1.42</v>
+      </c>
+      <c r="AD6">
+        <v>2.51</v>
+      </c>
+      <c r="AE6">
+        <v>2.42</v>
+      </c>
+      <c r="AF6">
+        <v>1.54</v>
+      </c>
+      <c r="AG6">
+        <v>4.33</v>
+      </c>
+      <c r="AH6">
+        <v>1.15</v>
+      </c>
+      <c r="AI6">
+        <v>8.5</v>
+      </c>
+      <c r="AJ6">
+        <v>1.01</v>
+      </c>
+      <c r="AK6">
+        <v>2.05</v>
+      </c>
+      <c r="AL6">
+        <v>1.69</v>
+      </c>
+      <c r="AM6">
+        <v>1.33</v>
+      </c>
+      <c r="AN6">
+        <v>1.71</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>1.5</v>
+      </c>
+      <c r="AQ6">
+        <v>1.84</v>
+      </c>
+      <c r="AR6">
+        <v>2.35</v>
+      </c>
+      <c r="AS6">
+        <v>3.1</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>2.38</v>
+      </c>
+      <c r="AV6">
+        <v>1.84</v>
+      </c>
+      <c r="AW6">
+        <v>1.5</v>
+      </c>
+      <c r="AX6">
+        <v>1.3</v>
+      </c>
+      <c r="AY6">
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <v>1.65</v>
+      </c>
+      <c r="BA6">
+        <v>2.43</v>
+      </c>
+      <c r="BB6">
+        <v>1.33</v>
+      </c>
+      <c r="BC6">
+        <v>2.53</v>
+      </c>
+      <c r="BD6">
         <v>3.04</v>
       </c>
-      <c r="Y6">
-        <v>1.33</v>
-      </c>
-      <c r="Z6">
-        <v>7.7</v>
-      </c>
-      <c r="AA6">
-        <v>1.03</v>
-      </c>
-      <c r="AB6">
-        <v>1.02</v>
-      </c>
-      <c r="AC6">
-        <v>1.31</v>
-      </c>
-      <c r="AD6">
-        <v>2.94</v>
-      </c>
-      <c r="AE6">
-        <v>2.1</v>
-      </c>
-      <c r="AF6">
-        <v>1.71</v>
-      </c>
-      <c r="AG6">
-        <v>3.54</v>
-      </c>
-      <c r="AH6">
-        <v>1.22</v>
-      </c>
-      <c r="AI6">
-        <v>7.1</v>
-      </c>
-      <c r="AJ6">
-        <v>1.04</v>
-      </c>
-      <c r="AK6">
-        <v>1.83</v>
-      </c>
-      <c r="AL6">
-        <v>1.87</v>
-      </c>
-      <c r="AM6">
-        <v>1.31</v>
-      </c>
-      <c r="AN6">
-        <v>1.64</v>
-      </c>
-      <c r="AO6">
-        <v>0</v>
-      </c>
-      <c r="AP6">
-        <v>1.45</v>
-      </c>
-      <c r="AQ6">
-        <v>1.76</v>
-      </c>
-      <c r="AR6">
-        <v>2.23</v>
-      </c>
-      <c r="AS6">
-        <v>2.9</v>
-      </c>
-      <c r="AT6">
-        <v>0</v>
-      </c>
-      <c r="AU6">
-        <v>2.5</v>
-      </c>
-      <c r="AV6">
-        <v>1.93</v>
-      </c>
-      <c r="AW6">
-        <v>1.57</v>
-      </c>
-      <c r="AX6">
-        <v>1.35</v>
-      </c>
-      <c r="AY6">
-        <v>0</v>
-      </c>
-      <c r="AZ6">
-        <v>1.72</v>
-      </c>
-      <c r="BA6">
-        <v>2.3</v>
-      </c>
-      <c r="BB6">
-        <v>1.25</v>
-      </c>
-      <c r="BC6">
-        <v>2.27</v>
-      </c>
-      <c r="BD6">
-        <v>3.42</v>
-      </c>
       <c r="BE6">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="BF6">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="BG6">
         <v>0</v>
@@ -3360,7 +3360,7 @@
         <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D14" t="s">
         <v>105</v>
@@ -3399,133 +3399,133 @@
         <v>188</v>
       </c>
       <c r="P14">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R14">
-        <v>5.59</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>5.61</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD14">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AH14">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI14">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AJ14">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK14">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM14">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AN14">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AO14">
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AQ14">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AR14">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AS14">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT14">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AU14">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AV14">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AW14">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AX14">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AY14">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ14">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BA14">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="BB14">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC14">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BD14">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="BE14">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BF14">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG14">
         <v>0</v>
@@ -3730,10 +3730,10 @@
         <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E16" t="s">
         <v>121</v>
@@ -3778,70 +3778,70 @@
         <v>0</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL16">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AM16">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO16">
         <v>0</v>
@@ -3883,19 +3883,19 @@
         <v>0</v>
       </c>
       <c r="BB16">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC16">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BD16">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="BE16">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF16">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG16">
         <v>0</v>
@@ -3915,10 +3915,10 @@
         <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E17" t="s">
         <v>122</v>
@@ -3954,133 +3954,133 @@
         <v>188</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>5.59</v>
       </c>
       <c r="S17">
-        <v>3.3</v>
+        <v>2.01</v>
       </c>
       <c r="T17">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="U17">
-        <v>3.42</v>
+        <v>5.61</v>
       </c>
       <c r="V17">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="W17">
-        <v>2.56</v>
+        <v>3.2</v>
       </c>
       <c r="X17">
-        <v>2.99</v>
+        <v>2.39</v>
       </c>
       <c r="Y17">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="Z17">
-        <v>8</v>
+        <v>5.75</v>
       </c>
       <c r="AA17">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AB17">
         <v>1.02</v>
       </c>
       <c r="AC17">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AD17">
-        <v>2.97</v>
+        <v>4.24</v>
       </c>
       <c r="AE17">
+        <v>1.62</v>
+      </c>
+      <c r="AF17">
         <v>2.13</v>
       </c>
-      <c r="AF17">
-        <v>1.73</v>
-      </c>
       <c r="AG17">
-        <v>3.72</v>
+        <v>2.52</v>
       </c>
       <c r="AH17">
+        <v>1.47</v>
+      </c>
+      <c r="AI17">
+        <v>4.65</v>
+      </c>
+      <c r="AJ17">
+        <v>1.12</v>
+      </c>
+      <c r="AK17">
+        <v>1.69</v>
+      </c>
+      <c r="AL17">
+        <v>2</v>
+      </c>
+      <c r="AM17">
+        <v>1.16</v>
+      </c>
+      <c r="AN17">
+        <v>2.32</v>
+      </c>
+      <c r="AO17">
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <v>1.19</v>
+      </c>
+      <c r="AQ17">
+        <v>1.37</v>
+      </c>
+      <c r="AR17">
+        <v>1.95</v>
+      </c>
+      <c r="AS17">
+        <v>2.18</v>
+      </c>
+      <c r="AT17">
+        <v>2.86</v>
+      </c>
+      <c r="AU17">
+        <v>3.68</v>
+      </c>
+      <c r="AV17">
+        <v>2.57</v>
+      </c>
+      <c r="AW17">
+        <v>1.97</v>
+      </c>
+      <c r="AX17">
+        <v>1.6</v>
+      </c>
+      <c r="AY17">
+        <v>1.34</v>
+      </c>
+      <c r="AZ17">
+        <v>1.44</v>
+      </c>
+      <c r="BA17">
+        <v>3.16</v>
+      </c>
+      <c r="BB17">
+        <v>1.13</v>
+      </c>
+      <c r="BC17">
+        <v>1.84</v>
+      </c>
+      <c r="BD17">
+        <v>4.55</v>
+      </c>
+      <c r="BE17">
+        <v>1.84</v>
+      </c>
+      <c r="BF17">
         <v>1.21</v>
-      </c>
-      <c r="AI17">
-        <v>7.4</v>
-      </c>
-      <c r="AJ17">
-        <v>1.03</v>
-      </c>
-      <c r="AK17">
-        <v>1.75</v>
-      </c>
-      <c r="AL17">
-        <v>1.89</v>
-      </c>
-      <c r="AM17">
-        <v>1.33</v>
-      </c>
-      <c r="AN17">
-        <v>1.44</v>
-      </c>
-      <c r="AO17">
-        <v>0</v>
-      </c>
-      <c r="AP17">
-        <v>0</v>
-      </c>
-      <c r="AQ17">
-        <v>0</v>
-      </c>
-      <c r="AR17">
-        <v>0</v>
-      </c>
-      <c r="AS17">
-        <v>0</v>
-      </c>
-      <c r="AT17">
-        <v>0</v>
-      </c>
-      <c r="AU17">
-        <v>0</v>
-      </c>
-      <c r="AV17">
-        <v>0</v>
-      </c>
-      <c r="AW17">
-        <v>0</v>
-      </c>
-      <c r="AX17">
-        <v>0</v>
-      </c>
-      <c r="AY17">
-        <v>0</v>
-      </c>
-      <c r="AZ17">
-        <v>0</v>
-      </c>
-      <c r="BA17">
-        <v>0</v>
-      </c>
-      <c r="BB17">
-        <v>1.24</v>
-      </c>
-      <c r="BC17">
-        <v>2.27</v>
-      </c>
-      <c r="BD17">
-        <v>3.44</v>
-      </c>
-      <c r="BE17">
-        <v>1.58</v>
-      </c>
-      <c r="BF17">
-        <v>1.11</v>
       </c>
       <c r="BG17">
         <v>0</v>
@@ -4324,10 +4324,10 @@
         <v>188</v>
       </c>
       <c r="P19">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="Q19">
-        <v>3.2</v>
+        <v>3.29</v>
       </c>
       <c r="R19">
         <v>2.38</v>
@@ -6144,7 +6144,7 @@
         <v>134</v>
       </c>
       <c r="F29" t="s">
-        <v>175</v>
+        <v>145</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -6329,7 +6329,7 @@
         <v>135</v>
       </c>
       <c r="F30" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -6690,7 +6690,7 @@
         <v>80</v>
       </c>
       <c r="C32" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D32" t="s">
         <v>105</v>
@@ -6729,133 +6729,133 @@
         <v>188</v>
       </c>
       <c r="P32">
-        <v>1.95</v>
+        <v>4.75</v>
       </c>
       <c r="Q32">
+        <v>3.3</v>
+      </c>
+      <c r="R32">
+        <v>1.72</v>
+      </c>
+      <c r="S32">
+        <v>6.17</v>
+      </c>
+      <c r="T32">
+        <v>1.87</v>
+      </c>
+      <c r="U32">
+        <v>2.45</v>
+      </c>
+      <c r="V32">
+        <v>1.56</v>
+      </c>
+      <c r="W32">
+        <v>2.26</v>
+      </c>
+      <c r="X32">
         <v>3.25</v>
       </c>
-      <c r="R32">
-        <v>3.79</v>
-      </c>
-      <c r="S32">
-        <v>2.48</v>
-      </c>
-      <c r="T32">
-        <v>2.1</v>
-      </c>
-      <c r="U32">
-        <v>4.1</v>
-      </c>
-      <c r="V32">
-        <v>1.37</v>
-      </c>
-      <c r="W32">
-        <v>2.7</v>
-      </c>
-      <c r="X32">
-        <v>2.88</v>
-      </c>
       <c r="Y32">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>7</v>
+        <v>9.1</v>
       </c>
       <c r="AA32">
         <v>1.03</v>
       </c>
       <c r="AB32">
+        <v>1.06</v>
+      </c>
+      <c r="AC32">
+        <v>1.46</v>
+      </c>
+      <c r="AD32">
+        <v>2.38</v>
+      </c>
+      <c r="AE32">
+        <v>2.75</v>
+      </c>
+      <c r="AF32">
+        <v>1.47</v>
+      </c>
+      <c r="AG32">
+        <v>5.36</v>
+      </c>
+      <c r="AH32">
+        <v>1.12</v>
+      </c>
+      <c r="AI32">
+        <v>10</v>
+      </c>
+      <c r="AJ32">
         <v>1.02</v>
       </c>
-      <c r="AC32">
-        <v>1.32</v>
-      </c>
-      <c r="AD32">
-        <v>3</v>
-      </c>
-      <c r="AE32">
-        <v>2.02</v>
-      </c>
-      <c r="AF32">
-        <v>1.68</v>
-      </c>
-      <c r="AG32">
-        <v>3.6</v>
-      </c>
-      <c r="AH32">
-        <v>1.24</v>
-      </c>
-      <c r="AI32">
-        <v>6.75</v>
-      </c>
-      <c r="AJ32">
-        <v>1.07</v>
-      </c>
       <c r="AK32">
-        <v>1.8</v>
+        <v>2.28</v>
       </c>
       <c r="AL32">
-        <v>1.84</v>
+        <v>1.55</v>
       </c>
       <c r="AM32">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AN32">
-        <v>1.75</v>
+        <v>1.1</v>
       </c>
       <c r="AO32">
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ32">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AR32">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AS32">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AT32">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AU32">
         <v>2.7</v>
       </c>
       <c r="AV32">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AW32">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AX32">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AY32">
         <v>1.23</v>
       </c>
       <c r="AZ32">
-        <v>1.68</v>
+        <v>2.43</v>
       </c>
       <c r="BA32">
-        <v>2.5</v>
+        <v>1.89</v>
       </c>
       <c r="BB32">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="BC32">
-        <v>2.25</v>
+        <v>2.59</v>
       </c>
       <c r="BD32">
-        <v>3.7</v>
+        <v>2.91</v>
       </c>
       <c r="BE32">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="BF32">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="BG32">
         <v>0</v>
@@ -7060,7 +7060,7 @@
         <v>80</v>
       </c>
       <c r="C34" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D34" t="s">
         <v>105</v>
@@ -7099,133 +7099,133 @@
         <v>188</v>
       </c>
       <c r="P34">
-        <v>4.75</v>
+        <v>1.95</v>
       </c>
       <c r="Q34">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R34">
-        <v>1.72</v>
+        <v>3.79</v>
       </c>
       <c r="S34">
-        <v>6.17</v>
+        <v>2.48</v>
       </c>
       <c r="T34">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="U34">
-        <v>2.45</v>
+        <v>4.1</v>
       </c>
       <c r="V34">
-        <v>1.56</v>
+        <v>1.37</v>
       </c>
       <c r="W34">
-        <v>2.26</v>
+        <v>2.7</v>
       </c>
       <c r="X34">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="Y34">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="Z34">
-        <v>9.1</v>
+        <v>7</v>
       </c>
       <c r="AA34">
         <v>1.03</v>
       </c>
       <c r="AB34">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC34">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="AD34">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="AE34">
-        <v>2.75</v>
+        <v>2.02</v>
       </c>
       <c r="AF34">
-        <v>1.47</v>
+        <v>1.68</v>
       </c>
       <c r="AG34">
-        <v>5.36</v>
+        <v>3.6</v>
       </c>
       <c r="AH34">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AI34">
-        <v>10</v>
+        <v>6.75</v>
       </c>
       <c r="AJ34">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AK34">
-        <v>2.28</v>
+        <v>1.8</v>
       </c>
       <c r="AL34">
-        <v>1.55</v>
+        <v>1.84</v>
       </c>
       <c r="AM34">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AN34">
-        <v>1.1</v>
+        <v>1.75</v>
       </c>
       <c r="AO34">
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AQ34">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AR34">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AS34">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AT34">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AU34">
         <v>2.7</v>
       </c>
       <c r="AV34">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AW34">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AX34">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AY34">
         <v>1.23</v>
       </c>
       <c r="AZ34">
-        <v>2.43</v>
+        <v>1.68</v>
       </c>
       <c r="BA34">
-        <v>1.89</v>
+        <v>2.5</v>
       </c>
       <c r="BB34">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="BC34">
-        <v>2.59</v>
+        <v>2.25</v>
       </c>
       <c r="BD34">
-        <v>2.91</v>
+        <v>3.7</v>
       </c>
       <c r="BE34">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="BF34">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="BG34">
         <v>0</v>
@@ -7654,79 +7654,79 @@
         <v>188</v>
       </c>
       <c r="P37">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q37">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="R37">
-        <v>3.37</v>
+        <v>2.15</v>
       </c>
       <c r="S37">
-        <v>3.01</v>
+        <v>4.43</v>
       </c>
       <c r="T37">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="U37">
-        <v>4.53</v>
+        <v>2.88</v>
       </c>
       <c r="V37">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="W37">
-        <v>2.17</v>
+        <v>2.31</v>
       </c>
       <c r="X37">
-        <v>4.1</v>
+        <v>3.38</v>
       </c>
       <c r="Y37">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="Z37">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="AA37">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AB37">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AC37">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AD37">
-        <v>2.09</v>
+        <v>2.46</v>
       </c>
       <c r="AE37">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="AF37">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AG37">
-        <v>6.35</v>
+        <v>5.1</v>
       </c>
       <c r="AH37">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AI37">
-        <v>10.5</v>
+        <v>8.5</v>
       </c>
       <c r="AJ37">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK37">
-        <v>2.4</v>
+        <v>2.04</v>
       </c>
       <c r="AL37">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AM37">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AN37">
-        <v>1.54</v>
+        <v>1.29</v>
       </c>
       <c r="AO37">
         <v>0</v>
@@ -7735,52 +7735,52 @@
         <v>1.39</v>
       </c>
       <c r="AQ37">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AR37">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="AS37">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="AT37">
-        <v>4.36</v>
+        <v>4.15</v>
       </c>
       <c r="AU37">
-        <v>2.57</v>
+        <v>2.66</v>
       </c>
       <c r="AV37">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AW37">
         <v>1.6</v>
       </c>
       <c r="AX37">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AY37">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AZ37">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="BA37">
-        <v>2.39</v>
+        <v>2.12</v>
       </c>
       <c r="BB37">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="BC37">
-        <v>3.12</v>
+        <v>2.59</v>
       </c>
       <c r="BD37">
-        <v>2.53</v>
+        <v>2.96</v>
       </c>
       <c r="BE37">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="BF37">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="BG37">
         <v>0</v>
@@ -7839,79 +7839,79 @@
         <v>188</v>
       </c>
       <c r="P38">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q38">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="R38">
-        <v>2.15</v>
+        <v>3.37</v>
       </c>
       <c r="S38">
-        <v>4.43</v>
+        <v>3.01</v>
       </c>
       <c r="T38">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="U38">
-        <v>2.88</v>
+        <v>4.53</v>
       </c>
       <c r="V38">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="W38">
-        <v>2.31</v>
+        <v>2.17</v>
       </c>
       <c r="X38">
-        <v>3.38</v>
+        <v>4.1</v>
       </c>
       <c r="Y38">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="Z38">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA38">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AB38">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AC38">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AD38">
-        <v>2.46</v>
+        <v>2.09</v>
       </c>
       <c r="AE38">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="AF38">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="AG38">
-        <v>5.1</v>
+        <v>6.35</v>
       </c>
       <c r="AH38">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AI38">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="AJ38">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK38">
-        <v>2.04</v>
+        <v>2.4</v>
       </c>
       <c r="AL38">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AM38">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="AN38">
-        <v>1.29</v>
+        <v>1.54</v>
       </c>
       <c r="AO38">
         <v>0</v>
@@ -7920,52 +7920,52 @@
         <v>1.39</v>
       </c>
       <c r="AQ38">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AR38">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="AS38">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="AT38">
-        <v>4.15</v>
+        <v>4.36</v>
       </c>
       <c r="AU38">
-        <v>2.66</v>
+        <v>2.57</v>
       </c>
       <c r="AV38">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AW38">
         <v>1.6</v>
       </c>
       <c r="AX38">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AY38">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AZ38">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="BA38">
-        <v>2.12</v>
+        <v>2.39</v>
       </c>
       <c r="BB38">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="BC38">
-        <v>2.59</v>
+        <v>3.12</v>
       </c>
       <c r="BD38">
-        <v>2.96</v>
+        <v>2.53</v>
       </c>
       <c r="BE38">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="BF38">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="BG38">
         <v>0</v>

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -355,36 +355,36 @@
     <t>Madura United</t>
   </si>
   <si>
+    <t>Ethiopia Nigd Bank</t>
+  </si>
+  <si>
     <t>FC Seoul</t>
   </si>
   <si>
-    <t>Ethiopia Nigd Bank</t>
-  </si>
-  <si>
     <t>Qingdao Youth Island</t>
   </si>
   <si>
     <t>Tanjong Pagar</t>
   </si>
   <si>
+    <t>Shandong Luneng</t>
+  </si>
+  <si>
     <t>Shenyang Urban</t>
   </si>
   <si>
-    <t>Shandong Luneng</t>
+    <t>Borneo</t>
+  </si>
+  <si>
+    <t>Karvan FK</t>
   </si>
   <si>
     <t>Dire Dawa Kenema</t>
   </si>
   <si>
-    <t>Karvan FK</t>
-  </si>
-  <si>
     <t>Chongqing Tongliang Long</t>
   </si>
   <si>
-    <t>Borneo</t>
-  </si>
-  <si>
     <t>Mekelle Kenema</t>
   </si>
   <si>
@@ -415,28 +415,31 @@
     <t>Maccabi Tel Aviv</t>
   </si>
   <si>
+    <t>Bani Yas</t>
+  </si>
+  <si>
     <t>Dibba Al Fujairah</t>
   </si>
   <si>
     <t>Al Ittihad Kalba</t>
   </si>
   <si>
-    <t>Bani Yas</t>
+    <t>Smouha SC</t>
   </si>
   <si>
     <t>Al Ahly</t>
   </si>
   <si>
-    <t>Smouha SC</t>
+    <t>Lokomotiv Sofia 1929</t>
+  </si>
+  <si>
+    <t>Falkenberg</t>
   </si>
   <si>
     <t>Ceramica Cleopatra</t>
   </si>
   <si>
-    <t>Lokomotiv Sofia 1929</t>
-  </si>
-  <si>
-    <t>Falkenberg</t>
+    <t>Stellenbosch</t>
   </si>
   <si>
     <t>Magesi</t>
@@ -448,9 +451,6 @@
     <t>Siwelele</t>
   </si>
   <si>
-    <t>Stellenbosch</t>
-  </si>
-  <si>
     <t>Al Khaleej</t>
   </si>
   <si>
@@ -478,36 +478,36 @@
     <t>Bali United</t>
   </si>
   <si>
+    <t>Kedus Giorgis</t>
+  </si>
+  <si>
     <t>Anyang</t>
   </si>
   <si>
-    <t>Kedus Giorgis</t>
-  </si>
-  <si>
     <t>Tianjin Teda</t>
   </si>
   <si>
     <t>Hougang United</t>
   </si>
   <si>
+    <t>Shanghai Shenhua</t>
+  </si>
+  <si>
     <t>Chengdu Better City FC</t>
   </si>
   <si>
-    <t>Shanghai Shenhua</t>
+    <t>Persita</t>
+  </si>
+  <si>
+    <t>Neftçi</t>
   </si>
   <si>
     <t>Ethiopia Bunna</t>
   </si>
   <si>
-    <t>Neftçi</t>
-  </si>
-  <si>
     <t>Henan Jianye</t>
   </si>
   <si>
-    <t>Persita</t>
-  </si>
-  <si>
     <t>Arba Minch Kenema</t>
   </si>
   <si>
@@ -538,25 +538,28 @@
     <t>Hapoel Petah Tikva</t>
   </si>
   <si>
+    <t>Al Dhafra</t>
+  </si>
+  <si>
     <t>Al Bataeh</t>
   </si>
   <si>
-    <t>Al Dhafra</t>
+    <t>Zamalek</t>
   </si>
   <si>
     <t>ENPPI</t>
   </si>
   <si>
-    <t>Zamalek</t>
+    <t>Botev Vratsa</t>
+  </si>
+  <si>
+    <t>Norrköping</t>
   </si>
   <si>
     <t>Pyramids FC</t>
   </si>
   <si>
-    <t>Botev Vratsa</t>
-  </si>
-  <si>
-    <t>Norrköping</t>
+    <t>Orlando Pirates</t>
   </si>
   <si>
     <t>Orbit College</t>
@@ -566,9 +569,6 @@
   </si>
   <si>
     <t>Durban City</t>
-  </si>
-  <si>
-    <t>Orlando Pirates</t>
   </si>
   <si>
     <t>Al Hilal</t>
@@ -1179,13 +1179,13 @@
         <v>188</v>
       </c>
       <c r="P2">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q2">
         <v>3</v>
       </c>
       <c r="R2">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG2">
         <v>0</v>
@@ -1364,22 +1364,22 @@
         <v>188</v>
       </c>
       <c r="P3">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="Q3">
-        <v>4.2</v>
+        <v>4.63</v>
       </c>
       <c r="R3">
-        <v>6.5</v>
+        <v>9.44</v>
       </c>
       <c r="S3">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="T3">
         <v>2.28</v>
       </c>
       <c r="U3">
-        <v>7.95</v>
+        <v>8.15</v>
       </c>
       <c r="V3">
         <v>1.38</v>
@@ -1403,16 +1403,16 @@
         <v>1</v>
       </c>
       <c r="AC3">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AD3">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="AE3">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AF3">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG3">
         <v>3.24</v>
@@ -1427,61 +1427,61 @@
         <v>1.06</v>
       </c>
       <c r="AK3">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="AL3">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AM3">
         <v>1.17</v>
       </c>
       <c r="AN3">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="AO3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AQ3">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AR3">
-        <v>3.01</v>
+        <v>3.12</v>
       </c>
       <c r="AS3">
         <v>3.34</v>
       </c>
       <c r="AT3">
-        <v>4.97</v>
+        <v>5.2</v>
       </c>
       <c r="AU3">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="AV3">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AW3">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AX3">
         <v>1.24</v>
       </c>
       <c r="AY3">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AZ3">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="BA3">
-        <v>5.49</v>
+        <v>7.5</v>
       </c>
       <c r="BB3">
         <v>1.22</v>
       </c>
       <c r="BC3">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="BD3">
         <v>3.66</v>
@@ -1549,22 +1549,22 @@
         <v>188</v>
       </c>
       <c r="P4">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="Q4">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R4">
         <v>2.83</v>
       </c>
       <c r="S4">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="T4">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="U4">
-        <v>4.12</v>
+        <v>3.65</v>
       </c>
       <c r="V4">
         <v>1.44</v>
@@ -1579,7 +1579,7 @@
         <v>1.33</v>
       </c>
       <c r="Z4">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="AA4">
         <v>1.03</v>
@@ -1597,10 +1597,10 @@
         <v>2.1</v>
       </c>
       <c r="AF4">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG4">
-        <v>3.54</v>
+        <v>3.78</v>
       </c>
       <c r="AH4">
         <v>1.22</v>
@@ -1612,49 +1612,49 @@
         <v>1.04</v>
       </c>
       <c r="AK4">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AL4">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AM4">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AN4">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AO4">
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="AQ4">
-        <v>1.76</v>
+        <v>1.96</v>
       </c>
       <c r="AR4">
-        <v>2.23</v>
+        <v>3.25</v>
       </c>
       <c r="AS4">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>5.47</v>
       </c>
       <c r="AU4">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="AV4">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AW4">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="AX4">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AY4">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AZ4">
         <v>1.72</v>
@@ -1663,13 +1663,13 @@
         <v>2.3</v>
       </c>
       <c r="BB4">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BC4">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="BD4">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="BE4">
         <v>1.59</v>
@@ -1743,25 +1743,25 @@
         <v>0</v>
       </c>
       <c r="S5">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="T5">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="U5">
-        <v>2.88</v>
+        <v>3.24</v>
       </c>
       <c r="V5">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="W5">
-        <v>2.77</v>
+        <v>2.94</v>
       </c>
       <c r="X5">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="Y5">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="Z5">
         <v>7.5</v>
@@ -1773,28 +1773,28 @@
         <v>1.02</v>
       </c>
       <c r="AC5">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AD5">
-        <v>3.37</v>
+        <v>3.18</v>
       </c>
       <c r="AE5">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="AF5">
         <v>1.8</v>
       </c>
       <c r="AG5">
-        <v>3.38</v>
+        <v>3.48</v>
       </c>
       <c r="AH5">
         <v>1.24</v>
       </c>
       <c r="AI5">
-        <v>6.75</v>
+        <v>6.73</v>
       </c>
       <c r="AJ5">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AK5">
         <v>1.73</v>
@@ -1803,7 +1803,7 @@
         <v>2</v>
       </c>
       <c r="AM5">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AN5">
         <v>1.46</v>
@@ -1812,7 +1812,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AQ5">
         <v>1.64</v>
@@ -1821,25 +1821,25 @@
         <v>2.02</v>
       </c>
       <c r="AS5">
-        <v>2.6</v>
+        <v>2.79</v>
       </c>
       <c r="AT5">
-        <v>3.45</v>
+        <v>3.96</v>
       </c>
       <c r="AU5">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AV5">
         <v>2.1</v>
       </c>
       <c r="AW5">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AX5">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AY5">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AZ5">
         <v>1.81</v>
@@ -1919,31 +1919,31 @@
         <v>188</v>
       </c>
       <c r="P6">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="Q6">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R6">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="S6">
         <v>2.77</v>
       </c>
       <c r="T6">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="U6">
-        <v>4.76</v>
+        <v>3.79</v>
       </c>
       <c r="V6">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W6">
-        <v>2.34</v>
+        <v>2.43</v>
       </c>
       <c r="X6">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="Y6">
         <v>1.27</v>
@@ -1964,19 +1964,19 @@
         <v>2.51</v>
       </c>
       <c r="AE6">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AF6">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG6">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AH6">
         <v>1.15</v>
       </c>
       <c r="AI6">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AJ6">
         <v>1.01</v>
@@ -1991,58 +1991,58 @@
         <v>1.33</v>
       </c>
       <c r="AN6">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AO6">
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AQ6">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="AR6">
-        <v>2.35</v>
+        <v>3.14</v>
       </c>
       <c r="AS6">
-        <v>3.1</v>
+        <v>3.48</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="AU6">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="AV6">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AW6">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AX6">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AY6">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AZ6">
         <v>1.65</v>
       </c>
       <c r="BA6">
-        <v>2.43</v>
+        <v>3.02</v>
       </c>
       <c r="BB6">
         <v>1.33</v>
       </c>
       <c r="BC6">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="BD6">
         <v>3.04</v>
       </c>
       <c r="BE6">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="BF6">
         <v>1.08</v>
@@ -2250,10 +2250,10 @@
         <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E8" t="s">
         <v>113</v>
@@ -2289,133 +2289,133 @@
         <v>188</v>
       </c>
       <c r="P8">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R8">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>5.42</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="X8">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Y8">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA8">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC8">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD8">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AE8">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AH8">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK8">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AL8">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN8">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AO8">
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ8">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR8">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AS8">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT8">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AU8">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AV8">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AW8">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AX8">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY8">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ8">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BA8">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BB8">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC8">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="BD8">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE8">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="BF8">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG8">
         <v>0</v>
@@ -2435,10 +2435,10 @@
         <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E9" t="s">
         <v>114</v>
@@ -2474,133 +2474,133 @@
         <v>188</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AO9">
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU9">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AV9">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AX9">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ9">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BA9">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BD9">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE9">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG9">
         <v>0</v>
@@ -2668,10 +2668,10 @@
         <v>0</v>
       </c>
       <c r="S10">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="T10">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="U10">
         <v>3.98</v>
@@ -2683,31 +2683,31 @@
         <v>2.66</v>
       </c>
       <c r="X10">
-        <v>3.01</v>
+        <v>2.85</v>
       </c>
       <c r="Y10">
         <v>1.36</v>
       </c>
       <c r="Z10">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="AA10">
         <v>1.04</v>
       </c>
       <c r="AB10">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AC10">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AD10">
-        <v>3.29</v>
+        <v>3.04</v>
       </c>
       <c r="AE10">
         <v>2.03</v>
       </c>
       <c r="AF10">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AG10">
         <v>3.28</v>
@@ -2716,7 +2716,7 @@
         <v>1.25</v>
       </c>
       <c r="AI10">
-        <v>6.25</v>
+        <v>6.68</v>
       </c>
       <c r="AJ10">
         <v>1.06</v>
@@ -2731,58 +2731,58 @@
         <v>1.32</v>
       </c>
       <c r="AN10">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AO10">
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AQ10">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="AR10">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AS10">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="AT10">
-        <v>3.08</v>
+        <v>2.86</v>
       </c>
       <c r="AU10">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="AV10">
-        <v>2.49</v>
+        <v>2.67</v>
       </c>
       <c r="AW10">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="AX10">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AY10">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AZ10">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="BA10">
-        <v>3.34</v>
+        <v>2.7</v>
       </c>
       <c r="BB10">
         <v>1.24</v>
       </c>
       <c r="BC10">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="BD10">
         <v>3.44</v>
       </c>
       <c r="BE10">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="BF10">
         <v>1.13</v>
@@ -3029,133 +3029,133 @@
         <v>188</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S12">
-        <v>5.1</v>
+        <v>3</v>
       </c>
       <c r="T12">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="U12">
-        <v>2.14</v>
+        <v>2.81</v>
       </c>
       <c r="V12">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="W12">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="X12">
-        <v>2.62</v>
+        <v>2.08</v>
       </c>
       <c r="Y12">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="Z12">
-        <v>6.2</v>
+        <v>4.45</v>
       </c>
       <c r="AA12">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AB12">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AC12">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AD12">
-        <v>3.5</v>
+        <v>5.65</v>
       </c>
       <c r="AE12">
+        <v>1.44</v>
+      </c>
+      <c r="AF12">
+        <v>2.65</v>
+      </c>
+      <c r="AG12">
+        <v>2.06</v>
+      </c>
+      <c r="AH12">
+        <v>1.73</v>
+      </c>
+      <c r="AI12">
+        <v>3.33</v>
+      </c>
+      <c r="AJ12">
+        <v>1.3</v>
+      </c>
+      <c r="AK12">
+        <v>1.36</v>
+      </c>
+      <c r="AL12">
+        <v>2.9</v>
+      </c>
+      <c r="AM12">
+        <v>1.28</v>
+      </c>
+      <c r="AN12">
+        <v>1.44</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>1.11</v>
+      </c>
+      <c r="AQ12">
+        <v>1.26</v>
+      </c>
+      <c r="AR12">
+        <v>1.65</v>
+      </c>
+      <c r="AS12">
         <v>1.85</v>
       </c>
-      <c r="AF12">
-        <v>1.97</v>
-      </c>
-      <c r="AG12">
-        <v>3.01</v>
-      </c>
-      <c r="AH12">
-        <v>1.31</v>
-      </c>
-      <c r="AI12">
-        <v>5.5</v>
-      </c>
-      <c r="AJ12">
+      <c r="AT12">
+        <v>2.32</v>
+      </c>
+      <c r="AU12">
+        <v>4.84</v>
+      </c>
+      <c r="AV12">
+        <v>3.19</v>
+      </c>
+      <c r="AW12">
+        <v>2.44</v>
+      </c>
+      <c r="AX12">
+        <v>1.91</v>
+      </c>
+      <c r="AY12">
+        <v>1.52</v>
+      </c>
+      <c r="AZ12">
+        <v>1.93</v>
+      </c>
+      <c r="BA12">
+        <v>2.09</v>
+      </c>
+      <c r="BB12">
         <v>1.08</v>
       </c>
-      <c r="AK12">
-        <v>1.85</v>
-      </c>
-      <c r="AL12">
-        <v>1.85</v>
-      </c>
-      <c r="AM12">
-        <v>1.24</v>
-      </c>
-      <c r="AN12">
-        <v>1.16</v>
-      </c>
-      <c r="AO12">
-        <v>0</v>
-      </c>
-      <c r="AP12">
-        <v>0</v>
-      </c>
-      <c r="AQ12">
-        <v>0</v>
-      </c>
-      <c r="AR12">
-        <v>0</v>
-      </c>
-      <c r="AS12">
-        <v>0</v>
-      </c>
-      <c r="AT12">
-        <v>0</v>
-      </c>
-      <c r="AU12">
-        <v>0</v>
-      </c>
-      <c r="AV12">
-        <v>0</v>
-      </c>
-      <c r="AW12">
-        <v>0</v>
-      </c>
-      <c r="AX12">
-        <v>0</v>
-      </c>
-      <c r="AY12">
-        <v>0</v>
-      </c>
-      <c r="AZ12">
-        <v>0</v>
-      </c>
-      <c r="BA12">
-        <v>0</v>
-      </c>
-      <c r="BB12">
-        <v>1.19</v>
-      </c>
       <c r="BC12">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="BD12">
-        <v>3.9</v>
+        <v>5.7</v>
       </c>
       <c r="BE12">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="BF12">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="BG12">
         <v>0</v>
@@ -3214,133 +3214,133 @@
         <v>188</v>
       </c>
       <c r="P13">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q13">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R13">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S13">
-        <v>3.13</v>
+        <v>5</v>
       </c>
       <c r="T13">
+        <v>2.24</v>
+      </c>
+      <c r="U13">
+        <v>2.19</v>
+      </c>
+      <c r="V13">
+        <v>1.33</v>
+      </c>
+      <c r="W13">
+        <v>2.95</v>
+      </c>
+      <c r="X13">
+        <v>2.5</v>
+      </c>
+      <c r="Y13">
+        <v>1.42</v>
+      </c>
+      <c r="Z13">
+        <v>6.2</v>
+      </c>
+      <c r="AA13">
+        <v>1.06</v>
+      </c>
+      <c r="AB13">
+        <v>1.05</v>
+      </c>
+      <c r="AC13">
+        <v>1.22</v>
+      </c>
+      <c r="AD13">
+        <v>3.5</v>
+      </c>
+      <c r="AE13">
+        <v>1.82</v>
+      </c>
+      <c r="AF13">
+        <v>1.94</v>
+      </c>
+      <c r="AG13">
+        <v>3</v>
+      </c>
+      <c r="AH13">
+        <v>1.31</v>
+      </c>
+      <c r="AI13">
+        <v>5.5</v>
+      </c>
+      <c r="AJ13">
+        <v>1.08</v>
+      </c>
+      <c r="AK13">
+        <v>1.81</v>
+      </c>
+      <c r="AL13">
+        <v>1.9</v>
+      </c>
+      <c r="AM13">
+        <v>1.24</v>
+      </c>
+      <c r="AN13">
+        <v>1.16</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>1.19</v>
+      </c>
+      <c r="AQ13">
+        <v>1.38</v>
+      </c>
+      <c r="AR13">
+        <v>1.69</v>
+      </c>
+      <c r="AS13">
+        <v>2.11</v>
+      </c>
+      <c r="AT13">
+        <v>2.84</v>
+      </c>
+      <c r="AU13">
+        <v>3.72</v>
+      </c>
+      <c r="AV13">
         <v>2.59</v>
       </c>
-      <c r="U13">
-        <v>2.81</v>
-      </c>
-      <c r="V13">
+      <c r="AW13">
+        <v>2.02</v>
+      </c>
+      <c r="AX13">
+        <v>1.6</v>
+      </c>
+      <c r="AY13">
+        <v>1.34</v>
+      </c>
+      <c r="AZ13">
+        <v>5.03</v>
+      </c>
+      <c r="BA13">
+        <v>1.29</v>
+      </c>
+      <c r="BB13">
         <v>1.22</v>
       </c>
-      <c r="W13">
-        <v>3.6</v>
-      </c>
-      <c r="X13">
-        <v>2.1</v>
-      </c>
-      <c r="Y13">
+      <c r="BC13">
+        <v>2.05</v>
+      </c>
+      <c r="BD13">
+        <v>3.9</v>
+      </c>
+      <c r="BE13">
         <v>1.71</v>
       </c>
-      <c r="Z13">
-        <v>4.45</v>
-      </c>
-      <c r="AA13">
-        <v>1.15</v>
-      </c>
-      <c r="AB13">
-        <v>1.02</v>
-      </c>
-      <c r="AC13">
-        <v>1.13</v>
-      </c>
-      <c r="AD13">
-        <v>5.81</v>
-      </c>
-      <c r="AE13">
-        <v>1.39</v>
-      </c>
-      <c r="AF13">
-        <v>2.59</v>
-      </c>
-      <c r="AG13">
-        <v>2.09</v>
-      </c>
-      <c r="AH13">
-        <v>1.76</v>
-      </c>
-      <c r="AI13">
-        <v>3.28</v>
-      </c>
-      <c r="AJ13">
-        <v>1.25</v>
-      </c>
-      <c r="AK13">
-        <v>1.36</v>
-      </c>
-      <c r="AL13">
-        <v>2.84</v>
-      </c>
-      <c r="AM13">
-        <v>1.28</v>
-      </c>
-      <c r="AN13">
-        <v>1.44</v>
-      </c>
-      <c r="AO13">
-        <v>0</v>
-      </c>
-      <c r="AP13">
-        <v>1.12</v>
-      </c>
-      <c r="AQ13">
-        <v>1.26</v>
-      </c>
-      <c r="AR13">
-        <v>1.66</v>
-      </c>
-      <c r="AS13">
-        <v>1.86</v>
-      </c>
-      <c r="AT13">
-        <v>2.29</v>
-      </c>
-      <c r="AU13">
-        <v>4.8</v>
-      </c>
-      <c r="AV13">
-        <v>3.2</v>
-      </c>
-      <c r="AW13">
-        <v>2.32</v>
-      </c>
-      <c r="AX13">
-        <v>1.84</v>
-      </c>
-      <c r="AY13">
-        <v>1.57</v>
-      </c>
-      <c r="AZ13">
-        <v>1.84</v>
-      </c>
-      <c r="BA13">
-        <v>2.21</v>
-      </c>
-      <c r="BB13">
-        <v>1.12</v>
-      </c>
-      <c r="BC13">
-        <v>1.62</v>
-      </c>
-      <c r="BD13">
-        <v>5.3</v>
-      </c>
-      <c r="BE13">
-        <v>2.15</v>
-      </c>
       <c r="BF13">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="BG13">
         <v>0</v>
@@ -3360,7 +3360,7 @@
         <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D14" t="s">
         <v>105</v>
@@ -3399,133 +3399,133 @@
         <v>188</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>5.59</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AO14">
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AU14">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AV14">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AW14">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX14">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY14">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ14">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BA14">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="BB14">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC14">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BD14">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="BE14">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BF14">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG14">
         <v>0</v>
@@ -3730,10 +3730,10 @@
         <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E16" t="s">
         <v>121</v>
@@ -3778,70 +3778,70 @@
         <v>0</v>
       </c>
       <c r="S16">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="V16">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W16">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="X16">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z16">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC16">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD16">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AE16">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AH16">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI16">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AJ16">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK16">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL16">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AM16">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN16">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AO16">
         <v>0</v>
@@ -3883,19 +3883,19 @@
         <v>0</v>
       </c>
       <c r="BB16">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC16">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="BD16">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="BE16">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BF16">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG16">
         <v>0</v>
@@ -3915,10 +3915,10 @@
         <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E17" t="s">
         <v>122</v>
@@ -3954,133 +3954,133 @@
         <v>188</v>
       </c>
       <c r="P17">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R17">
-        <v>5.59</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>5.61</v>
+        <v>0</v>
       </c>
       <c r="V17">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W17">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X17">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y17">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z17">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA17">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC17">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD17">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="AE17">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AG17">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AH17">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI17">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AJ17">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK17">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM17">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AN17">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AO17">
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AQ17">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AR17">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AS17">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT17">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AU17">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AV17">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AW17">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AX17">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AY17">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ17">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BA17">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="BB17">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC17">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BD17">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="BE17">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BF17">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG17">
         <v>0</v>
@@ -5064,13 +5064,13 @@
         <v>188</v>
       </c>
       <c r="P23">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="Q23">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R23">
-        <v>4.36</v>
+        <v>4.33</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -5804,73 +5804,73 @@
         <v>188</v>
       </c>
       <c r="P27">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Q27">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="R27">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="S27">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="T27">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="U27">
-        <v>6.71</v>
+        <v>6.66</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X27">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="Y27">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC27">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AD27">
-        <v>5.4</v>
+        <v>4.85</v>
       </c>
       <c r="AE27">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AF27">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="AG27">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="AH27">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="AI27">
-        <v>3.83</v>
+        <v>3.96</v>
       </c>
       <c r="AJ27">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK27">
         <v>1.63</v>
       </c>
       <c r="AL27">
-        <v>2.07</v>
+        <v>1.97</v>
       </c>
       <c r="AM27">
         <v>1.12</v>
@@ -5882,55 +5882,55 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AU27">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AV27">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AW27">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AX27">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AY27">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ27">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BA27">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BB27">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC27">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="BD27">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BE27">
         <v>2.02</v>
       </c>
       <c r="BF27">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BG27">
         <v>0</v>
@@ -6144,7 +6144,7 @@
         <v>134</v>
       </c>
       <c r="F29" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -6329,7 +6329,7 @@
         <v>135</v>
       </c>
       <c r="F30" t="s">
-        <v>175</v>
+        <v>145</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -6544,133 +6544,133 @@
         <v>188</v>
       </c>
       <c r="P31">
-        <v>1.42</v>
+        <v>5.48</v>
       </c>
       <c r="Q31">
-        <v>3.85</v>
+        <v>3.12</v>
       </c>
       <c r="R31">
-        <v>7.4</v>
+        <v>1.7</v>
       </c>
       <c r="S31">
-        <v>2.01</v>
+        <v>6</v>
       </c>
       <c r="T31">
-        <v>2.09</v>
+        <v>1.87</v>
       </c>
       <c r="U31">
-        <v>7.7</v>
+        <v>2.42</v>
       </c>
       <c r="V31">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="W31">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="X31">
-        <v>2.96</v>
+        <v>3.5</v>
       </c>
       <c r="Y31">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="Z31">
-        <v>7.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA31">
         <v>1.03</v>
       </c>
       <c r="AB31">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AC31">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="AD31">
-        <v>3.01</v>
+        <v>2.38</v>
       </c>
       <c r="AE31">
-        <v>2.06</v>
+        <v>2.66</v>
       </c>
       <c r="AF31">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="AG31">
-        <v>3.75</v>
+        <v>5.25</v>
       </c>
       <c r="AH31">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AI31">
-        <v>6.75</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AJ31">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AK31">
         <v>2.3</v>
       </c>
       <c r="AL31">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AM31">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AN31">
-        <v>2.57</v>
+        <v>1.1</v>
       </c>
       <c r="AO31">
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AQ31">
-        <v>1.46</v>
+        <v>1.69</v>
       </c>
       <c r="AR31">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="AS31">
-        <v>2.33</v>
+        <v>2.88</v>
       </c>
       <c r="AT31">
-        <v>2.95</v>
+        <v>3.7</v>
       </c>
       <c r="AU31">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="AV31">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AW31">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AX31">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="AY31">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="AZ31">
-        <v>1.3</v>
+        <v>2.39</v>
       </c>
       <c r="BA31">
-        <v>4.2</v>
+        <v>1.89</v>
       </c>
       <c r="BB31">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="BC31">
-        <v>2.24</v>
+        <v>2.48</v>
       </c>
       <c r="BD31">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="BE31">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="BF31">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BG31">
         <v>0</v>
@@ -6729,133 +6729,133 @@
         <v>188</v>
       </c>
       <c r="P32">
-        <v>4.75</v>
+        <v>1.4</v>
       </c>
       <c r="Q32">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="R32">
-        <v>1.72</v>
+        <v>6.5</v>
       </c>
       <c r="S32">
-        <v>6.17</v>
+        <v>1.88</v>
       </c>
       <c r="T32">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="U32">
-        <v>2.45</v>
+        <v>8.1</v>
       </c>
       <c r="V32">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="W32">
-        <v>2.26</v>
+        <v>2.56</v>
       </c>
       <c r="X32">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="Y32">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="Z32">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="AA32">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AB32">
         <v>1.06</v>
       </c>
       <c r="AC32">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="AD32">
+        <v>2.92</v>
+      </c>
+      <c r="AE32">
+        <v>2.02</v>
+      </c>
+      <c r="AF32">
+        <v>1.71</v>
+      </c>
+      <c r="AG32">
+        <v>3.42</v>
+      </c>
+      <c r="AH32">
+        <v>1.27</v>
+      </c>
+      <c r="AI32">
+        <v>6.45</v>
+      </c>
+      <c r="AJ32">
+        <v>1.05</v>
+      </c>
+      <c r="AK32">
+        <v>2.25</v>
+      </c>
+      <c r="AL32">
+        <v>1.6</v>
+      </c>
+      <c r="AM32">
+        <v>1.16</v>
+      </c>
+      <c r="AN32">
+        <v>2.5</v>
+      </c>
+      <c r="AO32">
+        <v>0</v>
+      </c>
+      <c r="AP32">
+        <v>1.24</v>
+      </c>
+      <c r="AQ32">
+        <v>1.52</v>
+      </c>
+      <c r="AR32">
+        <v>1.83</v>
+      </c>
+      <c r="AS32">
+        <v>2.33</v>
+      </c>
+      <c r="AT32">
+        <v>3.14</v>
+      </c>
+      <c r="AU32">
+        <v>3.34</v>
+      </c>
+      <c r="AV32">
         <v>2.38</v>
       </c>
-      <c r="AE32">
-        <v>2.75</v>
-      </c>
-      <c r="AF32">
-        <v>1.47</v>
-      </c>
-      <c r="AG32">
-        <v>5.36</v>
-      </c>
-      <c r="AH32">
+      <c r="AW32">
+        <v>1.83</v>
+      </c>
+      <c r="AX32">
+        <v>1.48</v>
+      </c>
+      <c r="AY32">
+        <v>1.27</v>
+      </c>
+      <c r="AZ32">
+        <v>1.3</v>
+      </c>
+      <c r="BA32">
+        <v>4.32</v>
+      </c>
+      <c r="BB32">
+        <v>1.22</v>
+      </c>
+      <c r="BC32">
+        <v>2.3</v>
+      </c>
+      <c r="BD32">
+        <v>3.7</v>
+      </c>
+      <c r="BE32">
+        <v>1.53</v>
+      </c>
+      <c r="BF32">
         <v>1.12</v>
-      </c>
-      <c r="AI32">
-        <v>10</v>
-      </c>
-      <c r="AJ32">
-        <v>1.02</v>
-      </c>
-      <c r="AK32">
-        <v>2.28</v>
-      </c>
-      <c r="AL32">
-        <v>1.55</v>
-      </c>
-      <c r="AM32">
-        <v>1.28</v>
-      </c>
-      <c r="AN32">
-        <v>1.1</v>
-      </c>
-      <c r="AO32">
-        <v>0</v>
-      </c>
-      <c r="AP32">
-        <v>1.36</v>
-      </c>
-      <c r="AQ32">
-        <v>1.69</v>
-      </c>
-      <c r="AR32">
-        <v>2.14</v>
-      </c>
-      <c r="AS32">
-        <v>2.88</v>
-      </c>
-      <c r="AT32">
-        <v>3.7</v>
-      </c>
-      <c r="AU32">
-        <v>2.7</v>
-      </c>
-      <c r="AV32">
-        <v>2</v>
-      </c>
-      <c r="AW32">
-        <v>1.57</v>
-      </c>
-      <c r="AX32">
-        <v>1.32</v>
-      </c>
-      <c r="AY32">
-        <v>1.23</v>
-      </c>
-      <c r="AZ32">
-        <v>2.43</v>
-      </c>
-      <c r="BA32">
-        <v>1.89</v>
-      </c>
-      <c r="BB32">
-        <v>1.33</v>
-      </c>
-      <c r="BC32">
-        <v>2.59</v>
-      </c>
-      <c r="BD32">
-        <v>2.91</v>
-      </c>
-      <c r="BE32">
-        <v>1.41</v>
-      </c>
-      <c r="BF32">
-        <v>1.06</v>
       </c>
       <c r="BG32">
         <v>0</v>
@@ -6875,7 +6875,7 @@
         <v>80</v>
       </c>
       <c r="C33" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D33" t="s">
         <v>105</v>
@@ -6914,133 +6914,133 @@
         <v>188</v>
       </c>
       <c r="P33">
-        <v>4.4</v>
+        <v>1.95</v>
       </c>
       <c r="Q33">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="R33">
-        <v>1.8</v>
+        <v>3.79</v>
       </c>
       <c r="S33">
-        <v>5.18</v>
+        <v>2.48</v>
       </c>
       <c r="T33">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="U33">
-        <v>2.46</v>
+        <v>4.1</v>
       </c>
       <c r="V33">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="W33">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="X33">
-        <v>3.32</v>
+        <v>2.88</v>
       </c>
       <c r="Y33">
         <v>1.33</v>
       </c>
       <c r="Z33">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="AA33">
+        <v>1.03</v>
+      </c>
+      <c r="AB33">
         <v>1.02</v>
       </c>
-      <c r="AB33">
-        <v>1.04</v>
-      </c>
       <c r="AC33">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AD33">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="AE33">
+        <v>2.02</v>
+      </c>
+      <c r="AF33">
+        <v>1.68</v>
+      </c>
+      <c r="AG33">
+        <v>3.6</v>
+      </c>
+      <c r="AH33">
+        <v>1.24</v>
+      </c>
+      <c r="AI33">
+        <v>6.75</v>
+      </c>
+      <c r="AJ33">
+        <v>1.07</v>
+      </c>
+      <c r="AK33">
+        <v>1.8</v>
+      </c>
+      <c r="AL33">
+        <v>1.84</v>
+      </c>
+      <c r="AM33">
+        <v>1.27</v>
+      </c>
+      <c r="AN33">
+        <v>1.75</v>
+      </c>
+      <c r="AO33">
+        <v>0</v>
+      </c>
+      <c r="AP33">
+        <v>1.4</v>
+      </c>
+      <c r="AQ33">
+        <v>1.67</v>
+      </c>
+      <c r="AR33">
+        <v>2.1</v>
+      </c>
+      <c r="AS33">
+        <v>2.7</v>
+      </c>
+      <c r="AT33">
+        <v>3.65</v>
+      </c>
+      <c r="AU33">
+        <v>2.7</v>
+      </c>
+      <c r="AV33">
+        <v>2.04</v>
+      </c>
+      <c r="AW33">
+        <v>1.64</v>
+      </c>
+      <c r="AX33">
+        <v>1.38</v>
+      </c>
+      <c r="AY33">
+        <v>1.23</v>
+      </c>
+      <c r="AZ33">
+        <v>1.68</v>
+      </c>
+      <c r="BA33">
+        <v>2.5</v>
+      </c>
+      <c r="BB33">
+        <v>1.23</v>
+      </c>
+      <c r="BC33">
         <v>2.25</v>
       </c>
-      <c r="AF33">
-        <v>1.62</v>
-      </c>
-      <c r="AG33">
-        <v>3.8</v>
-      </c>
-      <c r="AH33">
-        <v>1.19</v>
-      </c>
-      <c r="AI33">
-        <v>7.3</v>
-      </c>
-      <c r="AJ33">
-        <v>1.03</v>
-      </c>
-      <c r="AK33">
-        <v>1.97</v>
-      </c>
-      <c r="AL33">
-        <v>1.73</v>
-      </c>
-      <c r="AM33">
-        <v>1.26</v>
-      </c>
-      <c r="AN33">
-        <v>1.14</v>
-      </c>
-      <c r="AO33">
-        <v>0</v>
-      </c>
-      <c r="AP33">
-        <v>1.28</v>
-      </c>
-      <c r="AQ33">
-        <v>1.53</v>
-      </c>
-      <c r="AR33">
-        <v>1.95</v>
-      </c>
-      <c r="AS33">
-        <v>2.52</v>
-      </c>
-      <c r="AT33">
-        <v>3.48</v>
-      </c>
-      <c r="AU33">
-        <v>3.05</v>
-      </c>
-      <c r="AV33">
-        <v>2.21</v>
-      </c>
-      <c r="AW33">
-        <v>1.73</v>
-      </c>
-      <c r="AX33">
-        <v>1.41</v>
-      </c>
-      <c r="AY33">
-        <v>1.22</v>
-      </c>
-      <c r="AZ33">
-        <v>2.48</v>
-      </c>
-      <c r="BA33">
-        <v>1.84</v>
-      </c>
-      <c r="BB33">
-        <v>1.27</v>
-      </c>
-      <c r="BC33">
-        <v>2.29</v>
-      </c>
       <c r="BD33">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="BE33">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="BF33">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="BG33">
         <v>0</v>
@@ -7060,10 +7060,10 @@
         <v>80</v>
       </c>
       <c r="C34" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D34" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E34" t="s">
         <v>139</v>
@@ -7099,133 +7099,133 @@
         <v>188</v>
       </c>
       <c r="P34">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="Q34">
-        <v>3.25</v>
+        <v>3.54</v>
       </c>
       <c r="R34">
-        <v>3.79</v>
+        <v>2.52</v>
       </c>
       <c r="S34">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="T34">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U34">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="V34">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W34">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X34">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y34">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z34">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA34">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB34">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC34">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD34">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE34">
-        <v>2.02</v>
+        <v>1.66</v>
       </c>
       <c r="AF34">
-        <v>1.68</v>
+        <v>2.15</v>
       </c>
       <c r="AG34">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AH34">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI34">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AJ34">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK34">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL34">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AM34">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN34">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AO34">
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AQ34">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AR34">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS34">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AT34">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AU34">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV34">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AW34">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AX34">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AY34">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ34">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BA34">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BB34">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC34">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD34">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BE34">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BF34">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG34">
         <v>0</v>
@@ -7245,10 +7245,10 @@
         <v>80</v>
       </c>
       <c r="C35" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D35" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E35" t="s">
         <v>140</v>
@@ -7284,133 +7284,133 @@
         <v>188</v>
       </c>
       <c r="P35">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="Q35">
-        <v>3.52</v>
+        <v>3.2</v>
       </c>
       <c r="R35">
-        <v>2.53</v>
+        <v>1.8</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AE35">
-        <v>1.66</v>
+        <v>2.16</v>
       </c>
       <c r="AF35">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AH35">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI35">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL35">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM35">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN35">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AO35">
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ35">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR35">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AS35">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AT35">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AU35">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV35">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AW35">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AX35">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY35">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ35">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BA35">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BB35">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC35">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BD35">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE35">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF35">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG35">
         <v>0</v>
@@ -7469,79 +7469,79 @@
         <v>188</v>
       </c>
       <c r="P36">
-        <v>2.07</v>
+        <v>5.6</v>
       </c>
       <c r="Q36">
-        <v>2.79</v>
+        <v>3.5</v>
       </c>
       <c r="R36">
-        <v>4.05</v>
+        <v>1.5</v>
       </c>
       <c r="S36">
-        <v>2.88</v>
+        <v>7</v>
       </c>
       <c r="T36">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="U36">
-        <v>5.37</v>
+        <v>2.13</v>
       </c>
       <c r="V36">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="W36">
-        <v>2.11</v>
+        <v>2.31</v>
       </c>
       <c r="X36">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="Y36">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z36">
-        <v>8.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA36">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AB36">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AC36">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AD36">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="AE36">
-        <v>2.74</v>
+        <v>2.53</v>
       </c>
       <c r="AF36">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AG36">
-        <v>6.25</v>
+        <v>4.65</v>
       </c>
       <c r="AH36">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AI36">
-        <v>9.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AJ36">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AK36">
-        <v>2.32</v>
+        <v>2.51</v>
       </c>
       <c r="AL36">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AM36">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AN36">
-        <v>1.63</v>
+        <v>1.04</v>
       </c>
       <c r="AO36">
         <v>0</v>
@@ -7550,52 +7550,52 @@
         <v>1.42</v>
       </c>
       <c r="AQ36">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AR36">
+        <v>2.73</v>
+      </c>
+      <c r="AS36">
+        <v>3.04</v>
+      </c>
+      <c r="AT36">
+        <v>4.41</v>
+      </c>
+      <c r="AU36">
         <v>2.7</v>
       </c>
-      <c r="AS36">
-        <v>3</v>
-      </c>
-      <c r="AT36">
-        <v>4.34</v>
-      </c>
-      <c r="AU36">
-        <v>2.58</v>
-      </c>
       <c r="AV36">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AW36">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AX36">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AY36">
         <v>1.13</v>
       </c>
       <c r="AZ36">
-        <v>1.54</v>
+        <v>3.85</v>
       </c>
       <c r="BA36">
-        <v>3.42</v>
+        <v>1.42</v>
       </c>
       <c r="BB36">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="BC36">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="BD36">
-        <v>2.66</v>
+        <v>2.91</v>
       </c>
       <c r="BE36">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BF36">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BG36">
         <v>0</v>
@@ -7654,133 +7654,133 @@
         <v>188</v>
       </c>
       <c r="P37">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="Q37">
+        <v>2.9</v>
+      </c>
+      <c r="R37">
+        <v>3.95</v>
+      </c>
+      <c r="S37">
+        <v>2.88</v>
+      </c>
+      <c r="T37">
+        <v>1.75</v>
+      </c>
+      <c r="U37">
+        <v>5.1</v>
+      </c>
+      <c r="V37">
+        <v>1.64</v>
+      </c>
+      <c r="W37">
+        <v>2.11</v>
+      </c>
+      <c r="X37">
+        <v>3.9</v>
+      </c>
+      <c r="Y37">
+        <v>1.18</v>
+      </c>
+      <c r="Z37">
+        <v>13</v>
+      </c>
+      <c r="AA37">
+        <v>1.02</v>
+      </c>
+      <c r="AB37">
+        <v>1.12</v>
+      </c>
+      <c r="AC37">
+        <v>1.58</v>
+      </c>
+      <c r="AD37">
+        <v>2.25</v>
+      </c>
+      <c r="AE37">
+        <v>2.74</v>
+      </c>
+      <c r="AF37">
+        <v>1.35</v>
+      </c>
+      <c r="AG37">
+        <v>6.33</v>
+      </c>
+      <c r="AH37">
+        <v>1.1</v>
+      </c>
+      <c r="AI37">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AJ37">
+        <v>1.01</v>
+      </c>
+      <c r="AK37">
+        <v>2.3</v>
+      </c>
+      <c r="AL37">
+        <v>1.53</v>
+      </c>
+      <c r="AM37">
+        <v>1.35</v>
+      </c>
+      <c r="AN37">
+        <v>1.63</v>
+      </c>
+      <c r="AO37">
+        <v>0</v>
+      </c>
+      <c r="AP37">
+        <v>1.42</v>
+      </c>
+      <c r="AQ37">
+        <v>1.76</v>
+      </c>
+      <c r="AR37">
+        <v>2.7</v>
+      </c>
+      <c r="AS37">
         <v>3</v>
       </c>
-      <c r="R37">
-        <v>2.15</v>
-      </c>
-      <c r="S37">
-        <v>4.43</v>
-      </c>
-      <c r="T37">
-        <v>1.88</v>
-      </c>
-      <c r="U37">
-        <v>2.88</v>
-      </c>
-      <c r="V37">
-        <v>1.51</v>
-      </c>
-      <c r="W37">
-        <v>2.31</v>
-      </c>
-      <c r="X37">
-        <v>3.38</v>
-      </c>
-      <c r="Y37">
-        <v>1.25</v>
-      </c>
-      <c r="Z37">
-        <v>9.1</v>
-      </c>
-      <c r="AA37">
-        <v>1</v>
-      </c>
-      <c r="AB37">
-        <v>1.05</v>
-      </c>
-      <c r="AC37">
-        <v>1.53</v>
-      </c>
-      <c r="AD37">
-        <v>2.46</v>
-      </c>
-      <c r="AE37">
-        <v>2.65</v>
-      </c>
-      <c r="AF37">
-        <v>1.41</v>
-      </c>
-      <c r="AG37">
-        <v>5.1</v>
-      </c>
-      <c r="AH37">
+      <c r="AT37">
+        <v>4.34</v>
+      </c>
+      <c r="AU37">
+        <v>2.58</v>
+      </c>
+      <c r="AV37">
+        <v>1.95</v>
+      </c>
+      <c r="AW37">
+        <v>1.57</v>
+      </c>
+      <c r="AX37">
+        <v>1.3</v>
+      </c>
+      <c r="AY37">
         <v>1.13</v>
       </c>
-      <c r="AI37">
-        <v>8.5</v>
-      </c>
-      <c r="AJ37">
+      <c r="AZ37">
+        <v>1.52</v>
+      </c>
+      <c r="BA37">
+        <v>3.42</v>
+      </c>
+      <c r="BB37">
+        <v>1.39</v>
+      </c>
+      <c r="BC37">
+        <v>2.7</v>
+      </c>
+      <c r="BD37">
+        <v>2.66</v>
+      </c>
+      <c r="BE37">
+        <v>1.33</v>
+      </c>
+      <c r="BF37">
         <v>1.03</v>
-      </c>
-      <c r="AK37">
-        <v>2.04</v>
-      </c>
-      <c r="AL37">
-        <v>1.68</v>
-      </c>
-      <c r="AM37">
-        <v>1.57</v>
-      </c>
-      <c r="AN37">
-        <v>1.29</v>
-      </c>
-      <c r="AO37">
-        <v>0</v>
-      </c>
-      <c r="AP37">
-        <v>1.39</v>
-      </c>
-      <c r="AQ37">
-        <v>1.72</v>
-      </c>
-      <c r="AR37">
-        <v>2.6</v>
-      </c>
-      <c r="AS37">
-        <v>2.9</v>
-      </c>
-      <c r="AT37">
-        <v>4.15</v>
-      </c>
-      <c r="AU37">
-        <v>2.66</v>
-      </c>
-      <c r="AV37">
-        <v>2</v>
-      </c>
-      <c r="AW37">
-        <v>1.6</v>
-      </c>
-      <c r="AX37">
-        <v>1.32</v>
-      </c>
-      <c r="AY37">
-        <v>1.15</v>
-      </c>
-      <c r="AZ37">
-        <v>2.12</v>
-      </c>
-      <c r="BA37">
-        <v>2.12</v>
-      </c>
-      <c r="BB37">
-        <v>1.32</v>
-      </c>
-      <c r="BC37">
-        <v>2.59</v>
-      </c>
-      <c r="BD37">
-        <v>2.96</v>
-      </c>
-      <c r="BE37">
-        <v>1.41</v>
-      </c>
-      <c r="BF37">
-        <v>1.06</v>
       </c>
       <c r="BG37">
         <v>0</v>
@@ -7839,133 +7839,133 @@
         <v>188</v>
       </c>
       <c r="P38">
-        <v>2.2</v>
+        <v>3.45</v>
       </c>
       <c r="Q38">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="R38">
-        <v>3.37</v>
+        <v>2.15</v>
       </c>
       <c r="S38">
-        <v>3.01</v>
+        <v>3.95</v>
       </c>
       <c r="T38">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="U38">
-        <v>4.53</v>
+        <v>2.9</v>
       </c>
       <c r="V38">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="W38">
-        <v>2.17</v>
+        <v>2.31</v>
       </c>
       <c r="X38">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="Y38">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="Z38">
-        <v>9.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="AA38">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AB38">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AC38">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AD38">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="AE38">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="AF38">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
       <c r="AG38">
-        <v>6.35</v>
+        <v>4.6</v>
       </c>
       <c r="AH38">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AI38">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="AJ38">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK38">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AL38">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AM38">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AN38">
-        <v>1.54</v>
+        <v>1.24</v>
       </c>
       <c r="AO38">
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AQ38">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AR38">
-        <v>2.71</v>
+        <v>2.02</v>
       </c>
       <c r="AS38">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="AT38">
-        <v>4.36</v>
+        <v>3.4</v>
       </c>
       <c r="AU38">
-        <v>2.57</v>
+        <v>2.8</v>
       </c>
       <c r="AV38">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AW38">
         <v>1.6</v>
       </c>
       <c r="AX38">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AY38">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AZ38">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="BA38">
-        <v>2.39</v>
+        <v>2.08</v>
       </c>
       <c r="BB38">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="BC38">
-        <v>3.12</v>
+        <v>2.59</v>
       </c>
       <c r="BD38">
-        <v>2.53</v>
+        <v>2.96</v>
       </c>
       <c r="BE38">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="BF38">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="BG38">
         <v>0</v>
@@ -8024,79 +8024,79 @@
         <v>188</v>
       </c>
       <c r="P39">
-        <v>4.65</v>
+        <v>2.11</v>
       </c>
       <c r="Q39">
+        <v>2.8</v>
+      </c>
+      <c r="R39">
         <v>3.3</v>
       </c>
-      <c r="R39">
-        <v>1.62</v>
-      </c>
       <c r="S39">
-        <v>6.93</v>
+        <v>2.9</v>
       </c>
       <c r="T39">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="U39">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="V39">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="W39">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="X39">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="Y39">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z39">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AA39">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB39">
+        <v>1.12</v>
+      </c>
+      <c r="AC39">
+        <v>1.67</v>
+      </c>
+      <c r="AD39">
+        <v>2.15</v>
+      </c>
+      <c r="AE39">
+        <v>3.1</v>
+      </c>
+      <c r="AF39">
+        <v>1.36</v>
+      </c>
+      <c r="AG39">
+        <v>6.5</v>
+      </c>
+      <c r="AH39">
         <v>1.1</v>
       </c>
-      <c r="AC39">
-        <v>1.53</v>
-      </c>
-      <c r="AD39">
-        <v>2.35</v>
-      </c>
-      <c r="AE39">
-        <v>2.65</v>
-      </c>
-      <c r="AF39">
-        <v>1.45</v>
-      </c>
-      <c r="AG39">
-        <v>4.9</v>
-      </c>
-      <c r="AH39">
-        <v>1.11</v>
-      </c>
       <c r="AI39">
-        <v>8.300000000000001</v>
+        <v>11</v>
       </c>
       <c r="AJ39">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AK39">
         <v>2.4</v>
       </c>
       <c r="AL39">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AM39">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AN39">
-        <v>1.07</v>
+        <v>1.55</v>
       </c>
       <c r="AO39">
         <v>0</v>
@@ -8105,52 +8105,52 @@
         <v>1.42</v>
       </c>
       <c r="AQ39">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AR39">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="AS39">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="AT39">
-        <v>4.41</v>
+        <v>4.36</v>
       </c>
       <c r="AU39">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="AV39">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="AW39">
         <v>1.56</v>
       </c>
       <c r="AX39">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AY39">
         <v>1.13</v>
       </c>
       <c r="AZ39">
-        <v>4.1</v>
+        <v>1.93</v>
       </c>
       <c r="BA39">
-        <v>1.42</v>
+        <v>2.31</v>
       </c>
       <c r="BB39">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="BC39">
-        <v>2.66</v>
+        <v>3.12</v>
       </c>
       <c r="BD39">
-        <v>2.82</v>
+        <v>2.65</v>
       </c>
       <c r="BE39">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="BF39">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="BG39">
         <v>0</v>
@@ -8209,13 +8209,13 @@
         <v>188</v>
       </c>
       <c r="P40">
-        <v>8.5</v>
+        <v>9.9</v>
       </c>
       <c r="Q40">
-        <v>5.5</v>
+        <v>6.39</v>
       </c>
       <c r="R40">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="S40">
         <v>0</v>

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -343,45 +343,45 @@
     <t>Jeonbuk Motors</t>
   </si>
   <si>
+    <t>Gangwon</t>
+  </si>
+  <si>
     <t>Daejeon Citizen</t>
   </si>
   <si>
     <t>Sangju Sangmu</t>
   </si>
   <si>
-    <t>Gangwon</t>
-  </si>
-  <si>
     <t>Madura United</t>
   </si>
   <si>
+    <t>FC Seoul</t>
+  </si>
+  <si>
     <t>Ethiopia Nigd Bank</t>
   </si>
   <si>
-    <t>FC Seoul</t>
-  </si>
-  <si>
     <t>Qingdao Youth Island</t>
   </si>
   <si>
     <t>Tanjong Pagar</t>
   </si>
   <si>
+    <t>Shenyang Urban</t>
+  </si>
+  <si>
     <t>Shandong Luneng</t>
   </si>
   <si>
-    <t>Shenyang Urban</t>
+    <t>Karvan FK</t>
+  </si>
+  <si>
+    <t>Dire Dawa Kenema</t>
   </si>
   <si>
     <t>Borneo</t>
   </si>
   <si>
-    <t>Karvan FK</t>
-  </si>
-  <si>
-    <t>Dire Dawa Kenema</t>
-  </si>
-  <si>
     <t>Chongqing Tongliang Long</t>
   </si>
   <si>
@@ -415,39 +415,39 @@
     <t>Maccabi Tel Aviv</t>
   </si>
   <si>
+    <t>Dibba Al Fujairah</t>
+  </si>
+  <si>
     <t>Bani Yas</t>
   </si>
   <si>
-    <t>Dibba Al Fujairah</t>
-  </si>
-  <si>
     <t>Al Ittihad Kalba</t>
   </si>
   <si>
     <t>Smouha SC</t>
   </si>
   <si>
+    <t>Falkenberg</t>
+  </si>
+  <si>
     <t>Al Ahly</t>
   </si>
   <si>
+    <t>Ceramica Cleopatra</t>
+  </si>
+  <si>
     <t>Lokomotiv Sofia 1929</t>
   </si>
   <si>
-    <t>Falkenberg</t>
-  </si>
-  <si>
-    <t>Ceramica Cleopatra</t>
+    <t>Chippa United</t>
+  </si>
+  <si>
+    <t>Magesi</t>
   </si>
   <si>
     <t>Stellenbosch</t>
   </si>
   <si>
-    <t>Magesi</t>
-  </si>
-  <si>
-    <t>Chippa United</t>
-  </si>
-  <si>
     <t>Siwelele</t>
   </si>
   <si>
@@ -466,45 +466,45 @@
     <t>Gwangju</t>
   </si>
   <si>
+    <t>Pohang Steelers</t>
+  </si>
+  <si>
     <t>Incheon United</t>
   </si>
   <si>
     <t>Ulsan</t>
   </si>
   <si>
-    <t>Pohang Steelers</t>
-  </si>
-  <si>
     <t>Bali United</t>
   </si>
   <si>
+    <t>Anyang</t>
+  </si>
+  <si>
     <t>Kedus Giorgis</t>
   </si>
   <si>
-    <t>Anyang</t>
-  </si>
-  <si>
     <t>Tianjin Teda</t>
   </si>
   <si>
     <t>Hougang United</t>
   </si>
   <si>
+    <t>Chengdu Better City FC</t>
+  </si>
+  <si>
     <t>Shanghai Shenhua</t>
   </si>
   <si>
-    <t>Chengdu Better City FC</t>
+    <t>Neftçi</t>
+  </si>
+  <si>
+    <t>Ethiopia Bunna</t>
   </si>
   <si>
     <t>Persita</t>
   </si>
   <si>
-    <t>Neftçi</t>
-  </si>
-  <si>
-    <t>Ethiopia Bunna</t>
-  </si>
-  <si>
     <t>Henan Jianye</t>
   </si>
   <si>
@@ -538,34 +538,34 @@
     <t>Hapoel Petah Tikva</t>
   </si>
   <si>
+    <t>Al Bataeh</t>
+  </si>
+  <si>
     <t>Al Dhafra</t>
   </si>
   <si>
-    <t>Al Bataeh</t>
-  </si>
-  <si>
     <t>Zamalek</t>
   </si>
   <si>
+    <t>Norrköping</t>
+  </si>
+  <si>
     <t>ENPPI</t>
   </si>
   <si>
+    <t>Pyramids FC</t>
+  </si>
+  <si>
     <t>Botev Vratsa</t>
   </si>
   <si>
-    <t>Norrköping</t>
-  </si>
-  <si>
-    <t>Pyramids FC</t>
+    <t>Sekhukhune United</t>
+  </si>
+  <si>
+    <t>Orbit College</t>
   </si>
   <si>
     <t>Orlando Pirates</t>
-  </si>
-  <si>
-    <t>Orbit College</t>
-  </si>
-  <si>
-    <t>Sekhukhune United</t>
   </si>
   <si>
     <t>Durban City</t>
@@ -1549,133 +1549,133 @@
         <v>188</v>
       </c>
       <c r="P4">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q4">
         <v>3.1</v>
       </c>
       <c r="R4">
-        <v>2.83</v>
+        <v>3.8</v>
       </c>
       <c r="S4">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="T4">
+        <v>2</v>
+      </c>
+      <c r="U4">
+        <v>3.79</v>
+      </c>
+      <c r="V4">
+        <v>1.52</v>
+      </c>
+      <c r="W4">
+        <v>2.43</v>
+      </c>
+      <c r="X4">
+        <v>3.4</v>
+      </c>
+      <c r="Y4">
+        <v>1.27</v>
+      </c>
+      <c r="Z4">
+        <v>8.5</v>
+      </c>
+      <c r="AA4">
+        <v>1.01</v>
+      </c>
+      <c r="AB4">
+        <v>1.05</v>
+      </c>
+      <c r="AC4">
+        <v>1.42</v>
+      </c>
+      <c r="AD4">
+        <v>2.51</v>
+      </c>
+      <c r="AE4">
+        <v>2.38</v>
+      </c>
+      <c r="AF4">
+        <v>1.53</v>
+      </c>
+      <c r="AG4">
+        <v>4.5</v>
+      </c>
+      <c r="AH4">
+        <v>1.15</v>
+      </c>
+      <c r="AI4">
+        <v>9</v>
+      </c>
+      <c r="AJ4">
+        <v>1.01</v>
+      </c>
+      <c r="AK4">
         <v>2.05</v>
       </c>
-      <c r="U4">
-        <v>3.65</v>
-      </c>
-      <c r="V4">
+      <c r="AL4">
+        <v>1.69</v>
+      </c>
+      <c r="AM4">
+        <v>1.33</v>
+      </c>
+      <c r="AN4">
+        <v>1.7</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>1.53</v>
+      </c>
+      <c r="AQ4">
+        <v>1.92</v>
+      </c>
+      <c r="AR4">
+        <v>3.14</v>
+      </c>
+      <c r="AS4">
+        <v>3.48</v>
+      </c>
+      <c r="AT4">
+        <v>5.24</v>
+      </c>
+      <c r="AU4">
+        <v>2.31</v>
+      </c>
+      <c r="AV4">
+        <v>1.79</v>
+      </c>
+      <c r="AW4">
         <v>1.44</v>
       </c>
-      <c r="W4">
-        <v>2.59</v>
-      </c>
-      <c r="X4">
+      <c r="AX4">
+        <v>1.22</v>
+      </c>
+      <c r="AY4">
+        <v>1.08</v>
+      </c>
+      <c r="AZ4">
+        <v>1.65</v>
+      </c>
+      <c r="BA4">
+        <v>3.02</v>
+      </c>
+      <c r="BB4">
+        <v>1.33</v>
+      </c>
+      <c r="BC4">
+        <v>2.5</v>
+      </c>
+      <c r="BD4">
         <v>3.04</v>
       </c>
-      <c r="Y4">
-        <v>1.33</v>
-      </c>
-      <c r="Z4">
-        <v>7.6</v>
-      </c>
-      <c r="AA4">
-        <v>1.03</v>
-      </c>
-      <c r="AB4">
-        <v>1.02</v>
-      </c>
-      <c r="AC4">
-        <v>1.31</v>
-      </c>
-      <c r="AD4">
-        <v>2.94</v>
-      </c>
-      <c r="AE4">
-        <v>2.1</v>
-      </c>
-      <c r="AF4">
-        <v>1.7</v>
-      </c>
-      <c r="AG4">
-        <v>3.78</v>
-      </c>
-      <c r="AH4">
-        <v>1.22</v>
-      </c>
-      <c r="AI4">
-        <v>7.1</v>
-      </c>
-      <c r="AJ4">
-        <v>1.04</v>
-      </c>
-      <c r="AK4">
-        <v>1.82</v>
-      </c>
-      <c r="AL4">
-        <v>1.88</v>
-      </c>
-      <c r="AM4">
-        <v>1.32</v>
-      </c>
-      <c r="AN4">
-        <v>1.6</v>
-      </c>
-      <c r="AO4">
-        <v>0</v>
-      </c>
-      <c r="AP4">
-        <v>1.56</v>
-      </c>
-      <c r="AQ4">
-        <v>1.96</v>
-      </c>
-      <c r="AR4">
-        <v>3.25</v>
-      </c>
-      <c r="AS4">
-        <v>3.6</v>
-      </c>
-      <c r="AT4">
-        <v>5.47</v>
-      </c>
-      <c r="AU4">
-        <v>2.26</v>
-      </c>
-      <c r="AV4">
-        <v>1.75</v>
-      </c>
-      <c r="AW4">
-        <v>1.42</v>
-      </c>
-      <c r="AX4">
-        <v>1.2</v>
-      </c>
-      <c r="AY4">
-        <v>1.07</v>
-      </c>
-      <c r="AZ4">
-        <v>1.72</v>
-      </c>
-      <c r="BA4">
-        <v>2.3</v>
-      </c>
-      <c r="BB4">
-        <v>1.24</v>
-      </c>
-      <c r="BC4">
-        <v>2.3</v>
-      </c>
-      <c r="BD4">
-        <v>3.5</v>
-      </c>
       <c r="BE4">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="BF4">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="BG4">
         <v>0</v>
@@ -1734,37 +1734,37 @@
         <v>188</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S5">
-        <v>3.24</v>
+        <v>2.7</v>
       </c>
       <c r="T5">
         <v>2.05</v>
       </c>
       <c r="U5">
-        <v>3.24</v>
+        <v>3.65</v>
       </c>
       <c r="V5">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W5">
-        <v>2.94</v>
+        <v>2.59</v>
       </c>
       <c r="X5">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="Y5">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="Z5">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="AA5">
         <v>1.03</v>
@@ -1773,94 +1773,94 @@
         <v>1.02</v>
       </c>
       <c r="AC5">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AD5">
-        <v>3.18</v>
+        <v>2.94</v>
       </c>
       <c r="AE5">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AF5">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AG5">
-        <v>3.48</v>
+        <v>3.78</v>
       </c>
       <c r="AH5">
+        <v>1.22</v>
+      </c>
+      <c r="AI5">
+        <v>7.1</v>
+      </c>
+      <c r="AJ5">
+        <v>1.04</v>
+      </c>
+      <c r="AK5">
+        <v>1.82</v>
+      </c>
+      <c r="AL5">
+        <v>1.88</v>
+      </c>
+      <c r="AM5">
+        <v>1.32</v>
+      </c>
+      <c r="AN5">
+        <v>1.6</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>1.56</v>
+      </c>
+      <c r="AQ5">
+        <v>1.96</v>
+      </c>
+      <c r="AR5">
+        <v>3.25</v>
+      </c>
+      <c r="AS5">
+        <v>3.6</v>
+      </c>
+      <c r="AT5">
+        <v>5.47</v>
+      </c>
+      <c r="AU5">
+        <v>2.26</v>
+      </c>
+      <c r="AV5">
+        <v>1.75</v>
+      </c>
+      <c r="AW5">
+        <v>1.42</v>
+      </c>
+      <c r="AX5">
+        <v>1.2</v>
+      </c>
+      <c r="AY5">
+        <v>1.07</v>
+      </c>
+      <c r="AZ5">
+        <v>1.72</v>
+      </c>
+      <c r="BA5">
+        <v>2.3</v>
+      </c>
+      <c r="BB5">
         <v>1.24</v>
       </c>
-      <c r="AI5">
-        <v>6.73</v>
-      </c>
-      <c r="AJ5">
-        <v>1.11</v>
-      </c>
-      <c r="AK5">
-        <v>1.73</v>
-      </c>
-      <c r="AL5">
-        <v>2</v>
-      </c>
-      <c r="AM5">
-        <v>1.27</v>
-      </c>
-      <c r="AN5">
-        <v>1.46</v>
-      </c>
-      <c r="AO5">
-        <v>0</v>
-      </c>
-      <c r="AP5">
-        <v>1.36</v>
-      </c>
-      <c r="AQ5">
-        <v>1.64</v>
-      </c>
-      <c r="AR5">
-        <v>2.02</v>
-      </c>
-      <c r="AS5">
-        <v>2.79</v>
-      </c>
-      <c r="AT5">
-        <v>3.96</v>
-      </c>
-      <c r="AU5">
-        <v>2.75</v>
-      </c>
-      <c r="AV5">
-        <v>2.1</v>
-      </c>
-      <c r="AW5">
-        <v>1.64</v>
-      </c>
-      <c r="AX5">
-        <v>1.35</v>
-      </c>
-      <c r="AY5">
-        <v>1.16</v>
-      </c>
-      <c r="AZ5">
-        <v>1.81</v>
-      </c>
-      <c r="BA5">
-        <v>2.17</v>
-      </c>
-      <c r="BB5">
-        <v>1.22</v>
-      </c>
       <c r="BC5">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="BD5">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="BE5">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="BF5">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BG5">
         <v>0</v>
@@ -1919,133 +1919,133 @@
         <v>188</v>
       </c>
       <c r="P6">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>2.77</v>
+        <v>3.24</v>
       </c>
       <c r="T6">
+        <v>2.05</v>
+      </c>
+      <c r="U6">
+        <v>3.24</v>
+      </c>
+      <c r="V6">
+        <v>1.39</v>
+      </c>
+      <c r="W6">
+        <v>2.94</v>
+      </c>
+      <c r="X6">
+        <v>3</v>
+      </c>
+      <c r="Y6">
+        <v>1.39</v>
+      </c>
+      <c r="Z6">
+        <v>7.5</v>
+      </c>
+      <c r="AA6">
+        <v>1.03</v>
+      </c>
+      <c r="AB6">
+        <v>1.02</v>
+      </c>
+      <c r="AC6">
+        <v>1.27</v>
+      </c>
+      <c r="AD6">
+        <v>3.18</v>
+      </c>
+      <c r="AE6">
+        <v>1.99</v>
+      </c>
+      <c r="AF6">
+        <v>1.8</v>
+      </c>
+      <c r="AG6">
+        <v>3.48</v>
+      </c>
+      <c r="AH6">
+        <v>1.24</v>
+      </c>
+      <c r="AI6">
+        <v>6.73</v>
+      </c>
+      <c r="AJ6">
+        <v>1.11</v>
+      </c>
+      <c r="AK6">
+        <v>1.73</v>
+      </c>
+      <c r="AL6">
         <v>2</v>
       </c>
-      <c r="U6">
-        <v>3.79</v>
-      </c>
-      <c r="V6">
-        <v>1.52</v>
-      </c>
-      <c r="W6">
-        <v>2.43</v>
-      </c>
-      <c r="X6">
-        <v>3.4</v>
-      </c>
-      <c r="Y6">
+      <c r="AM6">
         <v>1.27</v>
       </c>
-      <c r="Z6">
-        <v>8.5</v>
-      </c>
-      <c r="AA6">
-        <v>1.01</v>
-      </c>
-      <c r="AB6">
-        <v>1.05</v>
-      </c>
-      <c r="AC6">
-        <v>1.42</v>
-      </c>
-      <c r="AD6">
-        <v>2.51</v>
-      </c>
-      <c r="AE6">
-        <v>2.38</v>
-      </c>
-      <c r="AF6">
-        <v>1.53</v>
-      </c>
-      <c r="AG6">
-        <v>4.5</v>
-      </c>
-      <c r="AH6">
-        <v>1.15</v>
-      </c>
-      <c r="AI6">
-        <v>9</v>
-      </c>
-      <c r="AJ6">
-        <v>1.01</v>
-      </c>
-      <c r="AK6">
-        <v>2.05</v>
-      </c>
-      <c r="AL6">
-        <v>1.69</v>
-      </c>
-      <c r="AM6">
-        <v>1.33</v>
-      </c>
       <c r="AN6">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="AO6">
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AQ6">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="AR6">
-        <v>3.14</v>
+        <v>2.02</v>
       </c>
       <c r="AS6">
-        <v>3.48</v>
+        <v>2.79</v>
       </c>
       <c r="AT6">
-        <v>5.24</v>
+        <v>3.96</v>
       </c>
       <c r="AU6">
-        <v>2.31</v>
+        <v>2.75</v>
       </c>
       <c r="AV6">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="AW6">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="AX6">
+        <v>1.35</v>
+      </c>
+      <c r="AY6">
+        <v>1.16</v>
+      </c>
+      <c r="AZ6">
+        <v>1.81</v>
+      </c>
+      <c r="BA6">
+        <v>2.17</v>
+      </c>
+      <c r="BB6">
         <v>1.22</v>
       </c>
-      <c r="AY6">
-        <v>1.08</v>
-      </c>
-      <c r="AZ6">
-        <v>1.65</v>
-      </c>
-      <c r="BA6">
-        <v>3.02</v>
-      </c>
-      <c r="BB6">
-        <v>1.33</v>
-      </c>
       <c r="BC6">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="BD6">
-        <v>3.04</v>
+        <v>3.66</v>
       </c>
       <c r="BE6">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="BF6">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="BG6">
         <v>0</v>
@@ -2113,28 +2113,28 @@
         <v>0</v>
       </c>
       <c r="S7">
-        <v>3.58</v>
+        <v>2.97</v>
       </c>
       <c r="T7">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="U7">
-        <v>2.86</v>
+        <v>3.12</v>
       </c>
       <c r="V7">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W7">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="X7">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="Y7">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="Z7">
-        <v>5.65</v>
+        <v>5.55</v>
       </c>
       <c r="AA7">
         <v>1.08</v>
@@ -2146,37 +2146,37 @@
         <v>1.21</v>
       </c>
       <c r="AD7">
-        <v>4.11</v>
+        <v>3.82</v>
       </c>
       <c r="AE7">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AF7">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AG7">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AH7">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AI7">
-        <v>4.65</v>
+        <v>4.77</v>
       </c>
       <c r="AJ7">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AK7">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AL7">
         <v>2.24</v>
       </c>
       <c r="AM7">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AN7">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AO7">
         <v>0</v>
@@ -2185,10 +2185,10 @@
         <v>1.14</v>
       </c>
       <c r="AQ7">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AR7">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AS7">
         <v>1.99</v>
@@ -2206,7 +2206,7 @@
         <v>2.15</v>
       </c>
       <c r="AX7">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AY7">
         <v>1.43</v>
@@ -2218,16 +2218,16 @@
         <v>2.12</v>
       </c>
       <c r="BB7">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="BC7">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="BD7">
         <v>4.15</v>
       </c>
       <c r="BE7">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="BF7">
         <v>1.21</v>
@@ -2250,10 +2250,10 @@
         <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E8" t="s">
         <v>113</v>
@@ -2289,133 +2289,133 @@
         <v>188</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AO8">
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG8">
         <v>0</v>
@@ -2435,10 +2435,10 @@
         <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E9" t="s">
         <v>114</v>
@@ -2474,133 +2474,133 @@
         <v>188</v>
       </c>
       <c r="P9">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z9">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC9">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD9">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AH9">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI9">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AJ9">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK9">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AL9">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AM9">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN9">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AO9">
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ9">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AR9">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AS9">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU9">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AV9">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AW9">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AX9">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY9">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ9">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="BA9">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="BB9">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC9">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="BD9">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE9">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="BF9">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG9">
         <v>0</v>
@@ -3029,133 +3029,133 @@
         <v>188</v>
       </c>
       <c r="P12">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S12">
+        <v>5</v>
+      </c>
+      <c r="T12">
+        <v>2.24</v>
+      </c>
+      <c r="U12">
+        <v>2.19</v>
+      </c>
+      <c r="V12">
+        <v>1.33</v>
+      </c>
+      <c r="W12">
+        <v>2.95</v>
+      </c>
+      <c r="X12">
+        <v>2.5</v>
+      </c>
+      <c r="Y12">
+        <v>1.42</v>
+      </c>
+      <c r="Z12">
+        <v>6.2</v>
+      </c>
+      <c r="AA12">
+        <v>1.06</v>
+      </c>
+      <c r="AB12">
+        <v>1.05</v>
+      </c>
+      <c r="AC12">
+        <v>1.22</v>
+      </c>
+      <c r="AD12">
+        <v>3.5</v>
+      </c>
+      <c r="AE12">
+        <v>1.82</v>
+      </c>
+      <c r="AF12">
+        <v>1.94</v>
+      </c>
+      <c r="AG12">
         <v>3</v>
       </c>
-      <c r="T12">
-        <v>2.27</v>
-      </c>
-      <c r="U12">
-        <v>2.81</v>
-      </c>
-      <c r="V12">
+      <c r="AH12">
+        <v>1.31</v>
+      </c>
+      <c r="AI12">
+        <v>5.5</v>
+      </c>
+      <c r="AJ12">
+        <v>1.08</v>
+      </c>
+      <c r="AK12">
+        <v>1.81</v>
+      </c>
+      <c r="AL12">
+        <v>1.9</v>
+      </c>
+      <c r="AM12">
+        <v>1.24</v>
+      </c>
+      <c r="AN12">
+        <v>1.16</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>1.19</v>
+      </c>
+      <c r="AQ12">
+        <v>1.38</v>
+      </c>
+      <c r="AR12">
+        <v>1.69</v>
+      </c>
+      <c r="AS12">
+        <v>2.11</v>
+      </c>
+      <c r="AT12">
+        <v>2.84</v>
+      </c>
+      <c r="AU12">
+        <v>3.72</v>
+      </c>
+      <c r="AV12">
+        <v>2.59</v>
+      </c>
+      <c r="AW12">
+        <v>2.02</v>
+      </c>
+      <c r="AX12">
+        <v>1.6</v>
+      </c>
+      <c r="AY12">
+        <v>1.34</v>
+      </c>
+      <c r="AZ12">
+        <v>5.03</v>
+      </c>
+      <c r="BA12">
+        <v>1.29</v>
+      </c>
+      <c r="BB12">
         <v>1.22</v>
       </c>
-      <c r="W12">
-        <v>3.6</v>
-      </c>
-      <c r="X12">
-        <v>2.08</v>
-      </c>
-      <c r="Y12">
-        <v>1.69</v>
-      </c>
-      <c r="Z12">
-        <v>4.45</v>
-      </c>
-      <c r="AA12">
-        <v>1.14</v>
-      </c>
-      <c r="AB12">
-        <v>1.02</v>
-      </c>
-      <c r="AC12">
-        <v>1.13</v>
-      </c>
-      <c r="AD12">
-        <v>5.65</v>
-      </c>
-      <c r="AE12">
-        <v>1.44</v>
-      </c>
-      <c r="AF12">
-        <v>2.65</v>
-      </c>
-      <c r="AG12">
-        <v>2.06</v>
-      </c>
-      <c r="AH12">
-        <v>1.73</v>
-      </c>
-      <c r="AI12">
-        <v>3.33</v>
-      </c>
-      <c r="AJ12">
-        <v>1.3</v>
-      </c>
-      <c r="AK12">
-        <v>1.36</v>
-      </c>
-      <c r="AL12">
-        <v>2.9</v>
-      </c>
-      <c r="AM12">
-        <v>1.28</v>
-      </c>
-      <c r="AN12">
-        <v>1.44</v>
-      </c>
-      <c r="AO12">
-        <v>0</v>
-      </c>
-      <c r="AP12">
-        <v>1.11</v>
-      </c>
-      <c r="AQ12">
-        <v>1.26</v>
-      </c>
-      <c r="AR12">
-        <v>1.65</v>
-      </c>
-      <c r="AS12">
-        <v>1.85</v>
-      </c>
-      <c r="AT12">
-        <v>2.32</v>
-      </c>
-      <c r="AU12">
-        <v>4.84</v>
-      </c>
-      <c r="AV12">
-        <v>3.19</v>
-      </c>
-      <c r="AW12">
-        <v>2.44</v>
-      </c>
-      <c r="AX12">
-        <v>1.91</v>
-      </c>
-      <c r="AY12">
-        <v>1.52</v>
-      </c>
-      <c r="AZ12">
-        <v>1.93</v>
-      </c>
-      <c r="BA12">
-        <v>2.09</v>
-      </c>
-      <c r="BB12">
-        <v>1.08</v>
-      </c>
       <c r="BC12">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="BD12">
-        <v>5.7</v>
+        <v>3.9</v>
       </c>
       <c r="BE12">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="BF12">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="BG12">
         <v>0</v>
@@ -3214,133 +3214,133 @@
         <v>188</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T13">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="U13">
-        <v>2.19</v>
+        <v>2.81</v>
       </c>
       <c r="V13">
+        <v>1.22</v>
+      </c>
+      <c r="W13">
+        <v>3.6</v>
+      </c>
+      <c r="X13">
+        <v>2.08</v>
+      </c>
+      <c r="Y13">
+        <v>1.69</v>
+      </c>
+      <c r="Z13">
+        <v>4.45</v>
+      </c>
+      <c r="AA13">
+        <v>1.14</v>
+      </c>
+      <c r="AB13">
+        <v>1.02</v>
+      </c>
+      <c r="AC13">
+        <v>1.13</v>
+      </c>
+      <c r="AD13">
+        <v>5.65</v>
+      </c>
+      <c r="AE13">
+        <v>1.44</v>
+      </c>
+      <c r="AF13">
+        <v>2.65</v>
+      </c>
+      <c r="AG13">
+        <v>2.06</v>
+      </c>
+      <c r="AH13">
+        <v>1.73</v>
+      </c>
+      <c r="AI13">
+        <v>3.33</v>
+      </c>
+      <c r="AJ13">
+        <v>1.3</v>
+      </c>
+      <c r="AK13">
+        <v>1.36</v>
+      </c>
+      <c r="AL13">
+        <v>2.9</v>
+      </c>
+      <c r="AM13">
+        <v>1.28</v>
+      </c>
+      <c r="AN13">
+        <v>1.44</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>1.11</v>
+      </c>
+      <c r="AQ13">
+        <v>1.26</v>
+      </c>
+      <c r="AR13">
+        <v>1.65</v>
+      </c>
+      <c r="AS13">
+        <v>1.85</v>
+      </c>
+      <c r="AT13">
+        <v>2.32</v>
+      </c>
+      <c r="AU13">
+        <v>4.84</v>
+      </c>
+      <c r="AV13">
+        <v>3.19</v>
+      </c>
+      <c r="AW13">
+        <v>2.44</v>
+      </c>
+      <c r="AX13">
+        <v>1.91</v>
+      </c>
+      <c r="AY13">
+        <v>1.52</v>
+      </c>
+      <c r="AZ13">
+        <v>1.93</v>
+      </c>
+      <c r="BA13">
+        <v>2.09</v>
+      </c>
+      <c r="BB13">
+        <v>1.08</v>
+      </c>
+      <c r="BC13">
+        <v>1.6</v>
+      </c>
+      <c r="BD13">
+        <v>5.7</v>
+      </c>
+      <c r="BE13">
+        <v>2.2</v>
+      </c>
+      <c r="BF13">
         <v>1.33</v>
-      </c>
-      <c r="W13">
-        <v>2.95</v>
-      </c>
-      <c r="X13">
-        <v>2.5</v>
-      </c>
-      <c r="Y13">
-        <v>1.42</v>
-      </c>
-      <c r="Z13">
-        <v>6.2</v>
-      </c>
-      <c r="AA13">
-        <v>1.06</v>
-      </c>
-      <c r="AB13">
-        <v>1.05</v>
-      </c>
-      <c r="AC13">
-        <v>1.22</v>
-      </c>
-      <c r="AD13">
-        <v>3.5</v>
-      </c>
-      <c r="AE13">
-        <v>1.82</v>
-      </c>
-      <c r="AF13">
-        <v>1.94</v>
-      </c>
-      <c r="AG13">
-        <v>3</v>
-      </c>
-      <c r="AH13">
-        <v>1.31</v>
-      </c>
-      <c r="AI13">
-        <v>5.5</v>
-      </c>
-      <c r="AJ13">
-        <v>1.08</v>
-      </c>
-      <c r="AK13">
-        <v>1.81</v>
-      </c>
-      <c r="AL13">
-        <v>1.9</v>
-      </c>
-      <c r="AM13">
-        <v>1.24</v>
-      </c>
-      <c r="AN13">
-        <v>1.16</v>
-      </c>
-      <c r="AO13">
-        <v>0</v>
-      </c>
-      <c r="AP13">
-        <v>1.19</v>
-      </c>
-      <c r="AQ13">
-        <v>1.38</v>
-      </c>
-      <c r="AR13">
-        <v>1.69</v>
-      </c>
-      <c r="AS13">
-        <v>2.11</v>
-      </c>
-      <c r="AT13">
-        <v>2.84</v>
-      </c>
-      <c r="AU13">
-        <v>3.72</v>
-      </c>
-      <c r="AV13">
-        <v>2.59</v>
-      </c>
-      <c r="AW13">
-        <v>2.02</v>
-      </c>
-      <c r="AX13">
-        <v>1.6</v>
-      </c>
-      <c r="AY13">
-        <v>1.34</v>
-      </c>
-      <c r="AZ13">
-        <v>5.03</v>
-      </c>
-      <c r="BA13">
-        <v>1.29</v>
-      </c>
-      <c r="BB13">
-        <v>1.22</v>
-      </c>
-      <c r="BC13">
-        <v>2.05</v>
-      </c>
-      <c r="BD13">
-        <v>3.9</v>
-      </c>
-      <c r="BE13">
-        <v>1.71</v>
-      </c>
-      <c r="BF13">
-        <v>1.16</v>
       </c>
       <c r="BG13">
         <v>0</v>
@@ -3360,7 +3360,7 @@
         <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D14" t="s">
         <v>105</v>
@@ -3399,133 +3399,133 @@
         <v>188</v>
       </c>
       <c r="P14">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R14">
-        <v>5.59</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>5.61</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AD14">
-        <v>4.24</v>
+        <v>4.8</v>
       </c>
       <c r="AE14">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="AF14">
-        <v>2.13</v>
+        <v>2.43</v>
       </c>
       <c r="AG14">
-        <v>2.52</v>
+        <v>2.14</v>
       </c>
       <c r="AH14">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="AI14">
-        <v>4.65</v>
+        <v>3.5</v>
       </c>
       <c r="AJ14">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="AK14">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM14">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AN14">
-        <v>2.32</v>
+        <v>1.05</v>
       </c>
       <c r="AO14">
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AQ14">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AR14">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AS14">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT14">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AU14">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AV14">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AW14">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AX14">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AY14">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ14">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BA14">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="BB14">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC14">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BD14">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="BE14">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BF14">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG14">
         <v>0</v>
@@ -3545,7 +3545,7 @@
         <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D15" t="s">
         <v>105</v>
@@ -3623,28 +3623,28 @@
         <v>0</v>
       </c>
       <c r="AC15">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AD15">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AE15">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AF15">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AG15">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH15">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI15">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AJ15">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK15">
         <v>0</v>
@@ -3653,10 +3653,10 @@
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN15">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AO15">
         <v>0</v>
@@ -3730,7 +3730,7 @@
         <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D16" t="s">
         <v>105</v>
@@ -3769,133 +3769,133 @@
         <v>188</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL16">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AM16">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AO16">
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AU16">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AV16">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AW16">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AX16">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY16">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AZ16">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BA16">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="BB16">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC16">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BD16">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="BE16">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BF16">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG16">
         <v>0</v>
@@ -4694,76 +4694,76 @@
         <v>188</v>
       </c>
       <c r="P21">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q21">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="R21">
-        <v>3.6</v>
+        <v>3.84</v>
       </c>
       <c r="S21">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="T21">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="U21">
-        <v>4.34</v>
+        <v>3.8</v>
       </c>
       <c r="V21">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W21">
-        <v>2.62</v>
+        <v>2.39</v>
       </c>
       <c r="X21">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Y21">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z21">
         <v>8.5</v>
       </c>
       <c r="AA21">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AB21">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AC21">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AD21">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AE21">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="AF21">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG21">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="AH21">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AI21">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="AJ21">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AK21">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL21">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AM21">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AN21">
         <v>1.73</v>
@@ -4772,52 +4772,52 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AQ21">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AR21">
-        <v>2</v>
+        <v>2.64</v>
       </c>
       <c r="AS21">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="AT21">
-        <v>3.35</v>
+        <v>4.24</v>
       </c>
       <c r="AU21">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="AV21">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="AW21">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AX21">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="AY21">
         <v>1.27</v>
       </c>
       <c r="AZ21">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="BA21">
-        <v>2.17</v>
+        <v>2.53</v>
       </c>
       <c r="BB21">
         <v>1.3</v>
       </c>
       <c r="BC21">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="BD21">
         <v>3.16</v>
       </c>
       <c r="BE21">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="BF21">
         <v>1.08</v>
@@ -6690,10 +6690,10 @@
         <v>80</v>
       </c>
       <c r="C32" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E32" t="s">
         <v>137</v>
@@ -6729,133 +6729,133 @@
         <v>188</v>
       </c>
       <c r="P32">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q32">
-        <v>4</v>
+        <v>3.54</v>
       </c>
       <c r="R32">
-        <v>6.5</v>
+        <v>2.52</v>
       </c>
       <c r="S32">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="T32">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U32">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="V32">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W32">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="X32">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y32">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z32">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AA32">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB32">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC32">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AD32">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AE32">
-        <v>2.02</v>
+        <v>1.66</v>
       </c>
       <c r="AF32">
-        <v>1.71</v>
+        <v>2.15</v>
       </c>
       <c r="AG32">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AH32">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI32">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="AJ32">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK32">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AL32">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AM32">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AN32">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AO32">
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ32">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AR32">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AS32">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AT32">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AU32">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AV32">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AW32">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AX32">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AY32">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ32">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BA32">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="BB32">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC32">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD32">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BE32">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF32">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG32">
         <v>0</v>
@@ -6875,7 +6875,7 @@
         <v>80</v>
       </c>
       <c r="C33" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D33" t="s">
         <v>105</v>
@@ -6914,133 +6914,133 @@
         <v>188</v>
       </c>
       <c r="P33">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="Q33">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="R33">
-        <v>3.79</v>
+        <v>6.5</v>
       </c>
       <c r="S33">
-        <v>2.48</v>
+        <v>1.88</v>
       </c>
       <c r="T33">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="U33">
-        <v>4.1</v>
+        <v>8.1</v>
       </c>
       <c r="V33">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="W33">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="X33">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="Y33">
         <v>1.33</v>
       </c>
       <c r="Z33">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="AA33">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AB33">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AC33">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AD33">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AE33">
         <v>2.02</v>
       </c>
       <c r="AF33">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AG33">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="AH33">
+        <v>1.27</v>
+      </c>
+      <c r="AI33">
+        <v>6.45</v>
+      </c>
+      <c r="AJ33">
+        <v>1.05</v>
+      </c>
+      <c r="AK33">
+        <v>2.25</v>
+      </c>
+      <c r="AL33">
+        <v>1.6</v>
+      </c>
+      <c r="AM33">
+        <v>1.16</v>
+      </c>
+      <c r="AN33">
+        <v>2.5</v>
+      </c>
+      <c r="AO33">
+        <v>0</v>
+      </c>
+      <c r="AP33">
         <v>1.24</v>
       </c>
-      <c r="AI33">
-        <v>6.75</v>
-      </c>
-      <c r="AJ33">
-        <v>1.07</v>
-      </c>
-      <c r="AK33">
-        <v>1.8</v>
-      </c>
-      <c r="AL33">
-        <v>1.84</v>
-      </c>
-      <c r="AM33">
+      <c r="AQ33">
+        <v>1.52</v>
+      </c>
+      <c r="AR33">
+        <v>1.83</v>
+      </c>
+      <c r="AS33">
+        <v>2.33</v>
+      </c>
+      <c r="AT33">
+        <v>3.14</v>
+      </c>
+      <c r="AU33">
+        <v>3.34</v>
+      </c>
+      <c r="AV33">
+        <v>2.38</v>
+      </c>
+      <c r="AW33">
+        <v>1.83</v>
+      </c>
+      <c r="AX33">
+        <v>1.48</v>
+      </c>
+      <c r="AY33">
         <v>1.27</v>
       </c>
-      <c r="AN33">
-        <v>1.75</v>
-      </c>
-      <c r="AO33">
-        <v>0</v>
-      </c>
-      <c r="AP33">
-        <v>1.4</v>
-      </c>
-      <c r="AQ33">
-        <v>1.67</v>
-      </c>
-      <c r="AR33">
-        <v>2.1</v>
-      </c>
-      <c r="AS33">
-        <v>2.7</v>
-      </c>
-      <c r="AT33">
-        <v>3.65</v>
-      </c>
-      <c r="AU33">
-        <v>2.7</v>
-      </c>
-      <c r="AV33">
-        <v>2.04</v>
-      </c>
-      <c r="AW33">
-        <v>1.64</v>
-      </c>
-      <c r="AX33">
-        <v>1.38</v>
-      </c>
-      <c r="AY33">
-        <v>1.23</v>
-      </c>
       <c r="AZ33">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="BA33">
-        <v>2.5</v>
+        <v>4.32</v>
       </c>
       <c r="BB33">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BC33">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="BD33">
         <v>3.7</v>
       </c>
       <c r="BE33">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BF33">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="BG33">
         <v>0</v>
@@ -7060,10 +7060,10 @@
         <v>80</v>
       </c>
       <c r="C34" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E34" t="s">
         <v>139</v>
@@ -7099,133 +7099,133 @@
         <v>188</v>
       </c>
       <c r="P34">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="Q34">
-        <v>3.54</v>
+        <v>3.2</v>
       </c>
       <c r="R34">
+        <v>1.8</v>
+      </c>
+      <c r="S34">
+        <v>5.29</v>
+      </c>
+      <c r="T34">
+        <v>1.96</v>
+      </c>
+      <c r="U34">
+        <v>2.46</v>
+      </c>
+      <c r="V34">
+        <v>1.47</v>
+      </c>
+      <c r="W34">
+        <v>2.41</v>
+      </c>
+      <c r="X34">
+        <v>3</v>
+      </c>
+      <c r="Y34">
+        <v>1.3</v>
+      </c>
+      <c r="Z34">
+        <v>7.7</v>
+      </c>
+      <c r="AA34">
+        <v>1.02</v>
+      </c>
+      <c r="AB34">
+        <v>1.04</v>
+      </c>
+      <c r="AC34">
+        <v>1.4</v>
+      </c>
+      <c r="AD34">
+        <v>2.97</v>
+      </c>
+      <c r="AE34">
+        <v>2.16</v>
+      </c>
+      <c r="AF34">
+        <v>1.62</v>
+      </c>
+      <c r="AG34">
+        <v>4.1</v>
+      </c>
+      <c r="AH34">
+        <v>1.19</v>
+      </c>
+      <c r="AI34">
+        <v>7.3</v>
+      </c>
+      <c r="AJ34">
+        <v>1.03</v>
+      </c>
+      <c r="AK34">
+        <v>1.93</v>
+      </c>
+      <c r="AL34">
+        <v>1.73</v>
+      </c>
+      <c r="AM34">
+        <v>1.26</v>
+      </c>
+      <c r="AN34">
+        <v>1.14</v>
+      </c>
+      <c r="AO34">
+        <v>0</v>
+      </c>
+      <c r="AP34">
+        <v>1.28</v>
+      </c>
+      <c r="AQ34">
+        <v>1.53</v>
+      </c>
+      <c r="AR34">
+        <v>1.95</v>
+      </c>
+      <c r="AS34">
         <v>2.52</v>
       </c>
-      <c r="S34">
-        <v>0</v>
-      </c>
-      <c r="T34">
-        <v>0</v>
-      </c>
-      <c r="U34">
-        <v>0</v>
-      </c>
-      <c r="V34">
-        <v>0</v>
-      </c>
-      <c r="W34">
-        <v>0</v>
-      </c>
-      <c r="X34">
-        <v>0</v>
-      </c>
-      <c r="Y34">
-        <v>0</v>
-      </c>
-      <c r="Z34">
-        <v>0</v>
-      </c>
-      <c r="AA34">
-        <v>0</v>
-      </c>
-      <c r="AB34">
-        <v>0</v>
-      </c>
-      <c r="AC34">
-        <v>0</v>
-      </c>
-      <c r="AD34">
-        <v>0</v>
-      </c>
-      <c r="AE34">
-        <v>1.66</v>
-      </c>
-      <c r="AF34">
-        <v>2.15</v>
-      </c>
-      <c r="AG34">
-        <v>0</v>
-      </c>
-      <c r="AH34">
-        <v>0</v>
-      </c>
-      <c r="AI34">
-        <v>0</v>
-      </c>
-      <c r="AJ34">
-        <v>0</v>
-      </c>
-      <c r="AK34">
-        <v>0</v>
-      </c>
-      <c r="AL34">
-        <v>0</v>
-      </c>
-      <c r="AM34">
-        <v>0</v>
-      </c>
-      <c r="AN34">
-        <v>0</v>
-      </c>
-      <c r="AO34">
-        <v>0</v>
-      </c>
-      <c r="AP34">
-        <v>0</v>
-      </c>
-      <c r="AQ34">
-        <v>0</v>
-      </c>
-      <c r="AR34">
-        <v>0</v>
-      </c>
-      <c r="AS34">
-        <v>0</v>
-      </c>
       <c r="AT34">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AU34">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV34">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AW34">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AX34">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY34">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ34">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BA34">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BB34">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC34">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BD34">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE34">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF34">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG34">
         <v>0</v>
@@ -7245,7 +7245,7 @@
         <v>80</v>
       </c>
       <c r="C35" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D35" t="s">
         <v>105</v>
@@ -7284,133 +7284,133 @@
         <v>188</v>
       </c>
       <c r="P35">
-        <v>4</v>
+        <v>1.99</v>
       </c>
       <c r="Q35">
+        <v>3.3</v>
+      </c>
+      <c r="R35">
+        <v>3.5</v>
+      </c>
+      <c r="S35">
+        <v>2.5</v>
+      </c>
+      <c r="T35">
+        <v>2.16</v>
+      </c>
+      <c r="U35">
+        <v>4.31</v>
+      </c>
+      <c r="V35">
+        <v>1.36</v>
+      </c>
+      <c r="W35">
+        <v>2.9</v>
+      </c>
+      <c r="X35">
+        <v>2.89</v>
+      </c>
+      <c r="Y35">
+        <v>1.33</v>
+      </c>
+      <c r="Z35">
+        <v>7</v>
+      </c>
+      <c r="AA35">
+        <v>1.06</v>
+      </c>
+      <c r="AB35">
+        <v>1.02</v>
+      </c>
+      <c r="AC35">
+        <v>1.27</v>
+      </c>
+      <c r="AD35">
         <v>3.2</v>
       </c>
-      <c r="R35">
+      <c r="AE35">
+        <v>2.02</v>
+      </c>
+      <c r="AF35">
+        <v>1.68</v>
+      </c>
+      <c r="AG35">
+        <v>3.6</v>
+      </c>
+      <c r="AH35">
+        <v>1.24</v>
+      </c>
+      <c r="AI35">
+        <v>6.75</v>
+      </c>
+      <c r="AJ35">
+        <v>1.06</v>
+      </c>
+      <c r="AK35">
         <v>1.8</v>
       </c>
-      <c r="S35">
-        <v>5.29</v>
-      </c>
-      <c r="T35">
-        <v>1.96</v>
-      </c>
-      <c r="U35">
-        <v>2.46</v>
-      </c>
-      <c r="V35">
-        <v>1.47</v>
-      </c>
-      <c r="W35">
-        <v>2.41</v>
-      </c>
-      <c r="X35">
-        <v>3</v>
-      </c>
-      <c r="Y35">
+      <c r="AL35">
+        <v>1.92</v>
+      </c>
+      <c r="AM35">
         <v>1.3</v>
       </c>
-      <c r="Z35">
-        <v>7.7</v>
-      </c>
-      <c r="AA35">
-        <v>1.02</v>
-      </c>
-      <c r="AB35">
-        <v>1.04</v>
-      </c>
-      <c r="AC35">
+      <c r="AN35">
+        <v>1.76</v>
+      </c>
+      <c r="AO35">
+        <v>0</v>
+      </c>
+      <c r="AP35">
         <v>1.4</v>
       </c>
-      <c r="AD35">
-        <v>2.97</v>
-      </c>
-      <c r="AE35">
-        <v>2.16</v>
-      </c>
-      <c r="AF35">
-        <v>1.62</v>
-      </c>
-      <c r="AG35">
-        <v>4.1</v>
-      </c>
-      <c r="AH35">
-        <v>1.19</v>
-      </c>
-      <c r="AI35">
-        <v>7.3</v>
-      </c>
-      <c r="AJ35">
-        <v>1.03</v>
-      </c>
-      <c r="AK35">
-        <v>1.93</v>
-      </c>
-      <c r="AL35">
-        <v>1.73</v>
-      </c>
-      <c r="AM35">
-        <v>1.26</v>
-      </c>
-      <c r="AN35">
-        <v>1.14</v>
-      </c>
-      <c r="AO35">
-        <v>0</v>
-      </c>
-      <c r="AP35">
-        <v>1.28</v>
-      </c>
       <c r="AQ35">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="AR35">
-        <v>1.95</v>
+        <v>2.51</v>
       </c>
       <c r="AS35">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="AT35">
-        <v>3.48</v>
+        <v>3.65</v>
       </c>
       <c r="AU35">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="AV35">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="AW35">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AX35">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AY35">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AZ35">
-        <v>2.46</v>
+        <v>1.68</v>
       </c>
       <c r="BA35">
-        <v>1.82</v>
+        <v>2.5</v>
       </c>
       <c r="BB35">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BC35">
-        <v>2.55</v>
+        <v>2.12</v>
       </c>
       <c r="BD35">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="BE35">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="BF35">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="BG35">
         <v>0</v>
@@ -7469,22 +7469,22 @@
         <v>188</v>
       </c>
       <c r="P36">
-        <v>5.6</v>
+        <v>3.45</v>
       </c>
       <c r="Q36">
-        <v>3.5</v>
+        <v>2.98</v>
       </c>
       <c r="R36">
-        <v>1.5</v>
+        <v>2.15</v>
       </c>
       <c r="S36">
-        <v>7</v>
+        <v>3.95</v>
       </c>
       <c r="T36">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="U36">
-        <v>2.13</v>
+        <v>2.9</v>
       </c>
       <c r="V36">
         <v>1.51</v>
@@ -7499,103 +7499,103 @@
         <v>1.25</v>
       </c>
       <c r="Z36">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AA36">
         <v>1</v>
       </c>
       <c r="AB36">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AC36">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AD36">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="AE36">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
       <c r="AF36">
         <v>1.49</v>
       </c>
       <c r="AG36">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="AH36">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AI36">
-        <v>8.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="AJ36">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AK36">
-        <v>2.51</v>
+        <v>2.05</v>
       </c>
       <c r="AL36">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AM36">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AN36">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="AO36">
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AQ36">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AR36">
-        <v>2.73</v>
+        <v>2.02</v>
       </c>
       <c r="AS36">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="AT36">
-        <v>4.41</v>
+        <v>3.4</v>
       </c>
       <c r="AU36">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AV36">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AW36">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AX36">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="AY36">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AZ36">
-        <v>3.85</v>
+        <v>2.12</v>
       </c>
       <c r="BA36">
-        <v>1.42</v>
+        <v>2.08</v>
       </c>
       <c r="BB36">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BC36">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="BD36">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="BE36">
         <v>1.41</v>
       </c>
       <c r="BF36">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="BG36">
         <v>0</v>
@@ -7839,22 +7839,22 @@
         <v>188</v>
       </c>
       <c r="P38">
-        <v>3.45</v>
+        <v>5.6</v>
       </c>
       <c r="Q38">
-        <v>2.98</v>
+        <v>3.5</v>
       </c>
       <c r="R38">
-        <v>2.15</v>
+        <v>1.5</v>
       </c>
       <c r="S38">
-        <v>3.95</v>
+        <v>7</v>
       </c>
       <c r="T38">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="U38">
-        <v>2.9</v>
+        <v>2.13</v>
       </c>
       <c r="V38">
         <v>1.51</v>
@@ -7869,103 +7869,103 @@
         <v>1.25</v>
       </c>
       <c r="Z38">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA38">
         <v>1</v>
       </c>
       <c r="AB38">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AC38">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AD38">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="AE38">
-        <v>2.65</v>
+        <v>2.53</v>
       </c>
       <c r="AF38">
         <v>1.49</v>
       </c>
       <c r="AG38">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="AH38">
+        <v>1.12</v>
+      </c>
+      <c r="AI38">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AJ38">
+        <v>1.05</v>
+      </c>
+      <c r="AK38">
+        <v>2.51</v>
+      </c>
+      <c r="AL38">
+        <v>1.53</v>
+      </c>
+      <c r="AM38">
+        <v>1.22</v>
+      </c>
+      <c r="AN38">
+        <v>1.04</v>
+      </c>
+      <c r="AO38">
+        <v>0</v>
+      </c>
+      <c r="AP38">
+        <v>1.42</v>
+      </c>
+      <c r="AQ38">
+        <v>1.77</v>
+      </c>
+      <c r="AR38">
+        <v>2.73</v>
+      </c>
+      <c r="AS38">
+        <v>3.04</v>
+      </c>
+      <c r="AT38">
+        <v>4.41</v>
+      </c>
+      <c r="AU38">
+        <v>2.7</v>
+      </c>
+      <c r="AV38">
+        <v>1.94</v>
+      </c>
+      <c r="AW38">
+        <v>1.56</v>
+      </c>
+      <c r="AX38">
+        <v>1.29</v>
+      </c>
+      <c r="AY38">
         <v>1.13</v>
       </c>
-      <c r="AI38">
-        <v>9.5</v>
-      </c>
-      <c r="AJ38">
-        <v>1.03</v>
-      </c>
-      <c r="AK38">
-        <v>2.05</v>
-      </c>
-      <c r="AL38">
-        <v>1.62</v>
-      </c>
-      <c r="AM38">
-        <v>1.3</v>
-      </c>
-      <c r="AN38">
-        <v>1.24</v>
-      </c>
-      <c r="AO38">
-        <v>0</v>
-      </c>
-      <c r="AP38">
-        <v>1.37</v>
-      </c>
-      <c r="AQ38">
-        <v>1.72</v>
-      </c>
-      <c r="AR38">
-        <v>2.02</v>
-      </c>
-      <c r="AS38">
-        <v>2.9</v>
-      </c>
-      <c r="AT38">
-        <v>3.4</v>
-      </c>
-      <c r="AU38">
-        <v>2.8</v>
-      </c>
-      <c r="AV38">
-        <v>2</v>
-      </c>
-      <c r="AW38">
-        <v>1.6</v>
-      </c>
-      <c r="AX38">
-        <v>1.43</v>
-      </c>
-      <c r="AY38">
-        <v>1.15</v>
-      </c>
       <c r="AZ38">
-        <v>2.12</v>
+        <v>3.85</v>
       </c>
       <c r="BA38">
-        <v>2.08</v>
+        <v>1.42</v>
       </c>
       <c r="BB38">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="BC38">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="BD38">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="BE38">
         <v>1.41</v>
       </c>
       <c r="BF38">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="BG38">
         <v>0</v>
@@ -8394,79 +8394,79 @@
         <v>188</v>
       </c>
       <c r="P41">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Q41">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="R41">
-        <v>4.7</v>
+        <v>5.21</v>
       </c>
       <c r="S41">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="T41">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="U41">
-        <v>5.7</v>
+        <v>5.25</v>
       </c>
       <c r="V41">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W41">
-        <v>2.85</v>
+        <v>3.13</v>
       </c>
       <c r="X41">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="Y41">
         <v>1.43</v>
       </c>
       <c r="Z41">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="AA41">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AB41">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC41">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AD41">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AE41">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AF41">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AG41">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AH41">
         <v>1.3</v>
       </c>
       <c r="AI41">
-        <v>5.95</v>
+        <v>7.5</v>
       </c>
       <c r="AJ41">
         <v>1.07</v>
       </c>
       <c r="AK41">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AL41">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AM41">
         <v>1.28</v>
       </c>
       <c r="AN41">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AO41">
         <v>0</v>
@@ -8478,46 +8478,46 @@
         <v>1.42</v>
       </c>
       <c r="AR41">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AS41">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AT41">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="AU41">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AV41">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AW41">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AX41">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AY41">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AZ41">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="BA41">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BB41">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BC41">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="BD41">
-        <v>3.94</v>
+        <v>4.05</v>
       </c>
       <c r="BE41">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="BF41">
         <v>1.18</v>

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -343,48 +343,48 @@
     <t>Jeonbuk Motors</t>
   </si>
   <si>
+    <t>Sangju Sangmu</t>
+  </si>
+  <si>
     <t>Gangwon</t>
   </si>
   <si>
     <t>Daejeon Citizen</t>
   </si>
   <si>
-    <t>Sangju Sangmu</t>
-  </si>
-  <si>
     <t>Madura United</t>
   </si>
   <si>
+    <t>Ethiopia Nigd Bank</t>
+  </si>
+  <si>
     <t>FC Seoul</t>
   </si>
   <si>
-    <t>Ethiopia Nigd Bank</t>
-  </si>
-  <si>
     <t>Qingdao Youth Island</t>
   </si>
   <si>
     <t>Tanjong Pagar</t>
   </si>
   <si>
+    <t>Shandong Luneng</t>
+  </si>
+  <si>
     <t>Shenyang Urban</t>
   </si>
   <si>
-    <t>Shandong Luneng</t>
+    <t>Chongqing Tongliang Long</t>
+  </si>
+  <si>
+    <t>Dire Dawa Kenema</t>
+  </si>
+  <si>
+    <t>Borneo</t>
   </si>
   <si>
     <t>Karvan FK</t>
   </si>
   <si>
-    <t>Dire Dawa Kenema</t>
-  </si>
-  <si>
-    <t>Borneo</t>
-  </si>
-  <si>
-    <t>Chongqing Tongliang Long</t>
-  </si>
-  <si>
     <t>Mekelle Kenema</t>
   </si>
   <si>
@@ -415,39 +415,39 @@
     <t>Maccabi Tel Aviv</t>
   </si>
   <si>
+    <t>Bani Yas</t>
+  </si>
+  <si>
+    <t>Al Ittihad Kalba</t>
+  </si>
+  <si>
     <t>Dibba Al Fujairah</t>
   </si>
   <si>
-    <t>Bani Yas</t>
-  </si>
-  <si>
-    <t>Al Ittihad Kalba</t>
+    <t>Al Ahly</t>
+  </si>
+  <si>
+    <t>Ceramica Cleopatra</t>
+  </si>
+  <si>
+    <t>Lokomotiv Sofia 1929</t>
+  </si>
+  <si>
+    <t>Falkenberg</t>
   </si>
   <si>
     <t>Smouha SC</t>
   </si>
   <si>
-    <t>Falkenberg</t>
-  </si>
-  <si>
-    <t>Al Ahly</t>
-  </si>
-  <si>
-    <t>Ceramica Cleopatra</t>
-  </si>
-  <si>
-    <t>Lokomotiv Sofia 1929</t>
-  </si>
-  <si>
     <t>Chippa United</t>
   </si>
   <si>
+    <t>Stellenbosch</t>
+  </si>
+  <si>
     <t>Magesi</t>
   </si>
   <si>
-    <t>Stellenbosch</t>
-  </si>
-  <si>
     <t>Siwelele</t>
   </si>
   <si>
@@ -466,48 +466,48 @@
     <t>Gwangju</t>
   </si>
   <si>
+    <t>Ulsan</t>
+  </si>
+  <si>
     <t>Pohang Steelers</t>
   </si>
   <si>
     <t>Incheon United</t>
   </si>
   <si>
-    <t>Ulsan</t>
-  </si>
-  <si>
     <t>Bali United</t>
   </si>
   <si>
+    <t>Kedus Giorgis</t>
+  </si>
+  <si>
     <t>Anyang</t>
   </si>
   <si>
-    <t>Kedus Giorgis</t>
-  </si>
-  <si>
     <t>Tianjin Teda</t>
   </si>
   <si>
     <t>Hougang United</t>
   </si>
   <si>
+    <t>Shanghai Shenhua</t>
+  </si>
+  <si>
     <t>Chengdu Better City FC</t>
   </si>
   <si>
-    <t>Shanghai Shenhua</t>
+    <t>Henan Jianye</t>
+  </si>
+  <si>
+    <t>Ethiopia Bunna</t>
+  </si>
+  <si>
+    <t>Persita</t>
   </si>
   <si>
     <t>Neftçi</t>
   </si>
   <si>
-    <t>Ethiopia Bunna</t>
-  </si>
-  <si>
-    <t>Persita</t>
-  </si>
-  <si>
-    <t>Henan Jianye</t>
-  </si>
-  <si>
     <t>Arba Minch Kenema</t>
   </si>
   <si>
@@ -538,34 +538,34 @@
     <t>Hapoel Petah Tikva</t>
   </si>
   <si>
+    <t>Al Dhafra</t>
+  </si>
+  <si>
     <t>Al Bataeh</t>
   </si>
   <si>
-    <t>Al Dhafra</t>
+    <t>ENPPI</t>
+  </si>
+  <si>
+    <t>Pyramids FC</t>
+  </si>
+  <si>
+    <t>Botev Vratsa</t>
+  </si>
+  <si>
+    <t>Norrköping</t>
   </si>
   <si>
     <t>Zamalek</t>
   </si>
   <si>
-    <t>Norrköping</t>
-  </si>
-  <si>
-    <t>ENPPI</t>
-  </si>
-  <si>
-    <t>Pyramids FC</t>
-  </si>
-  <si>
-    <t>Botev Vratsa</t>
-  </si>
-  <si>
     <t>Sekhukhune United</t>
   </si>
   <si>
+    <t>Orlando Pirates</t>
+  </si>
+  <si>
     <t>Orbit College</t>
-  </si>
-  <si>
-    <t>Orlando Pirates</t>
   </si>
   <si>
     <t>Durban City</t>
@@ -1179,7 +1179,7 @@
         <v>188</v>
       </c>
       <c r="P2">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q2">
         <v>3</v>
@@ -1364,13 +1364,13 @@
         <v>188</v>
       </c>
       <c r="P3">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="Q3">
-        <v>4.63</v>
+        <v>4.3</v>
       </c>
       <c r="R3">
-        <v>9.44</v>
+        <v>7.1</v>
       </c>
       <c r="S3">
         <v>1.85</v>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="AC3">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AD3">
         <v>3.18</v>
@@ -1421,7 +1421,7 @@
         <v>1.26</v>
       </c>
       <c r="AI3">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="AJ3">
         <v>1.06</v>
@@ -1436,7 +1436,7 @@
         <v>1.17</v>
       </c>
       <c r="AN3">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="AO3">
         <v>0</v>
@@ -1445,22 +1445,22 @@
         <v>1.52</v>
       </c>
       <c r="AQ3">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AR3">
-        <v>3.12</v>
+        <v>2.48</v>
       </c>
       <c r="AS3">
         <v>3.34</v>
       </c>
       <c r="AT3">
-        <v>5.2</v>
+        <v>5.16</v>
       </c>
       <c r="AU3">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="AV3">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AW3">
         <v>1.45</v>
@@ -1475,7 +1475,7 @@
         <v>1.18</v>
       </c>
       <c r="BA3">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="BB3">
         <v>1.22</v>
@@ -1549,133 +1549,133 @@
         <v>188</v>
       </c>
       <c r="P4">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>2.77</v>
+        <v>3.24</v>
       </c>
       <c r="T4">
+        <v>2.05</v>
+      </c>
+      <c r="U4">
+        <v>3.24</v>
+      </c>
+      <c r="V4">
+        <v>1.39</v>
+      </c>
+      <c r="W4">
+        <v>2.94</v>
+      </c>
+      <c r="X4">
+        <v>3</v>
+      </c>
+      <c r="Y4">
+        <v>1.39</v>
+      </c>
+      <c r="Z4">
+        <v>7.5</v>
+      </c>
+      <c r="AA4">
+        <v>1.03</v>
+      </c>
+      <c r="AB4">
+        <v>1.02</v>
+      </c>
+      <c r="AC4">
+        <v>1.27</v>
+      </c>
+      <c r="AD4">
+        <v>3.18</v>
+      </c>
+      <c r="AE4">
+        <v>1.99</v>
+      </c>
+      <c r="AF4">
+        <v>1.8</v>
+      </c>
+      <c r="AG4">
+        <v>3.48</v>
+      </c>
+      <c r="AH4">
+        <v>1.24</v>
+      </c>
+      <c r="AI4">
+        <v>6.73</v>
+      </c>
+      <c r="AJ4">
+        <v>1.11</v>
+      </c>
+      <c r="AK4">
+        <v>1.73</v>
+      </c>
+      <c r="AL4">
         <v>2</v>
       </c>
-      <c r="U4">
-        <v>3.79</v>
-      </c>
-      <c r="V4">
-        <v>1.52</v>
-      </c>
-      <c r="W4">
-        <v>2.43</v>
-      </c>
-      <c r="X4">
-        <v>3.4</v>
-      </c>
-      <c r="Y4">
+      <c r="AM4">
         <v>1.27</v>
       </c>
-      <c r="Z4">
-        <v>8.5</v>
-      </c>
-      <c r="AA4">
-        <v>1.01</v>
-      </c>
-      <c r="AB4">
-        <v>1.05</v>
-      </c>
-      <c r="AC4">
-        <v>1.42</v>
-      </c>
-      <c r="AD4">
-        <v>2.51</v>
-      </c>
-      <c r="AE4">
-        <v>2.38</v>
-      </c>
-      <c r="AF4">
-        <v>1.53</v>
-      </c>
-      <c r="AG4">
-        <v>4.5</v>
-      </c>
-      <c r="AH4">
-        <v>1.15</v>
-      </c>
-      <c r="AI4">
-        <v>9</v>
-      </c>
-      <c r="AJ4">
-        <v>1.01</v>
-      </c>
-      <c r="AK4">
-        <v>2.05</v>
-      </c>
-      <c r="AL4">
-        <v>1.69</v>
-      </c>
-      <c r="AM4">
-        <v>1.33</v>
-      </c>
       <c r="AN4">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="AO4">
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="AQ4">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="AR4">
-        <v>3.14</v>
+        <v>2.02</v>
       </c>
       <c r="AS4">
-        <v>3.48</v>
+        <v>2.8</v>
       </c>
       <c r="AT4">
-        <v>5.24</v>
+        <v>3.98</v>
       </c>
       <c r="AU4">
-        <v>2.31</v>
+        <v>2.74</v>
       </c>
       <c r="AV4">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="AW4">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="AX4">
+        <v>1.35</v>
+      </c>
+      <c r="AY4">
+        <v>1.16</v>
+      </c>
+      <c r="AZ4">
+        <v>1.81</v>
+      </c>
+      <c r="BA4">
+        <v>2.17</v>
+      </c>
+      <c r="BB4">
         <v>1.22</v>
       </c>
-      <c r="AY4">
-        <v>1.08</v>
-      </c>
-      <c r="AZ4">
-        <v>1.65</v>
-      </c>
-      <c r="BA4">
-        <v>3.02</v>
-      </c>
-      <c r="BB4">
-        <v>1.33</v>
-      </c>
       <c r="BC4">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="BD4">
-        <v>3.04</v>
+        <v>3.66</v>
       </c>
       <c r="BE4">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="BF4">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="BG4">
         <v>0</v>
@@ -1734,133 +1734,133 @@
         <v>188</v>
       </c>
       <c r="P5">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q5">
         <v>3.1</v>
       </c>
       <c r="R5">
-        <v>2.83</v>
+        <v>3.8</v>
       </c>
       <c r="S5">
+        <v>2.77</v>
+      </c>
+      <c r="T5">
+        <v>2</v>
+      </c>
+      <c r="U5">
+        <v>3.79</v>
+      </c>
+      <c r="V5">
+        <v>1.52</v>
+      </c>
+      <c r="W5">
+        <v>2.43</v>
+      </c>
+      <c r="X5">
+        <v>3.4</v>
+      </c>
+      <c r="Y5">
+        <v>1.27</v>
+      </c>
+      <c r="Z5">
+        <v>8.5</v>
+      </c>
+      <c r="AA5">
+        <v>1.01</v>
+      </c>
+      <c r="AB5">
+        <v>1.06</v>
+      </c>
+      <c r="AC5">
+        <v>1.47</v>
+      </c>
+      <c r="AD5">
         <v>2.7</v>
       </c>
-      <c r="T5">
+      <c r="AE5">
+        <v>2.38</v>
+      </c>
+      <c r="AF5">
+        <v>1.53</v>
+      </c>
+      <c r="AG5">
+        <v>4.5</v>
+      </c>
+      <c r="AH5">
+        <v>1.15</v>
+      </c>
+      <c r="AI5">
+        <v>9</v>
+      </c>
+      <c r="AJ5">
+        <v>1.01</v>
+      </c>
+      <c r="AK5">
         <v>2.05</v>
       </c>
-      <c r="U5">
-        <v>3.65</v>
-      </c>
-      <c r="V5">
+      <c r="AL5">
+        <v>1.69</v>
+      </c>
+      <c r="AM5">
+        <v>1.33</v>
+      </c>
+      <c r="AN5">
+        <v>1.7</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>1.5</v>
+      </c>
+      <c r="AQ5">
+        <v>1.92</v>
+      </c>
+      <c r="AR5">
+        <v>2.35</v>
+      </c>
+      <c r="AS5">
+        <v>3.48</v>
+      </c>
+      <c r="AT5">
+        <v>5.24</v>
+      </c>
+      <c r="AU5">
+        <v>2.48</v>
+      </c>
+      <c r="AV5">
+        <v>1.79</v>
+      </c>
+      <c r="AW5">
         <v>1.44</v>
       </c>
-      <c r="W5">
-        <v>2.59</v>
-      </c>
-      <c r="X5">
+      <c r="AX5">
+        <v>1.22</v>
+      </c>
+      <c r="AY5">
+        <v>1.08</v>
+      </c>
+      <c r="AZ5">
+        <v>1.65</v>
+      </c>
+      <c r="BA5">
+        <v>3.02</v>
+      </c>
+      <c r="BB5">
+        <v>1.33</v>
+      </c>
+      <c r="BC5">
+        <v>2.5</v>
+      </c>
+      <c r="BD5">
         <v>3.04</v>
       </c>
-      <c r="Y5">
-        <v>1.33</v>
-      </c>
-      <c r="Z5">
-        <v>7.6</v>
-      </c>
-      <c r="AA5">
-        <v>1.03</v>
-      </c>
-      <c r="AB5">
-        <v>1.02</v>
-      </c>
-      <c r="AC5">
-        <v>1.31</v>
-      </c>
-      <c r="AD5">
-        <v>2.94</v>
-      </c>
-      <c r="AE5">
-        <v>2.1</v>
-      </c>
-      <c r="AF5">
-        <v>1.7</v>
-      </c>
-      <c r="AG5">
-        <v>3.78</v>
-      </c>
-      <c r="AH5">
-        <v>1.22</v>
-      </c>
-      <c r="AI5">
-        <v>7.1</v>
-      </c>
-      <c r="AJ5">
-        <v>1.04</v>
-      </c>
-      <c r="AK5">
-        <v>1.82</v>
-      </c>
-      <c r="AL5">
-        <v>1.88</v>
-      </c>
-      <c r="AM5">
-        <v>1.32</v>
-      </c>
-      <c r="AN5">
-        <v>1.6</v>
-      </c>
-      <c r="AO5">
-        <v>0</v>
-      </c>
-      <c r="AP5">
-        <v>1.56</v>
-      </c>
-      <c r="AQ5">
-        <v>1.96</v>
-      </c>
-      <c r="AR5">
-        <v>3.25</v>
-      </c>
-      <c r="AS5">
-        <v>3.6</v>
-      </c>
-      <c r="AT5">
-        <v>5.47</v>
-      </c>
-      <c r="AU5">
-        <v>2.26</v>
-      </c>
-      <c r="AV5">
-        <v>1.75</v>
-      </c>
-      <c r="AW5">
-        <v>1.42</v>
-      </c>
-      <c r="AX5">
-        <v>1.2</v>
-      </c>
-      <c r="AY5">
-        <v>1.07</v>
-      </c>
-      <c r="AZ5">
-        <v>1.72</v>
-      </c>
-      <c r="BA5">
-        <v>2.3</v>
-      </c>
-      <c r="BB5">
-        <v>1.24</v>
-      </c>
-      <c r="BC5">
-        <v>2.3</v>
-      </c>
-      <c r="BD5">
-        <v>3.5</v>
-      </c>
       <c r="BE5">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="BF5">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="BG5">
         <v>0</v>
@@ -1919,37 +1919,37 @@
         <v>188</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S6">
-        <v>3.24</v>
+        <v>2.91</v>
       </c>
       <c r="T6">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="U6">
-        <v>3.24</v>
+        <v>4.06</v>
       </c>
       <c r="V6">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W6">
-        <v>2.94</v>
+        <v>2.59</v>
       </c>
       <c r="X6">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="Y6">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="Z6">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="AA6">
         <v>1.03</v>
@@ -1958,94 +1958,94 @@
         <v>1.02</v>
       </c>
       <c r="AC6">
+        <v>1.31</v>
+      </c>
+      <c r="AD6">
+        <v>2.94</v>
+      </c>
+      <c r="AE6">
+        <v>2.12</v>
+      </c>
+      <c r="AF6">
+        <v>1.7</v>
+      </c>
+      <c r="AG6">
+        <v>3.65</v>
+      </c>
+      <c r="AH6">
         <v>1.27</v>
       </c>
-      <c r="AD6">
-        <v>3.18</v>
-      </c>
-      <c r="AE6">
-        <v>1.99</v>
-      </c>
-      <c r="AF6">
-        <v>1.8</v>
-      </c>
-      <c r="AG6">
-        <v>3.48</v>
-      </c>
-      <c r="AH6">
+      <c r="AI6">
+        <v>7.1</v>
+      </c>
+      <c r="AJ6">
+        <v>1.04</v>
+      </c>
+      <c r="AK6">
+        <v>1.78</v>
+      </c>
+      <c r="AL6">
+        <v>1.88</v>
+      </c>
+      <c r="AM6">
+        <v>1.32</v>
+      </c>
+      <c r="AN6">
+        <v>1.6</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>1.56</v>
+      </c>
+      <c r="AQ6">
+        <v>1.96</v>
+      </c>
+      <c r="AR6">
+        <v>3.25</v>
+      </c>
+      <c r="AS6">
+        <v>3.6</v>
+      </c>
+      <c r="AT6">
+        <v>5.47</v>
+      </c>
+      <c r="AU6">
+        <v>2.26</v>
+      </c>
+      <c r="AV6">
+        <v>1.75</v>
+      </c>
+      <c r="AW6">
+        <v>1.42</v>
+      </c>
+      <c r="AX6">
+        <v>1.2</v>
+      </c>
+      <c r="AY6">
+        <v>1.07</v>
+      </c>
+      <c r="AZ6">
+        <v>1.72</v>
+      </c>
+      <c r="BA6">
+        <v>2.3</v>
+      </c>
+      <c r="BB6">
         <v>1.24</v>
       </c>
-      <c r="AI6">
-        <v>6.73</v>
-      </c>
-      <c r="AJ6">
-        <v>1.11</v>
-      </c>
-      <c r="AK6">
-        <v>1.73</v>
-      </c>
-      <c r="AL6">
-        <v>2</v>
-      </c>
-      <c r="AM6">
-        <v>1.27</v>
-      </c>
-      <c r="AN6">
-        <v>1.46</v>
-      </c>
-      <c r="AO6">
-        <v>0</v>
-      </c>
-      <c r="AP6">
-        <v>1.36</v>
-      </c>
-      <c r="AQ6">
-        <v>1.64</v>
-      </c>
-      <c r="AR6">
-        <v>2.02</v>
-      </c>
-      <c r="AS6">
-        <v>2.79</v>
-      </c>
-      <c r="AT6">
-        <v>3.96</v>
-      </c>
-      <c r="AU6">
-        <v>2.75</v>
-      </c>
-      <c r="AV6">
-        <v>2.1</v>
-      </c>
-      <c r="AW6">
-        <v>1.64</v>
-      </c>
-      <c r="AX6">
-        <v>1.35</v>
-      </c>
-      <c r="AY6">
-        <v>1.16</v>
-      </c>
-      <c r="AZ6">
-        <v>1.81</v>
-      </c>
-      <c r="BA6">
-        <v>2.17</v>
-      </c>
-      <c r="BB6">
-        <v>1.22</v>
-      </c>
       <c r="BC6">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="BD6">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="BE6">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="BF6">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BG6">
         <v>0</v>
@@ -2250,10 +2250,10 @@
         <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E8" t="s">
         <v>113</v>
@@ -2289,133 +2289,133 @@
         <v>188</v>
       </c>
       <c r="P8">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R8">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="X8">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Y8">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA8">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC8">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD8">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AE8">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AH8">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK8">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AL8">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN8">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AO8">
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ8">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AR8">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AS8">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU8">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AV8">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AW8">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AX8">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY8">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ8">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="BA8">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="BB8">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC8">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="BD8">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE8">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="BF8">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG8">
         <v>0</v>
@@ -2435,10 +2435,10 @@
         <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E9" t="s">
         <v>114</v>
@@ -2474,133 +2474,133 @@
         <v>188</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AO9">
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AU9">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AV9">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AX9">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ9">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BA9">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BD9">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE9">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG9">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>2.66</v>
       </c>
       <c r="X10">
-        <v>2.85</v>
+        <v>3.01</v>
       </c>
       <c r="Y10">
         <v>1.36</v>
@@ -2704,7 +2704,7 @@
         <v>3.04</v>
       </c>
       <c r="AE10">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AF10">
         <v>1.79</v>
@@ -2749,10 +2749,10 @@
         <v>2.17</v>
       </c>
       <c r="AT10">
-        <v>2.86</v>
+        <v>2.74</v>
       </c>
       <c r="AU10">
-        <v>3.68</v>
+        <v>3.84</v>
       </c>
       <c r="AV10">
         <v>2.67</v>
@@ -2764,7 +2764,7 @@
         <v>1.6</v>
       </c>
       <c r="AY10">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AZ10">
         <v>1.56</v>
@@ -3029,133 +3029,133 @@
         <v>188</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T12">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="U12">
-        <v>2.19</v>
+        <v>2.8</v>
       </c>
       <c r="V12">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="W12">
-        <v>2.95</v>
+        <v>3.6</v>
       </c>
       <c r="X12">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="Y12">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="Z12">
-        <v>6.2</v>
+        <v>4.45</v>
       </c>
       <c r="AA12">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AB12">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AC12">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AD12">
-        <v>3.5</v>
+        <v>5.65</v>
       </c>
       <c r="AE12">
-        <v>1.82</v>
+        <v>1.45</v>
       </c>
       <c r="AF12">
-        <v>1.94</v>
+        <v>2.69</v>
       </c>
       <c r="AG12">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="AH12">
-        <v>1.31</v>
+        <v>1.76</v>
       </c>
       <c r="AI12">
-        <v>5.5</v>
+        <v>3.33</v>
       </c>
       <c r="AJ12">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AK12">
-        <v>1.81</v>
+        <v>1.36</v>
       </c>
       <c r="AL12">
-        <v>1.9</v>
+        <v>2.84</v>
       </c>
       <c r="AM12">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AN12">
-        <v>1.16</v>
+        <v>1.44</v>
       </c>
       <c r="AO12">
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AQ12">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AR12">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AS12">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="AT12">
-        <v>2.84</v>
+        <v>2.32</v>
       </c>
       <c r="AU12">
-        <v>3.72</v>
+        <v>4.84</v>
       </c>
       <c r="AV12">
-        <v>2.59</v>
+        <v>3.19</v>
       </c>
       <c r="AW12">
-        <v>2.02</v>
+        <v>2.44</v>
       </c>
       <c r="AX12">
+        <v>1.91</v>
+      </c>
+      <c r="AY12">
+        <v>1.52</v>
+      </c>
+      <c r="AZ12">
+        <v>1.93</v>
+      </c>
+      <c r="BA12">
+        <v>2.09</v>
+      </c>
+      <c r="BB12">
+        <v>1.1</v>
+      </c>
+      <c r="BC12">
         <v>1.6</v>
       </c>
-      <c r="AY12">
-        <v>1.34</v>
-      </c>
-      <c r="AZ12">
-        <v>5.03</v>
-      </c>
-      <c r="BA12">
-        <v>1.29</v>
-      </c>
-      <c r="BB12">
-        <v>1.22</v>
-      </c>
-      <c r="BC12">
-        <v>2.05</v>
-      </c>
       <c r="BD12">
-        <v>3.9</v>
+        <v>5.8</v>
       </c>
       <c r="BE12">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="BF12">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="BG12">
         <v>0</v>
@@ -3214,133 +3214,133 @@
         <v>188</v>
       </c>
       <c r="P13">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q13">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R13">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S13">
+        <v>5</v>
+      </c>
+      <c r="T13">
+        <v>2.24</v>
+      </c>
+      <c r="U13">
+        <v>2.19</v>
+      </c>
+      <c r="V13">
+        <v>1.33</v>
+      </c>
+      <c r="W13">
+        <v>2.95</v>
+      </c>
+      <c r="X13">
+        <v>2.5</v>
+      </c>
+      <c r="Y13">
+        <v>1.42</v>
+      </c>
+      <c r="Z13">
+        <v>6.2</v>
+      </c>
+      <c r="AA13">
+        <v>1.1</v>
+      </c>
+      <c r="AB13">
+        <v>1.05</v>
+      </c>
+      <c r="AC13">
+        <v>1.22</v>
+      </c>
+      <c r="AD13">
+        <v>3.5</v>
+      </c>
+      <c r="AE13">
+        <v>1.82</v>
+      </c>
+      <c r="AF13">
+        <v>1.94</v>
+      </c>
+      <c r="AG13">
         <v>3</v>
       </c>
-      <c r="T13">
-        <v>2.27</v>
-      </c>
-      <c r="U13">
-        <v>2.81</v>
-      </c>
-      <c r="V13">
+      <c r="AH13">
+        <v>1.31</v>
+      </c>
+      <c r="AI13">
+        <v>5.5</v>
+      </c>
+      <c r="AJ13">
+        <v>1.08</v>
+      </c>
+      <c r="AK13">
+        <v>1.81</v>
+      </c>
+      <c r="AL13">
+        <v>1.9</v>
+      </c>
+      <c r="AM13">
+        <v>1.24</v>
+      </c>
+      <c r="AN13">
+        <v>1.16</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>1.19</v>
+      </c>
+      <c r="AQ13">
+        <v>1.38</v>
+      </c>
+      <c r="AR13">
+        <v>1.69</v>
+      </c>
+      <c r="AS13">
+        <v>2.16</v>
+      </c>
+      <c r="AT13">
+        <v>2.84</v>
+      </c>
+      <c r="AU13">
+        <v>3.72</v>
+      </c>
+      <c r="AV13">
+        <v>2.59</v>
+      </c>
+      <c r="AW13">
+        <v>2.02</v>
+      </c>
+      <c r="AX13">
+        <v>1.61</v>
+      </c>
+      <c r="AY13">
+        <v>1.34</v>
+      </c>
+      <c r="AZ13">
+        <v>5.03</v>
+      </c>
+      <c r="BA13">
+        <v>1.29</v>
+      </c>
+      <c r="BB13">
         <v>1.22</v>
       </c>
-      <c r="W13">
-        <v>3.6</v>
-      </c>
-      <c r="X13">
-        <v>2.08</v>
-      </c>
-      <c r="Y13">
-        <v>1.69</v>
-      </c>
-      <c r="Z13">
-        <v>4.45</v>
-      </c>
-      <c r="AA13">
-        <v>1.14</v>
-      </c>
-      <c r="AB13">
-        <v>1.02</v>
-      </c>
-      <c r="AC13">
-        <v>1.13</v>
-      </c>
-      <c r="AD13">
-        <v>5.65</v>
-      </c>
-      <c r="AE13">
-        <v>1.44</v>
-      </c>
-      <c r="AF13">
-        <v>2.65</v>
-      </c>
-      <c r="AG13">
-        <v>2.06</v>
-      </c>
-      <c r="AH13">
-        <v>1.73</v>
-      </c>
-      <c r="AI13">
-        <v>3.33</v>
-      </c>
-      <c r="AJ13">
-        <v>1.3</v>
-      </c>
-      <c r="AK13">
-        <v>1.36</v>
-      </c>
-      <c r="AL13">
-        <v>2.9</v>
-      </c>
-      <c r="AM13">
-        <v>1.28</v>
-      </c>
-      <c r="AN13">
-        <v>1.44</v>
-      </c>
-      <c r="AO13">
-        <v>0</v>
-      </c>
-      <c r="AP13">
-        <v>1.11</v>
-      </c>
-      <c r="AQ13">
-        <v>1.26</v>
-      </c>
-      <c r="AR13">
-        <v>1.65</v>
-      </c>
-      <c r="AS13">
-        <v>1.85</v>
-      </c>
-      <c r="AT13">
-        <v>2.32</v>
-      </c>
-      <c r="AU13">
-        <v>4.84</v>
-      </c>
-      <c r="AV13">
-        <v>3.19</v>
-      </c>
-      <c r="AW13">
-        <v>2.44</v>
-      </c>
-      <c r="AX13">
-        <v>1.91</v>
-      </c>
-      <c r="AY13">
-        <v>1.52</v>
-      </c>
-      <c r="AZ13">
-        <v>1.93</v>
-      </c>
-      <c r="BA13">
-        <v>2.09</v>
-      </c>
-      <c r="BB13">
-        <v>1.08</v>
-      </c>
       <c r="BC13">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="BD13">
-        <v>5.7</v>
+        <v>3.9</v>
       </c>
       <c r="BE13">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="BF13">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="BG13">
         <v>0</v>
@@ -3360,10 +3360,10 @@
         <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E14" t="s">
         <v>119</v>
@@ -3408,124 +3408,124 @@
         <v>0</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC14">
-        <v>1.12</v>
+        <v>1.35</v>
       </c>
       <c r="AD14">
-        <v>4.8</v>
+        <v>3.13</v>
       </c>
       <c r="AE14">
-        <v>1.45</v>
+        <v>2.14</v>
       </c>
       <c r="AF14">
-        <v>2.43</v>
+        <v>1.69</v>
       </c>
       <c r="AG14">
-        <v>2.14</v>
+        <v>3.73</v>
       </c>
       <c r="AH14">
-        <v>1.58</v>
+        <v>1.21</v>
       </c>
       <c r="AI14">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="AJ14">
-        <v>1.23</v>
+        <v>1.03</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM14">
+        <v>1.36</v>
+      </c>
+      <c r="AN14">
+        <v>1.46</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>1.1</v>
+      </c>
+      <c r="AQ14">
+        <v>1.26</v>
+      </c>
+      <c r="AR14">
+        <v>1.65</v>
+      </c>
+      <c r="AS14">
+        <v>1.85</v>
+      </c>
+      <c r="AT14">
+        <v>2.31</v>
+      </c>
+      <c r="AU14">
+        <v>4.86</v>
+      </c>
+      <c r="AV14">
+        <v>3.2</v>
+      </c>
+      <c r="AW14">
+        <v>2.34</v>
+      </c>
+      <c r="AX14">
+        <v>1.85</v>
+      </c>
+      <c r="AY14">
+        <v>1.52</v>
+      </c>
+      <c r="AZ14">
+        <v>1.78</v>
+      </c>
+      <c r="BA14">
+        <v>2.57</v>
+      </c>
+      <c r="BB14">
+        <v>1.24</v>
+      </c>
+      <c r="BC14">
+        <v>2.29</v>
+      </c>
+      <c r="BD14">
+        <v>3.44</v>
+      </c>
+      <c r="BE14">
+        <v>1.57</v>
+      </c>
+      <c r="BF14">
         <v>1.11</v>
-      </c>
-      <c r="AN14">
-        <v>1.05</v>
-      </c>
-      <c r="AO14">
-        <v>0</v>
-      </c>
-      <c r="AP14">
-        <v>0</v>
-      </c>
-      <c r="AQ14">
-        <v>0</v>
-      </c>
-      <c r="AR14">
-        <v>0</v>
-      </c>
-      <c r="AS14">
-        <v>0</v>
-      </c>
-      <c r="AT14">
-        <v>0</v>
-      </c>
-      <c r="AU14">
-        <v>0</v>
-      </c>
-      <c r="AV14">
-        <v>0</v>
-      </c>
-      <c r="AW14">
-        <v>0</v>
-      </c>
-      <c r="AX14">
-        <v>0</v>
-      </c>
-      <c r="AY14">
-        <v>0</v>
-      </c>
-      <c r="AZ14">
-        <v>0</v>
-      </c>
-      <c r="BA14">
-        <v>0</v>
-      </c>
-      <c r="BB14">
-        <v>0</v>
-      </c>
-      <c r="BC14">
-        <v>0</v>
-      </c>
-      <c r="BD14">
-        <v>0</v>
-      </c>
-      <c r="BE14">
-        <v>0</v>
-      </c>
-      <c r="BF14">
-        <v>0</v>
       </c>
       <c r="BG14">
         <v>0</v>
@@ -3915,10 +3915,10 @@
         <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E17" t="s">
         <v>122</v>
@@ -3993,28 +3993,28 @@
         <v>0</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI17">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK17">
         <v>0</v>
@@ -4023,10 +4023,10 @@
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AO17">
         <v>0</v>
@@ -4694,13 +4694,13 @@
         <v>188</v>
       </c>
       <c r="P21">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q21">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R21">
-        <v>3.84</v>
+        <v>3.75</v>
       </c>
       <c r="S21">
         <v>2.71</v>
@@ -4721,7 +4721,7 @@
         <v>3.25</v>
       </c>
       <c r="Y21">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z21">
         <v>8.5</v>
@@ -4733,13 +4733,13 @@
         <v>1.04</v>
       </c>
       <c r="AC21">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AD21">
         <v>2.62</v>
       </c>
       <c r="AE21">
-        <v>2.16</v>
+        <v>2.31</v>
       </c>
       <c r="AF21">
         <v>1.58</v>
@@ -4799,7 +4799,7 @@
         <v>1.31</v>
       </c>
       <c r="AY21">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AZ21">
         <v>1.87</v>
@@ -6144,7 +6144,7 @@
         <v>134</v>
       </c>
       <c r="F29" t="s">
-        <v>175</v>
+        <v>145</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -6329,7 +6329,7 @@
         <v>135</v>
       </c>
       <c r="F30" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -6544,133 +6544,133 @@
         <v>188</v>
       </c>
       <c r="P31">
-        <v>5.48</v>
+        <v>1.4</v>
       </c>
       <c r="Q31">
-        <v>3.12</v>
+        <v>4</v>
       </c>
       <c r="R31">
-        <v>1.7</v>
+        <v>6.5</v>
       </c>
       <c r="S31">
-        <v>6</v>
+        <v>1.88</v>
       </c>
       <c r="T31">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="U31">
-        <v>2.42</v>
+        <v>8.1</v>
       </c>
       <c r="V31">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="W31">
-        <v>2.26</v>
+        <v>2.56</v>
       </c>
       <c r="X31">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="Y31">
+        <v>1.33</v>
+      </c>
+      <c r="Z31">
+        <v>7.1</v>
+      </c>
+      <c r="AA31">
+        <v>1.04</v>
+      </c>
+      <c r="AB31">
+        <v>1.06</v>
+      </c>
+      <c r="AC31">
+        <v>1.31</v>
+      </c>
+      <c r="AD31">
+        <v>2.92</v>
+      </c>
+      <c r="AE31">
+        <v>2.02</v>
+      </c>
+      <c r="AF31">
+        <v>1.71</v>
+      </c>
+      <c r="AG31">
+        <v>3.42</v>
+      </c>
+      <c r="AH31">
+        <v>1.27</v>
+      </c>
+      <c r="AI31">
+        <v>6.45</v>
+      </c>
+      <c r="AJ31">
+        <v>1.05</v>
+      </c>
+      <c r="AK31">
+        <v>2.25</v>
+      </c>
+      <c r="AL31">
+        <v>1.6</v>
+      </c>
+      <c r="AM31">
+        <v>1.16</v>
+      </c>
+      <c r="AN31">
+        <v>2.5</v>
+      </c>
+      <c r="AO31">
+        <v>0</v>
+      </c>
+      <c r="AP31">
+        <v>1.24</v>
+      </c>
+      <c r="AQ31">
+        <v>1.52</v>
+      </c>
+      <c r="AR31">
+        <v>1.83</v>
+      </c>
+      <c r="AS31">
+        <v>2.33</v>
+      </c>
+      <c r="AT31">
+        <v>3.14</v>
+      </c>
+      <c r="AU31">
+        <v>3.34</v>
+      </c>
+      <c r="AV31">
+        <v>2.38</v>
+      </c>
+      <c r="AW31">
+        <v>1.83</v>
+      </c>
+      <c r="AX31">
+        <v>1.48</v>
+      </c>
+      <c r="AY31">
+        <v>1.27</v>
+      </c>
+      <c r="AZ31">
+        <v>1.3</v>
+      </c>
+      <c r="BA31">
+        <v>4.32</v>
+      </c>
+      <c r="BB31">
         <v>1.22</v>
       </c>
-      <c r="Z31">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AA31">
-        <v>1.03</v>
-      </c>
-      <c r="AB31">
-        <v>1.11</v>
-      </c>
-      <c r="AC31">
+      <c r="BC31">
+        <v>2.3</v>
+      </c>
+      <c r="BD31">
+        <v>3.7</v>
+      </c>
+      <c r="BE31">
         <v>1.53</v>
       </c>
-      <c r="AD31">
-        <v>2.38</v>
-      </c>
-      <c r="AE31">
-        <v>2.66</v>
-      </c>
-      <c r="AF31">
-        <v>1.47</v>
-      </c>
-      <c r="AG31">
-        <v>5.25</v>
-      </c>
-      <c r="AH31">
+      <c r="BF31">
         <v>1.12</v>
-      </c>
-      <c r="AI31">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AJ31">
-        <v>1</v>
-      </c>
-      <c r="AK31">
-        <v>2.3</v>
-      </c>
-      <c r="AL31">
-        <v>1.55</v>
-      </c>
-      <c r="AM31">
-        <v>1.27</v>
-      </c>
-      <c r="AN31">
-        <v>1.1</v>
-      </c>
-      <c r="AO31">
-        <v>0</v>
-      </c>
-      <c r="AP31">
-        <v>1.36</v>
-      </c>
-      <c r="AQ31">
-        <v>1.69</v>
-      </c>
-      <c r="AR31">
-        <v>2.14</v>
-      </c>
-      <c r="AS31">
-        <v>2.88</v>
-      </c>
-      <c r="AT31">
-        <v>3.7</v>
-      </c>
-      <c r="AU31">
-        <v>2.7</v>
-      </c>
-      <c r="AV31">
-        <v>2</v>
-      </c>
-      <c r="AW31">
-        <v>1.57</v>
-      </c>
-      <c r="AX31">
-        <v>1.32</v>
-      </c>
-      <c r="AY31">
-        <v>1.23</v>
-      </c>
-      <c r="AZ31">
-        <v>2.39</v>
-      </c>
-      <c r="BA31">
-        <v>1.89</v>
-      </c>
-      <c r="BB31">
-        <v>1.33</v>
-      </c>
-      <c r="BC31">
-        <v>2.48</v>
-      </c>
-      <c r="BD31">
-        <v>3</v>
-      </c>
-      <c r="BE31">
-        <v>1.45</v>
-      </c>
-      <c r="BF31">
-        <v>1.06</v>
       </c>
       <c r="BG31">
         <v>0</v>
@@ -6690,10 +6690,10 @@
         <v>80</v>
       </c>
       <c r="C32" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D32" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E32" t="s">
         <v>137</v>
@@ -6729,133 +6729,133 @@
         <v>188</v>
       </c>
       <c r="P32">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="Q32">
-        <v>3.54</v>
+        <v>3.2</v>
       </c>
       <c r="R32">
+        <v>1.8</v>
+      </c>
+      <c r="S32">
+        <v>5.29</v>
+      </c>
+      <c r="T32">
+        <v>1.96</v>
+      </c>
+      <c r="U32">
+        <v>2.46</v>
+      </c>
+      <c r="V32">
+        <v>1.47</v>
+      </c>
+      <c r="W32">
+        <v>2.41</v>
+      </c>
+      <c r="X32">
+        <v>3</v>
+      </c>
+      <c r="Y32">
+        <v>1.3</v>
+      </c>
+      <c r="Z32">
+        <v>7.7</v>
+      </c>
+      <c r="AA32">
+        <v>1.02</v>
+      </c>
+      <c r="AB32">
+        <v>1.04</v>
+      </c>
+      <c r="AC32">
+        <v>1.4</v>
+      </c>
+      <c r="AD32">
+        <v>2.97</v>
+      </c>
+      <c r="AE32">
+        <v>2.16</v>
+      </c>
+      <c r="AF32">
+        <v>1.62</v>
+      </c>
+      <c r="AG32">
+        <v>4.1</v>
+      </c>
+      <c r="AH32">
+        <v>1.19</v>
+      </c>
+      <c r="AI32">
+        <v>7.3</v>
+      </c>
+      <c r="AJ32">
+        <v>1.03</v>
+      </c>
+      <c r="AK32">
+        <v>1.93</v>
+      </c>
+      <c r="AL32">
+        <v>1.73</v>
+      </c>
+      <c r="AM32">
+        <v>1.26</v>
+      </c>
+      <c r="AN32">
+        <v>1.14</v>
+      </c>
+      <c r="AO32">
+        <v>0</v>
+      </c>
+      <c r="AP32">
+        <v>1.28</v>
+      </c>
+      <c r="AQ32">
+        <v>1.53</v>
+      </c>
+      <c r="AR32">
+        <v>1.95</v>
+      </c>
+      <c r="AS32">
         <v>2.52</v>
       </c>
-      <c r="S32">
-        <v>0</v>
-      </c>
-      <c r="T32">
-        <v>0</v>
-      </c>
-      <c r="U32">
-        <v>0</v>
-      </c>
-      <c r="V32">
-        <v>0</v>
-      </c>
-      <c r="W32">
-        <v>0</v>
-      </c>
-      <c r="X32">
-        <v>0</v>
-      </c>
-      <c r="Y32">
-        <v>0</v>
-      </c>
-      <c r="Z32">
-        <v>0</v>
-      </c>
-      <c r="AA32">
-        <v>0</v>
-      </c>
-      <c r="AB32">
-        <v>0</v>
-      </c>
-      <c r="AC32">
-        <v>0</v>
-      </c>
-      <c r="AD32">
-        <v>0</v>
-      </c>
-      <c r="AE32">
-        <v>1.66</v>
-      </c>
-      <c r="AF32">
-        <v>2.15</v>
-      </c>
-      <c r="AG32">
-        <v>0</v>
-      </c>
-      <c r="AH32">
-        <v>0</v>
-      </c>
-      <c r="AI32">
-        <v>0</v>
-      </c>
-      <c r="AJ32">
-        <v>0</v>
-      </c>
-      <c r="AK32">
-        <v>0</v>
-      </c>
-      <c r="AL32">
-        <v>0</v>
-      </c>
-      <c r="AM32">
-        <v>0</v>
-      </c>
-      <c r="AN32">
-        <v>0</v>
-      </c>
-      <c r="AO32">
-        <v>0</v>
-      </c>
-      <c r="AP32">
-        <v>0</v>
-      </c>
-      <c r="AQ32">
-        <v>0</v>
-      </c>
-      <c r="AR32">
-        <v>0</v>
-      </c>
-      <c r="AS32">
-        <v>0</v>
-      </c>
       <c r="AT32">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AU32">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV32">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AW32">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AX32">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY32">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ32">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BA32">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BB32">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC32">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BD32">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE32">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF32">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG32">
         <v>0</v>
@@ -6875,7 +6875,7 @@
         <v>80</v>
       </c>
       <c r="C33" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D33" t="s">
         <v>105</v>
@@ -6914,133 +6914,133 @@
         <v>188</v>
       </c>
       <c r="P33">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="Q33">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="R33">
-        <v>6.5</v>
+        <v>3.65</v>
       </c>
       <c r="S33">
-        <v>1.88</v>
+        <v>2.5</v>
       </c>
       <c r="T33">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="U33">
-        <v>8.1</v>
+        <v>4.4</v>
       </c>
       <c r="V33">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="W33">
-        <v>2.56</v>
+        <v>2.73</v>
       </c>
       <c r="X33">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="Y33">
         <v>1.33</v>
       </c>
       <c r="Z33">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="AA33">
         <v>1.04</v>
       </c>
       <c r="AB33">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AC33">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AD33">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="AE33">
         <v>2.02</v>
       </c>
       <c r="AF33">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AG33">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="AH33">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AI33">
-        <v>6.45</v>
+        <v>6.75</v>
       </c>
       <c r="AJ33">
         <v>1.05</v>
       </c>
       <c r="AK33">
-        <v>2.25</v>
+        <v>1.79</v>
       </c>
       <c r="AL33">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="AM33">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AN33">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="AO33">
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AQ33">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AR33">
-        <v>1.83</v>
+        <v>2.63</v>
       </c>
       <c r="AS33">
-        <v>2.33</v>
+        <v>2.93</v>
       </c>
       <c r="AT33">
-        <v>3.14</v>
+        <v>4.2</v>
       </c>
       <c r="AU33">
+        <v>2.63</v>
+      </c>
+      <c r="AV33">
+        <v>1.98</v>
+      </c>
+      <c r="AW33">
+        <v>1.59</v>
+      </c>
+      <c r="AX33">
+        <v>1.32</v>
+      </c>
+      <c r="AY33">
+        <v>1.14</v>
+      </c>
+      <c r="AZ33">
+        <v>1.68</v>
+      </c>
+      <c r="BA33">
         <v>3.34</v>
       </c>
-      <c r="AV33">
-        <v>2.38</v>
-      </c>
-      <c r="AW33">
-        <v>1.83</v>
-      </c>
-      <c r="AX33">
-        <v>1.48</v>
-      </c>
-      <c r="AY33">
-        <v>1.27</v>
-      </c>
-      <c r="AZ33">
-        <v>1.3</v>
-      </c>
-      <c r="BA33">
-        <v>4.32</v>
-      </c>
       <c r="BB33">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="BC33">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="BD33">
-        <v>3.7</v>
+        <v>3.52</v>
       </c>
       <c r="BE33">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="BF33">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BG33">
         <v>0</v>
@@ -7060,10 +7060,10 @@
         <v>80</v>
       </c>
       <c r="C34" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D34" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E34" t="s">
         <v>139</v>
@@ -7099,133 +7099,133 @@
         <v>188</v>
       </c>
       <c r="P34">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="Q34">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="R34">
-        <v>1.8</v>
+        <v>2.32</v>
       </c>
       <c r="S34">
-        <v>5.29</v>
+        <v>0</v>
       </c>
       <c r="T34">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="U34">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="V34">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W34">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="X34">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y34">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z34">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AA34">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB34">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC34">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD34">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AE34">
-        <v>2.16</v>
+        <v>1.66</v>
       </c>
       <c r="AF34">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="AG34">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AH34">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI34">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AJ34">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK34">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AL34">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM34">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN34">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AO34">
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ34">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR34">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AS34">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AT34">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AU34">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AV34">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AW34">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AX34">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY34">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ34">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="BA34">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="BB34">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BC34">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BD34">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BE34">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BF34">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG34">
         <v>0</v>
@@ -7245,7 +7245,7 @@
         <v>80</v>
       </c>
       <c r="C35" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D35" t="s">
         <v>105</v>
@@ -7284,133 +7284,133 @@
         <v>188</v>
       </c>
       <c r="P35">
-        <v>1.99</v>
+        <v>5.48</v>
       </c>
       <c r="Q35">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="R35">
+        <v>1.7</v>
+      </c>
+      <c r="S35">
+        <v>6</v>
+      </c>
+      <c r="T35">
+        <v>1.87</v>
+      </c>
+      <c r="U35">
+        <v>2.42</v>
+      </c>
+      <c r="V35">
+        <v>1.56</v>
+      </c>
+      <c r="W35">
+        <v>2.26</v>
+      </c>
+      <c r="X35">
         <v>3.5</v>
       </c>
-      <c r="S35">
-        <v>2.5</v>
-      </c>
-      <c r="T35">
-        <v>2.16</v>
-      </c>
-      <c r="U35">
-        <v>4.31</v>
-      </c>
-      <c r="V35">
+      <c r="Y35">
+        <v>1.22</v>
+      </c>
+      <c r="Z35">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AA35">
+        <v>1.03</v>
+      </c>
+      <c r="AB35">
+        <v>1.11</v>
+      </c>
+      <c r="AC35">
+        <v>1.53</v>
+      </c>
+      <c r="AD35">
+        <v>2.38</v>
+      </c>
+      <c r="AE35">
+        <v>2.66</v>
+      </c>
+      <c r="AF35">
+        <v>1.47</v>
+      </c>
+      <c r="AG35">
+        <v>5.25</v>
+      </c>
+      <c r="AH35">
+        <v>1.12</v>
+      </c>
+      <c r="AI35">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AJ35">
+        <v>1</v>
+      </c>
+      <c r="AK35">
+        <v>2.3</v>
+      </c>
+      <c r="AL35">
+        <v>1.55</v>
+      </c>
+      <c r="AM35">
+        <v>1.27</v>
+      </c>
+      <c r="AN35">
+        <v>1.1</v>
+      </c>
+      <c r="AO35">
+        <v>0</v>
+      </c>
+      <c r="AP35">
         <v>1.36</v>
-      </c>
-      <c r="W35">
-        <v>2.9</v>
-      </c>
-      <c r="X35">
-        <v>2.89</v>
-      </c>
-      <c r="Y35">
-        <v>1.33</v>
-      </c>
-      <c r="Z35">
-        <v>7</v>
-      </c>
-      <c r="AA35">
-        <v>1.06</v>
-      </c>
-      <c r="AB35">
-        <v>1.02</v>
-      </c>
-      <c r="AC35">
-        <v>1.27</v>
-      </c>
-      <c r="AD35">
-        <v>3.2</v>
-      </c>
-      <c r="AE35">
-        <v>2.02</v>
-      </c>
-      <c r="AF35">
-        <v>1.68</v>
-      </c>
-      <c r="AG35">
-        <v>3.6</v>
-      </c>
-      <c r="AH35">
-        <v>1.24</v>
-      </c>
-      <c r="AI35">
-        <v>6.75</v>
-      </c>
-      <c r="AJ35">
-        <v>1.06</v>
-      </c>
-      <c r="AK35">
-        <v>1.8</v>
-      </c>
-      <c r="AL35">
-        <v>1.92</v>
-      </c>
-      <c r="AM35">
-        <v>1.3</v>
-      </c>
-      <c r="AN35">
-        <v>1.76</v>
-      </c>
-      <c r="AO35">
-        <v>0</v>
-      </c>
-      <c r="AP35">
-        <v>1.4</v>
       </c>
       <c r="AQ35">
         <v>1.69</v>
       </c>
       <c r="AR35">
-        <v>2.51</v>
+        <v>2.14</v>
       </c>
       <c r="AS35">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AT35">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AU35">
         <v>2.7</v>
       </c>
       <c r="AV35">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AW35">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AX35">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AY35">
         <v>1.23</v>
       </c>
       <c r="AZ35">
-        <v>1.68</v>
+        <v>2.39</v>
       </c>
       <c r="BA35">
-        <v>2.5</v>
+        <v>1.89</v>
       </c>
       <c r="BB35">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="BC35">
-        <v>2.12</v>
+        <v>2.48</v>
       </c>
       <c r="BD35">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="BE35">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="BF35">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="BG35">
         <v>0</v>
@@ -7654,79 +7654,79 @@
         <v>188</v>
       </c>
       <c r="P37">
-        <v>2</v>
+        <v>5.6</v>
       </c>
       <c r="Q37">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="R37">
-        <v>3.95</v>
+        <v>1.5</v>
       </c>
       <c r="S37">
-        <v>2.88</v>
+        <v>7</v>
       </c>
       <c r="T37">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="U37">
-        <v>5.1</v>
+        <v>2.13</v>
       </c>
       <c r="V37">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="W37">
-        <v>2.11</v>
+        <v>2.31</v>
       </c>
       <c r="X37">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="Y37">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z37">
-        <v>13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA37">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AB37">
+        <v>1.07</v>
+      </c>
+      <c r="AC37">
+        <v>1.44</v>
+      </c>
+      <c r="AD37">
+        <v>2.43</v>
+      </c>
+      <c r="AE37">
+        <v>2.53</v>
+      </c>
+      <c r="AF37">
+        <v>1.49</v>
+      </c>
+      <c r="AG37">
+        <v>4.65</v>
+      </c>
+      <c r="AH37">
         <v>1.12</v>
       </c>
-      <c r="AC37">
-        <v>1.58</v>
-      </c>
-      <c r="AD37">
-        <v>2.25</v>
-      </c>
-      <c r="AE37">
-        <v>2.74</v>
-      </c>
-      <c r="AF37">
-        <v>1.35</v>
-      </c>
-      <c r="AG37">
-        <v>6.33</v>
-      </c>
-      <c r="AH37">
-        <v>1.1</v>
-      </c>
       <c r="AI37">
-        <v>9.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AJ37">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AK37">
-        <v>2.3</v>
+        <v>2.51</v>
       </c>
       <c r="AL37">
         <v>1.53</v>
       </c>
       <c r="AM37">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AN37">
-        <v>1.63</v>
+        <v>1.04</v>
       </c>
       <c r="AO37">
         <v>0</v>
@@ -7735,52 +7735,52 @@
         <v>1.42</v>
       </c>
       <c r="AQ37">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AR37">
+        <v>2.73</v>
+      </c>
+      <c r="AS37">
+        <v>3.04</v>
+      </c>
+      <c r="AT37">
+        <v>4.41</v>
+      </c>
+      <c r="AU37">
         <v>2.7</v>
       </c>
-      <c r="AS37">
-        <v>3</v>
-      </c>
-      <c r="AT37">
-        <v>4.34</v>
-      </c>
-      <c r="AU37">
-        <v>2.58</v>
-      </c>
       <c r="AV37">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AW37">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AX37">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AY37">
         <v>1.13</v>
       </c>
       <c r="AZ37">
-        <v>1.52</v>
+        <v>3.85</v>
       </c>
       <c r="BA37">
-        <v>3.42</v>
+        <v>1.42</v>
       </c>
       <c r="BB37">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="BC37">
         <v>2.7</v>
       </c>
       <c r="BD37">
-        <v>2.66</v>
+        <v>2.91</v>
       </c>
       <c r="BE37">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="BF37">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BG37">
         <v>0</v>
@@ -7839,79 +7839,79 @@
         <v>188</v>
       </c>
       <c r="P38">
-        <v>5.6</v>
+        <v>2</v>
       </c>
       <c r="Q38">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="R38">
-        <v>1.5</v>
+        <v>3.95</v>
       </c>
       <c r="S38">
-        <v>7</v>
+        <v>2.88</v>
       </c>
       <c r="T38">
-        <v>1.96</v>
+        <v>1.75</v>
       </c>
       <c r="U38">
-        <v>2.13</v>
+        <v>5.1</v>
       </c>
       <c r="V38">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="W38">
-        <v>2.31</v>
+        <v>2.11</v>
       </c>
       <c r="X38">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="Y38">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z38">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AA38">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AB38">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AC38">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AD38">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AE38">
-        <v>2.53</v>
+        <v>2.74</v>
       </c>
       <c r="AF38">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="AG38">
-        <v>4.65</v>
+        <v>6.33</v>
       </c>
       <c r="AH38">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AI38">
-        <v>8.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AJ38">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AK38">
-        <v>2.51</v>
+        <v>2.3</v>
       </c>
       <c r="AL38">
         <v>1.53</v>
       </c>
       <c r="AM38">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AN38">
-        <v>1.04</v>
+        <v>1.63</v>
       </c>
       <c r="AO38">
         <v>0</v>
@@ -7920,52 +7920,52 @@
         <v>1.42</v>
       </c>
       <c r="AQ38">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AR38">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="AS38">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="AT38">
-        <v>4.41</v>
+        <v>4.34</v>
       </c>
       <c r="AU38">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="AV38">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AW38">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AX38">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AY38">
         <v>1.13</v>
       </c>
       <c r="AZ38">
-        <v>3.85</v>
+        <v>1.52</v>
       </c>
       <c r="BA38">
-        <v>1.42</v>
+        <v>3.42</v>
       </c>
       <c r="BB38">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="BC38">
         <v>2.7</v>
       </c>
       <c r="BD38">
-        <v>2.91</v>
+        <v>2.66</v>
       </c>
       <c r="BE38">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="BF38">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="BG38">
         <v>0</v>

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -310,12 +310,12 @@
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
     <t>Egypt Egyptian Premier League</t>
   </si>
   <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
     <t>South Africa Premier Soccer League</t>
   </si>
   <si>
@@ -337,10 +337,13 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Jeonbuk Motors</t>
+  </si>
+  <si>
     <t>Bucheon 1995</t>
   </si>
   <si>
-    <t>Jeonbuk Motors</t>
+    <t>Daejeon Citizen</t>
   </si>
   <si>
     <t>Sangju Sangmu</t>
@@ -349,28 +352,28 @@
     <t>Gangwon</t>
   </si>
   <si>
-    <t>Daejeon Citizen</t>
-  </si>
-  <si>
     <t>Madura United</t>
   </si>
   <si>
+    <t>FC Seoul</t>
+  </si>
+  <si>
     <t>Ethiopia Nigd Bank</t>
   </si>
   <si>
-    <t>FC Seoul</t>
-  </si>
-  <si>
     <t>Qingdao Youth Island</t>
   </si>
   <si>
     <t>Tanjong Pagar</t>
   </si>
   <si>
+    <t>Shenyang Urban</t>
+  </si>
+  <si>
     <t>Shandong Luneng</t>
   </si>
   <si>
-    <t>Shenyang Urban</t>
+    <t>Karvan FK</t>
   </si>
   <si>
     <t>Chongqing Tongliang Long</t>
@@ -382,9 +385,6 @@
     <t>Borneo</t>
   </si>
   <si>
-    <t>Karvan FK</t>
-  </si>
-  <si>
     <t>Mekelle Kenema</t>
   </si>
   <si>
@@ -415,13 +415,22 @@
     <t>Maccabi Tel Aviv</t>
   </si>
   <si>
+    <t>Dibba Al Fujairah</t>
+  </si>
+  <si>
     <t>Bani Yas</t>
   </si>
   <si>
     <t>Al Ittihad Kalba</t>
   </si>
   <si>
-    <t>Dibba Al Fujairah</t>
+    <t>Falkenberg</t>
+  </si>
+  <si>
+    <t>Lokomotiv Sofia 1929</t>
+  </si>
+  <si>
+    <t>Smouha SC</t>
   </si>
   <si>
     <t>Al Ahly</t>
@@ -430,27 +439,18 @@
     <t>Ceramica Cleopatra</t>
   </si>
   <si>
-    <t>Lokomotiv Sofia 1929</t>
-  </si>
-  <si>
-    <t>Falkenberg</t>
-  </si>
-  <si>
-    <t>Smouha SC</t>
+    <t>Magesi</t>
   </si>
   <si>
     <t>Chippa United</t>
   </si>
   <si>
+    <t>Siwelele</t>
+  </si>
+  <si>
     <t>Stellenbosch</t>
   </si>
   <si>
-    <t>Magesi</t>
-  </si>
-  <si>
-    <t>Siwelele</t>
-  </si>
-  <si>
     <t>Al Khaleej</t>
   </si>
   <si>
@@ -460,10 +460,13 @@
     <t>New York City II</t>
   </si>
   <si>
+    <t>Gwangju</t>
+  </si>
+  <si>
     <t>Jeju United</t>
   </si>
   <si>
-    <t>Gwangju</t>
+    <t>Incheon United</t>
   </si>
   <si>
     <t>Ulsan</t>
@@ -472,28 +475,28 @@
     <t>Pohang Steelers</t>
   </si>
   <si>
-    <t>Incheon United</t>
-  </si>
-  <si>
     <t>Bali United</t>
   </si>
   <si>
+    <t>Anyang</t>
+  </si>
+  <si>
     <t>Kedus Giorgis</t>
   </si>
   <si>
-    <t>Anyang</t>
-  </si>
-  <si>
     <t>Tianjin Teda</t>
   </si>
   <si>
     <t>Hougang United</t>
   </si>
   <si>
+    <t>Chengdu Better City FC</t>
+  </si>
+  <si>
     <t>Shanghai Shenhua</t>
   </si>
   <si>
-    <t>Chengdu Better City FC</t>
+    <t>Neftçi</t>
   </si>
   <si>
     <t>Henan Jianye</t>
@@ -505,9 +508,6 @@
     <t>Persita</t>
   </si>
   <si>
-    <t>Neftçi</t>
-  </si>
-  <si>
     <t>Arba Minch Kenema</t>
   </si>
   <si>
@@ -538,10 +538,19 @@
     <t>Hapoel Petah Tikva</t>
   </si>
   <si>
+    <t>Al Bataeh</t>
+  </si>
+  <si>
     <t>Al Dhafra</t>
   </si>
   <si>
-    <t>Al Bataeh</t>
+    <t>Norrköping</t>
+  </si>
+  <si>
+    <t>Botev Vratsa</t>
+  </si>
+  <si>
+    <t>Zamalek</t>
   </si>
   <si>
     <t>ENPPI</t>
@@ -550,25 +559,16 @@
     <t>Pyramids FC</t>
   </si>
   <si>
-    <t>Botev Vratsa</t>
-  </si>
-  <si>
-    <t>Norrköping</t>
-  </si>
-  <si>
-    <t>Zamalek</t>
+    <t>Orbit College</t>
   </si>
   <si>
     <t>Sekhukhune United</t>
   </si>
   <si>
+    <t>Durban City</t>
+  </si>
+  <si>
     <t>Orlando Pirates</t>
-  </si>
-  <si>
-    <t>Orbit College</t>
-  </si>
-  <si>
-    <t>Durban City</t>
   </si>
   <si>
     <t>Al Hilal</t>
@@ -1179,133 +1179,133 @@
         <v>188</v>
       </c>
       <c r="P2">
-        <v>2.4</v>
+        <v>1.35</v>
       </c>
       <c r="Q2">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="R2">
-        <v>2.8</v>
+        <v>7.1</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>8.15</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AE2">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AF2">
+        <v>1.8</v>
+      </c>
+      <c r="AG2">
+        <v>3.24</v>
+      </c>
+      <c r="AH2">
+        <v>1.26</v>
+      </c>
+      <c r="AI2">
+        <v>6.5</v>
+      </c>
+      <c r="AJ2">
+        <v>1.06</v>
+      </c>
+      <c r="AK2">
+        <v>2.15</v>
+      </c>
+      <c r="AL2">
         <v>1.57</v>
       </c>
-      <c r="AG2">
-        <v>0</v>
-      </c>
-      <c r="AH2">
-        <v>0</v>
-      </c>
-      <c r="AI2">
-        <v>0</v>
-      </c>
-      <c r="AJ2">
-        <v>0</v>
-      </c>
-      <c r="AK2">
-        <v>0</v>
-      </c>
-      <c r="AL2">
-        <v>0</v>
-      </c>
       <c r="AM2">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AO2">
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="AU2">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AV2">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AW2">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AX2">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AY2">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AZ2">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BA2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BB2">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC2">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD2">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="BE2">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF2">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG2">
         <v>0</v>
@@ -1364,133 +1364,133 @@
         <v>188</v>
       </c>
       <c r="P3">
-        <v>1.35</v>
+        <v>2.4</v>
       </c>
       <c r="Q3">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="R3">
-        <v>7.1</v>
+        <v>2.8</v>
       </c>
       <c r="S3">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>8.15</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Y3">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z3">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC3">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD3">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AE3">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AF3">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG3">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AH3">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK3">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AL3">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN3">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AO3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AQ3">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AR3">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AS3">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AT3">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="AU3">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AV3">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AW3">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AX3">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AY3">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AZ3">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BA3">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BB3">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC3">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BD3">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="BE3">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF3">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG3">
         <v>0</v>
@@ -1549,37 +1549,37 @@
         <v>188</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S4">
-        <v>3.24</v>
+        <v>2.91</v>
       </c>
       <c r="T4">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="U4">
-        <v>3.24</v>
+        <v>4.06</v>
       </c>
       <c r="V4">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W4">
-        <v>2.94</v>
+        <v>2.59</v>
       </c>
       <c r="X4">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="Y4">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="Z4">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="AA4">
         <v>1.03</v>
@@ -1588,94 +1588,94 @@
         <v>1.02</v>
       </c>
       <c r="AC4">
+        <v>1.31</v>
+      </c>
+      <c r="AD4">
+        <v>2.94</v>
+      </c>
+      <c r="AE4">
+        <v>2.12</v>
+      </c>
+      <c r="AF4">
+        <v>1.7</v>
+      </c>
+      <c r="AG4">
+        <v>3.65</v>
+      </c>
+      <c r="AH4">
         <v>1.27</v>
       </c>
-      <c r="AD4">
-        <v>3.18</v>
-      </c>
-      <c r="AE4">
-        <v>1.99</v>
-      </c>
-      <c r="AF4">
-        <v>1.8</v>
-      </c>
-      <c r="AG4">
-        <v>3.48</v>
-      </c>
-      <c r="AH4">
+      <c r="AI4">
+        <v>7.1</v>
+      </c>
+      <c r="AJ4">
+        <v>1.04</v>
+      </c>
+      <c r="AK4">
+        <v>1.78</v>
+      </c>
+      <c r="AL4">
+        <v>1.88</v>
+      </c>
+      <c r="AM4">
+        <v>1.32</v>
+      </c>
+      <c r="AN4">
+        <v>1.6</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>1.56</v>
+      </c>
+      <c r="AQ4">
+        <v>1.96</v>
+      </c>
+      <c r="AR4">
+        <v>3.25</v>
+      </c>
+      <c r="AS4">
+        <v>3.6</v>
+      </c>
+      <c r="AT4">
+        <v>5.47</v>
+      </c>
+      <c r="AU4">
+        <v>2.26</v>
+      </c>
+      <c r="AV4">
+        <v>1.75</v>
+      </c>
+      <c r="AW4">
+        <v>1.42</v>
+      </c>
+      <c r="AX4">
+        <v>1.2</v>
+      </c>
+      <c r="AY4">
+        <v>1.07</v>
+      </c>
+      <c r="AZ4">
+        <v>1.72</v>
+      </c>
+      <c r="BA4">
+        <v>2.3</v>
+      </c>
+      <c r="BB4">
         <v>1.24</v>
       </c>
-      <c r="AI4">
-        <v>6.73</v>
-      </c>
-      <c r="AJ4">
-        <v>1.11</v>
-      </c>
-      <c r="AK4">
-        <v>1.73</v>
-      </c>
-      <c r="AL4">
-        <v>2</v>
-      </c>
-      <c r="AM4">
-        <v>1.27</v>
-      </c>
-      <c r="AN4">
-        <v>1.46</v>
-      </c>
-      <c r="AO4">
-        <v>0</v>
-      </c>
-      <c r="AP4">
-        <v>1.37</v>
-      </c>
-      <c r="AQ4">
-        <v>1.64</v>
-      </c>
-      <c r="AR4">
-        <v>2.02</v>
-      </c>
-      <c r="AS4">
-        <v>2.8</v>
-      </c>
-      <c r="AT4">
-        <v>3.98</v>
-      </c>
-      <c r="AU4">
-        <v>2.74</v>
-      </c>
-      <c r="AV4">
-        <v>2.1</v>
-      </c>
-      <c r="AW4">
-        <v>1.64</v>
-      </c>
-      <c r="AX4">
-        <v>1.35</v>
-      </c>
-      <c r="AY4">
-        <v>1.16</v>
-      </c>
-      <c r="AZ4">
-        <v>1.81</v>
-      </c>
-      <c r="BA4">
-        <v>2.17</v>
-      </c>
-      <c r="BB4">
-        <v>1.22</v>
-      </c>
       <c r="BC4">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="BD4">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="BE4">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="BF4">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BG4">
         <v>0</v>
@@ -1734,133 +1734,133 @@
         <v>188</v>
       </c>
       <c r="P5">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R5">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>2.77</v>
+        <v>3.24</v>
       </c>
       <c r="T5">
+        <v>2.05</v>
+      </c>
+      <c r="U5">
+        <v>3.24</v>
+      </c>
+      <c r="V5">
+        <v>1.39</v>
+      </c>
+      <c r="W5">
+        <v>2.94</v>
+      </c>
+      <c r="X5">
+        <v>3</v>
+      </c>
+      <c r="Y5">
+        <v>1.39</v>
+      </c>
+      <c r="Z5">
+        <v>7.5</v>
+      </c>
+      <c r="AA5">
+        <v>1.03</v>
+      </c>
+      <c r="AB5">
+        <v>1.02</v>
+      </c>
+      <c r="AC5">
+        <v>1.27</v>
+      </c>
+      <c r="AD5">
+        <v>3.18</v>
+      </c>
+      <c r="AE5">
+        <v>1.99</v>
+      </c>
+      <c r="AF5">
+        <v>1.8</v>
+      </c>
+      <c r="AG5">
+        <v>3.48</v>
+      </c>
+      <c r="AH5">
+        <v>1.24</v>
+      </c>
+      <c r="AI5">
+        <v>6.73</v>
+      </c>
+      <c r="AJ5">
+        <v>1.11</v>
+      </c>
+      <c r="AK5">
+        <v>1.73</v>
+      </c>
+      <c r="AL5">
         <v>2</v>
       </c>
-      <c r="U5">
-        <v>3.79</v>
-      </c>
-      <c r="V5">
-        <v>1.52</v>
-      </c>
-      <c r="W5">
-        <v>2.43</v>
-      </c>
-      <c r="X5">
-        <v>3.4</v>
-      </c>
-      <c r="Y5">
+      <c r="AM5">
         <v>1.27</v>
       </c>
-      <c r="Z5">
-        <v>8.5</v>
-      </c>
-      <c r="AA5">
-        <v>1.01</v>
-      </c>
-      <c r="AB5">
-        <v>1.06</v>
-      </c>
-      <c r="AC5">
-        <v>1.47</v>
-      </c>
-      <c r="AD5">
-        <v>2.7</v>
-      </c>
-      <c r="AE5">
-        <v>2.38</v>
-      </c>
-      <c r="AF5">
-        <v>1.53</v>
-      </c>
-      <c r="AG5">
-        <v>4.5</v>
-      </c>
-      <c r="AH5">
-        <v>1.15</v>
-      </c>
-      <c r="AI5">
-        <v>9</v>
-      </c>
-      <c r="AJ5">
-        <v>1.01</v>
-      </c>
-      <c r="AK5">
-        <v>2.05</v>
-      </c>
-      <c r="AL5">
-        <v>1.69</v>
-      </c>
-      <c r="AM5">
-        <v>1.33</v>
-      </c>
       <c r="AN5">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="AO5">
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AQ5">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="AR5">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="AS5">
-        <v>3.48</v>
+        <v>2.8</v>
       </c>
       <c r="AT5">
-        <v>5.24</v>
+        <v>3.98</v>
       </c>
       <c r="AU5">
-        <v>2.48</v>
+        <v>2.74</v>
       </c>
       <c r="AV5">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="AW5">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="AX5">
+        <v>1.35</v>
+      </c>
+      <c r="AY5">
+        <v>1.16</v>
+      </c>
+      <c r="AZ5">
+        <v>1.81</v>
+      </c>
+      <c r="BA5">
+        <v>2.17</v>
+      </c>
+      <c r="BB5">
         <v>1.22</v>
       </c>
-      <c r="AY5">
-        <v>1.08</v>
-      </c>
-      <c r="AZ5">
-        <v>1.65</v>
-      </c>
-      <c r="BA5">
-        <v>3.02</v>
-      </c>
-      <c r="BB5">
-        <v>1.33</v>
-      </c>
       <c r="BC5">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="BD5">
-        <v>3.04</v>
+        <v>3.66</v>
       </c>
       <c r="BE5">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="BF5">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="BG5">
         <v>0</v>
@@ -1919,133 +1919,133 @@
         <v>188</v>
       </c>
       <c r="P6">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="Q6">
         <v>3.1</v>
       </c>
       <c r="R6">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="S6">
-        <v>2.91</v>
+        <v>2.77</v>
       </c>
       <c r="T6">
         <v>2</v>
       </c>
       <c r="U6">
-        <v>4.06</v>
+        <v>3.79</v>
       </c>
       <c r="V6">
+        <v>1.52</v>
+      </c>
+      <c r="W6">
+        <v>2.43</v>
+      </c>
+      <c r="X6">
+        <v>3.4</v>
+      </c>
+      <c r="Y6">
+        <v>1.27</v>
+      </c>
+      <c r="Z6">
+        <v>8.5</v>
+      </c>
+      <c r="AA6">
+        <v>1.01</v>
+      </c>
+      <c r="AB6">
+        <v>1.06</v>
+      </c>
+      <c r="AC6">
+        <v>1.47</v>
+      </c>
+      <c r="AD6">
+        <v>2.7</v>
+      </c>
+      <c r="AE6">
+        <v>2.38</v>
+      </c>
+      <c r="AF6">
+        <v>1.53</v>
+      </c>
+      <c r="AG6">
+        <v>4.5</v>
+      </c>
+      <c r="AH6">
+        <v>1.15</v>
+      </c>
+      <c r="AI6">
+        <v>9</v>
+      </c>
+      <c r="AJ6">
+        <v>1.01</v>
+      </c>
+      <c r="AK6">
+        <v>2.05</v>
+      </c>
+      <c r="AL6">
+        <v>1.69</v>
+      </c>
+      <c r="AM6">
+        <v>1.33</v>
+      </c>
+      <c r="AN6">
+        <v>1.7</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>1.5</v>
+      </c>
+      <c r="AQ6">
+        <v>1.92</v>
+      </c>
+      <c r="AR6">
+        <v>2.35</v>
+      </c>
+      <c r="AS6">
+        <v>3.48</v>
+      </c>
+      <c r="AT6">
+        <v>5.24</v>
+      </c>
+      <c r="AU6">
+        <v>2.48</v>
+      </c>
+      <c r="AV6">
+        <v>1.79</v>
+      </c>
+      <c r="AW6">
         <v>1.44</v>
       </c>
-      <c r="W6">
-        <v>2.59</v>
-      </c>
-      <c r="X6">
+      <c r="AX6">
+        <v>1.22</v>
+      </c>
+      <c r="AY6">
+        <v>1.08</v>
+      </c>
+      <c r="AZ6">
+        <v>1.65</v>
+      </c>
+      <c r="BA6">
+        <v>3.02</v>
+      </c>
+      <c r="BB6">
+        <v>1.33</v>
+      </c>
+      <c r="BC6">
+        <v>2.5</v>
+      </c>
+      <c r="BD6">
         <v>3.04</v>
       </c>
-      <c r="Y6">
-        <v>1.36</v>
-      </c>
-      <c r="Z6">
-        <v>7.6</v>
-      </c>
-      <c r="AA6">
-        <v>1.03</v>
-      </c>
-      <c r="AB6">
-        <v>1.02</v>
-      </c>
-      <c r="AC6">
-        <v>1.31</v>
-      </c>
-      <c r="AD6">
-        <v>2.94</v>
-      </c>
-      <c r="AE6">
-        <v>2.12</v>
-      </c>
-      <c r="AF6">
-        <v>1.7</v>
-      </c>
-      <c r="AG6">
-        <v>3.65</v>
-      </c>
-      <c r="AH6">
-        <v>1.27</v>
-      </c>
-      <c r="AI6">
-        <v>7.1</v>
-      </c>
-      <c r="AJ6">
-        <v>1.04</v>
-      </c>
-      <c r="AK6">
-        <v>1.78</v>
-      </c>
-      <c r="AL6">
-        <v>1.88</v>
-      </c>
-      <c r="AM6">
-        <v>1.32</v>
-      </c>
-      <c r="AN6">
-        <v>1.6</v>
-      </c>
-      <c r="AO6">
-        <v>0</v>
-      </c>
-      <c r="AP6">
-        <v>1.56</v>
-      </c>
-      <c r="AQ6">
-        <v>1.96</v>
-      </c>
-      <c r="AR6">
-        <v>3.25</v>
-      </c>
-      <c r="AS6">
-        <v>3.6</v>
-      </c>
-      <c r="AT6">
-        <v>5.47</v>
-      </c>
-      <c r="AU6">
-        <v>2.26</v>
-      </c>
-      <c r="AV6">
-        <v>1.75</v>
-      </c>
-      <c r="AW6">
-        <v>1.42</v>
-      </c>
-      <c r="AX6">
-        <v>1.2</v>
-      </c>
-      <c r="AY6">
-        <v>1.07</v>
-      </c>
-      <c r="AZ6">
-        <v>1.72</v>
-      </c>
-      <c r="BA6">
-        <v>2.3</v>
-      </c>
-      <c r="BB6">
-        <v>1.24</v>
-      </c>
-      <c r="BC6">
-        <v>2.3</v>
-      </c>
-      <c r="BD6">
-        <v>3.5</v>
-      </c>
       <c r="BE6">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="BF6">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="BG6">
         <v>0</v>
@@ -2131,7 +2131,7 @@
         <v>2.4</v>
       </c>
       <c r="Y7">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="Z7">
         <v>5.55</v>
@@ -2152,7 +2152,7 @@
         <v>1.71</v>
       </c>
       <c r="AF7">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AG7">
         <v>2.62</v>
@@ -2170,7 +2170,7 @@
         <v>1.62</v>
       </c>
       <c r="AL7">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AM7">
         <v>1.18</v>
@@ -2250,10 +2250,10 @@
         <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E8" t="s">
         <v>113</v>
@@ -2289,133 +2289,133 @@
         <v>188</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AO8">
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG8">
         <v>0</v>
@@ -2435,10 +2435,10 @@
         <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E9" t="s">
         <v>114</v>
@@ -2474,133 +2474,133 @@
         <v>188</v>
       </c>
       <c r="P9">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z9">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC9">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD9">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AH9">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI9">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AJ9">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK9">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AL9">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AM9">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN9">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AO9">
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ9">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AR9">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AS9">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT9">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AU9">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AV9">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AW9">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AX9">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY9">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ9">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BA9">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="BB9">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC9">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="BD9">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE9">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="BF9">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG9">
         <v>0</v>
@@ -2713,13 +2713,13 @@
         <v>3.28</v>
       </c>
       <c r="AH10">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AI10">
         <v>6.68</v>
       </c>
       <c r="AJ10">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AK10">
         <v>1.78</v>
@@ -2731,7 +2731,7 @@
         <v>1.32</v>
       </c>
       <c r="AN10">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AO10">
         <v>0</v>
@@ -2740,10 +2740,10 @@
         <v>1.18</v>
       </c>
       <c r="AQ10">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AR10">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AS10">
         <v>2.17</v>
@@ -2755,10 +2755,10 @@
         <v>3.84</v>
       </c>
       <c r="AV10">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="AW10">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="AX10">
         <v>1.6</v>
@@ -3029,133 +3029,133 @@
         <v>188</v>
       </c>
       <c r="P12">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T12">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="U12">
-        <v>2.8</v>
+        <v>2.18</v>
       </c>
       <c r="V12">
+        <v>1.33</v>
+      </c>
+      <c r="W12">
+        <v>2.99</v>
+      </c>
+      <c r="X12">
+        <v>2.5</v>
+      </c>
+      <c r="Y12">
+        <v>1.43</v>
+      </c>
+      <c r="Z12">
+        <v>6.15</v>
+      </c>
+      <c r="AA12">
+        <v>1.06</v>
+      </c>
+      <c r="AB12">
+        <v>1.05</v>
+      </c>
+      <c r="AC12">
         <v>1.22</v>
       </c>
-      <c r="W12">
-        <v>3.6</v>
-      </c>
-      <c r="X12">
-        <v>2.08</v>
-      </c>
-      <c r="Y12">
-        <v>1.69</v>
-      </c>
-      <c r="Z12">
-        <v>4.45</v>
-      </c>
-      <c r="AA12">
-        <v>1.15</v>
-      </c>
-      <c r="AB12">
-        <v>1.02</v>
-      </c>
-      <c r="AC12">
+      <c r="AD12">
+        <v>3.5</v>
+      </c>
+      <c r="AE12">
+        <v>1.8</v>
+      </c>
+      <c r="AF12">
+        <v>1.98</v>
+      </c>
+      <c r="AG12">
+        <v>2.95</v>
+      </c>
+      <c r="AH12">
+        <v>1.32</v>
+      </c>
+      <c r="AI12">
+        <v>5.7</v>
+      </c>
+      <c r="AJ12">
         <v>1.13</v>
       </c>
-      <c r="AD12">
-        <v>5.65</v>
-      </c>
-      <c r="AE12">
-        <v>1.45</v>
-      </c>
-      <c r="AF12">
-        <v>2.69</v>
-      </c>
-      <c r="AG12">
-        <v>2.05</v>
-      </c>
-      <c r="AH12">
-        <v>1.76</v>
-      </c>
-      <c r="AI12">
-        <v>3.33</v>
-      </c>
-      <c r="AJ12">
-        <v>1.25</v>
-      </c>
       <c r="AK12">
-        <v>1.36</v>
+        <v>1.81</v>
       </c>
       <c r="AL12">
+        <v>1.9</v>
+      </c>
+      <c r="AM12">
+        <v>2.4</v>
+      </c>
+      <c r="AN12">
+        <v>1.16</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>1.19</v>
+      </c>
+      <c r="AQ12">
+        <v>1.38</v>
+      </c>
+      <c r="AR12">
+        <v>1.94</v>
+      </c>
+      <c r="AS12">
+        <v>2.16</v>
+      </c>
+      <c r="AT12">
         <v>2.84</v>
       </c>
-      <c r="AM12">
-        <v>1.28</v>
-      </c>
-      <c r="AN12">
-        <v>1.44</v>
-      </c>
-      <c r="AO12">
-        <v>0</v>
-      </c>
-      <c r="AP12">
-        <v>1.11</v>
-      </c>
-      <c r="AQ12">
-        <v>1.26</v>
-      </c>
-      <c r="AR12">
-        <v>1.65</v>
-      </c>
-      <c r="AS12">
-        <v>1.85</v>
-      </c>
-      <c r="AT12">
-        <v>2.32</v>
-      </c>
       <c r="AU12">
-        <v>4.84</v>
+        <v>3.72</v>
       </c>
       <c r="AV12">
-        <v>3.19</v>
+        <v>2.59</v>
       </c>
       <c r="AW12">
-        <v>2.44</v>
+        <v>1.98</v>
       </c>
       <c r="AX12">
-        <v>1.91</v>
+        <v>1.61</v>
       </c>
       <c r="AY12">
-        <v>1.52</v>
+        <v>1.34</v>
       </c>
       <c r="AZ12">
-        <v>1.93</v>
+        <v>5.03</v>
       </c>
       <c r="BA12">
-        <v>2.09</v>
+        <v>1.35</v>
       </c>
       <c r="BB12">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="BC12">
-        <v>1.6</v>
+        <v>2.03</v>
       </c>
       <c r="BD12">
-        <v>5.8</v>
+        <v>3.95</v>
       </c>
       <c r="BE12">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="BF12">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="BG12">
         <v>0</v>
@@ -3214,133 +3214,133 @@
         <v>188</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T13">
-        <v>2.24</v>
+        <v>2.59</v>
       </c>
       <c r="U13">
-        <v>2.19</v>
+        <v>2.8</v>
       </c>
       <c r="V13">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="W13">
-        <v>2.95</v>
+        <v>3.6</v>
       </c>
       <c r="X13">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Y13">
+        <v>1.71</v>
+      </c>
+      <c r="Z13">
+        <v>4.45</v>
+      </c>
+      <c r="AA13">
+        <v>1.15</v>
+      </c>
+      <c r="AB13">
+        <v>1.02</v>
+      </c>
+      <c r="AC13">
+        <v>1.13</v>
+      </c>
+      <c r="AD13">
+        <v>5.65</v>
+      </c>
+      <c r="AE13">
+        <v>1.44</v>
+      </c>
+      <c r="AF13">
+        <v>2.65</v>
+      </c>
+      <c r="AG13">
+        <v>2.05</v>
+      </c>
+      <c r="AH13">
+        <v>1.76</v>
+      </c>
+      <c r="AI13">
+        <v>3.33</v>
+      </c>
+      <c r="AJ13">
+        <v>1.25</v>
+      </c>
+      <c r="AK13">
+        <v>1.36</v>
+      </c>
+      <c r="AL13">
+        <v>2.84</v>
+      </c>
+      <c r="AM13">
+        <v>1.2</v>
+      </c>
+      <c r="AN13">
         <v>1.42</v>
       </c>
-      <c r="Z13">
-        <v>6.2</v>
-      </c>
-      <c r="AA13">
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>1.09</v>
+      </c>
+      <c r="AQ13">
+        <v>1.23</v>
+      </c>
+      <c r="AR13">
+        <v>1.58</v>
+      </c>
+      <c r="AS13">
+        <v>1.78</v>
+      </c>
+      <c r="AT13">
+        <v>2.27</v>
+      </c>
+      <c r="AU13">
+        <v>5.3</v>
+      </c>
+      <c r="AV13">
+        <v>3.39</v>
+      </c>
+      <c r="AW13">
+        <v>2.46</v>
+      </c>
+      <c r="AX13">
+        <v>1.92</v>
+      </c>
+      <c r="AY13">
+        <v>1.58</v>
+      </c>
+      <c r="AZ13">
+        <v>1.94</v>
+      </c>
+      <c r="BA13">
+        <v>2.08</v>
+      </c>
+      <c r="BB13">
         <v>1.1</v>
       </c>
-      <c r="AB13">
-        <v>1.05</v>
-      </c>
-      <c r="AC13">
-        <v>1.22</v>
-      </c>
-      <c r="AD13">
-        <v>3.5</v>
-      </c>
-      <c r="AE13">
-        <v>1.82</v>
-      </c>
-      <c r="AF13">
-        <v>1.94</v>
-      </c>
-      <c r="AG13">
-        <v>3</v>
-      </c>
-      <c r="AH13">
-        <v>1.31</v>
-      </c>
-      <c r="AI13">
-        <v>5.5</v>
-      </c>
-      <c r="AJ13">
-        <v>1.08</v>
-      </c>
-      <c r="AK13">
-        <v>1.81</v>
-      </c>
-      <c r="AL13">
-        <v>1.9</v>
-      </c>
-      <c r="AM13">
-        <v>1.24</v>
-      </c>
-      <c r="AN13">
-        <v>1.16</v>
-      </c>
-      <c r="AO13">
-        <v>0</v>
-      </c>
-      <c r="AP13">
-        <v>1.19</v>
-      </c>
-      <c r="AQ13">
-        <v>1.38</v>
-      </c>
-      <c r="AR13">
-        <v>1.69</v>
-      </c>
-      <c r="AS13">
-        <v>2.16</v>
-      </c>
-      <c r="AT13">
-        <v>2.84</v>
-      </c>
-      <c r="AU13">
-        <v>3.72</v>
-      </c>
-      <c r="AV13">
-        <v>2.59</v>
-      </c>
-      <c r="AW13">
-        <v>2.02</v>
-      </c>
-      <c r="AX13">
+      <c r="BC13">
         <v>1.61</v>
       </c>
-      <c r="AY13">
-        <v>1.34</v>
-      </c>
-      <c r="AZ13">
-        <v>5.03</v>
-      </c>
-      <c r="BA13">
-        <v>1.29</v>
-      </c>
-      <c r="BB13">
-        <v>1.22</v>
-      </c>
-      <c r="BC13">
-        <v>2.05</v>
-      </c>
       <c r="BD13">
-        <v>3.9</v>
+        <v>5.8</v>
       </c>
       <c r="BE13">
-        <v>1.71</v>
+        <v>2.15</v>
       </c>
       <c r="BF13">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="BG13">
         <v>0</v>
@@ -3360,10 +3360,10 @@
         <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E14" t="s">
         <v>119</v>
@@ -3408,124 +3408,124 @@
         <v>0</v>
       </c>
       <c r="S14">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>1.35</v>
+        <v>1.12</v>
       </c>
       <c r="AD14">
-        <v>3.13</v>
+        <v>4.8</v>
       </c>
       <c r="AE14">
+        <v>1.45</v>
+      </c>
+      <c r="AF14">
+        <v>2.43</v>
+      </c>
+      <c r="AG14">
         <v>2.14</v>
       </c>
-      <c r="AF14">
-        <v>1.69</v>
-      </c>
-      <c r="AG14">
-        <v>3.73</v>
-      </c>
       <c r="AH14">
-        <v>1.21</v>
+        <v>1.58</v>
       </c>
       <c r="AI14">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="AJ14">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="AK14">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL14">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AM14">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AN14">
-        <v>1.46</v>
+        <v>1.05</v>
       </c>
       <c r="AO14">
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AQ14">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AR14">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AS14">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AT14">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AU14">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="AV14">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AW14">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AX14">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AY14">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AZ14">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BA14">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="BB14">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC14">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD14">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="BE14">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF14">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG14">
         <v>0</v>
@@ -3545,10 +3545,10 @@
         <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E15" t="s">
         <v>120</v>
@@ -3593,124 +3593,124 @@
         <v>0</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI15">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM15">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN15">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AO15">
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AU15">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="AV15">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AW15">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AX15">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AY15">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AZ15">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BA15">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="BB15">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC15">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD15">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="BE15">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF15">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG15">
         <v>0</v>
@@ -3730,7 +3730,7 @@
         <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D16" t="s">
         <v>105</v>
@@ -3769,133 +3769,133 @@
         <v>188</v>
       </c>
       <c r="P16">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q16">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R16">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="V16">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W16">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="X16">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z16">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC16">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AD16">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AE16">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AH16">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AI16">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AJ16">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK16">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL16">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AM16">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AN16">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AO16">
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ16">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR16">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AS16">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AT16">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AU16">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AV16">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AW16">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AX16">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AY16">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AZ16">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="BA16">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="BB16">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC16">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="BD16">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="BE16">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="BF16">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG16">
         <v>0</v>
@@ -3915,7 +3915,7 @@
         <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D17" t="s">
         <v>105</v>
@@ -3954,133 +3954,133 @@
         <v>188</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC17">
+        <v>1.19</v>
+      </c>
+      <c r="AD17">
+        <v>4.35</v>
+      </c>
+      <c r="AE17">
+        <v>1.65</v>
+      </c>
+      <c r="AF17">
+        <v>2.19</v>
+      </c>
+      <c r="AG17">
+        <v>2.46</v>
+      </c>
+      <c r="AH17">
+        <v>1.43</v>
+      </c>
+      <c r="AI17">
+        <v>4.5</v>
+      </c>
+      <c r="AJ17">
+        <v>1.13</v>
+      </c>
+      <c r="AK17">
+        <v>1.67</v>
+      </c>
+      <c r="AL17">
+        <v>1.96</v>
+      </c>
+      <c r="AM17">
+        <v>1.06</v>
+      </c>
+      <c r="AN17">
+        <v>2.49</v>
+      </c>
+      <c r="AO17">
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <v>1.18</v>
+      </c>
+      <c r="AQ17">
+        <v>1.42</v>
+      </c>
+      <c r="AR17">
+        <v>1.95</v>
+      </c>
+      <c r="AS17">
+        <v>2.18</v>
+      </c>
+      <c r="AT17">
+        <v>2.86</v>
+      </c>
+      <c r="AU17">
+        <v>3.68</v>
+      </c>
+      <c r="AV17">
+        <v>2.57</v>
+      </c>
+      <c r="AW17">
+        <v>1.97</v>
+      </c>
+      <c r="AX17">
+        <v>1.6</v>
+      </c>
+      <c r="AY17">
+        <v>1.35</v>
+      </c>
+      <c r="AZ17">
+        <v>1.43</v>
+      </c>
+      <c r="BA17">
+        <v>3.9</v>
+      </c>
+      <c r="BB17">
         <v>1.12</v>
       </c>
-      <c r="AD17">
-        <v>4.8</v>
-      </c>
-      <c r="AE17">
-        <v>1.45</v>
-      </c>
-      <c r="AF17">
-        <v>2.43</v>
-      </c>
-      <c r="AG17">
-        <v>2.14</v>
-      </c>
-      <c r="AH17">
-        <v>1.58</v>
-      </c>
-      <c r="AI17">
-        <v>3.5</v>
-      </c>
-      <c r="AJ17">
-        <v>1.23</v>
-      </c>
-      <c r="AK17">
-        <v>0</v>
-      </c>
-      <c r="AL17">
-        <v>0</v>
-      </c>
-      <c r="AM17">
-        <v>1.11</v>
-      </c>
-      <c r="AN17">
-        <v>1.05</v>
-      </c>
-      <c r="AO17">
-        <v>0</v>
-      </c>
-      <c r="AP17">
-        <v>0</v>
-      </c>
-      <c r="AQ17">
-        <v>0</v>
-      </c>
-      <c r="AR17">
-        <v>0</v>
-      </c>
-      <c r="AS17">
-        <v>0</v>
-      </c>
-      <c r="AT17">
-        <v>0</v>
-      </c>
-      <c r="AU17">
-        <v>0</v>
-      </c>
-      <c r="AV17">
-        <v>0</v>
-      </c>
-      <c r="AW17">
-        <v>0</v>
-      </c>
-      <c r="AX17">
-        <v>0</v>
-      </c>
-      <c r="AY17">
-        <v>0</v>
-      </c>
-      <c r="AZ17">
-        <v>0</v>
-      </c>
-      <c r="BA17">
-        <v>0</v>
-      </c>
-      <c r="BB17">
-        <v>0</v>
-      </c>
       <c r="BC17">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BD17">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="BE17">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BF17">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG17">
         <v>0</v>
@@ -4324,7 +4324,7 @@
         <v>188</v>
       </c>
       <c r="P19">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="Q19">
         <v>3.29</v>
@@ -4694,19 +4694,19 @@
         <v>188</v>
       </c>
       <c r="P21">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q21">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="R21">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="S21">
         <v>2.71</v>
       </c>
       <c r="T21">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="U21">
         <v>3.8</v>
@@ -4736,19 +4736,19 @@
         <v>1.37</v>
       </c>
       <c r="AD21">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AE21">
         <v>2.31</v>
       </c>
       <c r="AF21">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AG21">
         <v>3.9</v>
       </c>
       <c r="AH21">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AI21">
         <v>8.4</v>
@@ -4760,7 +4760,7 @@
         <v>1.95</v>
       </c>
       <c r="AL21">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AM21">
         <v>1.33</v>
@@ -4805,7 +4805,7 @@
         <v>1.87</v>
       </c>
       <c r="BA21">
-        <v>2.53</v>
+        <v>2.17</v>
       </c>
       <c r="BB21">
         <v>1.3</v>
@@ -5064,13 +5064,13 @@
         <v>188</v>
       </c>
       <c r="P23">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="Q23">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R23">
-        <v>4.33</v>
+        <v>4.24</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -5503,7 +5503,7 @@
         <v>1.76</v>
       </c>
       <c r="AM25">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AN25">
         <v>2.23</v>
@@ -6144,7 +6144,7 @@
         <v>134</v>
       </c>
       <c r="F29" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -6329,7 +6329,7 @@
         <v>135</v>
       </c>
       <c r="F30" t="s">
-        <v>175</v>
+        <v>145</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -6508,7 +6508,7 @@
         <v>98</v>
       </c>
       <c r="D31" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E31" t="s">
         <v>136</v>
@@ -6544,133 +6544,133 @@
         <v>188</v>
       </c>
       <c r="P31">
-        <v>1.4</v>
+        <v>2.49</v>
       </c>
       <c r="Q31">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="R31">
-        <v>6.5</v>
+        <v>2.32</v>
       </c>
       <c r="S31">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="T31">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U31">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="V31">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W31">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="X31">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y31">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z31">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AA31">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB31">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC31">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AD31">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AE31">
-        <v>2.02</v>
+        <v>1.66</v>
       </c>
       <c r="AF31">
-        <v>1.71</v>
+        <v>2.15</v>
       </c>
       <c r="AG31">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AH31">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI31">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="AJ31">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK31">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AL31">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AM31">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AN31">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AO31">
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ31">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AR31">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AS31">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AT31">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AU31">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AV31">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AW31">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AX31">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AY31">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ31">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BA31">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="BB31">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC31">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD31">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BE31">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF31">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG31">
         <v>0</v>
@@ -6690,7 +6690,7 @@
         <v>80</v>
       </c>
       <c r="C32" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D32" t="s">
         <v>105</v>
@@ -6729,133 +6729,133 @@
         <v>188</v>
       </c>
       <c r="P32">
-        <v>4</v>
+        <v>1.99</v>
       </c>
       <c r="Q32">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R32">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="S32">
-        <v>5.29</v>
+        <v>2.5</v>
       </c>
       <c r="T32">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="U32">
-        <v>2.46</v>
+        <v>4.4</v>
       </c>
       <c r="V32">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="W32">
-        <v>2.41</v>
+        <v>2.73</v>
       </c>
       <c r="X32">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="Y32">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z32">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="AA32">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AB32">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC32">
+        <v>1.32</v>
+      </c>
+      <c r="AD32">
+        <v>3.08</v>
+      </c>
+      <c r="AE32">
+        <v>2.02</v>
+      </c>
+      <c r="AF32">
+        <v>1.78</v>
+      </c>
+      <c r="AG32">
+        <v>3.6</v>
+      </c>
+      <c r="AH32">
+        <v>1.28</v>
+      </c>
+      <c r="AI32">
+        <v>6.5</v>
+      </c>
+      <c r="AJ32">
+        <v>1.05</v>
+      </c>
+      <c r="AK32">
+        <v>1.79</v>
+      </c>
+      <c r="AL32">
+        <v>1.92</v>
+      </c>
+      <c r="AM32">
+        <v>1.28</v>
+      </c>
+      <c r="AN32">
+        <v>1.75</v>
+      </c>
+      <c r="AO32">
+        <v>0</v>
+      </c>
+      <c r="AP32">
         <v>1.4</v>
       </c>
-      <c r="AD32">
-        <v>2.97</v>
-      </c>
-      <c r="AE32">
-        <v>2.16</v>
-      </c>
-      <c r="AF32">
+      <c r="AQ32">
+        <v>1.69</v>
+      </c>
+      <c r="AR32">
+        <v>2.19</v>
+      </c>
+      <c r="AS32">
+        <v>2.93</v>
+      </c>
+      <c r="AT32">
+        <v>4.2</v>
+      </c>
+      <c r="AU32">
+        <v>2.63</v>
+      </c>
+      <c r="AV32">
+        <v>1.98</v>
+      </c>
+      <c r="AW32">
+        <v>1.59</v>
+      </c>
+      <c r="AX32">
+        <v>1.32</v>
+      </c>
+      <c r="AY32">
+        <v>1.14</v>
+      </c>
+      <c r="AZ32">
+        <v>1.56</v>
+      </c>
+      <c r="BA32">
+        <v>3.34</v>
+      </c>
+      <c r="BB32">
+        <v>1.23</v>
+      </c>
+      <c r="BC32">
+        <v>2.2</v>
+      </c>
+      <c r="BD32">
+        <v>3.52</v>
+      </c>
+      <c r="BE32">
         <v>1.62</v>
       </c>
-      <c r="AG32">
-        <v>4.1</v>
-      </c>
-      <c r="AH32">
-        <v>1.19</v>
-      </c>
-      <c r="AI32">
-        <v>7.3</v>
-      </c>
-      <c r="AJ32">
-        <v>1.03</v>
-      </c>
-      <c r="AK32">
-        <v>1.93</v>
-      </c>
-      <c r="AL32">
-        <v>1.73</v>
-      </c>
-      <c r="AM32">
-        <v>1.26</v>
-      </c>
-      <c r="AN32">
-        <v>1.14</v>
-      </c>
-      <c r="AO32">
-        <v>0</v>
-      </c>
-      <c r="AP32">
-        <v>1.28</v>
-      </c>
-      <c r="AQ32">
-        <v>1.53</v>
-      </c>
-      <c r="AR32">
-        <v>1.95</v>
-      </c>
-      <c r="AS32">
-        <v>2.52</v>
-      </c>
-      <c r="AT32">
-        <v>3.48</v>
-      </c>
-      <c r="AU32">
-        <v>3.05</v>
-      </c>
-      <c r="AV32">
-        <v>2.21</v>
-      </c>
-      <c r="AW32">
-        <v>1.73</v>
-      </c>
-      <c r="AX32">
-        <v>1.41</v>
-      </c>
-      <c r="AY32">
-        <v>1.22</v>
-      </c>
-      <c r="AZ32">
-        <v>2.46</v>
-      </c>
-      <c r="BA32">
-        <v>1.82</v>
-      </c>
-      <c r="BB32">
-        <v>1.27</v>
-      </c>
-      <c r="BC32">
-        <v>2.55</v>
-      </c>
-      <c r="BD32">
-        <v>3.25</v>
-      </c>
-      <c r="BE32">
-        <v>1.44</v>
-      </c>
       <c r="BF32">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="BG32">
         <v>0</v>
@@ -6875,7 +6875,7 @@
         <v>80</v>
       </c>
       <c r="C33" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D33" t="s">
         <v>105</v>
@@ -6914,133 +6914,133 @@
         <v>188</v>
       </c>
       <c r="P33">
-        <v>1.95</v>
+        <v>5.48</v>
       </c>
       <c r="Q33">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="R33">
-        <v>3.65</v>
+        <v>1.7</v>
       </c>
       <c r="S33">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="T33">
-        <v>2.06</v>
+        <v>1.87</v>
       </c>
       <c r="U33">
-        <v>4.4</v>
+        <v>2.42</v>
       </c>
       <c r="V33">
-        <v>1.39</v>
+        <v>1.56</v>
       </c>
       <c r="W33">
-        <v>2.73</v>
+        <v>2.26</v>
       </c>
       <c r="X33">
-        <v>2.96</v>
+        <v>3.5</v>
       </c>
       <c r="Y33">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="Z33">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA33">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AB33">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AC33">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="AD33">
-        <v>3.08</v>
+        <v>2.38</v>
       </c>
       <c r="AE33">
-        <v>2.02</v>
+        <v>2.66</v>
       </c>
       <c r="AF33">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="AG33">
-        <v>3.6</v>
+        <v>5.25</v>
       </c>
       <c r="AH33">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AI33">
-        <v>6.75</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AJ33">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AK33">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="AL33">
-        <v>1.92</v>
+        <v>1.55</v>
       </c>
       <c r="AM33">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AN33">
-        <v>1.75</v>
+        <v>1.1</v>
       </c>
       <c r="AO33">
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ33">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AR33">
-        <v>2.63</v>
+        <v>2.14</v>
       </c>
       <c r="AS33">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="AT33">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="AU33">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AV33">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AW33">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AX33">
         <v>1.32</v>
       </c>
       <c r="AY33">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AZ33">
-        <v>1.68</v>
+        <v>2.39</v>
       </c>
       <c r="BA33">
-        <v>3.34</v>
+        <v>1.89</v>
       </c>
       <c r="BB33">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="BC33">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="BD33">
-        <v>3.52</v>
+        <v>3</v>
       </c>
       <c r="BE33">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="BF33">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="BG33">
         <v>0</v>
@@ -7063,7 +7063,7 @@
         <v>99</v>
       </c>
       <c r="D34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E34" t="s">
         <v>139</v>
@@ -7099,133 +7099,133 @@
         <v>188</v>
       </c>
       <c r="P34">
+        <v>1.4</v>
+      </c>
+      <c r="Q34">
+        <v>4</v>
+      </c>
+      <c r="R34">
+        <v>6.5</v>
+      </c>
+      <c r="S34">
+        <v>1.88</v>
+      </c>
+      <c r="T34">
+        <v>2.25</v>
+      </c>
+      <c r="U34">
+        <v>8.1</v>
+      </c>
+      <c r="V34">
+        <v>1.45</v>
+      </c>
+      <c r="W34">
+        <v>2.56</v>
+      </c>
+      <c r="X34">
+        <v>3</v>
+      </c>
+      <c r="Y34">
+        <v>1.33</v>
+      </c>
+      <c r="Z34">
+        <v>7.1</v>
+      </c>
+      <c r="AA34">
+        <v>1.04</v>
+      </c>
+      <c r="AB34">
+        <v>1.06</v>
+      </c>
+      <c r="AC34">
+        <v>1.31</v>
+      </c>
+      <c r="AD34">
+        <v>2.92</v>
+      </c>
+      <c r="AE34">
+        <v>2.02</v>
+      </c>
+      <c r="AF34">
+        <v>1.71</v>
+      </c>
+      <c r="AG34">
+        <v>3.42</v>
+      </c>
+      <c r="AH34">
+        <v>1.27</v>
+      </c>
+      <c r="AI34">
+        <v>6.45</v>
+      </c>
+      <c r="AJ34">
+        <v>1.05</v>
+      </c>
+      <c r="AK34">
+        <v>2.25</v>
+      </c>
+      <c r="AL34">
+        <v>1.6</v>
+      </c>
+      <c r="AM34">
+        <v>1.16</v>
+      </c>
+      <c r="AN34">
         <v>2.5</v>
       </c>
-      <c r="Q34">
-        <v>3.55</v>
-      </c>
-      <c r="R34">
-        <v>2.32</v>
-      </c>
-      <c r="S34">
-        <v>0</v>
-      </c>
-      <c r="T34">
-        <v>0</v>
-      </c>
-      <c r="U34">
-        <v>0</v>
-      </c>
-      <c r="V34">
-        <v>0</v>
-      </c>
-      <c r="W34">
-        <v>0</v>
-      </c>
-      <c r="X34">
-        <v>0</v>
-      </c>
-      <c r="Y34">
-        <v>0</v>
-      </c>
-      <c r="Z34">
-        <v>0</v>
-      </c>
-      <c r="AA34">
-        <v>0</v>
-      </c>
-      <c r="AB34">
-        <v>0</v>
-      </c>
-      <c r="AC34">
-        <v>0</v>
-      </c>
-      <c r="AD34">
-        <v>0</v>
-      </c>
-      <c r="AE34">
-        <v>1.66</v>
-      </c>
-      <c r="AF34">
-        <v>2.15</v>
-      </c>
-      <c r="AG34">
-        <v>0</v>
-      </c>
-      <c r="AH34">
-        <v>0</v>
-      </c>
-      <c r="AI34">
-        <v>0</v>
-      </c>
-      <c r="AJ34">
-        <v>0</v>
-      </c>
-      <c r="AK34">
-        <v>0</v>
-      </c>
-      <c r="AL34">
-        <v>0</v>
-      </c>
-      <c r="AM34">
-        <v>0</v>
-      </c>
-      <c r="AN34">
-        <v>0</v>
-      </c>
       <c r="AO34">
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ34">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR34">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AS34">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT34">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AU34">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AV34">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW34">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AX34">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY34">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ34">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BA34">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="BB34">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC34">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD34">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE34">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF34">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG34">
         <v>0</v>
@@ -7245,7 +7245,7 @@
         <v>80</v>
       </c>
       <c r="C35" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D35" t="s">
         <v>105</v>
@@ -7284,133 +7284,133 @@
         <v>188</v>
       </c>
       <c r="P35">
-        <v>5.48</v>
+        <v>4</v>
       </c>
       <c r="Q35">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="R35">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="S35">
-        <v>6</v>
+        <v>5.29</v>
       </c>
       <c r="T35">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="U35">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="V35">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="W35">
-        <v>2.26</v>
+        <v>2.41</v>
       </c>
       <c r="X35">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="Y35">
+        <v>1.3</v>
+      </c>
+      <c r="Z35">
+        <v>7.7</v>
+      </c>
+      <c r="AA35">
+        <v>1.02</v>
+      </c>
+      <c r="AB35">
+        <v>1.04</v>
+      </c>
+      <c r="AC35">
+        <v>1.4</v>
+      </c>
+      <c r="AD35">
+        <v>2.97</v>
+      </c>
+      <c r="AE35">
+        <v>2.16</v>
+      </c>
+      <c r="AF35">
+        <v>1.62</v>
+      </c>
+      <c r="AG35">
+        <v>4.1</v>
+      </c>
+      <c r="AH35">
+        <v>1.19</v>
+      </c>
+      <c r="AI35">
+        <v>7.3</v>
+      </c>
+      <c r="AJ35">
+        <v>1.03</v>
+      </c>
+      <c r="AK35">
+        <v>1.93</v>
+      </c>
+      <c r="AL35">
+        <v>1.73</v>
+      </c>
+      <c r="AM35">
+        <v>1.26</v>
+      </c>
+      <c r="AN35">
+        <v>1.14</v>
+      </c>
+      <c r="AO35">
+        <v>0</v>
+      </c>
+      <c r="AP35">
+        <v>1.28</v>
+      </c>
+      <c r="AQ35">
+        <v>1.53</v>
+      </c>
+      <c r="AR35">
+        <v>1.95</v>
+      </c>
+      <c r="AS35">
+        <v>2.52</v>
+      </c>
+      <c r="AT35">
+        <v>3.48</v>
+      </c>
+      <c r="AU35">
+        <v>3.05</v>
+      </c>
+      <c r="AV35">
+        <v>2.21</v>
+      </c>
+      <c r="AW35">
+        <v>1.73</v>
+      </c>
+      <c r="AX35">
+        <v>1.41</v>
+      </c>
+      <c r="AY35">
         <v>1.22</v>
       </c>
-      <c r="Z35">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AA35">
-        <v>1.03</v>
-      </c>
-      <c r="AB35">
-        <v>1.11</v>
-      </c>
-      <c r="AC35">
-        <v>1.53</v>
-      </c>
-      <c r="AD35">
-        <v>2.38</v>
-      </c>
-      <c r="AE35">
-        <v>2.66</v>
-      </c>
-      <c r="AF35">
-        <v>1.47</v>
-      </c>
-      <c r="AG35">
-        <v>5.25</v>
-      </c>
-      <c r="AH35">
-        <v>1.12</v>
-      </c>
-      <c r="AI35">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AJ35">
-        <v>1</v>
-      </c>
-      <c r="AK35">
-        <v>2.3</v>
-      </c>
-      <c r="AL35">
-        <v>1.55</v>
-      </c>
-      <c r="AM35">
+      <c r="AZ35">
+        <v>2.46</v>
+      </c>
+      <c r="BA35">
+        <v>1.82</v>
+      </c>
+      <c r="BB35">
         <v>1.27</v>
       </c>
-      <c r="AN35">
+      <c r="BC35">
+        <v>2.55</v>
+      </c>
+      <c r="BD35">
+        <v>3.25</v>
+      </c>
+      <c r="BE35">
+        <v>1.44</v>
+      </c>
+      <c r="BF35">
         <v>1.1</v>
-      </c>
-      <c r="AO35">
-        <v>0</v>
-      </c>
-      <c r="AP35">
-        <v>1.36</v>
-      </c>
-      <c r="AQ35">
-        <v>1.69</v>
-      </c>
-      <c r="AR35">
-        <v>2.14</v>
-      </c>
-      <c r="AS35">
-        <v>2.88</v>
-      </c>
-      <c r="AT35">
-        <v>3.7</v>
-      </c>
-      <c r="AU35">
-        <v>2.7</v>
-      </c>
-      <c r="AV35">
-        <v>2</v>
-      </c>
-      <c r="AW35">
-        <v>1.57</v>
-      </c>
-      <c r="AX35">
-        <v>1.32</v>
-      </c>
-      <c r="AY35">
-        <v>1.23</v>
-      </c>
-      <c r="AZ35">
-        <v>2.39</v>
-      </c>
-      <c r="BA35">
-        <v>1.89</v>
-      </c>
-      <c r="BB35">
-        <v>1.33</v>
-      </c>
-      <c r="BC35">
-        <v>2.48</v>
-      </c>
-      <c r="BD35">
-        <v>3</v>
-      </c>
-      <c r="BE35">
-        <v>1.45</v>
-      </c>
-      <c r="BF35">
-        <v>1.06</v>
       </c>
       <c r="BG35">
         <v>0</v>
@@ -7469,133 +7469,133 @@
         <v>188</v>
       </c>
       <c r="P36">
-        <v>3.45</v>
+        <v>2</v>
       </c>
       <c r="Q36">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="R36">
-        <v>2.15</v>
+        <v>3.8</v>
       </c>
       <c r="S36">
-        <v>3.95</v>
+        <v>2.88</v>
       </c>
       <c r="T36">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="U36">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="V36">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="W36">
-        <v>2.31</v>
+        <v>2.11</v>
       </c>
       <c r="X36">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="Y36">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z36">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AA36">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AB36">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AC36">
+        <v>1.58</v>
+      </c>
+      <c r="AD36">
+        <v>2.25</v>
+      </c>
+      <c r="AE36">
+        <v>2.74</v>
+      </c>
+      <c r="AF36">
+        <v>1.35</v>
+      </c>
+      <c r="AG36">
+        <v>6.33</v>
+      </c>
+      <c r="AH36">
+        <v>1.07</v>
+      </c>
+      <c r="AI36">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AJ36">
+        <v>1.01</v>
+      </c>
+      <c r="AK36">
+        <v>2.3</v>
+      </c>
+      <c r="AL36">
         <v>1.53</v>
       </c>
-      <c r="AD36">
-        <v>2.3</v>
-      </c>
-      <c r="AE36">
-        <v>2.65</v>
-      </c>
-      <c r="AF36">
-        <v>1.49</v>
-      </c>
-      <c r="AG36">
-        <v>4.6</v>
-      </c>
-      <c r="AH36">
+      <c r="AM36">
+        <v>1.35</v>
+      </c>
+      <c r="AN36">
+        <v>1.63</v>
+      </c>
+      <c r="AO36">
+        <v>0</v>
+      </c>
+      <c r="AP36">
+        <v>1.42</v>
+      </c>
+      <c r="AQ36">
+        <v>1.74</v>
+      </c>
+      <c r="AR36">
+        <v>2.7</v>
+      </c>
+      <c r="AS36">
+        <v>3</v>
+      </c>
+      <c r="AT36">
+        <v>4.34</v>
+      </c>
+      <c r="AU36">
+        <v>2.58</v>
+      </c>
+      <c r="AV36">
+        <v>1.95</v>
+      </c>
+      <c r="AW36">
+        <v>1.57</v>
+      </c>
+      <c r="AX36">
+        <v>1.3</v>
+      </c>
+      <c r="AY36">
         <v>1.13</v>
       </c>
-      <c r="AI36">
-        <v>9.5</v>
-      </c>
-      <c r="AJ36">
+      <c r="AZ36">
+        <v>1.52</v>
+      </c>
+      <c r="BA36">
+        <v>3.26</v>
+      </c>
+      <c r="BB36">
+        <v>1.39</v>
+      </c>
+      <c r="BC36">
+        <v>2.7</v>
+      </c>
+      <c r="BD36">
+        <v>2.66</v>
+      </c>
+      <c r="BE36">
+        <v>1.33</v>
+      </c>
+      <c r="BF36">
         <v>1.03</v>
-      </c>
-      <c r="AK36">
-        <v>2.05</v>
-      </c>
-      <c r="AL36">
-        <v>1.62</v>
-      </c>
-      <c r="AM36">
-        <v>1.3</v>
-      </c>
-      <c r="AN36">
-        <v>1.24</v>
-      </c>
-      <c r="AO36">
-        <v>0</v>
-      </c>
-      <c r="AP36">
-        <v>1.37</v>
-      </c>
-      <c r="AQ36">
-        <v>1.72</v>
-      </c>
-      <c r="AR36">
-        <v>2.02</v>
-      </c>
-      <c r="AS36">
-        <v>2.9</v>
-      </c>
-      <c r="AT36">
-        <v>3.4</v>
-      </c>
-      <c r="AU36">
-        <v>2.8</v>
-      </c>
-      <c r="AV36">
-        <v>2</v>
-      </c>
-      <c r="AW36">
-        <v>1.6</v>
-      </c>
-      <c r="AX36">
-        <v>1.43</v>
-      </c>
-      <c r="AY36">
-        <v>1.15</v>
-      </c>
-      <c r="AZ36">
-        <v>2.12</v>
-      </c>
-      <c r="BA36">
-        <v>2.08</v>
-      </c>
-      <c r="BB36">
-        <v>1.32</v>
-      </c>
-      <c r="BC36">
-        <v>2.59</v>
-      </c>
-      <c r="BD36">
-        <v>2.96</v>
-      </c>
-      <c r="BE36">
-        <v>1.41</v>
-      </c>
-      <c r="BF36">
-        <v>1.1</v>
       </c>
       <c r="BG36">
         <v>0</v>
@@ -7654,133 +7654,133 @@
         <v>188</v>
       </c>
       <c r="P37">
-        <v>5.6</v>
+        <v>3.3</v>
       </c>
       <c r="Q37">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="R37">
-        <v>1.5</v>
+        <v>2.15</v>
       </c>
       <c r="S37">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T37">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="U37">
-        <v>2.13</v>
+        <v>2.95</v>
       </c>
       <c r="V37">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W37">
         <v>2.31</v>
       </c>
       <c r="X37">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="Y37">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z37">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AA37">
         <v>1</v>
       </c>
       <c r="AB37">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AC37">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AD37">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AE37">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
       <c r="AF37">
         <v>1.49</v>
       </c>
       <c r="AG37">
-        <v>4.65</v>
+        <v>5.1</v>
       </c>
       <c r="AH37">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AI37">
-        <v>8.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="AJ37">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AK37">
-        <v>2.51</v>
+        <v>2.05</v>
       </c>
       <c r="AL37">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AM37">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AN37">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="AO37">
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ37">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AR37">
-        <v>2.73</v>
+        <v>2.19</v>
       </c>
       <c r="AS37">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AT37">
-        <v>4.41</v>
+        <v>4.15</v>
       </c>
       <c r="AU37">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AV37">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AW37">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AX37">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="AY37">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AZ37">
-        <v>3.85</v>
+        <v>2.12</v>
       </c>
       <c r="BA37">
-        <v>1.42</v>
+        <v>2.08</v>
       </c>
       <c r="BB37">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="BC37">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="BD37">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="BE37">
         <v>1.41</v>
       </c>
       <c r="BF37">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="BG37">
         <v>0</v>
@@ -7839,37 +7839,37 @@
         <v>188</v>
       </c>
       <c r="P38">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="Q38">
+        <v>2.8</v>
+      </c>
+      <c r="R38">
+        <v>3.3</v>
+      </c>
+      <c r="S38">
         <v>2.9</v>
       </c>
-      <c r="R38">
-        <v>3.95</v>
-      </c>
-      <c r="S38">
-        <v>2.88</v>
-      </c>
       <c r="T38">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="U38">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="V38">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="W38">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="X38">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="Y38">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z38">
-        <v>13</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA38">
         <v>1.02</v>
@@ -7878,40 +7878,40 @@
         <v>1.12</v>
       </c>
       <c r="AC38">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AD38">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="AE38">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="AF38">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AG38">
-        <v>6.33</v>
+        <v>6.35</v>
       </c>
       <c r="AH38">
         <v>1.1</v>
       </c>
       <c r="AI38">
-        <v>9.699999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AJ38">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AK38">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AL38">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AM38">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AN38">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AO38">
         <v>0</v>
@@ -7923,22 +7923,22 @@
         <v>1.76</v>
       </c>
       <c r="AR38">
-        <v>2.7</v>
+        <v>2.24</v>
       </c>
       <c r="AS38">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="AT38">
-        <v>4.34</v>
+        <v>4.36</v>
       </c>
       <c r="AU38">
-        <v>2.58</v>
+        <v>2.3</v>
       </c>
       <c r="AV38">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AW38">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AX38">
         <v>1.3</v>
@@ -7947,25 +7947,25 @@
         <v>1.13</v>
       </c>
       <c r="AZ38">
-        <v>1.52</v>
+        <v>1.93</v>
       </c>
       <c r="BA38">
-        <v>3.42</v>
+        <v>2.31</v>
       </c>
       <c r="BB38">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="BC38">
-        <v>2.7</v>
+        <v>3.12</v>
       </c>
       <c r="BD38">
-        <v>2.66</v>
+        <v>2.53</v>
       </c>
       <c r="BE38">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="BF38">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BG38">
         <v>0</v>
@@ -8024,67 +8024,67 @@
         <v>188</v>
       </c>
       <c r="P39">
-        <v>2.11</v>
+        <v>5.6</v>
       </c>
       <c r="Q39">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="R39">
+        <v>1.52</v>
+      </c>
+      <c r="S39">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="T39">
+        <v>2.05</v>
+      </c>
+      <c r="U39">
+        <v>2.1</v>
+      </c>
+      <c r="V39">
+        <v>1.53</v>
+      </c>
+      <c r="W39">
+        <v>2.44</v>
+      </c>
+      <c r="X39">
         <v>3.3</v>
       </c>
-      <c r="S39">
-        <v>2.9</v>
-      </c>
-      <c r="T39">
-        <v>1.81</v>
-      </c>
-      <c r="U39">
-        <v>4.2</v>
-      </c>
-      <c r="V39">
-        <v>1.61</v>
-      </c>
-      <c r="W39">
-        <v>2.17</v>
-      </c>
-      <c r="X39">
-        <v>4.1</v>
-      </c>
       <c r="Y39">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="Z39">
-        <v>13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA39">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AB39">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AC39">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="AD39">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="AE39">
-        <v>3.1</v>
+        <v>2.53</v>
       </c>
       <c r="AF39">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="AG39">
-        <v>6.5</v>
+        <v>4.65</v>
       </c>
       <c r="AH39">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="AI39">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AJ39">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AK39">
         <v>2.4</v>
@@ -8093,64 +8093,64 @@
         <v>1.5</v>
       </c>
       <c r="AM39">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AN39">
-        <v>1.55</v>
+        <v>1.1</v>
       </c>
       <c r="AO39">
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ39">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AR39">
-        <v>2.71</v>
+        <v>2.52</v>
       </c>
       <c r="AS39">
-        <v>3.02</v>
+        <v>2.65</v>
       </c>
       <c r="AT39">
-        <v>4.36</v>
+        <v>4.41</v>
       </c>
       <c r="AU39">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="AV39">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="AW39">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AX39">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AY39">
         <v>1.13</v>
       </c>
       <c r="AZ39">
-        <v>1.93</v>
+        <v>3.85</v>
       </c>
       <c r="BA39">
-        <v>2.31</v>
+        <v>1.43</v>
       </c>
       <c r="BB39">
+        <v>1.33</v>
+      </c>
+      <c r="BC39">
+        <v>2.59</v>
+      </c>
+      <c r="BD39">
+        <v>2.91</v>
+      </c>
+      <c r="BE39">
         <v>1.41</v>
       </c>
-      <c r="BC39">
-        <v>3.12</v>
-      </c>
-      <c r="BD39">
-        <v>2.65</v>
-      </c>
-      <c r="BE39">
-        <v>1.29</v>
-      </c>
       <c r="BF39">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="BG39">
         <v>0</v>

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -337,30 +337,30 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Bucheon 1995</t>
+  </si>
+  <si>
     <t>Jeonbuk Motors</t>
   </si>
   <si>
-    <t>Bucheon 1995</t>
+    <t>Gangwon</t>
+  </si>
+  <si>
+    <t>Sangju Sangmu</t>
   </si>
   <si>
     <t>Daejeon Citizen</t>
   </si>
   <si>
-    <t>Sangju Sangmu</t>
-  </si>
-  <si>
-    <t>Gangwon</t>
-  </si>
-  <si>
     <t>Madura United</t>
   </si>
   <si>
+    <t>Ethiopia Nigd Bank</t>
+  </si>
+  <si>
     <t>FC Seoul</t>
   </si>
   <si>
-    <t>Ethiopia Nigd Bank</t>
-  </si>
-  <si>
     <t>Qingdao Youth Island</t>
   </si>
   <si>
@@ -373,18 +373,18 @@
     <t>Shandong Luneng</t>
   </si>
   <si>
+    <t>Dire Dawa Kenema</t>
+  </si>
+  <si>
+    <t>Chongqing Tongliang Long</t>
+  </si>
+  <si>
+    <t>Borneo</t>
+  </si>
+  <si>
     <t>Karvan FK</t>
   </si>
   <si>
-    <t>Chongqing Tongliang Long</t>
-  </si>
-  <si>
-    <t>Dire Dawa Kenema</t>
-  </si>
-  <si>
-    <t>Borneo</t>
-  </si>
-  <si>
     <t>Mekelle Kenema</t>
   </si>
   <si>
@@ -427,30 +427,30 @@
     <t>Falkenberg</t>
   </si>
   <si>
+    <t>Ceramica Cleopatra</t>
+  </si>
+  <si>
     <t>Lokomotiv Sofia 1929</t>
   </si>
   <si>
+    <t>Al Ahly</t>
+  </si>
+  <si>
     <t>Smouha SC</t>
   </si>
   <si>
-    <t>Al Ahly</t>
-  </si>
-  <si>
-    <t>Ceramica Cleopatra</t>
+    <t>Stellenbosch</t>
+  </si>
+  <si>
+    <t>Chippa United</t>
   </si>
   <si>
     <t>Magesi</t>
   </si>
   <si>
-    <t>Chippa United</t>
-  </si>
-  <si>
     <t>Siwelele</t>
   </si>
   <si>
-    <t>Stellenbosch</t>
-  </si>
-  <si>
     <t>Al Khaleej</t>
   </si>
   <si>
@@ -460,30 +460,30 @@
     <t>New York City II</t>
   </si>
   <si>
+    <t>Jeju United</t>
+  </si>
+  <si>
     <t>Gwangju</t>
   </si>
   <si>
-    <t>Jeju United</t>
+    <t>Pohang Steelers</t>
+  </si>
+  <si>
+    <t>Ulsan</t>
   </si>
   <si>
     <t>Incheon United</t>
   </si>
   <si>
-    <t>Ulsan</t>
-  </si>
-  <si>
-    <t>Pohang Steelers</t>
-  </si>
-  <si>
     <t>Bali United</t>
   </si>
   <si>
+    <t>Kedus Giorgis</t>
+  </si>
+  <si>
     <t>Anyang</t>
   </si>
   <si>
-    <t>Kedus Giorgis</t>
-  </si>
-  <si>
     <t>Tianjin Teda</t>
   </si>
   <si>
@@ -496,18 +496,18 @@
     <t>Shanghai Shenhua</t>
   </si>
   <si>
+    <t>Ethiopia Bunna</t>
+  </si>
+  <si>
+    <t>Henan Jianye</t>
+  </si>
+  <si>
+    <t>Persita</t>
+  </si>
+  <si>
     <t>Neftçi</t>
   </si>
   <si>
-    <t>Henan Jianye</t>
-  </si>
-  <si>
-    <t>Ethiopia Bunna</t>
-  </si>
-  <si>
-    <t>Persita</t>
-  </si>
-  <si>
     <t>Arba Minch Kenema</t>
   </si>
   <si>
@@ -547,28 +547,28 @@
     <t>Norrköping</t>
   </si>
   <si>
+    <t>Pyramids FC</t>
+  </si>
+  <si>
     <t>Botev Vratsa</t>
   </si>
   <si>
+    <t>ENPPI</t>
+  </si>
+  <si>
     <t>Zamalek</t>
   </si>
   <si>
-    <t>ENPPI</t>
-  </si>
-  <si>
-    <t>Pyramids FC</t>
+    <t>Orlando Pirates</t>
+  </si>
+  <si>
+    <t>Sekhukhune United</t>
   </si>
   <si>
     <t>Orbit College</t>
   </si>
   <si>
-    <t>Sekhukhune United</t>
-  </si>
-  <si>
     <t>Durban City</t>
-  </si>
-  <si>
-    <t>Orlando Pirates</t>
   </si>
   <si>
     <t>Al Hilal</t>
@@ -1179,133 +1179,133 @@
         <v>188</v>
       </c>
       <c r="P2">
-        <v>1.35</v>
+        <v>2.49</v>
       </c>
       <c r="Q2">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="R2">
-        <v>7.1</v>
+        <v>2.8</v>
       </c>
       <c r="S2">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>8.15</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W2">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="X2">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Y2">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z2">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC2">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AE2">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AF2">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG2">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AH2">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK2">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AL2">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN2">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AO2">
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AQ2">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AR2">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AS2">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AT2">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="AU2">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AV2">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AW2">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AX2">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AY2">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AZ2">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BA2">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BB2">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC2">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BD2">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="BE2">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF2">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG2">
         <v>0</v>
@@ -1364,133 +1364,133 @@
         <v>188</v>
       </c>
       <c r="P3">
-        <v>2.4</v>
+        <v>1.33</v>
       </c>
       <c r="Q3">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="R3">
-        <v>2.8</v>
+        <v>7.75</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>5.99</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AE3">
-        <v>2.35</v>
+        <v>1.96</v>
       </c>
       <c r="AF3">
+        <v>1.85</v>
+      </c>
+      <c r="AG3">
+        <v>3.18</v>
+      </c>
+      <c r="AH3">
+        <v>1.3</v>
+      </c>
+      <c r="AI3">
+        <v>6.5</v>
+      </c>
+      <c r="AJ3">
+        <v>1.11</v>
+      </c>
+      <c r="AK3">
+        <v>2.26</v>
+      </c>
+      <c r="AL3">
         <v>1.57</v>
       </c>
-      <c r="AG3">
-        <v>0</v>
-      </c>
-      <c r="AH3">
-        <v>0</v>
-      </c>
-      <c r="AI3">
-        <v>0</v>
-      </c>
-      <c r="AJ3">
-        <v>0</v>
-      </c>
-      <c r="AK3">
-        <v>0</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
       <c r="AM3">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AO3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="AU3">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV3">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AW3">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AX3">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AY3">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AZ3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BA3">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BB3">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC3">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="BD3">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BE3">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF3">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG3">
         <v>0</v>
@@ -1549,133 +1549,133 @@
         <v>188</v>
       </c>
       <c r="P4">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="Q4">
         <v>3.1</v>
       </c>
       <c r="R4">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="S4">
-        <v>2.91</v>
+        <v>2.77</v>
       </c>
       <c r="T4">
         <v>2</v>
       </c>
       <c r="U4">
-        <v>4.06</v>
+        <v>4.76</v>
       </c>
       <c r="V4">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W4">
-        <v>2.59</v>
+        <v>2.34</v>
       </c>
       <c r="X4">
+        <v>3.4</v>
+      </c>
+      <c r="Y4">
+        <v>1.27</v>
+      </c>
+      <c r="Z4">
+        <v>9.5</v>
+      </c>
+      <c r="AA4">
+        <v>1.01</v>
+      </c>
+      <c r="AB4">
+        <v>1.05</v>
+      </c>
+      <c r="AC4">
+        <v>1.42</v>
+      </c>
+      <c r="AD4">
+        <v>2.7</v>
+      </c>
+      <c r="AE4">
+        <v>2.38</v>
+      </c>
+      <c r="AF4">
+        <v>1.55</v>
+      </c>
+      <c r="AG4">
+        <v>4.5</v>
+      </c>
+      <c r="AH4">
+        <v>1.15</v>
+      </c>
+      <c r="AI4">
+        <v>9</v>
+      </c>
+      <c r="AJ4">
+        <v>1.01</v>
+      </c>
+      <c r="AK4">
+        <v>1.94</v>
+      </c>
+      <c r="AL4">
+        <v>1.68</v>
+      </c>
+      <c r="AM4">
+        <v>1.33</v>
+      </c>
+      <c r="AN4">
+        <v>1.71</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>1.53</v>
+      </c>
+      <c r="AQ4">
+        <v>1.92</v>
+      </c>
+      <c r="AR4">
+        <v>2.39</v>
+      </c>
+      <c r="AS4">
+        <v>3.48</v>
+      </c>
+      <c r="AT4">
+        <v>5.23</v>
+      </c>
+      <c r="AU4">
+        <v>2.31</v>
+      </c>
+      <c r="AV4">
+        <v>1.79</v>
+      </c>
+      <c r="AW4">
+        <v>1.45</v>
+      </c>
+      <c r="AX4">
+        <v>1.22</v>
+      </c>
+      <c r="AY4">
+        <v>1.08</v>
+      </c>
+      <c r="AZ4">
+        <v>1.65</v>
+      </c>
+      <c r="BA4">
+        <v>3.1</v>
+      </c>
+      <c r="BB4">
+        <v>1.33</v>
+      </c>
+      <c r="BC4">
+        <v>2.53</v>
+      </c>
+      <c r="BD4">
         <v>3.04</v>
       </c>
-      <c r="Y4">
-        <v>1.36</v>
-      </c>
-      <c r="Z4">
-        <v>7.6</v>
-      </c>
-      <c r="AA4">
-        <v>1.03</v>
-      </c>
-      <c r="AB4">
-        <v>1.02</v>
-      </c>
-      <c r="AC4">
-        <v>1.31</v>
-      </c>
-      <c r="AD4">
-        <v>2.94</v>
-      </c>
-      <c r="AE4">
-        <v>2.12</v>
-      </c>
-      <c r="AF4">
-        <v>1.7</v>
-      </c>
-      <c r="AG4">
-        <v>3.65</v>
-      </c>
-      <c r="AH4">
-        <v>1.27</v>
-      </c>
-      <c r="AI4">
-        <v>7.1</v>
-      </c>
-      <c r="AJ4">
-        <v>1.04</v>
-      </c>
-      <c r="AK4">
-        <v>1.78</v>
-      </c>
-      <c r="AL4">
-        <v>1.88</v>
-      </c>
-      <c r="AM4">
-        <v>1.32</v>
-      </c>
-      <c r="AN4">
-        <v>1.6</v>
-      </c>
-      <c r="AO4">
-        <v>0</v>
-      </c>
-      <c r="AP4">
-        <v>1.56</v>
-      </c>
-      <c r="AQ4">
-        <v>1.96</v>
-      </c>
-      <c r="AR4">
-        <v>3.25</v>
-      </c>
-      <c r="AS4">
-        <v>3.6</v>
-      </c>
-      <c r="AT4">
-        <v>5.47</v>
-      </c>
-      <c r="AU4">
-        <v>2.26</v>
-      </c>
-      <c r="AV4">
-        <v>1.75</v>
-      </c>
-      <c r="AW4">
-        <v>1.42</v>
-      </c>
-      <c r="AX4">
-        <v>1.2</v>
-      </c>
-      <c r="AY4">
-        <v>1.07</v>
-      </c>
-      <c r="AZ4">
-        <v>1.72</v>
-      </c>
-      <c r="BA4">
-        <v>2.3</v>
-      </c>
-      <c r="BB4">
-        <v>1.24</v>
-      </c>
-      <c r="BC4">
-        <v>2.3</v>
-      </c>
-      <c r="BD4">
-        <v>3.5</v>
-      </c>
       <c r="BE4">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="BF4">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="BG4">
         <v>0</v>
@@ -1755,13 +1755,13 @@
         <v>1.39</v>
       </c>
       <c r="W5">
-        <v>2.94</v>
+        <v>2.77</v>
       </c>
       <c r="X5">
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="Z5">
         <v>7.5</v>
@@ -1776,7 +1776,7 @@
         <v>1.27</v>
       </c>
       <c r="AD5">
-        <v>3.18</v>
+        <v>3.35</v>
       </c>
       <c r="AE5">
         <v>1.99</v>
@@ -1794,7 +1794,7 @@
         <v>6.73</v>
       </c>
       <c r="AJ5">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AK5">
         <v>1.73</v>
@@ -1803,49 +1803,49 @@
         <v>2</v>
       </c>
       <c r="AM5">
-        <v>1.27</v>
+        <v>1.46</v>
       </c>
       <c r="AN5">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AO5">
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AQ5">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AR5">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="AS5">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AT5">
-        <v>3.98</v>
+        <v>4.16</v>
       </c>
       <c r="AU5">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AV5">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AW5">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AX5">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AY5">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AZ5">
         <v>1.81</v>
       </c>
       <c r="BA5">
-        <v>2.17</v>
+        <v>2.6</v>
       </c>
       <c r="BB5">
         <v>1.22</v>
@@ -1857,7 +1857,7 @@
         <v>3.66</v>
       </c>
       <c r="BE5">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="BF5">
         <v>1.13</v>
@@ -1919,133 +1919,133 @@
         <v>188</v>
       </c>
       <c r="P6">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="Q6">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R6">
-        <v>3.8</v>
+        <v>3.19</v>
       </c>
       <c r="S6">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="T6">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="U6">
-        <v>3.79</v>
+        <v>4.06</v>
       </c>
       <c r="V6">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="W6">
-        <v>2.43</v>
+        <v>2.59</v>
       </c>
       <c r="X6">
-        <v>3.4</v>
+        <v>3.04</v>
       </c>
       <c r="Y6">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z6">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="AA6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AB6">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC6">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="AD6">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="AE6">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="AF6">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="AG6">
-        <v>4.5</v>
+        <v>3.54</v>
       </c>
       <c r="AH6">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AI6">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="AJ6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AK6">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AL6">
-        <v>1.69</v>
+        <v>1.88</v>
       </c>
       <c r="AM6">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AN6">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AO6">
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AQ6">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AR6">
-        <v>2.35</v>
+        <v>2.46</v>
       </c>
       <c r="AS6">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="AT6">
-        <v>5.24</v>
+        <v>5.11</v>
       </c>
       <c r="AU6">
-        <v>2.48</v>
+        <v>2.34</v>
       </c>
       <c r="AV6">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AW6">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AX6">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AY6">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AZ6">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="BA6">
-        <v>3.02</v>
+        <v>2.3</v>
       </c>
       <c r="BB6">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="BC6">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="BD6">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="BE6">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="BF6">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="BG6">
         <v>0</v>
@@ -2250,10 +2250,10 @@
         <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E8" t="s">
         <v>113</v>
@@ -2289,133 +2289,133 @@
         <v>188</v>
       </c>
       <c r="P8">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R8">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="X8">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Y8">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA8">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC8">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD8">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AE8">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AH8">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK8">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AL8">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN8">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AO8">
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ8">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AR8">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AS8">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT8">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AU8">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AV8">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AW8">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AX8">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY8">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ8">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BA8">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="BB8">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC8">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="BD8">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE8">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="BF8">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG8">
         <v>0</v>
@@ -2435,10 +2435,10 @@
         <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E9" t="s">
         <v>114</v>
@@ -2474,133 +2474,133 @@
         <v>188</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AO9">
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AU9">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AV9">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AX9">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AZ9">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BA9">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD9">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE9">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG9">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>2.66</v>
       </c>
       <c r="X10">
-        <v>3.01</v>
+        <v>2.88</v>
       </c>
       <c r="Y10">
         <v>1.36</v>
@@ -2704,22 +2704,22 @@
         <v>3.04</v>
       </c>
       <c r="AE10">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AF10">
         <v>1.79</v>
       </c>
       <c r="AG10">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AH10">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AI10">
         <v>6.68</v>
       </c>
       <c r="AJ10">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AK10">
         <v>1.78</v>
@@ -2731,46 +2731,46 @@
         <v>1.32</v>
       </c>
       <c r="AN10">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AO10">
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AQ10">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AR10">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AS10">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AT10">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AU10">
-        <v>3.84</v>
+        <v>3.64</v>
       </c>
       <c r="AV10">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="AW10">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AX10">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AY10">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AZ10">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="BA10">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="BB10">
         <v>1.24</v>
@@ -3044,7 +3044,7 @@
         <v>2.25</v>
       </c>
       <c r="U12">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="V12">
         <v>1.33</v>
@@ -3053,7 +3053,7 @@
         <v>2.99</v>
       </c>
       <c r="X12">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="Y12">
         <v>1.43</v>
@@ -3065,31 +3065,31 @@
         <v>1.06</v>
       </c>
       <c r="AB12">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AC12">
         <v>1.22</v>
       </c>
       <c r="AD12">
-        <v>3.5</v>
+        <v>3.77</v>
       </c>
       <c r="AE12">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AF12">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AG12">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AH12">
         <v>1.32</v>
       </c>
       <c r="AI12">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="AJ12">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AK12">
         <v>1.81</v>
@@ -3098,10 +3098,10 @@
         <v>1.9</v>
       </c>
       <c r="AM12">
-        <v>2.4</v>
+        <v>1.24</v>
       </c>
       <c r="AN12">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AO12">
         <v>0</v>
@@ -3140,7 +3140,7 @@
         <v>5.03</v>
       </c>
       <c r="BA12">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="BB12">
         <v>1.18</v>
@@ -3226,10 +3226,10 @@
         <v>3</v>
       </c>
       <c r="T13">
-        <v>2.59</v>
+        <v>2.28</v>
       </c>
       <c r="U13">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="V13">
         <v>1.22</v>
@@ -3259,19 +3259,19 @@
         <v>5.65</v>
       </c>
       <c r="AE13">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AF13">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="AG13">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AH13">
         <v>1.76</v>
       </c>
       <c r="AI13">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="AJ13">
         <v>1.25</v>
@@ -3280,13 +3280,13 @@
         <v>1.36</v>
       </c>
       <c r="AL13">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="AM13">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AN13">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AO13">
         <v>0</v>
@@ -3304,13 +3304,13 @@
         <v>1.78</v>
       </c>
       <c r="AT13">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="AU13">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AV13">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="AW13">
         <v>2.46</v>
@@ -3322,25 +3322,25 @@
         <v>1.58</v>
       </c>
       <c r="AZ13">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="BA13">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="BB13">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="BC13">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="BD13">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BE13">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="BF13">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BG13">
         <v>0</v>
@@ -3360,7 +3360,7 @@
         <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D14" t="s">
         <v>105</v>
@@ -3438,28 +3438,28 @@
         <v>0</v>
       </c>
       <c r="AC14">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AD14">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH14">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI14">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AJ14">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK14">
         <v>0</v>
@@ -3468,10 +3468,10 @@
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN14">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AO14">
         <v>0</v>
@@ -3593,28 +3593,28 @@
         <v>0</v>
       </c>
       <c r="S15">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="T15">
         <v>2</v>
       </c>
       <c r="U15">
-        <v>3.39</v>
+        <v>3.41</v>
       </c>
       <c r="V15">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W15">
-        <v>2.65</v>
+        <v>2.54</v>
       </c>
       <c r="X15">
-        <v>2.9</v>
+        <v>2.99</v>
       </c>
       <c r="Y15">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z15">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AA15">
         <v>1.02</v>
@@ -3623,10 +3623,10 @@
         <v>1.07</v>
       </c>
       <c r="AC15">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AD15">
-        <v>3.13</v>
+        <v>2.92</v>
       </c>
       <c r="AE15">
         <v>2.14</v>
@@ -3653,49 +3653,49 @@
         <v>1.9</v>
       </c>
       <c r="AM15">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AN15">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AO15">
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ15">
         <v>1.26</v>
       </c>
       <c r="AR15">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="AS15">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AT15">
         <v>2.31</v>
       </c>
       <c r="AU15">
-        <v>4.86</v>
+        <v>4.89</v>
       </c>
       <c r="AV15">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="AW15">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AX15">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AY15">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AZ15">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="BA15">
-        <v>2.57</v>
+        <v>2.1</v>
       </c>
       <c r="BB15">
         <v>1.24</v>
@@ -3710,7 +3710,7 @@
         <v>1.57</v>
       </c>
       <c r="BF15">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BG15">
         <v>0</v>
@@ -3730,7 +3730,7 @@
         <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D16" t="s">
         <v>105</v>
@@ -3769,133 +3769,133 @@
         <v>188</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL16">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AM16">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AO16">
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AU16">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AV16">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AW16">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX16">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY16">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AZ16">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BA16">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BB16">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC16">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BD16">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="BE16">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BF16">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG16">
         <v>0</v>
@@ -3915,7 +3915,7 @@
         <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D17" t="s">
         <v>105</v>
@@ -3954,133 +3954,133 @@
         <v>188</v>
       </c>
       <c r="P17">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R17">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="V17">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="W17">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="X17">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Y17">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z17">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="AA17">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC17">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AD17">
-        <v>4.35</v>
+        <v>4.8</v>
       </c>
       <c r="AE17">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AF17">
-        <v>2.19</v>
+        <v>2.43</v>
       </c>
       <c r="AG17">
-        <v>2.46</v>
+        <v>2.14</v>
       </c>
       <c r="AH17">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="AI17">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="AJ17">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AK17">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL17">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AM17">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AN17">
-        <v>2.49</v>
+        <v>1.05</v>
       </c>
       <c r="AO17">
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ17">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR17">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AS17">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT17">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AU17">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AV17">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AW17">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AX17">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AY17">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AZ17">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="BA17">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BB17">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC17">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="BD17">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="BE17">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="BF17">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG17">
         <v>0</v>
@@ -4324,13 +4324,13 @@
         <v>188</v>
       </c>
       <c r="P19">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q19">
-        <v>3.29</v>
+        <v>3.36</v>
       </c>
       <c r="R19">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -4697,13 +4697,13 @@
         <v>1.98</v>
       </c>
       <c r="Q21">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="R21">
         <v>3.84</v>
       </c>
       <c r="S21">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="T21">
         <v>2.05</v>
@@ -4721,7 +4721,7 @@
         <v>3.25</v>
       </c>
       <c r="Y21">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z21">
         <v>8.5</v>
@@ -4733,22 +4733,22 @@
         <v>1.04</v>
       </c>
       <c r="AC21">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AD21">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AE21">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="AF21">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AG21">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="AH21">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AI21">
         <v>8.4</v>
@@ -4760,7 +4760,7 @@
         <v>1.95</v>
       </c>
       <c r="AL21">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AM21">
         <v>1.33</v>
@@ -4772,10 +4772,10 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AQ21">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AR21">
         <v>2.64</v>
@@ -4784,13 +4784,13 @@
         <v>2.95</v>
       </c>
       <c r="AT21">
-        <v>4.24</v>
+        <v>3.35</v>
       </c>
       <c r="AU21">
         <v>2.62</v>
       </c>
       <c r="AV21">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AW21">
         <v>1.58</v>
@@ -4811,13 +4811,13 @@
         <v>1.3</v>
       </c>
       <c r="BC21">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="BD21">
         <v>3.16</v>
       </c>
       <c r="BE21">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="BF21">
         <v>1.08</v>
@@ -5064,13 +5064,13 @@
         <v>188</v>
       </c>
       <c r="P23">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q23">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="R23">
-        <v>4.24</v>
+        <v>3.95</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -5109,10 +5109,10 @@
         <v>0</v>
       </c>
       <c r="AE23">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AF23">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AG23">
         <v>0</v>
@@ -5804,7 +5804,7 @@
         <v>188</v>
       </c>
       <c r="P27">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Q27">
         <v>4.75</v>
@@ -5813,10 +5813,10 @@
         <v>6.25</v>
       </c>
       <c r="S27">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="T27">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="U27">
         <v>6.66</v>
@@ -5828,7 +5828,7 @@
         <v>3.52</v>
       </c>
       <c r="X27">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="Y27">
         <v>1.58</v>
@@ -5843,10 +5843,10 @@
         <v>1.02</v>
       </c>
       <c r="AC27">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AD27">
-        <v>4.85</v>
+        <v>4.9</v>
       </c>
       <c r="AE27">
         <v>1.48</v>
@@ -5861,61 +5861,61 @@
         <v>1.56</v>
       </c>
       <c r="AI27">
-        <v>3.96</v>
+        <v>3.45</v>
       </c>
       <c r="AJ27">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AK27">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AL27">
         <v>1.97</v>
       </c>
       <c r="AM27">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AN27">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="AO27">
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AQ27">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AR27">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="AS27">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AT27">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="AU27">
-        <v>2.93</v>
+        <v>2.97</v>
       </c>
       <c r="AV27">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AW27">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AX27">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AY27">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AZ27">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="BA27">
-        <v>7.4</v>
+        <v>7.01</v>
       </c>
       <c r="BB27">
         <v>1.11</v>
@@ -6544,13 +6544,13 @@
         <v>188</v>
       </c>
       <c r="P31">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="Q31">
         <v>3.55</v>
       </c>
       <c r="R31">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -6690,7 +6690,7 @@
         <v>80</v>
       </c>
       <c r="C32" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D32" t="s">
         <v>105</v>
@@ -6729,133 +6729,133 @@
         <v>188</v>
       </c>
       <c r="P32">
-        <v>1.99</v>
+        <v>4.33</v>
       </c>
       <c r="Q32">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R32">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="S32">
-        <v>2.5</v>
+        <v>5.29</v>
       </c>
       <c r="T32">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="U32">
-        <v>4.4</v>
+        <v>2.46</v>
       </c>
       <c r="V32">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="W32">
-        <v>2.73</v>
+        <v>2.41</v>
       </c>
       <c r="X32">
-        <v>2.96</v>
+        <v>3.08</v>
       </c>
       <c r="Y32">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z32">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="AA32">
+        <v>1.02</v>
+      </c>
+      <c r="AB32">
         <v>1.04</v>
       </c>
-      <c r="AB32">
-        <v>1.01</v>
-      </c>
       <c r="AC32">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AD32">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="AE32">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AF32">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AG32">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AH32">
+        <v>1.19</v>
+      </c>
+      <c r="AI32">
+        <v>7.3</v>
+      </c>
+      <c r="AJ32">
+        <v>1.03</v>
+      </c>
+      <c r="AK32">
+        <v>1.97</v>
+      </c>
+      <c r="AL32">
+        <v>1.73</v>
+      </c>
+      <c r="AM32">
+        <v>1.26</v>
+      </c>
+      <c r="AN32">
+        <v>1.14</v>
+      </c>
+      <c r="AO32">
+        <v>0</v>
+      </c>
+      <c r="AP32">
         <v>1.28</v>
       </c>
-      <c r="AI32">
-        <v>6.5</v>
-      </c>
-      <c r="AJ32">
-        <v>1.05</v>
-      </c>
-      <c r="AK32">
-        <v>1.79</v>
-      </c>
-      <c r="AL32">
-        <v>1.92</v>
-      </c>
-      <c r="AM32">
-        <v>1.28</v>
-      </c>
-      <c r="AN32">
-        <v>1.75</v>
-      </c>
-      <c r="AO32">
-        <v>0</v>
-      </c>
-      <c r="AP32">
+      <c r="AQ32">
+        <v>1.61</v>
+      </c>
+      <c r="AR32">
+        <v>1.95</v>
+      </c>
+      <c r="AS32">
+        <v>2.52</v>
+      </c>
+      <c r="AT32">
+        <v>3.55</v>
+      </c>
+      <c r="AU32">
+        <v>2.7</v>
+      </c>
+      <c r="AV32">
+        <v>2.21</v>
+      </c>
+      <c r="AW32">
+        <v>1.73</v>
+      </c>
+      <c r="AX32">
         <v>1.4</v>
       </c>
-      <c r="AQ32">
-        <v>1.69</v>
-      </c>
-      <c r="AR32">
-        <v>2.19</v>
-      </c>
-      <c r="AS32">
-        <v>2.93</v>
-      </c>
-      <c r="AT32">
-        <v>4.2</v>
-      </c>
-      <c r="AU32">
-        <v>2.63</v>
-      </c>
-      <c r="AV32">
-        <v>1.98</v>
-      </c>
-      <c r="AW32">
-        <v>1.59</v>
-      </c>
-      <c r="AX32">
-        <v>1.32</v>
-      </c>
       <c r="AY32">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AZ32">
-        <v>1.56</v>
+        <v>2.46</v>
       </c>
       <c r="BA32">
-        <v>3.34</v>
+        <v>1.82</v>
       </c>
       <c r="BB32">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="BC32">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="BD32">
-        <v>3.52</v>
+        <v>3.25</v>
       </c>
       <c r="BE32">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="BF32">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="BG32">
         <v>0</v>
@@ -6875,7 +6875,7 @@
         <v>80</v>
       </c>
       <c r="C33" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D33" t="s">
         <v>105</v>
@@ -6914,106 +6914,106 @@
         <v>188</v>
       </c>
       <c r="P33">
-        <v>5.48</v>
+        <v>1.95</v>
       </c>
       <c r="Q33">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="R33">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="S33">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="T33">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="U33">
-        <v>2.42</v>
+        <v>4.4</v>
       </c>
       <c r="V33">
-        <v>1.56</v>
+        <v>1.39</v>
       </c>
       <c r="W33">
-        <v>2.26</v>
+        <v>2.73</v>
       </c>
       <c r="X33">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="Y33">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="Z33">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AA33">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AB33">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="AC33">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="AD33">
-        <v>2.38</v>
+        <v>3.08</v>
       </c>
       <c r="AE33">
-        <v>2.66</v>
+        <v>2.02</v>
       </c>
       <c r="AF33">
-        <v>1.47</v>
+        <v>1.78</v>
       </c>
       <c r="AG33">
-        <v>5.25</v>
+        <v>3.6</v>
       </c>
       <c r="AH33">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AI33">
-        <v>9.199999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="AJ33">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AK33">
-        <v>2.3</v>
+        <v>1.79</v>
       </c>
       <c r="AL33">
-        <v>1.55</v>
+        <v>1.92</v>
       </c>
       <c r="AM33">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AN33">
-        <v>1.1</v>
+        <v>1.75</v>
       </c>
       <c r="AO33">
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AQ33">
         <v>1.69</v>
       </c>
       <c r="AR33">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AS33">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="AT33">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AU33">
         <v>2.7</v>
       </c>
       <c r="AV33">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AW33">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AX33">
         <v>1.32</v>
@@ -7022,25 +7022,25 @@
         <v>1.23</v>
       </c>
       <c r="AZ33">
-        <v>2.39</v>
+        <v>1.56</v>
       </c>
       <c r="BA33">
-        <v>1.89</v>
+        <v>3.34</v>
       </c>
       <c r="BB33">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="BC33">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="BD33">
-        <v>3</v>
+        <v>3.52</v>
       </c>
       <c r="BE33">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="BF33">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="BG33">
         <v>0</v>
@@ -7099,13 +7099,13 @@
         <v>188</v>
       </c>
       <c r="P34">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Q34">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="R34">
-        <v>6.5</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="S34">
         <v>1.88</v>
@@ -7117,13 +7117,13 @@
         <v>8.1</v>
       </c>
       <c r="V34">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W34">
         <v>2.56</v>
       </c>
       <c r="X34">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="Y34">
         <v>1.33</v>
@@ -7147,7 +7147,7 @@
         <v>2.02</v>
       </c>
       <c r="AF34">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AG34">
         <v>3.42</v>
@@ -7171,7 +7171,7 @@
         <v>1.16</v>
       </c>
       <c r="AN34">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="AO34">
         <v>0</v>
@@ -7180,10 +7180,10 @@
         <v>1.24</v>
       </c>
       <c r="AQ34">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AR34">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AS34">
         <v>2.33</v>
@@ -7207,19 +7207,19 @@
         <v>1.27</v>
       </c>
       <c r="AZ34">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BA34">
         <v>4.32</v>
       </c>
       <c r="BB34">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="BC34">
         <v>2.3</v>
       </c>
       <c r="BD34">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="BE34">
         <v>1.53</v>
@@ -7284,76 +7284,76 @@
         <v>188</v>
       </c>
       <c r="P35">
-        <v>4</v>
+        <v>5.48</v>
       </c>
       <c r="Q35">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="R35">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="S35">
-        <v>5.29</v>
+        <v>6.1</v>
       </c>
       <c r="T35">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="U35">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="V35">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="W35">
-        <v>2.41</v>
+        <v>2.24</v>
       </c>
       <c r="X35">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="Y35">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z35">
-        <v>7.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA35">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AB35">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AC35">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AD35">
-        <v>2.97</v>
+        <v>2.38</v>
       </c>
       <c r="AE35">
-        <v>2.16</v>
+        <v>2.52</v>
       </c>
       <c r="AF35">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="AG35">
-        <v>4.1</v>
+        <v>5.25</v>
       </c>
       <c r="AH35">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AI35">
-        <v>7.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AJ35">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AK35">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AL35">
-        <v>1.73</v>
+        <v>1.54</v>
       </c>
       <c r="AM35">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AN35">
         <v>1.14</v>
@@ -7362,55 +7362,55 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AQ35">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="AR35">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="AS35">
-        <v>2.52</v>
+        <v>2.75</v>
       </c>
       <c r="AT35">
-        <v>3.48</v>
+        <v>3.7</v>
       </c>
       <c r="AU35">
-        <v>3.05</v>
+        <v>2.65</v>
       </c>
       <c r="AV35">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="AW35">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AX35">
+        <v>1.38</v>
+      </c>
+      <c r="AY35">
+        <v>1.23</v>
+      </c>
+      <c r="AZ35">
+        <v>2.39</v>
+      </c>
+      <c r="BA35">
+        <v>1.87</v>
+      </c>
+      <c r="BB35">
+        <v>1.33</v>
+      </c>
+      <c r="BC35">
+        <v>2.59</v>
+      </c>
+      <c r="BD35">
+        <v>2.91</v>
+      </c>
+      <c r="BE35">
         <v>1.41</v>
       </c>
-      <c r="AY35">
-        <v>1.22</v>
-      </c>
-      <c r="AZ35">
-        <v>2.46</v>
-      </c>
-      <c r="BA35">
-        <v>1.82</v>
-      </c>
-      <c r="BB35">
-        <v>1.27</v>
-      </c>
-      <c r="BC35">
-        <v>2.55</v>
-      </c>
-      <c r="BD35">
-        <v>3.25</v>
-      </c>
-      <c r="BE35">
-        <v>1.44</v>
-      </c>
       <c r="BF35">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="BG35">
         <v>0</v>
@@ -7469,133 +7469,133 @@
         <v>188</v>
       </c>
       <c r="P36">
-        <v>2</v>
+        <v>5.6</v>
       </c>
       <c r="Q36">
-        <v>2.88</v>
+        <v>3.55</v>
       </c>
       <c r="R36">
-        <v>3.8</v>
+        <v>1.52</v>
       </c>
       <c r="S36">
-        <v>2.88</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="T36">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="U36">
-        <v>5.1</v>
+        <v>2.1</v>
       </c>
       <c r="V36">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="W36">
-        <v>2.11</v>
+        <v>2.44</v>
       </c>
       <c r="X36">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="Y36">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="Z36">
-        <v>13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA36">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AB36">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AC36">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="AD36">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="AE36">
-        <v>2.74</v>
+        <v>2.53</v>
       </c>
       <c r="AF36">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="AG36">
-        <v>6.33</v>
+        <v>4.65</v>
       </c>
       <c r="AH36">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AI36">
-        <v>9.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AJ36">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AK36">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AL36">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AM36">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AN36">
-        <v>1.63</v>
+        <v>1.1</v>
       </c>
       <c r="AO36">
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ36">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AR36">
+        <v>2.52</v>
+      </c>
+      <c r="AS36">
+        <v>2.65</v>
+      </c>
+      <c r="AT36">
+        <v>4.41</v>
+      </c>
+      <c r="AU36">
         <v>2.7</v>
       </c>
-      <c r="AS36">
-        <v>3</v>
-      </c>
-      <c r="AT36">
-        <v>4.34</v>
-      </c>
-      <c r="AU36">
-        <v>2.58</v>
-      </c>
       <c r="AV36">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AW36">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AX36">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AY36">
         <v>1.13</v>
       </c>
       <c r="AZ36">
-        <v>1.52</v>
+        <v>3.85</v>
       </c>
       <c r="BA36">
-        <v>3.26</v>
+        <v>1.43</v>
       </c>
       <c r="BB36">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="BC36">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="BD36">
-        <v>2.66</v>
+        <v>2.91</v>
       </c>
       <c r="BE36">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="BF36">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BG36">
         <v>0</v>
@@ -7839,79 +7839,79 @@
         <v>188</v>
       </c>
       <c r="P38">
+        <v>2</v>
+      </c>
+      <c r="Q38">
+        <v>2.88</v>
+      </c>
+      <c r="R38">
+        <v>3.8</v>
+      </c>
+      <c r="S38">
+        <v>2.88</v>
+      </c>
+      <c r="T38">
+        <v>1.75</v>
+      </c>
+      <c r="U38">
+        <v>5.1</v>
+      </c>
+      <c r="V38">
+        <v>1.64</v>
+      </c>
+      <c r="W38">
         <v>2.11</v>
       </c>
-      <c r="Q38">
-        <v>2.8</v>
-      </c>
-      <c r="R38">
-        <v>3.3</v>
-      </c>
-      <c r="S38">
-        <v>2.9</v>
-      </c>
-      <c r="T38">
-        <v>1.81</v>
-      </c>
-      <c r="U38">
-        <v>4.2</v>
-      </c>
-      <c r="V38">
-        <v>1.66</v>
-      </c>
-      <c r="W38">
-        <v>2.15</v>
-      </c>
       <c r="X38">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="Y38">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z38">
-        <v>9.300000000000001</v>
+        <v>13</v>
       </c>
       <c r="AA38">
         <v>1.02</v>
       </c>
       <c r="AB38">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AC38">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AD38">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="AE38">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="AF38">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AG38">
-        <v>6.35</v>
+        <v>6.33</v>
       </c>
       <c r="AH38">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AI38">
-        <v>10.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AJ38">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AK38">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AL38">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AM38">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AN38">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="AO38">
         <v>0</v>
@@ -7920,25 +7920,25 @@
         <v>1.42</v>
       </c>
       <c r="AQ38">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AR38">
-        <v>2.24</v>
+        <v>2.7</v>
       </c>
       <c r="AS38">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="AT38">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="AU38">
-        <v>2.3</v>
+        <v>2.58</v>
       </c>
       <c r="AV38">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AW38">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AX38">
         <v>1.3</v>
@@ -7947,25 +7947,25 @@
         <v>1.13</v>
       </c>
       <c r="AZ38">
-        <v>1.93</v>
+        <v>1.52</v>
       </c>
       <c r="BA38">
-        <v>2.31</v>
+        <v>3.26</v>
       </c>
       <c r="BB38">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="BC38">
-        <v>3.12</v>
+        <v>2.7</v>
       </c>
       <c r="BD38">
-        <v>2.53</v>
+        <v>2.66</v>
       </c>
       <c r="BE38">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BF38">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="BG38">
         <v>0</v>
@@ -8024,133 +8024,133 @@
         <v>188</v>
       </c>
       <c r="P39">
-        <v>5.6</v>
+        <v>2.11</v>
       </c>
       <c r="Q39">
-        <v>3.55</v>
+        <v>2.8</v>
       </c>
       <c r="R39">
-        <v>1.52</v>
+        <v>3.3</v>
       </c>
       <c r="S39">
-        <v>8.050000000000001</v>
+        <v>2.9</v>
       </c>
       <c r="T39">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="U39">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="V39">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="W39">
-        <v>2.44</v>
+        <v>2.15</v>
       </c>
       <c r="X39">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="Y39">
+        <v>1.16</v>
+      </c>
+      <c r="Z39">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AA39">
+        <v>1.02</v>
+      </c>
+      <c r="AB39">
+        <v>1.12</v>
+      </c>
+      <c r="AC39">
+        <v>1.66</v>
+      </c>
+      <c r="AD39">
+        <v>2.09</v>
+      </c>
+      <c r="AE39">
+        <v>3.1</v>
+      </c>
+      <c r="AF39">
+        <v>1.36</v>
+      </c>
+      <c r="AG39">
+        <v>6.35</v>
+      </c>
+      <c r="AH39">
+        <v>1.1</v>
+      </c>
+      <c r="AI39">
+        <v>10.5</v>
+      </c>
+      <c r="AJ39">
+        <v>1.02</v>
+      </c>
+      <c r="AK39">
+        <v>2.28</v>
+      </c>
+      <c r="AL39">
+        <v>1.54</v>
+      </c>
+      <c r="AM39">
+        <v>1.32</v>
+      </c>
+      <c r="AN39">
+        <v>1.55</v>
+      </c>
+      <c r="AO39">
+        <v>0</v>
+      </c>
+      <c r="AP39">
+        <v>1.42</v>
+      </c>
+      <c r="AQ39">
+        <v>1.76</v>
+      </c>
+      <c r="AR39">
+        <v>2.24</v>
+      </c>
+      <c r="AS39">
+        <v>3.02</v>
+      </c>
+      <c r="AT39">
+        <v>4.36</v>
+      </c>
+      <c r="AU39">
+        <v>2.3</v>
+      </c>
+      <c r="AV39">
+        <v>1.94</v>
+      </c>
+      <c r="AW39">
+        <v>1.56</v>
+      </c>
+      <c r="AX39">
         <v>1.3</v>
-      </c>
-      <c r="Z39">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AA39">
-        <v>1</v>
-      </c>
-      <c r="AB39">
-        <v>1.07</v>
-      </c>
-      <c r="AC39">
-        <v>1.38</v>
-      </c>
-      <c r="AD39">
-        <v>2.7</v>
-      </c>
-      <c r="AE39">
-        <v>2.53</v>
-      </c>
-      <c r="AF39">
-        <v>1.56</v>
-      </c>
-      <c r="AG39">
-        <v>4.65</v>
-      </c>
-      <c r="AH39">
-        <v>1.19</v>
-      </c>
-      <c r="AI39">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AJ39">
-        <v>1</v>
-      </c>
-      <c r="AK39">
-        <v>2.4</v>
-      </c>
-      <c r="AL39">
-        <v>1.5</v>
-      </c>
-      <c r="AM39">
-        <v>1.22</v>
-      </c>
-      <c r="AN39">
-        <v>1.1</v>
-      </c>
-      <c r="AO39">
-        <v>0</v>
-      </c>
-      <c r="AP39">
-        <v>1.38</v>
-      </c>
-      <c r="AQ39">
-        <v>1.77</v>
-      </c>
-      <c r="AR39">
-        <v>2.52</v>
-      </c>
-      <c r="AS39">
-        <v>2.65</v>
-      </c>
-      <c r="AT39">
-        <v>4.41</v>
-      </c>
-      <c r="AU39">
-        <v>2.7</v>
-      </c>
-      <c r="AV39">
-        <v>1.99</v>
-      </c>
-      <c r="AW39">
-        <v>1.61</v>
-      </c>
-      <c r="AX39">
-        <v>1.4</v>
       </c>
       <c r="AY39">
         <v>1.13</v>
       </c>
       <c r="AZ39">
-        <v>3.85</v>
+        <v>1.93</v>
       </c>
       <c r="BA39">
+        <v>2.31</v>
+      </c>
+      <c r="BB39">
         <v>1.43</v>
       </c>
-      <c r="BB39">
-        <v>1.33</v>
-      </c>
       <c r="BC39">
-        <v>2.59</v>
+        <v>3.12</v>
       </c>
       <c r="BD39">
-        <v>2.91</v>
+        <v>2.53</v>
       </c>
       <c r="BE39">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="BF39">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="BG39">
         <v>0</v>
@@ -8209,133 +8209,133 @@
         <v>188</v>
       </c>
       <c r="P40">
-        <v>9.9</v>
+        <v>8.9</v>
       </c>
       <c r="Q40">
-        <v>6.39</v>
+        <v>6</v>
       </c>
       <c r="R40">
+        <v>1.25</v>
+      </c>
+      <c r="S40">
+        <v>6.75</v>
+      </c>
+      <c r="T40">
+        <v>2.84</v>
+      </c>
+      <c r="U40">
+        <v>1.62</v>
+      </c>
+      <c r="V40">
+        <v>1.16</v>
+      </c>
+      <c r="W40">
+        <v>4.15</v>
+      </c>
+      <c r="X40">
+        <v>1.9</v>
+      </c>
+      <c r="Y40">
+        <v>1.8</v>
+      </c>
+      <c r="Z40">
+        <v>3.68</v>
+      </c>
+      <c r="AA40">
+        <v>1.2</v>
+      </c>
+      <c r="AB40">
+        <v>1.01</v>
+      </c>
+      <c r="AC40">
+        <v>1.06</v>
+      </c>
+      <c r="AD40">
+        <v>6.15</v>
+      </c>
+      <c r="AE40">
+        <v>1.3</v>
+      </c>
+      <c r="AF40">
+        <v>2.97</v>
+      </c>
+      <c r="AG40">
+        <v>1.86</v>
+      </c>
+      <c r="AH40">
+        <v>1.88</v>
+      </c>
+      <c r="AI40">
+        <v>2.88</v>
+      </c>
+      <c r="AJ40">
+        <v>1.35</v>
+      </c>
+      <c r="AK40">
+        <v>1.61</v>
+      </c>
+      <c r="AL40">
+        <v>2.1</v>
+      </c>
+      <c r="AM40">
+        <v>1.1</v>
+      </c>
+      <c r="AN40">
+        <v>1.04</v>
+      </c>
+      <c r="AO40">
+        <v>0</v>
+      </c>
+      <c r="AP40">
         <v>1.22</v>
       </c>
-      <c r="S40">
-        <v>0</v>
-      </c>
-      <c r="T40">
-        <v>0</v>
-      </c>
-      <c r="U40">
-        <v>0</v>
-      </c>
-      <c r="V40">
-        <v>0</v>
-      </c>
-      <c r="W40">
-        <v>0</v>
-      </c>
-      <c r="X40">
-        <v>0</v>
-      </c>
-      <c r="Y40">
-        <v>0</v>
-      </c>
-      <c r="Z40">
-        <v>0</v>
-      </c>
-      <c r="AA40">
-        <v>0</v>
-      </c>
-      <c r="AB40">
-        <v>0</v>
-      </c>
-      <c r="AC40">
-        <v>0</v>
-      </c>
-      <c r="AD40">
-        <v>0</v>
-      </c>
-      <c r="AE40">
-        <v>0</v>
-      </c>
-      <c r="AF40">
-        <v>0</v>
-      </c>
-      <c r="AG40">
-        <v>0</v>
-      </c>
-      <c r="AH40">
-        <v>0</v>
-      </c>
-      <c r="AI40">
-        <v>0</v>
-      </c>
-      <c r="AJ40">
-        <v>0</v>
-      </c>
-      <c r="AK40">
-        <v>0</v>
-      </c>
-      <c r="AL40">
-        <v>0</v>
-      </c>
-      <c r="AM40">
-        <v>0</v>
-      </c>
-      <c r="AN40">
-        <v>0</v>
-      </c>
-      <c r="AO40">
-        <v>0</v>
-      </c>
-      <c r="AP40">
-        <v>0</v>
-      </c>
       <c r="AQ40">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR40">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AS40">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AT40">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AU40">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AV40">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AW40">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AX40">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY40">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ40">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BA40">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BB40">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC40">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BD40">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BE40">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BF40">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BG40">
         <v>0</v>

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -310,12 +310,12 @@
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
+    <t>Egypt Egyptian Premier League</t>
+  </si>
+  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
-    <t>Egypt Egyptian Premier League</t>
-  </si>
-  <si>
     <t>South Africa Premier Soccer League</t>
   </si>
   <si>
@@ -337,54 +337,54 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Jeonbuk Motors</t>
+  </si>
+  <si>
     <t>Bucheon 1995</t>
   </si>
   <si>
-    <t>Jeonbuk Motors</t>
+    <t>Sangju Sangmu</t>
   </si>
   <si>
     <t>Gangwon</t>
   </si>
   <si>
-    <t>Sangju Sangmu</t>
-  </si>
-  <si>
     <t>Daejeon Citizen</t>
   </si>
   <si>
     <t>Madura United</t>
   </si>
   <si>
+    <t>FC Seoul</t>
+  </si>
+  <si>
     <t>Ethiopia Nigd Bank</t>
   </si>
   <si>
-    <t>FC Seoul</t>
-  </si>
-  <si>
     <t>Qingdao Youth Island</t>
   </si>
   <si>
     <t>Tanjong Pagar</t>
   </si>
   <si>
+    <t>Shandong Luneng</t>
+  </si>
+  <si>
     <t>Shenyang Urban</t>
   </si>
   <si>
-    <t>Shandong Luneng</t>
-  </si>
-  <si>
     <t>Dire Dawa Kenema</t>
   </si>
   <si>
     <t>Chongqing Tongliang Long</t>
   </si>
   <si>
+    <t>Karvan FK</t>
+  </si>
+  <si>
     <t>Borneo</t>
   </si>
   <si>
-    <t>Karvan FK</t>
-  </si>
-  <si>
     <t>Mekelle Kenema</t>
   </si>
   <si>
@@ -418,36 +418,36 @@
     <t>Dibba Al Fujairah</t>
   </si>
   <si>
+    <t>Al Ittihad Kalba</t>
+  </si>
+  <si>
     <t>Bani Yas</t>
   </si>
   <si>
-    <t>Al Ittihad Kalba</t>
+    <t>Ceramica Cleopatra</t>
+  </si>
+  <si>
+    <t>Lokomotiv Sofia 1929</t>
+  </si>
+  <si>
+    <t>Smouha SC</t>
+  </si>
+  <si>
+    <t>Al Ahly</t>
   </si>
   <si>
     <t>Falkenberg</t>
   </si>
   <si>
-    <t>Ceramica Cleopatra</t>
-  </si>
-  <si>
-    <t>Lokomotiv Sofia 1929</t>
-  </si>
-  <si>
-    <t>Al Ahly</t>
-  </si>
-  <si>
-    <t>Smouha SC</t>
+    <t>Chippa United</t>
+  </si>
+  <si>
+    <t>Magesi</t>
   </si>
   <si>
     <t>Stellenbosch</t>
   </si>
   <si>
-    <t>Chippa United</t>
-  </si>
-  <si>
-    <t>Magesi</t>
-  </si>
-  <si>
     <t>Siwelele</t>
   </si>
   <si>
@@ -460,54 +460,54 @@
     <t>New York City II</t>
   </si>
   <si>
+    <t>Gwangju</t>
+  </si>
+  <si>
     <t>Jeju United</t>
   </si>
   <si>
-    <t>Gwangju</t>
+    <t>Ulsan</t>
   </si>
   <si>
     <t>Pohang Steelers</t>
   </si>
   <si>
-    <t>Ulsan</t>
-  </si>
-  <si>
     <t>Incheon United</t>
   </si>
   <si>
     <t>Bali United</t>
   </si>
   <si>
+    <t>Anyang</t>
+  </si>
+  <si>
     <t>Kedus Giorgis</t>
   </si>
   <si>
-    <t>Anyang</t>
-  </si>
-  <si>
     <t>Tianjin Teda</t>
   </si>
   <si>
     <t>Hougang United</t>
   </si>
   <si>
+    <t>Shanghai Shenhua</t>
+  </si>
+  <si>
     <t>Chengdu Better City FC</t>
   </si>
   <si>
-    <t>Shanghai Shenhua</t>
-  </si>
-  <si>
     <t>Ethiopia Bunna</t>
   </si>
   <si>
     <t>Henan Jianye</t>
   </si>
   <si>
+    <t>Neftçi</t>
+  </si>
+  <si>
     <t>Persita</t>
   </si>
   <si>
-    <t>Neftçi</t>
-  </si>
-  <si>
     <t>Arba Minch Kenema</t>
   </si>
   <si>
@@ -544,28 +544,28 @@
     <t>Al Dhafra</t>
   </si>
   <si>
+    <t>Pyramids FC</t>
+  </si>
+  <si>
+    <t>Botev Vratsa</t>
+  </si>
+  <si>
+    <t>Zamalek</t>
+  </si>
+  <si>
+    <t>ENPPI</t>
+  </si>
+  <si>
     <t>Norrköping</t>
   </si>
   <si>
-    <t>Pyramids FC</t>
-  </si>
-  <si>
-    <t>Botev Vratsa</t>
-  </si>
-  <si>
-    <t>ENPPI</t>
-  </si>
-  <si>
-    <t>Zamalek</t>
+    <t>Sekhukhune United</t>
+  </si>
+  <si>
+    <t>Orbit College</t>
   </si>
   <si>
     <t>Orlando Pirates</t>
-  </si>
-  <si>
-    <t>Sekhukhune United</t>
-  </si>
-  <si>
-    <t>Orbit College</t>
   </si>
   <si>
     <t>Durban City</t>
@@ -1179,133 +1179,133 @@
         <v>188</v>
       </c>
       <c r="P2">
-        <v>2.49</v>
+        <v>1.33</v>
       </c>
       <c r="Q2">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="R2">
-        <v>2.8</v>
+        <v>7.75</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>5.99</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AE2">
-        <v>2.35</v>
+        <v>1.96</v>
       </c>
       <c r="AF2">
+        <v>1.85</v>
+      </c>
+      <c r="AG2">
+        <v>3.18</v>
+      </c>
+      <c r="AH2">
+        <v>1.3</v>
+      </c>
+      <c r="AI2">
+        <v>6.5</v>
+      </c>
+      <c r="AJ2">
+        <v>1.11</v>
+      </c>
+      <c r="AK2">
+        <v>2.26</v>
+      </c>
+      <c r="AL2">
         <v>1.57</v>
       </c>
-      <c r="AG2">
-        <v>0</v>
-      </c>
-      <c r="AH2">
-        <v>0</v>
-      </c>
-      <c r="AI2">
-        <v>0</v>
-      </c>
-      <c r="AJ2">
-        <v>0</v>
-      </c>
-      <c r="AK2">
-        <v>0</v>
-      </c>
-      <c r="AL2">
-        <v>0</v>
-      </c>
       <c r="AM2">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AO2">
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="AU2">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV2">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AW2">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AX2">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AY2">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AZ2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BA2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BB2">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC2">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="BD2">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BE2">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF2">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG2">
         <v>0</v>
@@ -1364,133 +1364,133 @@
         <v>188</v>
       </c>
       <c r="P3">
-        <v>1.33</v>
+        <v>2.49</v>
       </c>
       <c r="Q3">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="R3">
-        <v>7.75</v>
+        <v>2.8</v>
       </c>
       <c r="S3">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y3">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z3">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC3">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AD3">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AE3">
-        <v>1.96</v>
+        <v>2.35</v>
       </c>
       <c r="AF3">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AG3">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AH3">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK3">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AL3">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AN3">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AO3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AQ3">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AR3">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AS3">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AT3">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="AU3">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV3">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AW3">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AX3">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AY3">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AZ3">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BA3">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BB3">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC3">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="BD3">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BE3">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BF3">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG3">
         <v>0</v>
@@ -1549,133 +1549,133 @@
         <v>188</v>
       </c>
       <c r="P4">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S4">
+        <v>3.24</v>
+      </c>
+      <c r="T4">
+        <v>2.05</v>
+      </c>
+      <c r="U4">
+        <v>3.24</v>
+      </c>
+      <c r="V4">
+        <v>1.39</v>
+      </c>
+      <c r="W4">
         <v>2.77</v>
       </c>
-      <c r="T4">
+      <c r="X4">
+        <v>3</v>
+      </c>
+      <c r="Y4">
+        <v>1.36</v>
+      </c>
+      <c r="Z4">
+        <v>7.5</v>
+      </c>
+      <c r="AA4">
+        <v>1.03</v>
+      </c>
+      <c r="AB4">
+        <v>1.02</v>
+      </c>
+      <c r="AC4">
+        <v>1.27</v>
+      </c>
+      <c r="AD4">
+        <v>3.35</v>
+      </c>
+      <c r="AE4">
+        <v>1.99</v>
+      </c>
+      <c r="AF4">
+        <v>1.8</v>
+      </c>
+      <c r="AG4">
+        <v>3.48</v>
+      </c>
+      <c r="AH4">
+        <v>1.24</v>
+      </c>
+      <c r="AI4">
+        <v>6.73</v>
+      </c>
+      <c r="AJ4">
+        <v>1.04</v>
+      </c>
+      <c r="AK4">
+        <v>1.73</v>
+      </c>
+      <c r="AL4">
         <v>2</v>
       </c>
-      <c r="U4">
-        <v>4.76</v>
-      </c>
-      <c r="V4">
-        <v>1.43</v>
-      </c>
-      <c r="W4">
-        <v>2.34</v>
-      </c>
-      <c r="X4">
-        <v>3.4</v>
-      </c>
-      <c r="Y4">
-        <v>1.27</v>
-      </c>
-      <c r="Z4">
-        <v>9.5</v>
-      </c>
-      <c r="AA4">
-        <v>1.01</v>
-      </c>
-      <c r="AB4">
-        <v>1.05</v>
-      </c>
-      <c r="AC4">
-        <v>1.42</v>
-      </c>
-      <c r="AD4">
-        <v>2.7</v>
-      </c>
-      <c r="AE4">
-        <v>2.38</v>
-      </c>
-      <c r="AF4">
-        <v>1.55</v>
-      </c>
-      <c r="AG4">
-        <v>4.5</v>
-      </c>
-      <c r="AH4">
+      <c r="AM4">
+        <v>1.46</v>
+      </c>
+      <c r="AN4">
+        <v>1.44</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>1.39</v>
+      </c>
+      <c r="AQ4">
+        <v>1.72</v>
+      </c>
+      <c r="AR4">
+        <v>2.18</v>
+      </c>
+      <c r="AS4">
+        <v>2.9</v>
+      </c>
+      <c r="AT4">
+        <v>4.16</v>
+      </c>
+      <c r="AU4">
+        <v>2.78</v>
+      </c>
+      <c r="AV4">
+        <v>2.04</v>
+      </c>
+      <c r="AW4">
+        <v>1.6</v>
+      </c>
+      <c r="AX4">
+        <v>1.32</v>
+      </c>
+      <c r="AY4">
         <v>1.15</v>
       </c>
-      <c r="AI4">
-        <v>9</v>
-      </c>
-      <c r="AJ4">
-        <v>1.01</v>
-      </c>
-      <c r="AK4">
-        <v>1.94</v>
-      </c>
-      <c r="AL4">
-        <v>1.68</v>
-      </c>
-      <c r="AM4">
-        <v>1.33</v>
-      </c>
-      <c r="AN4">
-        <v>1.71</v>
-      </c>
-      <c r="AO4">
-        <v>0</v>
-      </c>
-      <c r="AP4">
-        <v>1.53</v>
-      </c>
-      <c r="AQ4">
-        <v>1.92</v>
-      </c>
-      <c r="AR4">
-        <v>2.39</v>
-      </c>
-      <c r="AS4">
-        <v>3.48</v>
-      </c>
-      <c r="AT4">
-        <v>5.23</v>
-      </c>
-      <c r="AU4">
-        <v>2.31</v>
-      </c>
-      <c r="AV4">
-        <v>1.79</v>
-      </c>
-      <c r="AW4">
-        <v>1.45</v>
-      </c>
-      <c r="AX4">
+      <c r="AZ4">
+        <v>1.81</v>
+      </c>
+      <c r="BA4">
+        <v>2.6</v>
+      </c>
+      <c r="BB4">
         <v>1.22</v>
       </c>
-      <c r="AY4">
-        <v>1.08</v>
-      </c>
-      <c r="AZ4">
-        <v>1.65</v>
-      </c>
-      <c r="BA4">
-        <v>3.1</v>
-      </c>
-      <c r="BB4">
-        <v>1.33</v>
-      </c>
       <c r="BC4">
-        <v>2.53</v>
+        <v>2.18</v>
       </c>
       <c r="BD4">
-        <v>3.04</v>
+        <v>3.66</v>
       </c>
       <c r="BE4">
-        <v>1.46</v>
+        <v>1.66</v>
       </c>
       <c r="BF4">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="BG4">
         <v>0</v>
@@ -1734,133 +1734,133 @@
         <v>188</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S5">
-        <v>3.24</v>
+        <v>2.77</v>
       </c>
       <c r="T5">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="U5">
-        <v>3.24</v>
+        <v>4.76</v>
       </c>
       <c r="V5">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="W5">
-        <v>2.77</v>
+        <v>2.34</v>
       </c>
       <c r="X5">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="Y5">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="Z5">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="AA5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AB5">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AC5">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AD5">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="AE5">
-        <v>1.99</v>
+        <v>2.38</v>
       </c>
       <c r="AF5">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AG5">
+        <v>4.5</v>
+      </c>
+      <c r="AH5">
+        <v>1.15</v>
+      </c>
+      <c r="AI5">
+        <v>9</v>
+      </c>
+      <c r="AJ5">
+        <v>1.01</v>
+      </c>
+      <c r="AK5">
+        <v>1.94</v>
+      </c>
+      <c r="AL5">
+        <v>1.68</v>
+      </c>
+      <c r="AM5">
+        <v>1.33</v>
+      </c>
+      <c r="AN5">
+        <v>1.71</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>1.53</v>
+      </c>
+      <c r="AQ5">
+        <v>1.92</v>
+      </c>
+      <c r="AR5">
+        <v>2.39</v>
+      </c>
+      <c r="AS5">
         <v>3.48</v>
       </c>
-      <c r="AH5">
-        <v>1.24</v>
-      </c>
-      <c r="AI5">
-        <v>6.73</v>
-      </c>
-      <c r="AJ5">
-        <v>1.04</v>
-      </c>
-      <c r="AK5">
-        <v>1.73</v>
-      </c>
-      <c r="AL5">
-        <v>2</v>
-      </c>
-      <c r="AM5">
+      <c r="AT5">
+        <v>5.23</v>
+      </c>
+      <c r="AU5">
+        <v>2.31</v>
+      </c>
+      <c r="AV5">
+        <v>1.79</v>
+      </c>
+      <c r="AW5">
+        <v>1.45</v>
+      </c>
+      <c r="AX5">
+        <v>1.22</v>
+      </c>
+      <c r="AY5">
+        <v>1.08</v>
+      </c>
+      <c r="AZ5">
+        <v>1.65</v>
+      </c>
+      <c r="BA5">
+        <v>3.1</v>
+      </c>
+      <c r="BB5">
+        <v>1.33</v>
+      </c>
+      <c r="BC5">
+        <v>2.53</v>
+      </c>
+      <c r="BD5">
+        <v>3.04</v>
+      </c>
+      <c r="BE5">
         <v>1.46</v>
       </c>
-      <c r="AN5">
-        <v>1.44</v>
-      </c>
-      <c r="AO5">
-        <v>0</v>
-      </c>
-      <c r="AP5">
-        <v>1.39</v>
-      </c>
-      <c r="AQ5">
-        <v>1.72</v>
-      </c>
-      <c r="AR5">
-        <v>2.18</v>
-      </c>
-      <c r="AS5">
-        <v>2.9</v>
-      </c>
-      <c r="AT5">
-        <v>4.16</v>
-      </c>
-      <c r="AU5">
-        <v>2.78</v>
-      </c>
-      <c r="AV5">
-        <v>2.04</v>
-      </c>
-      <c r="AW5">
-        <v>1.6</v>
-      </c>
-      <c r="AX5">
-        <v>1.32</v>
-      </c>
-      <c r="AY5">
-        <v>1.15</v>
-      </c>
-      <c r="AZ5">
-        <v>1.81</v>
-      </c>
-      <c r="BA5">
-        <v>2.6</v>
-      </c>
-      <c r="BB5">
-        <v>1.22</v>
-      </c>
-      <c r="BC5">
-        <v>2.18</v>
-      </c>
-      <c r="BD5">
-        <v>3.66</v>
-      </c>
-      <c r="BE5">
-        <v>1.66</v>
-      </c>
       <c r="BF5">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="BG5">
         <v>0</v>
@@ -2122,10 +2122,10 @@
         <v>3.12</v>
       </c>
       <c r="V7">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W7">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="X7">
         <v>2.4</v>
@@ -2149,10 +2149,10 @@
         <v>3.82</v>
       </c>
       <c r="AE7">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AF7">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AG7">
         <v>2.62</v>
@@ -2170,13 +2170,13 @@
         <v>1.62</v>
       </c>
       <c r="AL7">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="AM7">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AN7">
-        <v>1.27</v>
+        <v>1.43</v>
       </c>
       <c r="AO7">
         <v>0</v>
@@ -2250,10 +2250,10 @@
         <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E8" t="s">
         <v>113</v>
@@ -2289,133 +2289,133 @@
         <v>188</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AO8">
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG8">
         <v>0</v>
@@ -2435,10 +2435,10 @@
         <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E9" t="s">
         <v>114</v>
@@ -2474,133 +2474,133 @@
         <v>188</v>
       </c>
       <c r="P9">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z9">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC9">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD9">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AH9">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI9">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AJ9">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK9">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AL9">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AM9">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN9">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AO9">
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ9">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AR9">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AS9">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AT9">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AU9">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AV9">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AW9">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AX9">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AY9">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AZ9">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="BA9">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="BB9">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC9">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD9">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE9">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF9">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG9">
         <v>0</v>
@@ -3029,133 +3029,133 @@
         <v>188</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T12">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="U12">
-        <v>2.17</v>
+        <v>2.78</v>
       </c>
       <c r="V12">
+        <v>1.22</v>
+      </c>
+      <c r="W12">
+        <v>3.6</v>
+      </c>
+      <c r="X12">
+        <v>2.1</v>
+      </c>
+      <c r="Y12">
+        <v>1.71</v>
+      </c>
+      <c r="Z12">
+        <v>4.45</v>
+      </c>
+      <c r="AA12">
+        <v>1.15</v>
+      </c>
+      <c r="AB12">
+        <v>1.02</v>
+      </c>
+      <c r="AC12">
+        <v>1.13</v>
+      </c>
+      <c r="AD12">
+        <v>5.65</v>
+      </c>
+      <c r="AE12">
+        <v>1.39</v>
+      </c>
+      <c r="AF12">
+        <v>2.59</v>
+      </c>
+      <c r="AG12">
+        <v>2.09</v>
+      </c>
+      <c r="AH12">
+        <v>1.76</v>
+      </c>
+      <c r="AI12">
+        <v>3.4</v>
+      </c>
+      <c r="AJ12">
+        <v>1.25</v>
+      </c>
+      <c r="AK12">
+        <v>1.36</v>
+      </c>
+      <c r="AL12">
+        <v>2.75</v>
+      </c>
+      <c r="AM12">
+        <v>1.22</v>
+      </c>
+      <c r="AN12">
+        <v>1.38</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>1.09</v>
+      </c>
+      <c r="AQ12">
+        <v>1.23</v>
+      </c>
+      <c r="AR12">
+        <v>1.58</v>
+      </c>
+      <c r="AS12">
+        <v>1.78</v>
+      </c>
+      <c r="AT12">
+        <v>2.21</v>
+      </c>
+      <c r="AU12">
+        <v>5.25</v>
+      </c>
+      <c r="AV12">
+        <v>3.4</v>
+      </c>
+      <c r="AW12">
+        <v>2.46</v>
+      </c>
+      <c r="AX12">
+        <v>1.92</v>
+      </c>
+      <c r="AY12">
+        <v>1.58</v>
+      </c>
+      <c r="AZ12">
+        <v>1.92</v>
+      </c>
+      <c r="BA12">
+        <v>2.1</v>
+      </c>
+      <c r="BB12">
+        <v>1.08</v>
+      </c>
+      <c r="BC12">
+        <v>1.62</v>
+      </c>
+      <c r="BD12">
+        <v>5.7</v>
+      </c>
+      <c r="BE12">
+        <v>2.19</v>
+      </c>
+      <c r="BF12">
         <v>1.33</v>
-      </c>
-      <c r="W12">
-        <v>2.99</v>
-      </c>
-      <c r="X12">
-        <v>2.59</v>
-      </c>
-      <c r="Y12">
-        <v>1.43</v>
-      </c>
-      <c r="Z12">
-        <v>6.15</v>
-      </c>
-      <c r="AA12">
-        <v>1.06</v>
-      </c>
-      <c r="AB12">
-        <v>1</v>
-      </c>
-      <c r="AC12">
-        <v>1.22</v>
-      </c>
-      <c r="AD12">
-        <v>3.77</v>
-      </c>
-      <c r="AE12">
-        <v>1.74</v>
-      </c>
-      <c r="AF12">
-        <v>1.99</v>
-      </c>
-      <c r="AG12">
-        <v>3</v>
-      </c>
-      <c r="AH12">
-        <v>1.32</v>
-      </c>
-      <c r="AI12">
-        <v>5.2</v>
-      </c>
-      <c r="AJ12">
-        <v>1.08</v>
-      </c>
-      <c r="AK12">
-        <v>1.81</v>
-      </c>
-      <c r="AL12">
-        <v>1.9</v>
-      </c>
-      <c r="AM12">
-        <v>1.24</v>
-      </c>
-      <c r="AN12">
-        <v>1.15</v>
-      </c>
-      <c r="AO12">
-        <v>0</v>
-      </c>
-      <c r="AP12">
-        <v>1.19</v>
-      </c>
-      <c r="AQ12">
-        <v>1.38</v>
-      </c>
-      <c r="AR12">
-        <v>1.94</v>
-      </c>
-      <c r="AS12">
-        <v>2.16</v>
-      </c>
-      <c r="AT12">
-        <v>2.84</v>
-      </c>
-      <c r="AU12">
-        <v>3.72</v>
-      </c>
-      <c r="AV12">
-        <v>2.59</v>
-      </c>
-      <c r="AW12">
-        <v>1.98</v>
-      </c>
-      <c r="AX12">
-        <v>1.61</v>
-      </c>
-      <c r="AY12">
-        <v>1.34</v>
-      </c>
-      <c r="AZ12">
-        <v>5.03</v>
-      </c>
-      <c r="BA12">
-        <v>1.4</v>
-      </c>
-      <c r="BB12">
-        <v>1.18</v>
-      </c>
-      <c r="BC12">
-        <v>2.03</v>
-      </c>
-      <c r="BD12">
-        <v>3.95</v>
-      </c>
-      <c r="BE12">
-        <v>1.72</v>
-      </c>
-      <c r="BF12">
-        <v>1.16</v>
       </c>
       <c r="BG12">
         <v>0</v>
@@ -3214,133 +3214,133 @@
         <v>188</v>
       </c>
       <c r="P13">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q13">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R13">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S13">
+        <v>5</v>
+      </c>
+      <c r="T13">
+        <v>2.25</v>
+      </c>
+      <c r="U13">
+        <v>2.17</v>
+      </c>
+      <c r="V13">
+        <v>1.33</v>
+      </c>
+      <c r="W13">
+        <v>2.99</v>
+      </c>
+      <c r="X13">
+        <v>2.59</v>
+      </c>
+      <c r="Y13">
+        <v>1.43</v>
+      </c>
+      <c r="Z13">
+        <v>6.15</v>
+      </c>
+      <c r="AA13">
+        <v>1.06</v>
+      </c>
+      <c r="AB13">
+        <v>1</v>
+      </c>
+      <c r="AC13">
+        <v>1.22</v>
+      </c>
+      <c r="AD13">
+        <v>3.77</v>
+      </c>
+      <c r="AE13">
+        <v>1.74</v>
+      </c>
+      <c r="AF13">
+        <v>1.99</v>
+      </c>
+      <c r="AG13">
         <v>3</v>
       </c>
-      <c r="T13">
-        <v>2.28</v>
-      </c>
-      <c r="U13">
-        <v>2.78</v>
-      </c>
-      <c r="V13">
-        <v>1.22</v>
-      </c>
-      <c r="W13">
-        <v>3.6</v>
-      </c>
-      <c r="X13">
-        <v>2.1</v>
-      </c>
-      <c r="Y13">
-        <v>1.71</v>
-      </c>
-      <c r="Z13">
-        <v>4.45</v>
-      </c>
-      <c r="AA13">
+      <c r="AH13">
+        <v>1.32</v>
+      </c>
+      <c r="AI13">
+        <v>5.2</v>
+      </c>
+      <c r="AJ13">
+        <v>1.08</v>
+      </c>
+      <c r="AK13">
+        <v>1.81</v>
+      </c>
+      <c r="AL13">
+        <v>1.9</v>
+      </c>
+      <c r="AM13">
+        <v>1.24</v>
+      </c>
+      <c r="AN13">
         <v>1.15</v>
       </c>
-      <c r="AB13">
-        <v>1.02</v>
-      </c>
-      <c r="AC13">
-        <v>1.13</v>
-      </c>
-      <c r="AD13">
-        <v>5.65</v>
-      </c>
-      <c r="AE13">
-        <v>1.39</v>
-      </c>
-      <c r="AF13">
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>1.19</v>
+      </c>
+      <c r="AQ13">
+        <v>1.38</v>
+      </c>
+      <c r="AR13">
+        <v>1.94</v>
+      </c>
+      <c r="AS13">
+        <v>2.16</v>
+      </c>
+      <c r="AT13">
+        <v>2.84</v>
+      </c>
+      <c r="AU13">
+        <v>3.72</v>
+      </c>
+      <c r="AV13">
         <v>2.59</v>
       </c>
-      <c r="AG13">
-        <v>2.09</v>
-      </c>
-      <c r="AH13">
-        <v>1.76</v>
-      </c>
-      <c r="AI13">
-        <v>3.4</v>
-      </c>
-      <c r="AJ13">
-        <v>1.25</v>
-      </c>
-      <c r="AK13">
-        <v>1.36</v>
-      </c>
-      <c r="AL13">
-        <v>2.75</v>
-      </c>
-      <c r="AM13">
-        <v>1.22</v>
-      </c>
-      <c r="AN13">
-        <v>1.38</v>
-      </c>
-      <c r="AO13">
-        <v>0</v>
-      </c>
-      <c r="AP13">
-        <v>1.09</v>
-      </c>
-      <c r="AQ13">
-        <v>1.23</v>
-      </c>
-      <c r="AR13">
-        <v>1.58</v>
-      </c>
-      <c r="AS13">
-        <v>1.78</v>
-      </c>
-      <c r="AT13">
-        <v>2.21</v>
-      </c>
-      <c r="AU13">
-        <v>5.25</v>
-      </c>
-      <c r="AV13">
-        <v>3.4</v>
-      </c>
       <c r="AW13">
-        <v>2.46</v>
+        <v>1.98</v>
       </c>
       <c r="AX13">
-        <v>1.92</v>
+        <v>1.61</v>
       </c>
       <c r="AY13">
-        <v>1.58</v>
+        <v>1.34</v>
       </c>
       <c r="AZ13">
-        <v>1.92</v>
+        <v>5.03</v>
       </c>
       <c r="BA13">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="BB13">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="BC13">
-        <v>1.62</v>
+        <v>2.03</v>
       </c>
       <c r="BD13">
-        <v>5.7</v>
+        <v>3.95</v>
       </c>
       <c r="BE13">
-        <v>2.19</v>
+        <v>1.72</v>
       </c>
       <c r="BF13">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="BG13">
         <v>0</v>
@@ -3730,7 +3730,7 @@
         <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D16" t="s">
         <v>105</v>
@@ -3769,133 +3769,133 @@
         <v>188</v>
       </c>
       <c r="P16">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q16">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R16">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="V16">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="W16">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="X16">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z16">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC16">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AD16">
-        <v>4.35</v>
+        <v>4.8</v>
       </c>
       <c r="AE16">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AF16">
-        <v>2.19</v>
+        <v>2.43</v>
       </c>
       <c r="AG16">
-        <v>2.46</v>
+        <v>2.14</v>
       </c>
       <c r="AH16">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="AI16">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="AJ16">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AK16">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL16">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AM16">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AN16">
-        <v>2.49</v>
+        <v>1.05</v>
       </c>
       <c r="AO16">
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ16">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR16">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AS16">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT16">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AU16">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AV16">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AW16">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AX16">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AY16">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AZ16">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="BA16">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BB16">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC16">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="BD16">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="BE16">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="BF16">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG16">
         <v>0</v>
@@ -3915,7 +3915,7 @@
         <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D17" t="s">
         <v>105</v>
@@ -3954,133 +3954,133 @@
         <v>188</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>6.08</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC17">
+        <v>1.19</v>
+      </c>
+      <c r="AD17">
+        <v>4.35</v>
+      </c>
+      <c r="AE17">
+        <v>1.65</v>
+      </c>
+      <c r="AF17">
+        <v>2.26</v>
+      </c>
+      <c r="AG17">
+        <v>2.63</v>
+      </c>
+      <c r="AH17">
+        <v>1.49</v>
+      </c>
+      <c r="AI17">
+        <v>4.5</v>
+      </c>
+      <c r="AJ17">
+        <v>1.13</v>
+      </c>
+      <c r="AK17">
+        <v>1.67</v>
+      </c>
+      <c r="AL17">
+        <v>1.96</v>
+      </c>
+      <c r="AM17">
+        <v>1.06</v>
+      </c>
+      <c r="AN17">
+        <v>2.49</v>
+      </c>
+      <c r="AO17">
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <v>1.18</v>
+      </c>
+      <c r="AQ17">
+        <v>1.42</v>
+      </c>
+      <c r="AR17">
+        <v>1.87</v>
+      </c>
+      <c r="AS17">
+        <v>2.18</v>
+      </c>
+      <c r="AT17">
+        <v>2.86</v>
+      </c>
+      <c r="AU17">
+        <v>3.68</v>
+      </c>
+      <c r="AV17">
+        <v>2.57</v>
+      </c>
+      <c r="AW17">
+        <v>1.97</v>
+      </c>
+      <c r="AX17">
+        <v>1.6</v>
+      </c>
+      <c r="AY17">
+        <v>1.34</v>
+      </c>
+      <c r="AZ17">
+        <v>1.43</v>
+      </c>
+      <c r="BA17">
+        <v>3.9</v>
+      </c>
+      <c r="BB17">
         <v>1.12</v>
       </c>
-      <c r="AD17">
-        <v>4.8</v>
-      </c>
-      <c r="AE17">
-        <v>1.45</v>
-      </c>
-      <c r="AF17">
-        <v>2.43</v>
-      </c>
-      <c r="AG17">
-        <v>2.14</v>
-      </c>
-      <c r="AH17">
-        <v>1.58</v>
-      </c>
-      <c r="AI17">
-        <v>3.5</v>
-      </c>
-      <c r="AJ17">
-        <v>1.23</v>
-      </c>
-      <c r="AK17">
-        <v>0</v>
-      </c>
-      <c r="AL17">
-        <v>0</v>
-      </c>
-      <c r="AM17">
-        <v>1.11</v>
-      </c>
-      <c r="AN17">
-        <v>1.05</v>
-      </c>
-      <c r="AO17">
-        <v>0</v>
-      </c>
-      <c r="AP17">
-        <v>0</v>
-      </c>
-      <c r="AQ17">
-        <v>0</v>
-      </c>
-      <c r="AR17">
-        <v>0</v>
-      </c>
-      <c r="AS17">
-        <v>0</v>
-      </c>
-      <c r="AT17">
-        <v>0</v>
-      </c>
-      <c r="AU17">
-        <v>0</v>
-      </c>
-      <c r="AV17">
-        <v>0</v>
-      </c>
-      <c r="AW17">
-        <v>0</v>
-      </c>
-      <c r="AX17">
-        <v>0</v>
-      </c>
-      <c r="AY17">
-        <v>0</v>
-      </c>
-      <c r="AZ17">
-        <v>0</v>
-      </c>
-      <c r="BA17">
-        <v>0</v>
-      </c>
-      <c r="BB17">
-        <v>0</v>
-      </c>
       <c r="BC17">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BD17">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="BE17">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BF17">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG17">
         <v>0</v>
@@ -4694,13 +4694,13 @@
         <v>188</v>
       </c>
       <c r="P21">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="Q21">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R21">
-        <v>3.84</v>
+        <v>3.4</v>
       </c>
       <c r="S21">
         <v>2.69</v>
@@ -4733,7 +4733,7 @@
         <v>1.04</v>
       </c>
       <c r="AC21">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AD21">
         <v>2.62</v>
@@ -4742,13 +4742,13 @@
         <v>2.35</v>
       </c>
       <c r="AF21">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG21">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="AH21">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AI21">
         <v>8.4</v>
@@ -4760,7 +4760,7 @@
         <v>1.95</v>
       </c>
       <c r="AL21">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AM21">
         <v>1.33</v>
@@ -4772,10 +4772,10 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AQ21">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AR21">
         <v>2.64</v>
@@ -4790,7 +4790,7 @@
         <v>2.62</v>
       </c>
       <c r="AV21">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AW21">
         <v>1.58</v>
@@ -4799,7 +4799,7 @@
         <v>1.31</v>
       </c>
       <c r="AY21">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AZ21">
         <v>1.87</v>
@@ -6144,7 +6144,7 @@
         <v>134</v>
       </c>
       <c r="F29" t="s">
-        <v>175</v>
+        <v>145</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -6329,7 +6329,7 @@
         <v>135</v>
       </c>
       <c r="F30" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -6508,7 +6508,7 @@
         <v>98</v>
       </c>
       <c r="D31" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E31" t="s">
         <v>136</v>
@@ -6544,133 +6544,133 @@
         <v>188</v>
       </c>
       <c r="P31">
-        <v>2.5</v>
+        <v>4.33</v>
       </c>
       <c r="Q31">
+        <v>3.2</v>
+      </c>
+      <c r="R31">
+        <v>1.8</v>
+      </c>
+      <c r="S31">
+        <v>5.29</v>
+      </c>
+      <c r="T31">
+        <v>1.96</v>
+      </c>
+      <c r="U31">
+        <v>2.46</v>
+      </c>
+      <c r="V31">
+        <v>1.47</v>
+      </c>
+      <c r="W31">
+        <v>2.41</v>
+      </c>
+      <c r="X31">
+        <v>3.08</v>
+      </c>
+      <c r="Y31">
+        <v>1.27</v>
+      </c>
+      <c r="Z31">
+        <v>7.7</v>
+      </c>
+      <c r="AA31">
+        <v>1.02</v>
+      </c>
+      <c r="AB31">
+        <v>1.04</v>
+      </c>
+      <c r="AC31">
+        <v>1.35</v>
+      </c>
+      <c r="AD31">
+        <v>2.97</v>
+      </c>
+      <c r="AE31">
+        <v>2.2</v>
+      </c>
+      <c r="AF31">
+        <v>1.62</v>
+      </c>
+      <c r="AG31">
+        <v>4.1</v>
+      </c>
+      <c r="AH31">
+        <v>1.19</v>
+      </c>
+      <c r="AI31">
+        <v>7.3</v>
+      </c>
+      <c r="AJ31">
+        <v>1.03</v>
+      </c>
+      <c r="AK31">
+        <v>1.97</v>
+      </c>
+      <c r="AL31">
+        <v>1.73</v>
+      </c>
+      <c r="AM31">
+        <v>1.26</v>
+      </c>
+      <c r="AN31">
+        <v>1.14</v>
+      </c>
+      <c r="AO31">
+        <v>0</v>
+      </c>
+      <c r="AP31">
+        <v>1.28</v>
+      </c>
+      <c r="AQ31">
+        <v>1.61</v>
+      </c>
+      <c r="AR31">
+        <v>1.95</v>
+      </c>
+      <c r="AS31">
+        <v>2.52</v>
+      </c>
+      <c r="AT31">
         <v>3.55</v>
       </c>
-      <c r="R31">
-        <v>2.4</v>
-      </c>
-      <c r="S31">
-        <v>0</v>
-      </c>
-      <c r="T31">
-        <v>0</v>
-      </c>
-      <c r="U31">
-        <v>0</v>
-      </c>
-      <c r="V31">
-        <v>0</v>
-      </c>
-      <c r="W31">
-        <v>0</v>
-      </c>
-      <c r="X31">
-        <v>0</v>
-      </c>
-      <c r="Y31">
-        <v>0</v>
-      </c>
-      <c r="Z31">
-        <v>0</v>
-      </c>
-      <c r="AA31">
-        <v>0</v>
-      </c>
-      <c r="AB31">
-        <v>0</v>
-      </c>
-      <c r="AC31">
-        <v>0</v>
-      </c>
-      <c r="AD31">
-        <v>0</v>
-      </c>
-      <c r="AE31">
-        <v>1.66</v>
-      </c>
-      <c r="AF31">
-        <v>2.15</v>
-      </c>
-      <c r="AG31">
-        <v>0</v>
-      </c>
-      <c r="AH31">
-        <v>0</v>
-      </c>
-      <c r="AI31">
-        <v>0</v>
-      </c>
-      <c r="AJ31">
-        <v>0</v>
-      </c>
-      <c r="AK31">
-        <v>0</v>
-      </c>
-      <c r="AL31">
-        <v>0</v>
-      </c>
-      <c r="AM31">
-        <v>0</v>
-      </c>
-      <c r="AN31">
-        <v>0</v>
-      </c>
-      <c r="AO31">
-        <v>0</v>
-      </c>
-      <c r="AP31">
-        <v>0</v>
-      </c>
-      <c r="AQ31">
-        <v>0</v>
-      </c>
-      <c r="AR31">
-        <v>0</v>
-      </c>
-      <c r="AS31">
-        <v>0</v>
-      </c>
-      <c r="AT31">
-        <v>0</v>
-      </c>
       <c r="AU31">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV31">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AW31">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AX31">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AY31">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AZ31">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BA31">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BB31">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC31">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BD31">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE31">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF31">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG31">
         <v>0</v>
@@ -6690,7 +6690,7 @@
         <v>80</v>
       </c>
       <c r="C32" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D32" t="s">
         <v>105</v>
@@ -6729,133 +6729,133 @@
         <v>188</v>
       </c>
       <c r="P32">
-        <v>4.33</v>
+        <v>2</v>
       </c>
       <c r="Q32">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R32">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="S32">
-        <v>5.29</v>
+        <v>2.5</v>
       </c>
       <c r="T32">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="U32">
-        <v>2.46</v>
+        <v>4.4</v>
       </c>
       <c r="V32">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="W32">
-        <v>2.41</v>
+        <v>2.73</v>
       </c>
       <c r="X32">
+        <v>2.96</v>
+      </c>
+      <c r="Y32">
+        <v>1.36</v>
+      </c>
+      <c r="Z32">
+        <v>7</v>
+      </c>
+      <c r="AA32">
+        <v>1.04</v>
+      </c>
+      <c r="AB32">
+        <v>1.01</v>
+      </c>
+      <c r="AC32">
+        <v>1.3</v>
+      </c>
+      <c r="AD32">
         <v>3.08</v>
       </c>
-      <c r="Y32">
-        <v>1.27</v>
-      </c>
-      <c r="Z32">
-        <v>7.7</v>
-      </c>
-      <c r="AA32">
-        <v>1.02</v>
-      </c>
-      <c r="AB32">
-        <v>1.04</v>
-      </c>
-      <c r="AC32">
-        <v>1.35</v>
-      </c>
-      <c r="AD32">
-        <v>2.97</v>
-      </c>
       <c r="AE32">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AF32">
+        <v>1.78</v>
+      </c>
+      <c r="AG32">
+        <v>3.45</v>
+      </c>
+      <c r="AH32">
+        <v>1.28</v>
+      </c>
+      <c r="AI32">
+        <v>6.75</v>
+      </c>
+      <c r="AJ32">
+        <v>1.07</v>
+      </c>
+      <c r="AK32">
+        <v>1.79</v>
+      </c>
+      <c r="AL32">
+        <v>1.92</v>
+      </c>
+      <c r="AM32">
+        <v>1.28</v>
+      </c>
+      <c r="AN32">
+        <v>1.75</v>
+      </c>
+      <c r="AO32">
+        <v>0</v>
+      </c>
+      <c r="AP32">
+        <v>1.4</v>
+      </c>
+      <c r="AQ32">
+        <v>1.69</v>
+      </c>
+      <c r="AR32">
+        <v>2.19</v>
+      </c>
+      <c r="AS32">
+        <v>2.83</v>
+      </c>
+      <c r="AT32">
+        <v>4.2</v>
+      </c>
+      <c r="AU32">
+        <v>2.63</v>
+      </c>
+      <c r="AV32">
+        <v>1.98</v>
+      </c>
+      <c r="AW32">
+        <v>1.63</v>
+      </c>
+      <c r="AX32">
+        <v>1.38</v>
+      </c>
+      <c r="AY32">
+        <v>1.14</v>
+      </c>
+      <c r="AZ32">
+        <v>1.56</v>
+      </c>
+      <c r="BA32">
+        <v>3.34</v>
+      </c>
+      <c r="BB32">
+        <v>1.23</v>
+      </c>
+      <c r="BC32">
+        <v>2.15</v>
+      </c>
+      <c r="BD32">
+        <v>3.52</v>
+      </c>
+      <c r="BE32">
         <v>1.62</v>
       </c>
-      <c r="AG32">
-        <v>4.1</v>
-      </c>
-      <c r="AH32">
-        <v>1.19</v>
-      </c>
-      <c r="AI32">
-        <v>7.3</v>
-      </c>
-      <c r="AJ32">
-        <v>1.03</v>
-      </c>
-      <c r="AK32">
-        <v>1.97</v>
-      </c>
-      <c r="AL32">
-        <v>1.73</v>
-      </c>
-      <c r="AM32">
-        <v>1.26</v>
-      </c>
-      <c r="AN32">
-        <v>1.14</v>
-      </c>
-      <c r="AO32">
-        <v>0</v>
-      </c>
-      <c r="AP32">
-        <v>1.28</v>
-      </c>
-      <c r="AQ32">
-        <v>1.61</v>
-      </c>
-      <c r="AR32">
-        <v>1.95</v>
-      </c>
-      <c r="AS32">
-        <v>2.52</v>
-      </c>
-      <c r="AT32">
-        <v>3.55</v>
-      </c>
-      <c r="AU32">
-        <v>2.7</v>
-      </c>
-      <c r="AV32">
-        <v>2.21</v>
-      </c>
-      <c r="AW32">
-        <v>1.73</v>
-      </c>
-      <c r="AX32">
-        <v>1.4</v>
-      </c>
-      <c r="AY32">
-        <v>1.24</v>
-      </c>
-      <c r="AZ32">
-        <v>2.46</v>
-      </c>
-      <c r="BA32">
-        <v>1.82</v>
-      </c>
-      <c r="BB32">
-        <v>1.27</v>
-      </c>
-      <c r="BC32">
-        <v>2.55</v>
-      </c>
-      <c r="BD32">
-        <v>3.25</v>
-      </c>
-      <c r="BE32">
-        <v>1.44</v>
-      </c>
       <c r="BF32">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="BG32">
         <v>0</v>
@@ -6875,7 +6875,7 @@
         <v>80</v>
       </c>
       <c r="C33" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D33" t="s">
         <v>105</v>
@@ -6914,133 +6914,133 @@
         <v>188</v>
       </c>
       <c r="P33">
-        <v>1.95</v>
+        <v>5.48</v>
       </c>
       <c r="Q33">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="R33">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="S33">
-        <v>2.5</v>
+        <v>6.1</v>
       </c>
       <c r="T33">
-        <v>2.06</v>
+        <v>1.87</v>
       </c>
       <c r="U33">
-        <v>4.4</v>
+        <v>2.41</v>
       </c>
       <c r="V33">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="W33">
-        <v>2.73</v>
+        <v>2.24</v>
       </c>
       <c r="X33">
-        <v>2.96</v>
+        <v>3.5</v>
       </c>
       <c r="Y33">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="Z33">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA33">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AB33">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AC33">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="AD33">
-        <v>3.08</v>
+        <v>2.38</v>
       </c>
       <c r="AE33">
-        <v>2.02</v>
+        <v>2.52</v>
       </c>
       <c r="AF33">
-        <v>1.78</v>
+        <v>1.46</v>
       </c>
       <c r="AG33">
-        <v>3.6</v>
+        <v>5.25</v>
       </c>
       <c r="AH33">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="AI33">
-        <v>6.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AJ33">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AK33">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="AL33">
-        <v>1.92</v>
+        <v>1.54</v>
       </c>
       <c r="AM33">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AN33">
-        <v>1.75</v>
+        <v>1.14</v>
       </c>
       <c r="AO33">
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ33">
         <v>1.69</v>
       </c>
       <c r="AR33">
-        <v>2.19</v>
+        <v>2.55</v>
       </c>
       <c r="AS33">
-        <v>2.93</v>
+        <v>2.75</v>
       </c>
       <c r="AT33">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AU33">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AV33">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AW33">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="AX33">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AY33">
         <v>1.23</v>
       </c>
       <c r="AZ33">
-        <v>1.56</v>
+        <v>2.39</v>
       </c>
       <c r="BA33">
-        <v>3.34</v>
+        <v>1.87</v>
       </c>
       <c r="BB33">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="BC33">
-        <v>2.2</v>
+        <v>2.59</v>
       </c>
       <c r="BD33">
-        <v>3.52</v>
+        <v>2.91</v>
       </c>
       <c r="BE33">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="BF33">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="BG33">
         <v>0</v>
@@ -7060,7 +7060,7 @@
         <v>80</v>
       </c>
       <c r="C34" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D34" t="s">
         <v>105</v>
@@ -7248,7 +7248,7 @@
         <v>99</v>
       </c>
       <c r="D35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E35" t="s">
         <v>140</v>
@@ -7284,133 +7284,133 @@
         <v>188</v>
       </c>
       <c r="P35">
-        <v>5.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q35">
-        <v>3.12</v>
+        <v>3.55</v>
       </c>
       <c r="R35">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="S35">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="T35">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U35">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="V35">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W35">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="X35">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y35">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z35">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA35">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB35">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC35">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD35">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AE35">
-        <v>2.52</v>
+        <v>1.66</v>
       </c>
       <c r="AF35">
-        <v>1.46</v>
+        <v>2.15</v>
       </c>
       <c r="AG35">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AH35">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AI35">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AJ35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK35">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL35">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AM35">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN35">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AO35">
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AQ35">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AR35">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AS35">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AT35">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AU35">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AV35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW35">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AX35">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AY35">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ35">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="BA35">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="BB35">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC35">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="BD35">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="BE35">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BF35">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BG35">
         <v>0</v>
@@ -7469,133 +7469,133 @@
         <v>188</v>
       </c>
       <c r="P36">
-        <v>5.6</v>
+        <v>3.3</v>
       </c>
       <c r="Q36">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="R36">
-        <v>1.52</v>
+        <v>2.15</v>
       </c>
       <c r="S36">
-        <v>8.050000000000001</v>
+        <v>4.43</v>
       </c>
       <c r="T36">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="U36">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="V36">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W36">
-        <v>2.44</v>
+        <v>2.31</v>
       </c>
       <c r="X36">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="Y36">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z36">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="AA36">
         <v>1</v>
       </c>
       <c r="AB36">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AC36">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AD36">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="AE36">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
       <c r="AF36">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="AG36">
-        <v>4.65</v>
+        <v>5.1</v>
       </c>
       <c r="AH36">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AI36">
-        <v>8.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="AJ36">
         <v>1</v>
       </c>
       <c r="AK36">
-        <v>2.4</v>
+        <v>2.04</v>
       </c>
       <c r="AL36">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AM36">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AN36">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="AO36">
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AQ36">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AR36">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="AS36">
-        <v>2.65</v>
+        <v>2.97</v>
       </c>
       <c r="AT36">
-        <v>4.41</v>
+        <v>4.15</v>
       </c>
       <c r="AU36">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AV36">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AW36">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AX36">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AY36">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AZ36">
-        <v>3.85</v>
+        <v>2.12</v>
       </c>
       <c r="BA36">
-        <v>1.43</v>
+        <v>2.08</v>
       </c>
       <c r="BB36">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BC36">
         <v>2.59</v>
       </c>
       <c r="BD36">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="BE36">
         <v>1.41</v>
       </c>
       <c r="BF36">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="BG36">
         <v>0</v>
@@ -7654,133 +7654,133 @@
         <v>188</v>
       </c>
       <c r="P37">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="Q37">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="R37">
-        <v>2.15</v>
+        <v>3.95</v>
       </c>
       <c r="S37">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="T37">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="U37">
-        <v>2.95</v>
+        <v>5.1</v>
       </c>
       <c r="V37">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="W37">
-        <v>2.31</v>
+        <v>2.11</v>
       </c>
       <c r="X37">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="Y37">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="Z37">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AA37">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AB37">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AC37">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="AD37">
-        <v>2.46</v>
+        <v>2.25</v>
       </c>
       <c r="AE37">
-        <v>2.65</v>
+        <v>2.74</v>
       </c>
       <c r="AF37">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="AG37">
-        <v>5.1</v>
+        <v>6.33</v>
       </c>
       <c r="AH37">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AI37">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AJ37">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AK37">
-        <v>2.05</v>
+        <v>2.32</v>
       </c>
       <c r="AL37">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AM37">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AN37">
-        <v>1.24</v>
+        <v>1.63</v>
       </c>
       <c r="AO37">
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AQ37">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AR37">
-        <v>2.19</v>
+        <v>2.7</v>
       </c>
       <c r="AS37">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AT37">
-        <v>4.15</v>
+        <v>4.34</v>
       </c>
       <c r="AU37">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="AV37">
         <v>1.95</v>
       </c>
       <c r="AW37">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AX37">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AY37">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AZ37">
-        <v>2.12</v>
+        <v>1.52</v>
       </c>
       <c r="BA37">
-        <v>2.08</v>
+        <v>3.26</v>
       </c>
       <c r="BB37">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="BC37">
-        <v>2.59</v>
+        <v>2.9</v>
       </c>
       <c r="BD37">
-        <v>2.9</v>
+        <v>2.66</v>
       </c>
       <c r="BE37">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="BF37">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="BG37">
         <v>0</v>
@@ -7839,79 +7839,79 @@
         <v>188</v>
       </c>
       <c r="P38">
-        <v>2</v>
+        <v>5.75</v>
       </c>
       <c r="Q38">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="R38">
-        <v>3.8</v>
+        <v>1.52</v>
       </c>
       <c r="S38">
-        <v>2.88</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="T38">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="U38">
-        <v>5.1</v>
+        <v>2.1</v>
       </c>
       <c r="V38">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="W38">
-        <v>2.11</v>
+        <v>2.44</v>
       </c>
       <c r="X38">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="Y38">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="Z38">
-        <v>13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA38">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AB38">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AC38">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="AD38">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="AE38">
-        <v>2.74</v>
+        <v>2.53</v>
       </c>
       <c r="AF38">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="AG38">
-        <v>6.33</v>
+        <v>4.65</v>
       </c>
       <c r="AH38">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AI38">
-        <v>9.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AJ38">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AK38">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AL38">
         <v>1.53</v>
       </c>
       <c r="AM38">
-        <v>1.35</v>
+        <v>2.31</v>
       </c>
       <c r="AN38">
-        <v>1.63</v>
+        <v>1.04</v>
       </c>
       <c r="AO38">
         <v>0</v>
@@ -7920,52 +7920,52 @@
         <v>1.42</v>
       </c>
       <c r="AQ38">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AR38">
+        <v>2.73</v>
+      </c>
+      <c r="AS38">
+        <v>3.04</v>
+      </c>
+      <c r="AT38">
+        <v>4.41</v>
+      </c>
+      <c r="AU38">
         <v>2.7</v>
       </c>
-      <c r="AS38">
-        <v>3</v>
-      </c>
-      <c r="AT38">
-        <v>4.34</v>
-      </c>
-      <c r="AU38">
-        <v>2.58</v>
-      </c>
       <c r="AV38">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AW38">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AX38">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AY38">
         <v>1.13</v>
       </c>
       <c r="AZ38">
-        <v>1.52</v>
+        <v>3.85</v>
       </c>
       <c r="BA38">
-        <v>3.26</v>
+        <v>1.43</v>
       </c>
       <c r="BB38">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="BC38">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="BD38">
-        <v>2.66</v>
+        <v>2.91</v>
       </c>
       <c r="BE38">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="BF38">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BG38">
         <v>0</v>
@@ -8024,7 +8024,7 @@
         <v>188</v>
       </c>
       <c r="P39">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="Q39">
         <v>2.8</v>
@@ -8042,16 +8042,16 @@
         <v>4.2</v>
       </c>
       <c r="V39">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W39">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="X39">
         <v>4.1</v>
       </c>
       <c r="Y39">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z39">
         <v>9.300000000000001</v>
@@ -8072,13 +8072,13 @@
         <v>3.1</v>
       </c>
       <c r="AF39">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AG39">
         <v>6.35</v>
       </c>
       <c r="AH39">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AI39">
         <v>10.5</v>
@@ -8087,7 +8087,7 @@
         <v>1.02</v>
       </c>
       <c r="AK39">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AL39">
         <v>1.54</v>
@@ -8117,7 +8117,7 @@
         <v>4.36</v>
       </c>
       <c r="AU39">
-        <v>2.3</v>
+        <v>2.57</v>
       </c>
       <c r="AV39">
         <v>1.94</v>
@@ -8132,10 +8132,10 @@
         <v>1.13</v>
       </c>
       <c r="AZ39">
-        <v>1.93</v>
+        <v>1.61</v>
       </c>
       <c r="BA39">
-        <v>2.31</v>
+        <v>2.96</v>
       </c>
       <c r="BB39">
         <v>1.43</v>
@@ -8209,10 +8209,10 @@
         <v>188</v>
       </c>
       <c r="P40">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="Q40">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="R40">
         <v>1.25</v>
@@ -8248,7 +8248,7 @@
         <v>1.01</v>
       </c>
       <c r="AC40">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AD40">
         <v>6.15</v>
@@ -8329,7 +8329,7 @@
         <v>1.52</v>
       </c>
       <c r="BD40">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BE40">
         <v>2.29</v>
@@ -8400,10 +8400,10 @@
         <v>4</v>
       </c>
       <c r="R41">
-        <v>5.21</v>
+        <v>5.25</v>
       </c>
       <c r="S41">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="T41">
         <v>2.2</v>
@@ -8412,25 +8412,25 @@
         <v>5.25</v>
       </c>
       <c r="V41">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W41">
-        <v>3.13</v>
+        <v>2.85</v>
       </c>
       <c r="X41">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="Y41">
         <v>1.43</v>
       </c>
       <c r="Z41">
-        <v>6.25</v>
+        <v>7.2</v>
       </c>
       <c r="AA41">
         <v>1.07</v>
       </c>
       <c r="AB41">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AC41">
         <v>1.3</v>
@@ -8451,10 +8451,10 @@
         <v>1.3</v>
       </c>
       <c r="AI41">
-        <v>7.5</v>
+        <v>6.25</v>
       </c>
       <c r="AJ41">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AK41">
         <v>1.85</v>
@@ -8472,37 +8472,37 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AQ41">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AR41">
         <v>1.68</v>
       </c>
       <c r="AS41">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AT41">
         <v>2.63</v>
       </c>
       <c r="AU41">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AV41">
         <v>2.63</v>
       </c>
       <c r="AW41">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AX41">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AY41">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AZ41">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="BA41">
         <v>4.6</v>
@@ -8511,13 +8511,13 @@
         <v>1.22</v>
       </c>
       <c r="BC41">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="BD41">
         <v>4.05</v>
       </c>
       <c r="BE41">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="BF41">
         <v>1.18</v>

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -343,24 +343,24 @@
     <t>Bucheon 1995</t>
   </si>
   <si>
+    <t>Daejeon Citizen</t>
+  </si>
+  <si>
     <t>Sangju Sangmu</t>
   </si>
   <si>
     <t>Gangwon</t>
   </si>
   <si>
-    <t>Daejeon Citizen</t>
-  </si>
-  <si>
     <t>Madura United</t>
   </si>
   <si>
+    <t>Ethiopia Nigd Bank</t>
+  </si>
+  <si>
     <t>FC Seoul</t>
   </si>
   <si>
-    <t>Ethiopia Nigd Bank</t>
-  </si>
-  <si>
     <t>Qingdao Youth Island</t>
   </si>
   <si>
@@ -373,18 +373,18 @@
     <t>Shenyang Urban</t>
   </si>
   <si>
+    <t>Borneo</t>
+  </si>
+  <si>
+    <t>Karvan FK</t>
+  </si>
+  <si>
     <t>Dire Dawa Kenema</t>
   </si>
   <si>
     <t>Chongqing Tongliang Long</t>
   </si>
   <si>
-    <t>Karvan FK</t>
-  </si>
-  <si>
-    <t>Borneo</t>
-  </si>
-  <si>
     <t>Mekelle Kenema</t>
   </si>
   <si>
@@ -415,42 +415,42 @@
     <t>Maccabi Tel Aviv</t>
   </si>
   <si>
+    <t>Al Ittihad Kalba</t>
+  </si>
+  <si>
     <t>Dibba Al Fujairah</t>
   </si>
   <si>
-    <t>Al Ittihad Kalba</t>
-  </si>
-  <si>
     <t>Bani Yas</t>
   </si>
   <si>
+    <t>Smouha SC</t>
+  </si>
+  <si>
+    <t>Falkenberg</t>
+  </si>
+  <si>
+    <t>Lokomotiv Sofia 1929</t>
+  </si>
+  <si>
     <t>Ceramica Cleopatra</t>
   </si>
   <si>
-    <t>Lokomotiv Sofia 1929</t>
-  </si>
-  <si>
-    <t>Smouha SC</t>
-  </si>
-  <si>
     <t>Al Ahly</t>
   </si>
   <si>
-    <t>Falkenberg</t>
-  </si>
-  <si>
     <t>Chippa United</t>
   </si>
   <si>
+    <t>Siwelele</t>
+  </si>
+  <si>
     <t>Magesi</t>
   </si>
   <si>
     <t>Stellenbosch</t>
   </si>
   <si>
-    <t>Siwelele</t>
-  </si>
-  <si>
     <t>Al Khaleej</t>
   </si>
   <si>
@@ -466,24 +466,24 @@
     <t>Jeju United</t>
   </si>
   <si>
+    <t>Incheon United</t>
+  </si>
+  <si>
     <t>Ulsan</t>
   </si>
   <si>
     <t>Pohang Steelers</t>
   </si>
   <si>
-    <t>Incheon United</t>
-  </si>
-  <si>
     <t>Bali United</t>
   </si>
   <si>
+    <t>Kedus Giorgis</t>
+  </si>
+  <si>
     <t>Anyang</t>
   </si>
   <si>
-    <t>Kedus Giorgis</t>
-  </si>
-  <si>
     <t>Tianjin Teda</t>
   </si>
   <si>
@@ -496,18 +496,18 @@
     <t>Chengdu Better City FC</t>
   </si>
   <si>
+    <t>Persita</t>
+  </si>
+  <si>
+    <t>Neftçi</t>
+  </si>
+  <si>
     <t>Ethiopia Bunna</t>
   </si>
   <si>
     <t>Henan Jianye</t>
   </si>
   <si>
-    <t>Neftçi</t>
-  </si>
-  <si>
-    <t>Persita</t>
-  </si>
-  <si>
     <t>Arba Minch Kenema</t>
   </si>
   <si>
@@ -544,31 +544,31 @@
     <t>Al Dhafra</t>
   </si>
   <si>
+    <t>Zamalek</t>
+  </si>
+  <si>
+    <t>Norrköping</t>
+  </si>
+  <si>
+    <t>Botev Vratsa</t>
+  </si>
+  <si>
     <t>Pyramids FC</t>
   </si>
   <si>
-    <t>Botev Vratsa</t>
-  </si>
-  <si>
-    <t>Zamalek</t>
-  </si>
-  <si>
     <t>ENPPI</t>
   </si>
   <si>
-    <t>Norrköping</t>
-  </si>
-  <si>
     <t>Sekhukhune United</t>
   </si>
   <si>
+    <t>Durban City</t>
+  </si>
+  <si>
     <t>Orbit College</t>
   </si>
   <si>
     <t>Orlando Pirates</t>
-  </si>
-  <si>
-    <t>Durban City</t>
   </si>
   <si>
     <t>Al Hilal</t>
@@ -1194,22 +1194,22 @@
         <v>2.3</v>
       </c>
       <c r="U2">
-        <v>5.99</v>
+        <v>8.15</v>
       </c>
       <c r="V2">
         <v>1.37</v>
       </c>
       <c r="W2">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="X2">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="Y2">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z2">
-        <v>6.85</v>
+        <v>6.9</v>
       </c>
       <c r="AA2">
         <v>1.04</v>
@@ -1227,7 +1227,7 @@
         <v>1.96</v>
       </c>
       <c r="AF2">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AG2">
         <v>3.18</v>
@@ -1239,7 +1239,7 @@
         <v>6.5</v>
       </c>
       <c r="AJ2">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AK2">
         <v>2.26</v>
@@ -1257,16 +1257,16 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AQ2">
         <v>1.9</v>
       </c>
       <c r="AR2">
-        <v>2.42</v>
+        <v>3.1</v>
       </c>
       <c r="AS2">
-        <v>2.7</v>
+        <v>3.44</v>
       </c>
       <c r="AT2">
         <v>5.16</v>
@@ -1275,13 +1275,13 @@
         <v>2.7</v>
       </c>
       <c r="AV2">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AW2">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="AX2">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
       <c r="AY2">
         <v>1.08</v>
@@ -1364,10 +1364,10 @@
         <v>188</v>
       </c>
       <c r="P3">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="Q3">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R3">
         <v>2.8</v>
@@ -1549,37 +1549,37 @@
         <v>188</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="S4">
-        <v>3.24</v>
+        <v>2.87</v>
       </c>
       <c r="T4">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="U4">
-        <v>3.24</v>
+        <v>4.06</v>
       </c>
       <c r="V4">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W4">
-        <v>2.77</v>
+        <v>2.59</v>
       </c>
       <c r="X4">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="Y4">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z4">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="AA4">
         <v>1.03</v>
@@ -1588,94 +1588,94 @@
         <v>1.02</v>
       </c>
       <c r="AC4">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AD4">
-        <v>3.35</v>
+        <v>3.19</v>
       </c>
       <c r="AE4">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="AF4">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AG4">
-        <v>3.48</v>
+        <v>3.54</v>
       </c>
       <c r="AH4">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AI4">
-        <v>6.73</v>
+        <v>7.5</v>
       </c>
       <c r="AJ4">
         <v>1.04</v>
       </c>
       <c r="AK4">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AL4">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AM4">
+        <v>1.35</v>
+      </c>
+      <c r="AN4">
+        <v>1.62</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>1.51</v>
+      </c>
+      <c r="AQ4">
+        <v>1.9</v>
+      </c>
+      <c r="AR4">
+        <v>2.46</v>
+      </c>
+      <c r="AS4">
+        <v>3.42</v>
+      </c>
+      <c r="AT4">
+        <v>5.11</v>
+      </c>
+      <c r="AU4">
+        <v>2.34</v>
+      </c>
+      <c r="AV4">
+        <v>1.81</v>
+      </c>
+      <c r="AW4">
         <v>1.46</v>
       </c>
-      <c r="AN4">
-        <v>1.44</v>
-      </c>
-      <c r="AO4">
-        <v>0</v>
-      </c>
-      <c r="AP4">
-        <v>1.39</v>
-      </c>
-      <c r="AQ4">
+      <c r="AX4">
+        <v>1.23</v>
+      </c>
+      <c r="AY4">
+        <v>1.11</v>
+      </c>
+      <c r="AZ4">
         <v>1.72</v>
       </c>
-      <c r="AR4">
-        <v>2.18</v>
-      </c>
-      <c r="AS4">
-        <v>2.9</v>
-      </c>
-      <c r="AT4">
-        <v>4.16</v>
-      </c>
-      <c r="AU4">
-        <v>2.78</v>
-      </c>
-      <c r="AV4">
-        <v>2.04</v>
-      </c>
-      <c r="AW4">
-        <v>1.6</v>
-      </c>
-      <c r="AX4">
-        <v>1.32</v>
-      </c>
-      <c r="AY4">
-        <v>1.15</v>
-      </c>
-      <c r="AZ4">
-        <v>1.81</v>
-      </c>
       <c r="BA4">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="BB4">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="BC4">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="BD4">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="BE4">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="BF4">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BG4">
         <v>0</v>
@@ -1734,133 +1734,133 @@
         <v>188</v>
       </c>
       <c r="P5">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R5">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S5">
+        <v>3.24</v>
+      </c>
+      <c r="T5">
+        <v>2.05</v>
+      </c>
+      <c r="U5">
+        <v>3.24</v>
+      </c>
+      <c r="V5">
+        <v>1.39</v>
+      </c>
+      <c r="W5">
         <v>2.77</v>
       </c>
-      <c r="T5">
+      <c r="X5">
+        <v>3</v>
+      </c>
+      <c r="Y5">
+        <v>1.36</v>
+      </c>
+      <c r="Z5">
+        <v>7.5</v>
+      </c>
+      <c r="AA5">
+        <v>1.03</v>
+      </c>
+      <c r="AB5">
+        <v>1.02</v>
+      </c>
+      <c r="AC5">
+        <v>1.32</v>
+      </c>
+      <c r="AD5">
+        <v>3.18</v>
+      </c>
+      <c r="AE5">
+        <v>1.99</v>
+      </c>
+      <c r="AF5">
+        <v>1.8</v>
+      </c>
+      <c r="AG5">
+        <v>3.48</v>
+      </c>
+      <c r="AH5">
+        <v>1.3</v>
+      </c>
+      <c r="AI5">
+        <v>6.73</v>
+      </c>
+      <c r="AJ5">
+        <v>1.07</v>
+      </c>
+      <c r="AK5">
+        <v>1.73</v>
+      </c>
+      <c r="AL5">
         <v>2</v>
       </c>
-      <c r="U5">
-        <v>4.76</v>
-      </c>
-      <c r="V5">
-        <v>1.43</v>
-      </c>
-      <c r="W5">
-        <v>2.34</v>
-      </c>
-      <c r="X5">
-        <v>3.4</v>
-      </c>
-      <c r="Y5">
-        <v>1.27</v>
-      </c>
-      <c r="Z5">
-        <v>9.5</v>
-      </c>
-      <c r="AA5">
-        <v>1.01</v>
-      </c>
-      <c r="AB5">
-        <v>1.05</v>
-      </c>
-      <c r="AC5">
-        <v>1.42</v>
-      </c>
-      <c r="AD5">
-        <v>2.7</v>
-      </c>
-      <c r="AE5">
-        <v>2.38</v>
-      </c>
-      <c r="AF5">
-        <v>1.55</v>
-      </c>
-      <c r="AG5">
-        <v>4.5</v>
-      </c>
-      <c r="AH5">
+      <c r="AM5">
+        <v>1.46</v>
+      </c>
+      <c r="AN5">
+        <v>1.44</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>1.39</v>
+      </c>
+      <c r="AQ5">
+        <v>1.72</v>
+      </c>
+      <c r="AR5">
+        <v>2.18</v>
+      </c>
+      <c r="AS5">
+        <v>2.9</v>
+      </c>
+      <c r="AT5">
+        <v>4.16</v>
+      </c>
+      <c r="AU5">
+        <v>2.8</v>
+      </c>
+      <c r="AV5">
+        <v>2.1</v>
+      </c>
+      <c r="AW5">
+        <v>1.6</v>
+      </c>
+      <c r="AX5">
+        <v>1.32</v>
+      </c>
+      <c r="AY5">
         <v>1.15</v>
       </c>
-      <c r="AI5">
-        <v>9</v>
-      </c>
-      <c r="AJ5">
-        <v>1.01</v>
-      </c>
-      <c r="AK5">
-        <v>1.94</v>
-      </c>
-      <c r="AL5">
-        <v>1.68</v>
-      </c>
-      <c r="AM5">
-        <v>1.33</v>
-      </c>
-      <c r="AN5">
-        <v>1.71</v>
-      </c>
-      <c r="AO5">
-        <v>0</v>
-      </c>
-      <c r="AP5">
-        <v>1.53</v>
-      </c>
-      <c r="AQ5">
-        <v>1.92</v>
-      </c>
-      <c r="AR5">
-        <v>2.39</v>
-      </c>
-      <c r="AS5">
-        <v>3.48</v>
-      </c>
-      <c r="AT5">
-        <v>5.23</v>
-      </c>
-      <c r="AU5">
-        <v>2.31</v>
-      </c>
-      <c r="AV5">
-        <v>1.79</v>
-      </c>
-      <c r="AW5">
-        <v>1.45</v>
-      </c>
-      <c r="AX5">
+      <c r="AZ5">
+        <v>1.81</v>
+      </c>
+      <c r="BA5">
+        <v>2.17</v>
+      </c>
+      <c r="BB5">
         <v>1.22</v>
       </c>
-      <c r="AY5">
-        <v>1.08</v>
-      </c>
-      <c r="AZ5">
-        <v>1.65</v>
-      </c>
-      <c r="BA5">
-        <v>3.1</v>
-      </c>
-      <c r="BB5">
-        <v>1.33</v>
-      </c>
       <c r="BC5">
-        <v>2.53</v>
+        <v>2.18</v>
       </c>
       <c r="BD5">
-        <v>3.04</v>
+        <v>3.66</v>
       </c>
       <c r="BE5">
-        <v>1.46</v>
+        <v>1.66</v>
       </c>
       <c r="BF5">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="BG5">
         <v>0</v>
@@ -1919,133 +1919,133 @@
         <v>188</v>
       </c>
       <c r="P6">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="Q6">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R6">
-        <v>3.19</v>
+        <v>3.4</v>
       </c>
       <c r="S6">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="T6">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="U6">
-        <v>4.06</v>
+        <v>4.76</v>
       </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W6">
-        <v>2.59</v>
+        <v>2.34</v>
       </c>
       <c r="X6">
+        <v>3.4</v>
+      </c>
+      <c r="Y6">
+        <v>1.27</v>
+      </c>
+      <c r="Z6">
+        <v>8.5</v>
+      </c>
+      <c r="AA6">
+        <v>1.01</v>
+      </c>
+      <c r="AB6">
+        <v>1.09</v>
+      </c>
+      <c r="AC6">
+        <v>1.42</v>
+      </c>
+      <c r="AD6">
+        <v>2.7</v>
+      </c>
+      <c r="AE6">
+        <v>2.38</v>
+      </c>
+      <c r="AF6">
+        <v>1.55</v>
+      </c>
+      <c r="AG6">
+        <v>4.5</v>
+      </c>
+      <c r="AH6">
+        <v>1.15</v>
+      </c>
+      <c r="AI6">
+        <v>9</v>
+      </c>
+      <c r="AJ6">
+        <v>1.01</v>
+      </c>
+      <c r="AK6">
+        <v>1.94</v>
+      </c>
+      <c r="AL6">
+        <v>1.68</v>
+      </c>
+      <c r="AM6">
+        <v>1.33</v>
+      </c>
+      <c r="AN6">
+        <v>1.71</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>1.53</v>
+      </c>
+      <c r="AQ6">
+        <v>1.92</v>
+      </c>
+      <c r="AR6">
+        <v>2.39</v>
+      </c>
+      <c r="AS6">
+        <v>3.48</v>
+      </c>
+      <c r="AT6">
+        <v>5.23</v>
+      </c>
+      <c r="AU6">
+        <v>2.31</v>
+      </c>
+      <c r="AV6">
+        <v>1.79</v>
+      </c>
+      <c r="AW6">
+        <v>1.45</v>
+      </c>
+      <c r="AX6">
+        <v>1.22</v>
+      </c>
+      <c r="AY6">
+        <v>1.08</v>
+      </c>
+      <c r="AZ6">
+        <v>1.65</v>
+      </c>
+      <c r="BA6">
+        <v>3.1</v>
+      </c>
+      <c r="BB6">
+        <v>1.33</v>
+      </c>
+      <c r="BC6">
+        <v>2.53</v>
+      </c>
+      <c r="BD6">
         <v>3.04</v>
       </c>
-      <c r="Y6">
-        <v>1.33</v>
-      </c>
-      <c r="Z6">
-        <v>7.6</v>
-      </c>
-      <c r="AA6">
-        <v>1.03</v>
-      </c>
-      <c r="AB6">
-        <v>1.02</v>
-      </c>
-      <c r="AC6">
-        <v>1.31</v>
-      </c>
-      <c r="AD6">
-        <v>2.94</v>
-      </c>
-      <c r="AE6">
-        <v>2.04</v>
-      </c>
-      <c r="AF6">
-        <v>1.72</v>
-      </c>
-      <c r="AG6">
-        <v>3.54</v>
-      </c>
-      <c r="AH6">
-        <v>1.22</v>
-      </c>
-      <c r="AI6">
-        <v>7.5</v>
-      </c>
-      <c r="AJ6">
-        <v>1.04</v>
-      </c>
-      <c r="AK6">
-        <v>1.78</v>
-      </c>
-      <c r="AL6">
-        <v>1.88</v>
-      </c>
-      <c r="AM6">
-        <v>1.35</v>
-      </c>
-      <c r="AN6">
-        <v>1.62</v>
-      </c>
-      <c r="AO6">
-        <v>0</v>
-      </c>
-      <c r="AP6">
-        <v>1.51</v>
-      </c>
-      <c r="AQ6">
-        <v>1.9</v>
-      </c>
-      <c r="AR6">
-        <v>2.46</v>
-      </c>
-      <c r="AS6">
-        <v>3.42</v>
-      </c>
-      <c r="AT6">
-        <v>5.11</v>
-      </c>
-      <c r="AU6">
-        <v>2.34</v>
-      </c>
-      <c r="AV6">
-        <v>1.81</v>
-      </c>
-      <c r="AW6">
+      <c r="BE6">
         <v>1.46</v>
       </c>
-      <c r="AX6">
-        <v>1.23</v>
-      </c>
-      <c r="AY6">
-        <v>1.11</v>
-      </c>
-      <c r="AZ6">
-        <v>1.72</v>
-      </c>
-      <c r="BA6">
-        <v>2.3</v>
-      </c>
-      <c r="BB6">
-        <v>1.24</v>
-      </c>
-      <c r="BC6">
-        <v>2.3</v>
-      </c>
-      <c r="BD6">
-        <v>3.3</v>
-      </c>
-      <c r="BE6">
-        <v>1.57</v>
-      </c>
       <c r="BF6">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="BG6">
         <v>0</v>
@@ -2250,10 +2250,10 @@
         <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E8" t="s">
         <v>113</v>
@@ -2289,133 +2289,133 @@
         <v>188</v>
       </c>
       <c r="P8">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R8">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="X8">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Y8">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA8">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC8">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD8">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AE8">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AH8">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK8">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AL8">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN8">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AO8">
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ8">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AR8">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AS8">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AT8">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AU8">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AV8">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AW8">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AX8">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AY8">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AZ8">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="BA8">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="BB8">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC8">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD8">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE8">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF8">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG8">
         <v>0</v>
@@ -2435,10 +2435,10 @@
         <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E9" t="s">
         <v>114</v>
@@ -2474,133 +2474,133 @@
         <v>188</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AO9">
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AU9">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AV9">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AX9">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ9">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BA9">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD9">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE9">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG9">
         <v>0</v>
@@ -2695,7 +2695,7 @@
         <v>1.04</v>
       </c>
       <c r="AB10">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC10">
         <v>1.29</v>
@@ -2710,10 +2710,10 @@
         <v>1.79</v>
       </c>
       <c r="AG10">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AH10">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AI10">
         <v>6.68</v>
@@ -2737,34 +2737,34 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AQ10">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AR10">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="AS10">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="AT10">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="AU10">
-        <v>3.64</v>
+        <v>3.57</v>
       </c>
       <c r="AV10">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="AW10">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AX10">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AY10">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AZ10">
         <v>1.55</v>
@@ -3053,10 +3053,10 @@
         <v>3.6</v>
       </c>
       <c r="X12">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Y12">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="Z12">
         <v>4.45</v>
@@ -3086,7 +3086,7 @@
         <v>1.76</v>
       </c>
       <c r="AI12">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="AJ12">
         <v>1.25</v>
@@ -3098,34 +3098,34 @@
         <v>2.75</v>
       </c>
       <c r="AM12">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AN12">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AO12">
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AQ12">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AR12">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AS12">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AT12">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AU12">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="AV12">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="AW12">
         <v>2.46</v>
@@ -3134,7 +3134,7 @@
         <v>1.92</v>
       </c>
       <c r="AY12">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AZ12">
         <v>1.92</v>
@@ -3223,70 +3223,70 @@
         <v>0</v>
       </c>
       <c r="S13">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="T13">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="U13">
-        <v>2.17</v>
+        <v>2.01</v>
       </c>
       <c r="V13">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W13">
-        <v>2.99</v>
+        <v>3.16</v>
       </c>
       <c r="X13">
-        <v>2.59</v>
+        <v>2.47</v>
       </c>
       <c r="Y13">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="Z13">
-        <v>6.15</v>
+        <v>5.7</v>
       </c>
       <c r="AA13">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AB13">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AC13">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AD13">
-        <v>3.77</v>
+        <v>3.88</v>
       </c>
       <c r="AE13">
         <v>1.74</v>
       </c>
       <c r="AF13">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="AG13">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AH13">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AI13">
         <v>5.2</v>
       </c>
       <c r="AJ13">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AK13">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AL13">
         <v>1.9</v>
       </c>
       <c r="AM13">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AN13">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AO13">
         <v>0</v>
@@ -3295,7 +3295,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ13">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AR13">
         <v>1.94</v>
@@ -3310,7 +3310,7 @@
         <v>3.72</v>
       </c>
       <c r="AV13">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="AW13">
         <v>1.98</v>
@@ -3328,19 +3328,19 @@
         <v>1.4</v>
       </c>
       <c r="BB13">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="BC13">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
       <c r="BD13">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BE13">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="BF13">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="BG13">
         <v>0</v>
@@ -3360,7 +3360,7 @@
         <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D14" t="s">
         <v>105</v>
@@ -3399,133 +3399,133 @@
         <v>188</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>6.08</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AO14">
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AU14">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AV14">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AW14">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX14">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY14">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ14">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BA14">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BB14">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC14">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BD14">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="BE14">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BF14">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG14">
         <v>0</v>
@@ -3545,10 +3545,10 @@
         <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E15" t="s">
         <v>120</v>
@@ -3593,124 +3593,124 @@
         <v>0</v>
       </c>
       <c r="S15">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="V15">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W15">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="X15">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Y15">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z15">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA15">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC15">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="AD15">
-        <v>2.92</v>
+        <v>4.8</v>
       </c>
       <c r="AE15">
+        <v>1.45</v>
+      </c>
+      <c r="AF15">
+        <v>2.43</v>
+      </c>
+      <c r="AG15">
         <v>2.14</v>
       </c>
-      <c r="AF15">
-        <v>1.72</v>
-      </c>
-      <c r="AG15">
-        <v>3.73</v>
-      </c>
       <c r="AH15">
-        <v>1.21</v>
+        <v>1.58</v>
       </c>
       <c r="AI15">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="AJ15">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="AK15">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL15">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AM15">
-        <v>1.44</v>
+        <v>1.11</v>
       </c>
       <c r="AN15">
-        <v>1.44</v>
+        <v>1.05</v>
       </c>
       <c r="AO15">
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AQ15">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AR15">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AS15">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AT15">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AU15">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="AV15">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AW15">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AX15">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AY15">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AZ15">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="BA15">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BB15">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC15">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD15">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="BE15">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF15">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG15">
         <v>0</v>
@@ -3730,7 +3730,7 @@
         <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D16" t="s">
         <v>105</v>
@@ -3808,28 +3808,28 @@
         <v>0</v>
       </c>
       <c r="AC16">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AD16">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AE16">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH16">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI16">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AJ16">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK16">
         <v>0</v>
@@ -3838,10 +3838,10 @@
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN16">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AO16">
         <v>0</v>
@@ -3915,10 +3915,10 @@
         <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E17" t="s">
         <v>122</v>
@@ -3954,133 +3954,133 @@
         <v>188</v>
       </c>
       <c r="P17">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R17">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>6.08</v>
+        <v>0</v>
       </c>
       <c r="V17">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="W17">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="X17">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Y17">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z17">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="AA17">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC17">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AD17">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AE17">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AG17">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AH17">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AI17">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AJ17">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK17">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL17">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AM17">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AN17">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AO17">
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ17">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR17">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AS17">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT17">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AU17">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AV17">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AW17">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AX17">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AY17">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ17">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="BA17">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BB17">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC17">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="BD17">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="BE17">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="BF17">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG17">
         <v>0</v>
@@ -5959,7 +5959,7 @@
         <v>133</v>
       </c>
       <c r="F28" t="s">
-        <v>174</v>
+        <v>145</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -6144,7 +6144,7 @@
         <v>134</v>
       </c>
       <c r="F29" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -6544,76 +6544,76 @@
         <v>188</v>
       </c>
       <c r="P31">
-        <v>4.33</v>
+        <v>5.48</v>
       </c>
       <c r="Q31">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="R31">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="S31">
-        <v>5.29</v>
+        <v>6.1</v>
       </c>
       <c r="T31">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="U31">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="V31">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="W31">
-        <v>2.41</v>
+        <v>2.24</v>
       </c>
       <c r="X31">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="Y31">
+        <v>1.22</v>
+      </c>
+      <c r="Z31">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AA31">
+        <v>1.03</v>
+      </c>
+      <c r="AB31">
+        <v>1.11</v>
+      </c>
+      <c r="AC31">
+        <v>1.53</v>
+      </c>
+      <c r="AD31">
+        <v>2.38</v>
+      </c>
+      <c r="AE31">
+        <v>2.52</v>
+      </c>
+      <c r="AF31">
+        <v>1.46</v>
+      </c>
+      <c r="AG31">
+        <v>5.25</v>
+      </c>
+      <c r="AH31">
+        <v>1.12</v>
+      </c>
+      <c r="AI31">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AJ31">
+        <v>1</v>
+      </c>
+      <c r="AK31">
+        <v>2.3</v>
+      </c>
+      <c r="AL31">
+        <v>1.54</v>
+      </c>
+      <c r="AM31">
         <v>1.27</v>
-      </c>
-      <c r="Z31">
-        <v>7.7</v>
-      </c>
-      <c r="AA31">
-        <v>1.02</v>
-      </c>
-      <c r="AB31">
-        <v>1.04</v>
-      </c>
-      <c r="AC31">
-        <v>1.35</v>
-      </c>
-      <c r="AD31">
-        <v>2.97</v>
-      </c>
-      <c r="AE31">
-        <v>2.2</v>
-      </c>
-      <c r="AF31">
-        <v>1.62</v>
-      </c>
-      <c r="AG31">
-        <v>4.1</v>
-      </c>
-      <c r="AH31">
-        <v>1.19</v>
-      </c>
-      <c r="AI31">
-        <v>7.3</v>
-      </c>
-      <c r="AJ31">
-        <v>1.03</v>
-      </c>
-      <c r="AK31">
-        <v>1.97</v>
-      </c>
-      <c r="AL31">
-        <v>1.73</v>
-      </c>
-      <c r="AM31">
-        <v>1.26</v>
       </c>
       <c r="AN31">
         <v>1.14</v>
@@ -6622,55 +6622,55 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AQ31">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="AR31">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="AS31">
-        <v>2.52</v>
+        <v>2.75</v>
       </c>
       <c r="AT31">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="AU31">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AV31">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="AW31">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AX31">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AY31">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AZ31">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="BA31">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="BB31">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="BC31">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="BD31">
-        <v>3.25</v>
+        <v>2.91</v>
       </c>
       <c r="BE31">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="BF31">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="BG31">
         <v>0</v>
@@ -6690,10 +6690,10 @@
         <v>80</v>
       </c>
       <c r="C32" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E32" t="s">
         <v>137</v>
@@ -6729,133 +6729,133 @@
         <v>188</v>
       </c>
       <c r="P32">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Q32">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="R32">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="S32">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T32">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="U32">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V32">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W32">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="X32">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="Y32">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z32">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA32">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB32">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC32">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD32">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AE32">
-        <v>1.98</v>
+        <v>1.66</v>
       </c>
       <c r="AF32">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AG32">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AH32">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI32">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AJ32">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK32">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AL32">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AM32">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN32">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AO32">
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AQ32">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AR32">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AS32">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AT32">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AU32">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AV32">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AW32">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AX32">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AY32">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AZ32">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BA32">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="BB32">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC32">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD32">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="BE32">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF32">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG32">
         <v>0</v>
@@ -6875,7 +6875,7 @@
         <v>80</v>
       </c>
       <c r="C33" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D33" t="s">
         <v>105</v>
@@ -6914,103 +6914,103 @@
         <v>188</v>
       </c>
       <c r="P33">
-        <v>5.48</v>
+        <v>2</v>
       </c>
       <c r="Q33">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="R33">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="S33">
-        <v>6.1</v>
+        <v>2.5</v>
       </c>
       <c r="T33">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="U33">
-        <v>2.41</v>
+        <v>4.4</v>
       </c>
       <c r="V33">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="W33">
-        <v>2.24</v>
+        <v>2.73</v>
       </c>
       <c r="X33">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="Y33">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="Z33">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AA33">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AB33">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="AC33">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AD33">
-        <v>2.38</v>
+        <v>3.08</v>
       </c>
       <c r="AE33">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="AF33">
-        <v>1.46</v>
+        <v>1.78</v>
       </c>
       <c r="AG33">
-        <v>5.25</v>
+        <v>3.45</v>
       </c>
       <c r="AH33">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AI33">
-        <v>9.199999999999999</v>
+        <v>6.75</v>
       </c>
       <c r="AJ33">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AK33">
-        <v>2.3</v>
+        <v>1.79</v>
       </c>
       <c r="AL33">
-        <v>1.54</v>
+        <v>1.92</v>
       </c>
       <c r="AM33">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AN33">
-        <v>1.14</v>
+        <v>1.75</v>
       </c>
       <c r="AO33">
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AQ33">
         <v>1.69</v>
       </c>
       <c r="AR33">
-        <v>2.55</v>
+        <v>2.19</v>
       </c>
       <c r="AS33">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="AT33">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AU33">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="AV33">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AW33">
         <v>1.63</v>
@@ -7019,28 +7019,28 @@
         <v>1.38</v>
       </c>
       <c r="AY33">
+        <v>1.14</v>
+      </c>
+      <c r="AZ33">
+        <v>1.56</v>
+      </c>
+      <c r="BA33">
+        <v>3.34</v>
+      </c>
+      <c r="BB33">
         <v>1.23</v>
       </c>
-      <c r="AZ33">
-        <v>2.39</v>
-      </c>
-      <c r="BA33">
-        <v>1.87</v>
-      </c>
-      <c r="BB33">
-        <v>1.33</v>
-      </c>
       <c r="BC33">
-        <v>2.59</v>
+        <v>2.15</v>
       </c>
       <c r="BD33">
-        <v>2.91</v>
+        <v>3.52</v>
       </c>
       <c r="BE33">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="BF33">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="BG33">
         <v>0</v>
@@ -7099,133 +7099,133 @@
         <v>188</v>
       </c>
       <c r="P34">
-        <v>1.36</v>
+        <v>4.33</v>
       </c>
       <c r="Q34">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="R34">
-        <v>8.550000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="S34">
-        <v>1.88</v>
+        <v>5.29</v>
       </c>
       <c r="T34">
-        <v>2.25</v>
+        <v>1.96</v>
       </c>
       <c r="U34">
-        <v>8.1</v>
+        <v>2.46</v>
       </c>
       <c r="V34">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="W34">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="X34">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="Y34">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z34">
-        <v>7.1</v>
+        <v>7.7</v>
       </c>
       <c r="AA34">
+        <v>1.02</v>
+      </c>
+      <c r="AB34">
         <v>1.04</v>
       </c>
-      <c r="AB34">
-        <v>1.06</v>
-      </c>
       <c r="AC34">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AD34">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AE34">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AF34">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AG34">
-        <v>3.42</v>
+        <v>4.1</v>
       </c>
       <c r="AH34">
+        <v>1.19</v>
+      </c>
+      <c r="AI34">
+        <v>7.3</v>
+      </c>
+      <c r="AJ34">
+        <v>1.03</v>
+      </c>
+      <c r="AK34">
+        <v>1.97</v>
+      </c>
+      <c r="AL34">
+        <v>1.73</v>
+      </c>
+      <c r="AM34">
+        <v>1.26</v>
+      </c>
+      <c r="AN34">
+        <v>1.14</v>
+      </c>
+      <c r="AO34">
+        <v>0</v>
+      </c>
+      <c r="AP34">
+        <v>1.28</v>
+      </c>
+      <c r="AQ34">
+        <v>1.61</v>
+      </c>
+      <c r="AR34">
+        <v>1.95</v>
+      </c>
+      <c r="AS34">
+        <v>2.52</v>
+      </c>
+      <c r="AT34">
+        <v>3.55</v>
+      </c>
+      <c r="AU34">
+        <v>2.7</v>
+      </c>
+      <c r="AV34">
+        <v>2.21</v>
+      </c>
+      <c r="AW34">
+        <v>1.73</v>
+      </c>
+      <c r="AX34">
+        <v>1.4</v>
+      </c>
+      <c r="AY34">
+        <v>1.24</v>
+      </c>
+      <c r="AZ34">
+        <v>2.46</v>
+      </c>
+      <c r="BA34">
+        <v>1.82</v>
+      </c>
+      <c r="BB34">
         <v>1.27</v>
       </c>
-      <c r="AI34">
-        <v>6.45</v>
-      </c>
-      <c r="AJ34">
-        <v>1.05</v>
-      </c>
-      <c r="AK34">
-        <v>2.25</v>
-      </c>
-      <c r="AL34">
-        <v>1.6</v>
-      </c>
-      <c r="AM34">
-        <v>1.16</v>
-      </c>
-      <c r="AN34">
-        <v>2.72</v>
-      </c>
-      <c r="AO34">
-        <v>0</v>
-      </c>
-      <c r="AP34">
-        <v>1.24</v>
-      </c>
-      <c r="AQ34">
-        <v>1.46</v>
-      </c>
-      <c r="AR34">
-        <v>1.87</v>
-      </c>
-      <c r="AS34">
-        <v>2.33</v>
-      </c>
-      <c r="AT34">
-        <v>3.14</v>
-      </c>
-      <c r="AU34">
-        <v>3.34</v>
-      </c>
-      <c r="AV34">
-        <v>2.38</v>
-      </c>
-      <c r="AW34">
-        <v>1.83</v>
-      </c>
-      <c r="AX34">
-        <v>1.48</v>
-      </c>
-      <c r="AY34">
-        <v>1.27</v>
-      </c>
-      <c r="AZ34">
-        <v>1.29</v>
-      </c>
-      <c r="BA34">
-        <v>4.32</v>
-      </c>
-      <c r="BB34">
-        <v>1.23</v>
-      </c>
       <c r="BC34">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="BD34">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="BE34">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="BF34">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="BG34">
         <v>0</v>
@@ -7245,10 +7245,10 @@
         <v>80</v>
       </c>
       <c r="C35" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D35" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E35" t="s">
         <v>140</v>
@@ -7284,133 +7284,133 @@
         <v>188</v>
       </c>
       <c r="P35">
-        <v>2.5</v>
+        <v>1.36</v>
       </c>
       <c r="Q35">
-        <v>3.55</v>
+        <v>4.05</v>
       </c>
       <c r="R35">
-        <v>2.4</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AE35">
-        <v>1.66</v>
+        <v>2.02</v>
       </c>
       <c r="AF35">
-        <v>2.15</v>
+        <v>1.74</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AH35">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI35">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL35">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AM35">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN35">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AO35">
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ35">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR35">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AS35">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT35">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AU35">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AV35">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW35">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AX35">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY35">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ35">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BA35">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="BB35">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC35">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD35">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="BE35">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF35">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG35">
         <v>0</v>
@@ -7654,79 +7654,79 @@
         <v>188</v>
       </c>
       <c r="P37">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q37">
+        <v>2.8</v>
+      </c>
+      <c r="R37">
+        <v>3.3</v>
+      </c>
+      <c r="S37">
         <v>2.9</v>
       </c>
-      <c r="R37">
-        <v>3.95</v>
-      </c>
-      <c r="S37">
-        <v>2.88</v>
-      </c>
       <c r="T37">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="U37">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="V37">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W37">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="X37">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="Y37">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z37">
-        <v>13</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA37">
         <v>1.02</v>
       </c>
       <c r="AB37">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AC37">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AD37">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="AE37">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="AF37">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AG37">
-        <v>6.33</v>
+        <v>6.35</v>
       </c>
       <c r="AH37">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AI37">
-        <v>9.699999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AJ37">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AK37">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="AL37">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AM37">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AN37">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AO37">
         <v>0</v>
@@ -7738,22 +7738,22 @@
         <v>1.76</v>
       </c>
       <c r="AR37">
-        <v>2.7</v>
+        <v>2.24</v>
       </c>
       <c r="AS37">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="AT37">
-        <v>4.34</v>
+        <v>4.36</v>
       </c>
       <c r="AU37">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="AV37">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AW37">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AX37">
         <v>1.3</v>
@@ -7762,25 +7762,25 @@
         <v>1.13</v>
       </c>
       <c r="AZ37">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="BA37">
-        <v>3.26</v>
+        <v>2.96</v>
       </c>
       <c r="BB37">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="BC37">
-        <v>2.9</v>
+        <v>3.12</v>
       </c>
       <c r="BD37">
-        <v>2.66</v>
+        <v>2.53</v>
       </c>
       <c r="BE37">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="BF37">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BG37">
         <v>0</v>
@@ -7839,79 +7839,79 @@
         <v>188</v>
       </c>
       <c r="P38">
-        <v>5.75</v>
+        <v>2</v>
       </c>
       <c r="Q38">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="R38">
-        <v>1.52</v>
+        <v>3.95</v>
       </c>
       <c r="S38">
-        <v>8.050000000000001</v>
+        <v>2.88</v>
       </c>
       <c r="T38">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="U38">
-        <v>2.1</v>
+        <v>5.1</v>
       </c>
       <c r="V38">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="W38">
-        <v>2.44</v>
+        <v>2.11</v>
       </c>
       <c r="X38">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="Y38">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="Z38">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AA38">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AB38">
+        <v>1.08</v>
+      </c>
+      <c r="AC38">
+        <v>1.58</v>
+      </c>
+      <c r="AD38">
+        <v>2.25</v>
+      </c>
+      <c r="AE38">
+        <v>2.74</v>
+      </c>
+      <c r="AF38">
+        <v>1.35</v>
+      </c>
+      <c r="AG38">
+        <v>6.33</v>
+      </c>
+      <c r="AH38">
         <v>1.07</v>
       </c>
-      <c r="AC38">
-        <v>1.38</v>
-      </c>
-      <c r="AD38">
-        <v>2.43</v>
-      </c>
-      <c r="AE38">
-        <v>2.53</v>
-      </c>
-      <c r="AF38">
-        <v>1.49</v>
-      </c>
-      <c r="AG38">
-        <v>4.65</v>
-      </c>
-      <c r="AH38">
-        <v>1.12</v>
-      </c>
       <c r="AI38">
-        <v>8.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AJ38">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AK38">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="AL38">
         <v>1.53</v>
       </c>
       <c r="AM38">
-        <v>2.31</v>
+        <v>1.35</v>
       </c>
       <c r="AN38">
-        <v>1.04</v>
+        <v>1.63</v>
       </c>
       <c r="AO38">
         <v>0</v>
@@ -7920,52 +7920,52 @@
         <v>1.42</v>
       </c>
       <c r="AQ38">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AR38">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="AS38">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="AT38">
-        <v>4.41</v>
+        <v>4.34</v>
       </c>
       <c r="AU38">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="AV38">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AW38">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AX38">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AY38">
         <v>1.13</v>
       </c>
       <c r="AZ38">
-        <v>3.85</v>
+        <v>1.52</v>
       </c>
       <c r="BA38">
-        <v>1.43</v>
+        <v>3.26</v>
       </c>
       <c r="BB38">
+        <v>1.39</v>
+      </c>
+      <c r="BC38">
+        <v>2.9</v>
+      </c>
+      <c r="BD38">
+        <v>2.66</v>
+      </c>
+      <c r="BE38">
         <v>1.33</v>
       </c>
-      <c r="BC38">
-        <v>2.59</v>
-      </c>
-      <c r="BD38">
-        <v>2.91</v>
-      </c>
-      <c r="BE38">
-        <v>1.41</v>
-      </c>
       <c r="BF38">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="BG38">
         <v>0</v>
@@ -8024,79 +8024,79 @@
         <v>188</v>
       </c>
       <c r="P39">
-        <v>2.2</v>
+        <v>5.75</v>
       </c>
       <c r="Q39">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="R39">
+        <v>1.52</v>
+      </c>
+      <c r="S39">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="T39">
+        <v>2.05</v>
+      </c>
+      <c r="U39">
+        <v>2.1</v>
+      </c>
+      <c r="V39">
+        <v>1.51</v>
+      </c>
+      <c r="W39">
+        <v>2.44</v>
+      </c>
+      <c r="X39">
         <v>3.3</v>
       </c>
-      <c r="S39">
-        <v>2.9</v>
-      </c>
-      <c r="T39">
-        <v>1.81</v>
-      </c>
-      <c r="U39">
-        <v>4.2</v>
-      </c>
-      <c r="V39">
-        <v>1.65</v>
-      </c>
-      <c r="W39">
-        <v>2.16</v>
-      </c>
-      <c r="X39">
-        <v>4.1</v>
-      </c>
       <c r="Y39">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z39">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA39">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AB39">
+        <v>1.07</v>
+      </c>
+      <c r="AC39">
+        <v>1.38</v>
+      </c>
+      <c r="AD39">
+        <v>2.43</v>
+      </c>
+      <c r="AE39">
+        <v>2.53</v>
+      </c>
+      <c r="AF39">
+        <v>1.49</v>
+      </c>
+      <c r="AG39">
+        <v>4.65</v>
+      </c>
+      <c r="AH39">
         <v>1.12</v>
       </c>
-      <c r="AC39">
-        <v>1.66</v>
-      </c>
-      <c r="AD39">
-        <v>2.09</v>
-      </c>
-      <c r="AE39">
-        <v>3.1</v>
-      </c>
-      <c r="AF39">
-        <v>1.31</v>
-      </c>
-      <c r="AG39">
-        <v>6.35</v>
-      </c>
-      <c r="AH39">
-        <v>1.06</v>
-      </c>
       <c r="AI39">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AJ39">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AK39">
         <v>2.4</v>
       </c>
       <c r="AL39">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AM39">
-        <v>1.32</v>
+        <v>2.31</v>
       </c>
       <c r="AN39">
-        <v>1.55</v>
+        <v>1.04</v>
       </c>
       <c r="AO39">
         <v>0</v>
@@ -8105,19 +8105,19 @@
         <v>1.42</v>
       </c>
       <c r="AQ39">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AR39">
-        <v>2.24</v>
+        <v>2.73</v>
       </c>
       <c r="AS39">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="AT39">
-        <v>4.36</v>
+        <v>4.41</v>
       </c>
       <c r="AU39">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="AV39">
         <v>1.94</v>
@@ -8126,31 +8126,31 @@
         <v>1.56</v>
       </c>
       <c r="AX39">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AY39">
         <v>1.13</v>
       </c>
       <c r="AZ39">
-        <v>1.61</v>
+        <v>3.85</v>
       </c>
       <c r="BA39">
-        <v>2.96</v>
+        <v>1.43</v>
       </c>
       <c r="BB39">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="BC39">
-        <v>3.12</v>
+        <v>2.59</v>
       </c>
       <c r="BD39">
-        <v>2.53</v>
+        <v>2.91</v>
       </c>
       <c r="BE39">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="BF39">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="BG39">
         <v>0</v>

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -310,12 +310,12 @@
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
     <t>Egypt Egyptian Premier League</t>
   </si>
   <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
     <t>South Africa Premier Soccer League</t>
   </si>
   <si>
@@ -337,12 +337,12 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Bucheon 1995</t>
+  </si>
+  <si>
     <t>Jeonbuk Motors</t>
   </si>
   <si>
-    <t>Bucheon 1995</t>
-  </si>
-  <si>
     <t>Daejeon Citizen</t>
   </si>
   <si>
@@ -355,36 +355,36 @@
     <t>Madura United</t>
   </si>
   <si>
+    <t>FC Seoul</t>
+  </si>
+  <si>
     <t>Ethiopia Nigd Bank</t>
   </si>
   <si>
-    <t>FC Seoul</t>
-  </si>
-  <si>
     <t>Qingdao Youth Island</t>
   </si>
   <si>
     <t>Tanjong Pagar</t>
   </si>
   <si>
+    <t>Shenyang Urban</t>
+  </si>
+  <si>
     <t>Shandong Luneng</t>
   </si>
   <si>
-    <t>Shenyang Urban</t>
+    <t>Karvan FK</t>
+  </si>
+  <si>
+    <t>Chongqing Tongliang Long</t>
+  </si>
+  <si>
+    <t>Dire Dawa Kenema</t>
   </si>
   <si>
     <t>Borneo</t>
   </si>
   <si>
-    <t>Karvan FK</t>
-  </si>
-  <si>
-    <t>Dire Dawa Kenema</t>
-  </si>
-  <si>
-    <t>Chongqing Tongliang Long</t>
-  </si>
-  <si>
     <t>Mekelle Kenema</t>
   </si>
   <si>
@@ -415,42 +415,42 @@
     <t>Maccabi Tel Aviv</t>
   </si>
   <si>
+    <t>Bani Yas</t>
+  </si>
+  <si>
+    <t>Dibba Al Fujairah</t>
+  </si>
+  <si>
     <t>Al Ittihad Kalba</t>
   </si>
   <si>
-    <t>Dibba Al Fujairah</t>
-  </si>
-  <si>
-    <t>Bani Yas</t>
+    <t>Falkenberg</t>
+  </si>
+  <si>
+    <t>Ceramica Cleopatra</t>
+  </si>
+  <si>
+    <t>Lokomotiv Sofia 1929</t>
+  </si>
+  <si>
+    <t>Al Ahly</t>
   </si>
   <si>
     <t>Smouha SC</t>
   </si>
   <si>
-    <t>Falkenberg</t>
-  </si>
-  <si>
-    <t>Lokomotiv Sofia 1929</t>
-  </si>
-  <si>
-    <t>Ceramica Cleopatra</t>
-  </si>
-  <si>
-    <t>Al Ahly</t>
+    <t>Siwelele</t>
   </si>
   <si>
     <t>Chippa United</t>
   </si>
   <si>
-    <t>Siwelele</t>
+    <t>Stellenbosch</t>
   </si>
   <si>
     <t>Magesi</t>
   </si>
   <si>
-    <t>Stellenbosch</t>
-  </si>
-  <si>
     <t>Al Khaleej</t>
   </si>
   <si>
@@ -460,12 +460,12 @@
     <t>New York City II</t>
   </si>
   <si>
+    <t>Jeju United</t>
+  </si>
+  <si>
     <t>Gwangju</t>
   </si>
   <si>
-    <t>Jeju United</t>
-  </si>
-  <si>
     <t>Incheon United</t>
   </si>
   <si>
@@ -478,36 +478,36 @@
     <t>Bali United</t>
   </si>
   <si>
+    <t>Anyang</t>
+  </si>
+  <si>
     <t>Kedus Giorgis</t>
   </si>
   <si>
-    <t>Anyang</t>
-  </si>
-  <si>
     <t>Tianjin Teda</t>
   </si>
   <si>
     <t>Hougang United</t>
   </si>
   <si>
+    <t>Chengdu Better City FC</t>
+  </si>
+  <si>
     <t>Shanghai Shenhua</t>
   </si>
   <si>
-    <t>Chengdu Better City FC</t>
+    <t>Neftçi</t>
+  </si>
+  <si>
+    <t>Henan Jianye</t>
+  </si>
+  <si>
+    <t>Ethiopia Bunna</t>
   </si>
   <si>
     <t>Persita</t>
   </si>
   <si>
-    <t>Neftçi</t>
-  </si>
-  <si>
-    <t>Ethiopia Bunna</t>
-  </si>
-  <si>
-    <t>Henan Jianye</t>
-  </si>
-  <si>
     <t>Arba Minch Kenema</t>
   </si>
   <si>
@@ -538,37 +538,37 @@
     <t>Hapoel Petah Tikva</t>
   </si>
   <si>
+    <t>Al Dhafra</t>
+  </si>
+  <si>
     <t>Al Bataeh</t>
   </si>
   <si>
-    <t>Al Dhafra</t>
+    <t>Norrköping</t>
+  </si>
+  <si>
+    <t>Pyramids FC</t>
+  </si>
+  <si>
+    <t>Botev Vratsa</t>
+  </si>
+  <si>
+    <t>ENPPI</t>
   </si>
   <si>
     <t>Zamalek</t>
   </si>
   <si>
-    <t>Norrköping</t>
-  </si>
-  <si>
-    <t>Botev Vratsa</t>
-  </si>
-  <si>
-    <t>Pyramids FC</t>
-  </si>
-  <si>
-    <t>ENPPI</t>
+    <t>Durban City</t>
   </si>
   <si>
     <t>Sekhukhune United</t>
   </si>
   <si>
-    <t>Durban City</t>
+    <t>Orlando Pirates</t>
   </si>
   <si>
     <t>Orbit College</t>
-  </si>
-  <si>
-    <t>Orlando Pirates</t>
   </si>
   <si>
     <t>Al Hilal</t>
@@ -1179,133 +1179,133 @@
         <v>188</v>
       </c>
       <c r="P2">
-        <v>1.33</v>
+        <v>2.47</v>
       </c>
       <c r="Q2">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="R2">
-        <v>7.75</v>
+        <v>2.8</v>
       </c>
       <c r="S2">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>8.15</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W2">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="X2">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y2">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z2">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC2">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AE2">
-        <v>1.96</v>
+        <v>2.35</v>
       </c>
       <c r="AF2">
-        <v>1.88</v>
+        <v>1.57</v>
       </c>
       <c r="AG2">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AH2">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK2">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AL2">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AN2">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AO2">
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AQ2">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AR2">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AS2">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AT2">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="AU2">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV2">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AW2">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AX2">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AY2">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AZ2">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BA2">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BB2">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC2">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="BD2">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BE2">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BF2">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG2">
         <v>0</v>
@@ -1364,133 +1364,133 @@
         <v>188</v>
       </c>
       <c r="P3">
-        <v>2.47</v>
+        <v>1.33</v>
       </c>
       <c r="Q3">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="R3">
-        <v>2.8</v>
+        <v>7.75</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>8.15</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AE3">
-        <v>2.35</v>
+        <v>1.96</v>
       </c>
       <c r="AF3">
+        <v>1.88</v>
+      </c>
+      <c r="AG3">
+        <v>3.18</v>
+      </c>
+      <c r="AH3">
+        <v>1.3</v>
+      </c>
+      <c r="AI3">
+        <v>6.5</v>
+      </c>
+      <c r="AJ3">
+        <v>1.06</v>
+      </c>
+      <c r="AK3">
+        <v>2.26</v>
+      </c>
+      <c r="AL3">
         <v>1.57</v>
       </c>
-      <c r="AG3">
-        <v>0</v>
-      </c>
-      <c r="AH3">
-        <v>0</v>
-      </c>
-      <c r="AI3">
-        <v>0</v>
-      </c>
-      <c r="AJ3">
-        <v>0</v>
-      </c>
-      <c r="AK3">
-        <v>0</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
       <c r="AM3">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AO3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="AU3">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV3">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AW3">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AX3">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY3">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AZ3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BA3">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BB3">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC3">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="BD3">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BE3">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF3">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG3">
         <v>0</v>
@@ -2250,10 +2250,10 @@
         <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E8" t="s">
         <v>113</v>
@@ -2289,133 +2289,133 @@
         <v>188</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AO8">
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG8">
         <v>0</v>
@@ -2435,10 +2435,10 @@
         <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E9" t="s">
         <v>114</v>
@@ -2474,133 +2474,133 @@
         <v>188</v>
       </c>
       <c r="P9">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z9">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC9">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD9">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AH9">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI9">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AJ9">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK9">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AL9">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AM9">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN9">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AO9">
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ9">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AR9">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AS9">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AT9">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AU9">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AV9">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AW9">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AX9">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AY9">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ9">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="BA9">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="BB9">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC9">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD9">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE9">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF9">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG9">
         <v>0</v>
@@ -3029,133 +3029,133 @@
         <v>188</v>
       </c>
       <c r="P12">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="T12">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="U12">
-        <v>2.78</v>
+        <v>2.01</v>
       </c>
       <c r="V12">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="W12">
-        <v>3.6</v>
+        <v>3.16</v>
       </c>
       <c r="X12">
-        <v>2.08</v>
+        <v>2.47</v>
       </c>
       <c r="Y12">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="Z12">
-        <v>4.45</v>
+        <v>5.7</v>
       </c>
       <c r="AA12">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AB12">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC12">
+        <v>1.18</v>
+      </c>
+      <c r="AD12">
+        <v>3.88</v>
+      </c>
+      <c r="AE12">
+        <v>1.74</v>
+      </c>
+      <c r="AF12">
+        <v>2.12</v>
+      </c>
+      <c r="AG12">
+        <v>2.9</v>
+      </c>
+      <c r="AH12">
+        <v>1.36</v>
+      </c>
+      <c r="AI12">
+        <v>5.2</v>
+      </c>
+      <c r="AJ12">
+        <v>1.11</v>
+      </c>
+      <c r="AK12">
+        <v>1.8</v>
+      </c>
+      <c r="AL12">
+        <v>1.9</v>
+      </c>
+      <c r="AM12">
+        <v>1.21</v>
+      </c>
+      <c r="AN12">
         <v>1.13</v>
       </c>
-      <c r="AD12">
-        <v>5.65</v>
-      </c>
-      <c r="AE12">
-        <v>1.39</v>
-      </c>
-      <c r="AF12">
-        <v>2.59</v>
-      </c>
-      <c r="AG12">
-        <v>2.09</v>
-      </c>
-      <c r="AH12">
-        <v>1.76</v>
-      </c>
-      <c r="AI12">
-        <v>3.33</v>
-      </c>
-      <c r="AJ12">
-        <v>1.25</v>
-      </c>
-      <c r="AK12">
-        <v>1.36</v>
-      </c>
-      <c r="AL12">
-        <v>2.75</v>
-      </c>
-      <c r="AM12">
-        <v>1.28</v>
-      </c>
-      <c r="AN12">
-        <v>1.43</v>
-      </c>
       <c r="AO12">
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="AQ12">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AR12">
-        <v>1.5</v>
+        <v>1.94</v>
       </c>
       <c r="AS12">
-        <v>1.8</v>
+        <v>2.16</v>
       </c>
       <c r="AT12">
-        <v>2.24</v>
+        <v>2.84</v>
       </c>
       <c r="AU12">
-        <v>5.1</v>
+        <v>3.72</v>
       </c>
       <c r="AV12">
-        <v>3.33</v>
+        <v>2.55</v>
       </c>
       <c r="AW12">
-        <v>2.46</v>
+        <v>1.98</v>
       </c>
       <c r="AX12">
-        <v>1.92</v>
+        <v>1.61</v>
       </c>
       <c r="AY12">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="AZ12">
-        <v>1.92</v>
+        <v>5.03</v>
       </c>
       <c r="BA12">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="BB12">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="BC12">
-        <v>1.62</v>
+        <v>1.94</v>
       </c>
       <c r="BD12">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="BE12">
-        <v>2.19</v>
+        <v>1.79</v>
       </c>
       <c r="BF12">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="BG12">
         <v>0</v>
@@ -3214,133 +3214,133 @@
         <v>188</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S13">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="T13">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="U13">
-        <v>2.01</v>
+        <v>2.78</v>
       </c>
       <c r="V13">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W13">
-        <v>3.16</v>
+        <v>3.6</v>
       </c>
       <c r="X13">
-        <v>2.47</v>
+        <v>2.08</v>
       </c>
       <c r="Y13">
-        <v>1.47</v>
+        <v>1.69</v>
       </c>
       <c r="Z13">
+        <v>4.45</v>
+      </c>
+      <c r="AA13">
+        <v>1.15</v>
+      </c>
+      <c r="AB13">
+        <v>1.02</v>
+      </c>
+      <c r="AC13">
+        <v>1.13</v>
+      </c>
+      <c r="AD13">
+        <v>5.65</v>
+      </c>
+      <c r="AE13">
+        <v>1.39</v>
+      </c>
+      <c r="AF13">
+        <v>2.59</v>
+      </c>
+      <c r="AG13">
+        <v>2.09</v>
+      </c>
+      <c r="AH13">
+        <v>1.76</v>
+      </c>
+      <c r="AI13">
+        <v>3.33</v>
+      </c>
+      <c r="AJ13">
+        <v>1.25</v>
+      </c>
+      <c r="AK13">
+        <v>1.36</v>
+      </c>
+      <c r="AL13">
+        <v>2.75</v>
+      </c>
+      <c r="AM13">
+        <v>1.28</v>
+      </c>
+      <c r="AN13">
+        <v>1.43</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>1.1</v>
+      </c>
+      <c r="AQ13">
+        <v>1.24</v>
+      </c>
+      <c r="AR13">
+        <v>1.5</v>
+      </c>
+      <c r="AS13">
+        <v>1.8</v>
+      </c>
+      <c r="AT13">
+        <v>2.24</v>
+      </c>
+      <c r="AU13">
+        <v>5.1</v>
+      </c>
+      <c r="AV13">
+        <v>3.33</v>
+      </c>
+      <c r="AW13">
+        <v>2.46</v>
+      </c>
+      <c r="AX13">
+        <v>1.92</v>
+      </c>
+      <c r="AY13">
+        <v>1.56</v>
+      </c>
+      <c r="AZ13">
+        <v>1.92</v>
+      </c>
+      <c r="BA13">
+        <v>2.1</v>
+      </c>
+      <c r="BB13">
+        <v>1.08</v>
+      </c>
+      <c r="BC13">
+        <v>1.62</v>
+      </c>
+      <c r="BD13">
         <v>5.7</v>
       </c>
-      <c r="AA13">
-        <v>1.08</v>
-      </c>
-      <c r="AB13">
-        <v>1.03</v>
-      </c>
-      <c r="AC13">
-        <v>1.18</v>
-      </c>
-      <c r="AD13">
-        <v>3.88</v>
-      </c>
-      <c r="AE13">
-        <v>1.74</v>
-      </c>
-      <c r="AF13">
-        <v>2.12</v>
-      </c>
-      <c r="AG13">
-        <v>2.9</v>
-      </c>
-      <c r="AH13">
-        <v>1.36</v>
-      </c>
-      <c r="AI13">
-        <v>5.2</v>
-      </c>
-      <c r="AJ13">
-        <v>1.11</v>
-      </c>
-      <c r="AK13">
-        <v>1.8</v>
-      </c>
-      <c r="AL13">
-        <v>1.9</v>
-      </c>
-      <c r="AM13">
-        <v>1.21</v>
-      </c>
-      <c r="AN13">
-        <v>1.13</v>
-      </c>
-      <c r="AO13">
-        <v>0</v>
-      </c>
-      <c r="AP13">
-        <v>1.19</v>
-      </c>
-      <c r="AQ13">
-        <v>1.44</v>
-      </c>
-      <c r="AR13">
-        <v>1.94</v>
-      </c>
-      <c r="AS13">
-        <v>2.16</v>
-      </c>
-      <c r="AT13">
-        <v>2.84</v>
-      </c>
-      <c r="AU13">
-        <v>3.72</v>
-      </c>
-      <c r="AV13">
-        <v>2.55</v>
-      </c>
-      <c r="AW13">
-        <v>1.98</v>
-      </c>
-      <c r="AX13">
-        <v>1.61</v>
-      </c>
-      <c r="AY13">
-        <v>1.34</v>
-      </c>
-      <c r="AZ13">
-        <v>5.03</v>
-      </c>
-      <c r="BA13">
-        <v>1.4</v>
-      </c>
-      <c r="BB13">
-        <v>1.16</v>
-      </c>
-      <c r="BC13">
-        <v>1.94</v>
-      </c>
-      <c r="BD13">
-        <v>4.2</v>
-      </c>
       <c r="BE13">
-        <v>1.79</v>
+        <v>2.19</v>
       </c>
       <c r="BF13">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="BG13">
         <v>0</v>
@@ -3360,7 +3360,7 @@
         <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D14" t="s">
         <v>105</v>
@@ -3399,133 +3399,133 @@
         <v>188</v>
       </c>
       <c r="P14">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R14">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>6.08</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AD14">
-        <v>4.35</v>
+        <v>4.8</v>
       </c>
       <c r="AE14">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AF14">
-        <v>2.26</v>
+        <v>2.43</v>
       </c>
       <c r="AG14">
-        <v>2.63</v>
+        <v>2.14</v>
       </c>
       <c r="AH14">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AI14">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="AJ14">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AK14">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL14">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AM14">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AN14">
-        <v>2.49</v>
+        <v>1.05</v>
       </c>
       <c r="AO14">
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ14">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR14">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AS14">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT14">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AU14">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AV14">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AW14">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AX14">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AY14">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ14">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="BA14">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BB14">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC14">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="BD14">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="BE14">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="BF14">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG14">
         <v>0</v>
@@ -3545,10 +3545,10 @@
         <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E15" t="s">
         <v>120</v>
@@ -3623,28 +3623,28 @@
         <v>0</v>
       </c>
       <c r="AC15">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AD15">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AE15">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AF15">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AG15">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH15">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI15">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AJ15">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK15">
         <v>0</v>
@@ -3653,10 +3653,10 @@
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN15">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AO15">
         <v>0</v>
@@ -3915,10 +3915,10 @@
         <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E17" t="s">
         <v>122</v>
@@ -3954,133 +3954,133 @@
         <v>188</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>6.08</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI17">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL17">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AM17">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AO17">
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AU17">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AV17">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AW17">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX17">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY17">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ17">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BA17">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BB17">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC17">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BD17">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="BE17">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BF17">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG17">
         <v>0</v>
@@ -5959,7 +5959,7 @@
         <v>133</v>
       </c>
       <c r="F28" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -6144,7 +6144,7 @@
         <v>134</v>
       </c>
       <c r="F29" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -6329,7 +6329,7 @@
         <v>135</v>
       </c>
       <c r="F30" t="s">
-        <v>175</v>
+        <v>145</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -6508,7 +6508,7 @@
         <v>98</v>
       </c>
       <c r="D31" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E31" t="s">
         <v>136</v>
@@ -6544,133 +6544,133 @@
         <v>188</v>
       </c>
       <c r="P31">
-        <v>5.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q31">
-        <v>3.12</v>
+        <v>3.55</v>
       </c>
       <c r="R31">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="S31">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="T31">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U31">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="V31">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W31">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="X31">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y31">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z31">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA31">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB31">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC31">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD31">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AE31">
-        <v>2.52</v>
+        <v>1.66</v>
       </c>
       <c r="AF31">
-        <v>1.46</v>
+        <v>2.15</v>
       </c>
       <c r="AG31">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AH31">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AI31">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AJ31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK31">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL31">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AM31">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN31">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AO31">
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AQ31">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AR31">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AS31">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AT31">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AU31">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AV31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW31">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AX31">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AY31">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ31">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="BA31">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="BB31">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC31">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="BD31">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="BE31">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BF31">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BG31">
         <v>0</v>
@@ -6693,7 +6693,7 @@
         <v>99</v>
       </c>
       <c r="D32" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E32" t="s">
         <v>137</v>
@@ -6729,133 +6729,133 @@
         <v>188</v>
       </c>
       <c r="P32">
-        <v>2.5</v>
+        <v>4.88</v>
       </c>
       <c r="Q32">
-        <v>3.55</v>
+        <v>3.32</v>
       </c>
       <c r="R32">
-        <v>2.4</v>
+        <v>1.68</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>5.76</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AE32">
-        <v>1.66</v>
+        <v>2.15</v>
       </c>
       <c r="AF32">
-        <v>2.15</v>
+        <v>1.64</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AH32">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI32">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AL32">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM32">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN32">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO32">
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ32">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR32">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AS32">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AT32">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AU32">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV32">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AW32">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AX32">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY32">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ32">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BA32">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BB32">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC32">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BD32">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE32">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BF32">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG32">
         <v>0</v>
@@ -7060,7 +7060,7 @@
         <v>80</v>
       </c>
       <c r="C34" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D34" t="s">
         <v>105</v>
@@ -7099,133 +7099,133 @@
         <v>188</v>
       </c>
       <c r="P34">
-        <v>4.33</v>
+        <v>1.36</v>
       </c>
       <c r="Q34">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="R34">
-        <v>1.8</v>
+        <v>7</v>
       </c>
       <c r="S34">
-        <v>5.29</v>
+        <v>1.88</v>
       </c>
       <c r="T34">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="U34">
-        <v>2.46</v>
+        <v>8.1</v>
       </c>
       <c r="V34">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="W34">
-        <v>2.41</v>
+        <v>2.56</v>
       </c>
       <c r="X34">
-        <v>3.08</v>
+        <v>2.91</v>
       </c>
       <c r="Y34">
+        <v>1.33</v>
+      </c>
+      <c r="Z34">
+        <v>7.1</v>
+      </c>
+      <c r="AA34">
+        <v>1.04</v>
+      </c>
+      <c r="AB34">
+        <v>1.06</v>
+      </c>
+      <c r="AC34">
+        <v>1.31</v>
+      </c>
+      <c r="AD34">
+        <v>2.92</v>
+      </c>
+      <c r="AE34">
+        <v>2.02</v>
+      </c>
+      <c r="AF34">
+        <v>1.71</v>
+      </c>
+      <c r="AG34">
+        <v>3.42</v>
+      </c>
+      <c r="AH34">
         <v>1.27</v>
       </c>
-      <c r="Z34">
-        <v>7.7</v>
-      </c>
-      <c r="AA34">
-        <v>1.02</v>
-      </c>
-      <c r="AB34">
-        <v>1.04</v>
-      </c>
-      <c r="AC34">
-        <v>1.35</v>
-      </c>
-      <c r="AD34">
-        <v>2.97</v>
-      </c>
-      <c r="AE34">
-        <v>2.2</v>
-      </c>
-      <c r="AF34">
-        <v>1.62</v>
-      </c>
-      <c r="AG34">
-        <v>4.1</v>
-      </c>
-      <c r="AH34">
-        <v>1.19</v>
-      </c>
       <c r="AI34">
-        <v>7.3</v>
+        <v>6.45</v>
       </c>
       <c r="AJ34">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AK34">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="AL34">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AM34">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AN34">
-        <v>1.14</v>
+        <v>2.72</v>
       </c>
       <c r="AO34">
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AQ34">
-        <v>1.61</v>
+        <v>1.46</v>
       </c>
       <c r="AR34">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AS34">
-        <v>2.52</v>
+        <v>2.33</v>
       </c>
       <c r="AT34">
-        <v>3.55</v>
+        <v>3.14</v>
       </c>
       <c r="AU34">
-        <v>2.7</v>
+        <v>3.34</v>
       </c>
       <c r="AV34">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="AW34">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AX34">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AY34">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AZ34">
-        <v>2.46</v>
+        <v>1.29</v>
       </c>
       <c r="BA34">
-        <v>1.82</v>
+        <v>4.32</v>
       </c>
       <c r="BB34">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="BC34">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="BD34">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="BE34">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="BF34">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="BG34">
         <v>0</v>
@@ -7245,7 +7245,7 @@
         <v>80</v>
       </c>
       <c r="C35" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D35" t="s">
         <v>105</v>
@@ -7284,133 +7284,133 @@
         <v>188</v>
       </c>
       <c r="P35">
-        <v>1.36</v>
+        <v>5.48</v>
       </c>
       <c r="Q35">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="R35">
-        <v>8.550000000000001</v>
+        <v>1.55</v>
       </c>
       <c r="S35">
-        <v>1.88</v>
+        <v>7.1</v>
       </c>
       <c r="T35">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="U35">
-        <v>8.1</v>
+        <v>2.23</v>
       </c>
       <c r="V35">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="W35">
-        <v>2.56</v>
+        <v>2.28</v>
       </c>
       <c r="X35">
-        <v>2.91</v>
+        <v>3.48</v>
       </c>
       <c r="Y35">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="Z35">
-        <v>7.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA35">
         <v>1.04</v>
       </c>
       <c r="AB35">
+        <v>1.1</v>
+      </c>
+      <c r="AC35">
+        <v>1.53</v>
+      </c>
+      <c r="AD35">
+        <v>2.43</v>
+      </c>
+      <c r="AE35">
+        <v>2.46</v>
+      </c>
+      <c r="AF35">
+        <v>1.45</v>
+      </c>
+      <c r="AG35">
+        <v>4.1</v>
+      </c>
+      <c r="AH35">
+        <v>1.14</v>
+      </c>
+      <c r="AI35">
+        <v>9.1</v>
+      </c>
+      <c r="AJ35">
+        <v>1</v>
+      </c>
+      <c r="AK35">
+        <v>2.45</v>
+      </c>
+      <c r="AL35">
+        <v>1.49</v>
+      </c>
+      <c r="AM35">
+        <v>1.24</v>
+      </c>
+      <c r="AN35">
+        <v>1.1</v>
+      </c>
+      <c r="AO35">
+        <v>0</v>
+      </c>
+      <c r="AP35">
+        <v>1.36</v>
+      </c>
+      <c r="AQ35">
+        <v>1.69</v>
+      </c>
+      <c r="AR35">
+        <v>2.14</v>
+      </c>
+      <c r="AS35">
+        <v>2.7</v>
+      </c>
+      <c r="AT35">
+        <v>3.6</v>
+      </c>
+      <c r="AU35">
+        <v>2.7</v>
+      </c>
+      <c r="AV35">
+        <v>2</v>
+      </c>
+      <c r="AW35">
+        <v>1.57</v>
+      </c>
+      <c r="AX35">
+        <v>1.38</v>
+      </c>
+      <c r="AY35">
+        <v>1.23</v>
+      </c>
+      <c r="AZ35">
+        <v>2.39</v>
+      </c>
+      <c r="BA35">
+        <v>1.87</v>
+      </c>
+      <c r="BB35">
+        <v>1.32</v>
+      </c>
+      <c r="BC35">
+        <v>2.56</v>
+      </c>
+      <c r="BD35">
+        <v>2.96</v>
+      </c>
+      <c r="BE35">
+        <v>1.42</v>
+      </c>
+      <c r="BF35">
         <v>1.06</v>
-      </c>
-      <c r="AC35">
-        <v>1.31</v>
-      </c>
-      <c r="AD35">
-        <v>2.92</v>
-      </c>
-      <c r="AE35">
-        <v>2.02</v>
-      </c>
-      <c r="AF35">
-        <v>1.74</v>
-      </c>
-      <c r="AG35">
-        <v>3.42</v>
-      </c>
-      <c r="AH35">
-        <v>1.27</v>
-      </c>
-      <c r="AI35">
-        <v>6.45</v>
-      </c>
-      <c r="AJ35">
-        <v>1.05</v>
-      </c>
-      <c r="AK35">
-        <v>2.25</v>
-      </c>
-      <c r="AL35">
-        <v>1.6</v>
-      </c>
-      <c r="AM35">
-        <v>1.16</v>
-      </c>
-      <c r="AN35">
-        <v>2.72</v>
-      </c>
-      <c r="AO35">
-        <v>0</v>
-      </c>
-      <c r="AP35">
-        <v>1.24</v>
-      </c>
-      <c r="AQ35">
-        <v>1.46</v>
-      </c>
-      <c r="AR35">
-        <v>1.87</v>
-      </c>
-      <c r="AS35">
-        <v>2.33</v>
-      </c>
-      <c r="AT35">
-        <v>3.14</v>
-      </c>
-      <c r="AU35">
-        <v>3.34</v>
-      </c>
-      <c r="AV35">
-        <v>2.38</v>
-      </c>
-      <c r="AW35">
-        <v>1.83</v>
-      </c>
-      <c r="AX35">
-        <v>1.48</v>
-      </c>
-      <c r="AY35">
-        <v>1.27</v>
-      </c>
-      <c r="AZ35">
-        <v>1.29</v>
-      </c>
-      <c r="BA35">
-        <v>4.32</v>
-      </c>
-      <c r="BB35">
-        <v>1.23</v>
-      </c>
-      <c r="BC35">
-        <v>2.3</v>
-      </c>
-      <c r="BD35">
-        <v>3.42</v>
-      </c>
-      <c r="BE35">
-        <v>1.53</v>
-      </c>
-      <c r="BF35">
-        <v>1.12</v>
       </c>
       <c r="BG35">
         <v>0</v>
@@ -7469,133 +7469,133 @@
         <v>188</v>
       </c>
       <c r="P36">
+        <v>2.2</v>
+      </c>
+      <c r="Q36">
+        <v>2.8</v>
+      </c>
+      <c r="R36">
         <v>3.3</v>
       </c>
-      <c r="Q36">
+      <c r="S36">
+        <v>2.9</v>
+      </c>
+      <c r="T36">
+        <v>1.81</v>
+      </c>
+      <c r="U36">
+        <v>4.2</v>
+      </c>
+      <c r="V36">
+        <v>1.65</v>
+      </c>
+      <c r="W36">
+        <v>2.16</v>
+      </c>
+      <c r="X36">
+        <v>4.1</v>
+      </c>
+      <c r="Y36">
+        <v>1.2</v>
+      </c>
+      <c r="Z36">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AA36">
+        <v>1.02</v>
+      </c>
+      <c r="AB36">
+        <v>1.12</v>
+      </c>
+      <c r="AC36">
+        <v>1.66</v>
+      </c>
+      <c r="AD36">
+        <v>2.09</v>
+      </c>
+      <c r="AE36">
         <v>3.1</v>
       </c>
-      <c r="R36">
-        <v>2.15</v>
-      </c>
-      <c r="S36">
-        <v>4.43</v>
-      </c>
-      <c r="T36">
-        <v>1.92</v>
-      </c>
-      <c r="U36">
-        <v>3.2</v>
-      </c>
-      <c r="V36">
-        <v>1.51</v>
-      </c>
-      <c r="W36">
-        <v>2.31</v>
-      </c>
-      <c r="X36">
-        <v>3.38</v>
-      </c>
-      <c r="Y36">
+      <c r="AF36">
+        <v>1.31</v>
+      </c>
+      <c r="AG36">
+        <v>6.35</v>
+      </c>
+      <c r="AH36">
+        <v>1.06</v>
+      </c>
+      <c r="AI36">
+        <v>10.5</v>
+      </c>
+      <c r="AJ36">
+        <v>1.02</v>
+      </c>
+      <c r="AK36">
+        <v>2.4</v>
+      </c>
+      <c r="AL36">
+        <v>1.54</v>
+      </c>
+      <c r="AM36">
+        <v>1.32</v>
+      </c>
+      <c r="AN36">
+        <v>1.55</v>
+      </c>
+      <c r="AO36">
+        <v>0</v>
+      </c>
+      <c r="AP36">
+        <v>1.42</v>
+      </c>
+      <c r="AQ36">
+        <v>1.76</v>
+      </c>
+      <c r="AR36">
+        <v>2.24</v>
+      </c>
+      <c r="AS36">
+        <v>3.02</v>
+      </c>
+      <c r="AT36">
+        <v>4.36</v>
+      </c>
+      <c r="AU36">
+        <v>2.57</v>
+      </c>
+      <c r="AV36">
+        <v>1.94</v>
+      </c>
+      <c r="AW36">
+        <v>1.56</v>
+      </c>
+      <c r="AX36">
+        <v>1.3</v>
+      </c>
+      <c r="AY36">
+        <v>1.13</v>
+      </c>
+      <c r="AZ36">
+        <v>1.61</v>
+      </c>
+      <c r="BA36">
+        <v>2.96</v>
+      </c>
+      <c r="BB36">
+        <v>1.43</v>
+      </c>
+      <c r="BC36">
+        <v>3.12</v>
+      </c>
+      <c r="BD36">
+        <v>2.53</v>
+      </c>
+      <c r="BE36">
         <v>1.29</v>
       </c>
-      <c r="Z36">
-        <v>9.1</v>
-      </c>
-      <c r="AA36">
-        <v>1</v>
-      </c>
-      <c r="AB36">
-        <v>1.1</v>
-      </c>
-      <c r="AC36">
-        <v>1.43</v>
-      </c>
-      <c r="AD36">
-        <v>2.46</v>
-      </c>
-      <c r="AE36">
-        <v>2.65</v>
-      </c>
-      <c r="AF36">
-        <v>1.49</v>
-      </c>
-      <c r="AG36">
-        <v>5.1</v>
-      </c>
-      <c r="AH36">
-        <v>1.13</v>
-      </c>
-      <c r="AI36">
-        <v>9.5</v>
-      </c>
-      <c r="AJ36">
-        <v>1</v>
-      </c>
-      <c r="AK36">
-        <v>2.04</v>
-      </c>
-      <c r="AL36">
-        <v>1.62</v>
-      </c>
-      <c r="AM36">
-        <v>1.3</v>
-      </c>
-      <c r="AN36">
-        <v>1.24</v>
-      </c>
-      <c r="AO36">
-        <v>0</v>
-      </c>
-      <c r="AP36">
-        <v>1.39</v>
-      </c>
-      <c r="AQ36">
-        <v>1.72</v>
-      </c>
-      <c r="AR36">
-        <v>2.53</v>
-      </c>
-      <c r="AS36">
-        <v>2.97</v>
-      </c>
-      <c r="AT36">
-        <v>4.15</v>
-      </c>
-      <c r="AU36">
-        <v>2.66</v>
-      </c>
-      <c r="AV36">
-        <v>1.95</v>
-      </c>
-      <c r="AW36">
-        <v>1.62</v>
-      </c>
-      <c r="AX36">
-        <v>1.43</v>
-      </c>
-      <c r="AY36">
-        <v>1.15</v>
-      </c>
-      <c r="AZ36">
-        <v>2.12</v>
-      </c>
-      <c r="BA36">
-        <v>2.08</v>
-      </c>
-      <c r="BB36">
-        <v>1.32</v>
-      </c>
-      <c r="BC36">
-        <v>2.59</v>
-      </c>
-      <c r="BD36">
-        <v>2.96</v>
-      </c>
-      <c r="BE36">
-        <v>1.41</v>
-      </c>
       <c r="BF36">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="BG36">
         <v>0</v>
@@ -7654,133 +7654,133 @@
         <v>188</v>
       </c>
       <c r="P37">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q37">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="R37">
-        <v>3.3</v>
+        <v>2.15</v>
       </c>
       <c r="S37">
-        <v>2.9</v>
+        <v>4.43</v>
       </c>
       <c r="T37">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="U37">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="V37">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="W37">
-        <v>2.16</v>
+        <v>2.31</v>
       </c>
       <c r="X37">
-        <v>4.1</v>
+        <v>3.38</v>
       </c>
       <c r="Y37">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="Z37">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="AA37">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AB37">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AC37">
-        <v>1.66</v>
+        <v>1.43</v>
       </c>
       <c r="AD37">
-        <v>2.09</v>
+        <v>2.46</v>
       </c>
       <c r="AE37">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="AF37">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
       <c r="AG37">
-        <v>6.35</v>
+        <v>5.1</v>
       </c>
       <c r="AH37">
+        <v>1.13</v>
+      </c>
+      <c r="AI37">
+        <v>9.5</v>
+      </c>
+      <c r="AJ37">
+        <v>1</v>
+      </c>
+      <c r="AK37">
+        <v>2.04</v>
+      </c>
+      <c r="AL37">
+        <v>1.62</v>
+      </c>
+      <c r="AM37">
+        <v>1.3</v>
+      </c>
+      <c r="AN37">
+        <v>1.24</v>
+      </c>
+      <c r="AO37">
+        <v>0</v>
+      </c>
+      <c r="AP37">
+        <v>1.39</v>
+      </c>
+      <c r="AQ37">
+        <v>1.72</v>
+      </c>
+      <c r="AR37">
+        <v>2.53</v>
+      </c>
+      <c r="AS37">
+        <v>2.97</v>
+      </c>
+      <c r="AT37">
+        <v>4.15</v>
+      </c>
+      <c r="AU37">
+        <v>2.66</v>
+      </c>
+      <c r="AV37">
+        <v>1.95</v>
+      </c>
+      <c r="AW37">
+        <v>1.62</v>
+      </c>
+      <c r="AX37">
+        <v>1.43</v>
+      </c>
+      <c r="AY37">
+        <v>1.15</v>
+      </c>
+      <c r="AZ37">
+        <v>2.12</v>
+      </c>
+      <c r="BA37">
+        <v>2.08</v>
+      </c>
+      <c r="BB37">
+        <v>1.32</v>
+      </c>
+      <c r="BC37">
+        <v>2.59</v>
+      </c>
+      <c r="BD37">
+        <v>2.96</v>
+      </c>
+      <c r="BE37">
+        <v>1.41</v>
+      </c>
+      <c r="BF37">
         <v>1.06</v>
-      </c>
-      <c r="AI37">
-        <v>10.5</v>
-      </c>
-      <c r="AJ37">
-        <v>1.02</v>
-      </c>
-      <c r="AK37">
-        <v>2.4</v>
-      </c>
-      <c r="AL37">
-        <v>1.54</v>
-      </c>
-      <c r="AM37">
-        <v>1.32</v>
-      </c>
-      <c r="AN37">
-        <v>1.55</v>
-      </c>
-      <c r="AO37">
-        <v>0</v>
-      </c>
-      <c r="AP37">
-        <v>1.42</v>
-      </c>
-      <c r="AQ37">
-        <v>1.76</v>
-      </c>
-      <c r="AR37">
-        <v>2.24</v>
-      </c>
-      <c r="AS37">
-        <v>3.02</v>
-      </c>
-      <c r="AT37">
-        <v>4.36</v>
-      </c>
-      <c r="AU37">
-        <v>2.57</v>
-      </c>
-      <c r="AV37">
-        <v>1.94</v>
-      </c>
-      <c r="AW37">
-        <v>1.56</v>
-      </c>
-      <c r="AX37">
-        <v>1.3</v>
-      </c>
-      <c r="AY37">
-        <v>1.13</v>
-      </c>
-      <c r="AZ37">
-        <v>1.61</v>
-      </c>
-      <c r="BA37">
-        <v>2.96</v>
-      </c>
-      <c r="BB37">
-        <v>1.43</v>
-      </c>
-      <c r="BC37">
-        <v>3.12</v>
-      </c>
-      <c r="BD37">
-        <v>2.53</v>
-      </c>
-      <c r="BE37">
-        <v>1.29</v>
-      </c>
-      <c r="BF37">
-        <v>1.02</v>
       </c>
       <c r="BG37">
         <v>0</v>
@@ -7839,79 +7839,79 @@
         <v>188</v>
       </c>
       <c r="P38">
-        <v>2</v>
+        <v>5.75</v>
       </c>
       <c r="Q38">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="R38">
-        <v>3.95</v>
+        <v>1.52</v>
       </c>
       <c r="S38">
-        <v>2.88</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="T38">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="U38">
-        <v>5.1</v>
+        <v>2.1</v>
       </c>
       <c r="V38">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="W38">
-        <v>2.11</v>
+        <v>2.44</v>
       </c>
       <c r="X38">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="Y38">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="Z38">
-        <v>13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA38">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AB38">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AC38">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="AD38">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="AE38">
-        <v>2.74</v>
+        <v>2.53</v>
       </c>
       <c r="AF38">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="AG38">
-        <v>6.33</v>
+        <v>4.65</v>
       </c>
       <c r="AH38">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AI38">
-        <v>9.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AJ38">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AK38">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="AL38">
         <v>1.53</v>
       </c>
       <c r="AM38">
-        <v>1.35</v>
+        <v>2.31</v>
       </c>
       <c r="AN38">
-        <v>1.63</v>
+        <v>1.04</v>
       </c>
       <c r="AO38">
         <v>0</v>
@@ -7920,52 +7920,52 @@
         <v>1.42</v>
       </c>
       <c r="AQ38">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AR38">
+        <v>2.73</v>
+      </c>
+      <c r="AS38">
+        <v>3.04</v>
+      </c>
+      <c r="AT38">
+        <v>4.41</v>
+      </c>
+      <c r="AU38">
         <v>2.7</v>
       </c>
-      <c r="AS38">
-        <v>3</v>
-      </c>
-      <c r="AT38">
-        <v>4.34</v>
-      </c>
-      <c r="AU38">
-        <v>2.58</v>
-      </c>
       <c r="AV38">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AW38">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AX38">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AY38">
         <v>1.13</v>
       </c>
       <c r="AZ38">
-        <v>1.52</v>
+        <v>3.85</v>
       </c>
       <c r="BA38">
-        <v>3.26</v>
+        <v>1.43</v>
       </c>
       <c r="BB38">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="BC38">
-        <v>2.9</v>
+        <v>2.59</v>
       </c>
       <c r="BD38">
-        <v>2.66</v>
+        <v>2.91</v>
       </c>
       <c r="BE38">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="BF38">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BG38">
         <v>0</v>
@@ -8024,79 +8024,79 @@
         <v>188</v>
       </c>
       <c r="P39">
-        <v>5.75</v>
+        <v>2</v>
       </c>
       <c r="Q39">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="R39">
-        <v>1.52</v>
+        <v>3.95</v>
       </c>
       <c r="S39">
-        <v>8.050000000000001</v>
+        <v>2.88</v>
       </c>
       <c r="T39">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="U39">
-        <v>2.1</v>
+        <v>5.1</v>
       </c>
       <c r="V39">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="W39">
-        <v>2.44</v>
+        <v>2.11</v>
       </c>
       <c r="X39">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="Y39">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="Z39">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AA39">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AB39">
+        <v>1.08</v>
+      </c>
+      <c r="AC39">
+        <v>1.58</v>
+      </c>
+      <c r="AD39">
+        <v>2.25</v>
+      </c>
+      <c r="AE39">
+        <v>2.74</v>
+      </c>
+      <c r="AF39">
+        <v>1.35</v>
+      </c>
+      <c r="AG39">
+        <v>6.33</v>
+      </c>
+      <c r="AH39">
         <v>1.07</v>
       </c>
-      <c r="AC39">
-        <v>1.38</v>
-      </c>
-      <c r="AD39">
-        <v>2.43</v>
-      </c>
-      <c r="AE39">
-        <v>2.53</v>
-      </c>
-      <c r="AF39">
-        <v>1.49</v>
-      </c>
-      <c r="AG39">
-        <v>4.65</v>
-      </c>
-      <c r="AH39">
-        <v>1.12</v>
-      </c>
       <c r="AI39">
-        <v>8.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AJ39">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AK39">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="AL39">
         <v>1.53</v>
       </c>
       <c r="AM39">
-        <v>2.31</v>
+        <v>1.35</v>
       </c>
       <c r="AN39">
-        <v>1.04</v>
+        <v>1.63</v>
       </c>
       <c r="AO39">
         <v>0</v>
@@ -8105,52 +8105,52 @@
         <v>1.42</v>
       </c>
       <c r="AQ39">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AR39">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="AS39">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="AT39">
-        <v>4.41</v>
+        <v>4.34</v>
       </c>
       <c r="AU39">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="AV39">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AW39">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AX39">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AY39">
         <v>1.13</v>
       </c>
       <c r="AZ39">
-        <v>3.85</v>
+        <v>1.52</v>
       </c>
       <c r="BA39">
-        <v>1.43</v>
+        <v>3.26</v>
       </c>
       <c r="BB39">
+        <v>1.39</v>
+      </c>
+      <c r="BC39">
+        <v>2.9</v>
+      </c>
+      <c r="BD39">
+        <v>2.66</v>
+      </c>
+      <c r="BE39">
         <v>1.33</v>
       </c>
-      <c r="BC39">
-        <v>2.59</v>
-      </c>
-      <c r="BD39">
-        <v>2.91</v>
-      </c>
-      <c r="BE39">
-        <v>1.41</v>
-      </c>
       <c r="BF39">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="BG39">
         <v>0</v>

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -310,12 +310,12 @@
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
+    <t>Egypt Egyptian Premier League</t>
+  </si>
+  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
-    <t>Egypt Egyptian Premier League</t>
-  </si>
-  <si>
     <t>South Africa Premier Soccer League</t>
   </si>
   <si>
@@ -337,48 +337,48 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Jeonbuk Motors</t>
+  </si>
+  <si>
     <t>Bucheon 1995</t>
   </si>
   <si>
-    <t>Jeonbuk Motors</t>
+    <t>Gangwon</t>
+  </si>
+  <si>
+    <t>Sangju Sangmu</t>
   </si>
   <si>
     <t>Daejeon Citizen</t>
   </si>
   <si>
-    <t>Sangju Sangmu</t>
-  </si>
-  <si>
-    <t>Gangwon</t>
-  </si>
-  <si>
     <t>Madura United</t>
   </si>
   <si>
+    <t>Ethiopia Nigd Bank</t>
+  </si>
+  <si>
     <t>FC Seoul</t>
   </si>
   <si>
-    <t>Ethiopia Nigd Bank</t>
-  </si>
-  <si>
     <t>Qingdao Youth Island</t>
   </si>
   <si>
     <t>Tanjong Pagar</t>
   </si>
   <si>
+    <t>Shandong Luneng</t>
+  </si>
+  <si>
     <t>Shenyang Urban</t>
   </si>
   <si>
-    <t>Shandong Luneng</t>
+    <t>Chongqing Tongliang Long</t>
   </si>
   <si>
     <t>Karvan FK</t>
   </si>
   <si>
-    <t>Chongqing Tongliang Long</t>
-  </si>
-  <si>
     <t>Dire Dawa Kenema</t>
   </si>
   <si>
@@ -415,42 +415,42 @@
     <t>Maccabi Tel Aviv</t>
   </si>
   <si>
+    <t>Dibba Al Fujairah</t>
+  </si>
+  <si>
     <t>Bani Yas</t>
   </si>
   <si>
-    <t>Dibba Al Fujairah</t>
-  </si>
-  <si>
     <t>Al Ittihad Kalba</t>
   </si>
   <si>
+    <t>Smouha SC</t>
+  </si>
+  <si>
     <t>Falkenberg</t>
   </si>
   <si>
+    <t>Lokomotiv Sofia 1929</t>
+  </si>
+  <si>
     <t>Ceramica Cleopatra</t>
   </si>
   <si>
-    <t>Lokomotiv Sofia 1929</t>
-  </si>
-  <si>
     <t>Al Ahly</t>
   </si>
   <si>
-    <t>Smouha SC</t>
-  </si>
-  <si>
     <t>Siwelele</t>
   </si>
   <si>
+    <t>Magesi</t>
+  </si>
+  <si>
+    <t>Stellenbosch</t>
+  </si>
+  <si>
     <t>Chippa United</t>
   </si>
   <si>
-    <t>Stellenbosch</t>
-  </si>
-  <si>
-    <t>Magesi</t>
-  </si>
-  <si>
     <t>Al Khaleej</t>
   </si>
   <si>
@@ -460,48 +460,48 @@
     <t>New York City II</t>
   </si>
   <si>
+    <t>Gwangju</t>
+  </si>
+  <si>
     <t>Jeju United</t>
   </si>
   <si>
-    <t>Gwangju</t>
+    <t>Pohang Steelers</t>
+  </si>
+  <si>
+    <t>Ulsan</t>
   </si>
   <si>
     <t>Incheon United</t>
   </si>
   <si>
-    <t>Ulsan</t>
-  </si>
-  <si>
-    <t>Pohang Steelers</t>
-  </si>
-  <si>
     <t>Bali United</t>
   </si>
   <si>
+    <t>Kedus Giorgis</t>
+  </si>
+  <si>
     <t>Anyang</t>
   </si>
   <si>
-    <t>Kedus Giorgis</t>
-  </si>
-  <si>
     <t>Tianjin Teda</t>
   </si>
   <si>
     <t>Hougang United</t>
   </si>
   <si>
+    <t>Shanghai Shenhua</t>
+  </si>
+  <si>
     <t>Chengdu Better City FC</t>
   </si>
   <si>
-    <t>Shanghai Shenhua</t>
+    <t>Henan Jianye</t>
   </si>
   <si>
     <t>Neftçi</t>
   </si>
   <si>
-    <t>Henan Jianye</t>
-  </si>
-  <si>
     <t>Ethiopia Bunna</t>
   </si>
   <si>
@@ -538,37 +538,37 @@
     <t>Hapoel Petah Tikva</t>
   </si>
   <si>
+    <t>Al Bataeh</t>
+  </si>
+  <si>
     <t>Al Dhafra</t>
   </si>
   <si>
-    <t>Al Bataeh</t>
+    <t>Zamalek</t>
   </si>
   <si>
     <t>Norrköping</t>
   </si>
   <si>
+    <t>Botev Vratsa</t>
+  </si>
+  <si>
     <t>Pyramids FC</t>
   </si>
   <si>
-    <t>Botev Vratsa</t>
-  </si>
-  <si>
     <t>ENPPI</t>
   </si>
   <si>
-    <t>Zamalek</t>
-  </si>
-  <si>
     <t>Durban City</t>
   </si>
   <si>
+    <t>Orbit College</t>
+  </si>
+  <si>
+    <t>Orlando Pirates</t>
+  </si>
+  <si>
     <t>Sekhukhune United</t>
-  </si>
-  <si>
-    <t>Orlando Pirates</t>
-  </si>
-  <si>
-    <t>Orbit College</t>
   </si>
   <si>
     <t>Al Hilal</t>
@@ -1179,133 +1179,133 @@
         <v>188</v>
       </c>
       <c r="P2">
-        <v>2.47</v>
+        <v>1.34</v>
       </c>
       <c r="Q2">
-        <v>3.2</v>
+        <v>4.35</v>
       </c>
       <c r="R2">
-        <v>2.8</v>
+        <v>7.91</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AE2">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="AF2">
+        <v>1.85</v>
+      </c>
+      <c r="AG2">
+        <v>3.4</v>
+      </c>
+      <c r="AH2">
+        <v>1.27</v>
+      </c>
+      <c r="AI2">
+        <v>6.1</v>
+      </c>
+      <c r="AJ2">
+        <v>1.06</v>
+      </c>
+      <c r="AK2">
+        <v>2.26</v>
+      </c>
+      <c r="AL2">
         <v>1.57</v>
       </c>
-      <c r="AG2">
-        <v>0</v>
-      </c>
-      <c r="AH2">
-        <v>0</v>
-      </c>
-      <c r="AI2">
-        <v>0</v>
-      </c>
-      <c r="AJ2">
-        <v>0</v>
-      </c>
-      <c r="AK2">
-        <v>0</v>
-      </c>
-      <c r="AL2">
-        <v>0</v>
-      </c>
       <c r="AM2">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AO2">
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AU2">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AV2">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AW2">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AX2">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AY2">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AZ2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BA2">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BB2">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC2">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="BD2">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BE2">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF2">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG2">
         <v>0</v>
@@ -1364,133 +1364,133 @@
         <v>188</v>
       </c>
       <c r="P3">
-        <v>1.33</v>
+        <v>2.45</v>
       </c>
       <c r="Q3">
-        <v>4.5</v>
+        <v>3.15</v>
       </c>
       <c r="R3">
-        <v>7.75</v>
+        <v>2.8</v>
       </c>
       <c r="S3">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>8.15</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y3">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z3">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC3">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AD3">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AE3">
-        <v>1.96</v>
+        <v>2.35</v>
       </c>
       <c r="AF3">
-        <v>1.88</v>
+        <v>1.57</v>
       </c>
       <c r="AG3">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AH3">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK3">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AL3">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AN3">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AO3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AQ3">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AR3">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AS3">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AT3">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="AU3">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV3">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AW3">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AX3">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AY3">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AZ3">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BA3">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BB3">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC3">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="BD3">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BE3">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BF3">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG3">
         <v>0</v>
@@ -1549,133 +1549,133 @@
         <v>188</v>
       </c>
       <c r="P4">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q4">
-        <v>3.29</v>
+        <v>3.15</v>
       </c>
       <c r="R4">
-        <v>3.19</v>
+        <v>3.64</v>
       </c>
       <c r="S4">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="T4">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="U4">
-        <v>4.06</v>
+        <v>4.76</v>
       </c>
       <c r="V4">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W4">
-        <v>2.59</v>
+        <v>2.34</v>
       </c>
       <c r="X4">
+        <v>3.4</v>
+      </c>
+      <c r="Y4">
+        <v>1.27</v>
+      </c>
+      <c r="Z4">
+        <v>8.5</v>
+      </c>
+      <c r="AA4">
+        <v>1.01</v>
+      </c>
+      <c r="AB4">
+        <v>1.05</v>
+      </c>
+      <c r="AC4">
+        <v>1.47</v>
+      </c>
+      <c r="AD4">
+        <v>2.7</v>
+      </c>
+      <c r="AE4">
+        <v>2.38</v>
+      </c>
+      <c r="AF4">
+        <v>1.53</v>
+      </c>
+      <c r="AG4">
+        <v>4.5</v>
+      </c>
+      <c r="AH4">
+        <v>1.15</v>
+      </c>
+      <c r="AI4">
+        <v>9</v>
+      </c>
+      <c r="AJ4">
+        <v>1.01</v>
+      </c>
+      <c r="AK4">
+        <v>1.94</v>
+      </c>
+      <c r="AL4">
+        <v>1.68</v>
+      </c>
+      <c r="AM4">
+        <v>1.33</v>
+      </c>
+      <c r="AN4">
+        <v>1.71</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>1.53</v>
+      </c>
+      <c r="AQ4">
+        <v>1.92</v>
+      </c>
+      <c r="AR4">
+        <v>3.14</v>
+      </c>
+      <c r="AS4">
+        <v>3.48</v>
+      </c>
+      <c r="AT4">
+        <v>5.23</v>
+      </c>
+      <c r="AU4">
+        <v>2.31</v>
+      </c>
+      <c r="AV4">
+        <v>1.79</v>
+      </c>
+      <c r="AW4">
+        <v>1.45</v>
+      </c>
+      <c r="AX4">
+        <v>1.22</v>
+      </c>
+      <c r="AY4">
+        <v>1.08</v>
+      </c>
+      <c r="AZ4">
+        <v>1.65</v>
+      </c>
+      <c r="BA4">
+        <v>3.1</v>
+      </c>
+      <c r="BB4">
+        <v>1.33</v>
+      </c>
+      <c r="BC4">
+        <v>2.53</v>
+      </c>
+      <c r="BD4">
         <v>3.04</v>
       </c>
-      <c r="Y4">
-        <v>1.33</v>
-      </c>
-      <c r="Z4">
-        <v>7.6</v>
-      </c>
-      <c r="AA4">
-        <v>1.03</v>
-      </c>
-      <c r="AB4">
-        <v>1.02</v>
-      </c>
-      <c r="AC4">
-        <v>1.35</v>
-      </c>
-      <c r="AD4">
-        <v>3.19</v>
-      </c>
-      <c r="AE4">
-        <v>2.04</v>
-      </c>
-      <c r="AF4">
-        <v>1.72</v>
-      </c>
-      <c r="AG4">
-        <v>3.54</v>
-      </c>
-      <c r="AH4">
-        <v>1.22</v>
-      </c>
-      <c r="AI4">
-        <v>7.5</v>
-      </c>
-      <c r="AJ4">
-        <v>1.04</v>
-      </c>
-      <c r="AK4">
-        <v>1.78</v>
-      </c>
-      <c r="AL4">
-        <v>1.88</v>
-      </c>
-      <c r="AM4">
-        <v>1.35</v>
-      </c>
-      <c r="AN4">
-        <v>1.62</v>
-      </c>
-      <c r="AO4">
-        <v>0</v>
-      </c>
-      <c r="AP4">
-        <v>1.51</v>
-      </c>
-      <c r="AQ4">
-        <v>1.9</v>
-      </c>
-      <c r="AR4">
-        <v>2.46</v>
-      </c>
-      <c r="AS4">
-        <v>3.42</v>
-      </c>
-      <c r="AT4">
-        <v>5.11</v>
-      </c>
-      <c r="AU4">
-        <v>2.34</v>
-      </c>
-      <c r="AV4">
-        <v>1.81</v>
-      </c>
-      <c r="AW4">
+      <c r="BE4">
         <v>1.46</v>
       </c>
-      <c r="AX4">
-        <v>1.23</v>
-      </c>
-      <c r="AY4">
-        <v>1.11</v>
-      </c>
-      <c r="AZ4">
-        <v>1.72</v>
-      </c>
-      <c r="BA4">
-        <v>2.3</v>
-      </c>
-      <c r="BB4">
-        <v>1.24</v>
-      </c>
-      <c r="BC4">
-        <v>2.3</v>
-      </c>
-      <c r="BD4">
-        <v>3.5</v>
-      </c>
-      <c r="BE4">
-        <v>1.59</v>
-      </c>
       <c r="BF4">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="BG4">
         <v>0</v>
@@ -1743,7 +1743,7 @@
         <v>0</v>
       </c>
       <c r="S5">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="T5">
         <v>2.05</v>
@@ -1758,7 +1758,7 @@
         <v>2.77</v>
       </c>
       <c r="X5">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="Y5">
         <v>1.36</v>
@@ -1773,7 +1773,7 @@
         <v>1.02</v>
       </c>
       <c r="AC5">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AD5">
         <v>3.18</v>
@@ -1788,13 +1788,13 @@
         <v>3.48</v>
       </c>
       <c r="AH5">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AI5">
         <v>6.73</v>
       </c>
       <c r="AJ5">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AK5">
         <v>1.73</v>
@@ -1827,7 +1827,7 @@
         <v>4.16</v>
       </c>
       <c r="AU5">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="AV5">
         <v>2.1</v>
@@ -1845,7 +1845,7 @@
         <v>1.81</v>
       </c>
       <c r="BA5">
-        <v>2.17</v>
+        <v>2.6</v>
       </c>
       <c r="BB5">
         <v>1.22</v>
@@ -1919,133 +1919,133 @@
         <v>188</v>
       </c>
       <c r="P6">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="Q6">
+        <v>3.3</v>
+      </c>
+      <c r="R6">
         <v>3.1</v>
       </c>
-      <c r="R6">
-        <v>3.4</v>
-      </c>
       <c r="S6">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="T6">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="U6">
-        <v>4.76</v>
+        <v>4.06</v>
       </c>
       <c r="V6">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W6">
+        <v>2.59</v>
+      </c>
+      <c r="X6">
+        <v>3.04</v>
+      </c>
+      <c r="Y6">
+        <v>1.33</v>
+      </c>
+      <c r="Z6">
+        <v>7.6</v>
+      </c>
+      <c r="AA6">
+        <v>1.03</v>
+      </c>
+      <c r="AB6">
+        <v>1.06</v>
+      </c>
+      <c r="AC6">
+        <v>1.35</v>
+      </c>
+      <c r="AD6">
+        <v>2.94</v>
+      </c>
+      <c r="AE6">
+        <v>2.1</v>
+      </c>
+      <c r="AF6">
+        <v>1.72</v>
+      </c>
+      <c r="AG6">
+        <v>3.65</v>
+      </c>
+      <c r="AH6">
+        <v>1.22</v>
+      </c>
+      <c r="AI6">
+        <v>6.75</v>
+      </c>
+      <c r="AJ6">
+        <v>1.04</v>
+      </c>
+      <c r="AK6">
+        <v>1.82</v>
+      </c>
+      <c r="AL6">
+        <v>1.82</v>
+      </c>
+      <c r="AM6">
+        <v>1.35</v>
+      </c>
+      <c r="AN6">
+        <v>1.62</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>1.51</v>
+      </c>
+      <c r="AQ6">
+        <v>1.9</v>
+      </c>
+      <c r="AR6">
+        <v>3.08</v>
+      </c>
+      <c r="AS6">
+        <v>3.42</v>
+      </c>
+      <c r="AT6">
+        <v>5.11</v>
+      </c>
+      <c r="AU6">
         <v>2.34</v>
       </c>
-      <c r="X6">
-        <v>3.4</v>
-      </c>
-      <c r="Y6">
-        <v>1.27</v>
-      </c>
-      <c r="Z6">
-        <v>8.5</v>
-      </c>
-      <c r="AA6">
-        <v>1.01</v>
-      </c>
-      <c r="AB6">
-        <v>1.09</v>
-      </c>
-      <c r="AC6">
-        <v>1.42</v>
-      </c>
-      <c r="AD6">
-        <v>2.7</v>
-      </c>
-      <c r="AE6">
-        <v>2.38</v>
-      </c>
-      <c r="AF6">
-        <v>1.55</v>
-      </c>
-      <c r="AG6">
-        <v>4.5</v>
-      </c>
-      <c r="AH6">
-        <v>1.15</v>
-      </c>
-      <c r="AI6">
-        <v>9</v>
-      </c>
-      <c r="AJ6">
-        <v>1.01</v>
-      </c>
-      <c r="AK6">
-        <v>1.94</v>
-      </c>
-      <c r="AL6">
-        <v>1.68</v>
-      </c>
-      <c r="AM6">
-        <v>1.33</v>
-      </c>
-      <c r="AN6">
-        <v>1.71</v>
-      </c>
-      <c r="AO6">
-        <v>0</v>
-      </c>
-      <c r="AP6">
-        <v>1.53</v>
-      </c>
-      <c r="AQ6">
-        <v>1.92</v>
-      </c>
-      <c r="AR6">
-        <v>2.39</v>
-      </c>
-      <c r="AS6">
-        <v>3.48</v>
-      </c>
-      <c r="AT6">
-        <v>5.23</v>
-      </c>
-      <c r="AU6">
-        <v>2.31</v>
-      </c>
       <c r="AV6">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AW6">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AX6">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AY6">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AZ6">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="BA6">
-        <v>3.1</v>
+        <v>2.21</v>
       </c>
       <c r="BB6">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="BC6">
-        <v>2.53</v>
+        <v>2.3</v>
       </c>
       <c r="BD6">
-        <v>3.04</v>
+        <v>3.5</v>
       </c>
       <c r="BE6">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="BF6">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="BG6">
         <v>0</v>
@@ -2250,10 +2250,10 @@
         <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E8" t="s">
         <v>113</v>
@@ -2289,133 +2289,133 @@
         <v>188</v>
       </c>
       <c r="P8">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R8">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="X8">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Y8">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA8">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC8">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD8">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AE8">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AH8">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK8">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AL8">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN8">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AO8">
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ8">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AR8">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AS8">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AT8">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AU8">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AV8">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AW8">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AX8">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AY8">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ8">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="BA8">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="BB8">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC8">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD8">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE8">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF8">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG8">
         <v>0</v>
@@ -2435,10 +2435,10 @@
         <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E9" t="s">
         <v>114</v>
@@ -2474,133 +2474,133 @@
         <v>188</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AO9">
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AU9">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AV9">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AX9">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ9">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BA9">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD9">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE9">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG9">
         <v>0</v>
@@ -2683,13 +2683,13 @@
         <v>2.66</v>
       </c>
       <c r="X10">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="Y10">
         <v>1.36</v>
       </c>
       <c r="Z10">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="AA10">
         <v>1.04</v>
@@ -2710,7 +2710,7 @@
         <v>1.79</v>
       </c>
       <c r="AG10">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="AH10">
         <v>1.29</v>
@@ -2737,40 +2737,40 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AQ10">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AR10">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="AS10">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="AT10">
-        <v>2.94</v>
+        <v>3.11</v>
       </c>
       <c r="AU10">
-        <v>3.57</v>
+        <v>3.37</v>
       </c>
       <c r="AV10">
-        <v>2.51</v>
+        <v>2.4</v>
       </c>
       <c r="AW10">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AX10">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AY10">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AZ10">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="BA10">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="BB10">
         <v>1.24</v>
@@ -3029,133 +3029,133 @@
         <v>188</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S12">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="T12">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="U12">
-        <v>2.01</v>
+        <v>2.78</v>
       </c>
       <c r="V12">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W12">
-        <v>3.16</v>
+        <v>3.6</v>
       </c>
       <c r="X12">
-        <v>2.47</v>
+        <v>2.08</v>
       </c>
       <c r="Y12">
-        <v>1.47</v>
+        <v>1.69</v>
       </c>
       <c r="Z12">
+        <v>4.45</v>
+      </c>
+      <c r="AA12">
+        <v>1.15</v>
+      </c>
+      <c r="AB12">
+        <v>1.02</v>
+      </c>
+      <c r="AC12">
+        <v>1.13</v>
+      </c>
+      <c r="AD12">
+        <v>5.65</v>
+      </c>
+      <c r="AE12">
+        <v>1.44</v>
+      </c>
+      <c r="AF12">
+        <v>2.59</v>
+      </c>
+      <c r="AG12">
+        <v>2.05</v>
+      </c>
+      <c r="AH12">
+        <v>1.76</v>
+      </c>
+      <c r="AI12">
+        <v>3.28</v>
+      </c>
+      <c r="AJ12">
+        <v>1.25</v>
+      </c>
+      <c r="AK12">
+        <v>1.36</v>
+      </c>
+      <c r="AL12">
+        <v>2.9</v>
+      </c>
+      <c r="AM12">
+        <v>1.28</v>
+      </c>
+      <c r="AN12">
+        <v>1.43</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>1.08</v>
+      </c>
+      <c r="AQ12">
+        <v>1.25</v>
+      </c>
+      <c r="AR12">
+        <v>1.44</v>
+      </c>
+      <c r="AS12">
+        <v>1.81</v>
+      </c>
+      <c r="AT12">
+        <v>2.26</v>
+      </c>
+      <c r="AU12">
+        <v>5.06</v>
+      </c>
+      <c r="AV12">
+        <v>3.31</v>
+      </c>
+      <c r="AW12">
+        <v>2.46</v>
+      </c>
+      <c r="AX12">
+        <v>1.89</v>
+      </c>
+      <c r="AY12">
+        <v>1.55</v>
+      </c>
+      <c r="AZ12">
+        <v>1.92</v>
+      </c>
+      <c r="BA12">
+        <v>2.1</v>
+      </c>
+      <c r="BB12">
+        <v>1.08</v>
+      </c>
+      <c r="BC12">
+        <v>1.62</v>
+      </c>
+      <c r="BD12">
         <v>5.7</v>
       </c>
-      <c r="AA12">
-        <v>1.08</v>
-      </c>
-      <c r="AB12">
-        <v>1.03</v>
-      </c>
-      <c r="AC12">
-        <v>1.18</v>
-      </c>
-      <c r="AD12">
-        <v>3.88</v>
-      </c>
-      <c r="AE12">
-        <v>1.74</v>
-      </c>
-      <c r="AF12">
-        <v>2.12</v>
-      </c>
-      <c r="AG12">
-        <v>2.9</v>
-      </c>
-      <c r="AH12">
-        <v>1.36</v>
-      </c>
-      <c r="AI12">
-        <v>5.2</v>
-      </c>
-      <c r="AJ12">
-        <v>1.11</v>
-      </c>
-      <c r="AK12">
-        <v>1.8</v>
-      </c>
-      <c r="AL12">
-        <v>1.9</v>
-      </c>
-      <c r="AM12">
-        <v>1.21</v>
-      </c>
-      <c r="AN12">
-        <v>1.13</v>
-      </c>
-      <c r="AO12">
-        <v>0</v>
-      </c>
-      <c r="AP12">
-        <v>1.19</v>
-      </c>
-      <c r="AQ12">
-        <v>1.44</v>
-      </c>
-      <c r="AR12">
-        <v>1.94</v>
-      </c>
-      <c r="AS12">
-        <v>2.16</v>
-      </c>
-      <c r="AT12">
-        <v>2.84</v>
-      </c>
-      <c r="AU12">
-        <v>3.72</v>
-      </c>
-      <c r="AV12">
-        <v>2.55</v>
-      </c>
-      <c r="AW12">
-        <v>1.98</v>
-      </c>
-      <c r="AX12">
-        <v>1.61</v>
-      </c>
-      <c r="AY12">
-        <v>1.34</v>
-      </c>
-      <c r="AZ12">
-        <v>5.03</v>
-      </c>
-      <c r="BA12">
-        <v>1.4</v>
-      </c>
-      <c r="BB12">
-        <v>1.16</v>
-      </c>
-      <c r="BC12">
-        <v>1.94</v>
-      </c>
-      <c r="BD12">
-        <v>4.2</v>
-      </c>
       <c r="BE12">
-        <v>1.79</v>
+        <v>2.19</v>
       </c>
       <c r="BF12">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="BG12">
         <v>0</v>
@@ -3214,133 +3214,133 @@
         <v>188</v>
       </c>
       <c r="P13">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q13">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R13">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S13">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="T13">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="U13">
-        <v>2.78</v>
+        <v>2</v>
       </c>
       <c r="V13">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="W13">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="X13">
-        <v>2.08</v>
+        <v>2.41</v>
       </c>
       <c r="Y13">
-        <v>1.69</v>
+        <v>1.49</v>
       </c>
       <c r="Z13">
-        <v>4.45</v>
+        <v>5.5</v>
       </c>
       <c r="AA13">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AB13">
         <v>1.02</v>
       </c>
       <c r="AC13">
+        <v>1.17</v>
+      </c>
+      <c r="AD13">
+        <v>4</v>
+      </c>
+      <c r="AE13">
+        <v>1.68</v>
+      </c>
+      <c r="AF13">
+        <v>2.16</v>
+      </c>
+      <c r="AG13">
+        <v>2.65</v>
+      </c>
+      <c r="AH13">
+        <v>1.39</v>
+      </c>
+      <c r="AI13">
+        <v>5.2</v>
+      </c>
+      <c r="AJ13">
+        <v>1.12</v>
+      </c>
+      <c r="AK13">
+        <v>1.77</v>
+      </c>
+      <c r="AL13">
+        <v>1.94</v>
+      </c>
+      <c r="AM13">
+        <v>1.21</v>
+      </c>
+      <c r="AN13">
         <v>1.13</v>
       </c>
-      <c r="AD13">
-        <v>5.65</v>
-      </c>
-      <c r="AE13">
-        <v>1.39</v>
-      </c>
-      <c r="AF13">
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>1.19</v>
+      </c>
+      <c r="AQ13">
+        <v>1.41</v>
+      </c>
+      <c r="AR13">
+        <v>1.94</v>
+      </c>
+      <c r="AS13">
+        <v>2.16</v>
+      </c>
+      <c r="AT13">
+        <v>2.84</v>
+      </c>
+      <c r="AU13">
+        <v>3.72</v>
+      </c>
+      <c r="AV13">
         <v>2.59</v>
       </c>
-      <c r="AG13">
-        <v>2.09</v>
-      </c>
-      <c r="AH13">
-        <v>1.76</v>
-      </c>
-      <c r="AI13">
-        <v>3.33</v>
-      </c>
-      <c r="AJ13">
-        <v>1.25</v>
-      </c>
-      <c r="AK13">
-        <v>1.36</v>
-      </c>
-      <c r="AL13">
-        <v>2.75</v>
-      </c>
-      <c r="AM13">
-        <v>1.28</v>
-      </c>
-      <c r="AN13">
-        <v>1.43</v>
-      </c>
-      <c r="AO13">
-        <v>0</v>
-      </c>
-      <c r="AP13">
-        <v>1.1</v>
-      </c>
-      <c r="AQ13">
-        <v>1.24</v>
-      </c>
-      <c r="AR13">
-        <v>1.5</v>
-      </c>
-      <c r="AS13">
-        <v>1.8</v>
-      </c>
-      <c r="AT13">
-        <v>2.24</v>
-      </c>
-      <c r="AU13">
-        <v>5.1</v>
-      </c>
-      <c r="AV13">
-        <v>3.33</v>
-      </c>
       <c r="AW13">
-        <v>2.46</v>
+        <v>1.98</v>
       </c>
       <c r="AX13">
-        <v>1.92</v>
+        <v>1.61</v>
       </c>
       <c r="AY13">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="AZ13">
-        <v>1.92</v>
+        <v>5.03</v>
       </c>
       <c r="BA13">
-        <v>2.1</v>
+        <v>1.29</v>
       </c>
       <c r="BB13">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="BC13">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="BD13">
-        <v>5.7</v>
+        <v>4.33</v>
       </c>
       <c r="BE13">
-        <v>2.19</v>
+        <v>1.82</v>
       </c>
       <c r="BF13">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="BG13">
         <v>0</v>
@@ -3360,10 +3360,10 @@
         <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E14" t="s">
         <v>119</v>
@@ -3408,124 +3408,124 @@
         <v>0</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC14">
-        <v>1.12</v>
+        <v>1.35</v>
       </c>
       <c r="AD14">
-        <v>4.8</v>
+        <v>2.92</v>
       </c>
       <c r="AE14">
-        <v>1.45</v>
+        <v>2.14</v>
       </c>
       <c r="AF14">
-        <v>2.43</v>
+        <v>1.72</v>
       </c>
       <c r="AG14">
-        <v>2.14</v>
+        <v>3.73</v>
       </c>
       <c r="AH14">
-        <v>1.58</v>
+        <v>1.21</v>
       </c>
       <c r="AI14">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="AJ14">
-        <v>1.23</v>
+        <v>1.03</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM14">
+        <v>1.36</v>
+      </c>
+      <c r="AN14">
+        <v>1.46</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>1.09</v>
+      </c>
+      <c r="AQ14">
+        <v>1.26</v>
+      </c>
+      <c r="AR14">
+        <v>1.51</v>
+      </c>
+      <c r="AS14">
+        <v>1.84</v>
+      </c>
+      <c r="AT14">
+        <v>2.31</v>
+      </c>
+      <c r="AU14">
+        <v>4.89</v>
+      </c>
+      <c r="AV14">
+        <v>3.22</v>
+      </c>
+      <c r="AW14">
+        <v>2.35</v>
+      </c>
+      <c r="AX14">
+        <v>1.86</v>
+      </c>
+      <c r="AY14">
+        <v>1.53</v>
+      </c>
+      <c r="AZ14">
+        <v>1.82</v>
+      </c>
+      <c r="BA14">
+        <v>2.45</v>
+      </c>
+      <c r="BB14">
+        <v>1.24</v>
+      </c>
+      <c r="BC14">
+        <v>2.29</v>
+      </c>
+      <c r="BD14">
+        <v>3.44</v>
+      </c>
+      <c r="BE14">
+        <v>1.57</v>
+      </c>
+      <c r="BF14">
         <v>1.11</v>
-      </c>
-      <c r="AN14">
-        <v>1.05</v>
-      </c>
-      <c r="AO14">
-        <v>0</v>
-      </c>
-      <c r="AP14">
-        <v>0</v>
-      </c>
-      <c r="AQ14">
-        <v>0</v>
-      </c>
-      <c r="AR14">
-        <v>0</v>
-      </c>
-      <c r="AS14">
-        <v>0</v>
-      </c>
-      <c r="AT14">
-        <v>0</v>
-      </c>
-      <c r="AU14">
-        <v>0</v>
-      </c>
-      <c r="AV14">
-        <v>0</v>
-      </c>
-      <c r="AW14">
-        <v>0</v>
-      </c>
-      <c r="AX14">
-        <v>0</v>
-      </c>
-      <c r="AY14">
-        <v>0</v>
-      </c>
-      <c r="AZ14">
-        <v>0</v>
-      </c>
-      <c r="BA14">
-        <v>0</v>
-      </c>
-      <c r="BB14">
-        <v>0</v>
-      </c>
-      <c r="BC14">
-        <v>0</v>
-      </c>
-      <c r="BD14">
-        <v>0</v>
-      </c>
-      <c r="BE14">
-        <v>0</v>
-      </c>
-      <c r="BF14">
-        <v>0</v>
       </c>
       <c r="BG14">
         <v>0</v>
@@ -3545,10 +3545,10 @@
         <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E15" t="s">
         <v>120</v>
@@ -3584,13 +3584,13 @@
         <v>188</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -4324,13 +4324,13 @@
         <v>188</v>
       </c>
       <c r="P19">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="Q19">
-        <v>3.36</v>
+        <v>3.29</v>
       </c>
       <c r="R19">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -4369,10 +4369,10 @@
         <v>0</v>
       </c>
       <c r="AE19">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AF19">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG19">
         <v>0</v>
@@ -5067,76 +5067,76 @@
         <v>1.89</v>
       </c>
       <c r="Q23">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="R23">
-        <v>3.95</v>
+        <v>3.73</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AE23">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AF23">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AH23">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI23">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL23">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM23">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN23">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AO23">
         <v>0</v>
@@ -5178,19 +5178,19 @@
         <v>0</v>
       </c>
       <c r="BB23">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC23">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BD23">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="BE23">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF23">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG23">
         <v>0</v>
@@ -5258,13 +5258,13 @@
         <v>1.8</v>
       </c>
       <c r="S24">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="T24">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="U24">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="V24">
         <v>0</v>
@@ -5276,7 +5276,7 @@
         <v>2.55</v>
       </c>
       <c r="Y24">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -5288,40 +5288,40 @@
         <v>0</v>
       </c>
       <c r="AC24">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AD24">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AE24">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AF24">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AG24">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AH24">
         <v>1.3</v>
       </c>
       <c r="AI24">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AJ24">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AK24">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AL24">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AM24">
-        <v>1.81</v>
+        <v>1.2</v>
       </c>
       <c r="AN24">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AO24">
         <v>0</v>
@@ -5366,13 +5366,13 @@
         <v>0</v>
       </c>
       <c r="BC24">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="BD24">
         <v>0</v>
       </c>
       <c r="BE24">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="BF24">
         <v>0</v>
@@ -5804,79 +5804,79 @@
         <v>188</v>
       </c>
       <c r="P27">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Q27">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="R27">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="S27">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="T27">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="U27">
-        <v>6.66</v>
+        <v>6.2</v>
       </c>
       <c r="V27">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W27">
-        <v>3.52</v>
+        <v>3.44</v>
       </c>
       <c r="X27">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
       <c r="Y27">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="Z27">
-        <v>5.15</v>
+        <v>5.3</v>
       </c>
       <c r="AA27">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AB27">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC27">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AD27">
-        <v>4.9</v>
+        <v>4.53</v>
       </c>
       <c r="AE27">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="AF27">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="AG27">
         <v>2.08</v>
       </c>
       <c r="AH27">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AI27">
         <v>3.45</v>
       </c>
       <c r="AJ27">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AK27">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AL27">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="AM27">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AN27">
-        <v>3</v>
+        <v>2.79</v>
       </c>
       <c r="AO27">
         <v>0</v>
@@ -5885,10 +5885,10 @@
         <v>1.31</v>
       </c>
       <c r="AQ27">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AR27">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="AS27">
         <v>2.59</v>
@@ -5900,7 +5900,7 @@
         <v>2.97</v>
       </c>
       <c r="AV27">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AW27">
         <v>1.72</v>
@@ -5918,19 +5918,19 @@
         <v>7.01</v>
       </c>
       <c r="BB27">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BC27">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="BD27">
-        <v>5.1</v>
+        <v>4.95</v>
       </c>
       <c r="BE27">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="BF27">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BG27">
         <v>0</v>
@@ -6508,7 +6508,7 @@
         <v>98</v>
       </c>
       <c r="D31" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E31" t="s">
         <v>136</v>
@@ -6544,133 +6544,133 @@
         <v>188</v>
       </c>
       <c r="P31">
-        <v>2.5</v>
+        <v>5.48</v>
       </c>
       <c r="Q31">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="R31">
-        <v>2.4</v>
+        <v>1.55</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AE31">
-        <v>1.66</v>
+        <v>2.46</v>
       </c>
       <c r="AF31">
-        <v>2.15</v>
+        <v>1.48</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AH31">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI31">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL31">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AM31">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN31">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AO31">
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR31">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU31">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW31">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AX31">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY31">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ31">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="BA31">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BB31">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BC31">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BD31">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BE31">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BF31">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG31">
         <v>0</v>
@@ -6693,7 +6693,7 @@
         <v>99</v>
       </c>
       <c r="D32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E32" t="s">
         <v>137</v>
@@ -6729,133 +6729,133 @@
         <v>188</v>
       </c>
       <c r="P32">
-        <v>4.88</v>
+        <v>2.49</v>
       </c>
       <c r="Q32">
-        <v>3.32</v>
+        <v>3.29</v>
       </c>
       <c r="R32">
-        <v>1.68</v>
+        <v>2.4</v>
       </c>
       <c r="S32">
-        <v>5.76</v>
+        <v>0</v>
       </c>
       <c r="T32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U32">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="V32">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W32">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X32">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Y32">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z32">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA32">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB32">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC32">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD32">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AE32">
+        <v>1.66</v>
+      </c>
+      <c r="AF32">
         <v>2.15</v>
       </c>
-      <c r="AF32">
-        <v>1.64</v>
-      </c>
       <c r="AG32">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AH32">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI32">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AJ32">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK32">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AL32">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM32">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN32">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AO32">
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ32">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR32">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AS32">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AT32">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AU32">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AV32">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AW32">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AX32">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY32">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ32">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="BA32">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="BB32">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC32">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BD32">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE32">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="BF32">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG32">
         <v>0</v>
@@ -7060,7 +7060,7 @@
         <v>80</v>
       </c>
       <c r="C34" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D34" t="s">
         <v>105</v>
@@ -7099,133 +7099,133 @@
         <v>188</v>
       </c>
       <c r="P34">
-        <v>1.36</v>
+        <v>4.88</v>
       </c>
       <c r="Q34">
-        <v>4.2</v>
+        <v>3.32</v>
       </c>
       <c r="R34">
-        <v>7</v>
+        <v>1.68</v>
       </c>
       <c r="S34">
-        <v>1.88</v>
+        <v>5.76</v>
       </c>
       <c r="T34">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="U34">
-        <v>8.1</v>
+        <v>2.32</v>
       </c>
       <c r="V34">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W34">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="X34">
-        <v>2.91</v>
+        <v>3.02</v>
       </c>
       <c r="Y34">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z34">
+        <v>7.5</v>
+      </c>
+      <c r="AA34">
+        <v>1.03</v>
+      </c>
+      <c r="AB34">
+        <v>1.04</v>
+      </c>
+      <c r="AC34">
+        <v>1.34</v>
+      </c>
+      <c r="AD34">
+        <v>2.78</v>
+      </c>
+      <c r="AE34">
+        <v>2.12</v>
+      </c>
+      <c r="AF34">
+        <v>1.64</v>
+      </c>
+      <c r="AG34">
+        <v>3.88</v>
+      </c>
+      <c r="AH34">
+        <v>1.2</v>
+      </c>
+      <c r="AI34">
         <v>7.1</v>
       </c>
-      <c r="AA34">
+      <c r="AJ34">
         <v>1.04</v>
       </c>
-      <c r="AB34">
-        <v>1.06</v>
-      </c>
-      <c r="AC34">
-        <v>1.31</v>
-      </c>
-      <c r="AD34">
-        <v>2.92</v>
-      </c>
-      <c r="AE34">
-        <v>2.02</v>
-      </c>
-      <c r="AF34">
-        <v>1.71</v>
-      </c>
-      <c r="AG34">
-        <v>3.42</v>
-      </c>
-      <c r="AH34">
-        <v>1.27</v>
-      </c>
-      <c r="AI34">
-        <v>6.45</v>
-      </c>
-      <c r="AJ34">
-        <v>1.05</v>
-      </c>
       <c r="AK34">
-        <v>2.25</v>
+        <v>2.01</v>
       </c>
       <c r="AL34">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AM34">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AN34">
-        <v>2.72</v>
+        <v>1.11</v>
       </c>
       <c r="AO34">
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AQ34">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="AR34">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AS34">
-        <v>2.33</v>
+        <v>2.52</v>
       </c>
       <c r="AT34">
-        <v>3.14</v>
+        <v>3.48</v>
       </c>
       <c r="AU34">
-        <v>3.34</v>
+        <v>3.05</v>
       </c>
       <c r="AV34">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="AW34">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AX34">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AY34">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AZ34">
-        <v>1.29</v>
+        <v>2.46</v>
       </c>
       <c r="BA34">
-        <v>4.32</v>
+        <v>1.82</v>
       </c>
       <c r="BB34">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="BC34">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="BD34">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="BE34">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="BF34">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BG34">
         <v>0</v>
@@ -7245,7 +7245,7 @@
         <v>80</v>
       </c>
       <c r="C35" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D35" t="s">
         <v>105</v>
@@ -7284,133 +7284,133 @@
         <v>188</v>
       </c>
       <c r="P35">
-        <v>5.48</v>
+        <v>1.35</v>
       </c>
       <c r="Q35">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="R35">
-        <v>1.55</v>
+        <v>8.65</v>
       </c>
       <c r="S35">
+        <v>1.86</v>
+      </c>
+      <c r="T35">
+        <v>2.15</v>
+      </c>
+      <c r="U35">
+        <v>8.35</v>
+      </c>
+      <c r="V35">
+        <v>1.42</v>
+      </c>
+      <c r="W35">
+        <v>2.56</v>
+      </c>
+      <c r="X35">
+        <v>2.91</v>
+      </c>
+      <c r="Y35">
+        <v>1.33</v>
+      </c>
+      <c r="Z35">
         <v>7.1</v>
-      </c>
-      <c r="T35">
-        <v>1.91</v>
-      </c>
-      <c r="U35">
-        <v>2.23</v>
-      </c>
-      <c r="V35">
-        <v>1.55</v>
-      </c>
-      <c r="W35">
-        <v>2.28</v>
-      </c>
-      <c r="X35">
-        <v>3.48</v>
-      </c>
-      <c r="Y35">
-        <v>1.22</v>
-      </c>
-      <c r="Z35">
-        <v>9.199999999999999</v>
       </c>
       <c r="AA35">
         <v>1.04</v>
       </c>
       <c r="AB35">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AC35">
-        <v>1.53</v>
+        <v>1.31</v>
       </c>
       <c r="AD35">
-        <v>2.43</v>
+        <v>2.92</v>
       </c>
       <c r="AE35">
-        <v>2.46</v>
+        <v>2</v>
       </c>
       <c r="AF35">
-        <v>1.45</v>
+        <v>1.72</v>
       </c>
       <c r="AG35">
-        <v>4.1</v>
+        <v>3.58</v>
       </c>
       <c r="AH35">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AI35">
-        <v>9.1</v>
+        <v>6.4</v>
       </c>
       <c r="AJ35">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AK35">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AL35">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="AM35">
+        <v>1.16</v>
+      </c>
+      <c r="AN35">
+        <v>2.76</v>
+      </c>
+      <c r="AO35">
+        <v>0</v>
+      </c>
+      <c r="AP35">
         <v>1.24</v>
       </c>
-      <c r="AN35">
-        <v>1.1</v>
-      </c>
-      <c r="AO35">
-        <v>0</v>
-      </c>
-      <c r="AP35">
-        <v>1.36</v>
-      </c>
       <c r="AQ35">
-        <v>1.69</v>
+        <v>1.46</v>
       </c>
       <c r="AR35">
-        <v>2.14</v>
+        <v>1.87</v>
       </c>
       <c r="AS35">
-        <v>2.7</v>
+        <v>2.33</v>
       </c>
       <c r="AT35">
-        <v>3.6</v>
+        <v>2.95</v>
       </c>
       <c r="AU35">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="AV35">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AW35">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AX35">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AY35">
+        <v>1.34</v>
+      </c>
+      <c r="AZ35">
+        <v>1.29</v>
+      </c>
+      <c r="BA35">
+        <v>4.32</v>
+      </c>
+      <c r="BB35">
         <v>1.23</v>
       </c>
-      <c r="AZ35">
-        <v>2.39</v>
-      </c>
-      <c r="BA35">
-        <v>1.87</v>
-      </c>
-      <c r="BB35">
-        <v>1.32</v>
-      </c>
       <c r="BC35">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="BD35">
-        <v>2.96</v>
+        <v>3.42</v>
       </c>
       <c r="BE35">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="BF35">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="BG35">
         <v>0</v>
@@ -7469,13 +7469,13 @@
         <v>188</v>
       </c>
       <c r="P36">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q36">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="R36">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="S36">
         <v>2.9</v>
@@ -7487,16 +7487,16 @@
         <v>4.2</v>
       </c>
       <c r="V36">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="W36">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="X36">
         <v>4.1</v>
       </c>
       <c r="Y36">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z36">
         <v>9.300000000000001</v>
@@ -7511,7 +7511,7 @@
         <v>1.66</v>
       </c>
       <c r="AD36">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="AE36">
         <v>3.1</v>
@@ -7535,7 +7535,7 @@
         <v>2.4</v>
       </c>
       <c r="AL36">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AM36">
         <v>1.32</v>
@@ -7547,28 +7547,28 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AQ36">
         <v>1.76</v>
       </c>
       <c r="AR36">
-        <v>2.24</v>
+        <v>2.7</v>
       </c>
       <c r="AS36">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="AT36">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="AU36">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="AV36">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AW36">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AX36">
         <v>1.3</v>
@@ -7577,10 +7577,10 @@
         <v>1.13</v>
       </c>
       <c r="AZ36">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="BA36">
-        <v>2.96</v>
+        <v>2.61</v>
       </c>
       <c r="BB36">
         <v>1.43</v>
@@ -7654,133 +7654,133 @@
         <v>188</v>
       </c>
       <c r="P37">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="Q37">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="R37">
-        <v>2.15</v>
+        <v>3.75</v>
       </c>
       <c r="S37">
-        <v>4.43</v>
+        <v>2.83</v>
       </c>
       <c r="T37">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="U37">
-        <v>3.2</v>
+        <v>5.1</v>
       </c>
       <c r="V37">
-        <v>1.51</v>
+        <v>1.63</v>
       </c>
       <c r="W37">
-        <v>2.31</v>
+        <v>2.13</v>
       </c>
       <c r="X37">
-        <v>3.38</v>
+        <v>3.9</v>
       </c>
       <c r="Y37">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="Z37">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA37">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AB37">
+        <v>1.12</v>
+      </c>
+      <c r="AC37">
+        <v>1.58</v>
+      </c>
+      <c r="AD37">
+        <v>2.23</v>
+      </c>
+      <c r="AE37">
+        <v>2.74</v>
+      </c>
+      <c r="AF37">
+        <v>1.35</v>
+      </c>
+      <c r="AG37">
+        <v>6</v>
+      </c>
+      <c r="AH37">
         <v>1.1</v>
       </c>
-      <c r="AC37">
-        <v>1.43</v>
-      </c>
-      <c r="AD37">
-        <v>2.46</v>
-      </c>
-      <c r="AE37">
-        <v>2.65</v>
-      </c>
-      <c r="AF37">
-        <v>1.49</v>
-      </c>
-      <c r="AG37">
-        <v>5.1</v>
-      </c>
-      <c r="AH37">
-        <v>1.13</v>
-      </c>
       <c r="AI37">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AJ37">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AK37">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="AL37">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AM37">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AN37">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="AO37">
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AQ37">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AR37">
-        <v>2.53</v>
+        <v>2.23</v>
       </c>
       <c r="AS37">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AT37">
-        <v>4.15</v>
+        <v>4.34</v>
       </c>
       <c r="AU37">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="AV37">
         <v>1.95</v>
       </c>
       <c r="AW37">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AX37">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AY37">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AZ37">
-        <v>2.12</v>
+        <v>1.52</v>
       </c>
       <c r="BA37">
-        <v>2.08</v>
+        <v>3.42</v>
       </c>
       <c r="BB37">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="BC37">
-        <v>2.59</v>
+        <v>2.91</v>
       </c>
       <c r="BD37">
-        <v>2.96</v>
+        <v>2.66</v>
       </c>
       <c r="BE37">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="BF37">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="BG37">
         <v>0</v>
@@ -7839,25 +7839,25 @@
         <v>188</v>
       </c>
       <c r="P38">
-        <v>5.75</v>
+        <v>6.39</v>
       </c>
       <c r="Q38">
         <v>3.5</v>
       </c>
       <c r="R38">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="S38">
         <v>8.050000000000001</v>
       </c>
       <c r="T38">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="U38">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="V38">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W38">
         <v>2.44</v>
@@ -7866,10 +7866,10 @@
         <v>3.3</v>
       </c>
       <c r="Y38">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z38">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AA38">
         <v>1</v>
@@ -7884,7 +7884,7 @@
         <v>2.43</v>
       </c>
       <c r="AE38">
-        <v>2.53</v>
+        <v>2.23</v>
       </c>
       <c r="AF38">
         <v>1.49</v>
@@ -7902,13 +7902,13 @@
         <v>1</v>
       </c>
       <c r="AK38">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="AL38">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AM38">
-        <v>2.31</v>
+        <v>1.22</v>
       </c>
       <c r="AN38">
         <v>1.04</v>
@@ -7923,7 +7923,7 @@
         <v>1.77</v>
       </c>
       <c r="AR38">
-        <v>2.73</v>
+        <v>2.16</v>
       </c>
       <c r="AS38">
         <v>3.04</v>
@@ -7932,7 +7932,7 @@
         <v>4.41</v>
       </c>
       <c r="AU38">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AV38">
         <v>1.94</v>
@@ -8024,133 +8024,133 @@
         <v>188</v>
       </c>
       <c r="P39">
+        <v>3.3</v>
+      </c>
+      <c r="Q39">
+        <v>3</v>
+      </c>
+      <c r="R39">
+        <v>2.1</v>
+      </c>
+      <c r="S39">
+        <v>4.43</v>
+      </c>
+      <c r="T39">
+        <v>1.92</v>
+      </c>
+      <c r="U39">
+        <v>2.88</v>
+      </c>
+      <c r="V39">
+        <v>1.51</v>
+      </c>
+      <c r="W39">
+        <v>2.31</v>
+      </c>
+      <c r="X39">
+        <v>3.38</v>
+      </c>
+      <c r="Y39">
+        <v>1.25</v>
+      </c>
+      <c r="Z39">
+        <v>9.1</v>
+      </c>
+      <c r="AA39">
+        <v>1</v>
+      </c>
+      <c r="AB39">
+        <v>1.1</v>
+      </c>
+      <c r="AC39">
+        <v>1.43</v>
+      </c>
+      <c r="AD39">
+        <v>2.46</v>
+      </c>
+      <c r="AE39">
+        <v>2.65</v>
+      </c>
+      <c r="AF39">
+        <v>1.51</v>
+      </c>
+      <c r="AG39">
+        <v>4.6</v>
+      </c>
+      <c r="AH39">
+        <v>1.17</v>
+      </c>
+      <c r="AI39">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AJ39">
+        <v>1.05</v>
+      </c>
+      <c r="AK39">
+        <v>2.04</v>
+      </c>
+      <c r="AL39">
+        <v>1.62</v>
+      </c>
+      <c r="AM39">
+        <v>1.3</v>
+      </c>
+      <c r="AN39">
+        <v>1.24</v>
+      </c>
+      <c r="AO39">
+        <v>0</v>
+      </c>
+      <c r="AP39">
+        <v>1.39</v>
+      </c>
+      <c r="AQ39">
+        <v>1.72</v>
+      </c>
+      <c r="AR39">
+        <v>2.17</v>
+      </c>
+      <c r="AS39">
+        <v>2.9</v>
+      </c>
+      <c r="AT39">
+        <v>4.15</v>
+      </c>
+      <c r="AU39">
+        <v>2.66</v>
+      </c>
+      <c r="AV39">
         <v>2</v>
       </c>
-      <c r="Q39">
-        <v>2.9</v>
-      </c>
-      <c r="R39">
-        <v>3.95</v>
-      </c>
-      <c r="S39">
-        <v>2.88</v>
-      </c>
-      <c r="T39">
-        <v>1.75</v>
-      </c>
-      <c r="U39">
-        <v>5.1</v>
-      </c>
-      <c r="V39">
-        <v>1.64</v>
-      </c>
-      <c r="W39">
-        <v>2.11</v>
-      </c>
-      <c r="X39">
-        <v>3.9</v>
-      </c>
-      <c r="Y39">
-        <v>1.18</v>
-      </c>
-      <c r="Z39">
-        <v>13</v>
-      </c>
-      <c r="AA39">
-        <v>1.02</v>
-      </c>
-      <c r="AB39">
-        <v>1.08</v>
-      </c>
-      <c r="AC39">
-        <v>1.58</v>
-      </c>
-      <c r="AD39">
-        <v>2.25</v>
-      </c>
-      <c r="AE39">
-        <v>2.74</v>
-      </c>
-      <c r="AF39">
-        <v>1.35</v>
-      </c>
-      <c r="AG39">
-        <v>6.33</v>
-      </c>
-      <c r="AH39">
-        <v>1.07</v>
-      </c>
-      <c r="AI39">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="AJ39">
-        <v>1.01</v>
-      </c>
-      <c r="AK39">
-        <v>2.32</v>
-      </c>
-      <c r="AL39">
-        <v>1.53</v>
-      </c>
-      <c r="AM39">
-        <v>1.35</v>
-      </c>
-      <c r="AN39">
-        <v>1.63</v>
-      </c>
-      <c r="AO39">
-        <v>0</v>
-      </c>
-      <c r="AP39">
-        <v>1.42</v>
-      </c>
-      <c r="AQ39">
-        <v>1.76</v>
-      </c>
-      <c r="AR39">
-        <v>2.7</v>
-      </c>
-      <c r="AS39">
-        <v>3</v>
-      </c>
-      <c r="AT39">
-        <v>4.34</v>
-      </c>
-      <c r="AU39">
-        <v>2.58</v>
-      </c>
-      <c r="AV39">
-        <v>1.95</v>
-      </c>
       <c r="AW39">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AX39">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AY39">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AZ39">
-        <v>1.52</v>
+        <v>2.12</v>
       </c>
       <c r="BA39">
-        <v>3.26</v>
+        <v>2.08</v>
       </c>
       <c r="BB39">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="BC39">
-        <v>2.9</v>
+        <v>2.59</v>
       </c>
       <c r="BD39">
-        <v>2.66</v>
+        <v>2.96</v>
       </c>
       <c r="BE39">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="BF39">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BG39">
         <v>0</v>
@@ -8209,79 +8209,79 @@
         <v>188</v>
       </c>
       <c r="P40">
-        <v>8.5</v>
+        <v>10.8</v>
       </c>
       <c r="Q40">
-        <v>5.75</v>
+        <v>6.8</v>
       </c>
       <c r="R40">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S40">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="T40">
-        <v>2.84</v>
+        <v>2.95</v>
       </c>
       <c r="U40">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="V40">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W40">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="X40">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="Y40">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Z40">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="AA40">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AB40">
         <v>1.01</v>
       </c>
       <c r="AC40">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AD40">
-        <v>6.15</v>
+        <v>6.4</v>
       </c>
       <c r="AE40">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AF40">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AG40">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AH40">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AI40">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="AJ40">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AK40">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AL40">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AM40">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AN40">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AO40">
         <v>0</v>
@@ -8326,16 +8326,16 @@
         <v>1.08</v>
       </c>
       <c r="BC40">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="BD40">
         <v>6.4</v>
       </c>
       <c r="BE40">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="BF40">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="BG40">
         <v>0</v>

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -310,12 +310,12 @@
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
     <t>Egypt Egyptian Premier League</t>
   </si>
   <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
     <t>South Africa Premier Soccer League</t>
   </si>
   <si>
@@ -337,10 +337,13 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Bucheon 1995</t>
+  </si>
+  <si>
     <t>Jeonbuk Motors</t>
   </si>
   <si>
-    <t>Bucheon 1995</t>
+    <t>Daejeon Citizen</t>
   </si>
   <si>
     <t>Gangwon</t>
@@ -349,30 +352,27 @@
     <t>Sangju Sangmu</t>
   </si>
   <si>
-    <t>Daejeon Citizen</t>
-  </si>
-  <si>
     <t>Madura United</t>
   </si>
   <si>
+    <t>FC Seoul</t>
+  </si>
+  <si>
     <t>Ethiopia Nigd Bank</t>
   </si>
   <si>
-    <t>FC Seoul</t>
-  </si>
-  <si>
     <t>Qingdao Youth Island</t>
   </si>
   <si>
     <t>Tanjong Pagar</t>
   </si>
   <si>
+    <t>Shenyang Urban</t>
+  </si>
+  <si>
     <t>Shandong Luneng</t>
   </si>
   <si>
-    <t>Shenyang Urban</t>
-  </si>
-  <si>
     <t>Chongqing Tongliang Long</t>
   </si>
   <si>
@@ -415,42 +415,42 @@
     <t>Maccabi Tel Aviv</t>
   </si>
   <si>
+    <t>Bani Yas</t>
+  </si>
+  <si>
+    <t>Al Ittihad Kalba</t>
+  </si>
+  <si>
     <t>Dibba Al Fujairah</t>
   </si>
   <si>
-    <t>Bani Yas</t>
-  </si>
-  <si>
-    <t>Al Ittihad Kalba</t>
+    <t>Lokomotiv Sofia 1929</t>
+  </si>
+  <si>
+    <t>Falkenberg</t>
+  </si>
+  <si>
+    <t>Ceramica Cleopatra</t>
+  </si>
+  <si>
+    <t>Al Ahly</t>
   </si>
   <si>
     <t>Smouha SC</t>
   </si>
   <si>
-    <t>Falkenberg</t>
-  </si>
-  <si>
-    <t>Lokomotiv Sofia 1929</t>
-  </si>
-  <si>
-    <t>Ceramica Cleopatra</t>
-  </si>
-  <si>
-    <t>Al Ahly</t>
-  </si>
-  <si>
     <t>Siwelele</t>
   </si>
   <si>
     <t>Magesi</t>
   </si>
   <si>
+    <t>Chippa United</t>
+  </si>
+  <si>
     <t>Stellenbosch</t>
   </si>
   <si>
-    <t>Chippa United</t>
-  </si>
-  <si>
     <t>Al Khaleej</t>
   </si>
   <si>
@@ -460,10 +460,13 @@
     <t>New York City II</t>
   </si>
   <si>
+    <t>Jeju United</t>
+  </si>
+  <si>
     <t>Gwangju</t>
   </si>
   <si>
-    <t>Jeju United</t>
+    <t>Incheon United</t>
   </si>
   <si>
     <t>Pohang Steelers</t>
@@ -472,30 +475,27 @@
     <t>Ulsan</t>
   </si>
   <si>
-    <t>Incheon United</t>
-  </si>
-  <si>
     <t>Bali United</t>
   </si>
   <si>
+    <t>Anyang</t>
+  </si>
+  <si>
     <t>Kedus Giorgis</t>
   </si>
   <si>
-    <t>Anyang</t>
-  </si>
-  <si>
     <t>Tianjin Teda</t>
   </si>
   <si>
     <t>Hougang United</t>
   </si>
   <si>
+    <t>Chengdu Better City FC</t>
+  </si>
+  <si>
     <t>Shanghai Shenhua</t>
   </si>
   <si>
-    <t>Chengdu Better City FC</t>
-  </si>
-  <si>
     <t>Henan Jianye</t>
   </si>
   <si>
@@ -538,37 +538,37 @@
     <t>Hapoel Petah Tikva</t>
   </si>
   <si>
+    <t>Al Dhafra</t>
+  </si>
+  <si>
     <t>Al Bataeh</t>
   </si>
   <si>
-    <t>Al Dhafra</t>
+    <t>Botev Vratsa</t>
+  </si>
+  <si>
+    <t>Norrköping</t>
+  </si>
+  <si>
+    <t>Pyramids FC</t>
+  </si>
+  <si>
+    <t>ENPPI</t>
   </si>
   <si>
     <t>Zamalek</t>
   </si>
   <si>
-    <t>Norrköping</t>
-  </si>
-  <si>
-    <t>Botev Vratsa</t>
-  </si>
-  <si>
-    <t>Pyramids FC</t>
-  </si>
-  <si>
-    <t>ENPPI</t>
-  </si>
-  <si>
     <t>Durban City</t>
   </si>
   <si>
     <t>Orbit College</t>
   </si>
   <si>
+    <t>Sekhukhune United</t>
+  </si>
+  <si>
     <t>Orlando Pirates</t>
-  </si>
-  <si>
-    <t>Sekhukhune United</t>
   </si>
   <si>
     <t>Al Hilal</t>
@@ -1179,133 +1179,133 @@
         <v>188</v>
       </c>
       <c r="P2">
-        <v>1.34</v>
+        <v>2.45</v>
       </c>
       <c r="Q2">
-        <v>4.35</v>
+        <v>3.15</v>
       </c>
       <c r="R2">
-        <v>7.91</v>
+        <v>2.8</v>
       </c>
       <c r="S2">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W2">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="X2">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y2">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z2">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC2">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AE2">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="AF2">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AG2">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AH2">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK2">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AL2">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN2">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AO2">
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AQ2">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AR2">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="AS2">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AT2">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AU2">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AV2">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AW2">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AX2">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AY2">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AZ2">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BA2">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="BB2">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC2">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="BD2">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BE2">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BF2">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG2">
         <v>0</v>
@@ -1364,133 +1364,133 @@
         <v>188</v>
       </c>
       <c r="P3">
-        <v>2.45</v>
+        <v>1.34</v>
       </c>
       <c r="Q3">
-        <v>3.15</v>
+        <v>4.35</v>
       </c>
       <c r="R3">
-        <v>2.8</v>
+        <v>7.91</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AE3">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="AF3">
+        <v>1.85</v>
+      </c>
+      <c r="AG3">
+        <v>3.4</v>
+      </c>
+      <c r="AH3">
+        <v>1.27</v>
+      </c>
+      <c r="AI3">
+        <v>6.1</v>
+      </c>
+      <c r="AJ3">
+        <v>1.06</v>
+      </c>
+      <c r="AK3">
+        <v>2.26</v>
+      </c>
+      <c r="AL3">
         <v>1.57</v>
       </c>
-      <c r="AG3">
-        <v>0</v>
-      </c>
-      <c r="AH3">
-        <v>0</v>
-      </c>
-      <c r="AI3">
-        <v>0</v>
-      </c>
-      <c r="AJ3">
-        <v>0</v>
-      </c>
-      <c r="AK3">
-        <v>0</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
       <c r="AM3">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AO3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AU3">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AV3">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AW3">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AX3">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AY3">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AZ3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BA3">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BB3">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC3">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="BD3">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BE3">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF3">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG3">
         <v>0</v>
@@ -1549,133 +1549,133 @@
         <v>188</v>
       </c>
       <c r="P4">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="Q4">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="R4">
-        <v>3.64</v>
+        <v>3.1</v>
       </c>
       <c r="S4">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="T4">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="U4">
-        <v>4.76</v>
+        <v>4.06</v>
       </c>
       <c r="V4">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W4">
+        <v>2.59</v>
+      </c>
+      <c r="X4">
+        <v>3.04</v>
+      </c>
+      <c r="Y4">
+        <v>1.33</v>
+      </c>
+      <c r="Z4">
+        <v>7.6</v>
+      </c>
+      <c r="AA4">
+        <v>1.03</v>
+      </c>
+      <c r="AB4">
+        <v>1.06</v>
+      </c>
+      <c r="AC4">
+        <v>1.35</v>
+      </c>
+      <c r="AD4">
+        <v>2.94</v>
+      </c>
+      <c r="AE4">
+        <v>2.1</v>
+      </c>
+      <c r="AF4">
+        <v>1.72</v>
+      </c>
+      <c r="AG4">
+        <v>3.65</v>
+      </c>
+      <c r="AH4">
+        <v>1.22</v>
+      </c>
+      <c r="AI4">
+        <v>6.75</v>
+      </c>
+      <c r="AJ4">
+        <v>1.04</v>
+      </c>
+      <c r="AK4">
+        <v>1.82</v>
+      </c>
+      <c r="AL4">
+        <v>1.82</v>
+      </c>
+      <c r="AM4">
+        <v>1.35</v>
+      </c>
+      <c r="AN4">
+        <v>1.62</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>1.51</v>
+      </c>
+      <c r="AQ4">
+        <v>1.9</v>
+      </c>
+      <c r="AR4">
+        <v>3.08</v>
+      </c>
+      <c r="AS4">
+        <v>3.42</v>
+      </c>
+      <c r="AT4">
+        <v>5.11</v>
+      </c>
+      <c r="AU4">
         <v>2.34</v>
       </c>
-      <c r="X4">
-        <v>3.4</v>
-      </c>
-      <c r="Y4">
-        <v>1.27</v>
-      </c>
-      <c r="Z4">
-        <v>8.5</v>
-      </c>
-      <c r="AA4">
-        <v>1.01</v>
-      </c>
-      <c r="AB4">
-        <v>1.05</v>
-      </c>
-      <c r="AC4">
-        <v>1.47</v>
-      </c>
-      <c r="AD4">
-        <v>2.7</v>
-      </c>
-      <c r="AE4">
-        <v>2.38</v>
-      </c>
-      <c r="AF4">
-        <v>1.53</v>
-      </c>
-      <c r="AG4">
-        <v>4.5</v>
-      </c>
-      <c r="AH4">
-        <v>1.15</v>
-      </c>
-      <c r="AI4">
-        <v>9</v>
-      </c>
-      <c r="AJ4">
-        <v>1.01</v>
-      </c>
-      <c r="AK4">
-        <v>1.94</v>
-      </c>
-      <c r="AL4">
-        <v>1.68</v>
-      </c>
-      <c r="AM4">
-        <v>1.33</v>
-      </c>
-      <c r="AN4">
-        <v>1.71</v>
-      </c>
-      <c r="AO4">
-        <v>0</v>
-      </c>
-      <c r="AP4">
-        <v>1.53</v>
-      </c>
-      <c r="AQ4">
-        <v>1.92</v>
-      </c>
-      <c r="AR4">
-        <v>3.14</v>
-      </c>
-      <c r="AS4">
-        <v>3.48</v>
-      </c>
-      <c r="AT4">
-        <v>5.23</v>
-      </c>
-      <c r="AU4">
-        <v>2.31</v>
-      </c>
       <c r="AV4">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AW4">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AX4">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AY4">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AZ4">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="BA4">
-        <v>3.1</v>
+        <v>2.21</v>
       </c>
       <c r="BB4">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="BC4">
-        <v>2.53</v>
+        <v>2.3</v>
       </c>
       <c r="BD4">
-        <v>3.04</v>
+        <v>3.5</v>
       </c>
       <c r="BE4">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="BF4">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="BG4">
         <v>0</v>
@@ -1734,133 +1734,133 @@
         <v>188</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="S5">
-        <v>3.25</v>
+        <v>2.77</v>
       </c>
       <c r="T5">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="U5">
-        <v>3.24</v>
+        <v>4.76</v>
       </c>
       <c r="V5">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="W5">
-        <v>2.77</v>
+        <v>2.34</v>
       </c>
       <c r="X5">
-        <v>2.65</v>
+        <v>3.4</v>
       </c>
       <c r="Y5">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="Z5">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AB5">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AC5">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="AD5">
-        <v>3.18</v>
+        <v>2.7</v>
       </c>
       <c r="AE5">
-        <v>1.99</v>
+        <v>2.38</v>
       </c>
       <c r="AF5">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AG5">
+        <v>4.5</v>
+      </c>
+      <c r="AH5">
+        <v>1.15</v>
+      </c>
+      <c r="AI5">
+        <v>9</v>
+      </c>
+      <c r="AJ5">
+        <v>1.01</v>
+      </c>
+      <c r="AK5">
+        <v>1.94</v>
+      </c>
+      <c r="AL5">
+        <v>1.68</v>
+      </c>
+      <c r="AM5">
+        <v>1.33</v>
+      </c>
+      <c r="AN5">
+        <v>1.71</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>1.53</v>
+      </c>
+      <c r="AQ5">
+        <v>1.92</v>
+      </c>
+      <c r="AR5">
+        <v>3.14</v>
+      </c>
+      <c r="AS5">
         <v>3.48</v>
       </c>
-      <c r="AH5">
-        <v>1.24</v>
-      </c>
-      <c r="AI5">
-        <v>6.73</v>
-      </c>
-      <c r="AJ5">
-        <v>1.04</v>
-      </c>
-      <c r="AK5">
-        <v>1.73</v>
-      </c>
-      <c r="AL5">
-        <v>2</v>
-      </c>
-      <c r="AM5">
+      <c r="AT5">
+        <v>5.23</v>
+      </c>
+      <c r="AU5">
+        <v>2.31</v>
+      </c>
+      <c r="AV5">
+        <v>1.79</v>
+      </c>
+      <c r="AW5">
+        <v>1.45</v>
+      </c>
+      <c r="AX5">
+        <v>1.22</v>
+      </c>
+      <c r="AY5">
+        <v>1.08</v>
+      </c>
+      <c r="AZ5">
+        <v>1.65</v>
+      </c>
+      <c r="BA5">
+        <v>3.1</v>
+      </c>
+      <c r="BB5">
+        <v>1.33</v>
+      </c>
+      <c r="BC5">
+        <v>2.53</v>
+      </c>
+      <c r="BD5">
+        <v>3.04</v>
+      </c>
+      <c r="BE5">
         <v>1.46</v>
       </c>
-      <c r="AN5">
-        <v>1.44</v>
-      </c>
-      <c r="AO5">
-        <v>0</v>
-      </c>
-      <c r="AP5">
-        <v>1.39</v>
-      </c>
-      <c r="AQ5">
-        <v>1.72</v>
-      </c>
-      <c r="AR5">
-        <v>2.18</v>
-      </c>
-      <c r="AS5">
-        <v>2.9</v>
-      </c>
-      <c r="AT5">
-        <v>4.16</v>
-      </c>
-      <c r="AU5">
-        <v>2.66</v>
-      </c>
-      <c r="AV5">
-        <v>2.1</v>
-      </c>
-      <c r="AW5">
-        <v>1.6</v>
-      </c>
-      <c r="AX5">
-        <v>1.32</v>
-      </c>
-      <c r="AY5">
-        <v>1.15</v>
-      </c>
-      <c r="AZ5">
-        <v>1.81</v>
-      </c>
-      <c r="BA5">
-        <v>2.6</v>
-      </c>
-      <c r="BB5">
-        <v>1.22</v>
-      </c>
-      <c r="BC5">
-        <v>2.18</v>
-      </c>
-      <c r="BD5">
-        <v>3.66</v>
-      </c>
-      <c r="BE5">
-        <v>1.66</v>
-      </c>
       <c r="BF5">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="BG5">
         <v>0</v>
@@ -1919,133 +1919,133 @@
         <v>188</v>
       </c>
       <c r="P6">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>2.87</v>
+        <v>3.25</v>
       </c>
       <c r="T6">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="U6">
-        <v>4.06</v>
+        <v>3.24</v>
       </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W6">
-        <v>2.59</v>
+        <v>2.77</v>
       </c>
       <c r="X6">
-        <v>3.04</v>
+        <v>2.65</v>
       </c>
       <c r="Y6">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z6">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="AA6">
         <v>1.03</v>
       </c>
       <c r="AB6">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC6">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AD6">
-        <v>2.94</v>
+        <v>3.18</v>
       </c>
       <c r="AE6">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="AF6">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AG6">
-        <v>3.65</v>
+        <v>3.48</v>
       </c>
       <c r="AH6">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AI6">
-        <v>6.75</v>
+        <v>6.73</v>
       </c>
       <c r="AJ6">
         <v>1.04</v>
       </c>
       <c r="AK6">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AL6">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AM6">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AN6">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AO6">
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="AQ6">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AR6">
-        <v>3.08</v>
+        <v>2.18</v>
       </c>
       <c r="AS6">
-        <v>3.42</v>
+        <v>2.9</v>
       </c>
       <c r="AT6">
-        <v>5.11</v>
+        <v>4.16</v>
       </c>
       <c r="AU6">
-        <v>2.34</v>
+        <v>2.66</v>
       </c>
       <c r="AV6">
+        <v>2.1</v>
+      </c>
+      <c r="AW6">
+        <v>1.6</v>
+      </c>
+      <c r="AX6">
+        <v>1.32</v>
+      </c>
+      <c r="AY6">
+        <v>1.15</v>
+      </c>
+      <c r="AZ6">
         <v>1.81</v>
       </c>
-      <c r="AW6">
-        <v>1.46</v>
-      </c>
-      <c r="AX6">
-        <v>1.23</v>
-      </c>
-      <c r="AY6">
-        <v>1.11</v>
-      </c>
-      <c r="AZ6">
-        <v>1.72</v>
-      </c>
       <c r="BA6">
-        <v>2.21</v>
+        <v>2.6</v>
       </c>
       <c r="BB6">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BC6">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="BD6">
-        <v>3.5</v>
+        <v>3.66</v>
       </c>
       <c r="BE6">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="BF6">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BG6">
         <v>0</v>
@@ -2113,25 +2113,25 @@
         <v>0</v>
       </c>
       <c r="S7">
-        <v>2.97</v>
+        <v>3.12</v>
       </c>
       <c r="T7">
         <v>2.14</v>
       </c>
       <c r="U7">
-        <v>3.12</v>
+        <v>2.97</v>
       </c>
       <c r="V7">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W7">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="X7">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="Y7">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Z7">
         <v>5.55</v>
@@ -2143,7 +2143,7 @@
         <v>1</v>
       </c>
       <c r="AC7">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AD7">
         <v>3.82</v>
@@ -2161,10 +2161,10 @@
         <v>1.38</v>
       </c>
       <c r="AI7">
-        <v>4.77</v>
+        <v>4.7</v>
       </c>
       <c r="AJ7">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AK7">
         <v>1.62</v>
@@ -2176,7 +2176,7 @@
         <v>1.24</v>
       </c>
       <c r="AN7">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AO7">
         <v>0</v>
@@ -2185,34 +2185,34 @@
         <v>1.14</v>
       </c>
       <c r="AQ7">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AR7">
         <v>1.8</v>
       </c>
       <c r="AS7">
+        <v>2.01</v>
+      </c>
+      <c r="AT7">
+        <v>2.58</v>
+      </c>
+      <c r="AU7">
+        <v>4.16</v>
+      </c>
+      <c r="AV7">
+        <v>2.83</v>
+      </c>
+      <c r="AW7">
+        <v>2.13</v>
+      </c>
+      <c r="AX7">
+        <v>1.71</v>
+      </c>
+      <c r="AY7">
+        <v>1.42</v>
+      </c>
+      <c r="AZ7">
         <v>1.99</v>
-      </c>
-      <c r="AT7">
-        <v>2.55</v>
-      </c>
-      <c r="AU7">
-        <v>4.23</v>
-      </c>
-      <c r="AV7">
-        <v>2.86</v>
-      </c>
-      <c r="AW7">
-        <v>2.15</v>
-      </c>
-      <c r="AX7">
-        <v>1.73</v>
-      </c>
-      <c r="AY7">
-        <v>1.43</v>
-      </c>
-      <c r="AZ7">
-        <v>2.07</v>
       </c>
       <c r="BA7">
         <v>2.12</v>
@@ -2250,10 +2250,10 @@
         <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E8" t="s">
         <v>113</v>
@@ -2289,133 +2289,133 @@
         <v>188</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AO8">
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG8">
         <v>0</v>
@@ -2435,10 +2435,10 @@
         <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E9" t="s">
         <v>114</v>
@@ -2474,133 +2474,133 @@
         <v>188</v>
       </c>
       <c r="P9">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z9">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC9">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD9">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AH9">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI9">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ9">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK9">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AL9">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AM9">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN9">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AO9">
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ9">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AR9">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AS9">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AT9">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AU9">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AV9">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AW9">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AX9">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AY9">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ9">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="BA9">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="BB9">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC9">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD9">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE9">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF9">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG9">
         <v>0</v>
@@ -3029,133 +3029,133 @@
         <v>188</v>
       </c>
       <c r="P12">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="T12">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="U12">
-        <v>2.78</v>
+        <v>2</v>
       </c>
       <c r="V12">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="W12">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="X12">
-        <v>2.08</v>
+        <v>2.41</v>
       </c>
       <c r="Y12">
-        <v>1.69</v>
+        <v>1.49</v>
       </c>
       <c r="Z12">
-        <v>4.45</v>
+        <v>5.5</v>
       </c>
       <c r="AA12">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AB12">
         <v>1.02</v>
       </c>
       <c r="AC12">
+        <v>1.17</v>
+      </c>
+      <c r="AD12">
+        <v>4</v>
+      </c>
+      <c r="AE12">
+        <v>1.68</v>
+      </c>
+      <c r="AF12">
+        <v>2.16</v>
+      </c>
+      <c r="AG12">
+        <v>2.65</v>
+      </c>
+      <c r="AH12">
+        <v>1.39</v>
+      </c>
+      <c r="AI12">
+        <v>5.2</v>
+      </c>
+      <c r="AJ12">
+        <v>1.12</v>
+      </c>
+      <c r="AK12">
+        <v>1.77</v>
+      </c>
+      <c r="AL12">
+        <v>1.94</v>
+      </c>
+      <c r="AM12">
+        <v>1.21</v>
+      </c>
+      <c r="AN12">
         <v>1.13</v>
       </c>
-      <c r="AD12">
-        <v>5.65</v>
-      </c>
-      <c r="AE12">
-        <v>1.44</v>
-      </c>
-      <c r="AF12">
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>1.19</v>
+      </c>
+      <c r="AQ12">
+        <v>1.41</v>
+      </c>
+      <c r="AR12">
+        <v>1.94</v>
+      </c>
+      <c r="AS12">
+        <v>2.16</v>
+      </c>
+      <c r="AT12">
+        <v>2.84</v>
+      </c>
+      <c r="AU12">
+        <v>3.72</v>
+      </c>
+      <c r="AV12">
         <v>2.59</v>
       </c>
-      <c r="AG12">
-        <v>2.05</v>
-      </c>
-      <c r="AH12">
-        <v>1.76</v>
-      </c>
-      <c r="AI12">
-        <v>3.28</v>
-      </c>
-      <c r="AJ12">
-        <v>1.25</v>
-      </c>
-      <c r="AK12">
-        <v>1.36</v>
-      </c>
-      <c r="AL12">
-        <v>2.9</v>
-      </c>
-      <c r="AM12">
-        <v>1.28</v>
-      </c>
-      <c r="AN12">
-        <v>1.43</v>
-      </c>
-      <c r="AO12">
-        <v>0</v>
-      </c>
-      <c r="AP12">
-        <v>1.08</v>
-      </c>
-      <c r="AQ12">
-        <v>1.25</v>
-      </c>
-      <c r="AR12">
-        <v>1.44</v>
-      </c>
-      <c r="AS12">
-        <v>1.81</v>
-      </c>
-      <c r="AT12">
-        <v>2.26</v>
-      </c>
-      <c r="AU12">
-        <v>5.06</v>
-      </c>
-      <c r="AV12">
-        <v>3.31</v>
-      </c>
       <c r="AW12">
-        <v>2.46</v>
+        <v>1.98</v>
       </c>
       <c r="AX12">
-        <v>1.89</v>
+        <v>1.61</v>
       </c>
       <c r="AY12">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="AZ12">
-        <v>1.92</v>
+        <v>5.03</v>
       </c>
       <c r="BA12">
-        <v>2.1</v>
+        <v>1.29</v>
       </c>
       <c r="BB12">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="BC12">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="BD12">
-        <v>5.7</v>
+        <v>4.33</v>
       </c>
       <c r="BE12">
-        <v>2.19</v>
+        <v>1.82</v>
       </c>
       <c r="BF12">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="BG12">
         <v>0</v>
@@ -3214,133 +3214,133 @@
         <v>188</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S13">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="T13">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="U13">
-        <v>2</v>
+        <v>2.78</v>
       </c>
       <c r="V13">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="W13">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="X13">
-        <v>2.41</v>
+        <v>2.08</v>
       </c>
       <c r="Y13">
-        <v>1.49</v>
+        <v>1.69</v>
       </c>
       <c r="Z13">
-        <v>5.5</v>
+        <v>4.45</v>
       </c>
       <c r="AA13">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AB13">
         <v>1.02</v>
       </c>
       <c r="AC13">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AD13">
-        <v>4</v>
+        <v>5.65</v>
       </c>
       <c r="AE13">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="AF13">
-        <v>2.16</v>
+        <v>2.59</v>
       </c>
       <c r="AG13">
-        <v>2.65</v>
+        <v>2.05</v>
       </c>
       <c r="AH13">
-        <v>1.39</v>
+        <v>1.76</v>
       </c>
       <c r="AI13">
-        <v>5.2</v>
+        <v>3.28</v>
       </c>
       <c r="AJ13">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AK13">
-        <v>1.77</v>
+        <v>1.36</v>
       </c>
       <c r="AL13">
-        <v>1.94</v>
+        <v>2.9</v>
       </c>
       <c r="AM13">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AN13">
-        <v>1.13</v>
+        <v>1.43</v>
       </c>
       <c r="AO13">
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="AQ13">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AR13">
-        <v>1.94</v>
+        <v>1.44</v>
       </c>
       <c r="AS13">
-        <v>2.16</v>
+        <v>1.81</v>
       </c>
       <c r="AT13">
-        <v>2.84</v>
+        <v>2.26</v>
       </c>
       <c r="AU13">
-        <v>3.72</v>
+        <v>5.06</v>
       </c>
       <c r="AV13">
-        <v>2.59</v>
+        <v>3.31</v>
       </c>
       <c r="AW13">
-        <v>1.98</v>
+        <v>2.46</v>
       </c>
       <c r="AX13">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="AY13">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="AZ13">
-        <v>5.03</v>
+        <v>1.92</v>
       </c>
       <c r="BA13">
-        <v>1.29</v>
+        <v>2.1</v>
       </c>
       <c r="BB13">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="BC13">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="BD13">
-        <v>4.33</v>
+        <v>5.7</v>
       </c>
       <c r="BE13">
-        <v>1.82</v>
+        <v>2.19</v>
       </c>
       <c r="BF13">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="BG13">
         <v>0</v>
@@ -3623,28 +3623,28 @@
         <v>0</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI15">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK15">
         <v>0</v>
@@ -3653,10 +3653,10 @@
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN15">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AO15">
         <v>0</v>
@@ -3954,22 +3954,22 @@
         <v>188</v>
       </c>
       <c r="P17">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q17">
-        <v>4.1</v>
+        <v>4.18</v>
       </c>
       <c r="R17">
-        <v>5.25</v>
+        <v>5.59</v>
       </c>
       <c r="S17">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="T17">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="U17">
-        <v>6.08</v>
+        <v>5.98</v>
       </c>
       <c r="V17">
         <v>1.26</v>
@@ -3978,13 +3978,13 @@
         <v>3.28</v>
       </c>
       <c r="X17">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Y17">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Z17">
-        <v>5.55</v>
+        <v>5.6</v>
       </c>
       <c r="AA17">
         <v>1.08</v>
@@ -3993,25 +3993,25 @@
         <v>1.01</v>
       </c>
       <c r="AC17">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AD17">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="AE17">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AF17">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="AG17">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="AH17">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="AI17">
-        <v>4.5</v>
+        <v>4.56</v>
       </c>
       <c r="AJ17">
         <v>1.13</v>
@@ -4035,37 +4035,37 @@
         <v>1.18</v>
       </c>
       <c r="AQ17">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AR17">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="AS17">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="AT17">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="AU17">
-        <v>3.68</v>
+        <v>3.82</v>
       </c>
       <c r="AV17">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="AW17">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AX17">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AY17">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AZ17">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="BA17">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BB17">
         <v>1.12</v>
@@ -4700,10 +4700,10 @@
         <v>3.1</v>
       </c>
       <c r="R21">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="S21">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="T21">
         <v>2.05</v>
@@ -4724,7 +4724,7 @@
         <v>1.28</v>
       </c>
       <c r="Z21">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="AA21">
         <v>1.01</v>
@@ -4733,7 +4733,7 @@
         <v>1.04</v>
       </c>
       <c r="AC21">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AD21">
         <v>2.62</v>
@@ -4742,10 +4742,10 @@
         <v>2.35</v>
       </c>
       <c r="AF21">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG21">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="AH21">
         <v>1.16</v>
@@ -4784,7 +4784,7 @@
         <v>2.95</v>
       </c>
       <c r="AT21">
-        <v>3.35</v>
+        <v>4.24</v>
       </c>
       <c r="AU21">
         <v>2.62</v>
@@ -4799,13 +4799,13 @@
         <v>1.31</v>
       </c>
       <c r="AY21">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AZ21">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="BA21">
-        <v>2.17</v>
+        <v>2.53</v>
       </c>
       <c r="BB21">
         <v>1.3</v>
@@ -4817,7 +4817,7 @@
         <v>3.16</v>
       </c>
       <c r="BE21">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BF21">
         <v>1.08</v>
@@ -6144,7 +6144,7 @@
         <v>134</v>
       </c>
       <c r="F29" t="s">
-        <v>175</v>
+        <v>145</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -6329,7 +6329,7 @@
         <v>135</v>
       </c>
       <c r="F30" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -6505,7 +6505,7 @@
         <v>80</v>
       </c>
       <c r="C31" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D31" t="s">
         <v>105</v>
@@ -6544,133 +6544,133 @@
         <v>188</v>
       </c>
       <c r="P31">
-        <v>5.48</v>
+        <v>1.98</v>
       </c>
       <c r="Q31">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="R31">
-        <v>1.55</v>
+        <v>3.45</v>
       </c>
       <c r="S31">
-        <v>7.1</v>
+        <v>2.5</v>
       </c>
       <c r="T31">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="U31">
-        <v>2.23</v>
+        <v>4.4</v>
       </c>
       <c r="V31">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="W31">
-        <v>2.28</v>
+        <v>2.73</v>
       </c>
       <c r="X31">
-        <v>3.48</v>
+        <v>2.96</v>
       </c>
       <c r="Y31">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="Z31">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AA31">
         <v>1.04</v>
       </c>
       <c r="AB31">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AC31">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AD31">
-        <v>2.43</v>
+        <v>3.43</v>
       </c>
       <c r="AE31">
-        <v>2.46</v>
+        <v>1.98</v>
       </c>
       <c r="AF31">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="AG31">
-        <v>4.65</v>
+        <v>3.45</v>
       </c>
       <c r="AH31">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AI31">
-        <v>9.199999999999999</v>
+        <v>6.75</v>
       </c>
       <c r="AJ31">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AK31">
-        <v>2.45</v>
+        <v>1.79</v>
       </c>
       <c r="AL31">
-        <v>1.49</v>
+        <v>1.92</v>
       </c>
       <c r="AM31">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AN31">
-        <v>1.1</v>
+        <v>1.75</v>
       </c>
       <c r="AO31">
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AQ31">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AR31">
-        <v>2.14</v>
+        <v>2.63</v>
       </c>
       <c r="AS31">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="AT31">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AU31">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AV31">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AW31">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AX31">
         <v>1.32</v>
       </c>
       <c r="AY31">
+        <v>1.14</v>
+      </c>
+      <c r="AZ31">
+        <v>1.56</v>
+      </c>
+      <c r="BA31">
+        <v>3.34</v>
+      </c>
+      <c r="BB31">
         <v>1.23</v>
       </c>
-      <c r="AZ31">
-        <v>2.39</v>
-      </c>
-      <c r="BA31">
-        <v>1.89</v>
-      </c>
-      <c r="BB31">
-        <v>1.32</v>
-      </c>
       <c r="BC31">
-        <v>2.56</v>
+        <v>2.2</v>
       </c>
       <c r="BD31">
-        <v>2.96</v>
+        <v>3.52</v>
       </c>
       <c r="BE31">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="BF31">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="BG31">
         <v>0</v>
@@ -6690,7 +6690,7 @@
         <v>80</v>
       </c>
       <c r="C32" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D32" t="s">
         <v>104</v>
@@ -6875,7 +6875,7 @@
         <v>80</v>
       </c>
       <c r="C33" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D33" t="s">
         <v>105</v>
@@ -6914,133 +6914,133 @@
         <v>188</v>
       </c>
       <c r="P33">
+        <v>4.88</v>
+      </c>
+      <c r="Q33">
+        <v>3.32</v>
+      </c>
+      <c r="R33">
+        <v>1.68</v>
+      </c>
+      <c r="S33">
+        <v>5.76</v>
+      </c>
+      <c r="T33">
         <v>2</v>
       </c>
-      <c r="Q33">
-        <v>3.3</v>
-      </c>
-      <c r="R33">
-        <v>3.4</v>
-      </c>
-      <c r="S33">
-        <v>2.5</v>
-      </c>
-      <c r="T33">
-        <v>2.06</v>
-      </c>
       <c r="U33">
-        <v>4.4</v>
+        <v>2.32</v>
       </c>
       <c r="V33">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="W33">
-        <v>2.73</v>
+        <v>2.47</v>
       </c>
       <c r="X33">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="Y33">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z33">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AA33">
+        <v>1.03</v>
+      </c>
+      <c r="AB33">
         <v>1.04</v>
       </c>
-      <c r="AB33">
-        <v>1.01</v>
-      </c>
       <c r="AC33">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AD33">
-        <v>3.08</v>
+        <v>2.78</v>
       </c>
       <c r="AE33">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="AF33">
-        <v>1.78</v>
+        <v>1.64</v>
       </c>
       <c r="AG33">
-        <v>3.45</v>
+        <v>3.88</v>
       </c>
       <c r="AH33">
+        <v>1.2</v>
+      </c>
+      <c r="AI33">
+        <v>7.1</v>
+      </c>
+      <c r="AJ33">
+        <v>1.04</v>
+      </c>
+      <c r="AK33">
+        <v>2.01</v>
+      </c>
+      <c r="AL33">
+        <v>1.7</v>
+      </c>
+      <c r="AM33">
+        <v>1.24</v>
+      </c>
+      <c r="AN33">
+        <v>1.11</v>
+      </c>
+      <c r="AO33">
+        <v>0</v>
+      </c>
+      <c r="AP33">
         <v>1.28</v>
       </c>
-      <c r="AI33">
-        <v>6.75</v>
-      </c>
-      <c r="AJ33">
-        <v>1.07</v>
-      </c>
-      <c r="AK33">
-        <v>1.79</v>
-      </c>
-      <c r="AL33">
-        <v>1.92</v>
-      </c>
-      <c r="AM33">
-        <v>1.28</v>
-      </c>
-      <c r="AN33">
-        <v>1.75</v>
-      </c>
-      <c r="AO33">
-        <v>0</v>
-      </c>
-      <c r="AP33">
-        <v>1.4</v>
-      </c>
       <c r="AQ33">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="AR33">
-        <v>2.19</v>
+        <v>1.95</v>
       </c>
       <c r="AS33">
-        <v>2.83</v>
+        <v>2.52</v>
       </c>
       <c r="AT33">
-        <v>4.2</v>
+        <v>3.48</v>
       </c>
       <c r="AU33">
-        <v>2.63</v>
+        <v>3.05</v>
       </c>
       <c r="AV33">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="AW33">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AX33">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AY33">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AZ33">
-        <v>1.56</v>
+        <v>2.46</v>
       </c>
       <c r="BA33">
-        <v>3.34</v>
+        <v>1.82</v>
       </c>
       <c r="BB33">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="BC33">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="BD33">
-        <v>3.52</v>
+        <v>3.28</v>
       </c>
       <c r="BE33">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="BF33">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="BG33">
         <v>0</v>
@@ -7060,7 +7060,7 @@
         <v>80</v>
       </c>
       <c r="C34" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D34" t="s">
         <v>105</v>
@@ -7099,133 +7099,133 @@
         <v>188</v>
       </c>
       <c r="P34">
-        <v>4.88</v>
+        <v>1.35</v>
       </c>
       <c r="Q34">
-        <v>3.32</v>
+        <v>4.1</v>
       </c>
       <c r="R34">
-        <v>1.68</v>
+        <v>8.65</v>
       </c>
       <c r="S34">
-        <v>5.76</v>
+        <v>1.86</v>
       </c>
       <c r="T34">
+        <v>2.15</v>
+      </c>
+      <c r="U34">
+        <v>8.35</v>
+      </c>
+      <c r="V34">
+        <v>1.42</v>
+      </c>
+      <c r="W34">
+        <v>2.56</v>
+      </c>
+      <c r="X34">
+        <v>2.91</v>
+      </c>
+      <c r="Y34">
+        <v>1.33</v>
+      </c>
+      <c r="Z34">
+        <v>7.1</v>
+      </c>
+      <c r="AA34">
+        <v>1.04</v>
+      </c>
+      <c r="AB34">
+        <v>1.06</v>
+      </c>
+      <c r="AC34">
+        <v>1.31</v>
+      </c>
+      <c r="AD34">
+        <v>2.92</v>
+      </c>
+      <c r="AE34">
         <v>2</v>
       </c>
-      <c r="U34">
-        <v>2.32</v>
-      </c>
-      <c r="V34">
-        <v>1.45</v>
-      </c>
-      <c r="W34">
-        <v>2.47</v>
-      </c>
-      <c r="X34">
-        <v>3.02</v>
-      </c>
-      <c r="Y34">
-        <v>1.31</v>
-      </c>
-      <c r="Z34">
-        <v>7.5</v>
-      </c>
-      <c r="AA34">
-        <v>1.03</v>
-      </c>
-      <c r="AB34">
-        <v>1.04</v>
-      </c>
-      <c r="AC34">
+      <c r="AF34">
+        <v>1.72</v>
+      </c>
+      <c r="AG34">
+        <v>3.58</v>
+      </c>
+      <c r="AH34">
+        <v>1.27</v>
+      </c>
+      <c r="AI34">
+        <v>6.4</v>
+      </c>
+      <c r="AJ34">
+        <v>1.05</v>
+      </c>
+      <c r="AK34">
+        <v>2.25</v>
+      </c>
+      <c r="AL34">
+        <v>1.6</v>
+      </c>
+      <c r="AM34">
+        <v>1.16</v>
+      </c>
+      <c r="AN34">
+        <v>2.76</v>
+      </c>
+      <c r="AO34">
+        <v>0</v>
+      </c>
+      <c r="AP34">
+        <v>1.24</v>
+      </c>
+      <c r="AQ34">
+        <v>1.46</v>
+      </c>
+      <c r="AR34">
+        <v>1.87</v>
+      </c>
+      <c r="AS34">
+        <v>2.33</v>
+      </c>
+      <c r="AT34">
+        <v>2.95</v>
+      </c>
+      <c r="AU34">
+        <v>3.15</v>
+      </c>
+      <c r="AV34">
+        <v>2.38</v>
+      </c>
+      <c r="AW34">
+        <v>1.83</v>
+      </c>
+      <c r="AX34">
+        <v>1.48</v>
+      </c>
+      <c r="AY34">
         <v>1.34</v>
       </c>
-      <c r="AD34">
-        <v>2.78</v>
-      </c>
-      <c r="AE34">
-        <v>2.12</v>
-      </c>
-      <c r="AF34">
-        <v>1.64</v>
-      </c>
-      <c r="AG34">
-        <v>3.88</v>
-      </c>
-      <c r="AH34">
-        <v>1.2</v>
-      </c>
-      <c r="AI34">
-        <v>7.1</v>
-      </c>
-      <c r="AJ34">
-        <v>1.04</v>
-      </c>
-      <c r="AK34">
-        <v>2.01</v>
-      </c>
-      <c r="AL34">
-        <v>1.7</v>
-      </c>
-      <c r="AM34">
-        <v>1.24</v>
-      </c>
-      <c r="AN34">
-        <v>1.11</v>
-      </c>
-      <c r="AO34">
-        <v>0</v>
-      </c>
-      <c r="AP34">
-        <v>1.28</v>
-      </c>
-      <c r="AQ34">
-        <v>1.61</v>
-      </c>
-      <c r="AR34">
-        <v>1.95</v>
-      </c>
-      <c r="AS34">
-        <v>2.52</v>
-      </c>
-      <c r="AT34">
-        <v>3.48</v>
-      </c>
-      <c r="AU34">
-        <v>3.05</v>
-      </c>
-      <c r="AV34">
-        <v>2.08</v>
-      </c>
-      <c r="AW34">
-        <v>1.73</v>
-      </c>
-      <c r="AX34">
-        <v>1.41</v>
-      </c>
-      <c r="AY34">
-        <v>1.22</v>
-      </c>
       <c r="AZ34">
-        <v>2.46</v>
+        <v>1.29</v>
       </c>
       <c r="BA34">
-        <v>1.82</v>
+        <v>4.32</v>
       </c>
       <c r="BB34">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BC34">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="BD34">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="BE34">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="BF34">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="BG34">
         <v>0</v>
@@ -7245,7 +7245,7 @@
         <v>80</v>
       </c>
       <c r="C35" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D35" t="s">
         <v>105</v>
@@ -7284,133 +7284,133 @@
         <v>188</v>
       </c>
       <c r="P35">
-        <v>1.35</v>
+        <v>5.48</v>
       </c>
       <c r="Q35">
-        <v>4.1</v>
+        <v>3.34</v>
       </c>
       <c r="R35">
-        <v>8.65</v>
+        <v>1.55</v>
       </c>
       <c r="S35">
-        <v>1.86</v>
+        <v>7.1</v>
       </c>
       <c r="T35">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="U35">
-        <v>8.35</v>
+        <v>2.23</v>
       </c>
       <c r="V35">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="W35">
-        <v>2.56</v>
+        <v>2.28</v>
       </c>
       <c r="X35">
-        <v>2.91</v>
+        <v>3.48</v>
       </c>
       <c r="Y35">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="Z35">
-        <v>7.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA35">
         <v>1.04</v>
       </c>
       <c r="AB35">
+        <v>1.1</v>
+      </c>
+      <c r="AC35">
+        <v>1.38</v>
+      </c>
+      <c r="AD35">
+        <v>2.43</v>
+      </c>
+      <c r="AE35">
+        <v>2.46</v>
+      </c>
+      <c r="AF35">
+        <v>1.48</v>
+      </c>
+      <c r="AG35">
+        <v>4.65</v>
+      </c>
+      <c r="AH35">
+        <v>1.12</v>
+      </c>
+      <c r="AI35">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AJ35">
+        <v>1</v>
+      </c>
+      <c r="AK35">
+        <v>2.45</v>
+      </c>
+      <c r="AL35">
+        <v>1.49</v>
+      </c>
+      <c r="AM35">
+        <v>1.24</v>
+      </c>
+      <c r="AN35">
+        <v>1.1</v>
+      </c>
+      <c r="AO35">
+        <v>0</v>
+      </c>
+      <c r="AP35">
+        <v>1.36</v>
+      </c>
+      <c r="AQ35">
+        <v>1.69</v>
+      </c>
+      <c r="AR35">
+        <v>2.14</v>
+      </c>
+      <c r="AS35">
+        <v>2.88</v>
+      </c>
+      <c r="AT35">
+        <v>3.6</v>
+      </c>
+      <c r="AU35">
+        <v>2.7</v>
+      </c>
+      <c r="AV35">
+        <v>2</v>
+      </c>
+      <c r="AW35">
+        <v>1.57</v>
+      </c>
+      <c r="AX35">
+        <v>1.32</v>
+      </c>
+      <c r="AY35">
+        <v>1.23</v>
+      </c>
+      <c r="AZ35">
+        <v>2.39</v>
+      </c>
+      <c r="BA35">
+        <v>1.89</v>
+      </c>
+      <c r="BB35">
+        <v>1.32</v>
+      </c>
+      <c r="BC35">
+        <v>2.56</v>
+      </c>
+      <c r="BD35">
+        <v>2.96</v>
+      </c>
+      <c r="BE35">
+        <v>1.42</v>
+      </c>
+      <c r="BF35">
         <v>1.06</v>
-      </c>
-      <c r="AC35">
-        <v>1.31</v>
-      </c>
-      <c r="AD35">
-        <v>2.92</v>
-      </c>
-      <c r="AE35">
-        <v>2</v>
-      </c>
-      <c r="AF35">
-        <v>1.72</v>
-      </c>
-      <c r="AG35">
-        <v>3.58</v>
-      </c>
-      <c r="AH35">
-        <v>1.27</v>
-      </c>
-      <c r="AI35">
-        <v>6.4</v>
-      </c>
-      <c r="AJ35">
-        <v>1.05</v>
-      </c>
-      <c r="AK35">
-        <v>2.25</v>
-      </c>
-      <c r="AL35">
-        <v>1.6</v>
-      </c>
-      <c r="AM35">
-        <v>1.16</v>
-      </c>
-      <c r="AN35">
-        <v>2.76</v>
-      </c>
-      <c r="AO35">
-        <v>0</v>
-      </c>
-      <c r="AP35">
-        <v>1.24</v>
-      </c>
-      <c r="AQ35">
-        <v>1.46</v>
-      </c>
-      <c r="AR35">
-        <v>1.87</v>
-      </c>
-      <c r="AS35">
-        <v>2.33</v>
-      </c>
-      <c r="AT35">
-        <v>2.95</v>
-      </c>
-      <c r="AU35">
-        <v>3.15</v>
-      </c>
-      <c r="AV35">
-        <v>2.38</v>
-      </c>
-      <c r="AW35">
-        <v>1.83</v>
-      </c>
-      <c r="AX35">
-        <v>1.48</v>
-      </c>
-      <c r="AY35">
-        <v>1.34</v>
-      </c>
-      <c r="AZ35">
-        <v>1.29</v>
-      </c>
-      <c r="BA35">
-        <v>4.32</v>
-      </c>
-      <c r="BB35">
-        <v>1.23</v>
-      </c>
-      <c r="BC35">
-        <v>2.3</v>
-      </c>
-      <c r="BD35">
-        <v>3.42</v>
-      </c>
-      <c r="BE35">
-        <v>1.6</v>
-      </c>
-      <c r="BF35">
-        <v>1.13</v>
       </c>
       <c r="BG35">
         <v>0</v>
@@ -7839,127 +7839,127 @@
         <v>188</v>
       </c>
       <c r="P38">
-        <v>6.39</v>
+        <v>3.3</v>
       </c>
       <c r="Q38">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="R38">
-        <v>1.54</v>
+        <v>2.1</v>
       </c>
       <c r="S38">
-        <v>8.050000000000001</v>
+        <v>4.43</v>
       </c>
       <c r="T38">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="U38">
-        <v>2.13</v>
+        <v>2.88</v>
       </c>
       <c r="V38">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W38">
-        <v>2.44</v>
+        <v>2.31</v>
       </c>
       <c r="X38">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="Y38">
         <v>1.25</v>
       </c>
       <c r="Z38">
-        <v>10</v>
+        <v>9.1</v>
       </c>
       <c r="AA38">
         <v>1</v>
       </c>
       <c r="AB38">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AC38">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AD38">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AE38">
-        <v>2.23</v>
+        <v>2.65</v>
       </c>
       <c r="AF38">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AG38">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="AH38">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AI38">
-        <v>8.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AJ38">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AK38">
-        <v>2.51</v>
+        <v>2.04</v>
       </c>
       <c r="AL38">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="AM38">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AN38">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="AO38">
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AQ38">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AR38">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AS38">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="AT38">
-        <v>4.41</v>
+        <v>4.15</v>
       </c>
       <c r="AU38">
-        <v>2.55</v>
+        <v>2.66</v>
       </c>
       <c r="AV38">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AW38">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AX38">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AY38">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AZ38">
-        <v>3.85</v>
+        <v>2.12</v>
       </c>
       <c r="BA38">
-        <v>1.43</v>
+        <v>2.08</v>
       </c>
       <c r="BB38">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BC38">
         <v>2.59</v>
       </c>
       <c r="BD38">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="BE38">
         <v>1.41</v>
@@ -8024,127 +8024,127 @@
         <v>188</v>
       </c>
       <c r="P39">
+        <v>6.39</v>
+      </c>
+      <c r="Q39">
+        <v>3.5</v>
+      </c>
+      <c r="R39">
+        <v>1.54</v>
+      </c>
+      <c r="S39">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="T39">
+        <v>2.08</v>
+      </c>
+      <c r="U39">
+        <v>2.13</v>
+      </c>
+      <c r="V39">
+        <v>1.53</v>
+      </c>
+      <c r="W39">
+        <v>2.44</v>
+      </c>
+      <c r="X39">
         <v>3.3</v>
-      </c>
-      <c r="Q39">
-        <v>3</v>
-      </c>
-      <c r="R39">
-        <v>2.1</v>
-      </c>
-      <c r="S39">
-        <v>4.43</v>
-      </c>
-      <c r="T39">
-        <v>1.92</v>
-      </c>
-      <c r="U39">
-        <v>2.88</v>
-      </c>
-      <c r="V39">
-        <v>1.51</v>
-      </c>
-      <c r="W39">
-        <v>2.31</v>
-      </c>
-      <c r="X39">
-        <v>3.38</v>
       </c>
       <c r="Y39">
         <v>1.25</v>
       </c>
       <c r="Z39">
-        <v>9.1</v>
+        <v>10</v>
       </c>
       <c r="AA39">
         <v>1</v>
       </c>
       <c r="AB39">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AC39">
+        <v>1.38</v>
+      </c>
+      <c r="AD39">
+        <v>2.43</v>
+      </c>
+      <c r="AE39">
+        <v>2.23</v>
+      </c>
+      <c r="AF39">
+        <v>1.49</v>
+      </c>
+      <c r="AG39">
+        <v>4.65</v>
+      </c>
+      <c r="AH39">
+        <v>1.12</v>
+      </c>
+      <c r="AI39">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AJ39">
+        <v>1</v>
+      </c>
+      <c r="AK39">
+        <v>2.51</v>
+      </c>
+      <c r="AL39">
+        <v>1.46</v>
+      </c>
+      <c r="AM39">
+        <v>1.22</v>
+      </c>
+      <c r="AN39">
+        <v>1.04</v>
+      </c>
+      <c r="AO39">
+        <v>0</v>
+      </c>
+      <c r="AP39">
+        <v>1.42</v>
+      </c>
+      <c r="AQ39">
+        <v>1.77</v>
+      </c>
+      <c r="AR39">
+        <v>2.16</v>
+      </c>
+      <c r="AS39">
+        <v>3.04</v>
+      </c>
+      <c r="AT39">
+        <v>4.41</v>
+      </c>
+      <c r="AU39">
+        <v>2.55</v>
+      </c>
+      <c r="AV39">
+        <v>1.94</v>
+      </c>
+      <c r="AW39">
+        <v>1.56</v>
+      </c>
+      <c r="AX39">
+        <v>1.29</v>
+      </c>
+      <c r="AY39">
+        <v>1.13</v>
+      </c>
+      <c r="AZ39">
+        <v>3.85</v>
+      </c>
+      <c r="BA39">
         <v>1.43</v>
       </c>
-      <c r="AD39">
-        <v>2.46</v>
-      </c>
-      <c r="AE39">
-        <v>2.65</v>
-      </c>
-      <c r="AF39">
-        <v>1.51</v>
-      </c>
-      <c r="AG39">
-        <v>4.6</v>
-      </c>
-      <c r="AH39">
-        <v>1.17</v>
-      </c>
-      <c r="AI39">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AJ39">
-        <v>1.05</v>
-      </c>
-      <c r="AK39">
-        <v>2.04</v>
-      </c>
-      <c r="AL39">
-        <v>1.62</v>
-      </c>
-      <c r="AM39">
-        <v>1.3</v>
-      </c>
-      <c r="AN39">
-        <v>1.24</v>
-      </c>
-      <c r="AO39">
-        <v>0</v>
-      </c>
-      <c r="AP39">
-        <v>1.39</v>
-      </c>
-      <c r="AQ39">
-        <v>1.72</v>
-      </c>
-      <c r="AR39">
-        <v>2.17</v>
-      </c>
-      <c r="AS39">
-        <v>2.9</v>
-      </c>
-      <c r="AT39">
-        <v>4.15</v>
-      </c>
-      <c r="AU39">
-        <v>2.66</v>
-      </c>
-      <c r="AV39">
-        <v>2</v>
-      </c>
-      <c r="AW39">
-        <v>1.6</v>
-      </c>
-      <c r="AX39">
-        <v>1.32</v>
-      </c>
-      <c r="AY39">
-        <v>1.15</v>
-      </c>
-      <c r="AZ39">
-        <v>2.12</v>
-      </c>
-      <c r="BA39">
-        <v>2.08</v>
-      </c>
       <c r="BB39">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="BC39">
         <v>2.59</v>
       </c>
       <c r="BD39">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="BE39">
         <v>1.41</v>
@@ -8397,10 +8397,10 @@
         <v>1.63</v>
       </c>
       <c r="Q41">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="R41">
-        <v>5.25</v>
+        <v>5.27</v>
       </c>
       <c r="S41">
         <v>2.18</v>
@@ -8418,13 +8418,13 @@
         <v>2.85</v>
       </c>
       <c r="X41">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="Y41">
         <v>1.43</v>
       </c>
       <c r="Z41">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="AA41">
         <v>1.07</v>
@@ -8439,7 +8439,7 @@
         <v>3.45</v>
       </c>
       <c r="AE41">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AF41">
         <v>1.9</v>
@@ -8448,19 +8448,19 @@
         <v>3.08</v>
       </c>
       <c r="AH41">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AI41">
         <v>6.25</v>
       </c>
       <c r="AJ41">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AK41">
         <v>1.85</v>
       </c>
       <c r="AL41">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AM41">
         <v>1.28</v>
@@ -8472,52 +8472,52 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AQ41">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AR41">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="AS41">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AT41">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AU41">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="AV41">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AW41">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="AX41">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AY41">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AZ41">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="BA41">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BB41">
         <v>1.22</v>
       </c>
       <c r="BC41">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="BD41">
         <v>4.05</v>
       </c>
       <c r="BE41">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="BF41">
         <v>1.18</v>

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -310,12 +310,12 @@
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
+    <t>Egypt Egyptian Premier League</t>
+  </si>
+  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
-    <t>Egypt Egyptian Premier League</t>
-  </si>
-  <si>
     <t>South Africa Premier Soccer League</t>
   </si>
   <si>
@@ -337,21 +337,21 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Jeonbuk Motors</t>
+  </si>
+  <si>
     <t>Bucheon 1995</t>
   </si>
   <si>
-    <t>Jeonbuk Motors</t>
+    <t>Sangju Sangmu</t>
+  </si>
+  <si>
+    <t>Gangwon</t>
   </si>
   <si>
     <t>Daejeon Citizen</t>
   </si>
   <si>
-    <t>Gangwon</t>
-  </si>
-  <si>
-    <t>Sangju Sangmu</t>
-  </si>
-  <si>
     <t>Madura United</t>
   </si>
   <si>
@@ -367,24 +367,24 @@
     <t>Tanjong Pagar</t>
   </si>
   <si>
+    <t>Shandong Luneng</t>
+  </si>
+  <si>
     <t>Shenyang Urban</t>
   </si>
   <si>
-    <t>Shandong Luneng</t>
+    <t>Karvan FK</t>
+  </si>
+  <si>
+    <t>Borneo</t>
+  </si>
+  <si>
+    <t>Dire Dawa Kenema</t>
   </si>
   <si>
     <t>Chongqing Tongliang Long</t>
   </si>
   <si>
-    <t>Karvan FK</t>
-  </si>
-  <si>
-    <t>Dire Dawa Kenema</t>
-  </si>
-  <si>
-    <t>Borneo</t>
-  </si>
-  <si>
     <t>Mekelle Kenema</t>
   </si>
   <si>
@@ -415,42 +415,42 @@
     <t>Maccabi Tel Aviv</t>
   </si>
   <si>
+    <t>Al Ittihad Kalba</t>
+  </si>
+  <si>
     <t>Bani Yas</t>
   </si>
   <si>
-    <t>Al Ittihad Kalba</t>
-  </si>
-  <si>
     <t>Dibba Al Fujairah</t>
   </si>
   <si>
+    <t>Smouha SC</t>
+  </si>
+  <si>
+    <t>Falkenberg</t>
+  </si>
+  <si>
     <t>Lokomotiv Sofia 1929</t>
   </si>
   <si>
-    <t>Falkenberg</t>
-  </si>
-  <si>
     <t>Ceramica Cleopatra</t>
   </si>
   <si>
     <t>Al Ahly</t>
   </si>
   <si>
-    <t>Smouha SC</t>
+    <t>Stellenbosch</t>
+  </si>
+  <si>
+    <t>Magesi</t>
+  </si>
+  <si>
+    <t>Chippa United</t>
   </si>
   <si>
     <t>Siwelele</t>
   </si>
   <si>
-    <t>Magesi</t>
-  </si>
-  <si>
-    <t>Chippa United</t>
-  </si>
-  <si>
-    <t>Stellenbosch</t>
-  </si>
-  <si>
     <t>Al Khaleej</t>
   </si>
   <si>
@@ -460,21 +460,21 @@
     <t>New York City II</t>
   </si>
   <si>
+    <t>Gwangju</t>
+  </si>
+  <si>
     <t>Jeju United</t>
   </si>
   <si>
-    <t>Gwangju</t>
+    <t>Ulsan</t>
+  </si>
+  <si>
+    <t>Pohang Steelers</t>
   </si>
   <si>
     <t>Incheon United</t>
   </si>
   <si>
-    <t>Pohang Steelers</t>
-  </si>
-  <si>
-    <t>Ulsan</t>
-  </si>
-  <si>
     <t>Bali United</t>
   </si>
   <si>
@@ -490,24 +490,24 @@
     <t>Hougang United</t>
   </si>
   <si>
+    <t>Shanghai Shenhua</t>
+  </si>
+  <si>
     <t>Chengdu Better City FC</t>
   </si>
   <si>
-    <t>Shanghai Shenhua</t>
+    <t>Neftçi</t>
+  </si>
+  <si>
+    <t>Persita</t>
+  </si>
+  <si>
+    <t>Ethiopia Bunna</t>
   </si>
   <si>
     <t>Henan Jianye</t>
   </si>
   <si>
-    <t>Neftçi</t>
-  </si>
-  <si>
-    <t>Ethiopia Bunna</t>
-  </si>
-  <si>
-    <t>Persita</t>
-  </si>
-  <si>
     <t>Arba Minch Kenema</t>
   </si>
   <si>
@@ -544,31 +544,31 @@
     <t>Al Bataeh</t>
   </si>
   <si>
+    <t>Zamalek</t>
+  </si>
+  <si>
+    <t>Norrköping</t>
+  </si>
+  <si>
     <t>Botev Vratsa</t>
   </si>
   <si>
-    <t>Norrköping</t>
-  </si>
-  <si>
     <t>Pyramids FC</t>
   </si>
   <si>
     <t>ENPPI</t>
   </si>
   <si>
-    <t>Zamalek</t>
+    <t>Orlando Pirates</t>
+  </si>
+  <si>
+    <t>Orbit College</t>
+  </si>
+  <si>
+    <t>Sekhukhune United</t>
   </si>
   <si>
     <t>Durban City</t>
-  </si>
-  <si>
-    <t>Orbit College</t>
-  </si>
-  <si>
-    <t>Sekhukhune United</t>
-  </si>
-  <si>
-    <t>Orlando Pirates</t>
   </si>
   <si>
     <t>Al Hilal</t>
@@ -1179,133 +1179,133 @@
         <v>188</v>
       </c>
       <c r="P2">
-        <v>2.45</v>
+        <v>1.34</v>
       </c>
       <c r="Q2">
-        <v>3.15</v>
+        <v>4.35</v>
       </c>
       <c r="R2">
-        <v>2.8</v>
+        <v>7.91</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AE2">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="AF2">
+        <v>1.85</v>
+      </c>
+      <c r="AG2">
+        <v>3.4</v>
+      </c>
+      <c r="AH2">
+        <v>1.27</v>
+      </c>
+      <c r="AI2">
+        <v>6.1</v>
+      </c>
+      <c r="AJ2">
+        <v>1.06</v>
+      </c>
+      <c r="AK2">
+        <v>2.26</v>
+      </c>
+      <c r="AL2">
         <v>1.57</v>
       </c>
-      <c r="AG2">
-        <v>0</v>
-      </c>
-      <c r="AH2">
-        <v>0</v>
-      </c>
-      <c r="AI2">
-        <v>0</v>
-      </c>
-      <c r="AJ2">
-        <v>0</v>
-      </c>
-      <c r="AK2">
-        <v>0</v>
-      </c>
-      <c r="AL2">
-        <v>0</v>
-      </c>
       <c r="AM2">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AO2">
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AU2">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AV2">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AW2">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AX2">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AY2">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AZ2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BA2">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BB2">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC2">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="BD2">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BE2">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF2">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG2">
         <v>0</v>
@@ -1364,133 +1364,133 @@
         <v>188</v>
       </c>
       <c r="P3">
-        <v>1.34</v>
+        <v>2.45</v>
       </c>
       <c r="Q3">
-        <v>4.35</v>
+        <v>3.15</v>
       </c>
       <c r="R3">
-        <v>7.91</v>
+        <v>2.8</v>
       </c>
       <c r="S3">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y3">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z3">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC3">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AD3">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AE3">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="AF3">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AG3">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AH3">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK3">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AL3">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN3">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AO3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AQ3">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AR3">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="AS3">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AT3">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AU3">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AV3">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AW3">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AX3">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AY3">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AZ3">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BA3">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="BB3">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC3">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="BD3">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BE3">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BF3">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG3">
         <v>0</v>
@@ -1549,133 +1549,133 @@
         <v>188</v>
       </c>
       <c r="P4">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>2.87</v>
+        <v>3.25</v>
       </c>
       <c r="T4">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="U4">
-        <v>4.06</v>
+        <v>3.24</v>
       </c>
       <c r="V4">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W4">
-        <v>2.59</v>
+        <v>2.77</v>
       </c>
       <c r="X4">
-        <v>3.04</v>
+        <v>2.65</v>
       </c>
       <c r="Y4">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z4">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="AA4">
         <v>1.03</v>
       </c>
       <c r="AB4">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC4">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AD4">
-        <v>2.94</v>
+        <v>3.18</v>
       </c>
       <c r="AE4">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="AF4">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AG4">
-        <v>3.65</v>
+        <v>3.48</v>
       </c>
       <c r="AH4">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AI4">
-        <v>6.75</v>
+        <v>6.73</v>
       </c>
       <c r="AJ4">
         <v>1.04</v>
       </c>
       <c r="AK4">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AL4">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AM4">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AN4">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AO4">
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="AQ4">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AR4">
-        <v>3.08</v>
+        <v>2.18</v>
       </c>
       <c r="AS4">
-        <v>3.42</v>
+        <v>2.9</v>
       </c>
       <c r="AT4">
-        <v>5.11</v>
+        <v>4.16</v>
       </c>
       <c r="AU4">
-        <v>2.34</v>
+        <v>2.66</v>
       </c>
       <c r="AV4">
+        <v>2.1</v>
+      </c>
+      <c r="AW4">
+        <v>1.6</v>
+      </c>
+      <c r="AX4">
+        <v>1.32</v>
+      </c>
+      <c r="AY4">
+        <v>1.15</v>
+      </c>
+      <c r="AZ4">
         <v>1.81</v>
       </c>
-      <c r="AW4">
-        <v>1.46</v>
-      </c>
-      <c r="AX4">
-        <v>1.23</v>
-      </c>
-      <c r="AY4">
-        <v>1.11</v>
-      </c>
-      <c r="AZ4">
-        <v>1.72</v>
-      </c>
       <c r="BA4">
-        <v>2.21</v>
+        <v>2.6</v>
       </c>
       <c r="BB4">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BC4">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="BD4">
-        <v>3.5</v>
+        <v>3.66</v>
       </c>
       <c r="BE4">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="BF4">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BG4">
         <v>0</v>
@@ -1919,133 +1919,133 @@
         <v>188</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S6">
-        <v>3.25</v>
+        <v>2.87</v>
       </c>
       <c r="T6">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="U6">
-        <v>3.24</v>
+        <v>4.06</v>
       </c>
       <c r="V6">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W6">
-        <v>2.77</v>
+        <v>2.59</v>
       </c>
       <c r="X6">
-        <v>2.65</v>
+        <v>3.04</v>
       </c>
       <c r="Y6">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z6">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="AA6">
         <v>1.03</v>
       </c>
       <c r="AB6">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AC6">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AD6">
-        <v>3.18</v>
+        <v>2.94</v>
       </c>
       <c r="AE6">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AF6">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AG6">
-        <v>3.48</v>
+        <v>3.65</v>
       </c>
       <c r="AH6">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AI6">
-        <v>6.73</v>
+        <v>6.75</v>
       </c>
       <c r="AJ6">
         <v>1.04</v>
       </c>
       <c r="AK6">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AL6">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AM6">
+        <v>1.35</v>
+      </c>
+      <c r="AN6">
+        <v>1.62</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>1.51</v>
+      </c>
+      <c r="AQ6">
+        <v>1.9</v>
+      </c>
+      <c r="AR6">
+        <v>3.08</v>
+      </c>
+      <c r="AS6">
+        <v>3.42</v>
+      </c>
+      <c r="AT6">
+        <v>5.11</v>
+      </c>
+      <c r="AU6">
+        <v>2.34</v>
+      </c>
+      <c r="AV6">
+        <v>1.81</v>
+      </c>
+      <c r="AW6">
         <v>1.46</v>
       </c>
-      <c r="AN6">
-        <v>1.44</v>
-      </c>
-      <c r="AO6">
-        <v>0</v>
-      </c>
-      <c r="AP6">
-        <v>1.39</v>
-      </c>
-      <c r="AQ6">
+      <c r="AX6">
+        <v>1.23</v>
+      </c>
+      <c r="AY6">
+        <v>1.11</v>
+      </c>
+      <c r="AZ6">
         <v>1.72</v>
       </c>
-      <c r="AR6">
-        <v>2.18</v>
-      </c>
-      <c r="AS6">
-        <v>2.9</v>
-      </c>
-      <c r="AT6">
-        <v>4.16</v>
-      </c>
-      <c r="AU6">
-        <v>2.66</v>
-      </c>
-      <c r="AV6">
-        <v>2.1</v>
-      </c>
-      <c r="AW6">
-        <v>1.6</v>
-      </c>
-      <c r="AX6">
-        <v>1.32</v>
-      </c>
-      <c r="AY6">
-        <v>1.15</v>
-      </c>
-      <c r="AZ6">
-        <v>1.81</v>
-      </c>
       <c r="BA6">
-        <v>2.6</v>
+        <v>2.21</v>
       </c>
       <c r="BB6">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="BC6">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="BD6">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="BE6">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="BF6">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BG6">
         <v>0</v>
@@ -2844,79 +2844,79 @@
         <v>188</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AO11">
         <v>0</v>
@@ -2958,19 +2958,19 @@
         <v>0</v>
       </c>
       <c r="BB11">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC11">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BD11">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE11">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BF11">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BG11">
         <v>0</v>
@@ -3029,133 +3029,133 @@
         <v>188</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S12">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="T12">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="U12">
-        <v>2</v>
+        <v>2.78</v>
       </c>
       <c r="V12">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="W12">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="X12">
-        <v>2.41</v>
+        <v>2.08</v>
       </c>
       <c r="Y12">
-        <v>1.49</v>
+        <v>1.69</v>
       </c>
       <c r="Z12">
-        <v>5.5</v>
+        <v>4.45</v>
       </c>
       <c r="AA12">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AB12">
         <v>1.02</v>
       </c>
       <c r="AC12">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AD12">
-        <v>4</v>
+        <v>5.65</v>
       </c>
       <c r="AE12">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="AF12">
-        <v>2.16</v>
+        <v>2.59</v>
       </c>
       <c r="AG12">
-        <v>2.65</v>
+        <v>2.05</v>
       </c>
       <c r="AH12">
-        <v>1.39</v>
+        <v>1.76</v>
       </c>
       <c r="AI12">
-        <v>5.2</v>
+        <v>3.28</v>
       </c>
       <c r="AJ12">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AK12">
-        <v>1.77</v>
+        <v>1.36</v>
       </c>
       <c r="AL12">
-        <v>1.94</v>
+        <v>2.9</v>
       </c>
       <c r="AM12">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AN12">
-        <v>1.13</v>
+        <v>1.43</v>
       </c>
       <c r="AO12">
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="AQ12">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AR12">
-        <v>1.94</v>
+        <v>1.44</v>
       </c>
       <c r="AS12">
-        <v>2.16</v>
+        <v>1.81</v>
       </c>
       <c r="AT12">
-        <v>2.84</v>
+        <v>2.26</v>
       </c>
       <c r="AU12">
-        <v>3.72</v>
+        <v>5.06</v>
       </c>
       <c r="AV12">
-        <v>2.59</v>
+        <v>3.31</v>
       </c>
       <c r="AW12">
-        <v>1.98</v>
+        <v>2.46</v>
       </c>
       <c r="AX12">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="AY12">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="AZ12">
-        <v>5.03</v>
+        <v>1.92</v>
       </c>
       <c r="BA12">
-        <v>1.29</v>
+        <v>2.1</v>
       </c>
       <c r="BB12">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="BC12">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="BD12">
-        <v>4.33</v>
+        <v>5.7</v>
       </c>
       <c r="BE12">
-        <v>1.82</v>
+        <v>2.19</v>
       </c>
       <c r="BF12">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="BG12">
         <v>0</v>
@@ -3214,133 +3214,133 @@
         <v>188</v>
       </c>
       <c r="P13">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q13">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R13">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S13">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="T13">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="U13">
-        <v>2.78</v>
+        <v>2</v>
       </c>
       <c r="V13">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="W13">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="X13">
-        <v>2.08</v>
+        <v>2.41</v>
       </c>
       <c r="Y13">
-        <v>1.69</v>
+        <v>1.49</v>
       </c>
       <c r="Z13">
-        <v>4.45</v>
+        <v>5.5</v>
       </c>
       <c r="AA13">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AB13">
         <v>1.02</v>
       </c>
       <c r="AC13">
+        <v>1.17</v>
+      </c>
+      <c r="AD13">
+        <v>4</v>
+      </c>
+      <c r="AE13">
+        <v>1.68</v>
+      </c>
+      <c r="AF13">
+        <v>2.16</v>
+      </c>
+      <c r="AG13">
+        <v>2.65</v>
+      </c>
+      <c r="AH13">
+        <v>1.39</v>
+      </c>
+      <c r="AI13">
+        <v>5.2</v>
+      </c>
+      <c r="AJ13">
+        <v>1.12</v>
+      </c>
+      <c r="AK13">
+        <v>1.77</v>
+      </c>
+      <c r="AL13">
+        <v>1.94</v>
+      </c>
+      <c r="AM13">
+        <v>1.21</v>
+      </c>
+      <c r="AN13">
         <v>1.13</v>
       </c>
-      <c r="AD13">
-        <v>5.65</v>
-      </c>
-      <c r="AE13">
-        <v>1.44</v>
-      </c>
-      <c r="AF13">
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>1.19</v>
+      </c>
+      <c r="AQ13">
+        <v>1.41</v>
+      </c>
+      <c r="AR13">
+        <v>1.94</v>
+      </c>
+      <c r="AS13">
+        <v>2.16</v>
+      </c>
+      <c r="AT13">
+        <v>2.84</v>
+      </c>
+      <c r="AU13">
+        <v>3.72</v>
+      </c>
+      <c r="AV13">
         <v>2.59</v>
       </c>
-      <c r="AG13">
-        <v>2.05</v>
-      </c>
-      <c r="AH13">
-        <v>1.76</v>
-      </c>
-      <c r="AI13">
-        <v>3.28</v>
-      </c>
-      <c r="AJ13">
-        <v>1.25</v>
-      </c>
-      <c r="AK13">
-        <v>1.36</v>
-      </c>
-      <c r="AL13">
-        <v>2.9</v>
-      </c>
-      <c r="AM13">
-        <v>1.28</v>
-      </c>
-      <c r="AN13">
-        <v>1.43</v>
-      </c>
-      <c r="AO13">
-        <v>0</v>
-      </c>
-      <c r="AP13">
-        <v>1.08</v>
-      </c>
-      <c r="AQ13">
-        <v>1.25</v>
-      </c>
-      <c r="AR13">
-        <v>1.44</v>
-      </c>
-      <c r="AS13">
-        <v>1.81</v>
-      </c>
-      <c r="AT13">
-        <v>2.26</v>
-      </c>
-      <c r="AU13">
-        <v>5.06</v>
-      </c>
-      <c r="AV13">
-        <v>3.31</v>
-      </c>
       <c r="AW13">
-        <v>2.46</v>
+        <v>1.98</v>
       </c>
       <c r="AX13">
-        <v>1.89</v>
+        <v>1.61</v>
       </c>
       <c r="AY13">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="AZ13">
-        <v>1.92</v>
+        <v>5.03</v>
       </c>
       <c r="BA13">
-        <v>2.1</v>
+        <v>1.29</v>
       </c>
       <c r="BB13">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="BC13">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="BD13">
-        <v>5.7</v>
+        <v>4.33</v>
       </c>
       <c r="BE13">
-        <v>2.19</v>
+        <v>1.82</v>
       </c>
       <c r="BF13">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="BG13">
         <v>0</v>
@@ -3360,10 +3360,10 @@
         <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E14" t="s">
         <v>119</v>
@@ -3399,133 +3399,133 @@
         <v>188</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S14">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>1.35</v>
+        <v>1.12</v>
       </c>
       <c r="AD14">
-        <v>2.92</v>
+        <v>4.8</v>
       </c>
       <c r="AE14">
+        <v>1.45</v>
+      </c>
+      <c r="AF14">
+        <v>2.43</v>
+      </c>
+      <c r="AG14">
         <v>2.14</v>
       </c>
-      <c r="AF14">
-        <v>1.72</v>
-      </c>
-      <c r="AG14">
-        <v>3.73</v>
-      </c>
       <c r="AH14">
-        <v>1.21</v>
+        <v>1.58</v>
       </c>
       <c r="AI14">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="AJ14">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="AK14">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL14">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AM14">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AN14">
-        <v>1.46</v>
+        <v>1.05</v>
       </c>
       <c r="AO14">
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AQ14">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AR14">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AS14">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AT14">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AU14">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="AV14">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AW14">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AX14">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AY14">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AZ14">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="BA14">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BB14">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC14">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD14">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="BE14">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF14">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG14">
         <v>0</v>
@@ -3545,7 +3545,7 @@
         <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D15" t="s">
         <v>105</v>
@@ -3584,133 +3584,133 @@
         <v>188</v>
       </c>
       <c r="P15">
-        <v>8</v>
+        <v>1.46</v>
       </c>
       <c r="Q15">
-        <v>4.9</v>
+        <v>4.18</v>
       </c>
       <c r="R15">
-        <v>1.31</v>
+        <v>5.59</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>5.98</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC15">
+        <v>1.2</v>
+      </c>
+      <c r="AD15">
+        <v>4.33</v>
+      </c>
+      <c r="AE15">
+        <v>1.6</v>
+      </c>
+      <c r="AF15">
+        <v>2.17</v>
+      </c>
+      <c r="AG15">
+        <v>2.57</v>
+      </c>
+      <c r="AH15">
+        <v>1.43</v>
+      </c>
+      <c r="AI15">
+        <v>4.56</v>
+      </c>
+      <c r="AJ15">
+        <v>1.13</v>
+      </c>
+      <c r="AK15">
+        <v>1.67</v>
+      </c>
+      <c r="AL15">
+        <v>1.96</v>
+      </c>
+      <c r="AM15">
+        <v>1.06</v>
+      </c>
+      <c r="AN15">
+        <v>2.49</v>
+      </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <v>1.18</v>
+      </c>
+      <c r="AQ15">
+        <v>1.39</v>
+      </c>
+      <c r="AR15">
+        <v>1.71</v>
+      </c>
+      <c r="AS15">
+        <v>2.12</v>
+      </c>
+      <c r="AT15">
+        <v>2.76</v>
+      </c>
+      <c r="AU15">
+        <v>3.82</v>
+      </c>
+      <c r="AV15">
+        <v>2.65</v>
+      </c>
+      <c r="AW15">
+        <v>2.02</v>
+      </c>
+      <c r="AX15">
+        <v>1.64</v>
+      </c>
+      <c r="AY15">
+        <v>1.36</v>
+      </c>
+      <c r="AZ15">
+        <v>1.39</v>
+      </c>
+      <c r="BA15">
+        <v>4.2</v>
+      </c>
+      <c r="BB15">
         <v>1.12</v>
       </c>
-      <c r="AD15">
-        <v>4.8</v>
-      </c>
-      <c r="AE15">
-        <v>1.45</v>
-      </c>
-      <c r="AF15">
-        <v>2.43</v>
-      </c>
-      <c r="AG15">
-        <v>2.14</v>
-      </c>
-      <c r="AH15">
-        <v>1.58</v>
-      </c>
-      <c r="AI15">
-        <v>3.5</v>
-      </c>
-      <c r="AJ15">
-        <v>1.23</v>
-      </c>
-      <c r="AK15">
-        <v>0</v>
-      </c>
-      <c r="AL15">
-        <v>0</v>
-      </c>
-      <c r="AM15">
-        <v>1.11</v>
-      </c>
-      <c r="AN15">
-        <v>1.05</v>
-      </c>
-      <c r="AO15">
-        <v>0</v>
-      </c>
-      <c r="AP15">
-        <v>0</v>
-      </c>
-      <c r="AQ15">
-        <v>0</v>
-      </c>
-      <c r="AR15">
-        <v>0</v>
-      </c>
-      <c r="AS15">
-        <v>0</v>
-      </c>
-      <c r="AT15">
-        <v>0</v>
-      </c>
-      <c r="AU15">
-        <v>0</v>
-      </c>
-      <c r="AV15">
-        <v>0</v>
-      </c>
-      <c r="AW15">
-        <v>0</v>
-      </c>
-      <c r="AX15">
-        <v>0</v>
-      </c>
-      <c r="AY15">
-        <v>0</v>
-      </c>
-      <c r="AZ15">
-        <v>0</v>
-      </c>
-      <c r="BA15">
-        <v>0</v>
-      </c>
-      <c r="BB15">
-        <v>0</v>
-      </c>
       <c r="BC15">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BD15">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="BE15">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BF15">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG15">
         <v>0</v>
@@ -3915,10 +3915,10 @@
         <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E17" t="s">
         <v>122</v>
@@ -3954,133 +3954,133 @@
         <v>188</v>
       </c>
       <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>3.3</v>
+      </c>
+      <c r="T17">
+        <v>2</v>
+      </c>
+      <c r="U17">
+        <v>3.41</v>
+      </c>
+      <c r="V17">
+        <v>1.44</v>
+      </c>
+      <c r="W17">
+        <v>2.54</v>
+      </c>
+      <c r="X17">
+        <v>2.99</v>
+      </c>
+      <c r="Y17">
+        <v>1.33</v>
+      </c>
+      <c r="Z17">
+        <v>8.1</v>
+      </c>
+      <c r="AA17">
+        <v>1.02</v>
+      </c>
+      <c r="AB17">
+        <v>1.07</v>
+      </c>
+      <c r="AC17">
+        <v>1.35</v>
+      </c>
+      <c r="AD17">
+        <v>2.92</v>
+      </c>
+      <c r="AE17">
+        <v>2.14</v>
+      </c>
+      <c r="AF17">
+        <v>1.72</v>
+      </c>
+      <c r="AG17">
+        <v>3.73</v>
+      </c>
+      <c r="AH17">
+        <v>1.21</v>
+      </c>
+      <c r="AI17">
+        <v>7.5</v>
+      </c>
+      <c r="AJ17">
+        <v>1.03</v>
+      </c>
+      <c r="AK17">
+        <v>1.8</v>
+      </c>
+      <c r="AL17">
+        <v>1.9</v>
+      </c>
+      <c r="AM17">
+        <v>1.36</v>
+      </c>
+      <c r="AN17">
         <v>1.46</v>
       </c>
-      <c r="Q17">
-        <v>4.18</v>
-      </c>
-      <c r="R17">
-        <v>5.59</v>
-      </c>
-      <c r="S17">
-        <v>1.92</v>
-      </c>
-      <c r="T17">
+      <c r="AO17">
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <v>1.09</v>
+      </c>
+      <c r="AQ17">
+        <v>1.26</v>
+      </c>
+      <c r="AR17">
+        <v>1.51</v>
+      </c>
+      <c r="AS17">
+        <v>1.84</v>
+      </c>
+      <c r="AT17">
+        <v>2.31</v>
+      </c>
+      <c r="AU17">
+        <v>4.89</v>
+      </c>
+      <c r="AV17">
+        <v>3.22</v>
+      </c>
+      <c r="AW17">
+        <v>2.35</v>
+      </c>
+      <c r="AX17">
+        <v>1.86</v>
+      </c>
+      <c r="AY17">
+        <v>1.53</v>
+      </c>
+      <c r="AZ17">
+        <v>1.82</v>
+      </c>
+      <c r="BA17">
+        <v>2.45</v>
+      </c>
+      <c r="BB17">
+        <v>1.24</v>
+      </c>
+      <c r="BC17">
         <v>2.29</v>
       </c>
-      <c r="U17">
-        <v>5.98</v>
-      </c>
-      <c r="V17">
-        <v>1.26</v>
-      </c>
-      <c r="W17">
-        <v>3.28</v>
-      </c>
-      <c r="X17">
-        <v>2.36</v>
-      </c>
-      <c r="Y17">
-        <v>1.48</v>
-      </c>
-      <c r="Z17">
-        <v>5.6</v>
-      </c>
-      <c r="AA17">
-        <v>1.08</v>
-      </c>
-      <c r="AB17">
-        <v>1.01</v>
-      </c>
-      <c r="AC17">
-        <v>1.2</v>
-      </c>
-      <c r="AD17">
-        <v>4.33</v>
-      </c>
-      <c r="AE17">
-        <v>1.6</v>
-      </c>
-      <c r="AF17">
-        <v>2.17</v>
-      </c>
-      <c r="AG17">
-        <v>2.57</v>
-      </c>
-      <c r="AH17">
-        <v>1.43</v>
-      </c>
-      <c r="AI17">
-        <v>4.56</v>
-      </c>
-      <c r="AJ17">
-        <v>1.13</v>
-      </c>
-      <c r="AK17">
-        <v>1.67</v>
-      </c>
-      <c r="AL17">
-        <v>1.96</v>
-      </c>
-      <c r="AM17">
-        <v>1.06</v>
-      </c>
-      <c r="AN17">
-        <v>2.49</v>
-      </c>
-      <c r="AO17">
-        <v>0</v>
-      </c>
-      <c r="AP17">
-        <v>1.18</v>
-      </c>
-      <c r="AQ17">
-        <v>1.39</v>
-      </c>
-      <c r="AR17">
-        <v>1.71</v>
-      </c>
-      <c r="AS17">
-        <v>2.12</v>
-      </c>
-      <c r="AT17">
-        <v>2.76</v>
-      </c>
-      <c r="AU17">
-        <v>3.82</v>
-      </c>
-      <c r="AV17">
-        <v>2.65</v>
-      </c>
-      <c r="AW17">
-        <v>2.02</v>
-      </c>
-      <c r="AX17">
-        <v>1.64</v>
-      </c>
-      <c r="AY17">
-        <v>1.36</v>
-      </c>
-      <c r="AZ17">
-        <v>1.39</v>
-      </c>
-      <c r="BA17">
-        <v>4.2</v>
-      </c>
-      <c r="BB17">
-        <v>1.12</v>
-      </c>
-      <c r="BC17">
-        <v>1.82</v>
-      </c>
       <c r="BD17">
-        <v>4.65</v>
+        <v>3.44</v>
       </c>
       <c r="BE17">
-        <v>1.86</v>
+        <v>1.57</v>
       </c>
       <c r="BF17">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="BG17">
         <v>0</v>
@@ -5959,7 +5959,7 @@
         <v>133</v>
       </c>
       <c r="F28" t="s">
-        <v>174</v>
+        <v>145</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -6144,7 +6144,7 @@
         <v>134</v>
       </c>
       <c r="F29" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -6505,7 +6505,7 @@
         <v>80</v>
       </c>
       <c r="C31" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D31" t="s">
         <v>105</v>
@@ -6544,133 +6544,133 @@
         <v>188</v>
       </c>
       <c r="P31">
-        <v>1.98</v>
+        <v>5.48</v>
       </c>
       <c r="Q31">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="R31">
-        <v>3.45</v>
+        <v>1.55</v>
       </c>
       <c r="S31">
-        <v>2.5</v>
+        <v>7.1</v>
       </c>
       <c r="T31">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="U31">
-        <v>4.4</v>
+        <v>2.23</v>
       </c>
       <c r="V31">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="W31">
-        <v>2.73</v>
+        <v>2.28</v>
       </c>
       <c r="X31">
-        <v>2.96</v>
+        <v>3.48</v>
       </c>
       <c r="Y31">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="Z31">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA31">
         <v>1.04</v>
       </c>
       <c r="AB31">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AC31">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AD31">
-        <v>3.43</v>
+        <v>2.43</v>
       </c>
       <c r="AE31">
-        <v>1.98</v>
+        <v>2.46</v>
       </c>
       <c r="AF31">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
       <c r="AG31">
-        <v>3.45</v>
+        <v>4.65</v>
       </c>
       <c r="AH31">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="AI31">
-        <v>6.75</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AJ31">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AK31">
-        <v>1.79</v>
+        <v>2.45</v>
       </c>
       <c r="AL31">
-        <v>1.92</v>
+        <v>1.49</v>
       </c>
       <c r="AM31">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AN31">
-        <v>1.75</v>
+        <v>1.1</v>
       </c>
       <c r="AO31">
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ31">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AR31">
-        <v>2.63</v>
+        <v>2.14</v>
       </c>
       <c r="AS31">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="AT31">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="AU31">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AV31">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AW31">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AX31">
         <v>1.32</v>
       </c>
       <c r="AY31">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AZ31">
-        <v>1.56</v>
+        <v>2.39</v>
       </c>
       <c r="BA31">
-        <v>3.34</v>
+        <v>1.89</v>
       </c>
       <c r="BB31">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="BC31">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="BD31">
-        <v>3.52</v>
+        <v>2.96</v>
       </c>
       <c r="BE31">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="BF31">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="BG31">
         <v>0</v>
@@ -6690,7 +6690,7 @@
         <v>80</v>
       </c>
       <c r="C32" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D32" t="s">
         <v>104</v>
@@ -6875,7 +6875,7 @@
         <v>80</v>
       </c>
       <c r="C33" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D33" t="s">
         <v>105</v>
@@ -6914,133 +6914,133 @@
         <v>188</v>
       </c>
       <c r="P33">
-        <v>4.88</v>
+        <v>1.98</v>
       </c>
       <c r="Q33">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="R33">
-        <v>1.68</v>
+        <v>3.45</v>
       </c>
       <c r="S33">
-        <v>5.76</v>
+        <v>2.5</v>
       </c>
       <c r="T33">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="U33">
-        <v>2.32</v>
+        <v>4.4</v>
       </c>
       <c r="V33">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="W33">
-        <v>2.47</v>
+        <v>2.73</v>
       </c>
       <c r="X33">
-        <v>3.02</v>
+        <v>2.96</v>
       </c>
       <c r="Y33">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Z33">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AA33">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AB33">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC33">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AD33">
-        <v>2.78</v>
+        <v>3.43</v>
       </c>
       <c r="AE33">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="AF33">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="AG33">
-        <v>3.88</v>
+        <v>3.45</v>
       </c>
       <c r="AH33">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AI33">
-        <v>7.1</v>
+        <v>6.75</v>
       </c>
       <c r="AJ33">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AK33">
-        <v>2.01</v>
+        <v>1.79</v>
       </c>
       <c r="AL33">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="AM33">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AN33">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="AO33">
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AQ33">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AR33">
-        <v>1.95</v>
+        <v>2.63</v>
       </c>
       <c r="AS33">
-        <v>2.52</v>
+        <v>2.93</v>
       </c>
       <c r="AT33">
-        <v>3.48</v>
+        <v>4.2</v>
       </c>
       <c r="AU33">
-        <v>3.05</v>
+        <v>2.63</v>
       </c>
       <c r="AV33">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="AW33">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="AX33">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="AY33">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AZ33">
-        <v>2.46</v>
+        <v>1.56</v>
       </c>
       <c r="BA33">
-        <v>1.82</v>
+        <v>3.34</v>
       </c>
       <c r="BB33">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BC33">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="BD33">
-        <v>3.28</v>
+        <v>3.52</v>
       </c>
       <c r="BE33">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="BF33">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="BG33">
         <v>0</v>
@@ -7060,7 +7060,7 @@
         <v>80</v>
       </c>
       <c r="C34" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D34" t="s">
         <v>105</v>
@@ -7099,133 +7099,133 @@
         <v>188</v>
       </c>
       <c r="P34">
-        <v>1.35</v>
+        <v>4.88</v>
       </c>
       <c r="Q34">
-        <v>4.1</v>
+        <v>3.32</v>
       </c>
       <c r="R34">
-        <v>8.65</v>
+        <v>1.68</v>
       </c>
       <c r="S34">
-        <v>1.86</v>
+        <v>5.76</v>
       </c>
       <c r="T34">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="U34">
-        <v>8.35</v>
+        <v>2.32</v>
       </c>
       <c r="V34">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W34">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="X34">
-        <v>2.91</v>
+        <v>3.02</v>
       </c>
       <c r="Y34">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z34">
+        <v>7.5</v>
+      </c>
+      <c r="AA34">
+        <v>1.03</v>
+      </c>
+      <c r="AB34">
+        <v>1.04</v>
+      </c>
+      <c r="AC34">
+        <v>1.34</v>
+      </c>
+      <c r="AD34">
+        <v>2.78</v>
+      </c>
+      <c r="AE34">
+        <v>2.12</v>
+      </c>
+      <c r="AF34">
+        <v>1.64</v>
+      </c>
+      <c r="AG34">
+        <v>3.88</v>
+      </c>
+      <c r="AH34">
+        <v>1.2</v>
+      </c>
+      <c r="AI34">
         <v>7.1</v>
       </c>
-      <c r="AA34">
+      <c r="AJ34">
         <v>1.04</v>
       </c>
-      <c r="AB34">
-        <v>1.06</v>
-      </c>
-      <c r="AC34">
-        <v>1.31</v>
-      </c>
-      <c r="AD34">
-        <v>2.92</v>
-      </c>
-      <c r="AE34">
-        <v>2</v>
-      </c>
-      <c r="AF34">
-        <v>1.72</v>
-      </c>
-      <c r="AG34">
-        <v>3.58</v>
-      </c>
-      <c r="AH34">
-        <v>1.27</v>
-      </c>
-      <c r="AI34">
-        <v>6.4</v>
-      </c>
-      <c r="AJ34">
-        <v>1.05</v>
-      </c>
       <c r="AK34">
-        <v>2.25</v>
+        <v>2.01</v>
       </c>
       <c r="AL34">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AM34">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AN34">
-        <v>2.76</v>
+        <v>1.11</v>
       </c>
       <c r="AO34">
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AQ34">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="AR34">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AS34">
-        <v>2.33</v>
+        <v>2.52</v>
       </c>
       <c r="AT34">
-        <v>2.95</v>
+        <v>3.48</v>
       </c>
       <c r="AU34">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="AV34">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="AW34">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AX34">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AY34">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AZ34">
-        <v>1.29</v>
+        <v>2.46</v>
       </c>
       <c r="BA34">
-        <v>4.32</v>
+        <v>1.82</v>
       </c>
       <c r="BB34">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="BC34">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="BD34">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="BE34">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="BF34">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="BG34">
         <v>0</v>
@@ -7245,7 +7245,7 @@
         <v>80</v>
       </c>
       <c r="C35" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D35" t="s">
         <v>105</v>
@@ -7284,133 +7284,133 @@
         <v>188</v>
       </c>
       <c r="P35">
-        <v>5.48</v>
+        <v>1.35</v>
       </c>
       <c r="Q35">
-        <v>3.34</v>
+        <v>4.1</v>
       </c>
       <c r="R35">
-        <v>1.55</v>
+        <v>8.65</v>
       </c>
       <c r="S35">
+        <v>1.86</v>
+      </c>
+      <c r="T35">
+        <v>2.15</v>
+      </c>
+      <c r="U35">
+        <v>8.35</v>
+      </c>
+      <c r="V35">
+        <v>1.42</v>
+      </c>
+      <c r="W35">
+        <v>2.56</v>
+      </c>
+      <c r="X35">
+        <v>2.91</v>
+      </c>
+      <c r="Y35">
+        <v>1.33</v>
+      </c>
+      <c r="Z35">
         <v>7.1</v>
-      </c>
-      <c r="T35">
-        <v>1.91</v>
-      </c>
-      <c r="U35">
-        <v>2.23</v>
-      </c>
-      <c r="V35">
-        <v>1.55</v>
-      </c>
-      <c r="W35">
-        <v>2.28</v>
-      </c>
-      <c r="X35">
-        <v>3.48</v>
-      </c>
-      <c r="Y35">
-        <v>1.22</v>
-      </c>
-      <c r="Z35">
-        <v>9.199999999999999</v>
       </c>
       <c r="AA35">
         <v>1.04</v>
       </c>
       <c r="AB35">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AC35">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AD35">
-        <v>2.43</v>
+        <v>2.92</v>
       </c>
       <c r="AE35">
-        <v>2.46</v>
+        <v>2</v>
       </c>
       <c r="AF35">
+        <v>1.72</v>
+      </c>
+      <c r="AG35">
+        <v>3.58</v>
+      </c>
+      <c r="AH35">
+        <v>1.27</v>
+      </c>
+      <c r="AI35">
+        <v>6.4</v>
+      </c>
+      <c r="AJ35">
+        <v>1.05</v>
+      </c>
+      <c r="AK35">
+        <v>2.25</v>
+      </c>
+      <c r="AL35">
+        <v>1.6</v>
+      </c>
+      <c r="AM35">
+        <v>1.16</v>
+      </c>
+      <c r="AN35">
+        <v>2.76</v>
+      </c>
+      <c r="AO35">
+        <v>0</v>
+      </c>
+      <c r="AP35">
+        <v>1.24</v>
+      </c>
+      <c r="AQ35">
+        <v>1.46</v>
+      </c>
+      <c r="AR35">
+        <v>1.87</v>
+      </c>
+      <c r="AS35">
+        <v>2.33</v>
+      </c>
+      <c r="AT35">
+        <v>2.95</v>
+      </c>
+      <c r="AU35">
+        <v>3.15</v>
+      </c>
+      <c r="AV35">
+        <v>2.38</v>
+      </c>
+      <c r="AW35">
+        <v>1.83</v>
+      </c>
+      <c r="AX35">
         <v>1.48</v>
       </c>
-      <c r="AG35">
-        <v>4.65</v>
-      </c>
-      <c r="AH35">
-        <v>1.12</v>
-      </c>
-      <c r="AI35">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AJ35">
-        <v>1</v>
-      </c>
-      <c r="AK35">
-        <v>2.45</v>
-      </c>
-      <c r="AL35">
-        <v>1.49</v>
-      </c>
-      <c r="AM35">
-        <v>1.24</v>
-      </c>
-      <c r="AN35">
-        <v>1.1</v>
-      </c>
-      <c r="AO35">
-        <v>0</v>
-      </c>
-      <c r="AP35">
-        <v>1.36</v>
-      </c>
-      <c r="AQ35">
-        <v>1.69</v>
-      </c>
-      <c r="AR35">
-        <v>2.14</v>
-      </c>
-      <c r="AS35">
-        <v>2.88</v>
-      </c>
-      <c r="AT35">
-        <v>3.6</v>
-      </c>
-      <c r="AU35">
-        <v>2.7</v>
-      </c>
-      <c r="AV35">
-        <v>2</v>
-      </c>
-      <c r="AW35">
-        <v>1.57</v>
-      </c>
-      <c r="AX35">
-        <v>1.32</v>
-      </c>
       <c r="AY35">
+        <v>1.34</v>
+      </c>
+      <c r="AZ35">
+        <v>1.29</v>
+      </c>
+      <c r="BA35">
+        <v>4.32</v>
+      </c>
+      <c r="BB35">
         <v>1.23</v>
       </c>
-      <c r="AZ35">
-        <v>2.39</v>
-      </c>
-      <c r="BA35">
-        <v>1.89</v>
-      </c>
-      <c r="BB35">
-        <v>1.32</v>
-      </c>
       <c r="BC35">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="BD35">
-        <v>2.96</v>
+        <v>3.42</v>
       </c>
       <c r="BE35">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="BF35">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="BG35">
         <v>0</v>
@@ -7469,133 +7469,133 @@
         <v>188</v>
       </c>
       <c r="P36">
-        <v>2.22</v>
+        <v>6.39</v>
       </c>
       <c r="Q36">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="R36">
-        <v>3.45</v>
+        <v>1.54</v>
       </c>
       <c r="S36">
-        <v>2.9</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="T36">
-        <v>1.81</v>
+        <v>2.08</v>
       </c>
       <c r="U36">
-        <v>4.2</v>
+        <v>2.13</v>
       </c>
       <c r="V36">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="W36">
-        <v>2.17</v>
+        <v>2.44</v>
       </c>
       <c r="X36">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="Y36">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="Z36">
-        <v>9.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="AA36">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AB36">
+        <v>1.07</v>
+      </c>
+      <c r="AC36">
+        <v>1.38</v>
+      </c>
+      <c r="AD36">
+        <v>2.43</v>
+      </c>
+      <c r="AE36">
+        <v>2.23</v>
+      </c>
+      <c r="AF36">
+        <v>1.49</v>
+      </c>
+      <c r="AG36">
+        <v>4.65</v>
+      </c>
+      <c r="AH36">
         <v>1.12</v>
       </c>
-      <c r="AC36">
-        <v>1.66</v>
-      </c>
-      <c r="AD36">
-        <v>2.13</v>
-      </c>
-      <c r="AE36">
-        <v>3.1</v>
-      </c>
-      <c r="AF36">
-        <v>1.31</v>
-      </c>
-      <c r="AG36">
-        <v>6.35</v>
-      </c>
-      <c r="AH36">
-        <v>1.06</v>
-      </c>
       <c r="AI36">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AJ36">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AK36">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="AL36">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AM36">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AN36">
-        <v>1.55</v>
+        <v>1.04</v>
       </c>
       <c r="AO36">
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AQ36">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AR36">
-        <v>2.7</v>
+        <v>2.16</v>
       </c>
       <c r="AS36">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="AT36">
-        <v>4.34</v>
+        <v>4.41</v>
       </c>
       <c r="AU36">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="AV36">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AW36">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AX36">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AY36">
         <v>1.13</v>
       </c>
       <c r="AZ36">
-        <v>1.75</v>
+        <v>3.85</v>
       </c>
       <c r="BA36">
-        <v>2.61</v>
+        <v>1.43</v>
       </c>
       <c r="BB36">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="BC36">
-        <v>3.12</v>
+        <v>2.59</v>
       </c>
       <c r="BD36">
-        <v>2.53</v>
+        <v>2.91</v>
       </c>
       <c r="BE36">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="BF36">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="BG36">
         <v>0</v>
@@ -8024,133 +8024,133 @@
         <v>188</v>
       </c>
       <c r="P39">
-        <v>6.39</v>
+        <v>2.22</v>
       </c>
       <c r="Q39">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="R39">
-        <v>1.54</v>
+        <v>3.45</v>
       </c>
       <c r="S39">
-        <v>8.050000000000001</v>
+        <v>2.9</v>
       </c>
       <c r="T39">
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="U39">
+        <v>4.2</v>
+      </c>
+      <c r="V39">
+        <v>1.61</v>
+      </c>
+      <c r="W39">
+        <v>2.17</v>
+      </c>
+      <c r="X39">
+        <v>4.1</v>
+      </c>
+      <c r="Y39">
+        <v>1.16</v>
+      </c>
+      <c r="Z39">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AA39">
+        <v>1.02</v>
+      </c>
+      <c r="AB39">
+        <v>1.12</v>
+      </c>
+      <c r="AC39">
+        <v>1.66</v>
+      </c>
+      <c r="AD39">
         <v>2.13</v>
       </c>
-      <c r="V39">
-        <v>1.53</v>
-      </c>
-      <c r="W39">
-        <v>2.44</v>
-      </c>
-      <c r="X39">
-        <v>3.3</v>
-      </c>
-      <c r="Y39">
-        <v>1.25</v>
-      </c>
-      <c r="Z39">
-        <v>10</v>
-      </c>
-      <c r="AA39">
-        <v>1</v>
-      </c>
-      <c r="AB39">
-        <v>1.07</v>
-      </c>
-      <c r="AC39">
-        <v>1.38</v>
-      </c>
-      <c r="AD39">
-        <v>2.43</v>
-      </c>
       <c r="AE39">
-        <v>2.23</v>
+        <v>3.1</v>
       </c>
       <c r="AF39">
-        <v>1.49</v>
+        <v>1.31</v>
       </c>
       <c r="AG39">
-        <v>4.65</v>
+        <v>6.35</v>
       </c>
       <c r="AH39">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AI39">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AJ39">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AK39">
-        <v>2.51</v>
+        <v>2.4</v>
       </c>
       <c r="AL39">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AM39">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AN39">
-        <v>1.04</v>
+        <v>1.55</v>
       </c>
       <c r="AO39">
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AQ39">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AR39">
-        <v>2.16</v>
+        <v>2.7</v>
       </c>
       <c r="AS39">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="AT39">
-        <v>4.41</v>
+        <v>4.34</v>
       </c>
       <c r="AU39">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AV39">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AW39">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AX39">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AY39">
         <v>1.13</v>
       </c>
       <c r="AZ39">
-        <v>3.85</v>
+        <v>1.75</v>
       </c>
       <c r="BA39">
+        <v>2.61</v>
+      </c>
+      <c r="BB39">
         <v>1.43</v>
       </c>
-      <c r="BB39">
-        <v>1.33</v>
-      </c>
       <c r="BC39">
-        <v>2.59</v>
+        <v>3.12</v>
       </c>
       <c r="BD39">
-        <v>2.91</v>
+        <v>2.53</v>
       </c>
       <c r="BE39">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="BF39">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="BG39">
         <v>0</v>

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.25</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>8.31</v>
+        <v>2.74</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="U2" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="V2" t="n">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
       <c r="W2" t="n">
-        <v>3.15</v>
+        <v>2.44</v>
       </c>
       <c r="X2" t="n">
-        <v>2.53</v>
+        <v>3.34</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="Z2" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.75</v>
+        <v>4.4</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="AI2" t="n">
-        <v>4.8</v>
+        <v>9.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AK2" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL2" t="n">
         <v>1.75</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AN2" t="n">
-        <v>3.4</v>
+        <v>1.44</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.2</v>
+        <v>3.66</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.72</v>
+        <v>5.57</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.45</v>
+        <v>2.23</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.29</v>
+        <v>1.96</v>
       </c>
       <c r="BA2" t="n">
-        <v>4</v>
+        <v>2.42</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="BC2" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="R3" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q3" t="n">
-        <v>3</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.95</v>
-      </c>
       <c r="U3" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="V3" t="n">
-        <v>1.49</v>
+        <v>1.31</v>
       </c>
       <c r="W3" t="n">
-        <v>2.44</v>
+        <v>3.15</v>
       </c>
       <c r="X3" t="n">
-        <v>3.34</v>
+        <v>2.53</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AC3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH3" t="n">
         <v>1.4</v>
       </c>
-      <c r="AD3" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AI3" t="n">
-        <v>9.5</v>
+        <v>4.8</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL3" t="n">
         <v>1.75</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.44</v>
+        <v>3.4</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.66</v>
+        <v>3.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.57</v>
+        <v>4.72</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="AX3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AY3" t="n">
         <v>1.2</v>
       </c>
-      <c r="AY3" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>1.96</v>
+        <v>1.29</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.42</v>
+        <v>4</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="BD3" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,37 +1195,37 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.57</v>
+        <v>2.15</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="R4" t="n">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="S4" t="n">
-        <v>3.28</v>
+        <v>2.7</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U4" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="V4" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="W4" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="X4" t="n">
-        <v>2.65</v>
+        <v>3.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z4" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AA4" t="n">
         <v>1.03</v>
@@ -1234,94 +1234,94 @@
         <v>1.06</v>
       </c>
       <c r="AC4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM4" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AN4" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.77</v>
+        <v>3.28</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.9</v>
+        <v>4.84</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.78</v>
+        <v>2.41</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,103 +1392,103 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="S5" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="V5" t="n">
         <v>1.43</v>
       </c>
       <c r="W5" t="n">
-        <v>2.62</v>
+        <v>2.34</v>
       </c>
       <c r="X5" t="n">
-        <v>3.04</v>
+        <v>3.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AB5" t="n">
         <v>1.06</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AD5" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AI5" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.36</v>
+        <v>2.97</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.84</v>
+        <v>4.89</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AW5" t="n">
         <v>1.49</v>
@@ -1497,28 +1497,28 @@
         <v>1.25</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.08</v>
+        <v>2.57</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="R6" t="n">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="S6" t="n">
-        <v>2.63</v>
+        <v>3.28</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="U6" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="V6" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="W6" t="n">
-        <v>2.34</v>
+        <v>2.77</v>
       </c>
       <c r="X6" t="n">
-        <v>3.4</v>
+        <v>2.65</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AB6" t="n">
         <v>1.06</v>
       </c>
       <c r="AC6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN6" t="n">
         <v>1.44</v>
       </c>
-      <c r="AD6" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AH6" t="n">
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AY6" t="n">
         <v>1.17</v>
       </c>
-      <c r="AI6" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AM6" t="n">
+      <c r="AZ6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BB6" t="n">
         <v>1.25</v>
       </c>
-      <c r="AN6" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AZ6" t="n">
+      <c r="BC6" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE6" t="n">
         <v>1.65</v>
       </c>
-      <c r="BA6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.44</v>
-      </c>
       <c r="BF6" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.53</v>
+        <v>2.35</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R7" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="S7" t="n">
         <v>3.12</v>
@@ -1825,7 +1825,7 @@
         <v>1</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AD7" t="n">
         <v>4</v>
@@ -1834,7 +1834,7 @@
         <v>1.7</v>
       </c>
       <c r="AF7" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AG7" t="n">
         <v>2.62</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.92</v>
+        <v>1.73</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.58</v>
+        <v>3.3</v>
       </c>
       <c r="R8" t="n">
-        <v>2.58</v>
+        <v>4.93</v>
       </c>
       <c r="S8" t="n">
-        <v>4.08</v>
+        <v>2.25</v>
       </c>
       <c r="T8" t="n">
-        <v>1.74</v>
+        <v>2.15</v>
       </c>
       <c r="U8" t="n">
-        <v>3.44</v>
+        <v>5</v>
       </c>
       <c r="V8" t="n">
-        <v>1.65</v>
+        <v>1.41</v>
       </c>
       <c r="W8" t="n">
-        <v>2.08</v>
+        <v>2.69</v>
       </c>
       <c r="X8" t="n">
-        <v>3.85</v>
+        <v>3.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.61</v>
+        <v>1.29</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.81</v>
+        <v>2.05</v>
       </c>
       <c r="AF8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
         <v>1.33</v>
       </c>
-      <c r="AG8" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.56</v>
+        <v>3.3</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.73</v>
+        <v>2.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.3</v>
+        <v>2.58</v>
       </c>
       <c r="R9" t="n">
-        <v>4.93</v>
+        <v>2.58</v>
       </c>
       <c r="S9" t="n">
-        <v>2.25</v>
+        <v>4.08</v>
       </c>
       <c r="T9" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AD9" t="n">
         <v>2.15</v>
       </c>
-      <c r="U9" t="n">
-        <v>5</v>
-      </c>
-      <c r="V9" t="n">
+      <c r="AE9" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
         <v>1.41</v>
       </c>
-      <c r="W9" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="X9" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Y9" t="n">
+      <c r="BC9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BE9" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.6</v>
-      </c>
       <c r="BF9" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2574,40 +2574,40 @@
         </is>
       </c>
       <c r="P11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Q11" t="n">
         <v>5.25</v>
       </c>
-      <c r="Q11" t="n">
-        <v>4.6</v>
-      </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="T11" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="U11" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="V11" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W11" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="X11" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AB11" t="n">
         <v>1.01</v>
@@ -2616,91 +2616,91 @@
         <v>1.08</v>
       </c>
       <c r="AD11" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF11" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>2.29</v>
+        <v>2.44</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.6</v>
+        <v>5.82</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3</v>
+        <v>1.48</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="T12" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="U12" t="n">
-        <v>2.78</v>
+        <v>1.95</v>
       </c>
       <c r="V12" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="W12" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="X12" t="n">
-        <v>2.08</v>
+        <v>2.39</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.45</v>
+        <v>5.45</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AB12" t="n">
         <v>1.02</v>
       </c>
       <c r="AC12" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN12" t="n">
         <v>1.13</v>
       </c>
-      <c r="AD12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AI12" t="n">
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AZ12" t="n">
         <v>3.4</v>
       </c>
-      <c r="AJ12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>5.86</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.92</v>
-      </c>
       <c r="BA12" t="n">
-        <v>2.11</v>
+        <v>1.26</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="BD12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>5.82</v>
+        <v>2.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="R13" t="n">
-        <v>1.48</v>
+        <v>2.3</v>
       </c>
       <c r="S13" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="U13" t="n">
-        <v>1.95</v>
+        <v>2.78</v>
       </c>
       <c r="V13" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="W13" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="X13" t="n">
-        <v>2.39</v>
+        <v>2.08</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.45</v>
+        <v>4.45</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AB13" t="n">
         <v>1.02</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AD13" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="AH13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK13" t="n">
         <v>1.4</v>
       </c>
-      <c r="AI13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AL13" t="n">
-        <v>1.95</v>
+        <v>2.8</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AN13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BB13" t="n">
         <v>1.13</v>
       </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.2</v>
-      </c>
       <c r="BC13" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="BD13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.07</v>
+        <v>2.8</v>
       </c>
       <c r="R14" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1</v>
+        <v>4.68</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="U14" t="n">
-        <v>3.35</v>
+        <v>3.12</v>
       </c>
       <c r="V14" t="n">
-        <v>1.46</v>
+        <v>1.65</v>
       </c>
       <c r="W14" t="n">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="X14" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="Z14" t="n">
-        <v>8.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AA14" t="n">
         <v>1.01</v>
       </c>
       <c r="AB14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BF14" t="n">
         <v>1.06</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>1.13</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,113 +3362,113 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>3.3</v>
+        <v>9</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>4.68</v>
+        <v>8</v>
       </c>
       <c r="T15" t="n">
-        <v>1.74</v>
+        <v>2.6</v>
       </c>
       <c r="U15" t="n">
-        <v>3.12</v>
+        <v>1.67</v>
       </c>
       <c r="V15" t="n">
-        <v>1.65</v>
+        <v>1.26</v>
       </c>
       <c r="W15" t="n">
-        <v>2.08</v>
+        <v>3.28</v>
       </c>
       <c r="X15" t="n">
-        <v>4</v>
+        <v>2.27</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC15" t="n">
         <v>1.17</v>
       </c>
-      <c r="Z15" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AA15" t="n">
+      <c r="AD15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AY15" t="n">
         <v>1.01</v>
       </c>
-      <c r="AB15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.97</v>
+        <v>1.85</v>
       </c>
       <c r="BD15" t="n">
-        <v>2.56</v>
+        <v>4.33</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.31</v>
+        <v>1.85</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>9</v>
+        <v>2.63</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>3.07</v>
       </c>
       <c r="R16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BB16" t="n">
         <v>1.3</v>
       </c>
-      <c r="S16" t="n">
-        <v>8</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W16" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AE16" t="n">
+      <c r="BC16" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BE16" t="n">
         <v>1.53</v>
       </c>
-      <c r="AF16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.85</v>
-      </c>
       <c r="BF16" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3756,7 +3756,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="Q17" t="n">
         <v>4.2</v>
@@ -3771,10 +3771,10 @@
         <v>2.4</v>
       </c>
       <c r="U17" t="n">
-        <v>6.08</v>
+        <v>5.98</v>
       </c>
       <c r="V17" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="W17" t="n">
         <v>3.28</v>
@@ -3792,25 +3792,25 @@
         <v>1.08</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AE17" t="n">
         <v>1.6</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AI17" t="n">
         <v>4.56</v>
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="R21" t="n">
-        <v>3.65</v>
+        <v>3.84</v>
       </c>
       <c r="S21" t="n">
         <v>2.57</v>
@@ -4571,13 +4571,13 @@
         <v>3.22</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z21" t="n">
         <v>9</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AB21" t="n">
         <v>1.08</v>
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Q27" t="n">
         <v>4.6</v>
       </c>
       <c r="R27" t="n">
-        <v>5.75</v>
+        <v>6.22</v>
       </c>
       <c r="S27" t="n">
         <v>1.87</v>
@@ -5762,19 +5762,19 @@
         <v>1.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AC27" t="n">
         <v>1.12</v>
       </c>
       <c r="AD27" t="n">
-        <v>4.53</v>
+        <v>4.7</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="AG27" t="n">
         <v>2.08</v>
@@ -5804,40 +5804,40 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AR27" t="n">
         <v>2.31</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="AT27" t="n">
-        <v>3.58</v>
+        <v>3.52</v>
       </c>
       <c r="AU27" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AV27" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AW27" t="n">
         <v>1.72</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AY27" t="n">
         <v>1.21</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BA27" t="n">
-        <v>7.01</v>
+        <v>7.6</v>
       </c>
       <c r="BB27" t="n">
         <v>1.12</v>
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.95</v>
+        <v>2.82</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="R31" t="n">
-        <v>3.3</v>
+        <v>2.32</v>
       </c>
       <c r="S31" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="T31" t="n">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="U31" t="n">
-        <v>4</v>
+        <v>2.96</v>
       </c>
       <c r="V31" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="W31" t="n">
-        <v>2.73</v>
+        <v>3.16</v>
       </c>
       <c r="X31" t="n">
-        <v>2.96</v>
+        <v>2.36</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="Z31" t="n">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.95</v>
+        <v>1.66</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AG31" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="AH31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BF31" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>1.15</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,37 +6711,37 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.35</v>
+        <v>1.95</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="R32" t="n">
-        <v>7.62</v>
+        <v>3.3</v>
       </c>
       <c r="S32" t="n">
-        <v>1.89</v>
+        <v>2.5</v>
       </c>
       <c r="T32" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="U32" t="n">
-        <v>8.449999999999999</v>
+        <v>4.49</v>
       </c>
       <c r="V32" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="W32" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="X32" t="n">
-        <v>2.82</v>
+        <v>2.97</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z32" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="AA32" t="n">
         <v>1.04</v>
@@ -6750,94 +6750,94 @@
         <v>1.06</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AE32" t="n">
         <v>1.95</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG32" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AI32" t="n">
-        <v>6.05</v>
+        <v>6.5</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.32</v>
+        <v>1.75</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AN32" t="n">
-        <v>2.84</v>
+        <v>1.75</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.33</v>
+        <v>2.79</v>
       </c>
       <c r="AT32" t="n">
-        <v>3.14</v>
+        <v>3.94</v>
       </c>
       <c r="AU32" t="n">
-        <v>3.34</v>
+        <v>2.76</v>
       </c>
       <c r="AV32" t="n">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
       <c r="BA32" t="n">
-        <v>4.71</v>
+        <v>2.81</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="BD32" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U33" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W33" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X33" t="n">
         <v>2.82</v>
       </c>
-      <c r="Q33" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="R33" t="n">
+      <c r="Y33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK33" t="n">
         <v>2.32</v>
       </c>
-      <c r="S33" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T33" t="n">
+      <c r="AL33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC33" t="n">
         <v>2.3</v>
       </c>
-      <c r="U33" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W33" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="X33" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>1.85</v>
-      </c>
       <c r="BD33" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>5.9</v>
+        <v>4.85</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R34" t="n">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="S34" t="n">
-        <v>7.9</v>
+        <v>5.25</v>
       </c>
       <c r="T34" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="U34" t="n">
-        <v>2.13</v>
+        <v>2.33</v>
       </c>
       <c r="V34" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="W34" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="X34" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AR34" t="n">
         <v>2.31</v>
       </c>
-      <c r="X34" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AD34" t="n">
+      <c r="AS34" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ34" t="n">
         <v>2.46</v>
       </c>
-      <c r="AE34" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>2.39</v>
-      </c>
       <c r="BA34" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.53</v>
+        <v>2.28</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.02</v>
+        <v>3.28</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>4.85</v>
+        <v>5.9</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R35" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S35" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W35" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="X35" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ35" t="n">
         <v>1.7</v>
       </c>
-      <c r="S35" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="T35" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="U35" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W35" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="X35" t="n">
+      <c r="AR35" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BD35" t="n">
         <v>3.02</v>
       </c>
-      <c r="Y35" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>3.28</v>
-      </c>
       <c r="BE35" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R36" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U36" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W36" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="X36" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE36" t="n">
         <v>3.1</v>
       </c>
-      <c r="R36" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S36" t="n">
-        <v>4</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2</v>
-      </c>
-      <c r="U36" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="W36" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="X36" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB36" t="n">
+      <c r="AF36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AH36" t="n">
         <v>1.1</v>
       </c>
-      <c r="AC36" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AI36" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AM36" t="n">
         <v>1.36</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.29</v>
+        <v>1.6</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AR36" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.94</v>
+        <v>2.85</v>
       </c>
       <c r="AT36" t="n">
-        <v>4.22</v>
+        <v>4.17</v>
       </c>
       <c r="AU36" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="AV36" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AY36" t="n">
         <v>1.14</v>
       </c>
       <c r="AZ36" t="n">
-        <v>2.12</v>
+        <v>1.75</v>
       </c>
       <c r="BA36" t="n">
-        <v>2.08</v>
+        <v>2.61</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="BD36" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>6.39</v>
+        <v>5.75</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="R37" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="S37" t="n">
         <v>8.050000000000001</v>
@@ -7714,10 +7714,10 @@
         <v>2.1</v>
       </c>
       <c r="V37" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W37" t="n">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="X37" t="n">
         <v>3.3</v>
@@ -7729,7 +7729,7 @@
         <v>10</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AB37" t="n">
         <v>1.07</v>
@@ -7744,7 +7744,7 @@
         <v>2.37</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG37" t="n">
         <v>4.65</v>
@@ -7753,7 +7753,7 @@
         <v>1.15</v>
       </c>
       <c r="AI37" t="n">
-        <v>11</v>
+        <v>9.1</v>
       </c>
       <c r="AJ37" t="n">
         <v>1</v>
@@ -7774,34 +7774,34 @@
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.16</v>
+        <v>2.07</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.96</v>
+        <v>2.89</v>
       </c>
       <c r="AT37" t="n">
-        <v>4.26</v>
+        <v>4.12</v>
       </c>
       <c r="AU37" t="n">
-        <v>2.61</v>
+        <v>2.67</v>
       </c>
       <c r="AV37" t="n">
         <v>2</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AZ37" t="n">
         <v>3.85</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.22</v>
+        <v>3.2</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="R38" t="n">
-        <v>3.28</v>
+        <v>2.1</v>
       </c>
       <c r="S38" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="T38" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="U38" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="V38" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="W38" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="X38" t="n">
-        <v>4.05</v>
+        <v>3.38</v>
       </c>
       <c r="Y38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AH38" t="n">
         <v>1.17</v>
       </c>
-      <c r="Z38" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AI38" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AK38" t="n">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AM38" t="n">
         <v>1.36</v>
       </c>
       <c r="AN38" t="n">
-        <v>1.6</v>
+        <v>1.29</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AR38" t="n">
-        <v>2.6</v>
+        <v>2.14</v>
       </c>
       <c r="AS38" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="AT38" t="n">
-        <v>4.34</v>
+        <v>3.4</v>
       </c>
       <c r="AU38" t="n">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="AV38" t="n">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="BA38" t="n">
-        <v>2.61</v>
+        <v>2.08</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="BC38" t="n">
-        <v>3</v>
+        <v>2.56</v>
       </c>
       <c r="BD38" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8093,10 +8093,10 @@
         <v>2</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="R39" t="n">
-        <v>3.75</v>
+        <v>4.05</v>
       </c>
       <c r="S39" t="n">
         <v>2.8</v>
@@ -8108,10 +8108,10 @@
         <v>5.1</v>
       </c>
       <c r="V39" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W39" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="X39" t="n">
         <v>3.9</v>
@@ -8129,22 +8129,22 @@
         <v>1.13</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AE39" t="n">
         <v>2.74</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AG39" t="n">
         <v>6</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AI39" t="n">
         <v>9.699999999999999</v>
@@ -8168,40 +8168,40 @@
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AR39" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="AS39" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AT39" t="n">
-        <v>4.34</v>
+        <v>4.42</v>
       </c>
       <c r="AU39" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="AV39" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AZ39" t="n">
         <v>1.55</v>
       </c>
       <c r="BA39" t="n">
-        <v>2.88</v>
+        <v>3.18</v>
       </c>
       <c r="BB39" t="n">
         <v>1.44</v>
@@ -8287,10 +8287,10 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>10.8</v>
+        <v>9</v>
       </c>
       <c r="Q40" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="R40" t="n">
         <v>1.22</v>
@@ -8299,16 +8299,16 @@
         <v>7.5</v>
       </c>
       <c r="T40" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="U40" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="V40" t="n">
         <v>1.15</v>
       </c>
       <c r="W40" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="X40" t="n">
         <v>1.87</v>
@@ -8317,103 +8317,103 @@
         <v>1.83</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AB40" t="n">
         <v>1.01</v>
       </c>
       <c r="AC40" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AM40" t="n">
         <v>1.11</v>
       </c>
-      <c r="AD40" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AH40" t="n">
+      <c r="AN40" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AW40" t="n">
         <v>1.94</v>
       </c>
-      <c r="AI40" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AX40" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AZ40" t="n">
-        <v>4.05</v>
+        <v>4.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="BD40" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="BE40" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="R2" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T2" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q2" t="n">
-        <v>3</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.95</v>
-      </c>
       <c r="U2" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="V2" t="n">
-        <v>1.49</v>
+        <v>1.31</v>
       </c>
       <c r="W2" t="n">
-        <v>2.44</v>
+        <v>3.15</v>
       </c>
       <c r="X2" t="n">
-        <v>3.34</v>
+        <v>2.53</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AC2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH2" t="n">
         <v>1.4</v>
       </c>
-      <c r="AD2" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AI2" t="n">
-        <v>9.5</v>
+        <v>4.8</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL2" t="n">
         <v>1.75</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.44</v>
+        <v>3.4</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.66</v>
+        <v>3.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.57</v>
+        <v>4.72</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="AX2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AY2" t="n">
         <v>1.2</v>
       </c>
-      <c r="AY2" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AZ2" t="n">
-        <v>1.96</v>
+        <v>1.29</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.42</v>
+        <v>4</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="BD2" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.25</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>8.31</v>
+        <v>2.74</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="U3" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="V3" t="n">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
       <c r="W3" t="n">
-        <v>3.15</v>
+        <v>2.44</v>
       </c>
       <c r="X3" t="n">
-        <v>2.53</v>
+        <v>3.34</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="Z3" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.75</v>
+        <v>4.4</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="AI3" t="n">
-        <v>4.8</v>
+        <v>9.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AK3" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL3" t="n">
         <v>1.75</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AN3" t="n">
-        <v>3.4</v>
+        <v>1.44</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.2</v>
+        <v>3.66</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.72</v>
+        <v>5.57</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.45</v>
+        <v>2.23</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.29</v>
+        <v>1.96</v>
       </c>
       <c r="BA3" t="n">
-        <v>4</v>
+        <v>2.42</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="BC3" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,37 +1195,37 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.15</v>
+        <v>2.57</v>
       </c>
       <c r="Q4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U4" t="n">
         <v>3.2</v>
       </c>
-      <c r="R4" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3.7</v>
-      </c>
       <c r="V4" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="W4" t="n">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="X4" t="n">
-        <v>3.04</v>
+        <v>2.65</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AA4" t="n">
         <v>1.03</v>
@@ -1234,94 +1234,94 @@
         <v>1.06</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AE4" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR4" t="n">
         <v>2.1</v>
       </c>
-      <c r="AF4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN4" t="n">
+      <c r="AS4" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE4" t="n">
         <v>1.65</v>
       </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.57</v>
-      </c>
       <c r="BF4" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,37 +1589,37 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.57</v>
+        <v>2.15</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="R6" t="n">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="S6" t="n">
-        <v>3.28</v>
+        <v>2.7</v>
       </c>
       <c r="T6" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U6" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="V6" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="W6" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="X6" t="n">
-        <v>2.65</v>
+        <v>3.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AA6" t="n">
         <v>1.03</v>
@@ -1628,94 +1628,94 @@
         <v>1.06</v>
       </c>
       <c r="AC6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM6" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AN6" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.77</v>
+        <v>3.28</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.9</v>
+        <v>4.84</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.78</v>
+        <v>2.41</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.73</v>
+        <v>2.77</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.3</v>
+        <v>2.65</v>
       </c>
       <c r="R8" t="n">
-        <v>4.93</v>
+        <v>2.55</v>
       </c>
       <c r="S8" t="n">
-        <v>2.25</v>
+        <v>4.04</v>
       </c>
       <c r="T8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AQ8" t="n">
         <v>2.15</v>
       </c>
-      <c r="U8" t="n">
-        <v>5</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="X8" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Y8" t="n">
+      <c r="AR8" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BE8" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.6</v>
-      </c>
       <c r="BF8" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.92</v>
+        <v>1.73</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.58</v>
+        <v>3.3</v>
       </c>
       <c r="R9" t="n">
-        <v>2.58</v>
+        <v>4.93</v>
       </c>
       <c r="S9" t="n">
-        <v>4.08</v>
+        <v>2.25</v>
       </c>
       <c r="T9" t="n">
-        <v>1.74</v>
+        <v>2.15</v>
       </c>
       <c r="U9" t="n">
-        <v>3.44</v>
+        <v>5</v>
       </c>
       <c r="V9" t="n">
-        <v>1.65</v>
+        <v>1.41</v>
       </c>
       <c r="W9" t="n">
-        <v>2.08</v>
+        <v>2.69</v>
       </c>
       <c r="X9" t="n">
-        <v>3.85</v>
+        <v>3.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.61</v>
+        <v>1.29</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.81</v>
+        <v>2.05</v>
       </c>
       <c r="AF9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
         <v>1.33</v>
       </c>
-      <c r="AG9" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.56</v>
+        <v>3.3</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>5.82</v>
+        <v>2.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.48</v>
+        <v>2.3</v>
       </c>
       <c r="S12" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="U12" t="n">
-        <v>1.95</v>
+        <v>2.78</v>
       </c>
       <c r="V12" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="W12" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="X12" t="n">
-        <v>2.39</v>
+        <v>2.08</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.45</v>
+        <v>4.45</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AB12" t="n">
         <v>1.02</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AD12" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="AH12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK12" t="n">
         <v>1.4</v>
       </c>
-      <c r="AI12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AL12" t="n">
-        <v>1.95</v>
+        <v>2.8</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AN12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BB12" t="n">
         <v>1.13</v>
       </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.2</v>
-      </c>
       <c r="BC12" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="BD12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.6</v>
+        <v>5.82</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="R13" t="n">
-        <v>2.3</v>
+        <v>1.48</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="U13" t="n">
-        <v>2.78</v>
+        <v>1.95</v>
       </c>
       <c r="V13" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="W13" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="X13" t="n">
-        <v>2.08</v>
+        <v>2.39</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.45</v>
+        <v>5.45</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AB13" t="n">
         <v>1.02</v>
       </c>
       <c r="AC13" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN13" t="n">
         <v>1.13</v>
       </c>
-      <c r="AD13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AI13" t="n">
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>3.4</v>
       </c>
-      <c r="AJ13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>5.86</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.92</v>
-      </c>
       <c r="BA13" t="n">
-        <v>2.11</v>
+        <v>1.26</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="BD13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3177,22 +3177,22 @@
         <v>4.68</v>
       </c>
       <c r="T14" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="U14" t="n">
-        <v>3.12</v>
+        <v>3.06</v>
       </c>
       <c r="V14" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="W14" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="X14" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z14" t="n">
         <v>9.6</v>
@@ -3201,37 +3201,37 @@
         <v>1.01</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AG14" t="n">
-        <v>5.95</v>
+        <v>5.75</v>
       </c>
       <c r="AH14" t="n">
         <v>1.07</v>
       </c>
       <c r="AI14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AJ14" t="n">
         <v>1.02</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AM14" t="n">
         <v>1.35</v>
@@ -3243,34 +3243,34 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,22 +3362,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>9</v>
+        <v>1.48</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3</v>
+        <v>5.25</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>1.92</v>
       </c>
       <c r="T15" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="U15" t="n">
-        <v>1.67</v>
+        <v>5.98</v>
       </c>
       <c r="V15" t="n">
         <v>1.26</v>
@@ -3386,109 +3386,109 @@
         <v>3.28</v>
       </c>
       <c r="X15" t="n">
-        <v>2.27</v>
+        <v>2.36</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AI15" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BA15" t="n">
         <v>4.2</v>
       </c>
-      <c r="AJ15" t="n">
+      <c r="BB15" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.18</v>
       </c>
       <c r="BC15" t="n">
         <v>1.85</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,22 +3756,22 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.48</v>
+        <v>9</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>5.25</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>1.92</v>
+        <v>8</v>
       </c>
       <c r="T17" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="U17" t="n">
-        <v>5.98</v>
+        <v>1.67</v>
       </c>
       <c r="V17" t="n">
         <v>1.26</v>
@@ -3780,109 +3780,109 @@
         <v>3.28</v>
       </c>
       <c r="X17" t="n">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AB17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AY17" t="n">
         <v>1.01</v>
       </c>
-      <c r="AC17" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="AJ17" t="n">
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.2</v>
       </c>
       <c r="BC17" t="n">
         <v>1.85</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3977,37 +3977,37 @@
         <v>2.03</v>
       </c>
       <c r="X18" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="Y18" t="n">
         <v>1.16</v>
       </c>
       <c r="Z18" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AA18" t="n">
         <v>1.03</v>
       </c>
       <c r="AB18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1.11</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.06</v>
       </c>
       <c r="AI18" t="n">
         <v>17</v>
@@ -4016,49 +4016,49 @@
         <v>1.02</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AM18" t="n">
         <v>1.37</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
@@ -4070,13 +4070,13 @@
         <v>1.43</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="BD18" t="n">
         <v>2.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="BF18" t="n">
         <v>1.05</v>
@@ -4741,112 +4741,112 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.3</v>
+        <v>3.82</v>
       </c>
       <c r="Q22" t="n">
         <v>2.55</v>
       </c>
       <c r="R22" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="S22" t="n">
-        <v>4.74</v>
+        <v>5.47</v>
       </c>
       <c r="T22" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="U22" t="n">
-        <v>3.42</v>
+        <v>2.99</v>
       </c>
       <c r="V22" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="W22" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="X22" t="n">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA22" t="n">
         <v>1.02</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AE22" t="n">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AG22" t="n">
-        <v>8.1</v>
+        <v>7.1</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AI22" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AJ22" t="n">
         <v>1.01</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22" t="n">
         <v>0</v>
@@ -4855,19 +4855,19 @@
         <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="BC22" t="n">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="BD22" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5732,16 +5732,16 @@
         <v>4.6</v>
       </c>
       <c r="R27" t="n">
-        <v>6.22</v>
+        <v>5.75</v>
       </c>
       <c r="S27" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="T27" t="n">
         <v>2.47</v>
       </c>
       <c r="U27" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="V27" t="n">
         <v>1.24</v>
@@ -5750,13 +5750,13 @@
         <v>3.44</v>
       </c>
       <c r="X27" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="Y27" t="n">
         <v>1.56</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.3</v>
+        <v>4.75</v>
       </c>
       <c r="AA27" t="n">
         <v>1.1</v>
@@ -5774,13 +5774,13 @@
         <v>1.57</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.35</v>
+        <v>2.26</v>
       </c>
       <c r="AG27" t="n">
         <v>2.08</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AI27" t="n">
         <v>3.45</v>
@@ -5792,7 +5792,7 @@
         <v>1.72</v>
       </c>
       <c r="AL27" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AM27" t="n">
         <v>1.15</v>
@@ -5810,7 +5810,7 @@
         <v>1.59</v>
       </c>
       <c r="AR27" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="AS27" t="n">
         <v>2.56</v>
@@ -5840,10 +5840,10 @@
         <v>7.6</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="BD27" t="n">
         <v>4.95</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="R28" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="S28" t="n">
-        <v>2.9</v>
+        <v>2.38</v>
       </c>
       <c r="T28" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="U28" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG28" t="n">
         <v>3</v>
       </c>
-      <c r="V28" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W28" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE28" t="n">
+      <c r="AH28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK28" t="n">
         <v>1.7</v>
       </c>
-      <c r="AF28" t="n">
+      <c r="AL28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC28" t="n">
         <v>2.05</v>
       </c>
-      <c r="AG28" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>1.91</v>
-      </c>
       <c r="BD28" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R29" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="S29" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="T29" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="U29" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="V29" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="W29" t="n">
-        <v>2.78</v>
+        <v>3.02</v>
       </c>
       <c r="X29" t="n">
-        <v>2.74</v>
+        <v>2.44</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="Z29" t="n">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA29" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB29" t="n">
         <v>1.04</v>
       </c>
-      <c r="AB29" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AC29" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AI29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AM29" t="n">
         <v>1.3</v>
       </c>
       <c r="AN29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF29" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>1.17</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,79 +6317,79 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R30" t="n">
-        <v>4</v>
+        <v>1.91</v>
       </c>
       <c r="S30" t="n">
-        <v>2.38</v>
+        <v>4.2</v>
       </c>
       <c r="T30" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U30" t="n">
-        <v>4.62</v>
+        <v>2.4</v>
       </c>
       <c r="V30" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W30" t="n">
-        <v>2.91</v>
+        <v>2.78</v>
       </c>
       <c r="X30" t="n">
-        <v>2.59</v>
+        <v>2.74</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="Z30" t="n">
-        <v>6.05</v>
+        <v>6.75</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AB30" t="n">
         <v>1.05</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF30" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG30" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AI30" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL30" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.91</v>
+        <v>1.22</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6401,7 +6401,7 @@
         <v>1.51</v>
       </c>
       <c r="AR30" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AS30" t="n">
         <v>2.37</v>
@@ -6413,10 +6413,10 @@
         <v>3.28</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AX30" t="n">
         <v>1.5</v>
@@ -6425,25 +6425,25 @@
         <v>1.26</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.88</v>
+        <v>4.11</v>
       </c>
       <c r="BA30" t="n">
-        <v>2.48</v>
+        <v>1.4</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U31" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W31" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X31" t="n">
         <v>2.82</v>
       </c>
-      <c r="Q31" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="R31" t="n">
+      <c r="Y31" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK31" t="n">
         <v>2.32</v>
       </c>
-      <c r="S31" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T31" t="n">
+      <c r="AL31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC31" t="n">
         <v>2.3</v>
       </c>
-      <c r="U31" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W31" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="X31" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>1.85</v>
-      </c>
       <c r="BD31" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.95</v>
+        <v>2.82</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="R32" t="n">
-        <v>3.3</v>
+        <v>2.32</v>
       </c>
       <c r="S32" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="T32" t="n">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="U32" t="n">
-        <v>4.49</v>
+        <v>2.96</v>
       </c>
       <c r="V32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W32" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="X32" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AY32" t="n">
         <v>1.39</v>
       </c>
-      <c r="W32" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AH32" t="n">
+      <c r="AZ32" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BF32" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>1.15</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.35</v>
+        <v>4.85</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="R33" t="n">
-        <v>7.62</v>
+        <v>1.7</v>
       </c>
       <c r="S33" t="n">
-        <v>1.89</v>
+        <v>5.25</v>
       </c>
       <c r="T33" t="n">
-        <v>2.18</v>
+        <v>1.99</v>
       </c>
       <c r="U33" t="n">
-        <v>8.449999999999999</v>
+        <v>2.33</v>
       </c>
       <c r="V33" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="W33" t="n">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="X33" t="n">
-        <v>2.82</v>
+        <v>3.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="Z33" t="n">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="AA33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AJ33" t="n">
         <v>1.04</v>
       </c>
-      <c r="AB33" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AK33" t="n">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AN33" t="n">
-        <v>2.84</v>
+        <v>1.11</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.9</v>
+        <v>2.31</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.33</v>
+        <v>2.58</v>
       </c>
       <c r="AT33" t="n">
-        <v>3.14</v>
+        <v>3.39</v>
       </c>
       <c r="AU33" t="n">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="AV33" t="n">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.29</v>
+        <v>2.46</v>
       </c>
       <c r="BA33" t="n">
-        <v>4.71</v>
+        <v>1.82</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="BD33" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>4.85</v>
+        <v>1.95</v>
       </c>
       <c r="Q34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R34" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U34" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W34" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="X34" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG34" t="n">
         <v>3.4</v>
       </c>
-      <c r="R34" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="S34" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="T34" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="U34" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W34" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="X34" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>3.96</v>
-      </c>
       <c r="AH34" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AI34" t="n">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AK34" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.58</v>
+        <v>2.79</v>
       </c>
       <c r="AT34" t="n">
-        <v>3.39</v>
+        <v>3.94</v>
       </c>
       <c r="AU34" t="n">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="AV34" t="n">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AZ34" t="n">
-        <v>2.46</v>
+        <v>1.49</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.82</v>
+        <v>2.81</v>
       </c>
       <c r="BB34" t="n">
         <v>1.25</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="R36" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="S36" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="T36" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="U36" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="V36" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="W36" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="X36" t="n">
-        <v>4.05</v>
+        <v>3.38</v>
       </c>
       <c r="Y36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AH36" t="n">
         <v>1.17</v>
       </c>
-      <c r="Z36" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AI36" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AM36" t="n">
         <v>1.36</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.6</v>
+        <v>1.29</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AR36" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="AT36" t="n">
-        <v>4.17</v>
+        <v>3.4</v>
       </c>
       <c r="AU36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BC36" t="n">
         <v>2.56</v>
       </c>
-      <c r="AV36" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>3</v>
-      </c>
       <c r="BD36" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,79 +7696,79 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>5.75</v>
+        <v>2.25</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.65</v>
+        <v>2.8</v>
       </c>
       <c r="R37" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="S37" t="n">
-        <v>8.050000000000001</v>
+        <v>2.9</v>
       </c>
       <c r="T37" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="U37" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W37" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="X37" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD37" t="n">
         <v>2.1</v>
       </c>
-      <c r="V37" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="W37" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="X37" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AE37" t="n">
-        <v>2.37</v>
+        <v>3.1</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AG37" t="n">
-        <v>4.65</v>
+        <v>6.25</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AI37" t="n">
-        <v>9.1</v>
+        <v>10.5</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
@@ -7777,52 +7777,52 @@
         <v>1.39</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="AT37" t="n">
-        <v>4.12</v>
+        <v>4.17</v>
       </c>
       <c r="AU37" t="n">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="AV37" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AW37" t="n">
         <v>1.6</v>
       </c>
       <c r="AX37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BE37" t="n">
         <v>1.33</v>
       </c>
-      <c r="AY37" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>1.4</v>
-      </c>
       <c r="BF37" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="R38" t="n">
-        <v>2.1</v>
+        <v>4.05</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="T38" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="U38" t="n">
-        <v>2.7</v>
+        <v>5.1</v>
       </c>
       <c r="V38" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="W38" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="X38" t="n">
-        <v>3.38</v>
+        <v>3.9</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z38" t="n">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA38" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AC38" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="BB38" t="n">
         <v>1.44</v>
       </c>
-      <c r="AD38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM38" t="n">
+      <c r="BC38" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BE38" t="n">
         <v>1.36</v>
       </c>
-      <c r="AN38" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BE38" t="n">
-        <v>1.42</v>
-      </c>
       <c r="BF38" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S39" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W39" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="X39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AV39" t="n">
         <v>2</v>
       </c>
-      <c r="Q39" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="R39" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="S39" t="n">
+      <c r="AW39" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BD39" t="n">
         <v>2.8</v>
       </c>
-      <c r="T39" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U39" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="W39" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="X39" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>6</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AM39" t="n">
+      <c r="BE39" t="n">
         <v>1.4</v>
       </c>
-      <c r="AN39" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>1.36</v>
-      </c>
       <c r="BF39" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8287,16 +8287,16 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Q40" t="n">
-        <v>6.5</v>
+        <v>6.58</v>
       </c>
       <c r="R40" t="n">
         <v>1.22</v>
       </c>
       <c r="S40" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="T40" t="n">
         <v>2.88</v>
@@ -8305,55 +8305,55 @@
         <v>1.57</v>
       </c>
       <c r="V40" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="W40" t="n">
         <v>4.2</v>
       </c>
       <c r="X40" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AB40" t="n">
         <v>1.01</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AD40" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AF40" t="n">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AI40" t="n">
-        <v>2.69</v>
+        <v>2.85</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AL40" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AM40" t="n">
         <v>1.11</v>
@@ -8365,40 +8365,40 @@
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AR40" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AS40" t="n">
         <v>2.27</v>
       </c>
       <c r="AT40" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="AU40" t="n">
-        <v>3.39</v>
+        <v>3.5</v>
       </c>
       <c r="AV40" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AX40" t="n">
         <v>1.61</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AZ40" t="n">
-        <v>4.5</v>
+        <v>4.05</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="BB40" t="n">
         <v>1.11</v>
@@ -8413,7 +8413,7 @@
         <v>2.2</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8484,16 +8484,16 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.88</v>
+        <v>3.95</v>
       </c>
       <c r="R41" t="n">
-        <v>5.27</v>
+        <v>5.1</v>
       </c>
       <c r="S41" t="n">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="T41" t="n">
         <v>2.2</v>
@@ -8502,49 +8502,49 @@
         <v>5.25</v>
       </c>
       <c r="V41" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W41" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="X41" t="n">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="Z41" t="n">
         <v>6.5</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AD41" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG41" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="AH41" t="n">
         <v>1.34</v>
       </c>
       <c r="AI41" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AK41" t="n">
         <v>1.85</v>
@@ -8553,64 +8553,64 @@
         <v>1.85</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AN41" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AS41" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="AT41" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AU41" t="n">
-        <v>3.55</v>
+        <v>4.15</v>
       </c>
       <c r="AV41" t="n">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="BA41" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BC41" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="BD41" t="n">
-        <v>4.05</v>
+        <v>3.5</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8681,67 +8681,67 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R42" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
       </c>
       <c r="T42" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="U42" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="V42" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W42" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="X42" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA42" t="n">
         <v>1.2</v>
       </c>
-      <c r="W42" t="n">
-        <v>4</v>
-      </c>
-      <c r="X42" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AB42" t="n">
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AD42" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.59</v>
+        <v>2.37</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="AI42" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AK42" t="n">
         <v>1.36</v>
@@ -8750,7 +8750,7 @@
         <v>2.75</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AN42" t="n">
         <v>1.36</v>
@@ -8798,16 +8798,16 @@
         <v>1.12</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="BD42" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BE42" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.25</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>8.31</v>
+        <v>2.74</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="U2" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="V2" t="n">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
       <c r="W2" t="n">
-        <v>3.15</v>
+        <v>2.44</v>
       </c>
       <c r="X2" t="n">
-        <v>2.53</v>
+        <v>3.34</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="Z2" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.75</v>
+        <v>4.4</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="AI2" t="n">
-        <v>4.8</v>
+        <v>9.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AK2" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL2" t="n">
         <v>1.75</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AN2" t="n">
-        <v>3.4</v>
+        <v>1.44</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.2</v>
+        <v>3.66</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.72</v>
+        <v>5.57</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.45</v>
+        <v>2.23</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.29</v>
+        <v>1.96</v>
       </c>
       <c r="BA2" t="n">
-        <v>4</v>
+        <v>2.42</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="BC2" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="R3" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q3" t="n">
-        <v>3</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.95</v>
-      </c>
       <c r="U3" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="V3" t="n">
-        <v>1.49</v>
+        <v>1.31</v>
       </c>
       <c r="W3" t="n">
-        <v>2.44</v>
+        <v>3.15</v>
       </c>
       <c r="X3" t="n">
-        <v>3.34</v>
+        <v>2.53</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AC3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH3" t="n">
         <v>1.4</v>
       </c>
-      <c r="AD3" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AI3" t="n">
-        <v>9.5</v>
+        <v>4.8</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL3" t="n">
         <v>1.75</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.44</v>
+        <v>3.4</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.66</v>
+        <v>3.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.57</v>
+        <v>4.72</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="AX3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AY3" t="n">
         <v>1.2</v>
       </c>
-      <c r="AY3" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>1.96</v>
+        <v>1.29</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.42</v>
+        <v>4</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="BD3" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.57</v>
+        <v>2.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="S4" t="n">
-        <v>3.28</v>
+        <v>2.63</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="W4" t="n">
-        <v>2.77</v>
+        <v>2.34</v>
       </c>
       <c r="X4" t="n">
-        <v>2.65</v>
+        <v>3.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="Z4" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AB4" t="n">
         <v>1.06</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.25</v>
+        <v>2.74</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.99</v>
+        <v>2.4</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.8</v>
+        <v>1.54</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.4</v>
+        <v>4.75</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AI4" t="n">
-        <v>6.5</v>
+        <v>9.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AL4" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="AN4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BE4" t="n">
         <v>1.44</v>
       </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.65</v>
-      </c>
       <c r="BF4" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,103 +1392,103 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R5" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="S5" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="U5" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="V5" t="n">
         <v>1.43</v>
       </c>
       <c r="W5" t="n">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="X5" t="n">
-        <v>3.4</v>
+        <v>3.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AB5" t="n">
         <v>1.06</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="AG5" t="n">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AI5" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.97</v>
+        <v>2.36</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.89</v>
+        <v>4.84</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AW5" t="n">
         <v>1.49</v>
@@ -1497,28 +1497,28 @@
         <v>1.25</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,37 +1589,37 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.15</v>
+        <v>2.57</v>
       </c>
       <c r="Q6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U6" t="n">
         <v>3.2</v>
       </c>
-      <c r="R6" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3.7</v>
-      </c>
       <c r="V6" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="W6" t="n">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="X6" t="n">
-        <v>3.04</v>
+        <v>2.65</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AA6" t="n">
         <v>1.03</v>
@@ -1628,94 +1628,94 @@
         <v>1.06</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AE6" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR6" t="n">
         <v>2.1</v>
       </c>
-      <c r="AF6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN6" t="n">
+      <c r="AS6" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE6" t="n">
         <v>1.65</v>
       </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.57</v>
-      </c>
       <c r="BF6" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.77</v>
+        <v>1.73</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.65</v>
+        <v>3.3</v>
       </c>
       <c r="R8" t="n">
-        <v>2.55</v>
+        <v>4.93</v>
       </c>
       <c r="S8" t="n">
-        <v>4.04</v>
+        <v>2.25</v>
       </c>
       <c r="T8" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="U8" t="n">
-        <v>3.44</v>
+        <v>5</v>
       </c>
       <c r="V8" t="n">
-        <v>1.64</v>
+        <v>1.41</v>
       </c>
       <c r="W8" t="n">
-        <v>2.1</v>
+        <v>2.69</v>
       </c>
       <c r="X8" t="n">
-        <v>3.78</v>
+        <v>3.04</v>
       </c>
       <c r="Y8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AY8" t="n">
         <v>1.19</v>
       </c>
-      <c r="Z8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>6.74</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.86</v>
+        <v>2.3</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.73</v>
+        <v>2.77</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.3</v>
+        <v>2.65</v>
       </c>
       <c r="R9" t="n">
-        <v>4.93</v>
+        <v>2.55</v>
       </c>
       <c r="S9" t="n">
-        <v>2.25</v>
+        <v>4.04</v>
       </c>
       <c r="T9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>2.15</v>
       </c>
-      <c r="U9" t="n">
-        <v>5</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="X9" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Y9" t="n">
+      <c r="AR9" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BE9" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.6</v>
-      </c>
       <c r="BF9" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.6</v>
+        <v>5.82</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3</v>
+        <v>1.48</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="T12" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="U12" t="n">
-        <v>2.78</v>
+        <v>1.95</v>
       </c>
       <c r="V12" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="W12" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="X12" t="n">
-        <v>2.08</v>
+        <v>2.39</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.45</v>
+        <v>5.45</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AB12" t="n">
         <v>1.02</v>
       </c>
       <c r="AC12" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN12" t="n">
         <v>1.13</v>
       </c>
-      <c r="AD12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AI12" t="n">
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AZ12" t="n">
         <v>3.4</v>
       </c>
-      <c r="AJ12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>5.86</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.92</v>
-      </c>
       <c r="BA12" t="n">
-        <v>2.11</v>
+        <v>1.26</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="BD12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>5.82</v>
+        <v>2.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="R13" t="n">
-        <v>1.48</v>
+        <v>2.3</v>
       </c>
       <c r="S13" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="U13" t="n">
-        <v>1.95</v>
+        <v>2.78</v>
       </c>
       <c r="V13" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="W13" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="X13" t="n">
-        <v>2.39</v>
+        <v>2.08</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.45</v>
+        <v>4.45</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AB13" t="n">
         <v>1.02</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AD13" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="AH13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK13" t="n">
         <v>1.4</v>
       </c>
-      <c r="AI13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AL13" t="n">
-        <v>1.95</v>
+        <v>2.8</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AN13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BB13" t="n">
         <v>1.13</v>
       </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.2</v>
-      </c>
       <c r="BC13" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="BD13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,22 +3362,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.48</v>
+        <v>9</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>5.25</v>
+        <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>1.92</v>
+        <v>8</v>
       </c>
       <c r="T15" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="U15" t="n">
-        <v>5.98</v>
+        <v>1.67</v>
       </c>
       <c r="V15" t="n">
         <v>1.26</v>
@@ -3386,109 +3386,109 @@
         <v>3.28</v>
       </c>
       <c r="X15" t="n">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AB15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AY15" t="n">
         <v>1.01</v>
       </c>
-      <c r="AC15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="AJ15" t="n">
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.2</v>
       </c>
       <c r="BC15" t="n">
         <v>1.85</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,22 +3756,22 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>9</v>
+        <v>1.48</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>5.25</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>1.92</v>
       </c>
       <c r="T17" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="U17" t="n">
-        <v>1.67</v>
+        <v>5.98</v>
       </c>
       <c r="V17" t="n">
         <v>1.26</v>
@@ -3780,109 +3780,109 @@
         <v>3.28</v>
       </c>
       <c r="X17" t="n">
-        <v>2.27</v>
+        <v>2.36</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AI17" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BA17" t="n">
         <v>4.2</v>
       </c>
-      <c r="AJ17" t="n">
+      <c r="BB17" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.18</v>
       </c>
       <c r="BC17" t="n">
         <v>1.85</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U29" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q29" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U29" t="n">
-        <v>3</v>
-      </c>
       <c r="V29" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="W29" t="n">
-        <v>3.02</v>
+        <v>2.78</v>
       </c>
       <c r="X29" t="n">
-        <v>2.44</v>
+        <v>2.74</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="Z29" t="n">
-        <v>5.5</v>
+        <v>6.75</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AD29" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AI29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AM29" t="n">
         <v>1.3</v>
       </c>
       <c r="AN29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AX29" t="n">
         <v>1.5</v>
       </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AY29" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.96</v>
+        <v>4.11</v>
       </c>
       <c r="BA29" t="n">
-        <v>2.34</v>
+        <v>1.4</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R30" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="S30" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="T30" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="U30" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="V30" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="W30" t="n">
-        <v>2.78</v>
+        <v>3.02</v>
       </c>
       <c r="X30" t="n">
-        <v>2.74</v>
+        <v>2.44</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="Z30" t="n">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB30" t="n">
         <v>1.04</v>
       </c>
-      <c r="AB30" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AC30" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG30" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AI30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AM30" t="n">
         <v>1.3</v>
       </c>
       <c r="AN30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF30" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>1.17</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.35</v>
+        <v>5.9</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="R31" t="n">
-        <v>7.62</v>
+        <v>1.47</v>
       </c>
       <c r="S31" t="n">
-        <v>1.89</v>
+        <v>7.9</v>
       </c>
       <c r="T31" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="U31" t="n">
-        <v>8.449999999999999</v>
+        <v>2.13</v>
       </c>
       <c r="V31" t="n">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="W31" t="n">
-        <v>2.62</v>
+        <v>2.31</v>
       </c>
       <c r="X31" t="n">
-        <v>2.82</v>
+        <v>3.42</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="Z31" t="n">
-        <v>6.75</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.05</v>
+        <v>2.46</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.95</v>
+        <v>2.41</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AG31" t="n">
-        <v>3.5</v>
+        <v>4.55</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AI31" t="n">
-        <v>6.05</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AN31" t="n">
-        <v>2.84</v>
+        <v>1.03</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.51</v>
+        <v>1.7</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.9</v>
+        <v>2.57</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.33</v>
+        <v>2.85</v>
       </c>
       <c r="AT31" t="n">
-        <v>3.14</v>
+        <v>3.79</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.34</v>
+        <v>2.72</v>
       </c>
       <c r="AV31" t="n">
-        <v>2.4</v>
+        <v>2.03</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.29</v>
+        <v>2.39</v>
       </c>
       <c r="BA31" t="n">
-        <v>4.71</v>
+        <v>1.85</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.5</v>
+        <v>3.02</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>4.85</v>
+        <v>1.95</v>
       </c>
       <c r="Q33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U33" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W33" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="X33" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG33" t="n">
         <v>3.4</v>
       </c>
-      <c r="R33" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="S33" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="T33" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="U33" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W33" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="X33" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>3.96</v>
-      </c>
       <c r="AH33" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AI33" t="n">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AK33" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.58</v>
+        <v>2.79</v>
       </c>
       <c r="AT33" t="n">
-        <v>3.39</v>
+        <v>3.94</v>
       </c>
       <c r="AU33" t="n">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="AV33" t="n">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AZ33" t="n">
-        <v>2.46</v>
+        <v>1.49</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.82</v>
+        <v>2.81</v>
       </c>
       <c r="BB33" t="n">
         <v>1.25</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="BD33" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.95</v>
+        <v>4.85</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="R34" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="S34" t="n">
-        <v>2.5</v>
+        <v>5.25</v>
       </c>
       <c r="T34" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="U34" t="n">
-        <v>4.49</v>
+        <v>2.33</v>
       </c>
       <c r="V34" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="W34" t="n">
-        <v>2.69</v>
+        <v>2.47</v>
       </c>
       <c r="X34" t="n">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z34" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AA34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AJ34" t="n">
         <v>1.04</v>
       </c>
-      <c r="AB34" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AH34" t="n">
+      <c r="AK34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AY34" t="n">
         <v>1.25</v>
       </c>
-      <c r="AI34" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AZ34" t="n">
-        <v>1.49</v>
+        <v>2.46</v>
       </c>
       <c r="BA34" t="n">
-        <v>2.81</v>
+        <v>1.82</v>
       </c>
       <c r="BB34" t="n">
         <v>1.25</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.19</v>
+        <v>2.28</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>5.9</v>
+        <v>1.35</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="R35" t="n">
-        <v>1.47</v>
+        <v>7.62</v>
       </c>
       <c r="S35" t="n">
-        <v>7.9</v>
+        <v>1.89</v>
       </c>
       <c r="T35" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="U35" t="n">
-        <v>2.13</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="V35" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="W35" t="n">
-        <v>2.31</v>
+        <v>2.62</v>
       </c>
       <c r="X35" t="n">
-        <v>3.42</v>
+        <v>2.82</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="Z35" t="n">
-        <v>9.300000000000001</v>
+        <v>6.75</v>
       </c>
       <c r="AA35" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.46</v>
+        <v>3.05</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.41</v>
+        <v>1.95</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AG35" t="n">
-        <v>4.55</v>
+        <v>3.5</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AI35" t="n">
-        <v>9.300000000000001</v>
+        <v>6.05</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="AM35" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="BB35" t="n">
         <v>1.22</v>
       </c>
-      <c r="AN35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>1.31</v>
-      </c>
       <c r="BC35" t="n">
-        <v>2.53</v>
+        <v>2.3</v>
       </c>
       <c r="BD35" t="n">
-        <v>3.02</v>
+        <v>3.5</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,43 +7499,43 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>3.2</v>
+        <v>5.75</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="R36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S36" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U36" t="n">
         <v>2.1</v>
       </c>
-      <c r="S36" t="n">
-        <v>4</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2</v>
-      </c>
-      <c r="U36" t="n">
-        <v>2.7</v>
-      </c>
       <c r="V36" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W36" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="X36" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="Y36" t="n">
         <v>1.25</v>
       </c>
       <c r="Z36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA36" t="n">
         <v>1</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AC36" t="n">
         <v>1.44</v>
@@ -7544,88 +7544,88 @@
         <v>2.5</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.65</v>
+        <v>2.37</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG36" t="n">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AI36" t="n">
-        <v>10</v>
+        <v>9.1</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AR36" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="AT36" t="n">
-        <v>3.4</v>
+        <v>4.12</v>
       </c>
       <c r="AU36" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="AV36" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AZ36" t="n">
-        <v>2.12</v>
+        <v>3.85</v>
       </c>
       <c r="BA36" t="n">
-        <v>2.08</v>
+        <v>1.41</v>
       </c>
       <c r="BB36" t="n">
         <v>1.36</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="BD36" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S38" t="n">
+        <v>4</v>
+      </c>
+      <c r="T38" t="n">
         <v>2</v>
       </c>
-      <c r="Q38" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="R38" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="S38" t="n">
+      <c r="U38" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W38" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="X38" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU38" t="n">
         <v>2.8</v>
       </c>
-      <c r="T38" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U38" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="V38" t="n">
+      <c r="AV38" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AW38" t="n">
         <v>1.62</v>
       </c>
-      <c r="W38" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="X38" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AF38" t="n">
+      <c r="AX38" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BB38" t="n">
         <v>1.36</v>
       </c>
-      <c r="AG38" t="n">
-        <v>6</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>1.44</v>
-      </c>
       <c r="BC38" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BD38" t="n">
         <v>2.9</v>
       </c>
-      <c r="BD38" t="n">
-        <v>2.63</v>
-      </c>
       <c r="BE38" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>5.75</v>
+        <v>2</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.65</v>
+        <v>2.92</v>
       </c>
       <c r="R39" t="n">
-        <v>1.5</v>
+        <v>4.05</v>
       </c>
       <c r="S39" t="n">
-        <v>8.050000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="T39" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="U39" t="n">
-        <v>2.1</v>
+        <v>5.1</v>
       </c>
       <c r="V39" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="W39" t="n">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="X39" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z39" t="n">
-        <v>10</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA39" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AC39" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="BB39" t="n">
         <v>1.44</v>
       </c>
-      <c r="AD39" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BB39" t="n">
+      <c r="BC39" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BE39" t="n">
         <v>1.36</v>
       </c>
-      <c r="BC39" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>1.4</v>
-      </c>
       <c r="BF39" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>

--- a/jogos_2026-05-05.xlsx
+++ b/jogos_2026-05-05.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="R2" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T2" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q2" t="n">
-        <v>3</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.95</v>
-      </c>
       <c r="U2" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="V2" t="n">
-        <v>1.49</v>
+        <v>1.31</v>
       </c>
       <c r="W2" t="n">
-        <v>2.44</v>
+        <v>3.15</v>
       </c>
       <c r="X2" t="n">
-        <v>3.34</v>
+        <v>2.53</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AC2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH2" t="n">
         <v>1.4</v>
       </c>
-      <c r="AD2" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AI2" t="n">
-        <v>9.5</v>
+        <v>4.8</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL2" t="n">
         <v>1.75</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.44</v>
+        <v>3.4</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.66</v>
+        <v>3.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.57</v>
+        <v>4.72</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="AX2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AY2" t="n">
         <v>1.2</v>
       </c>
-      <c r="AY2" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AZ2" t="n">
-        <v>1.96</v>
+        <v>1.29</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.42</v>
+        <v>4</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="BD2" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.25</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>8.31</v>
+        <v>2.74</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="U3" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="V3" t="n">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
       <c r="W3" t="n">
-        <v>3.15</v>
+        <v>2.44</v>
       </c>
       <c r="X3" t="n">
-        <v>2.53</v>
+        <v>3.34</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="Z3" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.75</v>
+        <v>4.4</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="AI3" t="n">
-        <v>4.8</v>
+        <v>9.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AK3" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL3" t="n">
         <v>1.75</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AN3" t="n">
-        <v>3.4</v>
+        <v>1.44</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.2</v>
+        <v>3.66</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.72</v>
+        <v>5.57</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.45</v>
+        <v>2.23</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.29</v>
+        <v>1.96</v>
       </c>
       <c r="BA3" t="n">
-        <v>4</v>
+        <v>2.42</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="BC3" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.73</v>
+        <v>2.77</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.3</v>
+        <v>2.65</v>
       </c>
       <c r="R8" t="n">
-        <v>4.93</v>
+        <v>2.55</v>
       </c>
       <c r="S8" t="n">
-        <v>2.25</v>
+        <v>4.04</v>
       </c>
       <c r="T8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AQ8" t="n">
         <v>2.15</v>
       </c>
-      <c r="U8" t="n">
-        <v>5</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="X8" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Y8" t="n">
+      <c r="AR8" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BE8" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.6</v>
-      </c>
       <c r="BF8" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.77</v>
+        <v>1.73</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.65</v>
+        <v>3.3</v>
       </c>
       <c r="R9" t="n">
-        <v>2.55</v>
+        <v>4.93</v>
       </c>
       <c r="S9" t="n">
-        <v>4.04</v>
+        <v>2.25</v>
       </c>
       <c r="T9" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="U9" t="n">
-        <v>3.44</v>
+        <v>5</v>
       </c>
       <c r="V9" t="n">
-        <v>1.64</v>
+        <v>1.41</v>
       </c>
       <c r="W9" t="n">
-        <v>2.1</v>
+        <v>2.69</v>
       </c>
       <c r="X9" t="n">
-        <v>3.78</v>
+        <v>3.04</v>
       </c>
       <c r="Y9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AY9" t="n">
         <v>1.19</v>
       </c>
-      <c r="Z9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>6.74</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.86</v>
+        <v>2.3</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,79 +3165,79 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>3.3</v>
+        <v>9</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>4.68</v>
+        <v>8</v>
       </c>
       <c r="T14" t="n">
-        <v>1.76</v>
+        <v>2.6</v>
       </c>
       <c r="U14" t="n">
-        <v>3.06</v>
+        <v>1.67</v>
       </c>
       <c r="V14" t="n">
-        <v>1.63</v>
+        <v>1.26</v>
       </c>
       <c r="W14" t="n">
-        <v>2.11</v>
+        <v>3.28</v>
       </c>
       <c r="X14" t="n">
-        <v>3.9</v>
+        <v>2.27</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.18</v>
+        <v>1.52</v>
       </c>
       <c r="Z14" t="n">
-        <v>9.6</v>
+        <v>5.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.17</v>
+        <v>4.6</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.78</v>
+        <v>1.53</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.34</v>
+        <v>2.3</v>
       </c>
       <c r="AG14" t="n">
-        <v>5.75</v>
+        <v>2.4</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.07</v>
+        <v>1.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>13</v>
+        <v>4.2</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.27</v>
+        <v>1.85</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.54</v>
+        <v>1.83</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.23</v>
+        <v>1.06</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.92</v>
+        <v>1.85</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.6</v>
+        <v>4.33</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.32</v>
+        <v>1.85</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,22 +3362,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>9</v>
+        <v>1.48</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3</v>
+        <v>5.25</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>1.92</v>
       </c>
       <c r="T15" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="U15" t="n">
-        <v>1.67</v>
+        <v>5.98</v>
       </c>
       <c r="V15" t="n">
         <v>1.26</v>
@@ -3386,109 +3386,109 @@
         <v>3.28</v>
       </c>
       <c r="X15" t="n">
-        <v>2.27</v>
+        <v>2.36</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AI15" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BA15" t="n">
         <v>4.2</v>
       </c>
-      <c r="AJ15" t="n">
+      <c r="BB15" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.18</v>
       </c>
       <c r="BC15" t="n">
         <v>1.85</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.07</v>
+        <v>2.8</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="S16" t="n">
-        <v>3.1</v>
+        <v>4.68</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="U16" t="n">
-        <v>3.35</v>
+        <v>3.06</v>
       </c>
       <c r="V16" t="n">
-        <v>1.46</v>
+        <v>1.63</v>
       </c>
       <c r="W16" t="n">
-        <v>2.5</v>
+        <v>2.11</v>
       </c>
       <c r="X16" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>8.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AA16" t="n">
         <v>1.01</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.88</v>
+        <v>2.17</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.2</v>
+        <v>2.78</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.66</v>
+        <v>1.34</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.88</v>
+        <v>5.75</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="AI16" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.8</v>
+        <v>2.27</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.91</v>
+        <v>1.54</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AN16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
         <v>1.4</v>
       </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.3</v>
-      </c>
       <c r="BC16" t="n">
-        <v>2.31</v>
+        <v>2.92</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.48</v>
+        <v>2.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.2</v>
+        <v>3.07</v>
       </c>
       <c r="R17" t="n">
-        <v>5.25</v>
+        <v>2.7</v>
       </c>
       <c r="S17" t="n">
-        <v>1.92</v>
+        <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>5.98</v>
+        <v>3.35</v>
       </c>
       <c r="V17" t="n">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="W17" t="n">
-        <v>3.28</v>
+        <v>2.5</v>
       </c>
       <c r="X17" t="n">
-        <v>2.36</v>
+        <v>3.1</v>
       </c>
       <c r="Y17" t="n">
-        <